--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1168">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES ORIENTAUX</t>
   </si>
@@ -785,6 +785,7 @@
         <sz val="9"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">王者</t>
     </r>
@@ -2314,34 +2315,6 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe hindou fondateur de l'école Dvaita (dualiste) du Vedanta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1288 – 1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GERSONIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gersonide"  title=" Wikipedia"&gt;GERSONIDE&lt;/a&gt; de son nom complet Lévi ben Gershom, est un des grands penseurs juifs du Moyen Âge, actif dans le sud de la France. Mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe, il est souvent considéré comme l’un des plus  &lt;a href="https://www.youtube.com/watch?v=zFnektKxZok" title="Levi ben Gerson (gersonides)  par Math Mystique"&gt;grands esprits juifs &lt;/a&gt; entre Maïmonide et la modernité. Il écrit en hébreu et en arabe, mêlant étude des textes religieux, science et philosophie, dans un esprit très critique et original. &lt;/p&gt; &lt;p&gt; Sa philosophie se veut un rapprochement systématique entre la pensée d’Aristote (via Averroès) et la pensée biblique‑talmudique. Dans son œuvre majeure, Milhamot Ha‑Shem (Les Guerres du Seigneur), il cherche à montrer que la raison et la révélation peuvent coexister et s’accorder sur la plupart des vérités importantes. Il adopte une cosmologie largement aristotélicienne tout en restant fidèle à un cadre théiste juif, en méditant par exemple  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1954_num_28_4_2056" title="les idées philosophiques de GERSONIDE par Persée"&gt;la création, la nature de Dieu &lt;/a&gt; et l’ordre du monde. &lt;/p&gt; &lt;p&gt; Parmi ses thèses les plus marquantes figurent sa conception de l’âme et de la prophétie : il soutient que l’âme humaine peut s’identifier à une intelligence universelle ou “raison active” qui unit l’homme à Dieu, et que l’immortalité de l’âme passe par l’acquisition de connaissances rationnelles adéquates. Il défend aussi une vision particulière de la connaissance divine : Dieu connaît toutes les possibilités humaines, mais ne prédétermine pas chaque choix, ce qui laisse une véritable place au libre arbitre humain, en rupture avec une vision toute‑puissante et strictement déterministe. &lt;/p&gt; &lt;p&gt; Il  est remarquable par son a href="https://www.youtube.com/watch?v=sq1YiI6BGVQ" title="medieval  philosopher GERSONIDE par Stay curious radio"&gt;rigoureux rationalisme &lt;/a&gt; et son goût pour les méthodes analytiques proches de la scolastique latine. Il utilise les mathématiques et l’astronomie non seulement comme sciences, mais comme instruments pour mieux comprendre Dieu et le monde créé. Sa tentative de fonder une théologie juive stable sur des bases scientifiques et rationnelles en fait un pont entre la pensée islamique‑aristotélicienne, la scolastique chrétienne et la tradition juive médiévale. &lt;/p&gt; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B7UNjm6-H_k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gersonide par VIS PHILO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/gersonide-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Française</t>
-  </si>
-  <si>
-    <t xml:space="preserve">philosophe juif, mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe.</t>
   </si>
   <si>
     <t xml:space="preserve">1296 – 1359</t>
@@ -3882,6 +3855,7 @@
       <sz val="9"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4019,91 +3993,91 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7593,59 +7567,59 @@
         <v>710</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="330" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
-        <v>1288</v>
-      </c>
-      <c r="B85" s="7" t="s">
+    <row r="85" customFormat="false" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>1359</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="D85" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="E85" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="F85" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="G85" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="H85" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="I85" s="2"/>
+      <c r="J85" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="I85" s="7"/>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L85" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
-        <v>1296</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>1359</v>
-      </c>
-      <c r="C86" s="1" t="s">
+    <row r="86" customFormat="false" ht="296.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="7" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>1390</v>
+      </c>
+      <c r="C86" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="E86" s="2" t="s">
+      <c r="E86" s="10" t="s">
         <v>722</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -7654,65 +7628,65 @@
       <c r="G86" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H86" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="I86" s="2"/>
+      <c r="I86" s="7"/>
       <c r="J86" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L86" s="2" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="283.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="C87" s="7" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="296.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
-        <v>1325</v>
-      </c>
-      <c r="B87" s="7" t="n">
-        <v>1390</v>
-      </c>
-      <c r="C87" s="7" t="s">
+      <c r="D87" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="E87" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="F87" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="G87" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="H87" s="9" t="s">
         <v>733</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>734</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="1" t="s">
-        <v>341</v>
+        <v>433</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>629</v>
+        <v>734</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="283.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
-        <v>1332</v>
+        <v>1355</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>736</v>
@@ -7737,21 +7711,21 @@
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="1" t="s">
-        <v>433</v>
+        <v>717</v>
       </c>
       <c r="K88" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="L88" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="233.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>745</v>
@@ -7776,98 +7750,98 @@
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="1" t="s">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>480</v>
+        <v>97</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>752</v>
+        <v>471</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="233.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="n">
-        <v>1357</v>
-      </c>
-      <c r="B90" s="7" t="s">
+    <row r="90" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>1442</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="D90" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="E90" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="F90" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="G90" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="H90" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="H90" s="9" t="s">
+      <c r="J90" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="I90" s="7"/>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L90" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="n">
-        <v>1380</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>1442</v>
-      </c>
-      <c r="C91" s="1" t="s">
+    <row r="91" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="7" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B91" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="C91" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="D91" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="E91" s="11" t="s">
         <v>766</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="F91" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="G91" s="9" t="s">
         <v>768</v>
       </c>
+      <c r="H91" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="I91" s="7"/>
       <c r="J91" s="1" t="s">
-        <v>769</v>
+        <v>545</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L91" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="L91" s="2" t="s">
         <v>770</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="204.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
-        <v>1402</v>
+        <v>1440</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>772</v>
@@ -7892,10 +7866,10 @@
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="1" t="s">
-        <v>545</v>
+        <v>50</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>629</v>
+        <v>315</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>779</v>
@@ -7904,598 +7878,597 @@
         <v>780</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="204.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="338.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
         <v>1440</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="7" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="D93" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="E93" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="F93" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="G93" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="H93" s="9" t="s">
         <v>786</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>787</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>315</v>
+        <v>629</v>
       </c>
       <c r="L93" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="7" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="M93" s="2" t="s">
+      <c r="C94" s="7" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="338.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="n">
-        <v>1440</v>
-      </c>
-      <c r="B94" s="7" t="n">
-        <v>1518</v>
-      </c>
-      <c r="C94" s="7" t="s">
+      <c r="D94" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="E94" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="F94" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="G94" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="G94" s="9" t="s">
+      <c r="H94" s="9" t="s">
         <v>794</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>795</v>
       </c>
       <c r="I94" s="7"/>
       <c r="J94" s="1" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>629</v>
+        <v>138</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>529</v>
+        <v>578</v>
       </c>
       <c r="M94" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>1571</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="n">
-        <v>1472</v>
-      </c>
-      <c r="B95" s="7" t="s">
+      <c r="D95" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="E95" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="F95" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="G95" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="H95" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="G95" s="9" t="s">
+      <c r="J95" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="H95" s="9" t="s">
+      <c r="K95" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L95" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="I95" s="7"/>
-      <c r="J95" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="145.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="n">
-        <v>1502</v>
-      </c>
-      <c r="B96" s="1" t="n">
+    <row r="96" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="7" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>808</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>811</v>
+      </c>
+      <c r="I96" s="7"/>
+      <c r="J96" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="7" t="n">
         <v>1571</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="M96" s="2" t="s">
+      <c r="B97" s="7" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="241.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="n">
-        <v>1527</v>
-      </c>
-      <c r="B97" s="7" t="s">
+      <c r="C97" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="D97" s="8" t="s">
         <v>815</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="E97" s="9" t="s">
         <v>816</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="F97" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>819</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>820</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="1" t="s">
-        <v>158</v>
+        <v>341</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>578</v>
+        <v>661</v>
       </c>
       <c r="M97" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="318.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="7" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7" t="n">
-        <v>1571</v>
-      </c>
-      <c r="B98" s="7" t="s">
+      <c r="C98" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="D98" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="E98" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="E98" s="9" t="s">
+      <c r="F98" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="G98" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="H98" s="9" t="s">
         <v>827</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>828</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="1" t="s">
-        <v>341</v>
+        <v>470</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>661</v>
+        <v>186</v>
       </c>
       <c r="M98" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="7" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="318.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="n">
-        <v>1583</v>
-      </c>
-      <c r="B99" s="7" t="s">
+      <c r="C99" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="D99" s="8" t="s">
         <v>831</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="E99" s="11" t="s">
         <v>832</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="F99" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="G99" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="G99" s="9" t="s">
+      <c r="H99" s="9" t="s">
         <v>835</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>836</v>
       </c>
       <c r="I99" s="7"/>
       <c r="J99" s="1" t="s">
-        <v>470</v>
+        <v>836</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>33</v>
+        <v>837</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>186</v>
+        <v>838</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
-        <v>1599</v>
+        <v>1615</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>841</v>
+        <v>842</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>843</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="1" t="s">
-        <v>845</v>
+        <v>50</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>846</v>
+        <v>97</v>
       </c>
       <c r="L100" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="M100" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="M100" s="2" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="n">
-        <v>1615</v>
-      </c>
-      <c r="B101" s="7" t="s">
+      <c r="C101" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="D101" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="E101" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="F101" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="G101" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="G101" s="9" t="s">
+      <c r="H101" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="H101" s="9" t="s">
+      <c r="J101" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="I101" s="7"/>
-      <c r="J101" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L101" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M101" s="2" t="s">
+      <c r="M101" s="1" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="177" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="255.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
-        <v>1622</v>
-      </c>
-      <c r="B102" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>1682</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" s="18" t="s">
         <v>859</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="F102" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="G102" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="H102" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="J102" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="M102" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="J102" s="1" t="s">
+    </row>
+    <row r="103" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K103" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L102" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="255.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="n">
-        <v>1633</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>1682</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>868</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="H103" s="2" t="s">
+      <c r="L103" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="M103" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="J103" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="M103" s="2" t="s">
+    </row>
+    <row r="104" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>1763</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="n">
-        <v>1666</v>
-      </c>
-      <c r="B104" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="E104" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="F104" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="G104" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="H104" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="J104" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="L104" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="M104" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="J104" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="M104" s="2" t="s">
+    </row>
+    <row r="105" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>1759</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="n">
-        <v>1681</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>1763</v>
-      </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" s="19" t="s">
         <v>882</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="F105" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="G105" s="20" t="s">
         <v>884</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="H105" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="J105" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="J105" s="1" t="s">
-        <v>811</v>
-      </c>
       <c r="K105" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="L105" s="1" t="s">
         <v>887</v>
       </c>
+      <c r="L105" s="2" t="s">
+        <v>888</v>
+      </c>
       <c r="M105" s="2" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>1703</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="E106" s="19" t="s">
         <v>891</v>
       </c>
+      <c r="E106" s="16" t="s">
+        <v>892</v>
+      </c>
       <c r="F106" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="G106" s="20" t="s">
         <v>893</v>
       </c>
+      <c r="G106" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="H106" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>895</v>
+        <v>50</v>
       </c>
       <c r="K106" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="M106" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="L106" s="2" t="s">
+    </row>
+    <row r="107" customFormat="false" ht="427.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="n">
+        <v>1730</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>1801</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="D107" s="1" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="n">
-        <v>1703</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>1762</v>
-      </c>
-      <c r="C107" s="1" t="s">
+      <c r="E107" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="F107" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="E107" s="16" t="s">
+      <c r="G107" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="H107" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="J107" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="K107" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="L107" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="427.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
-        <v>1730</v>
+        <v>1772</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>1801</v>
+        <v>1833</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E108" s="21" t="s">
         <v>908</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -8508,42 +8481,42 @@
         <v>911</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>470</v>
+        <v>50</v>
       </c>
       <c r="K108" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="L108" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="L108" s="1" t="s">
+      <c r="M108" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="M108" s="2" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="n">
+        <v>1817</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="n">
-        <v>1772</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>1833</v>
-      </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="E109" s="16" t="s">
         <v>916</v>
       </c>
-      <c r="E109" s="21" t="s">
+      <c r="F109" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="20" t="s">
         <v>918</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>920</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>50</v>
@@ -8551,119 +8524,119 @@
       <c r="K109" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="L109" s="2" t="s">
+      <c r="L109" s="22" t="s">
+        <v>920</v>
+      </c>
+      <c r="M109" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="M109" s="2" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="n">
+        <v>1838</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>1897</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="n">
-        <v>1817</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="E110" s="16" t="s">
+      <c r="F110" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="G110" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="G110" s="20" t="s">
+      <c r="H110" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="J110" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="J110" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="K110" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="L110" s="22" t="s">
         <v>929</v>
       </c>
+      <c r="L110" s="2" t="s">
+        <v>930</v>
+      </c>
       <c r="M110" s="2" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
-        <v>1838</v>
+        <v>1847</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>1897</v>
+        <v>1901</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>937</v>
+        <v>470</v>
       </c>
       <c r="K111" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L111" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="L111" s="2" t="s">
+      <c r="M111" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="M111" s="2" t="s">
+    </row>
+    <row r="112" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="n">
-        <v>1847</v>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>1901</v>
-      </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="E112" s="12" t="s">
         <v>942</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="F112" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="G112" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="H112" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="J112" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="J112" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="K112" s="2" t="s">
-        <v>194</v>
+        <v>42</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>947</v>
@@ -8672,12 +8645,12 @@
         <v>948</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
-        <v>1850</v>
+        <v>1861</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>1911</v>
+        <v>1941</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>949</v>
@@ -8685,266 +8658,266 @@
       <c r="D113" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="20" t="s">
         <v>951</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="20" t="s">
         <v>953</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>954</v>
       </c>
       <c r="J113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K113" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="K113" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="L113" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="M113" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="M113" s="2" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="n">
-        <v>1861</v>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>1941</v>
-      </c>
       <c r="C114" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="E114" s="20" t="s">
+      <c r="F114" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="G114" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="G114" s="20" t="s">
+      <c r="H114" s="2" t="s">
         <v>962</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>963</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K114" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="n">
+        <v>1869</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="L114" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="M114" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="n">
-        <v>1863</v>
-      </c>
-      <c r="B115" s="1" t="s">
+      <c r="D115" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="D115" s="2" t="s">
+      <c r="E115" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="F115" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="G115" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="H115" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>529</v>
+        <v>971</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="311.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
-        <v>1869</v>
-      </c>
-      <c r="B116" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="E116" s="18" t="s">
         <v>975</v>
       </c>
-      <c r="E116" s="2" t="s">
+      <c r="F116" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="G116" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="H116" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="J116" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="M116" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="J116" s="1" t="s">
+    </row>
+    <row r="117" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K116" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="311.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>984</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="H117" s="2" t="s">
+      <c r="K117" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M117" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="M117" s="2" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="118" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>1872</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="1" t="n">
+        <v>1949</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="E118" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="F118" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="G118" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="H118" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="I118" s="2"/>
+      <c r="J118" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M118" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="H118" s="2" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="291.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="n">
+        <v>1877</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="J118" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="M118" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>1949</v>
-      </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="16" t="s">
         <v>998</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="F119" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="G119" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="H119" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="J119" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="K119" s="2" t="s">
-        <v>88</v>
+        <v>903</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>63</v>
+        <v>1003</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="291.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>1877</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>1004</v>
+      <c r="B120" s="1" t="n">
+        <v>1938</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>1005</v>
@@ -8952,7 +8925,7 @@
       <c r="D120" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="E120" s="16" t="s">
+      <c r="E120" s="20" t="s">
         <v>1007</v>
       </c>
       <c r="F120" s="1" t="s">
@@ -8968,333 +8941,333 @@
         <v>1011</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>912</v>
+        <v>97</v>
       </c>
       <c r="L120" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="M120" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="M120" s="2" t="s">
+    </row>
+    <row r="121" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="n">
-        <v>1877</v>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>1938</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="E121" s="20" t="s">
         <v>1015</v>
       </c>
-      <c r="E121" s="20" t="s">
+      <c r="F121" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="G121" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="H121" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="H121" s="2" t="s">
-        <v>1019</v>
-      </c>
       <c r="J121" s="1" t="s">
-        <v>1020</v>
+        <v>50</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>97</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>939</v>
+        <v>490</v>
       </c>
       <c r="M121" s="2" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="350.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="n">
-        <v>1879</v>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="C122" s="1" t="s">
+      <c r="E122" s="16" t="s">
         <v>1022</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="F122" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="E122" s="20" t="s">
+      <c r="G122" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="H122" s="2" t="s">
         <v>1025</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>1027</v>
       </c>
       <c r="J122" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>490</v>
+        <v>42</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>1026</v>
       </c>
       <c r="M122" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>1986</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="350.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="n">
-        <v>1891</v>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>1956</v>
-      </c>
-      <c r="C123" s="1" t="s">
+      <c r="E123" s="20" t="s">
         <v>1029</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="E123" s="16" t="s">
+      <c r="G123" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="H123" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>1034</v>
       </c>
       <c r="J123" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="M123" s="2" t="s">
+      <c r="E124" s="16" t="s">
         <v>1036</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>1986</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="D124" s="2" t="s">
+      <c r="F124" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="G124" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="H124" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="J124" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="K124" s="2" t="s">
         <v>1041</v>
       </c>
-      <c r="J124" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="L124" s="2" t="s">
-        <v>529</v>
+        <v>1042</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>2001</v>
+        <v>1966</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E125" s="16" t="s">
         <v>1045</v>
       </c>
+      <c r="E125" s="20" t="s">
+        <v>1046</v>
+      </c>
       <c r="F125" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>1049</v>
+        <v>470</v>
       </c>
       <c r="K125" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="M125" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="L125" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="126" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>1909</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="C126" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="F126" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="E126" s="20" t="s">
+      <c r="G126" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="H126" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="J126" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L126" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="M126" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="J126" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="M126" s="2" t="s">
+    </row>
+    <row r="127" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B127" s="1" t="n">
-        <v>1972</v>
-      </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" s="19" t="s">
         <v>1061</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="F127" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="G127" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="H127" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="J127" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="J127" s="1" t="s">
-        <v>895</v>
-      </c>
       <c r="K127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L127" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M127" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="M127" s="2" t="s">
+    </row>
+    <row r="128" customFormat="false" ht="65.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="n">
+        <v>1917</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B128" s="1" t="n">
-        <v>2008</v>
-      </c>
       <c r="C128" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="E128" s="19" t="s">
+      <c r="F128" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="H128" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="J128" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="K128" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="J128" s="1" t="s">
+      <c r="L128" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="M128" s="2" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="65.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="n">
-        <v>1917</v>
-      </c>
-      <c r="B129" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>1986</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>1053</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" s="19" t="s">
         <v>1078</v>
       </c>
       <c r="F129" s="1" t="s">
@@ -9307,62 +9280,62 @@
         <v>1081</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>769</v>
+        <v>1040</v>
       </c>
       <c r="K129" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="M129" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="L129" s="2" t="s">
+    </row>
+    <row r="130" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="M129" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="130" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="n">
-        <v>1923</v>
-      </c>
-      <c r="B130" s="1" t="n">
-        <v>1986</v>
-      </c>
-      <c r="C130" s="1" t="s">
+      <c r="E130" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="F130" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="E130" s="19" t="s">
+      <c r="G130" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="H130" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="J130" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L130" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="M130" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="J130" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="L130" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="M130" s="2" t="s">
+    </row>
+    <row r="131" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>1091</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>1961</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>1092</v>
@@ -9370,7 +9343,7 @@
       <c r="D131" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E131" s="2" t="s">
         <v>1094</v>
       </c>
       <c r="F131" s="1" t="s">
@@ -9383,19 +9356,19 @@
         <v>1097</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>1074</v>
+        <v>1098</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>42</v>
+        <v>734</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>1098</v>
+        <v>947</v>
       </c>
       <c r="M131" s="2" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="n">
         <v>1931</v>
       </c>
@@ -9408,7 +9381,7 @@
       <c r="D132" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E132" s="18" t="s">
         <v>1103</v>
       </c>
       <c r="F132" s="1" t="s">
@@ -9421,100 +9394,100 @@
         <v>1106</v>
       </c>
       <c r="J132" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="M132" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="K132" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="M132" s="2" t="s">
+    </row>
+    <row r="133" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="133" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="n">
-        <v>1931</v>
-      </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="E133" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="E133" s="18" t="s">
+      <c r="F133" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="G133" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="H133" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="J133" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="M133" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="J133" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="M133" s="2" t="s">
+    </row>
+    <row r="134" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>1116</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="n">
-        <v>1934</v>
-      </c>
-      <c r="B134" s="1" t="s">
+      <c r="D134" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="E134" s="16" t="s">
         <v>1118</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="F134" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="G134" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="H134" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="J134" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="K134" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="M134" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L134" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="M134" s="2" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="135" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>1935</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>1125</v>
@@ -9522,7 +9495,7 @@
       <c r="D135" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="E135" s="16" t="s">
+      <c r="E135" s="18" t="s">
         <v>1127</v>
       </c>
       <c r="F135" s="1" t="s">
@@ -9538,94 +9511,94 @@
         <v>1131</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>896</v>
+        <v>1073</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>847</v>
+        <v>930</v>
       </c>
       <c r="M135" s="2" t="s">
         <v>1132</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B136" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="E136" s="18" t="s">
         <v>1135</v>
       </c>
-      <c r="E136" s="18" t="s">
+      <c r="F136" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="G136" s="2" t="s">
         <v>1137</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="H136" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="H136" s="2" t="s">
+      <c r="J136" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="J136" s="1" t="s">
+      <c r="K136" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="L136" s="2" t="s">
         <v>1140</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>939</v>
       </c>
       <c r="M136" s="2" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
-        <v>1936</v>
-      </c>
-      <c r="B137" s="1" t="n">
-        <v>2005</v>
+        <v>1941</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>1142</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E137" s="18" t="s">
         <v>1144</v>
       </c>
+      <c r="E137" s="2" t="s">
+        <v>1145</v>
+      </c>
       <c r="F137" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>938</v>
+        <v>1073</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>1149</v>
+        <v>947</v>
       </c>
       <c r="M137" s="2" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>1151</v>
@@ -9652,21 +9625,21 @@
         <v>1158</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>956</v>
+        <v>1159</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="251.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1160</v>
+        <v>1124</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>1161</v>
@@ -9674,7 +9647,7 @@
       <c r="D139" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="E139" s="2" t="s">
+      <c r="E139" s="18" t="s">
         <v>1163</v>
       </c>
       <c r="F139" s="1" t="s">
@@ -9687,59 +9660,27 @@
         <v>1166</v>
       </c>
       <c r="J139" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M139" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="K139" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="L139" s="2" t="s">
-        <v>1168</v>
-      </c>
-      <c r="M139" s="2" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="251.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E140" s="18" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L140" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M140" s="2" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="140" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D140" s="1"/>
+      <c r="E140" s="1"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
@@ -9750,13 +9691,13 @@
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D143" s="1"/>
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="1"/>
     </row>
-    <row r="144" customFormat="false" ht="128.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
@@ -9768,16 +9709,11 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D146" s="1"/>
-      <c r="K146" s="1"/>
-      <c r="L146" s="1"/>
-      <c r="M146" s="1"/>
-    </row>
+    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -9818,42 +9754,40 @@
     <hyperlink ref="H77" r:id="rId32" display="https://www.laphilo.fr/pho/maimonide-mini.webp"/>
     <hyperlink ref="E82" r:id="rId33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nasir_al-Din_al-Tusi&quot;  title=&quot; Wikipedia&quot;&gt;Nasir Al-DIN Al-TUSI&lt;/a&gt;  était un &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Na%E1%B9%A3%C4%ABr-al-D%C4%ABn-%E1%B9%AC%C5%ABs%C4%AB-sciences-astrales-et-legitimation-imperiale-a-l-age.html&quot;  title=&quot;Nasir al-DinTusi par lesclesdumoyenorient&quot;&gt;polymath persan, &lt;/a&gt; considéré comme l'un des plus grands penseurs musulmans de son époque. Philosophe, mathématicien, astronome et théologien, il a produit près de 150 œuvres couvrant la logique, la métaphysique, l'éthique et les sciences exactes, s'inscrivant dans la tradition aristotélicienne et avicennisienne. &lt;/p&gt; &lt;p&gt; Sa philosophie distingue les êtres nécessaires, comme Dieu dont l'existence est inhérente, des êtres contingents dépendant d'une cause première. Dans des ouvrages comme Akhlaq-e Nasiri, il fusionne morale coranique, éthique grecque et préislamique persane, explorant les vertus, le bonheur, l'amitié et la gouvernance pour harmoniser raison, passions et sagesse. &lt;/p&gt; &lt;p&gt; Il i excelle en sciences, fondant l'observatoire de Maragha et inventant le &quot;couple de Tusi&quot;, un dispositif géométrique résolvant les mouvements planétaires sans l'équant ptolémaïque, influençant plus tard Copernic. Ses commentaires sur Avicenne, comme Sharh al-Isharat, propagent l'avicennisme iranien, mêlant chiisme, soufisme et péripatétisme. &lt;/p&gt; &lt;p&gt; Au-delà de la métaphysique divine et cosmologique, sa pensée promeut un &lt;a href=&quot;https://www.youtube.com/watch?v=M5oSOsnxzgY&quot; title=&quot;Tusi : The greastest astrnomer in history par Let’s Talk Religion &quot;&gt;progrès intellectuel &lt;/a&gt; où la raison guide l'éthique et la politique, faisant de lui un &quot;troisième maître&quot; après Aristote et Al-Farabi, avec une vision holistique unissant spiritualité et empirisme. &lt;/p&gt; &#10;&#10;"/>
     <hyperlink ref="E84" r:id="rId34" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Madhva&quot;  title=&quot; Wikipedia&quot;&gt;MADHAVACHARYA&lt;/a&gt; également connu sous le nom de Madhva ou Anandatirtha, est l'une des figures les plus importantes de la philosophie indienne, en particulier dans le cadre de la tradition Vedanta. Il est le fondateur de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Dvaita&quot; title=&quot;Dvaita par Wikipedia&quot;&gt;l'école Dvaita&lt;/a&gt; (dualiste) du Vedanta, qui s'oppose à l'Advaita (non-dualiste) de Shankara et au Vishishtadvaita (non-dualisme qualifié) de Ramanuja. &lt;/p&gt;   &lt;p&gt;Il était un érudit prolifique et un débatteur redoutable. Il voyagea à travers l'Inde pour engager des discussions philosophiques avec des érudits d'autres traditions, défendant vigoureusement sa &lt;a href=&quot;https://www.youtube.com/watch?v=4nzaIUw1Stc&amp;t=22s&quot; title=&quot;Madhavacharya par Bhakti video&quot;&gt;vision dualiste&lt;/a&gt; de la réalité.  Il est également crédité d'avoir établi le temple de Krishna à Udupi, qui reste un lieu de pèlerinage important pour ses disciples. &lt;/p&gt; &lt;p&gt; Sa philosophie, connue sous le nom de Dvaita Vedanta, repose sur l'idée que Dieu (Vishnu ou Narayana) et les âmes individuelles (jivas) sont éternellement distincts. Cette vision s'oppose à l'Advaita Vedanta de Shankara, qui enseigne que l'âme individuelle (Atman) et la réalité ultime (Brahman) sont une seule et même chose. Il affirme que Dieu, les âmes individuelles et la matière sont des entités distinctes et éternelles. Dieu est suprême et indépendant, tandis que les âmes et la matière sont dépendantes de Lui et introduit une hiérarchie parmi les âmes, certaines étant destinées à la libération (moksha) et d'autres à des renaissances continues. Cette idée est unique à sa philosophie.  Il met l'accent sur la dévotion envers Vishnu comme moyen ultime d'atteindre la libération. La grâce divine est essentielle pour surmonter le cycle des renaissances. &lt;/p&gt;   &lt;p&gt; Il a composé de nombreux textes philosophiques, commentaires et poèmes dévotionnels. Parmi ses œuvres les plus importantes figurent : &lt;/p&gt;&#10;&lt;dd&gt; Brahma Sutra Bhashya : Un commentaire sur les &lt;a href=&quot;https://fr.wikipedia.org/wiki/Brahma_Sutra&quot;  title=&quot;Brahma Sutra par Wikipedia&quot;&gt;Brahma Sutras&lt;/a&gt;, qui est l'un des textes fondamentaux du Vedanta.&#10;&lt;/dd&gt; &lt;dd&gt; Anu Vyakhyana : Une explication détaillée de sa philosophie Dvaita. &lt;/dd&gt;&#10;&lt;dd&gt; Gita Bhashya : Un commentaire sur la Bhagavad Gita. &lt;/dd&gt;&#10;&lt;dd&gt; Dvadasha Stotra : Douze hymnes dévotionnels dédiés à Vishnu. &lt;/dd&gt;   &lt;p&gt; Madhva était connu pour ses positions fermes et ses critiques acerbes des autres écoles de pensée, en particulier l'Advaita. Ses idées sur la hiérarchie des âmes et la nature distincte de Dieu ont suscité des débats intenses avec les partisans de Shankara et Ramanuja. Ces débats ont enrichi la tradition philosophique indienne en encourageant une réflexion approfondie sur la nature de la réalité et de la libération. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; "/>
-    <hyperlink ref="E85" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gersonide&quot;  title=&quot; Wikipedia&quot;&gt;GERSONIDE&lt;/a&gt; de son nom complet Lévi ben Gershom, est un des grands penseurs juifs du Moyen Âge, actif dans le sud de la France. Mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe, il est souvent considéré comme l’un des plus  &lt;a href=&quot;https://www.youtube.com/watch?v=zFnektKxZok&quot; title=&quot;Levi ben Gerson (gersonides)  par Math Mystique&quot;&gt;grands esprits juifs &lt;/a&gt; entre Maïmonide et la modernité. Il écrit en hébreu et en arabe, mêlant étude des textes religieux, science et philosophie, dans un esprit très critique et original. &lt;/p&gt; &lt;p&gt; Sa philosophie se veut un rapprochement systématique entre la pensée d’Aristote (via Averroès) et la pensée biblique‑talmudique. Dans son œuvre majeure, Milhamot Ha‑Shem (Les Guerres du Seigneur), il cherche à montrer que la raison et la révélation peuvent coexister et s’accorder sur la plupart des vérités importantes. Il adopte une cosmologie largement aristotélicienne tout en restant fidèle à un cadre théiste juif, en méditant par exemple  &lt;a href=&quot;https://www.persee.fr/doc/rscir_0035-2217_1954_num_28_4_2056&quot; title=&quot;les idées philosophiques de GERSONIDE par Persée&quot;&gt;la création, la nature de Dieu &lt;/a&gt; et l’ordre du monde. &lt;/p&gt; &lt;p&gt; Parmi ses thèses les plus marquantes figurent sa conception de l’âme et de la prophétie : il soutient que l’âme humaine peut s’identifier à une intelligence universelle ou “raison active” qui unit l’homme à Dieu, et que l’immortalité de l’âme passe par l’acquisition de connaissances rationnelles adéquates. Il défend aussi une vision particulière de la connaissance divine : Dieu connaît toutes les possibilités humaines, mais ne prédétermine pas chaque choix, ce qui laisse une véritable place au libre arbitre humain, en rupture avec une vision toute‑puissante et strictement déterministe. &lt;/p&gt; &lt;p&gt; Il  est remarquable par son a href=&quot;https://www.youtube.com/watch?v=sq1YiI6BGVQ&quot; title=&quot;medieval  philosopher GERSONIDE par Stay curious radio&quot;&gt;rigoureux rationalisme &lt;/a&gt; et son goût pour les méthodes analytiques proches de la scolastique latine. Il utilise les mathématiques et l’astronomie non seulement comme sciences, mais comme instruments pour mieux comprendre Dieu et le monde créé. Sa tentative de fonder une théologie juive stable sur des bases scientifiques et rationnelles en fait un pont entre la pensée islamique‑aristotélicienne, la scolastique chrétienne et la tradition juive médiévale. &lt;/p&gt; &#10;&#10;&#10;&#10;"/>
-    <hyperlink ref="H85" r:id="rId36" display="https://www.laphilo.fr/pho/gersonide-mini.webp"/>
-    <hyperlink ref="E86" r:id="rId37" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas&quot;  title=&quot; Wikipedia&quot;&gt;Grégoire PALAMAS&lt;/a&gt; était un moine, théologien et philosophe byzantin, archevêque de Thessalonique, figure centrale de la tradition mystique et philosophique de l'Église orthodoxe. Né à Constantinople dans une famille noble, il entra très jeune dans les ordres monastiques au mont Athos, où il développa une pratique intense de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot;hésychasme par wikipedia&quot;&gt;prière hésychaste. &lt;/a&gt; Sa pensée constitue l'une des synthèses philosophiques et théologiques les plus originales de la tradition chrétienne orientale. &lt;/p&gt; &lt;p&gt; Sa doctrine philosophique centrale, le palamisme, s'articule autour de la distinction entre l'essence divine et les énergies divines. Contre les attaques du moine calabrais Barlaam qui accusait les hésychastes de prétendre voir l'essence de Dieu, il soutient que si l'essence de Dieu demeure absolument inaccessible et inconnaissable, ses énergies — qui ne sont pas des créatures mais Dieu lui-même en acte — peuvent être vues et participées par l'homme. C'est ainsi que les moines peuvent voir la Lumière du Thabor, lumière incréée, sans pour autant prétendre voir l'essence divine. &lt;/p&gt; &lt;p&gt; Cette distinction, exposée dans les &lt;em&gt;Triades pour la défense des saints hésychastes&lt;/em&gt; (1338-1341) et dans les &lt;em&gt;150 chapitres&lt;/em&gt;, eut des implications philosophiques considérables sur la conception de la connaissance, de la participation et du rapport entre l'humain et le divin. &lt;a href=&quot;https://www.persee.fr/doc/thlou_0080-2654_1973_num_4_4_1270&quot; title=&quot;Palamisme et scolastique par persée&quot;&gt;Le palamisme &lt;/a&gt;  fut adopté comme doctrine officielle de l'Église orthodoxe au concile de Constantinople de 1351. Son influence sur la philosophie et la spiritualité orthodoxes russes — notamment à travers les monastères athonites — fut et reste profonde et durable. &lt;/p&gt; &lt;audio controls title=&quot;Traités démostratifs de Grégoire Palamas par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10491-11.06.2017-ITEMA_21353577-2017C3184E0012-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E91" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nguy%C3%AAn_Trai&quot; title=&quot; Wikipedia&quot;&gt;Nguyễn Trãi&lt;/a&gt; était un lettré, stratège et homme d’État vietnamien, figure majeure de la pensée politique et morale du Vietnam médiéval. Sa pensée s’inscrit dans le Tam Giáo, la synthèse traditionnelle des trois enseignements — confucianisme, bouddhisme et taoïsme — caractéristique de la philosophie vietnamienne, qu’il met au service d’un idéal de gouvernement bienveillant et de résistance à l’occupation étrangère. Considéré comme l’un des &lt;a href=&quot;https://www.vietnammonpaysnatal.fr/nguyen_trai/&quot; title=&quot;ngueyn trai par vietnammonpays&quot;&gt;pères fondateurs &lt;/a&gt; de l’identité intellectuelle vietnamienne, son œuvre reste une référence de l’humanisme politique du pays.&lt;/p&gt;"/>
-    <hyperlink ref="H91" r:id="rId39" display="https://www.laphilo.fr/pho/ntrai-mini.webp"/>
-    <hyperlink ref="E93" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Kab%C3%AEr&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;KABIR&lt;/a&gt;  était un mystique et philosophe indien. Il est considéré comme l'une des figures les plus importantes de la tradition mystique indienne et est souvent associé au mouvement &lt;a href=&quot;https://fr.hdasianart.com/blogs/news/the-importance-of-bhakti-in-hinduism&quot; style=&quot;color:#88A1E9&quot; title=&quot;L'importance du Bhakti par Asian Art&quot;&gt;Bhakti &lt;/a&gt; , qui prône une dévotion personnelle et intime à Dieu, transcendant les rituels formels et les distinctions sociales. &lt;/p&gt; &lt;p&gt; Né dans une famille de tisserands musulmans, il a été profondément influencé par les enseignements hindous, en particulier ceux de Ramananda, un saint de la tradition Bhakti. Cette double influence se reflète dans ses écrits, où il synthétise des éléments des deux traditions tout en critiquant leurs aspects ritualistes et dogmatiques. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour ses poèmes et ses chants, qui expriment une spiritualité profondément personnelle et universelle et qui peuvent être résumés autour de plusieurs thèmes clés : &lt;/p&gt;&#10;&lt;dd&gt;- L'unité de Dieu : Il insiste sur l'unicité de Dieu, qu'il appelle par différents noms, tels que Ram, Allah, Hari ou Khuda. Il rejette les divisions sectaires entre hindous et musulmans, affirmant que Dieu est au-delà des religions et des formes.&lt;/dd&gt;&#10;&lt;dd&gt; - La critique des rituels et des institutions religieuses : Il dénonce les pratiques ritualistes, les pèlerinages, les sacrifices et les observances extérieures. Il critique également les prêtres, les gourous et les autorités religieuses qui exploitent la foi des gens.&lt;/dd&gt;&#10;&lt;dd&gt; - La dévotion intérieure (Bhakti) : La véritable dévotion consiste en une relation directe et intime avec Dieu, sans intermédiaires, par une spiritualité basée sur l'amour, la simplicité et la sincérité du cœur.&lt;/dd&gt;&#10;&lt;dd&gt;  - La recherche de la vérité intérieure : Chercher la vérité en soit-même plutôt que dans les textes sacrés ou les enseignements externes. &lt;/dd&gt;&#10;&lt;dd&gt; -  L'égalité sociale : Il rejette le système des castes et prône l'égalité de tous les êtres humains devant Dieu, de toutes les couches sociales, des plus humbles aux plus élevées, et insiste sur l'importance de l'humilité et de la compassion. &lt;/dd&gt;  &lt;p&gt; Ses  &lt;a href=&quot;https://fr.wikisource.org/wiki/Po%C3%A8mes_de_Kabir&quot;  title=&quot;poemes de Kabir par Wikisource&quot;&gt;poèmes &lt;/a&gt; , appelés &quot;dohas&quot; ou &quot;couplets&quot;, sont écrits dans une langue simple et directe, souvent en hindi vernaculaire mélangé à des éléments de persan et d'arabe. Ses vers sont riches en métaphores et en paradoxes, invitant le lecteur à réfléchir profondément sur la nature de la réalité et de la spiritualité. Par exemple, il compare souvent l'âme à une abeille cherchant le nectar de la vérité, ou à un oiseau migrateur cherchant à retourner à sa maison divine. &lt;/p&gt;  "/>
-    <hyperlink ref="H96" r:id="rId41" display="https://www.laphilo.fr/pho/yhwang-mini.webp"/>
-    <hyperlink ref="E97" r:id="rId42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Li_Zhi_(1527-1602)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Li ZHI&lt;/a&gt; était un penseur, écrivain et critique social chinois de la fin de la dynastie Ming. Ses idées avant-gardistes et sa critique des conventions sociales et religieuses ont marqué l'histoire intellectuelle chinoise. &lt;/p&gt; &lt;p&gt; Il était un critique virulent du &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_1994_num_7_1_913&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les rites et la question du droit: la constitution d'une nature dans le confucianisme en Chine et au Japon par Persée&quot;&gt;confucianisme orthodoxe&lt;/a&gt;, qu'il considérait comme rigide et hypocrite. Il prônait une approche plus individualiste et authentique de la vie, mettant l'accent sur la sincérité et l'expression personnelle. Il critiquait l'obsession des gens pour la réputation et les apparences, qu'il considérait comme des obstacles à la véritable réalisation de soi. &lt;/p&gt; &lt;p&gt;  Il était également connu pour ses vues progressistes sur les femmes. Il défendait l'idée que les femmes étaient tout aussi capables que les hommes sur le plan intellectuel et moral, une position rare à son époque. Bien qu'il ait été influencé par le bouddhisme et le taoïsme, il critiquait les institutions religieuses, qu'il jugeait souvent corrompues et éloignées des véritables enseignements spirituels. &lt;/p&gt; &lt;p&gt; Il  a laissé une œuvre écrite abondante, dont certaines ont été censurées ou perdues en raison de leur nature controversée. Parmi ses œuvres les plus connues, on trouve : &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Hide&quot;: Une collection de biographies et de commentaires sur des figures historiques, où il exprime ses opinions critiques sur la politique et la société. &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Burn&quot;: Un recueil d'essais et de lettres dans lequel il expose ses idées sur l'authenticité, la moralité et la critique sociale. &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Keep&quot;: Une suite de &quot;A Book to Hide&quot;, contenant des réflexions supplémentaires sur l'histoire et la philosophie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;Ses idées ont influencé des générations de penseurs chinois, et il est aujourd'hui considéré comme un précurseur des mouvements modernes pour l'individualisme et la liberté de pensée. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;  "/>
-    <hyperlink ref="E100" r:id="rId43" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Zera_Yacob&quot;  title=&quot; Wikipedia&quot;&gt;Zera YACOB&lt;/a&gt; est  l'un des premiers philosophes &lt;a href=&quot;https://www.willeime.com/classement.htm&quot;  title=&quot;rationalisme integral par willeime&quot;&gt;rationalistes&lt;/a&gt; de l'Afrique subsaharienne.  Pendant sept ans, il a vécu dans une grotte près de la rivière Tekezé, où il a médité et développé sa philosophie. C'est durant cette période qu'il a rédigé son œuvre la plus célèbre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Hatata&quot;  title=&quot;Hatata par Wikipedia&quot;&gt;Le Hatäta&lt;/a&gt;  (qui signifie &quot;enquête&quot; ou &quot;recherche&quot;) est un traité philosophique qui explore des questions métaphysiques, éthiques et religieuses. Il y aborde les questions fondamentales sur la nature de Dieu, la raison, la morale et la religion. Voici quelques-uns des principaux aspects de sa pensée : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;dd&gt; - La primauté de la raison : L'utilisation de la raison comme outil principal pour comprendre le monde et la vérité. Il critique les dogmes religieux et les superstitions, affirmant que la raison humaine est un don de Dieu qui doit être utilisé pour discerner le vrai du faux. &lt;/dd&gt;&#10; &lt;dd&gt; - La critique des religions :  Examine les différentes religions de son époque (christianisme, islam, judaïsme) et conclut qu'aucune n'a le monopole de la vérité. &lt;/dd&gt;&#10; &lt;dd&gt; - La morale naturelle : Morale universelle, innée en chaque être humain. Il soutient que les principes éthiques, tels que l'amour du prochain et le respect de la vie, sont inscrits dans la nature humaine par Dieu. &lt;/dd&gt; &#10;&lt;dd&gt; - L'égalité des êtres humains : Tous les êtres humains sont égaux devant Dieu, rejetant les discriminations fondées sur la race, le genre ou la religion. &lt;/dd&gt; &#10; &lt;dd&gt; - La tolérance religieuse : Tolérance et respect mutuel entre les différentes confessions religieuses. Il critique les conflits religieux et les persécutions, qu'il considère comme contraires à la volonté divine. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il est souvent comparé à des philosophes rationalistes européens comme Descartes ou Spinoza, bien qu'il ait développé sa pensée de manière indépendante. Son œuvre a été redécouverte au XXe siècle par des chercheurs éthiopiens et occidentaux, qui ont reconnu son importance dans l'histoire de la philosophie. &lt;/p&gt; "/>
-    <hyperlink ref="H102" r:id="rId44" display="https://www.laphilo.fr/pho/ysoko-mini.webp"/>
-    <hyperlink ref="H105" r:id="rId45" display="https://www.laphilo.fr/pho/yik-mini.webp"/>
-    <hyperlink ref="E106" r:id="rId46" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anton_Wilhelm_Amo&quot; title=&quot;Wikipedia&quot;&gt;Anton Wilhelm AMO &lt;/a&gt; était un philosophe et une figure fascinante des Lumières, né sur la côte de l’actuel Ghana et devenu &lt;a href=&quot;https://www.youtube.com/watch?v=qLgvLjt-HxI&quot;   title=&quot;the first african professor in europe par Africaon Griot Studio&quot;&gt;le premier Africain &lt;/a&gt; subsaharien connu à avoir obtenu un doctorat dans une université européenne. Il a enseigné en Allemagne et s’est imposé dans les débats philosophiques de son temps, ce qui fait de lui un penseur important de l’histoire de la philosophie européenne autant qu’africaine. &lt;/p&gt; &lt;p&gt; Sa pensée est surtout connue pour sa critique de l’idée selon laquelle l’âme serait le siège de la sensation. Dans sa thèse de 1734, il soutient que l’être humain perçoit le monde par le corps vivant et organique, et non par l’âme, ce qui le conduit à distinguer clairement les fonctions du corps et celles de l’esprit. &lt;/p&gt; &lt;p&gt; Il cherche ainsi à clarifier les &lt;a href=&quot;https://blogs.mediapart.fr/geographies-en-mouvement/blog/290825/amo-une-figure-africaine-enfin-visible&quot;   title=&quot;anton wilhelm Amo par le club Mediapart&quot;&gt;concepts philosophiques &lt;/a&gt;  avec rigueur, dans l’esprit des Lumières. Il s’intéresse aussi à l’épistémologie et à la relation entre sensation, jugement et connaissance, en dialogue avec les grandes doctrines de son époque, tout en gardant une position originale sur le rapport entre corps et esprit. &lt;/p&gt; &lt;p&gt; Il  est souvent relu comme une figure majeure de la philosophie africaine et de la pensée décoloniale, parce qu’il montre qu’un philosophe africain a pu participer au cœur même de la philosophie savante européenne tout en proposant une voie propre. Son importance tient autant à son œuvre qu’à sa place symbolique : celle d’un penseur noir des Lumières longtemps oublié, puis redécouvert. &lt;/p&gt; &#10; &lt;audio controls title=&quot;philosophe noir des lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-18.12.2024-ITEMA_23944950-2023C3330E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="H107" r:id="rId47" display="https://www.laphilo.fr/pho/waliullah-mini.webp"/>
-    <hyperlink ref="H108" r:id="rId48" display="https://www.laphilo.fr/pho/mnorinaga-mini.webp"/>
-    <hyperlink ref="E110" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Debendranath_Tagore&quot;  title=&quot; Wikipedia&quot;&gt;Debendranath TAGORE&lt;/a&gt; était un philosophe hindou et réformateur religieux indien, figure centrale du Brahmo Samaj (Société de Brahma).  Fils de l'industriel Dwarkanath Tagore, surnommé « Prince » pour son mode de vie extravagant, et de Digambari Devi, une femme très pieuse. Il reçoit une éducation d'abord à domicile, puis à l'Anglo Hindu College, et développe un profond intérêt pour la philosophie. En 1842, il rejoint le Brahmo Samaj et en devient le leader. Avec des amis, influencé par son ami Ram Mohan Roy et sous la tutelle du Pandit Ram Chandra Vidyabageesh, il fonde la Tattwabodhini Sabha en 1839, une société intellectuelle dédiée à  &lt;a href=&quot;https://www.youtube.com/watch?v=XzVRebsCpkc&quot;  title=&quot;De Tagore reform leaders par By Ju’s Ias&quot;&gt;l'étude de la philosophie &lt;/a&gt; et de la théologie. &lt;/p&gt;&lt;p&gt; Il publie le Brahmo Dharma Beej (Graine du Dharma Brahmo) et la Tattwabodhini Patrika en 1843 comme organe officiel de sa société. Grâce à ses efforts, l'influence  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Brahmo%C3%AFsme&quot;  title=&quot;Brahmoisme par wikipedia&quot;&gt;du brahmoïsme &lt;/a&gt; se répand dans toute l'Inde En 1848, il codifie le Brahmo Dharma (aussi appelé Adi Dharma), un mouvement religieux fondé sur les principes du monothéisme et de la rationalité. &lt;/p&gt; &lt;p&gt; Il est connu pour ses réalisations spirituelles et reçoit le titre de Maharshi (« grand sage »), confirmé par le grand sage hindou qui lui rend visite. Il joue un rôle considérable dans la Renaissance du Bengale (Bengal Renaissance), mouvement de renouveau culturel, social et religieux du XIXe siècle. &lt;/p&gt; &lt;p&gt; Il a 15 enfants avec son épouse Sarada Devi, dont beaucoup deviennent des figures influentes et réussies. En 1863, il établit un ashram à Bhubandanga, appelé Santiniketan (« lieu de paix »), qui sera plus tard transformé par &lt;a href=&quot;https://www.youtube.com/watch?v=FFbQqJG7n_8&quot;  title=&quot;relation between rabindranath et son père par VIS PHILO&quot;&gt;son fils Rabindranath &lt;/a&gt;  en centre international d'éducation spirituelle et de méditation. C'est lui qui emmène jeune Rabindranath en voyage à Santiniketan puis dans l'Himalaya, lui enseignant la discipline, la liberté et la responsabilité, et lui faisant découvrir en profondeur les Upanishads. &lt;/p&gt; "/>
-    <hyperlink ref="H110" r:id="rId50" display="https://www.laphilo.fr/pho/dtagore-mini.webp"/>
-    <hyperlink ref="E111" r:id="rId51" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Djem%C3%A2l_ad-D%C3%AEn_al-Afgh%C3%A2ni&quot;  title=&quot; Wikipedia&quot;&gt;Djemâm ad-Dîn al-AFGHĀNĪ&lt;/a&gt; était une figure centrale du réformisme islamique moderne, souvent considéré comme l’un des fondateurs du panislamisme et du « réformisme islamique ». Né dans une famille afghane, il a vécu et voyagé dans de nombreux pays musulmans (Inde, Égypte, Turquie, Iran, Europe), ce qui lui a permis de développer une pensée à la fois religieuse, politique et philosophique, orientée vers la résistance au colonialisme européen et la &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Jamal-al-Din-al-Afghani-fondateur.html&quot;   title=&quot;Jamal al-Din al-Afghani reforme islamique par lesclesdumoyensorients&quot;&gt;rénovation de la société musulmane. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il soutient que l’islam n’est pas incompatible avec la modernité et la raison, et qu’il a même été à l’origine d’un grand élan philosophique et scientifique dans l’histoire musulmane. Il affirme que la révélation coranique appelle à la réflexion et à la compréhension du monde, ce qui justifie, selon lui, l’usage de la raison et des sciences modernes, sans pour autant remettre en cause les fondements de la foi (unicité de Dieu, prophétie, création). &lt;a href=&quot;https://www.youtube.com/watch?v=EOTAUYYAzoE&quot;  title=&quot;Al-Afghani par TV5 monde &quot;&gt;Sa philosophie &lt;/a&gt; consiste donc à libérer l’islam de ce qu’il appelle les « superstitions » et les traditions sclérosées, tout en gardant l’essence de la doctrine religieuse. &lt;/p&gt; &lt;p&gt; Un autre pilier de sa pensée est l’appel à l’unité de la communauté musulmane (l’ūmma) face à la domination coloniale et politique occidentale. Il considère que le déclin des pays musulmans vient moins de l’islam lui‑même que de la fragmentation politique, de la tyrannie des gouvernants et de l’ignorance des élites. Pour lui, la solidarité religieuse et la conscience d’une même appartenance doivent être au cœur d’un projet de civilisation islamique moderne, capable de s’approprier les sciences européennes tout en restant fidèle à des valeurs morales communes. &lt;/p&gt; &lt;p&gt; Il est un penseur rationaliste qui refuse de séparer foi et raison, et qui place la liberté et la responsabilité de l’individu au centre de la vie morale et politique. Il critique la passivité religieuse et les gouvernements despotiques, qu’il accuse de conforter la domination étrangère ; il défend donc une réforme politique parallèle à la réforme religieuse, incluant la critique du pouvoir absolu et la promotion de débats publics. À travers ses écrits et ses discours (comme ceux menés avec son disciple Muḥammad ʿAbduh et la revue al‑ʿUrwa al‑wuṯqā), il jette les bases d’un modernisme islamique qui inspirera ensuite de nombreux mouvements réformistes et nationalistes du monde arabe et musulman. &lt;/p&gt; &#10;&#10;&#10;"/>
-    <hyperlink ref="H111" r:id="rId52" display="https://www.laphilo.fr/pho/afghani-mini.webp"/>
-    <hyperlink ref="H113" r:id="rId53" display="https://www.laphilo.fr/pho/jafirmin-mini.webp"/>
-    <hyperlink ref="E114" r:id="rId54" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Rabindranath_Tagore&quot;  title=&quot; Wikipedia&quot;&gt;Rabindranath TAGORE&lt;/a&gt; était un poète, romancier, dramaturge, philosophe et compositeur bangladais  &lt;a href=&quot;https://www.youtube.com/watch?v=q7c6zqn4L8g&quot;  title=&quot;National Anthem Tagore’s Own Voice par Gingerline Media&quot;&gt;d'expression bengalie et anglaise, &lt;/a&gt; devenu le premier non-Européen à recevoir le prix Nobel de littérature en 1913.  Né à Calcutta (Inde) dans une famille de lettrés, &lt;a href=&quot;https://agora.qc.ca/dossiers/rabindranath_tagore&quot;  title=&quot;Tagore par Agora&quot;&gt; philosophes et artistes, &lt;/a&gt;  il est le plus jeune fils de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Debendranath_Tagore&quot;  title=&quot; Debendranath Tagore par wikipedia&quot;&gt; Debendranath Tagore &lt;/a&gt;, un éminent philosophe et réformateur religieux leader du Brahmo Samaj, une nouvelle secte religieuse du Bengale qui tentait de rétablir le monisme ultime de l'hindouisme tel que décrit dans les Upanishads.. Il se rend en Occident vers 1880, renonçant à tout pour « mieux aimer la nature et Dieu ». &lt;/p&gt; &lt;p&gt; Entre 1901 et 1918, il traverse d'immenses souffrances : sa femme, trois de ses enfants et son père meurent successivement. Malgré cela, il transforme sa douleur en création et fonde un centre d'éducation international à Shantiniketan (près de Calcutta) où il applique ses idéaux éducatifs inspirés des Upanishads. Ce centre devient Visva-Bharati University, un lieu dynamique qui rayonne sur toute la région puis sur toute l'Inde. &lt;/p&gt; &lt;p&gt; Il  est avant tout poète et a écrit plus de 50 volumes de poésie, dont les plus célèbres sont Manasi (1890), Sonar Tari (1894) [Le Navire d'or], Gitanjali (1910) [Offrande lyrique], Gitimalya (1914) et Balaka (1916). C'est Gitanjali, traduit en anglais par lui-même en 1912, qui le rend  &lt;a href=&quot;https://www.youtube.com/watch?v=v3iix5GSB2I&quot;  title=&quot; Drabindranath TAGORE par Eclair Brut&quot;&gt; mondialement célèbre &lt;/a&gt; et lui vaut le Nobel. Le prix lui est décerné « pour ses vers profondément sensibles, frais et beaux, par lesquels, avec une maîtrise consommée, il a fait de sa pensée poétique, exprimée en ses propres mots anglais, une partie de la littérature occidentale ». &lt;/p&gt; &lt;p&gt; Il est un philosophe humaniste dont la pensée s'enracine dans  &lt;a href=&quot;https://www.youtube.com/watch?v=S3HO9PeoqP0&quot;  title=&quot;Les Upanishads par Resumons ça&quot;&gt;les Upanishads &lt;/a&gt; et la recherche de l'Absolu comme « unique réalité de la vie ». Il participe ponctuellement au mouvement nationaliste indien, mais de manière « non sentimentale et visionnaire », et entretient une amitié avec Gandhi, qu'il considère comme le père politique de l'Inde moderne. Il rejette le nationalisme étroit et prône un universalisme spirituel, devenant « la voix de l'héritage spirituel de l'Inde » pour le monde. &lt;/p&gt; &#10;                               &lt;audio controls title=&quot;Rabindranath TAGORE  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-11.02.2012-ITEMA_20344077-2012C3330E0006-ITE_00049084_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H114" r:id="rId55" display="https://www.laphilo.fr/pho/rtagore-mini.webp"/>
-    <hyperlink ref="E115" r:id="rId56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vivekananda&quot;  title=&quot; Wikipedia&quot;&gt;VIVEKANANDA&lt;/a&gt; était l'une des figures spirituelles les plus influentes de l'Inde moderne et un ardent défenseur de la  &lt;a href=&quot;https://www.rggpodcast.fr/c%C3%A9l%C3%A9brations/swami-vivekananda/&quot;  title=&quot;Radio Gandharva gana par Rggweb&quot;&gt;philosophie vedanta&lt;/a&gt; et du yoga. Né sous le nom de Narendranath Datta à Calcutta, il est devenu un disciple du grand saint et mystique Ramakrishna Paramahamsa, un saint mystique de Dakshineswar. &lt;/p&gt; &lt;p&gt; Il croyait que toutes les religions mènent au même but ultime et que les différences ne sont que superficielles. Selon lui, chaque être humain possède en lui une étincelle divine et peut réaliser sa nature divine par la pratique spirituelle. Il a insisté sur l'importance du service désintéressé (seva) envers les pauvres et les nécessiteux, considérant cela comme une forme de culte et a plaidé pour une éducation qui combine les connaissances modernes et les valeurs spirituelles traditionnelles. &lt;/p&gt; &lt;p&gt; Il  a fondé la Ramakrishna Mission, une organisation dédiée au service social, à l'éducation et à la diffusion des enseignements spirituels.  Il  est considéré comme un pionnier du dialogue interreligieux et un inspirateur du mouvement nationaliste indien. Ses enseignements ont influencé des leaders comme Mahatma Gandhi, Subhas Chandra Bose et Aurobindo Ghosh. Il est également crédité d'avoir &lt;a href=&quot;https://blog.green-yoga.fr/vivekananda-premier-maitre-yogi-moderne/&quot;  title=&quot;Vivekananda, premier maître yogi moderne par blog-green-yoga&quot;&gt;popularisé le yoga&lt;/a&gt; et la méditation en Occident. &lt;/p&gt;"/>
-    <hyperlink ref="H115" r:id="rId57" display="https://www.laphilo.fr/pho/vivekananda-mini.webp"/>
-    <hyperlink ref="E116" r:id="rId58" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohandas_Karamchand_Gandhi&quot;  title=&quot; Wikipedia&quot;&gt;Mohandas Karamchand GANDHI&lt;/a&gt;  était un &lt;a href=&quot;https://www.youtube.com/watch?v=zTmg8qs5B_w&amp;ab_channel=Brut&quot;  title=&quot;Une vie par Brut&quot;&gt;leader spirituel&lt;/a&gt; et un militant politique Indien. Il est surtout connu pour sa lutte pacifique pour l'indépendance de l'Inde vis-à-vis du Royaume-Uni par  des désobéissances civile non-violentes contre le gouvernement britannique,  grève de la faim, manifestations et boycotts. &lt;/p&gt; &lt;p&gt;   Gandhi était surtout un philosophe qui a développé sa propre vision du monde et de la vie. &lt;a href=&quot;https://www.psychaanalyse.com/pdf/ghandi_sa_pensee.pdf&quot;   title=&quot;Livre de Gandhi&quot;&gt;Sa philosophie&lt;/a&gt; est souvent appelée &quot;satyagraha&quot;, un terme sanskrit qui signifie &quot;force de la vérité&quot; ou &quot;force de l'âme&quot;. Elle est centrée sur la non-violence, l'amour et la vérité. C'est la seule façon de résoudre les conflits de manière pacifique et durable. &lt;/p&gt; &lt;p&gt;   l croyait que chaque être humain possède une âme divine, et que cette âme est la source de notre force intérieure. Il a encouragé les gens à chercher la vérité en eux-mêmes et à suivre leur conscience plutôt que de se conformer aux normes sociales ou religieuses imposées.&lt;/p&gt; &lt;p&gt;   Il a souligné l'importance de l'autonomie et de l'autosuffisance et a encouragé les gens à vivre de manière simple, à cultiver leur propre nourriture, à produire leurs propres vêtements et à être autosuffisants autant que possible. &lt;/p&gt; &lt;p&gt;  Cette vision était basée sur le concept de &lt;a href=&quot;https://www.editionscienceetbiencommun.org/wp-content/uploads/2018/01/Swaraj-des-savoirs-un-manifeste-indien-pour-la-science-et-la-technologie-1515376288.pdf&quot;    title=&quot;Un manifeste indien&quot;&gt;&quot;swaraj&quot;&lt;/a&gt;, ou l'autonomie, qui est devenu un thème majeur de la lutte de Gandhi pour l'indépendance de l'Inde. &lt;/P&gt;  &lt;audio controls title=&quot;Mémoires de Gandhi par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-29.01.2018-ITEMA_21570326-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H120" r:id="rId59" display="https://www.laphilo.fr/pho/coomaraswamy-mini.webp"/>
-    <hyperlink ref="E121" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohamed_Iqbal&quot; title=&quot;Wikipedia&quot;&gt;Muhammad IQBAL&lt;/a&gt; était un philosophe‑poète pakistanais, poète se plaçant à la croisée de l’islam, de la modernité et de la pensée occidentale. Considéré comme l’un des  &lt;a href=&quot;https://www.saphirnews.com/Mohammed-Iqbal-un-revolutionnaire-en-islam_a24652.html&quot; title=&quot;Mohamed Iqbal, un révolutionnaire en Islam par saphirnews&quot;&gt;grands penseurs musulmans &lt;/a&gt; de son époque, il cherche à réformer l’Islam en l’ouvrant à la rationalité et à l’action, tout en restant profondément enraciné dans la tradition soufie et coranique. &lt;/p&gt; &lt;p&gt; Sa philosophie tourne autour du « Khudi » (le Soi), c’est‑à‑dire une  &lt;a href=&quot;https://www.youtube.com/watch?v=ekC6_wffi10&quot; title=&quot;Mohamed Iqbal par Perennial Wisdom&quot;&gt;individualité spirituelle forte, &lt;/a&gt; capable de se libérer de toute passivité mystique et de toute soumission fataliste. Pour lui, l’homme n’est pas appelé à s’effacer dans un tout indifférencié, mais à affirmer son moi comme centre de liberté, de volonté et de responsabilité devant Dieu, en prolongeant ainsi la dynamique de la création. &lt;/p&gt; &lt;p&gt; Il  valorise aussi une lecture active et historique de l’Islam, où la loi et la pensée religieuse ne sont pas figées, mais appelées à se réinterpréter à la lumière de l’expérience humaine et du progrès. Il milite pour une société ouverte, où la foi se traduit par l’engagement, la justice, l’éducation et la dignité du travail, plutôt que par un rigorisme puritain ou un repli identitaire. &lt;/p&gt; &lt;p&gt; Il est souvent vu comme un penseur à la fois panislamiste et humaniste : il rêve d’une communauté musulmane unifiée, mais fondée sur la liberté intérieure, la créativité individuelle et le respect de la diversité humaine. Son œuvre, surtout poétique, mêle mystique et volonté de transformer le monde, ce qui fait de lui un des premiers philosophes à articuler Islam, modernité et affirmation de soi. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Iqbal : soufisme indo-pakistanais par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-02.10.2011-ITEMA_20312518-2011C14958E0033-ITE_00045911_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H123" r:id="rId61" display="https://www.laphilo.fr/pho/brambedkar-mini.webp"/>
-    <hyperlink ref="E124" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jiddu_Krishnamurti&quot;  title=&quot;Wikipedia&quot;&gt;Jiddu KRISHNAMURTI&lt;/a&gt;  était  un penseur indien qui a profondément marqué la réflexion sur la liberté intérieure, la conscience et l’éducation.  &lt;a href=&quot;https://citations.ouest-france.fr/citations-jiddu-krishnamurti-1049.html&quot; title=&quot;Citations Krishnamurti par citations ouest france&quot;&gt;Sa parole &lt;/a&gt; est souvent résumée par l’idée que « la vérité est un pays sans chemins » : on ne peut pas atteindre le réel par l’autorité, le dogme, le rituel ou un système de pensée tout fait.  .&lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve la critique du conditionnement psychologique. Il explique que l’être humain vit prisonnier de ses peurs, de ses habitudes, de ses croyances et des images qu’il se fabrique sur lui-même et sur les autres ; pour lui, cette prison mentale empêche de voir clairement. &lt;/p&gt; &lt;p&gt; Il ne propose pas une  &lt;a href=&quot;https://www.youtube.com/watch?v=Uk3Kdoouw-E&quot; title=&quot;Perceptions Empties consciousness : Krishnamurti &quot;&gt;méthode au sens classique, &lt;/a&gt; ni un chemin spirituel à suivre mécaniquement. À la place, il invite à une observation directe de l’esprit, sans jugement et sans choix, qu’il associe à une forme de méditation véritable ; cette attention nue permettrait de comprendre la pensée en train de se faire et de se défaire. &lt;/p&gt; &lt;p&gt; Il relie toujours la transformation individuelle au changement du monde. Il pense qu’une société plus juste ne peut naître que d’une conscience intérieure libérée de l’autorité, de la violence psychologique et de la dépendance aux systèmes ; sa philosophie est donc moins une doctrine qu’un appel à voir par soi-même, ici et maintenant. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Krishnamurti, une vie par France Culture&quot;&gt;&#10;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14090-10.10.2014-ITEMA_20678757-2014C23018S0283-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt;&#10;&lt;/audio&gt;"/>
-    <hyperlink ref="E125" r:id="rId63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor&quot; title=&quot;Wikipedia&quot;&gt;Léopold Sédar SENGHOR&lt;/a&gt; était à la fois un grand poète-philosophe francophone et un homme d’État sénégalais, premier président de la République du Sénégal (1960–1980) et premier Africain membre de l’Académie française. Formé dans le système scolaire français, il incarne une figure hybride, à la croisée de l’Afrique et de la France, de la négritude et de la francophonie. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot;Négridude par Wikipedia&quot;&gt;« négritude », &lt;/a&gt; qu’il définit comme la reconnaissance du fait d’être noir et l’acceptation de cette identité, de son histoire, de sa culture et de sa destinée. Il en fait une valeur poétique et politique : la négritude vise à restaurer la dignité du peuple noir après la colonisation, en affirmant la beauté de la culture afro‑africaine, de ses langues, de ses rythmes et de son rapport à la vie et à la nature. &lt;/p&gt; &lt;p&gt; Dans sa poésie, il met en avant une sensibilité particulière, une « sensorialité » et une intuition qu’il oppose à la rationalité occidentale jugée plus froide, ce qui fait de ses vers une ode à la terre africaine, aux corps noirs, aux masques, aux danses et aux ancêtres. Des textes comme Femme noire ou Chants d’ombre célèbrent à la fois la femme‑enfant, la femme‑mère, la terre‑Afrique et la mémoire collective, dans une langue riche en images et en musique. &lt;/p&gt; &lt;p&gt; Par‑delà la négritude, il rêve d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=sINJIeY4UKo&quot;  title=&quot;Senghor par RTS&quot;&gt;« Civilisation de l’Universel »,&lt;/a&gt;  c’est‑à‑dire d’un monde où différentes traditions (africaines, européennes, etc.) pourraient se mêler dans un métissage créateur plutôt que s’affronter. Philosophe politique, poète et humaniste, il reste l’une des figures majeures de la littérature francophone, à la fois comme chantre de la fierté noire et comme théoricien d’un dialogue entre cultures. &lt;/p&gt; &lt;audio controls title=&quot;Senghor ‘Tu te languis’ par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21713-25.11.2025-ITEMA_24321734-2025C53416E0132-ITE_00154728_RSCE-21-996409c1a2c68ce243e4f4ef83e00211.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E126" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Keiji_Nishitani&quot;  title=&quot;Wikipedia&quot;&gt;Keiji NISHITANI &lt;/a&gt; un philosophe japonais membre de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89cole_de_Kyoto&quot;  title=&quot;école de Kyoto par Wikipedia&quot;&gt;l’École de Kyoto, &lt;/a&gt;  au côté de Nishida Kitarō et Tanabe Hajime, et l’un des penseurs modernes les plus originaux sur la religion, le bouddhisme et l’expérience du néant. Il cherche à penser ensemble la crise métaphysique de la modernité occidentale et la voie spirituelle du bouddhisme, notamment le zen et le bouddhisme du Vide (śūnyatā). &lt;/p&gt; &lt;p&gt; Sa réflexion prend comme point de départ le nihilisme moderne, c’est‑à‑dire le sentiment profond que tout est vidé de sens, de valeur et d’origine absolue, auquel il confronte l’expérience bouddhique de la vacuité radicale. Selon lui, la modernité enferme l’homme dans un soi narcissique et isolé, coupé de tout fondement ultime, et ce qui surgit alors n’est pas seulement le doute, mais une « grande incertitude » qui mène au vide de soi‑même. &lt;/p&gt; &lt;p&gt; Il propose alors une  &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_2005_num_34_1_1419&quot;  title=&quot;l’un e le tout en question par Persée&quot;&gt;« conversion » spirituelle &lt;/a&gt; : le même néant qui menaçait d’anéantir l’individu peut devenir, lorsque l’on cesse de le fuir, le point de départ d’une nouvelle compréhension du religieux, où le soi s’efface au profit d’une ouverture à l’être tout entier. Pour lui, la religion ne se réduit ni à dogme, ni à institution, ni à simple psychologie, mais à une expérience où le sujet, au cœur de sa plus grande déréliction, découvre que le monde peut être habité de sacrement, de manière « immanemment sainte ». &lt;/p&gt; &lt;p&gt; Il s’inscrit dans une entreprise de « philosophie entre Orient et Occident », où la pensée occidentale rencontre la tradition bouddhique pour repenser ensemble l’être, le mal, la liberté et la responsabilité. À travers des ouvrages comme Religion et néant (Religion and Nothingness), il devient l’une des figures clés du dialogue philosophique et religieux entre Asie et Europe, articulant la crise de la modernité et la possibilité d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=Ak12Fplzo0U&quot;  title=&quot;The void is not the end Nishitani Keiji par NullSOPHY&quot;&gt;renaissance spirituelle &lt;/a&gt; fondée sur la vacuité éclairée. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H127" r:id="rId65" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
-    <hyperlink ref="E129" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E130" r:id="rId67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E131" r:id="rId68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="H131" r:id="rId69" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
-    <hyperlink ref="H140" r:id="rId70" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
+    <hyperlink ref="E85" r:id="rId35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas&quot;  title=&quot; Wikipedia&quot;&gt;Grégoire PALAMAS&lt;/a&gt; était un moine, théologien et philosophe byzantin, archevêque de Thessalonique, figure centrale de la tradition mystique et philosophique de l'Église orthodoxe. Né à Constantinople dans une famille noble, il entra très jeune dans les ordres monastiques au mont Athos, où il développa une pratique intense de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot;hésychasme par wikipedia&quot;&gt;prière hésychaste. &lt;/a&gt; Sa pensée constitue l'une des synthèses philosophiques et théologiques les plus originales de la tradition chrétienne orientale. &lt;/p&gt; &lt;p&gt; Sa doctrine philosophique centrale, le palamisme, s'articule autour de la distinction entre l'essence divine et les énergies divines. Contre les attaques du moine calabrais Barlaam qui accusait les hésychastes de prétendre voir l'essence de Dieu, il soutient que si l'essence de Dieu demeure absolument inaccessible et inconnaissable, ses énergies — qui ne sont pas des créatures mais Dieu lui-même en acte — peuvent être vues et participées par l'homme. C'est ainsi que les moines peuvent voir la Lumière du Thabor, lumière incréée, sans pour autant prétendre voir l'essence divine. &lt;/p&gt; &lt;p&gt; Cette distinction, exposée dans les &lt;em&gt;Triades pour la défense des saints hésychastes&lt;/em&gt; (1338-1341) et dans les &lt;em&gt;150 chapitres&lt;/em&gt;, eut des implications philosophiques considérables sur la conception de la connaissance, de la participation et du rapport entre l'humain et le divin. &lt;a href=&quot;https://www.persee.fr/doc/thlou_0080-2654_1973_num_4_4_1270&quot; title=&quot;Palamisme et scolastique par persée&quot;&gt;Le palamisme &lt;/a&gt;  fut adopté comme doctrine officielle de l'Église orthodoxe au concile de Constantinople de 1351. Son influence sur la philosophie et la spiritualité orthodoxes russes — notamment à travers les monastères athonites — fut et reste profonde et durable. &lt;/p&gt; &lt;audio controls title=&quot;Traités démostratifs de Grégoire Palamas par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10491-11.06.2017-ITEMA_21353577-2017C3184E0012-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E90" r:id="rId36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nguy%C3%AAn_Trai&quot; title=&quot; Wikipedia&quot;&gt;Nguyễn Trãi&lt;/a&gt; était un lettré, stratège et homme d’État vietnamien, figure majeure de la pensée politique et morale du Vietnam médiéval. Sa pensée s’inscrit dans le Tam Giáo, la synthèse traditionnelle des trois enseignements — confucianisme, bouddhisme et taoïsme — caractéristique de la philosophie vietnamienne, qu’il met au service d’un idéal de gouvernement bienveillant et de résistance à l’occupation étrangère. Considéré comme l’un des &lt;a href=&quot;https://www.vietnammonpaysnatal.fr/nguyen_trai/&quot; title=&quot;ngueyn trai par vietnammonpays&quot;&gt;pères fondateurs &lt;/a&gt; de l’identité intellectuelle vietnamienne, son œuvre reste une référence de l’humanisme politique du pays.&lt;/p&gt;"/>
+    <hyperlink ref="H90" r:id="rId37" display="https://www.laphilo.fr/pho/ntrai-mini.webp"/>
+    <hyperlink ref="E92" r:id="rId38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Kab%C3%AEr&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;KABIR&lt;/a&gt;  était un mystique et philosophe indien. Il est considéré comme l'une des figures les plus importantes de la tradition mystique indienne et est souvent associé au mouvement &lt;a href=&quot;https://fr.hdasianart.com/blogs/news/the-importance-of-bhakti-in-hinduism&quot; style=&quot;color:#88A1E9&quot; title=&quot;L'importance du Bhakti par Asian Art&quot;&gt;Bhakti &lt;/a&gt; , qui prône une dévotion personnelle et intime à Dieu, transcendant les rituels formels et les distinctions sociales. &lt;/p&gt; &lt;p&gt; Né dans une famille de tisserands musulmans, il a été profondément influencé par les enseignements hindous, en particulier ceux de Ramananda, un saint de la tradition Bhakti. Cette double influence se reflète dans ses écrits, où il synthétise des éléments des deux traditions tout en critiquant leurs aspects ritualistes et dogmatiques. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour ses poèmes et ses chants, qui expriment une spiritualité profondément personnelle et universelle et qui peuvent être résumés autour de plusieurs thèmes clés : &lt;/p&gt;&#10;&lt;dd&gt;- L'unité de Dieu : Il insiste sur l'unicité de Dieu, qu'il appelle par différents noms, tels que Ram, Allah, Hari ou Khuda. Il rejette les divisions sectaires entre hindous et musulmans, affirmant que Dieu est au-delà des religions et des formes.&lt;/dd&gt;&#10;&lt;dd&gt; - La critique des rituels et des institutions religieuses : Il dénonce les pratiques ritualistes, les pèlerinages, les sacrifices et les observances extérieures. Il critique également les prêtres, les gourous et les autorités religieuses qui exploitent la foi des gens.&lt;/dd&gt;&#10;&lt;dd&gt; - La dévotion intérieure (Bhakti) : La véritable dévotion consiste en une relation directe et intime avec Dieu, sans intermédiaires, par une spiritualité basée sur l'amour, la simplicité et la sincérité du cœur.&lt;/dd&gt;&#10;&lt;dd&gt;  - La recherche de la vérité intérieure : Chercher la vérité en soit-même plutôt que dans les textes sacrés ou les enseignements externes. &lt;/dd&gt;&#10;&lt;dd&gt; -  L'égalité sociale : Il rejette le système des castes et prône l'égalité de tous les êtres humains devant Dieu, de toutes les couches sociales, des plus humbles aux plus élevées, et insiste sur l'importance de l'humilité et de la compassion. &lt;/dd&gt;  &lt;p&gt; Ses  &lt;a href=&quot;https://fr.wikisource.org/wiki/Po%C3%A8mes_de_Kabir&quot;  title=&quot;poemes de Kabir par Wikisource&quot;&gt;poèmes &lt;/a&gt; , appelés &quot;dohas&quot; ou &quot;couplets&quot;, sont écrits dans une langue simple et directe, souvent en hindi vernaculaire mélangé à des éléments de persan et d'arabe. Ses vers sont riches en métaphores et en paradoxes, invitant le lecteur à réfléchir profondément sur la nature de la réalité et de la spiritualité. Par exemple, il compare souvent l'âme à une abeille cherchant le nectar de la vérité, ou à un oiseau migrateur cherchant à retourner à sa maison divine. &lt;/p&gt;  "/>
+    <hyperlink ref="H95" r:id="rId39" display="https://www.laphilo.fr/pho/yhwang-mini.webp"/>
+    <hyperlink ref="E96" r:id="rId40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Li_Zhi_(1527-1602)&quot;  style=&quot;color:#6A142A&quot;  title=&quot; Wikipedia&quot;&gt;Li ZHI&lt;/a&gt; était un penseur, écrivain et critique social chinois de la fin de la dynastie Ming. Ses idées avant-gardistes et sa critique des conventions sociales et religieuses ont marqué l'histoire intellectuelle chinoise. &lt;/p&gt; &lt;p&gt; Il était un critique virulent du &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_1994_num_7_1_913&quot; style=&quot;color:#88A1E9&quot; title=&quot;Les rites et la question du droit: la constitution d'une nature dans le confucianisme en Chine et au Japon par Persée&quot;&gt;confucianisme orthodoxe&lt;/a&gt;, qu'il considérait comme rigide et hypocrite. Il prônait une approche plus individualiste et authentique de la vie, mettant l'accent sur la sincérité et l'expression personnelle. Il critiquait l'obsession des gens pour la réputation et les apparences, qu'il considérait comme des obstacles à la véritable réalisation de soi. &lt;/p&gt; &lt;p&gt;  Il était également connu pour ses vues progressistes sur les femmes. Il défendait l'idée que les femmes étaient tout aussi capables que les hommes sur le plan intellectuel et moral, une position rare à son époque. Bien qu'il ait été influencé par le bouddhisme et le taoïsme, il critiquait les institutions religieuses, qu'il jugeait souvent corrompues et éloignées des véritables enseignements spirituels. &lt;/p&gt; &lt;p&gt; Il  a laissé une œuvre écrite abondante, dont certaines ont été censurées ou perdues en raison de leur nature controversée. Parmi ses œuvres les plus connues, on trouve : &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Hide&quot;: Une collection de biographies et de commentaires sur des figures historiques, où il exprime ses opinions critiques sur la politique et la société. &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Burn&quot;: Un recueil d'essais et de lettres dans lequel il expose ses idées sur l'authenticité, la moralité et la critique sociale. &lt;/p&gt; &#10;&lt;p&gt; - &quot;A Book to Keep&quot;: Une suite de &quot;A Book to Hide&quot;, contenant des réflexions supplémentaires sur l'histoire et la philosophie. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;Ses idées ont influencé des générations de penseurs chinois, et il est aujourd'hui considéré comme un précurseur des mouvements modernes pour l'individualisme et la liberté de pensée. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;  "/>
+    <hyperlink ref="E99" r:id="rId41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Zera_Yacob&quot;  title=&quot; Wikipedia&quot;&gt;Zera YACOB&lt;/a&gt; est  l'un des premiers philosophes &lt;a href=&quot;https://www.willeime.com/classement.htm&quot;  title=&quot;rationalisme integral par willeime&quot;&gt;rationalistes&lt;/a&gt; de l'Afrique subsaharienne.  Pendant sept ans, il a vécu dans une grotte près de la rivière Tekezé, où il a médité et développé sa philosophie. C'est durant cette période qu'il a rédigé son œuvre la plus célèbre &lt;a href=&quot;https://fr.wikipedia.org/wiki/Hatata&quot;  title=&quot;Hatata par Wikipedia&quot;&gt;Le Hatäta&lt;/a&gt;  (qui signifie &quot;enquête&quot; ou &quot;recherche&quot;) est un traité philosophique qui explore des questions métaphysiques, éthiques et religieuses. Il y aborde les questions fondamentales sur la nature de Dieu, la raison, la morale et la religion. Voici quelques-uns des principaux aspects de sa pensée : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;dd&gt; - La primauté de la raison : L'utilisation de la raison comme outil principal pour comprendre le monde et la vérité. Il critique les dogmes religieux et les superstitions, affirmant que la raison humaine est un don de Dieu qui doit être utilisé pour discerner le vrai du faux. &lt;/dd&gt;&#10; &lt;dd&gt; - La critique des religions :  Examine les différentes religions de son époque (christianisme, islam, judaïsme) et conclut qu'aucune n'a le monopole de la vérité. &lt;/dd&gt;&#10; &lt;dd&gt; - La morale naturelle : Morale universelle, innée en chaque être humain. Il soutient que les principes éthiques, tels que l'amour du prochain et le respect de la vie, sont inscrits dans la nature humaine par Dieu. &lt;/dd&gt; &#10;&lt;dd&gt; - L'égalité des êtres humains : Tous les êtres humains sont égaux devant Dieu, rejetant les discriminations fondées sur la race, le genre ou la religion. &lt;/dd&gt; &#10; &lt;dd&gt; - La tolérance religieuse : Tolérance et respect mutuel entre les différentes confessions religieuses. Il critique les conflits religieux et les persécutions, qu'il considère comme contraires à la volonté divine. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il est souvent comparé à des philosophes rationalistes européens comme Descartes ou Spinoza, bien qu'il ait développé sa pensée de manière indépendante. Son œuvre a été redécouverte au XXe siècle par des chercheurs éthiopiens et occidentaux, qui ont reconnu son importance dans l'histoire de la philosophie. &lt;/p&gt; "/>
+    <hyperlink ref="H101" r:id="rId42" display="https://www.laphilo.fr/pho/ysoko-mini.webp"/>
+    <hyperlink ref="H104" r:id="rId43" display="https://www.laphilo.fr/pho/yik-mini.webp"/>
+    <hyperlink ref="E105" r:id="rId44" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Anton_Wilhelm_Amo&quot; title=&quot;Wikipedia&quot;&gt;Anton Wilhelm AMO &lt;/a&gt; était un philosophe et une figure fascinante des Lumières, né sur la côte de l’actuel Ghana et devenu &lt;a href=&quot;https://www.youtube.com/watch?v=qLgvLjt-HxI&quot;   title=&quot;the first african professor in europe par Africaon Griot Studio&quot;&gt;le premier Africain &lt;/a&gt; subsaharien connu à avoir obtenu un doctorat dans une université européenne. Il a enseigné en Allemagne et s’est imposé dans les débats philosophiques de son temps, ce qui fait de lui un penseur important de l’histoire de la philosophie européenne autant qu’africaine. &lt;/p&gt; &lt;p&gt; Sa pensée est surtout connue pour sa critique de l’idée selon laquelle l’âme serait le siège de la sensation. Dans sa thèse de 1734, il soutient que l’être humain perçoit le monde par le corps vivant et organique, et non par l’âme, ce qui le conduit à distinguer clairement les fonctions du corps et celles de l’esprit. &lt;/p&gt; &lt;p&gt; Il cherche ainsi à clarifier les &lt;a href=&quot;https://blogs.mediapart.fr/geographies-en-mouvement/blog/290825/amo-une-figure-africaine-enfin-visible&quot;   title=&quot;anton wilhelm Amo par le club Mediapart&quot;&gt;concepts philosophiques &lt;/a&gt;  avec rigueur, dans l’esprit des Lumières. Il s’intéresse aussi à l’épistémologie et à la relation entre sensation, jugement et connaissance, en dialogue avec les grandes doctrines de son époque, tout en gardant une position originale sur le rapport entre corps et esprit. &lt;/p&gt; &lt;p&gt; Il  est souvent relu comme une figure majeure de la philosophie africaine et de la pensée décoloniale, parce qu’il montre qu’un philosophe africain a pu participer au cœur même de la philosophie savante européenne tout en proposant une voie propre. Son importance tient autant à son œuvre qu’à sa place symbolique : celle d’un penseur noir des Lumières longtemps oublié, puis redécouvert. &lt;/p&gt; &#10; &lt;audio controls title=&quot;philosophe noir des lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-18.12.2024-ITEMA_23944950-2023C3330E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H106" r:id="rId45" display="https://www.laphilo.fr/pho/waliullah-mini.webp"/>
+    <hyperlink ref="H107" r:id="rId46" display="https://www.laphilo.fr/pho/mnorinaga-mini.webp"/>
+    <hyperlink ref="E109" r:id="rId47" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Debendranath_Tagore&quot;  title=&quot; Wikipedia&quot;&gt;Debendranath TAGORE&lt;/a&gt; était un philosophe hindou et réformateur religieux indien, figure centrale du Brahmo Samaj (Société de Brahma).  Fils de l'industriel Dwarkanath Tagore, surnommé « Prince » pour son mode de vie extravagant, et de Digambari Devi, une femme très pieuse. Il reçoit une éducation d'abord à domicile, puis à l'Anglo Hindu College, et développe un profond intérêt pour la philosophie. En 1842, il rejoint le Brahmo Samaj et en devient le leader. Avec des amis, influencé par son ami Ram Mohan Roy et sous la tutelle du Pandit Ram Chandra Vidyabageesh, il fonde la Tattwabodhini Sabha en 1839, une société intellectuelle dédiée à  &lt;a href=&quot;https://www.youtube.com/watch?v=XzVRebsCpkc&quot;  title=&quot;De Tagore reform leaders par By Ju’s Ias&quot;&gt;l'étude de la philosophie &lt;/a&gt; et de la théologie. &lt;/p&gt;&lt;p&gt; Il publie le Brahmo Dharma Beej (Graine du Dharma Brahmo) et la Tattwabodhini Patrika en 1843 comme organe officiel de sa société. Grâce à ses efforts, l'influence  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Brahmo%C3%AFsme&quot;  title=&quot;Brahmoisme par wikipedia&quot;&gt;du brahmoïsme &lt;/a&gt; se répand dans toute l'Inde En 1848, il codifie le Brahmo Dharma (aussi appelé Adi Dharma), un mouvement religieux fondé sur les principes du monothéisme et de la rationalité. &lt;/p&gt; &lt;p&gt; Il est connu pour ses réalisations spirituelles et reçoit le titre de Maharshi (« grand sage »), confirmé par le grand sage hindou qui lui rend visite. Il joue un rôle considérable dans la Renaissance du Bengale (Bengal Renaissance), mouvement de renouveau culturel, social et religieux du XIXe siècle. &lt;/p&gt; &lt;p&gt; Il a 15 enfants avec son épouse Sarada Devi, dont beaucoup deviennent des figures influentes et réussies. En 1863, il établit un ashram à Bhubandanga, appelé Santiniketan (« lieu de paix »), qui sera plus tard transformé par &lt;a href=&quot;https://www.youtube.com/watch?v=FFbQqJG7n_8&quot;  title=&quot;relation between rabindranath et son père par VIS PHILO&quot;&gt;son fils Rabindranath &lt;/a&gt;  en centre international d'éducation spirituelle et de méditation. C'est lui qui emmène jeune Rabindranath en voyage à Santiniketan puis dans l'Himalaya, lui enseignant la discipline, la liberté et la responsabilité, et lui faisant découvrir en profondeur les Upanishads. &lt;/p&gt; "/>
+    <hyperlink ref="H109" r:id="rId48" display="https://www.laphilo.fr/pho/dtagore-mini.webp"/>
+    <hyperlink ref="E110" r:id="rId49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Djem%C3%A2l_ad-D%C3%AEn_al-Afgh%C3%A2ni&quot;  title=&quot; Wikipedia&quot;&gt;Djemâm ad-Dîn al-AFGHĀNĪ&lt;/a&gt; était une figure centrale du réformisme islamique moderne, souvent considéré comme l’un des fondateurs du panislamisme et du « réformisme islamique ». Né dans une famille afghane, il a vécu et voyagé dans de nombreux pays musulmans (Inde, Égypte, Turquie, Iran, Europe), ce qui lui a permis de développer une pensée à la fois religieuse, politique et philosophique, orientée vers la résistance au colonialisme européen et la &lt;a href=&quot;https://www.lesclesdumoyenorient.com/Jamal-al-Din-al-Afghani-fondateur.html&quot;   title=&quot;Jamal al-Din al-Afghani reforme islamique par lesclesdumoyensorients&quot;&gt;rénovation de la société musulmane. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Il soutient que l’islam n’est pas incompatible avec la modernité et la raison, et qu’il a même été à l’origine d’un grand élan philosophique et scientifique dans l’histoire musulmane. Il affirme que la révélation coranique appelle à la réflexion et à la compréhension du monde, ce qui justifie, selon lui, l’usage de la raison et des sciences modernes, sans pour autant remettre en cause les fondements de la foi (unicité de Dieu, prophétie, création). &lt;a href=&quot;https://www.youtube.com/watch?v=EOTAUYYAzoE&quot;  title=&quot;Al-Afghani par TV5 monde &quot;&gt;Sa philosophie &lt;/a&gt; consiste donc à libérer l’islam de ce qu’il appelle les « superstitions » et les traditions sclérosées, tout en gardant l’essence de la doctrine religieuse. &lt;/p&gt; &lt;p&gt; Un autre pilier de sa pensée est l’appel à l’unité de la communauté musulmane (l’ūmma) face à la domination coloniale et politique occidentale. Il considère que le déclin des pays musulmans vient moins de l’islam lui‑même que de la fragmentation politique, de la tyrannie des gouvernants et de l’ignorance des élites. Pour lui, la solidarité religieuse et la conscience d’une même appartenance doivent être au cœur d’un projet de civilisation islamique moderne, capable de s’approprier les sciences européennes tout en restant fidèle à des valeurs morales communes. &lt;/p&gt; &lt;p&gt; Il est un penseur rationaliste qui refuse de séparer foi et raison, et qui place la liberté et la responsabilité de l’individu au centre de la vie morale et politique. Il critique la passivité religieuse et les gouvernements despotiques, qu’il accuse de conforter la domination étrangère ; il défend donc une réforme politique parallèle à la réforme religieuse, incluant la critique du pouvoir absolu et la promotion de débats publics. À travers ses écrits et ses discours (comme ceux menés avec son disciple Muḥammad ʿAbduh et la revue al‑ʿUrwa al‑wuṯqā), il jette les bases d’un modernisme islamique qui inspirera ensuite de nombreux mouvements réformistes et nationalistes du monde arabe et musulman. &lt;/p&gt; &#10;&#10;&#10;"/>
+    <hyperlink ref="H110" r:id="rId50" display="https://www.laphilo.fr/pho/afghani-mini.webp"/>
+    <hyperlink ref="H112" r:id="rId51" display="https://www.laphilo.fr/pho/jafirmin-mini.webp"/>
+    <hyperlink ref="E113" r:id="rId52" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Rabindranath_Tagore&quot;  title=&quot; Wikipedia&quot;&gt;Rabindranath TAGORE&lt;/a&gt; était un poète, romancier, dramaturge, philosophe et compositeur bangladais  &lt;a href=&quot;https://www.youtube.com/watch?v=q7c6zqn4L8g&quot;  title=&quot;National Anthem Tagore’s Own Voice par Gingerline Media&quot;&gt;d'expression bengalie et anglaise, &lt;/a&gt; devenu le premier non-Européen à recevoir le prix Nobel de littérature en 1913.  Né à Calcutta (Inde) dans une famille de lettrés, &lt;a href=&quot;https://agora.qc.ca/dossiers/rabindranath_tagore&quot;  title=&quot;Tagore par Agora&quot;&gt; philosophes et artistes, &lt;/a&gt;  il est le plus jeune fils de &lt;a href=&quot;https://fr.wikipedia.org/wiki/Debendranath_Tagore&quot;  title=&quot; Debendranath Tagore par wikipedia&quot;&gt; Debendranath Tagore &lt;/a&gt;, un éminent philosophe et réformateur religieux leader du Brahmo Samaj, une nouvelle secte religieuse du Bengale qui tentait de rétablir le monisme ultime de l'hindouisme tel que décrit dans les Upanishads.. Il se rend en Occident vers 1880, renonçant à tout pour « mieux aimer la nature et Dieu ». &lt;/p&gt; &lt;p&gt; Entre 1901 et 1918, il traverse d'immenses souffrances : sa femme, trois de ses enfants et son père meurent successivement. Malgré cela, il transforme sa douleur en création et fonde un centre d'éducation international à Shantiniketan (près de Calcutta) où il applique ses idéaux éducatifs inspirés des Upanishads. Ce centre devient Visva-Bharati University, un lieu dynamique qui rayonne sur toute la région puis sur toute l'Inde. &lt;/p&gt; &lt;p&gt; Il  est avant tout poète et a écrit plus de 50 volumes de poésie, dont les plus célèbres sont Manasi (1890), Sonar Tari (1894) [Le Navire d'or], Gitanjali (1910) [Offrande lyrique], Gitimalya (1914) et Balaka (1916). C'est Gitanjali, traduit en anglais par lui-même en 1912, qui le rend  &lt;a href=&quot;https://www.youtube.com/watch?v=v3iix5GSB2I&quot;  title=&quot; Drabindranath TAGORE par Eclair Brut&quot;&gt; mondialement célèbre &lt;/a&gt; et lui vaut le Nobel. Le prix lui est décerné « pour ses vers profondément sensibles, frais et beaux, par lesquels, avec une maîtrise consommée, il a fait de sa pensée poétique, exprimée en ses propres mots anglais, une partie de la littérature occidentale ». &lt;/p&gt; &lt;p&gt; Il est un philosophe humaniste dont la pensée s'enracine dans  &lt;a href=&quot;https://www.youtube.com/watch?v=S3HO9PeoqP0&quot;  title=&quot;Les Upanishads par Resumons ça&quot;&gt;les Upanishads &lt;/a&gt; et la recherche de l'Absolu comme « unique réalité de la vie ». Il participe ponctuellement au mouvement nationaliste indien, mais de manière « non sentimentale et visionnaire », et entretient une amitié avec Gandhi, qu'il considère comme le père politique de l'Inde moderne. Il rejette le nationalisme étroit et prône un universalisme spirituel, devenant « la voix de l'héritage spirituel de l'Inde » pour le monde. &lt;/p&gt; &#10;                               &lt;audio controls title=&quot;Rabindranath TAGORE  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10471-11.02.2012-ITEMA_20344077-2012C3330E0006-ITE_00049084_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="H113" r:id="rId53" display="https://www.laphilo.fr/pho/rtagore-mini.webp"/>
+    <hyperlink ref="E114" r:id="rId54" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vivekananda&quot;  title=&quot; Wikipedia&quot;&gt;VIVEKANANDA&lt;/a&gt; était l'une des figures spirituelles les plus influentes de l'Inde moderne et un ardent défenseur de la  &lt;a href=&quot;https://www.rggpodcast.fr/c%C3%A9l%C3%A9brations/swami-vivekananda/&quot;  title=&quot;Radio Gandharva gana par Rggweb&quot;&gt;philosophie vedanta&lt;/a&gt; et du yoga. Né sous le nom de Narendranath Datta à Calcutta, il est devenu un disciple du grand saint et mystique Ramakrishna Paramahamsa, un saint mystique de Dakshineswar. &lt;/p&gt; &lt;p&gt; Il croyait que toutes les religions mènent au même but ultime et que les différences ne sont que superficielles. Selon lui, chaque être humain possède en lui une étincelle divine et peut réaliser sa nature divine par la pratique spirituelle. Il a insisté sur l'importance du service désintéressé (seva) envers les pauvres et les nécessiteux, considérant cela comme une forme de culte et a plaidé pour une éducation qui combine les connaissances modernes et les valeurs spirituelles traditionnelles. &lt;/p&gt; &lt;p&gt; Il  a fondé la Ramakrishna Mission, une organisation dédiée au service social, à l'éducation et à la diffusion des enseignements spirituels.  Il  est considéré comme un pionnier du dialogue interreligieux et un inspirateur du mouvement nationaliste indien. Ses enseignements ont influencé des leaders comme Mahatma Gandhi, Subhas Chandra Bose et Aurobindo Ghosh. Il est également crédité d'avoir &lt;a href=&quot;https://blog.green-yoga.fr/vivekananda-premier-maitre-yogi-moderne/&quot;  title=&quot;Vivekananda, premier maître yogi moderne par blog-green-yoga&quot;&gt;popularisé le yoga&lt;/a&gt; et la méditation en Occident. &lt;/p&gt;"/>
+    <hyperlink ref="H114" r:id="rId55" display="https://www.laphilo.fr/pho/vivekananda-mini.webp"/>
+    <hyperlink ref="E115" r:id="rId56" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohandas_Karamchand_Gandhi&quot;  title=&quot; Wikipedia&quot;&gt;Mohandas Karamchand GANDHI&lt;/a&gt;  était un &lt;a href=&quot;https://www.youtube.com/watch?v=zTmg8qs5B_w&amp;ab_channel=Brut&quot;  title=&quot;Une vie par Brut&quot;&gt;leader spirituel&lt;/a&gt; et un militant politique Indien. Il est surtout connu pour sa lutte pacifique pour l'indépendance de l'Inde vis-à-vis du Royaume-Uni par  des désobéissances civile non-violentes contre le gouvernement britannique,  grève de la faim, manifestations et boycotts. &lt;/p&gt; &lt;p&gt;   Gandhi était surtout un philosophe qui a développé sa propre vision du monde et de la vie. &lt;a href=&quot;https://www.psychaanalyse.com/pdf/ghandi_sa_pensee.pdf&quot;   title=&quot;Livre de Gandhi&quot;&gt;Sa philosophie&lt;/a&gt; est souvent appelée &quot;satyagraha&quot;, un terme sanskrit qui signifie &quot;force de la vérité&quot; ou &quot;force de l'âme&quot;. Elle est centrée sur la non-violence, l'amour et la vérité. C'est la seule façon de résoudre les conflits de manière pacifique et durable. &lt;/p&gt; &lt;p&gt;   l croyait que chaque être humain possède une âme divine, et que cette âme est la source de notre force intérieure. Il a encouragé les gens à chercher la vérité en eux-mêmes et à suivre leur conscience plutôt que de se conformer aux normes sociales ou religieuses imposées.&lt;/p&gt; &lt;p&gt;   Il a souligné l'importance de l'autonomie et de l'autosuffisance et a encouragé les gens à vivre de manière simple, à cultiver leur propre nourriture, à produire leurs propres vêtements et à être autosuffisants autant que possible. &lt;/p&gt; &lt;p&gt;  Cette vision était basée sur le concept de &lt;a href=&quot;https://www.editionscienceetbiencommun.org/wp-content/uploads/2018/01/Swaraj-des-savoirs-un-manifeste-indien-pour-la-science-et-la-technologie-1515376288.pdf&quot;    title=&quot;Un manifeste indien&quot;&gt;&quot;swaraj&quot;&lt;/a&gt;, ou l'autonomie, qui est devenu un thème majeur de la lutte de Gandhi pour l'indépendance de l'Inde. &lt;/P&gt;  &lt;audio controls title=&quot;Mémoires de Gandhi par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-29.01.2018-ITEMA_21570326-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="H119" r:id="rId57" display="https://www.laphilo.fr/pho/coomaraswamy-mini.webp"/>
+    <hyperlink ref="E120" r:id="rId58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohamed_Iqbal&quot; title=&quot;Wikipedia&quot;&gt;Muhammad IQBAL&lt;/a&gt; était un philosophe‑poète pakistanais, poète se plaçant à la croisée de l’islam, de la modernité et de la pensée occidentale. Considéré comme l’un des  &lt;a href=&quot;https://www.saphirnews.com/Mohammed-Iqbal-un-revolutionnaire-en-islam_a24652.html&quot; title=&quot;Mohamed Iqbal, un révolutionnaire en Islam par saphirnews&quot;&gt;grands penseurs musulmans &lt;/a&gt; de son époque, il cherche à réformer l’Islam en l’ouvrant à la rationalité et à l’action, tout en restant profondément enraciné dans la tradition soufie et coranique. &lt;/p&gt; &lt;p&gt; Sa philosophie tourne autour du « Khudi » (le Soi), c’est‑à‑dire une  &lt;a href=&quot;https://www.youtube.com/watch?v=ekC6_wffi10&quot; title=&quot;Mohamed Iqbal par Perennial Wisdom&quot;&gt;individualité spirituelle forte, &lt;/a&gt; capable de se libérer de toute passivité mystique et de toute soumission fataliste. Pour lui, l’homme n’est pas appelé à s’effacer dans un tout indifférencié, mais à affirmer son moi comme centre de liberté, de volonté et de responsabilité devant Dieu, en prolongeant ainsi la dynamique de la création. &lt;/p&gt; &lt;p&gt; Il  valorise aussi une lecture active et historique de l’Islam, où la loi et la pensée religieuse ne sont pas figées, mais appelées à se réinterpréter à la lumière de l’expérience humaine et du progrès. Il milite pour une société ouverte, où la foi se traduit par l’engagement, la justice, l’éducation et la dignité du travail, plutôt que par un rigorisme puritain ou un repli identitaire. &lt;/p&gt; &lt;p&gt; Il est souvent vu comme un penseur à la fois panislamiste et humaniste : il rêve d’une communauté musulmane unifiée, mais fondée sur la liberté intérieure, la créativité individuelle et le respect de la diversité humaine. Son œuvre, surtout poétique, mêle mystique et volonté de transformer le monde, ce qui fait de lui un des premiers philosophes à articuler Islam, modernité et affirmation de soi. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Iqbal : soufisme indo-pakistanais par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-02.10.2011-ITEMA_20312518-2011C14958E0033-ITE_00045911_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="H122" r:id="rId59" display="https://www.laphilo.fr/pho/brambedkar-mini.webp"/>
+    <hyperlink ref="E123" r:id="rId60" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jiddu_Krishnamurti&quot;  title=&quot;Wikipedia&quot;&gt;Jiddu KRISHNAMURTI&lt;/a&gt;  était  un penseur indien qui a profondément marqué la réflexion sur la liberté intérieure, la conscience et l’éducation.  &lt;a href=&quot;https://citations.ouest-france.fr/citations-jiddu-krishnamurti-1049.html&quot; title=&quot;Citations Krishnamurti par citations ouest france&quot;&gt;Sa parole &lt;/a&gt; est souvent résumée par l’idée que « la vérité est un pays sans chemins » : on ne peut pas atteindre le réel par l’autorité, le dogme, le rituel ou un système de pensée tout fait.  .&lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve la critique du conditionnement psychologique. Il explique que l’être humain vit prisonnier de ses peurs, de ses habitudes, de ses croyances et des images qu’il se fabrique sur lui-même et sur les autres ; pour lui, cette prison mentale empêche de voir clairement. &lt;/p&gt; &lt;p&gt; Il ne propose pas une  &lt;a href=&quot;https://www.youtube.com/watch?v=Uk3Kdoouw-E&quot; title=&quot;Perceptions Empties consciousness : Krishnamurti &quot;&gt;méthode au sens classique, &lt;/a&gt; ni un chemin spirituel à suivre mécaniquement. À la place, il invite à une observation directe de l’esprit, sans jugement et sans choix, qu’il associe à une forme de méditation véritable ; cette attention nue permettrait de comprendre la pensée en train de se faire et de se défaire. &lt;/p&gt; &lt;p&gt; Il relie toujours la transformation individuelle au changement du monde. Il pense qu’une société plus juste ne peut naître que d’une conscience intérieure libérée de l’autorité, de la violence psychologique et de la dépendance aux systèmes ; sa philosophie est donc moins une doctrine qu’un appel à voir par soi-même, ici et maintenant. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Krishnamurti, une vie par France Culture&quot;&gt;&#10;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14090-10.10.2014-ITEMA_20678757-2014C23018S0283-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt;&#10;&lt;/audio&gt;"/>
+    <hyperlink ref="E124" r:id="rId61" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor&quot; title=&quot;Wikipedia&quot;&gt;Léopold Sédar SENGHOR&lt;/a&gt; était à la fois un grand poète-philosophe francophone et un homme d’État sénégalais, premier président de la République du Sénégal (1960–1980) et premier Africain membre de l’Académie française. Formé dans le système scolaire français, il incarne une figure hybride, à la croisée de l’Afrique et de la France, de la négritude et de la francophonie. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot;Négridude par Wikipedia&quot;&gt;« négritude », &lt;/a&gt; qu’il définit comme la reconnaissance du fait d’être noir et l’acceptation de cette identité, de son histoire, de sa culture et de sa destinée. Il en fait une valeur poétique et politique : la négritude vise à restaurer la dignité du peuple noir après la colonisation, en affirmant la beauté de la culture afro‑africaine, de ses langues, de ses rythmes et de son rapport à la vie et à la nature. &lt;/p&gt; &lt;p&gt; Dans sa poésie, il met en avant une sensibilité particulière, une « sensorialité » et une intuition qu’il oppose à la rationalité occidentale jugée plus froide, ce qui fait de ses vers une ode à la terre africaine, aux corps noirs, aux masques, aux danses et aux ancêtres. Des textes comme Femme noire ou Chants d’ombre célèbrent à la fois la femme‑enfant, la femme‑mère, la terre‑Afrique et la mémoire collective, dans une langue riche en images et en musique. &lt;/p&gt; &lt;p&gt; Par‑delà la négritude, il rêve d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=sINJIeY4UKo&quot;  title=&quot;Senghor par RTS&quot;&gt;« Civilisation de l’Universel »,&lt;/a&gt;  c’est‑à‑dire d’un monde où différentes traditions (africaines, européennes, etc.) pourraient se mêler dans un métissage créateur plutôt que s’affronter. Philosophe politique, poète et humaniste, il reste l’une des figures majeures de la littérature francophone, à la fois comme chantre de la fierté noire et comme théoricien d’un dialogue entre cultures. &lt;/p&gt; &lt;audio controls title=&quot;Senghor ‘Tu te languis’ par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21713-25.11.2025-ITEMA_24321734-2025C53416E0132-ITE_00154728_RSCE-21-996409c1a2c68ce243e4f4ef83e00211.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E125" r:id="rId62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Keiji_Nishitani&quot;  title=&quot;Wikipedia&quot;&gt;Keiji NISHITANI &lt;/a&gt; un philosophe japonais membre de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89cole_de_Kyoto&quot;  title=&quot;école de Kyoto par Wikipedia&quot;&gt;l’École de Kyoto, &lt;/a&gt;  au côté de Nishida Kitarō et Tanabe Hajime, et l’un des penseurs modernes les plus originaux sur la religion, le bouddhisme et l’expérience du néant. Il cherche à penser ensemble la crise métaphysique de la modernité occidentale et la voie spirituelle du bouddhisme, notamment le zen et le bouddhisme du Vide (śūnyatā). &lt;/p&gt; &lt;p&gt; Sa réflexion prend comme point de départ le nihilisme moderne, c’est‑à‑dire le sentiment profond que tout est vidé de sens, de valeur et d’origine absolue, auquel il confronte l’expérience bouddhique de la vacuité radicale. Selon lui, la modernité enferme l’homme dans un soi narcissique et isolé, coupé de tout fondement ultime, et ce qui surgit alors n’est pas seulement le doute, mais une « grande incertitude » qui mène au vide de soi‑même. &lt;/p&gt; &lt;p&gt; Il propose alors une  &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_2005_num_34_1_1419&quot;  title=&quot;l’un e le tout en question par Persée&quot;&gt;« conversion » spirituelle &lt;/a&gt; : le même néant qui menaçait d’anéantir l’individu peut devenir, lorsque l’on cesse de le fuir, le point de départ d’une nouvelle compréhension du religieux, où le soi s’efface au profit d’une ouverture à l’être tout entier. Pour lui, la religion ne se réduit ni à dogme, ni à institution, ni à simple psychologie, mais à une expérience où le sujet, au cœur de sa plus grande déréliction, découvre que le monde peut être habité de sacrement, de manière « immanemment sainte ». &lt;/p&gt; &lt;p&gt; Il s’inscrit dans une entreprise de « philosophie entre Orient et Occident », où la pensée occidentale rencontre la tradition bouddhique pour repenser ensemble l’être, le mal, la liberté et la responsabilité. À travers des ouvrages comme Religion et néant (Religion and Nothingness), il devient l’une des figures clés du dialogue philosophique et religieux entre Asie et Europe, articulant la crise de la modernité et la possibilité d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=Ak12Fplzo0U&quot;  title=&quot;The void is not the end Nishitani Keiji par NullSOPHY&quot;&gt;renaissance spirituelle &lt;/a&gt; fondée sur la vacuité éclairée. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H126" r:id="rId63" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
+    <hyperlink ref="E128" r:id="rId64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E129" r:id="rId65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E130" r:id="rId66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H130" r:id="rId67" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
+    <hyperlink ref="H139" r:id="rId68" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -5187,15 +5187,15 @@
       </c>
     </row>
     <row r="76" ht="157.5" customHeight="1" s="25">
-      <c r="A76" s="30" t="n">
-        <v>1130</v>
-      </c>
-      <c r="B76" s="30" t="n">
-        <v>1200</v>
+      <c r="A76" s="30">
+        <v>1139</v>
+      </c>
+      <c r="B76" s="30">
+        <v>1193</v>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>1130 — 1200</t>
+          <t>1139 — 1193</t>
         </is>
       </c>
       <c r="D76" s="31" t="inlineStr">
@@ -6234,15 +6234,15 @@
       </c>
     </row>
     <row r="93" ht="338.25" customHeight="1" s="25">
-      <c r="A93" s="30" t="n">
-        <v>1440</v>
-      </c>
-      <c r="B93" s="30" t="n">
-        <v>1518</v>
+      <c r="A93" s="30">
+        <v>1498</v>
+      </c>
+      <c r="B93" s="30">
+        <v>1547</v>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>1440 - 1518</t>
+          <t>1498 – 1547</t>
         </is>
       </c>
       <c r="D93" s="31" t="inlineStr">
@@ -6792,15 +6792,15 @@
       </c>
     </row>
     <row r="102" ht="255.75" customHeight="1" s="25">
-      <c r="A102" s="23" t="n">
-        <v>1633</v>
-      </c>
-      <c r="B102" s="23" t="n">
-        <v>1682</v>
+      <c r="A102" s="23">
+        <v>1610</v>
+      </c>
+      <c r="B102" s="23">
+        <v>1695</v>
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
-          <t>1633 — 1682</t>
+          <t>1610 — 1695</t>
         </is>
       </c>
       <c r="D102" s="24" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="C114" s="23" t="inlineStr">
         <is>
-          <t>1238 — 1317</t>
+          <t>1863 — 1902</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="C117" s="23" t="inlineStr">
         <is>
-          <t>1895 — 1986</t>
+          <t>1872 — 1950</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr">

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9.869999999999999" customWidth="1" style="23" min="1" max="1"/>
@@ -728,6 +728,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="262.5" customHeight="1" s="25">
       <c r="A4" s="30" t="n">
@@ -2573,7 +2578,7 @@
       </c>
       <c r="D34" s="31" t="inlineStr">
         <is>
-          <t>HILLET Hazaken</t>
+          <t xml:space="preserve">HILLEL Hazaken</t>
         </is>
       </c>
       <c r="E34" s="32" t="inlineStr">
@@ -2617,6 +2622,11 @@
       <c r="M34" s="24" t="inlineStr">
         <is>
           <t>religieux érudit juif qui développa la tradition juive de façon structurée.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>
@@ -2809,6 +2819,11 @@
       <c r="M37" s="24" t="inlineStr">
         <is>
           <t>philosophe juif qui développa la Torah orale.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>
@@ -5306,6 +5321,11 @@
       <c r="M77" s="24" t="inlineStr">
         <is>
           <t>philosophe et médecin érudit juif.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -8363,7 +8363,7 @@
       </c>
       <c r="C128" s="23" t="inlineStr">
         <is>
-          <t>1909 — 1966</t>
+          <t xml:space="preserve">1917 — 1993</t>
         </is>
       </c>
       <c r="D128" s="24" t="inlineStr">

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -733,6 +733,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="O3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="P3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="262.5" customHeight="1" s="25">
       <c r="A4" s="30" t="n">
@@ -797,6 +807,11 @@
           <t>philosophe égyptien et le premier architecte et ingénieur de l'histoire.</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="220.5" customHeight="1" s="25">
       <c r="A5" s="30" t="n">
@@ -856,6 +871,11 @@
       <c r="M5" s="24" t="inlineStr">
         <is>
           <t>philosophe égyptien et le premier à avoir écrit un recueil de sagesse.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
         </is>
       </c>
     </row>
@@ -922,6 +942,11 @@
           <t>pharaon égyptien visionnaire qui a su rétablir l'ordre et la stabilité en Égypte.</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="229.5" customHeight="1" s="25">
       <c r="A7" s="23" t="n">
@@ -979,6 +1004,14 @@
         <is>
           <t>sage fondateur traditionnel de l'école Nyâya, logique et épistémologie indiennes.</t>
         </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="314.25" customHeight="1" s="25">
@@ -1044,6 +1077,11 @@
           <t>roi mésopotamien et personnage principal de "l'épopée de Gilgamesh".</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="128.25" customHeight="1" s="25">
       <c r="A9" s="23" t="n">
@@ -1102,6 +1140,11 @@
           <t>sage-voyant védique, compositeur traditionnel d'hymnes du Rig-Véda, figure fondatrice du védisme.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="147.75" customHeight="1" s="25">
       <c r="A10" s="30" t="n">
@@ -1163,6 +1206,11 @@
           <t>philosophe égyptien qui développa des idées sur l'ordre cosmique.</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="318.75" customHeight="1" s="25">
       <c r="A11" s="30" t="n">
@@ -1223,6 +1271,11 @@
           <t>philosophe de l’Inde védique connue principalement grâce à la Bṛhadāraṇyaka Upaniṣad.</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="71.25" customHeight="1" s="25">
       <c r="A12" s="23" t="n">
@@ -1281,6 +1334,11 @@
           <t>sage des Upanishads, fondateur de la réflexion brahmanique sur l'ātman et le brahman.</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="352.5" customHeight="1" s="25">
       <c r="A13" s="30" t="n">
@@ -1341,6 +1399,11 @@
           <t xml:space="preserve"> philosophe et débatteuse de l’Inde védique qui y apparaît comme une brahmavādin.</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="303.75" customHeight="1" s="25">
       <c r="A14" s="30" t="n">
@@ -1402,6 +1465,11 @@
           <t>figure mythique égypto-grecque père de l'Hermétisme et fondateur de l'alchimie.</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="184.5" customHeight="1" s="25">
       <c r="A15" s="23" t="n">
@@ -1460,6 +1528,11 @@
           <t>fondateur traditionnel de l'école Vaisheshika, physique atomiste indienne.</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="140.25" customHeight="1" s="25">
       <c r="A16" s="23" t="n">
@@ -1518,6 +1591,11 @@
           <t>sage fondateur traditionnel du Sâmkhya, dualisme conscience/matière de la philosophie indienne.</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="155.25" customHeight="1" s="25">
       <c r="A17" s="23" t="n">
@@ -1574,6 +1652,11 @@
       <c r="M17" s="24" t="inlineStr">
         <is>
           <t>fondateur légendaire du Lokâyata (Cârvâka), matérialisme et athéisme indiens.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -1640,6 +1723,14 @@
           <t>philosophe indien et enseignant spirituel du jaïnisme.</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" ht="252" customHeight="1" s="25">
       <c r="A19" s="30" t="n">
@@ -1702,6 +1793,14 @@
           <t>philosophe chinois considéré comme le fondateur de la doctrine Taoïste.</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" ht="252" customHeight="1" s="25">
       <c r="A20" s="30" t="n">
@@ -1762,6 +1861,14 @@
         <is>
           <t>philosophe indien connu sous le nom de Bouddha et enseignant du bouddhisme.</t>
         </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P20">
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="281.25" customHeight="1" s="25">
@@ -1825,6 +1932,11 @@
           <t>considéré comme l'auteur des Yoga Sutras, un texte fondamental du yoga classique.</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="252" customHeight="1" s="25">
       <c r="A22" s="30" t="n">
@@ -1887,6 +1999,14 @@
           <t>philosophe chinois fondateur du Confucianisme.</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" ht="394.5" customHeight="1" s="25">
       <c r="A23" s="30" t="n">
@@ -1947,6 +2067,11 @@
           <t>philosophe et stratège militaire chinois auteur de « l’art de la guerre ».</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="153.75" customHeight="1" s="25">
       <c r="A24" s="23" t="n">
@@ -2005,6 +2130,11 @@
           <t>fondateur de l'Ajîvika, déterminisme absolu dans la philosophie indienne ancienne.</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="219.75" customHeight="1" s="25">
       <c r="A25" s="30" t="n">
@@ -2065,6 +2195,14 @@
           <t>philosophe confucéen majeur de la période des Royaumes combattants en Chine.</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P25">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" ht="220.5" customHeight="1" s="25">
       <c r="A26" s="30" t="n">
@@ -2127,6 +2265,14 @@
           <t>philosophe chinois, fondateur du mohisme, une école rivale du confucianisme.</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" ht="134.25" customHeight="1" s="25">
       <c r="A27" s="23" t="n">
@@ -2183,6 +2329,11 @@
       <c r="M27" s="24" t="inlineStr">
         <is>
           <t>auteur traditionnel des Mîmâmsâ-sûtras, herméneutique védique indienne.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -2248,6 +2399,14 @@
         <is>
           <t>philosophe chinois qui développa le taoïsme avec une vision relativiste.</t>
         </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P28">
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="211.5" customHeight="1" s="25">
@@ -2315,6 +2474,14 @@
           <t>philosophe chinois qui développa la pensée Confucianiste.</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P29">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" ht="285" customHeight="1" s="25">
       <c r="A30" s="30" t="n">
@@ -2375,6 +2542,11 @@
           <t>penseur politique, économiste et stratège indien antique.</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="285.75" customHeight="1" s="25">
       <c r="A31" s="23" t="n">
@@ -2433,6 +2605,11 @@
           <t>philosophe chinois célèbre pour ses paradoxes logiques.</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="252" customHeight="1" s="25">
       <c r="A32" s="30" t="n">
@@ -2493,6 +2670,11 @@
       <c r="M32" s="24" t="inlineStr">
         <is>
           <t>philosophe et penseur politique chinois précurseur de Machiavel.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
     </row>
@@ -2561,6 +2743,11 @@
           <t>philosophe chinois qui établit le confucianisme comme idéologie d'État.</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="262.5" customHeight="1" s="25">
       <c r="A34" s="30" t="n">
@@ -2627,6 +2814,11 @@
       <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -2695,6 +2887,11 @@
           <t>philosophe chinois, penseur rationaliste et sceptique, en avance sur son temps.</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="168" customHeight="1" s="25">
       <c r="A36" s="30" t="n">
@@ -2754,6 +2951,11 @@
       <c r="M36" s="24" t="inlineStr">
         <is>
           <t>philosophe chinois considéré comme le fondateur du Taoïsme religieux.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
     </row>
@@ -2826,6 +3028,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="220.5" customHeight="1" s="25">
       <c r="A38" s="30" t="n">
@@ -2890,6 +3097,11 @@
           <t>philosophe jaïn ancien et père de la tradition jaïne digambara.</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="231" customHeight="1" s="25">
       <c r="A39" s="30" t="n">
@@ -2954,6 +3166,14 @@
           <t>philosophe et maître Bouddhiste indien qui se concentra sur la Vacuité.</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P39">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" ht="168" customHeight="1" s="25">
       <c r="A40" s="30" t="n">
@@ -3016,6 +3236,11 @@
           <t>philosophe persan connu pour avoir fondé le Manichéisme.</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="283.5" customHeight="1" s="25">
       <c r="A41" s="30" t="n">
@@ -3077,6 +3302,11 @@
           <t>philosophe chinois fondateur du néo-taoïsme.</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="294" customHeight="1" s="25">
       <c r="A42" s="30" t="n">
@@ -3137,6 +3367,11 @@
       <c r="M42" s="24" t="inlineStr">
         <is>
           <t>philosophe chinois célèbre pour ses contributions à la philosophie taoïste.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
     </row>
@@ -3201,6 +3436,11 @@
       <c r="M43" s="24" t="inlineStr">
         <is>
           <t>philosophe indien clé dans le développement du bouddhisme Mahāyāna en Inde.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -3272,6 +3512,14 @@
           <t>philosophe indien connu pour ses contributions majeures au bouddhisme.</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" ht="164.25" customHeight="1" s="25">
       <c r="A45" s="23" t="n">
@@ -3330,6 +3578,11 @@
           <t>commentateur et systématisateur du bouddhisme Theravâda, auteur du Visuddhimagga.</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="345" customHeight="1" s="25">
       <c r="A46" s="30" t="n">
@@ -3391,6 +3644,11 @@
           <t>philosophe et moine bouddhiste ayant introduit la philosophie de la vacuité en Chine.</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="235.5" customHeight="1" s="25">
       <c r="A47" s="30" t="n">
@@ -3450,6 +3708,11 @@
       <c r="M47" s="24" t="inlineStr">
         <is>
           <t>philosophe arménien fondateur de la philosophie arménienne médiévale.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3518,6 +3781,11 @@
           <t>Réformateur religieux et social iranien qui fonda le mazdakisme.</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="314.25" customHeight="1" s="25">
       <c r="A49" s="30" t="n">
@@ -3583,6 +3851,11 @@
           <t>philosophe indien penseur central du bouddhisme mahayana.</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="283.5" customHeight="1" s="25">
       <c r="A50" s="30" t="n">
@@ -3644,6 +3917,11 @@
           <t>moine bouddhiste chinois et l'un des grands traducteurs de soutras bouddhiques.</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="208.5" customHeight="1" s="25">
       <c r="A51" s="23" t="n">
@@ -3700,6 +3978,11 @@
       <c r="M51" s="24" t="inlineStr">
         <is>
           <t>fondateur du mutazilisme, théologie rationaliste de l'islam.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -3764,6 +4047,11 @@
       <c r="M52" s="24" t="inlineStr">
         <is>
           <t>philosophe arabe considéré comme le "père de la chimie".</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -3831,6 +4119,11 @@
           <t>philosophe érudit anglais qui a eu une grande influence sur l'éducation en Europe.</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="178.5" customHeight="1" s="25">
       <c r="A54" s="30" t="n">
@@ -3895,6 +4188,11 @@
           <t>philosophe chinois qui marqua la littérature chinoise du VIIIe et XIIe siècles.</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="347.25" customHeight="1" s="25">
       <c r="A55" s="30" t="n">
@@ -3956,6 +4254,11 @@
           <t>philosophe et sage fondateur japonais, initiateur du bouddhisme Shingon.</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="261.75" customHeight="1" s="25">
       <c r="A56" s="30" t="n">
@@ -4015,6 +4318,11 @@
       <c r="M56" s="24" t="inlineStr">
         <is>
           <t>mathématicien, penseur et astronome perse père de l'algèbre.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -4086,6 +4394,14 @@
           <t>philosophe indien qui accomplit sa mission de revitaliser l'hindouisme.</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P57">
+        <v>3</v>
+      </c>
     </row>
     <row r="58" ht="220.5" customHeight="1" s="25">
       <c r="A58" s="30" t="n">
@@ -4146,6 +4462,11 @@
           <t>philosophe indien connu pour ses travaux sur l’Advaita Vedānta.</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="199.5" customHeight="1" s="25">
       <c r="A59" s="30" t="n">
@@ -4207,6 +4528,14 @@
           <t>philosophe arabe considéré comme le père de la philosophie arabe.</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P59">
+        <v>3</v>
+      </c>
     </row>
     <row r="60" ht="231" customHeight="1" s="25">
       <c r="A60" s="30" t="n">
@@ -4266,6 +4595,11 @@
       <c r="M60" s="24" t="inlineStr">
         <is>
           <t>philosophe arabe qui développa une philosophie de la médecine.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -4333,6 +4667,14 @@
           <t>philosophe iranien qui permit la transmission de la philosophie grecque dans le monde islamique.</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P61">
+        <v>3</v>
+      </c>
     </row>
     <row r="62" ht="180" customHeight="1" s="25">
       <c r="A62" s="30" t="n">
@@ -4392,6 +4734,11 @@
       <c r="M62" s="24" t="inlineStr">
         <is>
           <t>philosophe indien qui développa la philosophie du Shivaisme Cachemirien.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -4456,6 +4803,11 @@
       <c r="M63" s="24" t="inlineStr">
         <is>
           <t>philosophe et mystique indien dans la tradition non dualiste du Shivaïsme.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -4526,6 +4878,11 @@
           <t>Figure mythologique de la culture Toltèque d'où sont issus les « Quatre Accords toltèques ».</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="251.25" customHeight="1" s="25">
       <c r="A65" s="30" t="n">
@@ -4586,6 +4943,11 @@
           <t>philosophe afghan appelé "le maître de l’an mille" dans l’histoire des sciences.</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="228.75" customHeight="1" s="25">
       <c r="A66" s="30" t="n">
@@ -4648,6 +5010,14 @@
         <is>
           <t>philosophe et médecin persan dit 'le prince des savants'.</t>
         </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P66">
+        <v>3</v>
       </c>
     </row>
     <row r="67" ht="174.75" customHeight="1" s="25">
@@ -4711,6 +5081,11 @@
           <t>philosophe et théologien indien majeur du courant viśiṣṭādvaita.</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="307.5" customHeight="1" s="25">
       <c r="A68" s="30" t="n">
@@ -4770,6 +5145,11 @@
           <t>philosophe néo-confucéen chinois de la dynastie Song.</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="304.5" customHeight="1" s="25">
       <c r="A69" s="30" t="n">
@@ -4830,6 +5210,11 @@
           <t>mathématicien et philosophe persan qui réforme le calendrier persan.</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="282" customHeight="1" s="25">
       <c r="A70" s="30" t="n">
@@ -4892,6 +5277,14 @@
           <t>philosophe persan l'un des plus grands penseurs soufis de l'islam.</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P70">
+        <v>3</v>
+      </c>
     </row>
     <row r="71" ht="241.5" customHeight="1" s="25">
       <c r="A71" s="30" t="n">
@@ -4953,6 +5346,11 @@
           <t>philosophe andalou qui voulut concilier Aristote avec la spiritualité islamique.</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="316.5" customHeight="1" s="25">
       <c r="A72" s="30" t="n">
@@ -5012,6 +5410,11 @@
       <c r="M72" s="24" t="inlineStr">
         <is>
           <t>philosophe autodidacte musulman andalou mais également médecin et poète.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -5078,6 +5481,14 @@
           <t>philosophe musulman andalou important de la civilisation islamique.</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P73">
+        <v>3</v>
+      </c>
     </row>
     <row r="74" ht="314.25" customHeight="1" s="25">
       <c r="A74" s="30" t="n">
@@ -5139,6 +5550,11 @@
           <t>philosophe et mystique soufi perse important dans la spiritualité iranienne.</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="167.25" customHeight="1" s="25">
       <c r="A75" s="30" t="n">
@@ -5200,6 +5616,14 @@
           <t>philosophe chinois qui a revitalisé le confucianisme en Chine.</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P75">
+        <v>3</v>
+      </c>
     </row>
     <row r="76" ht="157.5" customHeight="1" s="25">
       <c r="A76" s="30">
@@ -5257,6 +5681,11 @@
       <c r="M76" s="24" t="inlineStr">
         <is>
           <t>philosophe chinois et grand rival de Zhu Xi dans le néoconfucianisme des Song.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
     </row>
@@ -5328,6 +5757,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P77">
+        <v>3</v>
+      </c>
     </row>
     <row r="78" ht="294" customHeight="1" s="25">
       <c r="A78" s="30" t="n">
@@ -5390,6 +5827,14 @@
           <t>philosophe perse fondateur du courant de la sagesse illuminative (Ishrâq).</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P78">
+        <v>3</v>
+      </c>
     </row>
     <row r="79" ht="345" customHeight="1" s="25">
       <c r="A79" s="30" t="n">
@@ -5452,6 +5897,14 @@
           <t>philosophe soufi arabo-andalou dont l'oeuvre domine la spiritualité islamique.</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P79">
+        <v>3</v>
+      </c>
     </row>
     <row r="80" ht="204" customHeight="1" s="25">
       <c r="A80" s="30" t="n">
@@ -5512,6 +5965,11 @@
           <t>figure du bouddhisme japonais et le fondateur du "Jōdo Shinshū".</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="226.5" customHeight="1" s="25">
       <c r="A81" s="30" t="n">
@@ -5572,6 +6030,14 @@
           <t>philosophe et grand maître du zen japonais et le fondateur de l’école Sōtō au Japon.</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
     </row>
     <row r="82" ht="206.25" customHeight="1" s="25">
       <c r="A82" s="30" t="n">
@@ -5632,6 +6098,11 @@
       <c r="M82" s="24" t="inlineStr">
         <is>
           <t>polymath persan, un des plus grands penseurs musulmans de son époque.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -5699,6 +6170,14 @@
           <t>philosophe mystique perse qui fut une figure centrale du Soufisme.</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P83">
+        <v>3</v>
+      </c>
     </row>
     <row r="84" ht="303.75" customHeight="1" s="25">
       <c r="A84" s="30" t="n">
@@ -5762,6 +6241,11 @@
           <t>philosophe hindou fondateur de l'école Dvaita (dualiste) du Vedanta.</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="62.25" customHeight="1" s="25">
       <c r="A85" s="23" t="n">
@@ -5821,6 +6305,11 @@
           <t>philosophe byzantin figure centrale de la tradition mystique de l'Église orthodoxe.</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="296.25" customHeight="1" s="25">
       <c r="A86" s="30" t="n">
@@ -5878,6 +6367,11 @@
       <c r="M86" s="24" t="inlineStr">
         <is>
           <t>philosophe persan considéré comme le plus grand maître du Ghazal.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -5945,6 +6439,14 @@
           <t>philosophe arabe précurseur de la sociologie moderne.</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P87">
+        <v>3</v>
+      </c>
     </row>
     <row r="88" ht="199.5" customHeight="1" s="25">
       <c r="A88" s="30" t="n">
@@ -6006,6 +6508,11 @@
           <t>philosophe byzantin introducteur de la culture grecque dans la Renaissance italienne.</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="233.25" customHeight="1" s="25">
       <c r="A89" s="30" t="n">
@@ -6067,6 +6574,14 @@
           <t>philosophe hindou qui réforma le bouddhisme tibétain.</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P89">
+        <v>3</v>
+      </c>
     </row>
     <row r="90" ht="139.5" customHeight="1" s="25">
       <c r="A90" s="23" t="n">
@@ -6125,6 +6640,11 @@
           <t>lettré et homme d'État vietnamien, figure de la synthèse Tam Giáo (confucianisme, bouddhisme, taoïsme).</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="219" customHeight="1" s="25">
       <c r="A91" s="30" t="n">
@@ -6184,6 +6704,11 @@
       <c r="M91" s="24" t="inlineStr">
         <is>
           <t>philosophe et roi, grand penseur de la civilisation aztèque.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
     </row>
@@ -6252,6 +6777,11 @@
           <t>mystique indien prônant une spiritualité universelle.</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="338.25" customHeight="1" s="25">
       <c r="A93" s="30">
@@ -6310,6 +6840,11 @@
       <c r="M93" s="24" t="inlineStr">
         <is>
           <t>poétesse mystique indienne, souvent présentée comme une sainte du Bhakti.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
     </row>
@@ -6378,6 +6913,14 @@
           <t>philosophe chinois du courant néo-confucianiste.</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P94">
+        <v>3</v>
+      </c>
     </row>
     <row r="95" ht="145.5" customHeight="1" s="25">
       <c r="A95" s="23" t="n">
@@ -6435,6 +6978,14 @@
         <is>
           <t>plus grand représentant du confucianisme coréen, théoricien du néoconfucianisme de Corée.</t>
         </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P95">
+        <v>3</v>
       </c>
     </row>
     <row r="96" ht="241.5" customHeight="1" s="25">
@@ -6500,6 +7051,11 @@
           <t>philosophe chinois qui proclame la légitimité des désirs .</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="314.25" customHeight="1" s="25">
       <c r="A97" s="30" t="n">
@@ -6561,6 +7117,14 @@
           <t>philosophe et mystique de la tradition islamique.</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P97">
+        <v>3</v>
+      </c>
     </row>
     <row r="98" ht="318.75" customHeight="1" s="25">
       <c r="A98" s="30" t="n">
@@ -6621,6 +7185,11 @@
       <c r="M98" s="24" t="inlineStr">
         <is>
           <t>philosophe et intellectuel japonais qui prôna l'établissement du néoconfucianisme.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
     </row>
@@ -6689,6 +7258,14 @@
           <t>philosophe africain et l'un des premiers rationalistes.</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P99">
+        <v>3</v>
+      </c>
     </row>
     <row r="100" ht="199.5" customHeight="1" s="25">
       <c r="A100" s="30" t="n">
@@ -6750,6 +7327,11 @@
           <t>philosophe mongol qui chercha des convergences entre hindouisme et islam.</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="177" customHeight="1" s="25">
       <c r="A101" s="23" t="n">
@@ -6810,6 +7392,11 @@
           <t>stratège et philosophe japonais, fondateur du Bushidō, le code moral des samouraïs.</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="255.75" customHeight="1" s="25">
       <c r="A102" s="23">
@@ -6869,6 +7456,11 @@
           <t>philosophe considéré comme un pionnier de la pensée politique chinoise.</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="225" customHeight="1" s="25">
       <c r="A103" s="23" t="n">
@@ -6930,6 +7522,11 @@
           <t>philosophe japonais représentant du néoconfucianisme au Japon.</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="165" customHeight="1" s="25">
       <c r="A104" s="23" t="n">
@@ -6988,6 +7585,11 @@
           <t>érudit coréen, figure fondatrice du Silhak sous la dynastie Joseon.</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="54" customHeight="1" s="25">
       <c r="A105" s="23" t="n">
@@ -7048,6 +7650,16 @@
           <t>philosophe subsaharien 1er à avoir obtenu un doctorat dans une université européenne.</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="279.75" customHeight="1" s="25">
       <c r="A106" s="23" t="n">
@@ -7107,6 +7719,16 @@
           <t>philosophe indien et réformateur clé de l'islam dans le sous-continent.</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="427.5" customHeight="1" s="25">
       <c r="A107" s="23" t="n">
@@ -7165,6 +7787,11 @@
           <t>philologue japonais, figure majeure du Kokugaku et de l'étude du Kojiki.</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="262.5" customHeight="1" s="25">
       <c r="A108" s="23" t="n">
@@ -7223,6 +7850,11 @@
           <t>philosophe et réformateur indien considéré comme le père de la Renaissance indienne.</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="63" customHeight="1" s="25">
       <c r="A109" s="23" t="n">
@@ -7282,6 +7914,14 @@
           <t>philosophe hindou et réformateur religieux indien, figure centrale du Brahmo Samaj.</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P109">
+        <v>3</v>
+      </c>
     </row>
     <row r="110" ht="58.5" customHeight="1" s="25">
       <c r="A110" s="23" t="n">
@@ -7341,6 +7981,11 @@
           <t>philosophe afghan et figure centrale du réformisme islamique moderne.</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="291" customHeight="1" s="25">
       <c r="A111" s="23" t="n">
@@ -7400,6 +8045,11 @@
           <t>penseur du Japon moderne, souvent surnommé le 'Rousseau de l’Orient'.</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="281.25" customHeight="1" s="25">
       <c r="A112" s="23" t="n">
@@ -7459,6 +8109,11 @@
           <t>penseur haïtien et l’un des premiers penseurs noirs de la science de l’homme moderne.</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="92.25" customHeight="1" s="25">
       <c r="A113" s="23" t="n">
@@ -7519,6 +8174,14 @@
           <t>philosophe humaniste indien dont la pensée s'enracine dans les Upanishads et la recherche de l'Absolu.</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P113">
+        <v>3</v>
+      </c>
     </row>
     <row r="114" ht="153.75" customHeight="1" s="25">
       <c r="A114" s="23" t="n">
@@ -7579,6 +8242,14 @@
           <t>philosophe indien qui a popularisé le yoga et la méditation en Occident.</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P114">
+        <v>3</v>
+      </c>
     </row>
     <row r="115" ht="98.25" customHeight="1" s="25">
       <c r="A115" s="23" t="n">
@@ -7639,6 +8310,14 @@
           <t>philosophe indien connu pour sa lutte pacifique pour la non-violence.</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P115">
+        <v>3</v>
+      </c>
     </row>
     <row r="116" ht="311.25" customHeight="1" s="25">
       <c r="A116" s="23" t="n">
@@ -7697,6 +8376,14 @@
         <is>
           <t>philosophe et figure centrale de la pensée moderne japonaise.</t>
         </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P116">
+        <v>3</v>
       </c>
     </row>
     <row r="117" ht="292.5" customHeight="1" s="25">
@@ -7762,6 +8449,14 @@
           <t>philosophe indien qui a développé une vision intégrale de l'évolution humaine.</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P117">
+        <v>3</v>
+      </c>
     </row>
     <row r="118" ht="306.75" customHeight="1" s="25">
       <c r="A118" s="23" t="n">
@@ -7821,6 +8516,11 @@
           <t xml:space="preserve"> philosophe et chorégraphe d'origine gréco-arménienne, figure influente du mysticisme.</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="291.75" customHeight="1" s="25">
       <c r="A119" s="23" t="n">
@@ -7881,6 +8581,16 @@
           <t>philosophe srilankais traditionnaliste, historien de l’art, critique de la modernité.</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="45.75" customHeight="1" s="25">
       <c r="A120" s="23" t="n">
@@ -7940,6 +8650,16 @@
           <t>philosophe‑poète pakistanais entre l’islam, la modernité &amp; la pensée occidentale.</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="236.25" customHeight="1" s="25">
       <c r="A121" s="23" t="n">
@@ -7999,6 +8719,11 @@
           <t>philosophe et maître spirituel de la tradition de l’Advaita Vedānta.</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="350.25" customHeight="1" s="25">
       <c r="A122" s="23" t="n">
@@ -8056,6 +8781,14 @@
         <is>
           <t>juriste et philosophe indien, architecte de la Constitution, fondateur de la philosophie Dalit.</t>
         </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P122">
+        <v>3</v>
       </c>
     </row>
     <row r="123" ht="47.25" customHeight="1" s="25">
@@ -8118,6 +8851,11 @@
           <t>penseur indien axé sur la liberté intérieure, la conscience et l’éducation.</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="57.75" customHeight="1" s="25">
       <c r="A124" s="23" t="n">
@@ -8176,6 +8914,14 @@
           <t>poète-philosophe francophone et homme d’État sénégalais.</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P124">
+        <v>3</v>
+      </c>
     </row>
     <row r="125" ht="38.25" customHeight="1" s="25">
       <c r="A125" s="23" t="n">
@@ -8235,6 +8981,11 @@
           <t>philosophe japonais membre de l’École de Kyoto &amp; penseur moderne.</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="79.5" customHeight="1" s="25">
       <c r="A126" s="23" t="n">
@@ -8293,6 +9044,14 @@
           <t>homme d'État et philosophe ghanéen, théoricien du consciencisme et figure du panafricanisme.</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P126">
+        <v>3</v>
+      </c>
     </row>
     <row r="127" ht="236.25" customHeight="1" s="25">
       <c r="A127" s="23" t="n">
@@ -8351,6 +9110,14 @@
           <t>écrivain, homme politique et penseur martiniquais, cofondateur du mouvement de la "négritude".</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P127">
+        <v>3</v>
+      </c>
     </row>
     <row r="128" ht="65.25" customHeight="1" s="25">
       <c r="A128" s="23" t="n">
@@ -8413,6 +9180,16 @@
           <t>philosophe marxiste vietnamien qui s'intéresse à la conscience.</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="61.5" customHeight="1" s="25">
       <c r="A129" s="23" t="n">
@@ -8472,6 +9249,14 @@
           <t>intellectuel sénégalais fondateur de l’historicité de l’Afrique et de la pensée afrocentrée.</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P129">
+        <v>3</v>
+      </c>
     </row>
     <row r="130" ht="48" customHeight="1" s="25">
       <c r="A130" s="23" t="n">
@@ -8530,6 +9315,14 @@
           <t>penseur anticolonialiste devenu psychiatre, militant pour l'indépendance algérienne.</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P130">
+        <v>3</v>
+      </c>
     </row>
     <row r="131" ht="272.25" customHeight="1" s="25">
       <c r="A131" s="23" t="n">
@@ -8590,6 +9383,11 @@
           <t>philosophe camerounais qui interroge la place de la philosophie dans l'Afrique actuelle.</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="307.5" customHeight="1" s="25">
       <c r="A132" s="23" t="n">
@@ -8651,6 +9449,14 @@
           <t>philosophe ghanéen associé à la réflexion sur la décolonisation conceptuelle.</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P132">
+        <v>3</v>
+      </c>
     </row>
     <row r="133" ht="248.25" customHeight="1" s="25">
       <c r="A133" s="23" t="n">
@@ -8711,6 +9517,11 @@
           <t>philosophe camerounais contribuant au développement d'une théologie chrétienne africaine.</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="328.5" customHeight="1" s="25">
       <c r="A134" s="23" t="n">
@@ -8772,6 +9583,11 @@
           <t>première femme nigériane à obtenir un doctorat en philosophie dans son pays.</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="323.25" customHeight="1" s="25">
       <c r="A135" s="23" t="n">
@@ -8833,6 +9649,11 @@
           <t>philosophe marocain et penseur important de la pensée arabe contemporaine.</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="347.25" customHeight="1" s="25">
       <c r="A136" s="23" t="n">
@@ -8892,6 +9713,11 @@
           <t>intellectuel Sioux activiste pour les droits des peuples autochtones d’Amérique du Nord.</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="351.75" customHeight="1" s="25">
       <c r="A137" s="23" t="n">
@@ -8952,6 +9778,11 @@
           <t>philosophe congolais critique des représentations occidentales de l'Afrique.</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="303" customHeight="1" s="25">
       <c r="A138" s="23" t="n">
@@ -9013,6 +9844,14 @@
           <t>philosophe africain engagé sur la critique de l'ethnophilosophie.</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P138">
+        <v>3</v>
+      </c>
     </row>
     <row r="139" ht="251.25" customHeight="1" s="25">
       <c r="A139" s="23" t="n">
@@ -9073,6 +9912,11 @@
       <c r="M139" s="24" t="inlineStr">
         <is>
           <t>philosophe égyptien islamologue moderne, critique du discours religieux.</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -1010,9 +1010,7 @@
           <t xml:space="preserve">inde</t>
         </is>
       </c>
-      <c r="P7">
-        <v>3</v>
-      </c>
+      <c r="P7"/>
     </row>
     <row r="8" ht="314.25" customHeight="1" s="25">
       <c r="A8" s="30" t="n">
@@ -7919,9 +7917,7 @@
           <t xml:space="preserve">inde</t>
         </is>
       </c>
-      <c r="P109">
-        <v>3</v>
-      </c>
+      <c r="P109"/>
     </row>
     <row r="110" ht="58.5" customHeight="1" s="25">
       <c r="A110" s="23" t="n">

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:P159"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9.869999999999999" customWidth="1" style="23" min="1" max="1"/>
@@ -9917,41 +9917,992 @@
       </c>
     </row>
     <row r="140" ht="128.25" customHeight="1" s="25">
-      <c r="D140" s="23" t="n"/>
-      <c r="E140" s="23" t="n"/>
-      <c r="K140" s="23" t="n"/>
-      <c r="L140" s="23" t="n"/>
-      <c r="M140" s="23" t="n"/>
+      <c r="A140" s="23">
+        <v>-2600</v>
+      </c>
+      <c r="B140" s="23">
+        <v>-2540</v>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 2600 A JC</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAGEMNI</t>
+        </is>
+      </c>
+      <c r="E140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kagemni_(vizir_de_Snéfrou)"  title=" Wikipedia"&gt;KAGEMNI&lt;/a&gt; était un vizir de l'Ancien Empire égyptien, au service du pharaon Snéfrou (vers 2613-2589 avant J.-C.), fondateur de la IVe dynastie. Son nom reste attaché à l'&lt;em&gt;Enseignement pour Kagemni&lt;/em&gt;, un court texte de sagesse conservé sur le célèbre papyrus Prisse, le même manuscrit qui contient les maximes de Ptahhotep.&lt;/p&gt; &lt;p&gt;Comme beaucoup d'enseignements égyptiens, ce texte a sans doute été rédigé plus tard, au Moyen Empire, puis placé sous l'autorité d'un sage du passé. Il se présente comme les conseils d'un père à ses enfants : on y loue la modestie, la maîtrise de soi et la retenue à table comme dans les paroles, et l'on met en garde contre l'orgueil et la gloutonnerie.&lt;/p&gt; &lt;p&gt;L'enseignement commence par une phrase restée célèbre : « L'homme respectueux prospère, le modeste est loué ; la tente est ouverte au silencieux ». Le silence, la discrétion et la politesse y sont présentés comme des vertus sociales, qui protègent contre les conflits et attirent la faveur des supérieurs. La gourmandise est vue comme un manque de maîtrise : celui qui se jette sur la nourriture se laisse gouverner par ses désirs au lieu de se gouverner lui-même.&lt;/p&gt; &lt;p&gt;Ce type de texte, appelé &lt;em&gt;sebayt&lt;/em&gt; (« enseignement »), était copié et recopié par les apprentis scribes. Il servait à la fois à apprendre à écrire et à former le caractère des futurs fonctionnaires de l'État égyptien. La sagesse n'y est pas une spéculation abstraite, mais une éducation pratique à la vie en société.&lt;/p&gt; &lt;p&gt;Derrière ces règles de conduite se dessine une idée centrale de la pensée égyptienne : l'homme sage est celui qui sait se tenir à sa place et préserver l'harmonie de l'ordre social, reflet de la Maât, l'ordre juste du monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vizir égyptien à qui est attribué l'un des plus anciens enseignements de sagesse.</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15" customHeight="1" s="25">
-      <c r="D141" s="23" t="n"/>
-      <c r="K141" s="23" t="n"/>
-      <c r="L141" s="23" t="n"/>
-      <c r="M141" s="23" t="n"/>
+      <c r="A141" s="23">
+        <v>-2550</v>
+      </c>
+      <c r="B141" s="23">
+        <v>-2480</v>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 2550 A JC</t>
+        </is>
+      </c>
+      <c r="D141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HORDJÉDEF</t>
+        </is>
+      </c>
+      <c r="E141" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hordjédef"  title=" Wikipedia"&gt;HORDJÉDEF&lt;/a&gt; était un prince de la IVe dynastie égyptienne, fils du pharaon Khéops, qui vécut vers 2550 avant J.-C. Les Égyptiens eux-mêmes le tenaient pour l'un des plus grands sages de leur histoire : son nom est cité avec admiration jusqu'à l'époque romaine.&lt;/p&gt; &lt;p&gt;On lui attribue un &lt;em&gt;Enseignement&lt;/em&gt; adressé à son fils Aouibrê, dont il ne subsiste que des fragments. Le texte, sans doute composé au Moyen Empire, conseille de fonder un foyer, d'élever un fils et de préparer dignement sa tombe : la sagesse y est d'abord une manière de bien vivre pour bien mourir, en assurant sa mémoire et la continuité de sa lignée.&lt;/p&gt; &lt;p&gt;La célébrité d'Hordjédef dépasse largement ce texte. Un papyrus raconte qu'il fit venir à la cour de son père le magicien Djédi, et le Livre des morts lui attribue la découverte de certaines formules sacrées. Plus tard, les Égyptiens le rangèrent parmi les grands sages du passé, aux côtés d'Imhotep et de Ptahhotep, dont « les noms durent à cause de leurs livres ».&lt;/p&gt; &lt;p&gt;Cette idée est essentielle dans la culture égyptienne : l'écrit est une forme d'immortalité. Plus sûrement qu'une pyramide ou une tombe, le livre transmet le nom et la pensée de son auteur aux générations futures. Hordjédef devient ainsi le symbole du sage dont la parole survit au temps.&lt;/p&gt; &lt;p&gt;Hordjédef illustre une figure typique de la pensée égyptienne : le sage n'est pas un penseur solitaire mais un homme de rang qui transmet à ses descendants un art de vivre conforme à l'ordre du monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique;spiritualite</t>
+        </is>
+      </c>
+      <c r="L141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M141" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prince égyptien, fils de Khéops, auteur présumé de l'un des plus anciens enseignements de sagesse.</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15" customHeight="1" s="25">
-      <c r="D142" s="23" t="n"/>
-      <c r="K142" s="23" t="n"/>
-      <c r="L142" s="23" t="n"/>
-      <c r="M142" s="23" t="n"/>
+      <c r="A142" s="23">
+        <v>-2500</v>
+      </c>
+      <c r="B142" s="23">
+        <v>-2400</v>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 2500 A JC</t>
+        </is>
+      </c>
+      <c r="D142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHURUPPAK</t>
+        </is>
+      </c>
+      <c r="E142" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Instructions_de_Shuruppak"  title=" Wikipedia"&gt;Instructions de SHURUPPAK&lt;/a&gt; sont l'un des plus anciens textes de sagesse de l'humanité : leurs premières versions, rédigées en sumérien, remontent à environ 2500 avant J.-C. Elles mettent en scène Shuruppak, sage et roi légendaire, qui transmet ses conseils à son fils Ziusudra, le héros sumérien du Déluge.&lt;/p&gt; &lt;p&gt;Les préceptes couvrent tous les domaines de la vie : ne pas voler, ne pas commettre de violence, respecter ses parents, se méfier des paroles imprudentes, choisir avec soin ses terres et ses alliances, et gouverner avec mesure. On y trouve déjà la forme qui fera le succès de la littérature de sagesse du Proche-Orient : des maximes brèves, faciles à retenir, fondées sur l'expérience.&lt;/p&gt; &lt;p&gt;Le texte a été retrouvé sous plusieurs formes, du site d'Abu Salabikh à des copies plus tardives de l'époque paléo-babylonienne, signe qu'il a été enseigné et recopié pendant des siècles dans les écoles de scribes, les « maisons des tablettes ». Certains conseils paraissent très concrets, comme ne pas construire sa maison près d'une place publique ou ne pas acheter un âne qui braie ; d'autres ont une portée morale plus générale, comme ne pas proférer de mensonges ou ne pas se montrer arrogant.&lt;/p&gt; &lt;p&gt;La figure de Ziusudra, le fils qui reçoit ces instructions, est celle du survivant du Déluge dans la tradition sumérienne, l'équivalent d'Uta-napishti dans l'Épopée de Gilgamesh et de Noé dans la Bible. La sagesse est ainsi placée à l'origine même de l'humanité, comme un savoir transmis depuis les temps les plus anciens.&lt;/p&gt; &lt;p&gt;Ce texte montre qu'une réflexion morale structurée existait en Mésopotamie bien avant la philosophie grecque, et qu'elle a nourri toute une tradition, jusqu'aux Proverbes de la Bible.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique;politique</t>
+        </is>
+      </c>
+      <c r="L142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M142" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sage légendaire de Sumer, à qui sont attribuées les plus anciennes instructions de sagesse connues.</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="128.25" customHeight="1" s="25">
-      <c r="D143" s="23" t="n"/>
-      <c r="K143" s="23" t="n"/>
-      <c r="L143" s="23" t="n"/>
-      <c r="M143" s="23" t="n"/>
+      <c r="A143" s="23">
+        <v>-2285</v>
+      </c>
+      <c r="B143" s="23">
+        <v>-2250</v>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 2285 A JC - 2250 A JC</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENHEDUANNA</t>
+        </is>
+      </c>
+      <c r="E143" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enheduana"  title=" Wikipedia"&gt;ENHEDUANNA&lt;/a&gt; était la fille du roi Sargon d'Akkad et la grande prêtresse du dieu-lune Nanna dans la ville d'Ur, au XXIIIe siècle avant J.-C. Elle est la plus ancienne personne connue à nous avoir laissé une œuvre littéraire signée de son nom.&lt;/p&gt; &lt;p&gt;On lui attribue des hymnes majeurs, dont &lt;em&gt;L'Exaltation d'Inanna&lt;/em&gt;, où elle raconte à la première personne son exil et sa détresse avant son retour en grâce, et un recueil de quarante-deux &lt;em&gt;Hymnes aux temples&lt;/em&gt; de Sumer et d'Akkad. Par ces textes, elle contribua à unifier les croyances des Sumériens et des Akkadiens autour de divinités communes.&lt;/p&gt; &lt;p&gt;Sa nomination comme grande prêtresse d'Ur n'était pas seulement religieuse : en plaçant sa fille au cœur du culte sumérien, Sargon, roi akkadien, consolidait son pouvoir sur les cités de Sumer. Enheduanna fut ainsi à la fois une autorité spirituelle et un acteur politique. Lors d'une révolte, elle fut chassée de son temple, épisode qu'elle évoque dans ses hymnes avant d'être rétablie dans ses fonctions.&lt;/p&gt; &lt;p&gt;Ses textes furent recopiés pendant des siècles dans les écoles de scribes, bien après sa mort, ce qui montre l'importance qu'on leur accordait. Redécouverte au XXe siècle grâce aux fouilles d'Ur menées par l'archéologue Leonard Woolley, qui mit au jour un disque de calcite la représentant, elle est aujourd'hui étudiée comme la première autrice de l'histoire et une grande voix de la poésie religieuse.&lt;/p&gt; &lt;p&gt;Son œuvre mêle théologie, poésie et expérience personnelle : la relation au divin y devient une méditation sur le pouvoir, la souffrance et la fidélité, ce qui fait d'Enheduanna une figure fondatrice de la pensée religieuse et de la littérature.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite;esthetique</t>
+        </is>
+      </c>
+      <c r="L143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M143" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grande prêtresse d'Ur, fille de Sargon d'Akkad, premier auteur de l'histoire connu par son nom.</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P143">
+        <v>2</v>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1" s="25">
-      <c r="D144" s="23" t="n"/>
-      <c r="K144" s="23" t="n"/>
-      <c r="L144" s="23" t="n"/>
-      <c r="M144" s="23" t="n"/>
+      <c r="A144" s="23">
+        <v>-2000</v>
+      </c>
+      <c r="B144" s="23">
+        <v>-1950</v>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 2000 A JC</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enseignement pour MÉRIKARÊ</t>
+        </is>
+      </c>
+      <c r="E144" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;L'&lt;a href="https://fr.wikipedia.org/wiki/Enseignement_pour_Mérikarê"  title=" Wikipedia"&gt;Enseignement pour MÉRIKARÊ&lt;/a&gt; est un texte égyptien composé vers 2000 avant J.-C., durant la Première Période intermédiaire, une époque de divisions et de troubles. Il se présente comme le testament d'un roi de la dynastie d'Héracléopolis adressé à son fils, le futur pharaon Mérikarê.&lt;/p&gt; &lt;p&gt;C'est un véritable traité sur l'art de gouverner : le roi doit être éloquent, car « la parole est plus forte que le combat », juste envers ses sujets, prudent face aux rebelles et attentif aux dieux. Le texte a ceci de remarquable qu'il reconnaît les fautes du père et confronte l'idéal de la royauté à la réalité du pouvoir.&lt;/p&gt; &lt;p&gt;Le texte est l'un des rares à évoquer les déchirements de son temps. Le roi y avoue avoir laissé ses troupes saccager des tombeaux dans la région d'Abydos, et reconnaît que ce crime lui a été rendu : « un coup est payé par un coup semblable ». L'aveu d'une faute royale est exceptionnel dans une civilisation où le pharaon était censé incarner l'ordre parfait.&lt;/p&gt; &lt;p&gt;La fin de l'enseignement contient un hymne au dieu créateur, qui a fait le ciel et la terre « à cause des hommes », leur a donné le souffle, la nourriture et la lumière, et veille sur eux « comme un berger sur son troupeau ». On y trouve l'une des premières expressions d'une providence divine bienveillante envers l'humanité tout entière, et non seulement envers le roi.&lt;/p&gt; &lt;p&gt;On y trouve aussi une réflexion morale d'une grande profondeur : le dieu préfère la vertu du juste au sacrifice du méchant, et chacun sera jugé sur ses actes après la mort.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique;ethique</t>
+        </is>
+      </c>
+      <c r="L144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M144" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">texte de sagesse égyptien sur l'art de gouverner, testament d'un roi à son fils.</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1" s="25">
-      <c r="D145" s="23" t="n"/>
-      <c r="K145" s="23" t="n"/>
-      <c r="L145" s="23" t="n"/>
-      <c r="M145" s="23" t="n"/>
+      <c r="A145" s="23">
+        <v>-1860</v>
+      </c>
+      <c r="B145" s="23">
+        <v>-1814</v>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1860 A JC - 1814 A JC</t>
+        </is>
+      </c>
+      <c r="D145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dialogue du DÉSESPÉRÉ avec son ba</t>
+        </is>
+      </c>
+      <c r="E145" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://en.wikipedia.org/wiki/Dispute_between_a_man_and_his_Ba"  title=" Wikipedia"&gt;Dialogue du DÉSESPÉRÉ avec son ba&lt;/a&gt; est un texte égyptien du Moyen Empire, daté du règne d'Amenemhat III (vers 1860-1814 avant J.-C.). Un homme accablé par la souffrance et l'injustice y dialogue avec son &lt;em&gt;ba&lt;/em&gt;, une part de son âme.&lt;/p&gt; &lt;p&gt;L'homme songe à mourir et vante la mort comme une délivrance ; son ba lui oppose d'abord la joie de vivre, puis menace de l'abandonner. La discussion, faite de poèmes d'une grande beauté (« La mort est devant moi aujourd'hui comme la guérison d'un malade »), aborde le sens de la vie, la valeur des rites funéraires et la solitude dans un monde où « il n'y a plus de juste ».&lt;/p&gt; &lt;p&gt;Le texte, conservé sur un papyrus aujourd'hui à Berlin dont le début est perdu, est d'une forme très élaborée. Il alterne des passages en prose, où l'homme et le ba argumentent, et quatre poèmes, construits sur des refrains : « Vois, mon nom est méprisé », « À qui parler aujourd'hui ? », « La mort est devant moi aujourd'hui », « Certes, celui qui est là-bas sera un dieu vivant ».&lt;/p&gt; &lt;p&gt;Le ba, pour sa part, rappelle que les tombeaux les plus somptueux finissent en ruine, comme ceux des pauvres, et invite l'homme à « suivre le jour heureux » et à oublier ses soucis. Les spécialistes discutent encore de la conclusion : le ba accepte-t-il de rester avec l'homme jusqu'à sa mort naturelle, ou consent-il à le suivre ? Cette ambiguïté fait toute la richesse du texte.&lt;/p&gt; &lt;p&gt;Souvent présenté comme le premier texte philosophique sur le suicide et le sens de l'existence, ce dialogue montre que la pensée égyptienne savait aussi douter et s'interroger.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;ethique</t>
+        </is>
+      </c>
+      <c r="L145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M145" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">texte égyptien où un homme désespéré débat de la vie et de la mort avec son âme.</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="25">
+      <c r="A146" s="23">
+        <v>-1850</v>
+      </c>
+      <c r="B146" s="23">
+        <v>-1650</v>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1850 A JC</t>
+        </is>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPOU-OUR</t>
+        </is>
+      </c>
+      <c r="E146" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://en.wikipedia.org/wiki/Ipuwer_Papyrus"  title=" Wikipedia"&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie (vers 1850 avant J.-C.). Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Ipou-our reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui des « lamentations », qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J146" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K146" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique;ethique</t>
+        </is>
+      </c>
+      <c r="L146" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M146" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sage égyptien dont les Lamentations décrivent un monde en chaos et interrogent le mal.</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="25">
+      <c r="A147" s="23">
+        <v>-1792</v>
+      </c>
+      <c r="B147" s="23">
+        <v>-1750</v>
+      </c>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1792 A JC - 1750 A JC (règne)</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAMMURABI</t>
+        </is>
+      </c>
+      <c r="E147" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hammurabi"  title=" Wikipedia"&gt;HAMMURABI&lt;/a&gt; fut roi de Babylone de 1792 à 1750 avant J.-C. (chronologie moyenne). Par ses conquêtes, il fit de sa cité la capitale d'un grand royaume mésopotamien.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour le &lt;em&gt;Code de Hammurabi&lt;/em&gt;, gravé vers la fin de son règne sur une stèle de basalte aujourd'hui conservée au musée du Louvre. Ce recueil de près de trois cents décisions de justice règle la vie économique, familiale et sociale, avec le célèbre principe de la loi du talion (« œil pour œil »).&lt;/p&gt; &lt;p&gt;Le code ne se présente pas comme une législation abstraite mais comme une liste de cas : « si un homme a fait ceci, alors il lui sera fait cela ». Les peines varient selon le rang social de la victime et du coupable, homme libre, dépendant ou esclave, ce qui reflète une société très hiérarchisée. Le code traite des prix, des salaires, des prêts, du mariage, du divorce, de l'héritage, des soins médicaux et même de la responsabilité des architectes dont la maison s'effondre.&lt;/p&gt; &lt;p&gt;La loi du talion, qui paraît brutale aujourd'hui, avait aussi pour but de limiter la vengeance : la peine doit être proportionnée au dommage, et non illimitée. Le code affirme enfin que tout homme lésé peut venir lire la stèle pour connaître ses droits, idée d'une justice publique et accessible qui marque une étape importante dans l'histoire du droit.&lt;/p&gt; &lt;p&gt;Le prologue en donne la philosophie : le roi a reçu des dieux la mission de « faire apparaître la justice dans le pays, détruire le méchant et le pervers, afin que le fort n'opprime pas le faible ». L'idée que le pouvoir se justifie par la protection des plus faibles traversera toute l'histoire de la pensée politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J147" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K147" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique;ethique</t>
+        </is>
+      </c>
+      <c r="L147" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M147" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roi de Babylone, auteur du célèbre code de lois, réflexion sur la justice et l'ordre social.</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="25">
+      <c r="A148" s="23">
+        <v>-1370</v>
+      </c>
+      <c r="B148" s="23">
+        <v>-1337</v>
+      </c>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1370 A JC - 1337 A JC</t>
+        </is>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AKHENATON</t>
+        </is>
+      </c>
+      <c r="E148" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Akhenaton"  title=" Wikipedia"&gt;AKHENATON&lt;/a&gt;, d'abord nommé Amenhotep IV, fut pharaon d'Égypte de 1355 à 1337 avant J.-C. environ. Époux de Néfertiti et sans doute père de Toutânkhamon, il bouleversa la religion égyptienne en imposant le culte exclusif d'Aton, le disque solaire.&lt;/p&gt; &lt;p&gt;Il fit fermer les temples des autres dieux, fonda une nouvelle capitale, Akhetaton (Amarna), et composa ou inspira le &lt;em&gt;Grand Hymne à Aton&lt;/em&gt;, qui célèbre un dieu unique, créateur bienveillant de tous les êtres et de tous les peuples. On y voit souvent le premier monothéisme exclusif connu de l'histoire.&lt;/p&gt; &lt;p&gt;La révolution d'Akhenaton ne fut pas seulement religieuse. L'art de son règne, dit « amarnien », rompt avec les conventions séculaires : le roi est représenté avec un visage allongé et un corps aux formes étranges, dans des scènes de vie familiale intimes, entouré de Néfertiti et de leurs filles, sous les rayons du disque solaire terminés par des mains qui tendent la vie.&lt;/p&gt; &lt;p&gt;Le Grand Hymne à Aton, gravé dans une tombe d'Amarna, célèbre la lumière qui fait vivre toute la création : les hommes, les animaux, les plantes et même les pays étrangers, dont le dieu a fait les langues différentes. Certains passages présentent de fortes ressemblances avec le psaume 104 de la Bible. Freud, dans &lt;em&gt;Moïse et le monothéisme&lt;/em&gt;, alla jusqu'à supposer un lien entre la réforme d'Akhenaton et la religion de Moïse, hypothèse très discutée.&lt;/p&gt; &lt;p&gt;Sa réforme fut effacée après sa mort, mais elle pose une question philosophique durable : celle d'un principe unique à l'origine du monde, et du lien entre la vérité religieuse et le pouvoir politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J148" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K148" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite;metaphysique</t>
+        </is>
+      </c>
+      <c r="L148" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monothéisme</t>
+        </is>
+      </c>
+      <c r="M148" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pharaon égyptien qui imposa le culte du dieu unique Aton, parfois vu comme le premier monothéisme.</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="25">
+      <c r="A149" s="23">
+        <v>-1300</v>
+      </c>
+      <c r="B149" s="23">
+        <v>-1100</v>
+      </c>
+      <c r="C149" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1300 A JC - 1100 A JC</t>
+        </is>
+      </c>
+      <c r="D149" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUDLUL bel nemeqi</t>
+        </is>
+      </c>
+      <c r="E149" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Ludlul_bēl_nēmeqi"  title=" Wikipedia"&gt;LUDLUL bel nemeqi&lt;/a&gt;, ou &lt;em&gt;Poème du juste souffrant&lt;/em&gt;, est un texte babylonien de la seconde moitié du IIe millénaire avant J.-C. Son titre signifie « Je veux louer le Seigneur de la sagesse », c'est-à-dire le dieu Marduk.&lt;/p&gt; &lt;p&gt;Un homme pieux, Shubshi-meshre-Shakkan, raconte comment il a tout perdu : son rang, ses amis, sa santé, alors qu'il avait toujours honoré les dieux. Il s'interroge : les hommes peuvent-ils comprendre la volonté divine, quand ce qui leur semble bon déplaît aux dieux ? Finalement, Marduk le rétablit dans sa prospérité.&lt;/p&gt; &lt;p&gt;Le poème compte environ cinq cents vers répartis sur quatre tablettes. Sa description de la maladie est d'un réalisme saisissant : le juste souffrant perd le sommeil, l'appétit et la vue, ses membres se paralysent, ses proches l'abandonnent et ses ennemis se réjouissent. Les devins et les exorcistes ne trouvent aucune explication à son malheur, car il n'a commis aucune faute rituelle.&lt;/p&gt; &lt;p&gt;La guérison survient à la suite de rêves où apparaissent des envoyés de Marduk, qui purifient le malade et chassent les démons. Le poème se termine par une célébration de la puissance du dieu, capable de frapper comme de guérir. La leçon n'est pas que la souffrance a une raison compréhensible, mais que les voies divines dépassent la raison humaine et que l'homme doit garder confiance malgré tout.&lt;/p&gt; &lt;p&gt;Ce poème pose, bien avant le livre biblique de Job, la grande question de la souffrance de l'innocent et de la justice divine, un problème que la philosophie appellera plus tard la théodicée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J149" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K149" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;spiritualite</t>
+        </is>
+      </c>
+      <c r="L149" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M149" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poème babylonien du « juste souffrant », méditation sur le mal et la justice divine.</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="25">
+      <c r="A150" s="23">
+        <v>-1200</v>
+      </c>
+      <c r="B150" s="23">
+        <v>-1100</v>
+      </c>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1200 A JC</t>
+        </is>
+      </c>
+      <c r="D150" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMENEMOPET</t>
+        </is>
+      </c>
+      <c r="E150" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Enseignement_d'Aménémopé"  title=" Wikipedia"&gt;AMENEMOPET&lt;/a&gt;, fils de Kanakht, était un scribe égyptien de l'époque ramesside (vers 1300-1075 avant J.-C.). Il composa pour son fils un &lt;em&gt;Enseignement&lt;/em&gt; en trente chapitres, l'un des plus beaux textes de sagesse de l'Égypte ancienne.&lt;/p&gt; &lt;p&gt;Il y oppose l'homme « silencieux », calme, honnête et maître de lui, à l'homme « emporté », colérique et avide. Il recommande de ne pas déplacer les bornes des champs, de ne pas se moquer des faibles, de ne pas s'enrichir par la fraude, et rappelle que l'homme ne connaît pas l'avenir : « l'homme est argile et paille, le dieu est son bâtisseur ».&lt;/p&gt; &lt;p&gt;L'enseignement est connu principalement par un papyrus conservé au British Museum, et par de nombreux fragments sur des tablettes d'écoliers, signe qu'il servait à la formation des scribes. Il se distingue des enseignements plus anciens par la place qu'il accorde à la vie intérieure : la vraie valeur de l'homme ne réside pas dans sa réussite sociale mais dans son calme, sa droiture et sa confiance en la divinité.&lt;/p&gt; &lt;p&gt;Le rapprochement avec la Bible est particulièrement frappant pour un passage des Proverbes (22,17 à 24,22), qui reprend souvent de très près les conseils d'Amenemopet, jusqu'à la mention de « trente » sentences. Cette parenté montre que les sages d'Israël connaissaient la littérature de sagesse égyptienne et s'en inspiraient, en l'adaptant à leur propre foi.&lt;/p&gt; &lt;p&gt;Plusieurs passages ont été rapprochés du livre biblique des Proverbes, ce qui montre la circulation des idées de sagesse dans tout le Proche-Orient ancien.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J150" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K150" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L150" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M150" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scribe égyptien, auteur d'un enseignement de sagesse proche du livre biblique des Proverbes.</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1" s="25">
+      <c r="A151" s="23">
+        <v>-1200</v>
+      </c>
+      <c r="B151" s="23">
+        <v>-1150</v>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1200 A JC (?)</t>
+        </is>
+      </c>
+      <c r="D151" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHONIATHON</t>
+        </is>
+      </c>
+      <c r="E151" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sanchoniathon"  title=" Wikipedia"&gt;SANCHONIATHON&lt;/a&gt; est un auteur phénicien dont l'&lt;em&gt;Histoire phénicienne&lt;/em&gt; ne nous est connue que par les extraits traduits en grec par Philon de Byblos (Ier-IIe siècle), puis cités par Eusèbe de Césarée. Selon la tradition, il aurait vécu avant la guerre de Troie ; d'autres le placent bien plus tard, et son existence même est discutée.&lt;/p&gt; &lt;p&gt;Ces fragments constituent la principale source écrite sur la religion phénicienne. Ils proposent une cosmogonie, un récit de l'origine du monde à partir d'un chaos primitif et d'un souffle, puis l'apparition des dieux et des inventions humaines.&lt;/p&gt; &lt;p&gt;Selon Philon de Byblos, Sanchoniathon aurait rédigé son œuvre à partir d'archives conservées dans les temples et d'inscriptions sacrées. Son récit commence par un air sombre et venteux et un chaos trouble, d'où naît, par le désir du souffle pour ses propres principes, une matière originelle appelée &lt;em&gt;Môt&lt;/em&gt;, source de toutes les créatures. Viennent ensuite des générations de dieux et de héros civilisateurs qui inventent le feu, la pêche, la navigation ou l'écriture.&lt;/p&gt; &lt;p&gt;Longtemps, les savants ont douté de l'authenticité de ces fragments, qu'ils attribuaient à l'imagination de Philon. Mais la découverte, au XXe siècle, des textes mythologiques d'Ougarit, cité de la côte syrienne, a montré que plusieurs de ses récits correspondaient à d'authentiques traditions cananéennes, ce qui a redonné du crédit à Sanchoniathon.&lt;/p&gt; &lt;p&gt;Sanchoniathon témoigne de l'effort des anciens pour ordonner leurs mythes en une histoire du monde, et de la manière dont ces récits ont été relus par les philosophes grecs et chrétiens.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J151" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénicienne</t>
+        </is>
+      </c>
+      <c r="K151" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;spiritualite</t>
+        </is>
+      </c>
+      <c r="L151" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polythéisme</t>
+        </is>
+      </c>
+      <c r="M151" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auteur phénicien d'une histoire des origines du monde et des dieux, connue par Philon de Byblos.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1" s="25">
+      <c r="A152" s="23">
+        <v>-1000</v>
+      </c>
+      <c r="B152" s="23">
+        <v>-930</v>
+      </c>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1000 A JC</t>
+        </is>
+      </c>
+      <c r="D152" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZARATHOUSTRA</t>
+        </is>
+      </c>
+      <c r="E152" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zarathoustra"  title=" Wikipedia"&gt;ZARATHOUSTRA&lt;/a&gt;, ou Zoroastre, est le prophète fondateur du zoroastrisme, la religion de l'Iran ancien. Ses dates sont très discutées : l'analyse de la langue des &lt;em&gt;Gathas&lt;/em&gt;, les hymnes qui lui sont attribués, conduit aujourd'hui la plupart des spécialistes à le situer vers l'an 1000 avant J.-C.&lt;/p&gt; &lt;p&gt;Sa pensée repose sur l'opposition entre deux principes : l'esprit du bien, lié à Ahura Mazda, le « Seigneur sage », et l'esprit du mal et du mensonge. Chaque être humain est libre de choisir son camp par ses pensées, ses paroles et ses actions, et sera jugé selon ce choix.&lt;/p&gt; &lt;p&gt;Selon la tradition, Zarathoustra reçut sa révélation vers l'âge de trente ans, lors d'une vision au bord d'une rivière. Il dut affronter l'hostilité des prêtres de l'ancienne religion avant de trouver un protecteur, le roi Vishtaspa, qui se convertit à son enseignement. Ses &lt;em&gt;Gathas&lt;/em&gt;, dix-sept hymnes écrits dans une langue très archaïque, forment la partie la plus ancienne de l'Avesta, le livre sacré du zoroastrisme.&lt;/p&gt; &lt;p&gt;Le zoroastrisme devint plus tard la religion des grands empires perses, des Achéménides aux Sassanides, jusqu'à la conquête arabe au VIIe siècle. Il survit aujourd'hui dans de petites communautés en Iran et chez les Parsis de l'Inde. Le feu, symbole de la vérité et de la pureté, y occupe une place centrale, ce qui a valu aux zoroastriens le nom, inexact, d'« adorateurs du feu ».&lt;/p&gt; &lt;p&gt;Cette vision d'un combat cosmique entre le bien et le mal, de la responsabilité morale individuelle et d'un jugement final a profondément influencé le judaïsme, le christianisme et l'islam. Nietzsche a repris son nom dans &lt;em&gt;Ainsi parlait Zarathoustra&lt;/em&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J152" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perse</t>
+        </is>
+      </c>
+      <c r="K152" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite;ethique;metaphysique</t>
+        </is>
+      </c>
+      <c r="L152" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zoroastrisme</t>
+        </is>
+      </c>
+      <c r="M152" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prophète iranien, fondateur du zoroastrisme, penseur du combat entre le bien et le mal.</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" ht="15" customHeight="1" s="25">
+      <c r="A153" s="23">
+        <v>-1000</v>
+      </c>
+      <c r="B153" s="23">
+        <v>-900</v>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1000 A JC</t>
+        </is>
+      </c>
+      <c r="D153" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dialogue du PESSIMISME</t>
+        </is>
+      </c>
+      <c r="E153" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://en.wikipedia.org/wiki/Dialogue_of_Pessimism"  title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé peu après l'an 1000 avant J.-C. en Mésopotamie. Il met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître annonce tour à tour qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J153" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K153" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique;metaphysique</t>
+        </is>
+      </c>
+      <c r="L153" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M153" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialogue babylonien entre un maître et son esclave sur la vanité de toute action humaine.</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1" s="25">
+      <c r="A154" s="23">
+        <v>-700</v>
+      </c>
+      <c r="B154" s="23">
+        <v>-640</v>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIIe siècle A JC</t>
+        </is>
+      </c>
+      <c r="D154" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AHIQAR</t>
+        </is>
+      </c>
+      <c r="E154" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar"  title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup concernent la parole : « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs connaissaient Ahiqar : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une diffusion aussi large à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J154" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K154" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L154" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M154" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sage assyrien semi-légendaire, dont l'histoire et les maximes circulèrent dans tout le Proche-Orient.</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="25">
+      <c r="A155" s="23">
+        <v>-550</v>
+      </c>
+      <c r="B155" s="23">
+        <v>-400</v>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIe - IVe siècle A JC</t>
+        </is>
+      </c>
+      <c r="D155" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Livre de JOB</t>
+        </is>
+      </c>
+      <c r="E155" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Livre_de_Job"  title=" Wikipedia"&gt;Livre de JOB&lt;/a&gt; est un livre de la Bible hébraïque rédigé entre le VIe et le début du IVe siècle avant J.-C. Il raconte l'histoire de Job, un homme juste et prospère que Dieu laisse éprouver par Satan : il perd ses biens, ses enfants et sa santé.&lt;/p&gt; &lt;p&gt;Ses amis soutiennent qu'il doit avoir péché pour souffrir ainsi ; Job refuse cette explication, proclame son innocence et demande des comptes à Dieu. Dieu lui répond enfin du milieu de la tempête, non par une justification, mais en lui montrant l'immensité et le mystère de la création.&lt;/p&gt; &lt;p&gt;Le livre est construit comme une œuvre littéraire complexe : un prologue et un épilogue en prose, où Job est un modèle de patience (« Le Seigneur a donné, le Seigneur a repris »), encadrent de longs discours poétiques où Job, au contraire, se révolte, maudit le jour de sa naissance et accuse Dieu d'injustice. Trois amis, Éliphaz, Bildad et Tsophar, puis un jeune homme, Élihou, tentent en vain de le convaincre qu'il est puni pour ses fautes.&lt;/p&gt; &lt;p&gt;Le livre refuse ainsi la doctrine de la rétribution, selon laquelle le bonheur récompense les justes et le malheur punit les méchants. Dieu donne finalement tort aux amis et raison à Job, qui a parlé avec franchise. La souffrance n'est pas expliquée : elle reste un mystère que l'homme doit affronter sans réponse, dans une relation directe et exigeante avec Dieu.&lt;/p&gt; &lt;p&gt;Ce chef-d'œuvre poétique pose avec une force inégalée la question de la souffrance de l'innocent et des limites de la raison humaine face au mal. Il a inspiré de nombreux philosophes, de Kierkegaard à Levinas.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J155" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K155" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;spiritualite</t>
+        </is>
+      </c>
+      <c r="L155" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive</t>
+        </is>
+      </c>
+      <c r="M155" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">livre biblique sur la souffrance du juste et le silence de Dieu.</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="25">
+      <c r="A156" s="23">
+        <v>-340</v>
+      </c>
+      <c r="B156" s="23">
+        <v>-270</v>
+      </c>
+      <c r="C156" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 340 A JC - 270 A JC</t>
+        </is>
+      </c>
+      <c r="D156" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BÉROSE</t>
+        </is>
+      </c>
+      <c r="E156" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bérose"  title=" Wikipedia"&gt;BÉROSE&lt;/a&gt; était un prêtre du dieu Bêl à Babylone, astronome et historien, né vers 340 avant J.-C. Il vécut après la conquête de la Mésopotamie par Alexandre le Grand, à l'époque des rois séleucides.&lt;/p&gt; &lt;p&gt;Il rédigea en grec, entre 290 et 279 avant J.-C., une &lt;em&gt;Histoire de Babylone&lt;/em&gt; (&lt;em&gt;Babyloniaca&lt;/em&gt;) dédiée au roi Antiochos Ier. Il y présentait aux Grecs le savoir babylonien : la création du monde, les rois d'avant le Déluge, le récit du Déluge lui-même et l'histoire des grands empires mésopotamiens.&lt;/p&gt; &lt;p&gt;L'œuvre de Bérose est perdue : nous n'en connaissons que des fragments cités par des auteurs plus tardifs, comme l'historien juif Flavius Josèphe ou l'évêque Eusèbe de Césarée. Elle était divisée en trois livres : le premier sur la géographie de la Babylonie et la création du monde, où apparaît le monstre marin Oannès, maître civilisateur qui enseigne aux hommes l'écriture, les lois et les arts ; les deux autres sur les rois et l'histoire jusqu'à Alexandre.&lt;/p&gt; &lt;p&gt;Selon la tradition, Bérose se serait ensuite installé sur l'île grecque de Cos, où il aurait fondé une école d'astrologie, et les Athéniens lui auraient élevé une statue en l'honneur de ses prédictions. Réelle ou légendaire, cette figure du prêtre babylonien enseignant les Grecs résume bien le rôle de passeur que lui attribue l'histoire.&lt;/p&gt; &lt;p&gt;Bérose est l'un des premiers passeurs entre deux mondes : il transmit à la culture grecque une partie de la sagesse et de l'astronomie chaldéennes, à la fin de la longue histoire de la pensée mésopotamienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J156" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamienne</t>
+        </is>
+      </c>
+      <c r="K156" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie;spiritualite</t>
+        </is>
+      </c>
+      <c r="L156" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M156" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtre et astronome babylonien qui fit connaître aux Grecs l'histoire et le savoir de Babylone.</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="25">
+      <c r="A157" s="23">
+        <v>-250</v>
+      </c>
+      <c r="B157" s="23">
+        <v>-220</v>
+      </c>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 250 A JC</t>
+        </is>
+      </c>
+      <c r="D157" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QOHÉLET (l’Ecclésiaste)</t>
+        </is>
+      </c>
+      <c r="E157" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ecclésiaste"  title=" Wikipedia"&gt;QOHÉLET&lt;/a&gt;, ou l'&lt;em&gt;Ecclésiaste&lt;/em&gt;, est un livre de sagesse de la Bible hébraïque écrit vers 250 avant J.-C., à Jérusalem, à l'époque du Second Temple. Son auteur se présente comme « Qohélet », un fils de David, roi à Jérusalem.&lt;/p&gt; &lt;p&gt;Il s'ouvre sur une formule restée célèbre : « Vanité des vanités, tout est vanité ». Qohélet observe que la richesse, le travail, le plaisir et même la sagesse ne mettent pas l'homme à l'abri de la mort, qui frappe le sage comme l'insensé ; « rien de nouveau sous le soleil » et « il y a un temps pour tout ».&lt;/p&gt; &lt;p&gt;Le mot hébreu traduit par « vanité », &lt;em&gt;hèvèl&lt;/em&gt;, signifie d'abord « buée » ou « souffle » : ce qui est léger, insaisissable et passager. Qohélet l'applique à tout ce que l'homme entreprend sous le soleil. Il observe aussi l'injustice du monde : le juste peut périr dans sa justice et le méchant prolonger sa vie dans sa méchanceté, et l'homme ne peut pas comprendre l'œuvre de Dieu du début à la fin.&lt;/p&gt; &lt;p&gt;La tradition a attribué le livre au roi Salomon, ce qui a sans doute facilité son entrée dans la Bible malgré ses idées audacieuses. Son ton désabusé a souvent été rapproché de la philosophie grecque, du scepticisme et de l'épicurisme, sans qu'une influence directe soit certaine. Montaigne, Pascal ou Camus y ont trouvé un écho à leur propre réflexion sur la condition humaine.&lt;/p&gt; &lt;p&gt;Plutôt que de désespérer, il invite à profiter avec simplicité des joies de la vie, du pain et du vin, fruits du travail, comme d'un don de Dieu. Par son regard lucide et presque sceptique, Qohélet est l'un des textes les plus philosophiques de la Bible.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J157" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K157" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;ethique</t>
+        </is>
+      </c>
+      <c r="L157" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive</t>
+        </is>
+      </c>
+      <c r="M157" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">livre de sagesse biblique, méditation lucide sur la vanité et le sens de la vie.</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="P157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="25">
+      <c r="A158" s="23">
+        <v>-250</v>
+      </c>
+      <c r="B158" s="23">
+        <v>-100</v>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IIIe - Ier siècle A JC</t>
+        </is>
+      </c>
+      <c r="D158" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÂNKHSHESHONQY</t>
+        </is>
+      </c>
+      <c r="E158" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;L'&lt;a href="https://en.wikipedia.org/wiki/Instruction_of_Ankhsheshonq"  title=" Wikipedia"&gt;Enseignement d’ÂNKHSHESHONQY&lt;/a&gt; est un texte égyptien rédigé en démotique, daté de l'époque ptolémaïque (après 305 avant J.-C.), mais dont le contenu est peut-être plus ancien.&lt;/p&gt; &lt;p&gt;Un récit raconte qu'Ânkhsheshonqy, prêtre d'Héliopolis, fut jeté en prison pour n'avoir pas dénoncé un complot contre le pharaon ; ne pouvant plus éduquer son fils, il écrivit pour lui ses conseils sur des tessons de poterie. Suit une longue série de maximes brèves, souvent ironiques et pleines de bon sens, sur le travail, la famille, l'amitié, la prudence et les revers de la fortune.&lt;/p&gt; &lt;p&gt;Les maximes sont écrites sur un seul papyrus conservé au British Museum. Elles se succèdent sans ordre apparent, une par ligne, dans un style direct et imagé : « Ne dis pas : c'est l'été, il y a l'hiver aussi », « Celui qui envoie des épines récoltera des épines », « Ne fais pas confiance au feu tant qu'il brûle », ou encore « La femme sage ne quitte pas sa maison ». On y trouve aussi une réflexion sur la fortune et le destin, qui peuvent frapper chacun sans prévenir.&lt;/p&gt; &lt;p&gt;Le récit qui les introduit, avec son pharaon trompé, son complot et son sage emprisonné, rappelle l'histoire d'Ahiqar, ce qui montre les échanges entre les traditions égyptienne et araméenne. Contrairement aux enseignements anciens destinés aux fonctionnaires, celui d'Ânkhsheshonqy s'adresse à tous, paysans, artisans ou marchands : c'est une sagesse populaire, tournée vers la vie de tous les jours.&lt;/p&gt; &lt;p&gt;Ce texte, l'un des derniers grands enseignements égyptiens, montre la vitalité d'une sagesse pratique qui a traversé trois millénaires d'histoire.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J158" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Égyptienne</t>
+        </is>
+      </c>
+      <c r="K158" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L158" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique</t>
+        </is>
+      </c>
+      <c r="M158" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prêtre égyptien d'époque ptolémaïque, auteur d'un recueil de maximes écrit en prison pour son fils.</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="25">
+      <c r="A159" s="23">
+        <v>154</v>
+      </c>
+      <c r="B159" s="23">
+        <v>222</v>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154 - 222</t>
+        </is>
+      </c>
+      <c r="D159" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARDESANE</t>
+        </is>
+      </c>
+      <c r="E159" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bardesane"  title=" Wikipedia"&gt;BARDESANE&lt;/a&gt; (154-222) est un philosophe, poète et astronome né à Édesse, en Mésopotamie du Nord (aujourd'hui Şanlıurfa, en Turquie). Il fut l'un des premiers grands auteurs de langue syriaque et un proche de la cour du roi Abgar VIII.&lt;/p&gt; &lt;p&gt;Son œuvre principale, le &lt;em&gt;Livre des lois des pays&lt;/em&gt;, retrouvé en 1845, est un dialogue sur le destin et la liberté. Bardesane y combat l'idée que les astres déterminent entièrement la vie humaine : il montre que les peuples, soumis aux mêmes astres, ont des lois et des mœurs très différentes, preuve que l'homme reste libre de ses choix.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;Livre des lois des pays&lt;/em&gt; fut en réalité rédigé par un disciple, Philippe, qui rapporte la conversation de son maître avec un certain Awida. Bardesane y distingue trois niveaux dans l'existence humaine : la nature, commune à tous et qui règle la naissance, la croissance et la mort ; le destin, lié aux astres, qui explique la richesse, la maladie ou les accidents ; et la liberté, qui dépend de l'homme seul et fait de lui un être moral, responsable de ses actes.&lt;/p&gt; &lt;p&gt;Bardesane composa aussi des hymnes en syriaque, si populaires que saint Éphrem, un siècle plus tard, écrivit ses propres hymnes sur les mêmes mélodies pour combattre les idées de Bardesane. Son fils Harmonios poursuivit son œuvre poétique. Bardesane occupe ainsi une place importante dans les débuts de la littérature syriaque, qui sera plus tard un pont entre la philosophie grecque et le monde arabe.&lt;/p&gt; &lt;p&gt;Chrétien aux idées originales, marquées par l'astrologie et des influences gnostiques, il fut ensuite jugé hérétique. Il reste un témoin de la rencontre entre la sagesse orientale, la philosophie grecque et le christianisme naissant.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J159" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Syrienne</t>
+        </is>
+      </c>
+      <c r="K159" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique;ethique</t>
+        </is>
+      </c>
+      <c r="L159" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gnosticisme</t>
+        </is>
+      </c>
+      <c r="M159" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe syriaque d'Édesse, penseur du destin et de la liberté humaine.</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="1048572" ht="12.75" customHeight="1" s="25"/>
     <row r="1048573" ht="12.75" customHeight="1" s="25"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1437">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES ORIENTAUX</t>
   </si>
@@ -137,6 +137,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;a href="https://fr.wikipedia.org/wiki/Instructions_pour_Kagemni"  title="instructions pour kagemni par wikipedia"&gt;</t>
     </r>
@@ -311,35 +312,10 @@
     <t xml:space="preserve">IPOU-OUR</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our"  title=" Wikipedia"&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie. Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Il reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  &lt;a href="https://www.worldhistory.org/trans/fr/2-981/lamentations-dipou-our/"   title="lamentations d’Ipou-Our par worldhistory"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">des « lamentations »,&lt;/a&gt;  qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;</t>
-    </r>
+    <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our"  title=" Wikipedia"&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie. Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Il reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui   &lt;a href="https://www.worldhistory.org/trans/fr/2-981/lamentations-dipou-our/"   title="lamentations d’Ipou-Our par worldhistory"&gt;des « lamentations »,&lt;/a&gt;  qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL-OWz8Awm0</t>
   </si>
   <si>
     <t xml:space="preserve">The Ipuwer Payrus par Evidence 4 faith</t>
@@ -3944,7 +3920,7 @@
     <t xml:space="preserve">HORDJÉDEF</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hordjédef"  title=" Wikipedia"&gt;HORDJÉDEF&lt;/a&gt; était un prince de la IVe dynastie égyptienne, fils du pharaon Khéops, qui vécut vers 2550 avant J.-C. Les Égyptiens eux-mêmes le tenaient pour l'un des plus grands sages de leur histoire : son nom est cité avec admiration jusqu'à l'époque romaine.&lt;/p&gt; &lt;p&gt;On lui attribue un &lt;em&gt;Enseignement&lt;/em&gt; adressé à son fils Aouibrê, dont il ne subsiste que des fragments. Le texte, sans doute composé au Moyen Empire, conseille de fonder un foyer, d'élever un fils et de préparer dignement sa tombe : la sagesse y est d'abord une manière de bien vivre pour bien mourir, en assurant sa mémoire et la continuité de sa lignée.&lt;/p&gt; &lt;p&gt;La célébrité d'Hordjédef dépasse largement ce texte. Un papyrus raconte qu'il fit venir à la cour de son père le magicien Djédi, et le Livre des morts lui attribue la découverte de certaines formules sacrées. Plus tard, les Égyptiens le rangèrent parmi les grands sages du passé, aux côtés d'Imhotep et de Ptahhotep, dont « les noms durent à cause de leurs livres ».&lt;/p&gt; &lt;p&gt;Cette idée est essentielle dans la culture égyptienne : l'écrit est une forme d'immortalité. Plus sûrement qu'une pyramide ou une tombe, le livre transmet le nom et la pensée de son auteur aux générations futures. Hordjédef devient ainsi le symbole du sage dont la parole survit au temps.&lt;/p&gt; &lt;p&gt;Hordjédef illustre une figure typique de la pensée égyptienne : le sage n'est pas un penseur solitaire mais un homme de rang qui transmet à ses descendants un art de vivre conforme à l'ordre du monde.&lt;/p&gt;</t>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hordjédef"  title=" Wikipedia"&gt;HORDJÉDEF&lt;/a&gt; était un prince de la IVe dynastie égyptienne, fils du pharaon Khéops. Les Égyptiens eux-mêmes le tenaient pour l'un des plus grands sages de leur histoire : son nom est cité avec admiration jusqu'à l'époque romaine.&lt;/p&gt; &lt;p&gt;On lui attribue un &lt;em&gt;Enseignement&lt;/em&gt; adressé à son fils Aouibrê, dont il ne subsiste que des fragments. Le texte, sans doute composé au Moyen Empire, conseille de fonder un foyer, d'élever un fils et de préparer dignement sa tombe : la sagesse y est d'abord une manière de bien vivre pour bien mourir, en assurant sa mémoire et la continuité de sa lignée.&lt;/p&gt; &lt;p&gt;La célébrité d'Hordjédef dépasse largement ce texte. Un papyrus raconte qu'il fit venir à la cour de son père le magicien Djédi, et le Livre des morts lui attribue la découverte de certaines formules sacrées. Plus tard, les Égyptiens le rangèrent parmi les grands sages du passé, aux côtés d'Imhotep et de Ptahhotep, dont « les noms durent à cause de leurs livres ».&lt;/p&gt; &lt;p&gt;Cette idée est essentielle dans la culture égyptienne : l'écrit est une forme d'immortalité. Plus sûrement qu'une pyramide ou une tombe, le livre transmet le nom et la pensée de son auteur aux générations futures. Hordjédef devient ainsi le symbole du sage dont la parole survit au temps.&lt;/p&gt; &lt;p&gt;Hordjédef illustre une figure typique de la pensée égyptienne : le sage n'est pas un penseur solitaire mais un homme de rang qui transmet à ses descendants un art de vivre conforme à l'ordre du monde.&lt;/p&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">ethique;spiritualite</t>
@@ -4611,7 +4587,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4683,6 +4659,7 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -4693,18 +4670,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -4712,13 +4677,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -4911,8 +4869,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -4923,20 +4893,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -4944,22 +4914,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5215,7 +5173,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.87"/>
@@ -5601,7 +5559,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="300" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>-1850</v>
       </c>
@@ -5618,13 +5576,13 @@
         <v>85</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>25</v>
@@ -5636,51 +5594,49 @@
         <v>27</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="XFC11" s="0"/>
-      <c r="XFD11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>-1780</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>29</v>
@@ -5694,34 +5650,34 @@
         <v>-1400</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>74</v>
@@ -5732,38 +5688,38 @@
         <v>-1460</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>29</v>
@@ -5777,38 +5733,38 @@
         <v>-750</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>74</v>
@@ -5822,34 +5778,34 @@
         <v>-720</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>74</v>
@@ -5863,38 +5819,38 @@
         <v>-700</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>74</v>
@@ -5905,38 +5861,38 @@
         <v>-765</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>29</v>
@@ -5950,34 +5906,34 @@
         <v>-500</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>74</v>
@@ -5991,34 +5947,34 @@
         <v>-500</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>74</v>
@@ -6032,34 +5988,34 @@
         <v>-500</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>74</v>
@@ -6070,38 +6026,38 @@
         <v>-599</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>74</v>
@@ -6115,41 +6071,41 @@
         <v>-570</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>3</v>
@@ -6160,38 +6116,38 @@
         <v>-566</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>74</v>
@@ -6208,35 +6164,35 @@
         <v>-483</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>74</v>
@@ -6247,41 +6203,41 @@
         <v>-551</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>3</v>
@@ -6295,38 +6251,38 @@
         <v>-496</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6337,34 +6293,34 @@
         <v>-400</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>74</v>
@@ -6378,38 +6334,38 @@
         <v>-420</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P29" s="1" t="n">
         <v>3</v>
@@ -6420,41 +6376,41 @@
         <v>-470</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>3</v>
@@ -6468,22 +6424,22 @@
         <v>-300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>70</v>
@@ -6492,10 +6448,10 @@
         <v>26</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>74</v>
@@ -6506,41 +6462,41 @@
         <v>-372</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>3</v>
@@ -6551,41 +6507,41 @@
         <v>-372</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>3</v>
@@ -6599,35 +6555,35 @@
         <v>-283</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I34" s="7"/>
       <c r="J34" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>74</v>
@@ -6641,37 +6597,37 @@
         <v>-250</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="252" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6679,41 +6635,41 @@
         <v>-280</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6721,41 +6677,41 @@
         <v>-179</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6763,44 +6719,44 @@
         <v>-70</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6808,41 +6764,41 @@
         <v>27</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6850,41 +6806,41 @@
         <v>34</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="273" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6892,44 +6848,44 @@
         <v>50</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6937,38 +6893,38 @@
         <v>100</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>74</v>
@@ -6979,38 +6935,38 @@
         <v>158</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I43" s="7"/>
       <c r="J43" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>74</v>
@@ -7024,38 +6980,38 @@
         <v>216</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>29</v>
@@ -7066,41 +7022,41 @@
         <v>226</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I45" s="7"/>
       <c r="J45" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7108,41 +7064,41 @@
         <v>284</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I46" s="7"/>
       <c r="J46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7150,38 +7106,38 @@
         <v>300</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>74</v>
@@ -7192,38 +7148,38 @@
         <v>310</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I48" s="7"/>
       <c r="J48" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>74</v>
@@ -7240,34 +7196,34 @@
         <v>450</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>74</v>
@@ -7278,41 +7234,41 @@
         <v>374</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I50" s="7"/>
       <c r="J50" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="235.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7320,41 +7276,41 @@
         <v>470</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I51" s="7"/>
       <c r="J51" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7362,38 +7318,38 @@
         <v>478</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I52" s="7"/>
       <c r="J52" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>29</v>
@@ -7404,25 +7360,25 @@
         <v>530</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I53" s="7"/>
       <c r="J53" s="1" t="s">
@@ -7432,10 +7388,10 @@
         <v>71</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>74</v>
@@ -7446,41 +7402,41 @@
         <v>602</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I54" s="7"/>
       <c r="J54" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7491,37 +7447,37 @@
         <v>748</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="342.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7529,41 +7485,41 @@
         <v>721</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I56" s="7"/>
       <c r="J56" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7571,41 +7527,41 @@
         <v>724</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I57" s="7"/>
       <c r="J57" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7613,41 +7569,41 @@
         <v>768</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I58" s="7"/>
       <c r="J58" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7655,41 +7611,41 @@
         <v>774</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I59" s="7"/>
       <c r="J59" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="261.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7697,41 +7653,41 @@
         <v>780</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I60" s="7"/>
       <c r="J60" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="273" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7739,38 +7695,38 @@
         <v>788</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I61" s="7"/>
       <c r="J61" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>74</v>
@@ -7787,35 +7743,35 @@
         <v>820</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>74</v>
@@ -7826,41 +7782,41 @@
         <v>801</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P63" s="1" t="n">
         <v>3</v>
@@ -7871,41 +7827,41 @@
         <v>865</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="319.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7913,41 +7869,41 @@
         <v>872</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P65" s="1" t="n">
         <v>3</v>
@@ -7958,38 +7914,38 @@
         <v>900</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>74</v>
@@ -8000,38 +7956,38 @@
         <v>942</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>74</v>
@@ -8042,41 +7998,41 @@
         <v>947</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="251.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8087,38 +8043,38 @@
         <v>1048</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="228.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8126,41 +8082,41 @@
         <v>980</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P70" s="1" t="n">
         <v>3</v>
@@ -8174,35 +8130,35 @@
         <v>1137</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>74</v>
@@ -8216,38 +8172,38 @@
         <v>1077</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8258,38 +8214,38 @@
         <v>1131</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="282" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8297,41 +8253,41 @@
         <v>1058</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P74" s="1" t="n">
         <v>3</v>
@@ -8342,41 +8298,41 @@
         <v>1095</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="316.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8384,41 +8340,41 @@
         <v>1105</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="189" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8426,41 +8382,41 @@
         <v>1126</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P77" s="1" t="n">
         <v>3</v>
@@ -8471,41 +8427,41 @@
         <v>1128</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8513,41 +8469,41 @@
         <v>1130</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P79" s="1" t="n">
         <v>3</v>
@@ -8561,38 +8517,38 @@
         <v>1193</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="289.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8600,44 +8556,44 @@
         <v>1138</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P81" s="1" t="n">
         <v>3</v>
@@ -8648,41 +8604,41 @@
         <v>1155</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P82" s="1" t="n">
         <v>3</v>
@@ -8693,41 +8649,41 @@
         <v>1165</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P83" s="1" t="n">
         <v>3</v>
@@ -8741,38 +8697,38 @@
         <v>1262</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="226.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8783,38 +8739,38 @@
         <v>1253</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P85" s="1" t="n">
         <v>3</v>
@@ -8825,41 +8781,41 @@
         <v>1201</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="240" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8867,41 +8823,41 @@
         <v>1207</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P87" s="1" t="n">
         <v>3</v>
@@ -8915,35 +8871,35 @@
         <v>1317</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>74</v>
@@ -8957,38 +8913,38 @@
         <v>1359</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I89" s="2"/>
       <c r="J89" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="296.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8999,38 +8955,38 @@
         <v>1390</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="283.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9038,41 +8994,41 @@
         <v>1332</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P91" s="1" t="n">
         <v>3</v>
@@ -9083,41 +9039,41 @@
         <v>1355</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I92" s="7"/>
       <c r="J92" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="233.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9125,38 +9081,38 @@
         <v>1357</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I93" s="7"/>
       <c r="J93" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>74</v>
@@ -9173,37 +9129,37 @@
         <v>1442</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9211,41 +9167,41 @@
         <v>1402</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I95" s="7"/>
       <c r="J95" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="204.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9253,38 +9209,38 @@
         <v>1440</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="I96" s="7"/>
       <c r="J96" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>74</v>
@@ -9298,38 +9254,38 @@
         <v>1547</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I97" s="7"/>
       <c r="J97" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>74</v>
@@ -9340,41 +9296,41 @@
         <v>1472</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I98" s="7"/>
       <c r="J98" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P98" s="1" t="n">
         <v>3</v>
@@ -9388,37 +9344,37 @@
         <v>1571</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P99" s="1" t="n">
         <v>3</v>
@@ -9429,41 +9385,41 @@
         <v>1527</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I100" s="7"/>
       <c r="J100" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="314.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9471,41 +9427,41 @@
         <v>1571</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I101" s="7"/>
       <c r="J101" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P101" s="1" t="n">
         <v>3</v>
@@ -9516,41 +9472,41 @@
         <v>1583</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I102" s="7"/>
       <c r="J102" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9558,41 +9514,41 @@
         <v>1599</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I103" s="7"/>
       <c r="J103" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P103" s="1" t="n">
         <v>3</v>
@@ -9603,38 +9559,38 @@
         <v>1615</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="I104" s="7"/>
       <c r="J104" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O104" s="1" t="s">
         <v>74</v>
@@ -9645,40 +9601,40 @@
         <v>1622</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="255.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9689,37 +9645,37 @@
         <v>1695</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9727,40 +9683,40 @@
         <v>1666</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="165" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9771,37 +9727,37 @@
         <v>1763</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9812,40 +9768,40 @@
         <v>1759</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G109" s="21" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="279.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9856,40 +9812,40 @@
         <v>1762</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>74</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="427.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9900,37 +9856,37 @@
         <v>1801</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="262.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9941,34 +9897,34 @@
         <v>1833</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E112" s="22" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="O112" s="1" t="s">
         <v>74</v>
@@ -9982,34 +9938,34 @@
         <v>1905</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="O113" s="1" t="s">
         <v>74</v>
@@ -10023,37 +9979,37 @@
         <v>1897</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10064,37 +10020,37 @@
         <v>1901</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10105,37 +10061,37 @@
         <v>1911</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10146,34 +10102,34 @@
         <v>1941</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E117" s="21" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G117" s="21" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="O117" s="1" t="s">
         <v>74</v>
@@ -10187,37 +10143,37 @@
         <v>1863</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="O118" s="1" t="s">
         <v>74</v>
@@ -10231,25 +10187,25 @@
         <v>1869</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J119" s="1" t="s">
         <v>70</v>
@@ -10258,10 +10214,10 @@
         <v>45</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="O119" s="1" t="s">
         <v>74</v>
@@ -10278,37 +10234,37 @@
         <v>1945</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P120" s="1" t="n">
         <v>3</v>
@@ -10319,37 +10275,37 @@
         <v>1872</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O121" s="1" t="s">
         <v>74</v>
@@ -10366,38 +10322,38 @@
         <v>1949</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="I122" s="2"/>
       <c r="J122" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="291.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10405,40 +10361,40 @@
         <v>1877</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>74</v>
@@ -10452,40 +10408,40 @@
         <v>1938</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="N124" s="1" t="s">
         <v>74</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10496,34 +10452,34 @@
         <v>1950</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E125" s="21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="J125" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="O125" s="1" t="s">
         <v>74</v>
@@ -10537,22 +10493,22 @@
         <v>1956</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E126" s="18" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="J126" s="1" t="s">
         <v>70</v>
@@ -10561,10 +10517,10 @@
         <v>54</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="O126" s="1" t="s">
         <v>74</v>
@@ -10581,34 +10537,34 @@
         <v>1986</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E127" s="21" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O127" s="1" t="s">
         <v>74</v>
@@ -10622,37 +10578,37 @@
         <v>2001</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E128" s="18" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P128" s="1" t="n">
         <v>3</v>
@@ -10666,37 +10622,37 @@
         <v>1966</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E129" s="21" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="O129" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10707,37 +10663,37 @@
         <v>1972</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P130" s="1" t="n">
         <v>3</v>
@@ -10751,37 +10707,37 @@
         <v>2008</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P131" s="1" t="n">
         <v>3</v>
@@ -10792,43 +10748,43 @@
         <v>1917</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10839,37 +10795,37 @@
         <v>1986</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P133" s="1" t="n">
         <v>3</v>
@@ -10883,37 +10839,37 @@
         <v>1961</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P134" s="1" t="n">
         <v>3</v>
@@ -10924,40 +10880,40 @@
         <v>1931</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10965,40 +10921,40 @@
         <v>1931</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P136" s="1" t="n">
         <v>3</v>
@@ -11009,40 +10965,40 @@
         <v>1934</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>54</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11050,43 +11006,43 @@
         <v>1935</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E138" s="18" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11094,40 +11050,40 @@
         <v>1935</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11138,37 +11094,37 @@
         <v>2005</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11176,40 +11132,40 @@
         <v>1941</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11217,40 +11173,40 @@
         <v>1942</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P142" s="1" t="n">
         <v>3</v>
@@ -11261,25 +11217,25 @@
         <v>1943</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="J143" s="1" t="s">
         <v>25</v>
@@ -11288,13 +11244,13 @@
         <v>26</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="70.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11304,22 +11260,13 @@
       <c r="E145" s="10"/>
     </row>
     <row r="146" customFormat="false" ht="270.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0"/>
-      <c r="B146" s="0"/>
-      <c r="C146" s="0"/>
-      <c r="D146" s="0"/>
-      <c r="E146" s="0"/>
-      <c r="F146" s="0"/>
-      <c r="G146" s="0"/>
-      <c r="H146" s="0"/>
-      <c r="I146" s="0"/>
-      <c r="J146" s="0"/>
-      <c r="K146" s="0"/>
-      <c r="L146" s="0"/>
-      <c r="M146" s="0"/>
-      <c r="O146" s="0"/>
-      <c r="XFC146" s="0"/>
-      <c r="XFD146" s="0"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
     </row>
     <row r="147" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="n">
@@ -11329,25 +11276,25 @@
         <v>-2480</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="J147" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="L147" s="1" t="s">
         <v>27</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="O147" s="1" t="s">
         <v>29</v>
@@ -11361,25 +11308,25 @@
         <v>-2400</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>29</v>
@@ -11393,28 +11340,28 @@
         <v>-2250</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O149" s="1" t="s">
         <v>29</v>
@@ -11431,25 +11378,25 @@
         <v>-1750</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E150" s="10" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>62</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>29</v>
@@ -11466,25 +11413,25 @@
         <v>-1337</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>29</v>
@@ -11501,25 +11448,25 @@
         <v>-1100</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>29</v>
@@ -11533,13 +11480,13 @@
         <v>-1100</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>25</v>
@@ -11551,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>29</v>
@@ -11565,25 +11512,25 @@
         <v>-1150</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="O154" s="1" t="s">
         <v>29</v>
@@ -11597,25 +11544,25 @@
         <v>-930</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="O155" s="1" t="s">
         <v>29</v>
@@ -11632,25 +11579,25 @@
         <v>-900</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="O156" s="1" t="s">
         <v>29</v>
@@ -11664,25 +11611,25 @@
         <v>-640</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="O157" s="1" t="s">
         <v>29</v>
@@ -11696,28 +11643,28 @@
         <v>-400</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O158" s="1" t="s">
         <v>29</v>
@@ -11734,25 +11681,25 @@
         <v>-270</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>29</v>
@@ -11766,28 +11713,28 @@
         <v>-220</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O160" s="1" t="s">
         <v>29</v>
@@ -11804,13 +11751,13 @@
         <v>-100</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>25</v>
@@ -11822,7 +11769,7 @@
         <v>27</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="O161" s="1" t="s">
         <v>29</v>
@@ -11836,25 +11783,25 @@
         <v>222</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>81</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="O162" s="1" t="s">
         <v>29</v>
@@ -11868,31 +11815,31 @@
         <v>117</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>45</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P163" s="1" t="n">
         <v>2</v>
@@ -11906,28 +11853,28 @@
         <v>1160</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="J164" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>74</v>
@@ -11941,31 +11888,31 @@
         <v>932</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11976,28 +11923,28 @@
         <v>944</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12008,28 +11955,28 @@
         <v>936</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P167" s="1" t="n">
         <v>3</v>
@@ -12043,31 +11990,31 @@
         <v>942</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P168" s="1" t="n">
         <v>3</v>
@@ -12081,28 +12028,28 @@
         <v>931</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12113,28 +12060,28 @@
         <v>1064</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P170" s="1" t="n">
         <v>3</v>
@@ -12148,28 +12095,28 @@
         <v>1088</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12180,31 +12127,31 @@
         <v>1058</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P172" s="1" t="n">
         <v>3</v>
@@ -12218,31 +12165,31 @@
         <v>1120</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12253,31 +12200,31 @@
         <v>1141</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="N174" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O174" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P174" s="1" t="n">
         <v>3</v>
@@ -12291,31 +12238,31 @@
         <v>1167</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="N175" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O175" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12326,31 +12273,31 @@
         <v>1180</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12361,28 +12308,28 @@
         <v>1210</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="O177" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12393,31 +12340,31 @@
         <v>1270</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O178" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12428,28 +12375,28 @@
         <v>1328</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="O179" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P179" s="1" t="n">
         <v>2</v>
@@ -12463,31 +12410,31 @@
         <v>1411</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O180" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12498,31 +12445,31 @@
         <v>1444</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O181" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12533,31 +12480,31 @@
         <v>1508</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O182" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12568,28 +12515,28 @@
         <v>1631</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="O183" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12600,28 +12547,28 @@
         <v>1873</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="J184" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P184" s="1" t="n">
         <v>2</v>
@@ -12635,28 +12582,28 @@
         <v>1905</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P185" s="1" t="n">
         <v>3</v>
@@ -12670,28 +12617,28 @@
         <v>1966</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="J186" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12702,31 +12649,31 @@
         <v>1973</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O187" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12737,31 +12684,31 @@
         <v>2010</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K188" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O188" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P188" s="1" t="n">
         <v>3</v>
@@ -12775,31 +12722,31 @@
         <v>1977</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O189" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P189" s="1" t="n">
         <v>2</v>
@@ -12813,28 +12760,28 @@
         <v>2021</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="O190" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12845,31 +12792,31 @@
         <v>2009</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O191" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12880,31 +12827,31 @@
         <v>2015</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P192" s="1" t="n">
         <v>2</v>
@@ -12923,7 +12870,7 @@
     <hyperlink ref="E9" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Akshapada_Gautama&quot; title=&quot; Wikipedia&quot;&gt;Akshapada Gautama&lt;/a&gt; est le sage fondateur traditionnel de l’école Nyâya, l’une des six écoles orthodoxes (&lt;em&gt;āstika&lt;/em&gt;) de la philosophie indienne. Auteur présumé des &lt;em&gt;Nyâya-sûtras&lt;/em&gt;, il y pose les bases d’une logique et d’une épistémologie rigoureuses, centrées sur les moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : perception, inférence, comparaison et témoignage. Le&lt;a href=&quot;https://www.youtube.com/watch?v=axjvz9FZPfU&quot;  title=&quot;Nyaya philosophy par TrueColors&quot;&gt; Nyâya &lt;/a&gt; a profondément influencé le débat philosophique indien pendant plus de deux millénaires, notamment dans ses joutes argumentatives avec le bouddhisme et le jaïnisme.&lt;/p&gt;"/>
     <hyperlink ref="H9" r:id="rId4" display="https://www.laphilo.fr/pho/agautama-mini.webp"/>
     <hyperlink ref="H10" r:id="rId5" display="https://www.laphilo.fr/pho/deserpere-mini.webp"/>
-    <hyperlink ref="E11" r:id="rId6" display="https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our"/>
+    <hyperlink ref="E11" r:id="rId6" display="&lt;p&gt;Les &lt;a href=&quot;https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our&quot;  title=&quot; Wikipedia&quot;&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie. Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Il reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui   &lt;a href=&quot;https://www.worldhistory.org/trans/fr/2-981/lamentations-dipou-our/&quot;   title=&quot;lamentations d’Ipou-Our par worldhistory&quot;&gt;des « lamentations »,&lt;/a&gt;  qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;"/>
     <hyperlink ref="H11" r:id="rId7" display="https://www.laphilo.fr/pho/iour-mini.webp"/>
     <hyperlink ref="H13" r:id="rId8" display="https://www.laphilo.fr/pho/vishvamitra-mini.webp"/>
     <hyperlink ref="H15" r:id="rId9" display="https://www.laphilo.fr/pho/maitreyi-mini.webp"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -315,10 +315,10 @@
     <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our"  title=" Wikipedia"&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie. Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Il reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui   &lt;a href="https://www.worldhistory.org/trans/fr/2-981/lamentations-dipou-our/"   title="lamentations d’Ipou-Our par worldhistory"&gt;des « lamentations »,&lt;/a&gt;  qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">VL-OWz8Awm0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Ipuwer Payrus par Evidence 4 faith</t>
+    <t xml:space="preserve">vL-OWz8Awm0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Ipuwer Papyrus par Evidence 4 faith</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/iour-mini.webp</t>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -5789,8 +5789,10 @@
       <c r="K7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>53</v>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M7" s="2" t="s">
         <v>54</v>
@@ -5872,8 +5874,10 @@
       <c r="K9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M9" s="2" t="s">
         <v>71</v>
@@ -6125,8 +6129,10 @@
       <c r="K15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>53</v>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M15" s="2" t="s">
         <v>122</v>
@@ -6170,8 +6176,10 @@
       <c r="K16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>53</v>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M16" s="2" t="s">
         <v>131</v>
@@ -6338,8 +6346,10 @@
       <c r="K20" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>53</v>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M20" s="2" t="s">
         <v>165</v>
@@ -12035,8 +12045,10 @@
       <c r="K154" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="L154" s="2" t="s">
-        <v>53</v>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M154" s="2" t="s">
         <v>1289</v>
@@ -12067,8 +12079,10 @@
       <c r="K155" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L155" s="2" t="s">
-        <v>53</v>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M155" s="2" t="s">
         <v>1293</v>
@@ -12137,8 +12151,10 @@
       <c r="K157" s="2" t="s">
         <v>1301</v>
       </c>
-      <c r="L157" s="2" t="s">
-        <v>53</v>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
       </c>
       <c r="M157" s="2" t="s">
         <v>1302</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -7340,8 +7340,10 @@
       <c r="K43" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>361</v>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
       </c>
       <c r="M43" s="2" t="s">
         <v>362</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="1464">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES ORIENTAUX</t>
   </si>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">ethique;politique</t>
   </si>
   <si>
-    <t xml:space="preserve">Mysticisme</t>
+    <t xml:space="preserve">Mésopotamie antique</t>
   </si>
   <si>
     <t xml:space="preserve">sage légendaire de Sumer, à qui sont attribuées les plus anciennes instructions de sagesse connues.</t>
@@ -621,6 +621,37 @@
     <t xml:space="preserve">sage-voyant védique, compositeur traditionnel d'hymnes du Rig-Véda, figure fondatrice du védisme.</t>
   </si>
   <si>
+    <t xml:space="preserve">vers 1500 A JC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZARATHOUSTRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zarathoustra"  title=" Wikipedia"&gt;ZARATHOUSTRA&lt;/a&gt;, ou Zoroastre, est le prophète fondateur  &lt;a href="https://www.youtube.com/watch?v=bRmvF4sSxRs" title="Le zoroastrisme, religion du feu par Nat Geo Fr"&gt;du zoroastrisme, &lt;/a&gt;  la religion de l'Iran ancien. Ses dates sont très discutées : l'analyse de la langue des &lt;em&gt;Gathas&lt;/em&gt;, les hymnes qui lui sont attribués, conduit aujourd'hui la plupart des spécialistes à le situer vers l'an 1000 avant J.-C.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AupMQo89m6Y" title="avant Jésus, Mahomet par collapX"&gt;Sa pensée &lt;/a&gt;  repose sur l'opposition entre deux principes : l'esprit du bien, lié à Ahura Mazda, le « Seigneur sage », et l'esprit du mal et du mensonge. Chaque être humain est libre de choisir son camp par ses pensées, ses paroles et ses actions, et sera jugé selon ce choix.&lt;/p&gt; &lt;p&gt;Selon la tradition, il reçut sa révélation vers l'âge de trente ans, lors d'une vision au bord d'une rivière. Il dut affronter l'hostilité des prêtres de l'ancienne religion avant de trouver un protecteur, le roi Vishtaspa, qui se convertit à son enseignement. Ses &lt;em&gt;Gathas&lt;/em&gt;, dix-sept hymnes écrits dans une langue très archaïque, forment la partie la plus ancienne de l'Avesta, le livre sacré du zoroastrisme.&lt;/p&gt; &lt;p&gt;Le zoroastrisme devint plus tard la religion des grands empires perses, des Achéménides aux Sassanides, jusqu'à la conquête arabe au VIIe siècle. Il survit aujourd'hui dans de petites communautés en Iran et chez les Parsis de l'Inde. &lt;a href="https://www.histoire-et-civilisations.com/thematiques/antiquite/zarathoustra-le-prophete-du-feu-69413.php" title="Zarathoustra, le prophète du feu par histoire et civilisations"&gt; Le feu, symbole de la vérité &lt;/a&gt;  et de la pureté, y occupe une place centrale, ce qui a valu aux zoroastriens le nom, inexact, d'« adorateurs du feu ».&lt;/p&gt; &lt;p&gt;Cette vision d'un combat cosmique entre le bien et le mal, de la responsabilité morale individuelle et d'un jugement final a profondément influencé le judaïsme, le christianisme et l'islam. Nietzsche a repris son nom dans &lt;em&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ainsi_parlait_Zarathoustra" title="ainsi parlait Zarathoutra par wikipedia"&gt;Ainsi parlait Zarathoustra &lt;/a&gt; &lt;/em&gt;.&lt;/p&gt; &lt;audio controls title="L’iran, de Zarathoustra aux ayatollahs par France Culture"&gt;&lt;source src="https://media.radiofrance-podcast.net/podcast09/14006-17.10.2015-ITEMA_20820029-2015M22763E0049-21.mp3" type="audio/mpeg"&gt; &lt;/audio&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y6vHoF_GR68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Zarathoustra  – Le Prophète de la Lumière par Morale Mots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/zarathoustra-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spiritualite;ethique;metaphysique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoroastrisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prophète iranien, fondateur du zoroastrisme, penseur du combat entre le bien et le mal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">-1380</t>
   </si>
   <si>
@@ -736,6 +767,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;a href="https://www.pheniciens.com/articles/religion.php" title="La religion phénicienne par pheniciens,com"&gt;</t>
     </r>
@@ -755,6 +787,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;a href="https://www.mission-ougarit.fr/wp-content/pdf/mission_ougarit_publication_rso_121.pdf" title="Les textes rituels Ougarit XII par mission-ougarit"&gt;</t>
     </r>
@@ -786,131 +819,6 @@
   </si>
   <si>
     <t xml:space="preserve">auteur phénicien d'une histoire des origines du monde et des dieux, connue par Philon de Byblos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vers 1000 A JC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZARATHOUSTRA</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zarathoustra"  title=" Wikipedia"&gt;ZARATHOUSTRA&lt;/a&gt;, ou Zoroastre, est le prophète fondateur </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;a href="https://www.youtube.com/watch?v=bRmvF4sSxRs" title="Le zoroastrisme, religion du feu par Nat Geo Fr"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">du zoroastrisme, &lt;/a&gt;  la religion de l'Iran ancien. Ses dates sont très discutées : l'analyse de la langue des &lt;em&gt;Gathas&lt;/em&gt;, les hymnes qui lui sont attribués, conduit aujourd'hui la plupart des spécialistes à le situer vers l'an 1000 avant J.-C.&lt;/p&gt; &lt;p&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;a href="https://www.youtube.com/watch?v=AupMQo89m6Y" title="avant Jésus, Mahomet par collapX"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sa pensée &lt;/a&gt;  repose sur l'opposition entre deux principes : l'esprit du bien, lié à Ahura Mazda, le « Seigneur sage », et l'esprit du mal et du mensonge. Chaque être humain est libre de choisir son camp par ses pensées, ses paroles et ses actions, et sera jugé selon ce choix.&lt;/p&gt; &lt;p&gt;Selon la tradition, il reçut sa révélation vers l'âge de trente ans, lors d'une vision au bord d'une rivière. Il dut affronter l'hostilité des prêtres de l'ancienne religion avant de trouver un protecteur, le roi Vishtaspa, qui se convertit à son enseignement. Ses &lt;em&gt;Gathas&lt;/em&gt;, dix-sept hymnes écrits dans une langue très archaïque, forment la partie la plus ancienne de l'Avesta, le livre sacré du zoroastrisme.&lt;/p&gt; &lt;p&gt;Le zoroastrisme devint plus tard la religion des grands empires perses, des Achéménides aux Sassanides, jusqu'à la conquête arabe au VIIe siècle. Il survit aujourd'hui dans de petites communautés en Iran et chez les Parsis de l'Inde.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;a href="https://www.histoire-et-civilisations.com/thematiques/antiquite/zarathoustra-le-prophete-du-feu-69413.php" title="Zarathoustra, le prophète du feu par histoire et civilisations"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Le feu, symbole de la vérité &lt;/a&gt;  et de la pureté, y occupe une place centrale, ce qui a valu aux zoroastriens le nom, inexact, d'« adorateurs du feu ».&lt;/p&gt; &lt;p&gt;Cette vision d'un combat cosmique entre le bien et le mal, de la responsabilité morale individuelle et d'un jugement final a profondément influencé le judaïsme, le christianisme et l'islam. Nietzsche a repris son nom dans &lt;em&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/Ainsi_parlait_Zarathoustra" title="ainsi parlait Zarathoutra par wikipedia"&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ainsi parlait Zarathoustra &lt;/a&gt; &lt;/em&gt;.&lt;/p&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;audio controls title="L’iran, de Zarathoustra aux ayatollahs par France Culture"&gt;&lt;source src="https://media.radiofrance-podcast.net/podcast09/14006-17.10.2015-ITEMA_20820029-2015M22763E0049-21.mp3" type="audio/mpeg"&gt; &lt;/audio&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Y6vHoF_GR68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Zarathoustra  – Le Prophète de la Lumière par Morale Mots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/zarathoustra-mini.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spiritualite;ethique;metaphysique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoroastrisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prophète iranien, fondateur du zoroastrisme, penseur du combat entre le bien et le mal.</t>
   </si>
   <si>
     <t xml:space="preserve">820 A JC – 750 A JC</t>
@@ -1471,9 +1379,6 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/kautilya-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Légisme</t>
-  </si>
-  <si>
     <t xml:space="preserve">penseur politique, économiste et stratège indien antique.</t>
   </si>
   <si>
@@ -1524,6 +1429,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.laphilo.fr/pho/fei-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Légisme</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe et penseur politique chinois précurseur de Machiavel.</t>
@@ -3860,6 +3768,9 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/ggurdjieff-mini.webp</t>
   </si>
   <si>
+    <t xml:space="preserve">Mysticisme</t>
+  </si>
+  <si>
     <t xml:space="preserve"> philosophe et chorégraphe d'origine gréco-arménienne, figure influente du mysticisme.</t>
   </si>
   <si>
@@ -4405,6 +4316,9 @@
   </si>
   <si>
     <t xml:space="preserve">philosophe égyptien islamologue moderne, critique du discours religieux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vers 1000 A JC</t>
   </si>
   <si>
     <t xml:space="preserve">Dialogue du PESSIMISME</t>
@@ -4942,7 +4856,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5043,18 +4957,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -5244,7 +5146,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5256,19 +5170,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5276,7 +5178,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5284,7 +5186,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5789,10 +5691,8 @@
       <c r="K7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+      <c r="L7" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>54</v>
@@ -5874,10 +5774,8 @@
       <c r="K9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+      <c r="L9" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>71</v>
@@ -6129,10 +6027,8 @@
       <c r="K15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+      <c r="L15" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>122</v>
@@ -6176,10 +6072,8 @@
       <c r="K16" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+      <c r="L16" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>131</v>
@@ -6229,249 +6123,250 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="208.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>-1460</v>
-      </c>
-      <c r="B18" s="7" t="s">
+    <row r="18" customFormat="false" ht="87.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>-930</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="J18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="114.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>-1370</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>-1337</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="P18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="XFC18" s="0"/>
+      <c r="XFD18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="208.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>-1460</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="D19" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="E19" s="8" t="s">
         <v>154</v>
       </c>
+      <c r="F19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="8"/>
       <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P19" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="51.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="20" customFormat="false" ht="114.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>-1300</v>
+        <v>-1370</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>-1100</v>
+        <v>-1337</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+        <v>165</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P20" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="51.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>-1100</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>36</v>
+        <v>174</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="288.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>-1200</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>-1150</v>
+        <v>-1100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="XFC22" s="0"/>
-      <c r="XFD22" s="0"/>
-    </row>
-    <row r="23" customFormat="false" ht="415.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="23" customFormat="false" ht="288.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>-930</v>
+        <v>-1150</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G23" s="13" t="s">
         <v>185</v>
       </c>
+      <c r="G23" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="H23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>189</v>
@@ -6481,9 +6376,6 @@
       </c>
       <c r="O23" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="318.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7340,13 +7232,11 @@
       <c r="K43" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
+      <c r="L43" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>100</v>
@@ -7360,34 +7250,34 @@
         <v>-250</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="F44" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K44" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="M44" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>271</v>
@@ -7398,25 +7288,25 @@
         <v>-280</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="D45" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="F45" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="G45" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>377</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>378</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="1" t="s">
@@ -7426,7 +7316,7 @@
         <v>304</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>379</v>
@@ -7765,7 +7655,7 @@
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>206</v>
@@ -8103,7 +7993,7 @@
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>80</v>
@@ -8438,7 +8328,7 @@
       </c>
       <c r="I69" s="8"/>
       <c r="J69" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>592</v>
@@ -8612,7 +8502,7 @@
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>409</v>
@@ -8654,7 +8544,7 @@
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>268</v>
@@ -8825,7 +8715,7 @@
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>592</v>
@@ -8867,7 +8757,7 @@
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>231</v>
@@ -8996,7 +8886,7 @@
       </c>
       <c r="I82" s="8"/>
       <c r="J82" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>130</v>
@@ -9038,7 +8928,7 @@
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>206</v>
@@ -9212,7 +9102,7 @@
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>742</v>
@@ -9389,7 +9279,7 @@
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>206</v>
@@ -9566,7 +9456,7 @@
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>231</v>
@@ -9608,7 +9498,7 @@
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>742</v>
@@ -9736,7 +9626,7 @@
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>742</v>
@@ -10211,7 +10101,7 @@
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>206</v>
@@ -11108,10 +10998,10 @@
         <v>197</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>53</v>
+        <v>1109</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>513</v>
@@ -11122,37 +11012,37 @@
         <v>1877</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E132" s="20" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1017</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N132" s="1" t="s">
         <v>513</v>
@@ -11169,34 +11059,34 @@
         <v>1938</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>206</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N133" s="1" t="s">
         <v>100</v>
@@ -11213,22 +11103,22 @@
         <v>1950</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="J134" s="1" t="s">
         <v>96</v>
@@ -11240,7 +11130,7 @@
         <v>602</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="O134" s="1" t="s">
         <v>100</v>
@@ -11254,22 +11144,22 @@
         <v>1956</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>96</v>
@@ -11278,10 +11168,10 @@
         <v>80</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="O135" s="1" t="s">
         <v>100</v>
@@ -11298,22 +11188,22 @@
         <v>1986</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>96</v>
@@ -11325,7 +11215,7 @@
         <v>641</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="O136" s="1" t="s">
         <v>100</v>
@@ -11339,34 +11229,34 @@
         <v>2001</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="O137" s="1" t="s">
         <v>660</v>
@@ -11383,22 +11273,22 @@
         <v>1966</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J138" s="1" t="s">
         <v>582</v>
@@ -11410,7 +11300,7 @@
         <v>799</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>271</v>
@@ -11424,22 +11314,22 @@
         <v>1972</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="J139" s="1" t="s">
         <v>1000</v>
@@ -11448,10 +11338,10 @@
         <v>80</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="O139" s="1" t="s">
         <v>660</v>
@@ -11468,34 +11358,34 @@
         <v>2008</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O140" s="1" t="s">
         <v>660</v>
@@ -11509,37 +11399,37 @@
         <v>1917</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J141" s="1" t="s">
         <v>874</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N141" s="1" t="s">
         <v>513</v>
@@ -11556,25 +11446,25 @@
         <v>1986</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E142" s="22" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>848</v>
@@ -11583,7 +11473,7 @@
         <v>1061</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="O142" s="1" t="s">
         <v>660</v>
@@ -11600,34 +11490,34 @@
         <v>1961</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>80</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="O143" s="1" t="s">
         <v>660</v>
@@ -11641,28 +11531,28 @@
         <v>1931</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>848</v>
@@ -11671,7 +11561,7 @@
         <v>1061</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>660</v>
@@ -11682,25 +11572,25 @@
         <v>1931</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>1000</v>
@@ -11712,7 +11602,7 @@
         <v>952</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>660</v>
@@ -11726,28 +11616,28 @@
         <v>1934</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>80</v>
@@ -11756,7 +11646,7 @@
         <v>1061</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="O146" s="1" t="s">
         <v>660</v>
@@ -11767,28 +11657,28 @@
         <v>1935</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="E147" s="20" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>1001</v>
@@ -11797,7 +11687,7 @@
         <v>952</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N147" s="1" t="s">
         <v>72</v>
@@ -11811,37 +11701,37 @@
         <v>1935</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>401</v>
@@ -11855,34 +11745,34 @@
         <v>2005</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="O149" s="1" t="s">
         <v>660</v>
@@ -11893,37 +11783,37 @@
         <v>1941</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L150" s="2" t="s">
         <v>1061</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>660</v>
@@ -11934,37 +11824,37 @@
         <v>1942</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>660</v>
@@ -11978,25 +11868,25 @@
         <v>1943</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>25</v>
@@ -12008,7 +11898,7 @@
         <v>398</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>401</v>
@@ -12033,27 +11923,25 @@
         <v>-900</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>181</v>
+        <v>1287</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="J154" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>1288</v>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+        <v>1290</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="O154" s="1" t="s">
         <v>29</v>
@@ -12067,13 +11955,13 @@
         <v>-640</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>51</v>
@@ -12081,13 +11969,11 @@
       <c r="K155" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+      <c r="L155" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="O155" s="1" t="s">
         <v>29</v>
@@ -12101,25 +11987,25 @@
         <v>-400</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E156" s="10" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="J156" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L156" s="2" t="s">
         <v>398</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="N156" s="1" t="s">
         <v>400</v>
@@ -12139,27 +12025,25 @@
         <v>-270</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="J157" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie antique</t>
-        </is>
+        <v>1303</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="O157" s="1" t="s">
         <v>29</v>
@@ -12173,13 +12057,13 @@
         <v>-220</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E158" s="10" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="J158" s="1" t="s">
         <v>396</v>
@@ -12191,7 +12075,7 @@
         <v>398</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>400</v>
@@ -12211,13 +12095,13 @@
         <v>-100</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="J159" s="1" t="s">
         <v>25</v>
@@ -12229,7 +12113,7 @@
         <v>27</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>29</v>
@@ -12243,25 +12127,25 @@
         <v>222</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>107</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="O160" s="1" t="s">
         <v>29</v>
@@ -12275,13 +12159,13 @@
         <v>117</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>267</v>
@@ -12293,7 +12177,7 @@
         <v>296</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="N161" s="1" t="s">
         <v>72</v>
@@ -12313,13 +12197,13 @@
         <v>1160</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>96</v>
@@ -12331,7 +12215,7 @@
         <v>641</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="N162" s="1" t="s">
         <v>72</v>
@@ -12348,13 +12232,13 @@
         <v>932</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="J163" s="1" t="s">
         <v>396</v>
@@ -12363,10 +12247,10 @@
         <v>346</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="N163" s="1" t="s">
         <v>400</v>
@@ -12383,25 +12267,25 @@
         <v>944</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K164" s="2" t="s">
         <v>138</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>401</v>
@@ -12415,13 +12299,13 @@
         <v>936</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="J165" s="1" t="s">
         <v>545</v>
@@ -12430,10 +12314,10 @@
         <v>138</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>401</v>
@@ -12450,13 +12334,13 @@
         <v>942</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="J166" s="1" t="s">
         <v>396</v>
@@ -12465,10 +12349,10 @@
         <v>206</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="N166" s="1" t="s">
         <v>400</v>
@@ -12488,13 +12372,13 @@
         <v>931</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="J167" s="1" t="s">
         <v>545</v>
@@ -12503,10 +12387,10 @@
         <v>138</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>401</v>
@@ -12520,25 +12404,25 @@
         <v>1064</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="J168" s="1" t="s">
         <v>545</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>401</v>
@@ -12555,16 +12439,16 @@
         <v>1088</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K169" s="2" t="s">
         <v>206</v>
@@ -12573,7 +12457,7 @@
         <v>511</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>401</v>
@@ -12587,25 +12471,25 @@
         <v>1058</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="N170" s="1" t="s">
         <v>400</v>
@@ -12625,13 +12509,13 @@
         <v>1120</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="J171" s="1" t="s">
         <v>396</v>
@@ -12640,10 +12524,10 @@
         <v>397</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>400</v>
@@ -12660,13 +12544,13 @@
         <v>1141</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="J172" s="1" t="s">
         <v>396</v>
@@ -12675,10 +12559,10 @@
         <v>742</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="N172" s="1" t="s">
         <v>400</v>
@@ -12698,13 +12582,13 @@
         <v>1167</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="J173" s="1" t="s">
         <v>396</v>
@@ -12713,10 +12597,10 @@
         <v>546</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="N173" s="1" t="s">
         <v>400</v>
@@ -12733,13 +12617,13 @@
         <v>1180</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="J174" s="1" t="s">
         <v>396</v>
@@ -12748,10 +12632,10 @@
         <v>206</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="N174" s="1" t="s">
         <v>400</v>
@@ -12768,25 +12652,25 @@
         <v>1210</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="O175" s="1" t="s">
         <v>401</v>
@@ -12800,13 +12684,13 @@
         <v>1270</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>396</v>
@@ -12815,13 +12699,13 @@
         <v>791</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="O176" s="1" t="s">
         <v>401</v>
@@ -12835,25 +12719,25 @@
         <v>1328</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>545</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="O177" s="1" t="s">
         <v>401</v>
@@ -12870,13 +12754,13 @@
         <v>1411</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>396</v>
@@ -12885,13 +12769,13 @@
         <v>231</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>401</v>
@@ -12905,28 +12789,28 @@
         <v>1444</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="J179" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="O179" s="1" t="s">
         <v>401</v>
@@ -12940,13 +12824,13 @@
         <v>1508</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>396</v>
@@ -12955,13 +12839,13 @@
         <v>1043</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>401</v>
@@ -12975,16 +12859,16 @@
         <v>1631</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K181" s="2" t="s">
         <v>206</v>
@@ -12993,7 +12877,7 @@
         <v>775</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>401</v>
@@ -13007,13 +12891,13 @@
         <v>1873</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="J182" s="1" t="s">
         <v>25</v>
@@ -13022,10 +12906,10 @@
         <v>304</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="O182" s="1" t="s">
         <v>401</v>
@@ -13042,25 +12926,25 @@
         <v>1905</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="O183" s="1" t="s">
         <v>401</v>
@@ -13077,13 +12961,13 @@
         <v>1966</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="J184" s="1" t="s">
         <v>25</v>
@@ -13092,10 +12976,10 @@
         <v>304</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>401</v>
@@ -13109,25 +12993,25 @@
         <v>1973</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K185" s="2" t="s">
         <v>304</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="N185" s="1" t="s">
         <v>660</v>
@@ -13144,25 +13028,25 @@
         <v>2010</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>1440</v>
+      </c>
+      <c r="J186" s="1" t="s">
         <v>1436</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E186" s="10" t="s">
-        <v>1438</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>1434</v>
       </c>
       <c r="K186" s="2" t="s">
         <v>26</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="N186" s="1" t="s">
         <v>513</v>
@@ -13182,25 +13066,25 @@
         <v>1977</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="K187" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="N187" s="1" t="s">
         <v>660</v>
@@ -13220,13 +13104,13 @@
         <v>2021</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>25</v>
@@ -13235,10 +13119,10 @@
         <v>1043</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>401</v>
@@ -13252,25 +13136,25 @@
         <v>2009</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="N189" s="1" t="s">
         <v>660</v>
@@ -13287,25 +13171,25 @@
         <v>2015</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K190" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="N190" s="1" t="s">
         <v>72</v>
@@ -13339,15 +13223,15 @@
     <hyperlink ref="H14" r:id="rId10" display="https://www.laphilo.fr/pho/iour-mini.webp"/>
     <hyperlink ref="H15" r:id="rId11" display="https://www.laphilo.fr/pho/hammurabi-mini.webp"/>
     <hyperlink ref="H17" r:id="rId12" display="https://www.laphilo.fr/pho/vishvamitra-mini.webp"/>
-    <hyperlink ref="E19" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Akhenaton&quot;  title=&quot; Wikipedia&quot;&gt;AKHENATON&lt;/a&gt;, d'abord nommé Amenhotep IV, fut pharaon d'Égypte et époux de Néfertiti et sans doute père de Toutânkhamon, il bouleversa la religion égyptienne en imposant le culte exclusif d'Aton, le disque solaire.&lt;/p&gt; &lt;p&gt;Il fit fermer les temples des autres dieux, fonda une nouvelle capitale, Akhetaton (Amarna), et composa ou inspira le &lt;em&gt;Grand Hymne à Aton&lt;/em&gt;, qui célèbre un dieu unique, créateur bienveillant de tous les êtres et de tous les peuples. On y voit souvent le premier monothéisme exclusif connu de l'histoire.&lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=yJz4jiDS3ak&quot; title=&quot;la révolution religieuse d’Akhenaton par ARTE&quot;&gt;La révolution d'Akhenaton &lt;/a&gt; ne fut pas seulement religieuse. L'art de son règne, dit « amarnien », rompt avec les conventions séculaires : le roi est représenté avec un visage allongé et un corps aux formes étranges, dans des scènes de vie familiale intimes, entouré de Néfertiti et de leurs filles, sous les rayons du disque solaire terminés par des mains qui tendent la vie.&lt;/p&gt; &lt;p&gt;Le Grand Hymne à Aton, gravé dans une tombe d'Amarna, célèbre la lumière qui fait vivre toute la création : les hommes, les animaux, les plantes et même les pays étrangers, dont le dieu a fait les langues différentes. Certains passages présentent de fortes ressemblances avec le psaume 104 de la Bible. Freud, dans &lt;em&gt;Moïse et le monothéisme&lt;/em&gt;, alla jusqu'à supposer un lien entre la réforme d'Akhenaton et la religion de Moïse, hypothèse très discutée.&lt;/p&gt; &lt;p&gt;Sa réforme fut effacée après sa mort, mais elle pose une question philosophique durable : celle d'un principe unique à l'origine du monde, et du lien entre la vérité religieuse et le pouvoir politique.&lt;/p&gt;    &lt;audio controls title=&quot;Akhenaton et les dieux d’Egypte par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14864-14.01.2003-ITEMA_23747403-2003F4864S0008-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="H19" r:id="rId14" display="https://www.laphilo.fr/pho/akhenaton-mini.webp"/>
-    <hyperlink ref="E20" r:id="rId15" display="&lt;p&gt;Le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ludlul_bel_nemeqi&quot;  title=&quot; Wikipedia&quot;&gt;LUDLUL bel nemeqi&lt;/a&gt;, ou &lt;em&gt;Poème du juste souffrant&lt;/em&gt;, est un texte babylonien de la seconde moitié du IIe millénaire avant J.-C. Son titre signifie « Je veux louer le Seigneur de la sagesse », c'est-à-dire le dieu Marduk.&lt;/p&gt; &lt;p&gt;Un homme pieux, Shubshi-meshre-Shakkan, raconte comment il a tout perdu : son rang, ses amis, sa santé, alors qu'il avait toujours honoré les dieux.  &lt;a href=&quot;https://www.worldhistory.org/trans/fr/2-226/ludlul-bel-nemeqi/&quot; title=&quot;ludlul bel nemequi par worldhistory&quot;&gt;Il s'interroge : &lt;/a&gt; les hommes peuvent-ils comprendre la volonté divine, quand ce qui leur semble bon déplaît aux dieux ? Finalement, Marduk le rétablit dans sa prospérité.&lt;/p&gt; &lt;p&gt;Le poème compte environ cinq cents vers répartis sur quatre tablettes. Sa description de la maladie est d'un réalisme saisissant : le juste souffrant perd le sommeil, l'appétit et la vue, ses membres se paralysent, ses proches l'abandonnent et ses ennemis se réjouissent. Les devins et les exorcistes ne trouvent aucune explication à son malheur, car il n'a commis aucune faute rituelle.&lt;/p&gt; &lt;p&gt;La guérison survient à la suite de rêves où apparaissent des envoyés de Marduk, qui purifient le malade et chassent les démons. Le poème se termine par une célébration de la puissance du dieu, capable de frapper comme de guérir. La leçon n'est pas que la souffrance a une raison compréhensible, mais que les voies divines dépassent la raison humaine et que l'homme doit garder confiance malgré tout.&lt;/p&gt; &lt;p&gt;Ce poème pose, bien avant le livre biblique de Job, la grande question de la souffrance de l'innocent et de la justice divine, un problème que la philosophie appellera plus tard la théodicée.&lt;/p&gt;"/>
-    <hyperlink ref="H20" r:id="rId16" display="https://www.laphilo.fr/pho/ludlul-mini.webp"/>
-    <hyperlink ref="E21" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amenemopet_(scribe)&quot;  title=&quot; Wikipedia&quot;&gt;AMEMOPET&lt;/a&gt; , fils de Kanakht, était un scribe égyptien de &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89poque_ramesside&quot; title=&quot;epoque ramesside par wikipedia&quot;&gt;l'époque Ramesside . &lt;/a&gt; Il composa pour son fils un &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=Q_zws-8V_9g&quot; title=&quot;sagesse egyptienne par sinouhe&quot;&gt;Enseignement &lt;/a&gt; &lt;/em&gt; en trente chapitres, l'un des plus beaux textes de sagesse de l'Égypte ancienne.&lt;/p&gt; &lt;p&gt;Il y oppose l'homme « silencieux », calme, honnête et maître de lui, à l'homme « emporté », colérique et avide. Il recommande de ne pas déplacer les bornes des champs, de ne pas se moquer des faibles, de ne pas s'enrichir par la fraude, et rappelle que l'homme ne connaît pas l'avenir : « l'homme est argile et paille, le dieu est son bâtisseur ».&lt;/p&gt; &lt;p&gt;L'enseignement est connu principalement par un papyrus conservé au British Museum, et par de nombreux fragments sur des tablettes d'écoliers, signe qu'il servait à la formation des scribes. Il se distingue des enseignements plus anciens par la place qu'il accorde à la vie intérieure : la vraie valeur de l'homme ne réside pas dans sa réussite sociale mais dans son calme, sa droiture et sa confiance en la divinité.&lt;/p&gt; &lt;p&gt;Le rapprochement avec la Bible est particulièrement frappant pour un passage des Proverbes (22,17 à 24,22), qui reprend souvent de très près les conseils d'Amenemopet, jusqu'à la mention de « trente » sentences. Cette parenté montre que les sages d'Israël connaissaient la littérature de sagesse égyptienne et s'en inspiraient, en l'adaptant à leur propre foi.&lt;/p&gt; &lt;p&gt;Plusieurs passages ont été rapprochés du livre biblique des Proverbes, ce qui montre la circulation des idées de sagesse dans tout le Proche-Orient ancien.&lt;/p&gt;"/>
-    <hyperlink ref="H21" r:id="rId18" display="https://www.laphilo.fr/pho/eamenemopet-mini.webp"/>
-    <hyperlink ref="H22" r:id="rId19" display="https://www.laphilo.fr/pho/sanchoniathon-mini.webp"/>
-    <hyperlink ref="E23" r:id="rId20" display="https://www.histoire-et-civilisations.com/thematiques/antiquite/zarathoustra-le-prophete-du-feu-69413.php"/>
-    <hyperlink ref="H23" r:id="rId21" display="https://www.laphilo.fr/pho/zarathoustra-mini.webp"/>
+    <hyperlink ref="E18" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Zarathoustra&quot;  title=&quot; Wikipedia&quot;&gt;ZARATHOUSTRA&lt;/a&gt;, ou Zoroastre, est le prophète fondateur  &lt;a href=&quot;https://www.youtube.com/watch?v=bRmvF4sSxRs&quot; title=&quot;Le zoroastrisme, religion du feu par Nat Geo Fr&quot;&gt;du zoroastrisme, &lt;/a&gt;  la religion de l'Iran ancien. Ses dates sont très discutées : l'analyse de la langue des &lt;em&gt;Gathas&lt;/em&gt;, les hymnes qui lui sont attribués, conduit aujourd'hui la plupart des spécialistes à le situer vers l'an 1000 avant J.-C.&lt;/p&gt; &lt;p&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=AupMQo89m6Y&quot; title=&quot;avant Jésus, Mahomet par collapX&quot;&gt;Sa pensée &lt;/a&gt;  repose sur l'opposition entre deux principes : l'esprit du bien, lié à Ahura Mazda, le « Seigneur sage », et l'esprit du mal et du mensonge. Chaque être humain est libre de choisir son camp par ses pensées, ses paroles et ses actions, et sera jugé selon ce choix.&lt;/p&gt; &lt;p&gt;Selon la tradition, il reçut sa révélation vers l'âge de trente ans, lors d'une vision au bord d'une rivière. Il dut affronter l'hostilité des prêtres de l'ancienne religion avant de trouver un protecteur, le roi Vishtaspa, qui se convertit à son enseignement. Ses &lt;em&gt;Gathas&lt;/em&gt;, dix-sept hymnes écrits dans une langue très archaïque, forment la partie la plus ancienne de l'Avesta, le livre sacré du zoroastrisme.&lt;/p&gt; &lt;p&gt;Le zoroastrisme devint plus tard la religion des grands empires perses, des Achéménides aux Sassanides, jusqu'à la conquête arabe au VIIe siècle. Il survit aujourd'hui dans de petites communautés en Iran et chez les Parsis de l'Inde. &lt;a href=&quot;https://www.histoire-et-civilisations.com/thematiques/antiquite/zarathoustra-le-prophete-du-feu-69413.php&quot; title=&quot;Zarathoustra, le prophète du feu par histoire et civilisations&quot;&gt; Le feu, symbole de la vérité &lt;/a&gt;  et de la pureté, y occupe une place centrale, ce qui a valu aux zoroastriens le nom, inexact, d'« adorateurs du feu ».&lt;/p&gt; &lt;p&gt;Cette vision d'un combat cosmique entre le bien et le mal, de la responsabilité morale individuelle et d'un jugement final a profondément influencé le judaïsme, le christianisme et l'islam. Nietzsche a repris son nom dans &lt;em&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ainsi_parlait_Zarathoustra&quot; title=&quot;ainsi parlait Zarathoutra par wikipedia&quot;&gt;Ainsi parlait Zarathoustra &lt;/a&gt; &lt;/em&gt;.&lt;/p&gt; &lt;audio controls title=&quot;L’iran, de Zarathoustra aux ayatollahs par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14006-17.10.2015-ITEMA_20820029-2015M22763E0049-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H18" r:id="rId14" display="https://www.laphilo.fr/pho/zarathoustra-mini.webp"/>
+    <hyperlink ref="E20" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Akhenaton&quot;  title=&quot; Wikipedia&quot;&gt;AKHENATON&lt;/a&gt;, d'abord nommé Amenhotep IV, fut pharaon d'Égypte et époux de Néfertiti et sans doute père de Toutânkhamon, il bouleversa la religion égyptienne en imposant le culte exclusif d'Aton, le disque solaire.&lt;/p&gt; &lt;p&gt;Il fit fermer les temples des autres dieux, fonda une nouvelle capitale, Akhetaton (Amarna), et composa ou inspira le &lt;em&gt;Grand Hymne à Aton&lt;/em&gt;, qui célèbre un dieu unique, créateur bienveillant de tous les êtres et de tous les peuples. On y voit souvent le premier monothéisme exclusif connu de l'histoire.&lt;/p&gt; &lt;p&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=yJz4jiDS3ak&quot; title=&quot;la révolution religieuse d’Akhenaton par ARTE&quot;&gt;La révolution d'Akhenaton &lt;/a&gt; ne fut pas seulement religieuse. L'art de son règne, dit « amarnien », rompt avec les conventions séculaires : le roi est représenté avec un visage allongé et un corps aux formes étranges, dans des scènes de vie familiale intimes, entouré de Néfertiti et de leurs filles, sous les rayons du disque solaire terminés par des mains qui tendent la vie.&lt;/p&gt; &lt;p&gt;Le Grand Hymne à Aton, gravé dans une tombe d'Amarna, célèbre la lumière qui fait vivre toute la création : les hommes, les animaux, les plantes et même les pays étrangers, dont le dieu a fait les langues différentes. Certains passages présentent de fortes ressemblances avec le psaume 104 de la Bible. Freud, dans &lt;em&gt;Moïse et le monothéisme&lt;/em&gt;, alla jusqu'à supposer un lien entre la réforme d'Akhenaton et la religion de Moïse, hypothèse très discutée.&lt;/p&gt; &lt;p&gt;Sa réforme fut effacée après sa mort, mais elle pose une question philosophique durable : celle d'un principe unique à l'origine du monde, et du lien entre la vérité religieuse et le pouvoir politique.&lt;/p&gt;    &lt;audio controls title=&quot;Akhenaton et les dieux d’Egypte par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14864-14.01.2003-ITEMA_23747403-2003F4864S0008-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H20" r:id="rId16" display="https://www.laphilo.fr/pho/akhenaton-mini.webp"/>
+    <hyperlink ref="E21" r:id="rId17" display="&lt;p&gt;Le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ludlul_bel_nemeqi&quot;  title=&quot; Wikipedia&quot;&gt;LUDLUL bel nemeqi&lt;/a&gt;, ou &lt;em&gt;Poème du juste souffrant&lt;/em&gt;, est un texte babylonien de la seconde moitié du IIe millénaire avant J.-C. Son titre signifie « Je veux louer le Seigneur de la sagesse », c'est-à-dire le dieu Marduk.&lt;/p&gt; &lt;p&gt;Un homme pieux, Shubshi-meshre-Shakkan, raconte comment il a tout perdu : son rang, ses amis, sa santé, alors qu'il avait toujours honoré les dieux.  &lt;a href=&quot;https://www.worldhistory.org/trans/fr/2-226/ludlul-bel-nemeqi/&quot; title=&quot;ludlul bel nemequi par worldhistory&quot;&gt;Il s'interroge : &lt;/a&gt; les hommes peuvent-ils comprendre la volonté divine, quand ce qui leur semble bon déplaît aux dieux ? Finalement, Marduk le rétablit dans sa prospérité.&lt;/p&gt; &lt;p&gt;Le poème compte environ cinq cents vers répartis sur quatre tablettes. Sa description de la maladie est d'un réalisme saisissant : le juste souffrant perd le sommeil, l'appétit et la vue, ses membres se paralysent, ses proches l'abandonnent et ses ennemis se réjouissent. Les devins et les exorcistes ne trouvent aucune explication à son malheur, car il n'a commis aucune faute rituelle.&lt;/p&gt; &lt;p&gt;La guérison survient à la suite de rêves où apparaissent des envoyés de Marduk, qui purifient le malade et chassent les démons. Le poème se termine par une célébration de la puissance du dieu, capable de frapper comme de guérir. La leçon n'est pas que la souffrance a une raison compréhensible, mais que les voies divines dépassent la raison humaine et que l'homme doit garder confiance malgré tout.&lt;/p&gt; &lt;p&gt;Ce poème pose, bien avant le livre biblique de Job, la grande question de la souffrance de l'innocent et de la justice divine, un problème que la philosophie appellera plus tard la théodicée.&lt;/p&gt;"/>
+    <hyperlink ref="H21" r:id="rId18" display="https://www.laphilo.fr/pho/ludlul-mini.webp"/>
+    <hyperlink ref="E22" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Amenemopet_(scribe)&quot;  title=&quot; Wikipedia&quot;&gt;AMEMOPET&lt;/a&gt; , fils de Kanakht, était un scribe égyptien de &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89poque_ramesside&quot; title=&quot;epoque ramesside par wikipedia&quot;&gt;l'époque Ramesside . &lt;/a&gt; Il composa pour son fils un &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=Q_zws-8V_9g&quot; title=&quot;sagesse egyptienne par sinouhe&quot;&gt;Enseignement &lt;/a&gt; &lt;/em&gt; en trente chapitres, l'un des plus beaux textes de sagesse de l'Égypte ancienne.&lt;/p&gt; &lt;p&gt;Il y oppose l'homme « silencieux », calme, honnête et maître de lui, à l'homme « emporté », colérique et avide. Il recommande de ne pas déplacer les bornes des champs, de ne pas se moquer des faibles, de ne pas s'enrichir par la fraude, et rappelle que l'homme ne connaît pas l'avenir : « l'homme est argile et paille, le dieu est son bâtisseur ».&lt;/p&gt; &lt;p&gt;L'enseignement est connu principalement par un papyrus conservé au British Museum, et par de nombreux fragments sur des tablettes d'écoliers, signe qu'il servait à la formation des scribes. Il se distingue des enseignements plus anciens par la place qu'il accorde à la vie intérieure : la vraie valeur de l'homme ne réside pas dans sa réussite sociale mais dans son calme, sa droiture et sa confiance en la divinité.&lt;/p&gt; &lt;p&gt;Le rapprochement avec la Bible est particulièrement frappant pour un passage des Proverbes (22,17 à 24,22), qui reprend souvent de très près les conseils d'Amenemopet, jusqu'à la mention de « trente » sentences. Cette parenté montre que les sages d'Israël connaissaient la littérature de sagesse égyptienne et s'en inspiraient, en l'adaptant à leur propre foi.&lt;/p&gt; &lt;p&gt;Plusieurs passages ont été rapprochés du livre biblique des Proverbes, ce qui montre la circulation des idées de sagesse dans tout le Proche-Orient ancien.&lt;/p&gt;"/>
+    <hyperlink ref="H22" r:id="rId20" display="https://www.laphilo.fr/pho/eamenemopet-mini.webp"/>
+    <hyperlink ref="H23" r:id="rId21" display="https://www.laphilo.fr/pho/sanchoniathon-mini.webp"/>
     <hyperlink ref="H24" r:id="rId22" display="https://www.laphilo.fr/pho/maitreyi-mini.webp"/>
     <hyperlink ref="E25" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Y%C4%81j%C3%B1avalkya&quot; title=&quot; Wikipedia&quot;&gt;Yâjñavalkya&lt;/a&gt; est l’un des grands sages (&lt;em&gt;ṛṣi&lt;/em&gt;) des Upanishads, figure centrale de la &lt;em&gt;Brihadâranyaka Upanishad&lt;/em&gt;. Il y développe une réflexion fondatrice sur l’identité entre le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et le principe universel (&lt;em&gt;brahman&lt;/em&gt;), posant les bases philosophiques du brahmanisme et, plus tard, du Vedânta.  &lt;a href=&quot;https://www.youtube.com/watch?v=tdfdWUqQrwE&quot;  title=&quot;a masterpiece of indian philosophy par BharatVerse&quot;&gt; Ses dialogues, &lt;/a&gt; notamment avec son épouse Maitreyî sur la nature du désir et de la connaissance, comptent parmi les textes fondateurs de la métaphysique indienne.&lt;/p&gt;"/>
     <hyperlink ref="H25" r:id="rId24" display="https://www.laphilo.fr/pho/yajnavalkya-mini.webp"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="1738">
   <si>
     <t xml:space="preserve">FRISE DES PHILOSOPHES ORIENTAUX</t>
   </si>
@@ -414,7 +414,7 @@
     <t xml:space="preserve">Dialogue entre un homme et son Ba par Atum</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.laphilo.fr/pho/deserpere-mini.webp</t>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/desespere-mini.webp</t>
   </si>
   <si>
     <t xml:space="preserve">metaphysique;ethique</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jabir_ibn_Hayyan"    title=" Wikipedia"&gt;Jabir ibn HAYYAN&lt;/a&gt; , également connu sous le nom de Geber en Occident, est une figure majeure de l'histoire des sciences, en particulier dans les domaines de &lt;a href="https://www.youtube.com/watch?v=kyz45wAJEd4" title="De l'alchimie à la chimie : JABIR IBN HAYYAN par l'Histoire Oubliée"&gt;la chimie et de l'alchimie&lt;/a&gt;. Il est souvent considéré comme le "père de la chimie" en raison de ses contributions pionnières à cette discipline.  Il était d'origine persane et a vécu pendant l'âge d'or de la civilisation islamique. &lt;/p&gt; &lt;p&gt;Il a laissé une œuvre immense, avec des centaines de traités attribués à son nom.  &lt;a href="https://www.youtube.com/watch?v=AC68Ds1zEG4"  title="Les scientifiques musulman par AbuMuslimfr"&gt;Ses contributions&lt;/a&gt; couvrent plusieurs domaines, notamment la chimie, l'alchimie, la médecine, la philosophie et l'astronomie. Il  a introduit une approche systématique et expérimentale en chimie, insistant sur l'importance de l'expérimentation et de l'observation et a développé des techniques de laboratoire telles que la distillation, la cristallisation, la sublimation et la calcination. Il a adopté et développé la théorie des quatre éléments (terre, eau, air, feu) d'Aristote, mais il a également introduit la notion de "qualités" (chaud, froid, sec, humide) pour expliquer les transformations chimiques. &lt;/p&gt; &lt;p&gt;  Il a écrit plus de  &lt;a href="https://www.persee.fr/doc/pharm_0035-2349_1992_num_80_292_3264_t1_0102_0000_2" title="Inventaire et première étude des Oeuvres de Geber  par Persée"&gt;3 000 traités&lt;/a&gt;, bien que beaucoup aient été perdus ou attribués à tort. Parmi ses œuvres les plus célèbres figurent : &lt;/p&gt; 
 &lt;dd&gt; -  &lt;a href="https://www.persee.fr/doc/bcai_0259-7373_1989_num_6_1_908_t1_0195_0000_3" style="color:#88A1E9" title="Les dix premiers traités du Livre des Soixante-dixr  par Persée"&gt;Le Livre des Soixante-Dix&lt;/a&gt; : Un texte alchimique majeur. &lt;/dd&gt; 
 &lt;dd&gt; - Le Livre des Balances : Où il explore les relations entre les substances et leurs propriétés. &lt;/dd&gt; 
-&lt;dd&gt; - Le Livre des Pierres : Une étude sur les minéraux et leurs utilisations. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Ses travaux ont été traduits en latin au Moyen Âge et ont eu une influence profonde sur les alchimistes et scientifiques européens, notamment Albert le Grand et Roger Bacon. Il est devenu une figure légendaire dans le monde islamique et au-delà, symbolisant la quête de connaissance et la transformation de la matière. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Ibn Khaldûn, itinéraire d'un penseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.03.2025-ITEMA_24045140-2025C26163E0007-ITE_00148375_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+&lt;dd&gt; - Le Livre des Pierres : Une étude sur les minéraux et leurs utilisations. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Ses travaux ont été traduits en latin au Moyen Âge et ont eu une influence profonde sur les alchimistes et scientifiques européens, notamment Albert le Grand et Roger Bacon. Il est devenu une figure légendaire dans le monde islamique et au-delà, symbolisant la quête de connaissance et la transformation de la matière. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Ibn Khaldûn, itinéraire d'un penseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.03.2025-ITEMA_24045140-2025C26163E0007-ITE_00148375_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">tFtl5Xi06E8</t>
@@ -2028,7 +2028,7 @@
 En 781, Il est est devenu le chef de l'école du palais à Aix-la-Chapelle où il a supervisé l'éducation des enfants de &lt;a href="https://www.youtube.com/watch?v=yqIEe4nptPI&amp;ab_channel=PierrickAuger"  title="L'Empire carolingien par Pierrick Auger"&gt;  l'Empire Carolingien&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;
 Il était un érudit polyvalent qui maîtrisait plusieurs langues, notamment le latin, le grec et le hébreu. Il a écrit de nombreux ouvrages sur la grammaire, la rhétorique, la logique et la théologie, et a également compilé des manuels d'enseignement pour les écoles. &lt;/p&gt; &lt;p&gt;
 Sous son l'influence, Charlemagne a lancé une réforme éducative  en Europe qui visait à améliorer la qualité de l'enseignement et à étendre l'accès à l'éducation. Il a également participé à la réforme liturgique de Charlemagne, qui visait à standardiser les pratiques religieuses dans l'Empire. &lt;/p&gt; &lt;p&gt;
-Il est mort en 804, mais son influence sur l'éducation en Europe a perduré pendant des siècles. Il est aujourd'hui considéré comme l'un des érudits les plus importants de son époque, et son travail a eu un impact significatif sur l'histoire de l'Europe et de l'éducation. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+Il est mort en 804, mais son influence sur l'éducation en Europe a perduré pendant des siècles. Il est aujourd'hui considéré comme l'un des érudits les plus importants de son époque, et son travail a eu un impact significatif sur l'histoire de l'Europe et de l'éducation. &lt;/p&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">A3P2E6ljEUU</t>
@@ -4847,6 +4847,828 @@
   </si>
   <si>
     <t xml:space="preserve">sociologue marocaine, figure du féminisme dans le monde arabe, auteure du Harem politique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">613 – 696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WONCH'EUK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Woncheuk"  title=" Wikipedia (en)"&gt;WONCH'EUK&lt;/a&gt; était un moine bouddhiste originaire du royaume de Silla qui passa toute sa vie en Chine des Tang, où il devint l’un des plus grands exégètes de l’école Yogācāra (« Rien-que-conscience »). Disciple du célèbre traducteur Xuanzang, il enseigna au monastère Ximing de Chang’an et participa aux grands chantiers de traduction des textes indiens.&lt;/p&gt; &lt;p&gt;Son commentaire du &lt;em&gt;Saṃdhinirmocana-sūtra&lt;/em&gt;, traduit en tibétain, fut étudié jusque dans les monastères du Tibet. Contre l’interprétation stricte de Kuiji, pour qui certains êtres sont à jamais privés de la nature de bouddha, Wonch’euk défend une lecture plus conciliante, selon laquelle tous les êtres peuvent atteindre l’Éveil. Cette recherche d’harmonie entre doctrines rivales annonce l’un des traits durables de la pensée bouddhiste coréenne.&lt;/p&gt; &lt;p&gt;Arrivé en Chine vers l’âge de quinze ans, il avait d’abord étudié les traités de l’école Shelun et de l’Abhidharma, avant le retour d’Inde de Xuanzang en 645 : cette double formation explique son indépendance d’esprit face à l’école officielle de Kuiji. L’impératrice Wu Zetian le tenait en si haute estime que, selon la tradition, elle refusa de le laisser repartir lorsque le royaume de Silla demanda son retour. Mort à Luoyang en 696, il repose près de Xi’an, au monastère de Xingjiao, aux côtés de Xuanzang et de Kuiji. Au Tibet, son commentaire, traduit au IXe siècle, était encore cité par Tsongkhapa, ce qui fait de lui l’un des rares penseurs coréens dont l’influence s’étendit jusqu’à l’Himalaya.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/woncheuk-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moine de Silla installé en Chine, grand exégète de l’école bouddhiste Yogācāra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">617 – 686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WONHYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wonhyo"  title=" Wikipedia"&gt;WONHYO&lt;/a&gt; est le penseur le plus célèbre du bouddhisme coréen. Moine du royaume de Silla, il renonça selon la tradition à son voyage d’étude en Chine après une nuit passée dans une grotte : il y avait bu avec délice une eau qui se révéla, au matin, recueillie dans un crâne, et comprit que la pureté et l’impureté ne dépendent que de l’esprit. Il quitta ensuite la vie monastique, eut un fils, le lettré Seol Chong, et parcourut les villages pour enseigner le bouddhisme au peuple par le chant et la danse.&lt;/p&gt; &lt;p&gt;Auteur de près d’une centaine d’ouvrages, dont un commentaire majeur de l’&lt;em&gt;Éveil de la foi dans le Mahāyāna&lt;/em&gt;, il développe une philosophie de l’« Esprit unique » (&lt;em&gt;ilsim&lt;/em&gt;) : toutes les réalités sont les manifestations d’un même esprit, à la fois pur et agité. Sa méthode du &lt;em&gt;hwajaeng&lt;/em&gt;, l’« harmonisation des controverses », cherche à montrer que des doctrines bouddhistes en apparence opposées sont des points de vue partiels sur une même vérité. Cette pensée de la conciliation a profondément marqué l’identité intellectuelle coréenne.&lt;/p&gt; &lt;p&gt;Ses œuvres franchirent rapidement les frontières : son commentaire du &lt;em&gt;Sûtra du samādhi adamantin&lt;/em&gt; fut si admiré en Chine qu’on lui donna le titre de « traité » (&lt;em&gt;non&lt;/em&gt;), d’ordinaire réservé aux écrits des bodhisattvas, et ses textes furent lus au Japon dès l’époque de Nara. Se faisant appeler « petit laïc » (&lt;em&gt;Sobeong geosa&lt;/em&gt;), il chantait dans les villages une « chanson sans entrave » (&lt;em&gt;muae&lt;/em&gt;) en s’accompagnant d’une gourde, et enseignait aux plus humbles qu’il suffit d’invoquer le nom du Bouddha Amitābha pour renaître en Terre pure. Son &lt;em&gt;Traité des dix approches pour concilier les controverses&lt;/em&gt; est souvent tenu pour le texte fondateur de l’esprit de synthèse coréen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/wonhyo-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moine de Silla, penseur de l’« Esprit unique » et de l’harmonisation des doctrines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">625 – 702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UISANG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Uisang"  title=" Wikipedia"&gt;UISANG&lt;/a&gt; était un moine de Silla, ami de Wonhyo, qui partit étudier en Chine auprès de Zhiyan, deuxième patriarche de l’école Huayan (en coréen &lt;em&gt;Hwaeom&lt;/em&gt;, « Ornementation fleurie »). De retour en Corée vers 670, il fonda le monastère de Buseoksa et fit du Hwaeom l’une des écoles dominantes du bouddhisme coréen.&lt;/p&gt; &lt;p&gt;Son œuvre principale, le &lt;em&gt;Diagramme du monde du Dharma de l’Unique Véhicule&lt;/em&gt;, condense en un poème de 210 caractères disposés en labyrinthe la doctrine de l’interpénétration universelle : « un est tout, tout est un ». Chaque phénomène contient et reflète tous les autres, si bien que le plus petit grain de poussière enveloppe l’univers entier. Cette vision d’un monde où rien n’existe isolément a nourri durablement la réflexion coréenne sur l’unité du réel.&lt;/p&gt; &lt;p&gt;Selon la tradition, Uisang serait rentré en Corée pour avertir le roi Munmu d’une attaque chinoise imminente. La légende de Buseoksa, le « monastère de la pierre flottante », raconte qu’une jeune Chinoise éprise de lui, Seonmyo, se changea en dragon pour protéger sa traversée, puis souleva un rocher pour chasser ceux qui s’opposaient à la fondation du monastère. Mais Uisang fut surtout un maître austère : il refusa les terres et les serviteurs offerts par le roi, au nom de l’égalité de tous dans le Dharma, et conseilla au souverain de gouverner avec droiture plutôt que de bâtir des remparts. Ses nombreux disciples fondèrent les « dix monastères du Hwaeom », qui firent de son école la colonne vertébrale du bouddhisme de Silla.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/uisang-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moine de Silla, fondateur de l’école coréenne Hwaeom de l’interpénétration universelle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">857 – vers 910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHOE CHIWON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ch%27oe_Ch%27iw%C5%8Fn"  title=" Wikipedia (en)"&gt;CHOE CHIWON&lt;/a&gt; était un lettré et poète de Silla envoyé en Chine à l’âge de douze ans, où il réussit l’examen impérial des Tang et servit comme fonctionnaire. Rentré en Corée, il proposa des réformes à une cour en déclin, puis, déçu, se retira dans les montagnes, où sa trace se perd au début du Xe siècle.&lt;/p&gt; &lt;p&gt;Considéré comme l’un des pères de la littérature et de la pensée lettrée coréennes, il est célèbre pour avoir décrit une « voie profonde et mystérieuse » propre à la Corée, le &lt;em&gt;pungnyu&lt;/em&gt;, qui réunirait en elle les enseignements du confucianisme, du bouddhisme et du taoïsme. Cette idée d’une synthèse des trois enseignements, plutôt que de leur opposition, fait de lui une figure fondatrice de la réflexion sur l’identité spirituelle coréenne.&lt;/p&gt; &lt;p&gt;En Chine, il se rendit célèbre par sa proclamation contre le rebelle Huang Chao (881), si éloquente que, selon la légende, le chef rebelle en tomba de son siège. De retour à Silla en 885, il se heurta au système des « rangs d’os », qui réservait les plus hautes charges à l’aristocratie de naissance : ses dix propositions de réforme, présentées à la reine Jinseong en 894, restèrent lettre morte. Son recueil &lt;em&gt;Gyewon pilgyeong&lt;/em&gt; est la plus ancienne anthologie personnelle conservée de la littérature coréenne, et ses inscriptions pour les stèles de grands moines témoignent de sa connaissance intime du bouddhisme Seon. La tradition veut qu’il ait fini sa vie dans les montagnes de Gaya, près du monastère de Haeinsa, où il serait devenu un immortel taoïste.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/cchiwon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré de Silla, penseur d’une voie coréenne unissant confucianisme, bouddhisme et taoïsme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1055 – 1101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UICHEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Uicheon"  title=" Wikipedia"&gt;UICHEON&lt;/a&gt; était un prince de la dynastie Goryeo, quatrième fils du roi Munjong, devenu moine dès l’enfance. Parti étudier en Chine des Song, il en rapporta des milliers de textes et entreprit de rassembler l’ensemble des commentaires bouddhistes d’Asie orientale dans un vaste canon complémentaire.&lt;/p&gt; &lt;p&gt;Inquiet de l’affrontement entre l’école doctrinale (&lt;em&gt;Gyo&lt;/em&gt;) et l’école méditative (&lt;em&gt;Seon&lt;/em&gt;), il fonda en Corée l’école Cheontae (Tiantai), qui voulait unir l’étude des textes et la pratique de la contemplation. Pour lui, la compréhension doctrinale et l’expérience méditative sont les deux ailes indissociables de la voie bouddhiste : l’une sans l’autre mène soit au savoir stérile, soit à une illumination illusoire.&lt;/p&gt; &lt;p&gt;Parti en 1085 pour la Chine des Song malgré l’opposition de la cour, il y rencontra pendant plus d’un an les grands maîtres des écoles Huayan et Tiantai, notamment Jingyuan à Hangzhou. De retour, il fit rechercher des textes jusqu’au Japon et dans le royaume des Liao, et publia en 1090 un catalogue de plus de mille ouvrages, base du « Canon complémentaire » (&lt;em&gt;Gyojang&lt;/em&gt;) imprimé au monastère de Heungwangsa. En 1097, il inaugura le monastère de Gukcheongsa, siège de la nouvelle école Cheontae, qui attira de nombreux moines venus du Seon. Mort à quarante-six ans, il reçut le titre posthume de « Grand Éveillé, maître du royaume » (&lt;em&gt;Daegak guksa&lt;/em&gt;). Son projet de réconciliation, resté inachevé, fut repris un siècle plus tard par Jinul.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/uicheon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prince et moine de Goryeo, fondateur de l’école Cheontae unissant étude et méditation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1158 – 1210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JINUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jinul"  title=" Wikipedia"&gt;JINUL&lt;/a&gt;, connu sous le nom de Bojo, est la grande figure du bouddhisme Seon (Zen) coréen. Moine de l’époque Goryeo, il refusa la corruption d’un clergé proche du pouvoir et fonda une communauté de pratique au monastère de Suseonsa, l’actuel Songgwangsa, à l’origine de l’ordre Jogye qui domine aujourd’hui le bouddhisme coréen.&lt;/p&gt; &lt;p&gt;Sa doctrine de l’« éveil soudain suivi d’une culture graduelle » (&lt;em&gt;dono jeomsu&lt;/em&gt;) soutient que l’on peut reconnaître d’un coup sa nature de bouddha, mais que les habitudes accumulées exigent ensuite une longue pratique pour être dissoutes. Il réconcilie ainsi la méditation Seon et l’étude des sûtras, en particulier ceux de l’école Hwaeom, et introduit en Corée la méditation sur les &lt;em&gt;hwadu&lt;/em&gt; (les kōans). Cette synthèse entre intuition immédiate et effort patient reste au cœur de la pratique bouddhiste coréenne.&lt;/p&gt; &lt;p&gt;Fait remarquable, Jinul n’eut jamais de maître attitré : il rapporte avoir connu trois éveils successifs à la lecture de textes, le &lt;em&gt;Sûtra de l’estrade&lt;/em&gt; du sixième patriarche, le commentaire du &lt;em&gt;Sûtra de l’ornementation fleurie&lt;/em&gt; par Li Tongxuan, puis les écrits du maître chinois Dahui. En 1190, il fonda la « Société de la méditation et de la sagesse » (&lt;em&gt;Jeonghye gyeolsa&lt;/em&gt;), une communauté qui voulait renouer avec la pratique contre le formalisme des examens monastiques. Ses &lt;em&gt;Secrets pour cultiver l’esprit&lt;/em&gt; (&lt;em&gt;Susim gyeol&lt;/em&gt;) exposent dans une langue simple sa doctrine de la « culture conjointe de la concentration et de la sagesse » : l’esprit apaisé et l’esprit lucide ne sont pas deux états, mais les deux faces d’une même nature originelle.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jinul-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maître Seon de Goryeo, théoricien de l’éveil soudain suivi d’une culture graduelle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1337 – 1392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEONG MONG-JU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jeong_Mong-ju"  title=" Wikipedia"&gt;JEONG MONG-JU&lt;/a&gt;, dit Poeun, était un lettré et homme d’État de la fin de Goryeo, considéré comme l’un des pères du néoconfucianisme coréen. Professeur à l’académie nationale, il diffusa l’étude des commentaires de Zhu Xi et promut les rites familiaux confucéens dans une société encore largement bouddhiste.&lt;/p&gt; &lt;p&gt;Resté fidèle à la dynastie Goryeo alors que Yi Seong-gye préparait la fondation de Joseon, il fut assassiné en 1392 sur le pont de Seonjuk, à Kaesong. Son poème « Même si je devais mourir cent fois » fit de lui le symbole de la loyauté confucéenne. Paradoxalement, la dynastie qu’il avait refusée l’honora ensuite comme un modèle de rectitude morale, et son intégrité inspira des générations de lettrés coréens.&lt;/p&gt; &lt;p&gt;Diplomate habile, il se rendit à plusieurs reprises en Chine des Ming et, en 1377, au Japon, où il obtint la libération de centaines de Coréens capturés par les pirates. Son maître Yi Saek le saluait comme « l’ancêtre de l’étude du principe en Orient », car ses interprétations des classiques, faites sans les commentaires chinois les plus récents, se révélèrent conformes à ceux-ci lorsqu’ils parvinrent en Corée. L’échange poétique qui précéda sa mort est resté dans toutes les mémoires : au fils de Yi Seong-gye, Yi Bang-won, qui l’invitait à s’accommoder du changement comme les lianes s’enlacent, il répondit par son « Chant du cœur fidèle » (&lt;em&gt;Dansimga&lt;/em&gt;), avant d’être abattu sur ordre de celui-ci. En 1517, ses tablettes furent placées dans le sanctuaire de Confucius, la plus haute consécration pour un lettré coréen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jmongju-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré de la fin de Goryeo, père du néoconfucianisme coréen et symbole de la loyauté.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1342 – 1398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEONG DO-JEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jeong_Do-jeon"  title=" Wikipedia"&gt;JEONG DO-JEON&lt;/a&gt;, dit Sambong, était un lettré néoconfucéen et le principal architecte idéologique de la dynastie Joseon, fondée en 1392. Conseiller de Yi Seong-gye, il conçut les institutions du nouvel État, dessina le plan de la capitale Hanyang, l’actuelle Séoul, et rédigea le &lt;em&gt;Code pour gouverner Joseon&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Réfutations du bouddhisme&lt;/em&gt;, il attaque la doctrine bouddhiste au nom du néoconfucianisme de Zhu Xi : en tenant le monde pour illusoire et en invitant à quitter sa famille, le bouddhisme détruirait selon lui les relations humaines et l’ordre social. Il défend un gouvernement fondé sur la bienveillance, où le peuple est « la racine de l’État » et où le pouvoir effectif revient à des ministres lettrés plutôt qu’au seul roi. Il fut tué en 1398 lors d’une lutte de succession.&lt;/p&gt; &lt;p&gt;Son engagement politique est né d’une expérience personnelle : exilé en 1375 pour s’être opposé à une politique favorable aux Mongols, il vécut près de dix ans parmi les paysans de la région de Naju, dont il partagea la pauvreté. Rallié à Yi Seong-gye en 1383, il participa à la réforme foncière de 1391, qui redistribua les terres des grandes familles et des monastères. C’est lui qui donna leur nom au palais de Gyeongbok et à ses portes, en les tirant des classiques confucéens. Tué en 1398 par Yi Bang-won, le futur roi Taejong, qui refusait un pouvoir dominé par les ministres, il fut longtemps tenu pour un traître : réhabilité au XIXe siècle seulement, il est aujourd’hui reconnu comme l’un des grands bâtisseurs de l’État coréen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jdojeon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">architecte néoconfucéen de la dynastie Joseon et critique du bouddhisme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1376 – 1433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIHWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kihwa"  title=" Wikipedia (en)"&gt;GIHWA&lt;/a&gt;, aussi appelé Hamheo Deuktong, était un moine Seon du début de la dynastie Joseon. Formé d’abord aux classiques confucéens, il se tourna vers le bouddhisme à la mort d’un ami et devint l’un des principaux maîtres de son temps.&lt;/p&gt; &lt;p&gt;Face aux attaques néoconfucéennes de Jeong Do-jeon, il rédigea l’&lt;em&gt;Exposé de l’orthodoxie&lt;/em&gt;, qui répond point par point aux accusations portées contre le bouddhisme. Il y montre que la compassion bouddhiste et la bienveillance confucéenne procèdent d’une même source, et que les trois enseignements, confucianisme, bouddhisme et taoïsme, convergent vers le même but. Ses commentaires du &lt;em&gt;Sûtra de l’Éveil parfait&lt;/em&gt; et du &lt;em&gt;Sûtra du Diamant&lt;/em&gt; restèrent une référence pour les moines coréens.&lt;/p&gt; &lt;p&gt;Ancien étudiant de l’académie confucéenne de Seonggyungwan, il connaissait de l’intérieur les arguments de ses adversaires, ce qui donne à sa défense une force particulière. Disciple de Muhak, le maître qui avait conseillé Yi Seong-gye lors de la fondation de Joseon, il fut appelé auprès de la cour par le roi Sejong. Dans l’&lt;em&gt;Exposé de l’orthodoxie&lt;/em&gt; (&lt;em&gt;Hyeonjeong non&lt;/em&gt;), il fait correspondre les cinq préceptes bouddhistes, comme l’interdiction de tuer ou de voler, aux cinq vertus constantes du confucianisme, et rappelle que les confucéens eux-mêmes prônent la bienveillance envers tous les êtres vivants : le bouddhisme ne détruit donc pas l’ordre social, il en approfondit les fondements. Pour Gihwa, une même vérité se dit simplement en plusieurs langues.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/gihwa-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moine Seon du début de Joseon, défenseur du bouddhisme face au néoconfucianisme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1482 – 1519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JO GWANG-JO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jo_Gwang-jo"  title=" Wikipedia"&gt;JO GWANG-JO&lt;/a&gt;, dit Jeongam, était un lettré et réformateur néoconfucéen du début du XVIe siècle. Appelé à la cour par le roi Jungjong, il voulut faire de la Corée une société gouvernée par la vertu, selon la « voie parfaite » des anciens sages.&lt;/p&gt; &lt;p&gt;Il introduisit les pactes villageois (&lt;em&gt;hyangyak&lt;/em&gt;), qui organisaient l’entraide et l’éducation morale à l’échelle locale, créa un mode de recrutement fondé sur la recommandation et le mérite moral, et combattit les privilèges accordés aux familles puissantes. Ses adversaires obtinrent sa disgrâce lors de la purge de 1519, et il fut condamné à boire le poison. Devenu un martyr de l’intégrité lettrée, il inspira toute l’école Sarim, dont sortiront Yi Hwang et Yi I.&lt;/p&gt; &lt;p&gt;Sa chute fut provoquée par une réforme audacieuse : en 1519, il obtint que plus de soixante-dix « sujets méritants », récompensés sans raison valable après le coup d’État de 1506, perdent leurs titres et leurs terres. Ses ennemis firent alors circuler, selon la tradition, des feuilles où des insectes avaient rongé, en suivant un tracé de miel, les caractères signifiant « Jo deviendra roi ». Le roi, lassé de ses exigences morales, l’abandonna. Exilé à Neungju puis contraint au suicide, Jo Gwang-jo écrivit avant de mourir qu’il avait aimé son roi comme son père. Réhabilité quelques décennies plus tard, il entra en 1610 dans le sanctuaire de Confucius, et son nom reste associé à l’idéal d’une politique soumise à la morale.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jgwangjo-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">réformateur néoconfucéen martyr, promoteur d’un gouvernement par la vertu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1489 – 1546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO GYEONG-DEOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/S%C5%8F_Ky%C5%8Fngd%C5%8Fk"  title=" Wikipedia (en)"&gt;SEO GYEONG-DEOK&lt;/a&gt;, dit Hwadam, était un penseur néoconfucéen qui refusa toute carrière officielle pour se consacrer à l’étude et à l’enseignement près de Kaesong. Largement autodidacte, il avait la réputation de méditer longuement chaque question, en inscrivant son objet sur le mur avant d’y réfléchir.&lt;/p&gt; &lt;p&gt;Contrairement à l’orthodoxie de Zhu Xi, qui accorde la primauté au principe (&lt;em&gt;li&lt;/em&gt;), il place au centre du réel l’énergie vitale (&lt;em&gt;gi&lt;/em&gt;) : une substance originelle, le « Grand Vide », sans commencement ni fin, qui se condense et se disperse pour former toutes choses. La mort n’est ainsi qu’une dispersion du &lt;em&gt;gi&lt;/em&gt;, jamais un anéantissement. Cette philosophie du &lt;em&gt;gi&lt;/em&gt;, inspirée de Zhang Zai, fait de lui un précurseur des courants monistes de la pensée coréenne.&lt;/p&gt; &lt;p&gt;De famille modeste, il ne passa qu’à contrecœur, pour obéir à sa mère, le premier degré des examens, sans jamais accepter de charge. Il vécut pauvrement près de la cascade de Bakyeon, et la tradition de Kaesong le range, avec cette cascade et la poétesse Hwang Jini, parmi les « trois merveilles de Songdo » : Hwang Jini, qui avait séduit un moine réputé pour sa vertu, aurait échoué à le détourner de l’étude et serait devenue son disciple. Ses courts essais, comme &lt;em&gt;Sur l’origine du principe et de l’énergie&lt;/em&gt;, &lt;em&gt;Sur le Grand Vide&lt;/em&gt; ou &lt;em&gt;Sur les esprits, la vie et la mort&lt;/em&gt;, frappent par leur concision. Yi Hwang lui reprocha de confondre le principe et l’énergie, mais Yi I salua l’originalité d’un penseur qui avait trouvé par lui-même plutôt que dans les livres.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/sgyeongdeok-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penseur néoconfucéen indépendant, fondateur d’une philosophie coréenne de l’énergie vitale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1501 – 1572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JO SIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jo_Sik"  title=" Wikipedia"&gt;JO SIK&lt;/a&gt;, dit Nammyeong, était un lettré néoconfucéen contemporain de Yi Hwang, qui refusa toute sa vie les charges proposées par la cour pour vivre en retrait et enseigner dans la région de Gyeongsang.&lt;/p&gt; &lt;p&gt;Il jugeait vaines les disputes métaphysiques sur le principe et l’énergie : pour lui, le confucianisme devait d’abord former des caractères. Il résumait son enseignement par deux vertus, le recueillement intérieur (&lt;em&gt;gyeong&lt;/em&gt;) et la droiture dans l’action (&lt;em&gt;ui&lt;/em&gt;), et portait, dit-on, un poignard et une clochette pour se rappeler à la vigilance. Ses disciples furent nombreux à prendre les armes contre l’invasion japonaise de 1592, fidèles à cette morale de l’engagement.&lt;/p&gt; &lt;p&gt;En 1555, refusant un poste de magistrat, il adressa au roi Myeongjong une lettre d’une audace inouïe, où il qualifiait la reine mère, qui gouvernait en fait, de « simple veuve au fond du palais » et le roi lui-même d’« orphelin héritier » : le pays, disait-il, était comme un arbre rongé de l’intérieur. Sur son épée était gravée la maxime « Ce qui éclaire le dedans, c’est le recueillement ; ce qui tranche au dehors, c’est la justice ». Retiré au pied du mont Jiri, il formait ses élèves autant à l’examen de conscience qu’au sens des responsabilités publiques. Parmi eux, Gwak Jae-u devint l’un des plus célèbres chefs de milice de la guerre de 1592, et Jeong In-hong le chef de la faction du Nord, qui fit longtemps de Jo Sik un maître rival de Yi Hwang.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jsik-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré néoconfucéen retiré du pouvoir, maître d’une morale de la droiture en acte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1520 – 1604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYUJEONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hyujeong"  title=" Wikipedia (en)"&gt;HYUJEONG&lt;/a&gt;, plus connu sous le nom de Seosan Daesa, est le plus grand maître Seon de l’époque Joseon. Orphelin, il découvrit le bouddhisme lors d’un séjour dans les montagnes et devint moine, puis dirigea les ordres Seon et Gyo à une époque où l’État néoconfucéen marginalisait le bouddhisme.&lt;/p&gt; &lt;p&gt;Lors de l’invasion japonaise de 1592, alors âgé de plus de soixante-dix ans, il leva à l’appel du roi une armée de moines qui contribua à la reprise de Pyongyang. Dans son &lt;em&gt;Miroir pour les pratiquants du Seon&lt;/em&gt;, il affirme que le Seon est l’esprit du Bouddha et le Gyo sa parole : l’étude des textes doit conduire au-delà des mots, vers la méditation sur le &lt;em&gt;hwadu&lt;/em&gt;. Il écrivit aussi sur la convergence des trois enseignements, et la plupart des lignées bouddhistes coréennes actuelles se rattachent à lui.&lt;/p&gt; &lt;p&gt;Accusé à tort en 1589 d’avoir participé à un complot, il fut innocenté par le roi Seonjo, qui lui offrit en gage d’estime une peinture de bambou de sa main ; ce lien de confiance explique l’appel lancé au vieux moine trois ans plus tard. Son disciple Samyeong Yujeong commanda à ses côtés les moines-soldats, puis négocia au Japon, avec Tokugawa Ieyasu, le retour de milliers de prisonniers. Dans son &lt;em&gt;Miroir des trois écoles&lt;/em&gt; (&lt;em&gt;Samga gwigam&lt;/em&gt;), Hyujeong présente côte à côte l’essentiel du confucianisme, du taoïsme et du bouddhisme. Retiré au mont Myohyang, la « montagne de l’Ouest » d’où il tire son surnom de Seosan, il mourut en 1604 après avoir écrit, devant son propre portrait : « Il y a quatre-vingts ans, il était moi ; dans quatre-vingts ans, je serai lui. »&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hyujeong-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maître Seon de Joseon, chef des moines-soldats contre l’invasion japonaise de 1592.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1527 – 1572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GI DAE-SEUNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%EA%B8%B0%EB%8C%80%EC%8A%B9"  title=" Wikipedia (coréen)"&gt;GI DAE-SEUNG&lt;/a&gt;, dit Gobong, était un lettré néoconfucéen resté célèbre pour la correspondance qu’il entretint pendant huit ans, à partir de 1559, avec Yi Hwang, son aîné de vingt-six ans. Ce « débat des Quatre et des Sept » est l’un des moments les plus riches de la philosophie coréenne.&lt;/p&gt; &lt;p&gt;La question porte sur les « quatre commencements » de la vertu décrits par Mencius (compassion, honte, déférence, sens du juste et de l’injuste) et les « sept émotions » ordinaires (joie, colère, tristesse, peur, amour, haine, désir). Yi Hwang les distinguait, faisant naître les premiers du principe (&lt;em&gt;li&lt;/em&gt;) et les secondes de l’énergie (&lt;em&gt;gi&lt;/em&gt;). Gi Dae-seung objecte que principe et énergie ne peuvent être séparés dans aucun phénomène : les quatre commencements ne sont que la part juste des sept émotions. Sa position sera reprise et développée par Yi I.&lt;/p&gt; &lt;p&gt;Le jeune homme venait tout juste de réussir les examens lorsqu’il osa contester la formule du maître le plus respecté du royaume. Loin de s’en offusquer, Yi Hwang lui répondit longuement, reconnut certaines faiblesses de sa première rédaction et la corrigea : les quatre commencements seraient « émis par le principe, l’énergie les suivant », les sept émotions « émises par l’énergie, le principe les chevauchant ». Ce dialogue entre deux hommes séparés par l’âge et le rang, mené avec une courtoisie et une rigueur exemplaires, est souvent cité comme un modèle de controverse philosophique. Gi Dae-seung fit ensuite carrière à la cour, où il occupa de hautes charges, avant de mourir en 1572, à quarante-cinq ans, sur le chemin du retour vers sa région natale du Jeolla.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/gdaeseung-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré néoconfucéen, contradicteur de Yi Hwang dans le débat des Quatre et des Sept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1535 – 1598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEONG HON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/S%C5%8Fng_Hon"  title=" Wikipedia (en)"&gt;SEONG HON&lt;/a&gt;, dit Ugye, était un lettré néoconfucéen, ami de Yi I, qui passa l’essentiel de sa vie à enseigner à l’écart de la cour, dans la région de Paju.&lt;/p&gt; &lt;p&gt;À partir de 1572, il relança avec Yi I le débat des Quatre et des Sept, en prenant cette fois le parti de Yi Hwang : il défendait que les sentiments moraux et les émotions ordinaires ont des sources distinctes, et que l’« esprit humain » ne se confond pas avec l’« esprit de la Voie ». Ces échanges obligèrent Yi I à préciser sa propre théorie. Ses disciples contribuèrent ensuite à la formation de la faction de l’Ouest (Seoin), dont il est considéré comme l’un des maîtres.&lt;/p&gt; &lt;p&gt;Fils de Seong Su-chim, un disciple de Jo Gwang-jo qui s’était retiré après la purge de 1519, il hérita de son père le refus des honneurs et la priorité donnée à la culture de soi. Ses lettres avec Yi I forment, après celles de Yi Hwang et de Gi Dae-seung, la seconde grande correspondance du débat des Quatre et des Sept. Pendant la guerre de 1592, il rejoignit le prince héritier, mais on lui reprocha de ne pas être venu saluer le roi lors de sa fuite vers le nord, et la faction du Nord fit plus tard retirer ses titres posthumes. Réhabilité, il entra en 1681, en même temps que Yi I, dans le sanctuaire de Confucius, signe de l’influence durable de son école sur la vie intellectuelle de Joseon.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/shon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré néoconfucéen, interlocuteur de Yi I dans la seconde phase du débat des Quatre et des Sept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1536 – 1584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YI I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yi_I"  title=" Wikipedia"&gt;YI I&lt;/a&gt;, dit Yulgok, est avec Yi Hwang le plus grand philosophe du confucianisme coréen. Fils de la poétesse et peintre Sin Saimdang, il fut neuf fois reçu premier aux examens d’État et occupa les plus hautes fonctions, tout en restant un penseur d’une grande indépendance. Son portrait figure aujourd’hui sur le billet de 5 000 wons.&lt;/p&gt; &lt;p&gt;Contre Yi Hwang, il soutient que seule l’énergie (&lt;em&gt;gi&lt;/em&gt;) se met en mouvement, le principe (&lt;em&gt;li&lt;/em&gt;) se contentant de « chevaucher » ce mouvement : le principe est universel, mais l’énergie le particularise. Toutes les émotions, morales ou non, naissent ainsi d’un même processus. Cette théorie, qui fonde l’école de Giho, est inséparable d’un souci pratique : dans ses mémoires au roi, Yi I réclame des réformes fiscales, militaires et administratives, et invite à préparer le pays à la guerre, peu avant l’invasion japonaise de 1592. Son &lt;em&gt;Essentiel des études des sages&lt;/em&gt; servit de manuel de formation morale pendant des siècles.&lt;/p&gt; &lt;p&gt;Après la mort de sa mère, survenue quand il avait seize ans, il passa près d’une année dans un monastère des monts Kumgang à étudier le bouddhisme, avant de revenir au confucianisme ; ses adversaires ne cessèrent de le lui reprocher. Son &lt;em&gt;Secret pour chasser l’ignorance&lt;/em&gt; (&lt;em&gt;Gyeongmong yogyeol&lt;/em&gt;), écrit pour les débutants, servit de manuel scolaire jusqu’au XIXe siècle. Pour lui, la philosophie doit répondre aux urgences du temps : il distingue les époques de fondation, de maintien et de rénovation, et estime que la sienne exige des réformes profondes. La tradition lui attribue la proposition de lever une armée de cent mille hommes pour parer à une invasion, conseil que la cour aurait négligé. Ses disciples formèrent l’école de Giho, qui domina la pensée et la politique coréennes jusqu’à la fin de Joseon.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/yii-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grand philosophe confucéen coréen, théoricien du principe « chevauchant » l’énergie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1607 – 1689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONG SI-YEOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Song_Si-yeol"  title=" Wikipedia"&gt;SONG SI-YEOL&lt;/a&gt;, dit Uam, était le chef de file de la faction de l’Ouest puis de la faction Noron, et l’un des lettrés les plus influents de toute l’histoire de Joseon. Défenseur intransigeant de l’orthodoxie de Zhu Xi, il en fit la norme de la vie intellectuelle et politique coréenne.&lt;/p&gt; &lt;p&gt;Après l’humiliation infligée par les Mandchous en 1637, il défendit l’idée que la Corée devait rester fidèle à la civilisation des Ming et se considérer comme la dernière gardienne de l’héritage confucéen authentique. Il fut au cœur des « querelles des rites » sur la durée du deuil royal, qui mêlaient principes philosophiques et lutte des factions. Condamné à mort en 1689 lors d’un revirement politique, il reste le symbole de la rigueur doctrinale et de ses dangers.&lt;/p&gt; &lt;p&gt;Précepteur du roi Hyojong, qui avait été otage des Mandchous, il partagea son projet d’« expédition vers le nord » destinée à venger la Corée des Qing, projet resté sans suite à la mort du roi en 1659. Il est la personne la plus souvent citée dans les Annales de la dynastie Joseon, signe de la place qu’il occupa pendant un demi-siècle. Les querelles des rites de 1659 et 1674 portaient sur la durée du deuil que devait observer la reine douairière : derrière la question, il s’agissait de savoir si la famille royale est soumise aux mêmes règles rituelles que les autres lettrés, ce que soutenait Song Si-yeol. Son opposition à la désignation comme prince héritier du fils de la favorite Jang Hui-bin entraîna sa condamnation : il dut boire le poison à quatre-vingt-deux ans.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/ssiyeol-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chef de file de l’orthodoxie néoconfucéenne de Zhu Xi dans la Corée du XVIIe siècle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1622 – 1673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YU HYEONG-WON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yu_Hyeong-won"  title=" Wikipedia"&gt;YU HYEONG-WON&lt;/a&gt;, dit Bangye, est considéré comme le fondateur du Silhak, l’« étude pratique ». Après les désastres des invasions japonaises et mandchoues, il renonça à la carrière officielle et se retira dans un village du Jeolla pour étudier les causes de la misère paysanne.&lt;/p&gt; &lt;p&gt;Dans son grand ouvrage, le &lt;em&gt;Bangye surok&lt;/em&gt;, il propose une réforme complète de l’État : attribution publique des terres aux cultivateurs, allègement de la fiscalité, recrutement des fonctionnaires par l’éducation et le mérite plutôt que par la naissance. Il s’appuie sur les classiques confucéens, mais pour en tirer des institutions concrètes plutôt que des spéculations. Ignorée de son vivant, son œuvre inspira Yi Ik et toute la tradition réformatrice du XVIIIe siècle.&lt;/p&gt; &lt;p&gt;Installé à partir de 1653 à Ubanje, près de Buan, il y rédigea pendant près de vingt ans les vingt-six livres du &lt;em&gt;Bangye surok&lt;/em&gt;. Son projet, inspiré du système idéal des « champs en puits » de l’Antiquité chinoise, prévoit que chaque famille paysanne reçoive une parcelle de terre publique, à charge pour elle de fournir impôt et service militaire ; la richesse foncière ne pourrait plus s’accumuler entre les mains des grands propriétaires. Il critique aussi l’esclavage héréditaire, dont il souhaite la limitation progressive, et propose des écoles publiques ouvertes selon le mérite. Le roi Yeongjo, ayant découvert l’ouvrage près d’un siècle après sa rédaction, le fit imprimer en 1770, et ses idées nourrirent dès lors tous les débats sur la réforme de l’État.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/yhyeongwon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fondateur du Silhak, auteur d’un vaste projet de réforme agraire et politique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1649 – 1736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEONG JE-DU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%EC%A0%95%EC%A0%9C%EB%91%90"  title=" Wikipedia (coréen)"&gt;JEONG JE-DU&lt;/a&gt;, dit Hagok, est le principal représentant de l’école coréenne de Wang Yangming, dans un pays où l’orthodoxie de Zhu Xi tenait cette pensée pour hérétique. Il s’installa sur l’île de Ganghwa, où se forma autour de lui une école discrète, transmise surtout au sein de sa famille.&lt;/p&gt; &lt;p&gt;Suivant Wang Yangming, il affirme que le principe n’est pas à chercher dans les choses extérieures, mais dans l’esprit lui-même : la « connaissance innée du bien » (&lt;em&gt;yangji&lt;/em&gt;) est présente en chacun, et savoir le bien est inséparable de le faire. Il critique ainsi une érudition livresque qui sépare la connaissance de l’action morale. Au début du XXe siècle, l’école de Ganghwa inspira des réformateurs comme Pak Eun-sik, qui y virent la ressource d’un confucianisme renouvelé.&lt;/p&gt; &lt;p&gt;Descendant de Jeong Mong-ju, issu d’une grande famille de lettrés, il renonça très jeune à la carrière des examens pour se consacrer à l’étude. Ses amis de la faction Soron le pressèrent à plusieurs reprises d’abandonner une doctrine jugée dangereuse ; il leur répondit dans des lettres où il défendait, avec prudence mais fermeté, la pensée de Wang Yangming. Installé à Ganghwa en 1709, à soixante ans, il y rédigea ses principaux écrits, comme le &lt;em&gt;Hakbyeon&lt;/em&gt; (« Discussion sur l’étude »), sans jamais rompre ouvertement avec l’orthodoxie. Respecté pour sa droiture, il reçut des charges honorifiques sous le roi Yeongjo et mourut à quatre-vingt-sept ans. L’école de Ganghwa compta ensuite des calligraphes, des historiens et des philologues, jusqu’à Jeong In-bo au XXe siècle.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jjedu-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">principal penseur coréen de l’école de Wang Yangming, fondateur de l’école de Ganghwa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1682 – 1751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAN WON-JIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%ED%95%9C%EC%9B%90%EC%A7%84"  title=" Wikipedia (coréen)"&gt;HAN WON-JIN&lt;/a&gt;, dit Namdang, était un lettré néoconfucéen de l’école de Song Si-yeol et le principal protagoniste du débat Horak, qui divisa les lettrés coréens au XVIIIe siècle.&lt;/p&gt; &lt;p&gt;La question débattue était de savoir si la nature des êtres humains et celle des animaux et des choses sont identiques. Contre Yi Gan, qui défendait leur identité au nom de l’universalité du principe, Han Won-jin soutient qu’elles diffèrent : si le principe est le même partout, il s’actualise différemment selon l’énergie de chaque être, et seul l’être humain possède les vertus morales dans leur plénitude. Ce débat, apparemment abstrait, engageait la place de l’humanité dans la nature et la hiérarchie entre « civilisation » et « barbarie ».&lt;/p&gt; &lt;p&gt;Le nom du débat vient des deux camps : le &lt;em&gt;Ho&lt;/em&gt;, la région du Hoseo (Chungcheong) où vivait Han Won-jin, et le &lt;em&gt;Rak&lt;/em&gt;, la capitale, où ses adversaires étaient nombreux. Han Won-jin et Yi Gan étaient pourtant tous deux disciples de Gwon Sang-ha, lui-même héritier de Song Si-yeol. La controverse portait aussi sur l’état de l’esprit « avant l’éveil des émotions » : est-il toujours parfaitement bon, ou garde-t-il, même au repos, les inégalités de l’énergie propre à chacun ? Han Won-jin, fidèle à sa thèse des différences, penchait pour la seconde réponse. Il consacra aussi un grand ouvrage aux concordances et aux divergences entre les écrits successifs de Zhu Xi. Les historiens rapprochent souvent la thèse adverse, celle de l’identité des natures, de l’ouverture des savants du Bukhak, tandis que celle de Han Won-jin soutint une défense plus stricte de l’orthodoxie.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hwonjin-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré néoconfucéen, défenseur de la différence des natures humaine et animale dans le débat Horak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1731 – 1783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HONG DAE-YONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hong_Taeyong"  title=" Wikipedia (en)"&gt;HONG DAE-YONG&lt;/a&gt;, dit Damheon, était un savant de l’école Bukhak (« étude du Nord »), branche du Silhak favorable à l’apprentissage des sciences de la Chine des Qing. Lors d’un voyage à Pékin en 1765, il rencontra des lettrés chinois et découvrit l’astronomie et les mathématiques occidentales introduites par les jésuites.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Dialogue d’Uisan&lt;/em&gt;, un lettré attaché aux idées reçues est détrompé par un sage qui lui enseigne que la Terre est ronde, qu’elle tourne sur elle-même et que l’univers est infini. Hong Dae-yong en tire une leçon philosophique : dans un univers sans centre, aucune nation ne peut se dire le centre du monde, et la distinction entre « civilisés » et « barbares » perd son fondement. Il remet aussi en cause la supériorité supposée de l’homme sur les autres êtres, ouvrant la voie à une pensée relativiste et scientifique.&lt;/p&gt; &lt;p&gt;Passionné d’astronomie, il fit construire dans sa maison de campagne un petit observatoire, le Nongsugak, équipé d’une sphère armillaire réalisée avec le savant Na Gyeong-jeok, et rédigea un traité de mathématiques. À Pékin, il visita l’église du Sud et s’entretint avec les jésuites Hallerstein et Gogeisl, qui dirigeaient le Bureau impérial d’astronomie. Il noua aussi une amitié durable avec trois lettrés de Hangzhou, avec lesquels il échangea des lettres jusqu’à sa mort : cette correspondance, rare entre lettrés coréens et chinois, ouvrit la voie aux voyages de Bak Ji-won et de ses amis. Sa formule « vu du Ciel, l’homme et les choses sont égaux » résume sa remise en cause de l’anthropocentrisme confucéen.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hdaeyong-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">savant du Silhak, défenseur de la rotation de la Terre et critique de tout centre du monde.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1737 – 1805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAK JI-WON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Pak_Chiw%C5%8Fn_%28philosopher%29"  title=" Wikipedia (en)"&gt;BAK JI-WON&lt;/a&gt;, dit Yeonam, était un écrivain et penseur de l’école Bukhak, l’une des plumes les plus brillantes de la Corée du XVIIIe siècle. En 1780, il accompagna une ambassade en Chine et en tira le &lt;em&gt;Journal de Jehol&lt;/em&gt;, récit de voyage mêlant observations techniques, réflexions politiques et satire.&lt;/p&gt; &lt;p&gt;Il y invite ses compatriotes à apprendre des Qing, pourtant méprisés comme « barbares » mandchous, tout ce qui peut améliorer la vie du peuple : chariots, briques, commerce, techniques agricoles. Ses récits satiriques, comme &lt;em&gt;L’Histoire du lettré Heo&lt;/em&gt; ou &lt;em&gt;Histoire d’un yangban&lt;/em&gt;, ridiculisent l’oisiveté et l’hypocrisie de l’aristocratie lettrée. Pour lui, le savoir n’a de valeur que s’il sert à rendre les choses utiles et à enrichir la vie du peuple.&lt;/p&gt; &lt;p&gt;Issu d’une famille de haute noblesse, il renonça aux examens et réunit autour de lui, près de la pagode blanche de Séoul, un cercle de jeunes lettrés réformateurs, dont Pak Je-ga et Yi Deok-mu, avec Hong Dae-yong pour aîné. Son ambassade de 1780 devait saluer l’empereur Qianlong pour son soixante-dixième anniversaire, dans sa résidence d’été de Jehol (Rehe). Le style vivant et familier de son journal, mêlant langue parlée et anecdotes, inquiéta le roi Jeongjo, qui lança en 1792 une campagne pour « rectifier le style » et lui demanda de revenir à une prose classique. Nommé ensuite magistrat de petites circonscriptions, comme Anui, il y mit ses idées en pratique en faisant construire des moulins à eau. Il est aujourd’hui tenu pour l’un des plus grands prosateurs de la littérature coréenne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/bjiwon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">écrivain du Silhak, auteur du Journal de Jehol et satiriste de l’aristocratie lettrée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1762 – 1836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEONG YAK-YONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong"  title=" Wikipedia"&gt;JEONG YAK-YONG&lt;/a&gt;, dit Dasan, est considéré comme le plus grand penseur du Silhak et l’un des esprits les plus universels de l’histoire coréenne. Proche du roi Jeongjo, il conçut notamment une grue pour la construction de la forteresse de Hwaseong. Lié à des milieux catholiques, il fut exilé pendant dix-huit ans à Gangjin, où il rédigea l’essentiel de son œuvre, forte de quelque cinq cents volumes.&lt;/p&gt; &lt;p&gt;Relisant directement les classiques confucéens par-delà les commentaires de Zhu Xi, il rejette l’idée d’une nature humaine identique au principe : la nature est une inclination, un « goût » pour le bien, et la vertu ne se réalise que dans des actes concrets et par un libre choix. Il réhabilite l’idée d’un Seigneur d’en haut (&lt;em&gt;Sangje&lt;/em&gt;) qui veille sur la conscience morale. Ses ouvrages politiques, comme le &lt;em&gt;Mongmin simseo&lt;/em&gt; (« Réflexions sur le gouvernement du peuple »), proposent une administration au service des plus pauvres et une réforme agraire fondée sur le travail collectif de la terre.&lt;/p&gt; &lt;p&gt;Ses liens avec le catholicisme eurent un prix terrible : lors de la persécution de 1801, son frère Jeong Yak-jong fut exécuté, tandis qu’un autre frère, Jeong Yak-jeon, était exilé dans l’île de Heuksan, où il écrivit un traité sur les poissons de la région. Dans son ermitage de Gangjin, le Dasan chodang, Jeong Yak-yong se lia d’amitié avec des moines bouddhistes, dont le maître du thé Choui, et forma des élèves. Son œuvre politique forme une trilogie : le &lt;em&gt;Gyeongse yupyo&lt;/em&gt; sur la réforme de l’État, le &lt;em&gt;Mongmin simseo&lt;/em&gt; sur l’administration locale et le &lt;em&gt;Heumheum sinseo&lt;/em&gt; sur la justice pénale, où il demande que les peines soient prononcées avec prudence et compassion. Il écrivit aussi sur la médecine, notamment sur la rougeole et la variole. Libéré en 1818, il passa ses dernières années dans son village natal, au bord du fleuve Han.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/jyakyong-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plus grand penseur du Silhak, relecteur des classiques et théoricien d’un gouvernement du peuple.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1792 – 1868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YI HANG-RO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%EC%9D%B4%ED%95%AD%EB%A1%9C"  title=" Wikipedia (coréen)"&gt;YI HANG-RO&lt;/a&gt;, dit Hwaseo, était un lettré néoconfucéen qui refusa les charges officielles pour enseigner dans la province de Gyeonggi. Il est le fondateur du mouvement « défendre l’orthodoxie, rejeter l’hétérodoxie » (&lt;em&gt;wijeong cheoksa&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;Face à l’arrivée des navires occidentaux et à la diffusion du catholicisme, il voit dans la civilisation occidentale une menace pour l’ordre moral confucéen, qu’il fonde sur la primauté absolue du principe (&lt;em&gt;li&lt;/em&gt;) sur l’énergie. Il conseilla la résistance lors de l’expédition française de 1866. Ses disciples furent à l’origine des « armées vertueuses » (&lt;em&gt;uibyeong&lt;/em&gt;) qui combattirent la colonisation japonaise, faisant de sa pensée conservatrice une source paradoxale du nationalisme coréen.&lt;/p&gt; &lt;p&gt;Son refus de l’Occident n’était pas seulement politique : il appelait à rejeter jusqu’aux étoffes et objets importés, qu’il jugeait capables d’éveiller le goût du luxe et de dissoudre les mœurs. Lors de l’expédition française de 1866, il soutint que traiter avec l’ennemi conduirait à la perte de la civilisation elle-même, et que seule la résistance était juste. Philosophe, il défendit aussi une thèse selon laquelle l’esprit, dans ce qu’il a de plus essentiel, relève du principe, ce qui suscita parmi ses disciples une longue querelle sur la nature de l’esprit. Ses élèves Choe Ik-hyeon et Yu In-seok portèrent son héritage jusque dans le combat : Choe Ik-hyeon, chef d’une armée vertueuse en 1906, mourut en captivité à Tsushima en refusant, selon la tradition, toute nourriture japonaise.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/yhangro-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré néoconfucéen, fondateur du mouvement de défense de l’orthodoxie contre l’Occident.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1803 – 1877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHOE HAN-GI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi"  title=" Wikipedia (en)"&gt;CHOE HAN-GI&lt;/a&gt;, dit Hyegang, était un savant indépendant de Séoul, qui consacra sa fortune à acheter les livres de science occidentale traduits en chinois. Il laissa une œuvre immense, synthèse de la pensée confucéenne et des connaissances scientifiques de son temps.&lt;/p&gt; &lt;p&gt;Il fonde une philosophie du &lt;em&gt;gi&lt;/em&gt;, où l’énergie vitale, en perpétuel mouvement, est la seule réalité, le principe n’étant que l’ordre de ce mouvement. La connaissance ne vient ni de l’intuition morale ni de la seule étude des textes, mais de l’expérience et de la mesure : l’esprit est d’abord vierge et se forme au contact des choses. Il plaide aussi pour l’ouverture du pays et la communication entre les peuples. Sa pensée, souvent rapprochée de l’empirisme, fait de lui un pont entre le Silhak et la modernité.&lt;/p&gt; &lt;p&gt;Issu d’une famille d’officiers militaires originaire de Kaesong, il réussit le premier degré des examens en 1825 mais n’exerça jamais de fonction. On lui attribue près d’un millier de volumes, dont seule une partie subsiste : le &lt;em&gt;Gicheuk cheui&lt;/em&gt; (1836), sur la connaissance par l’expérience et la mesure, le &lt;em&gt;Gihak&lt;/em&gt; (« Science de l’énergie »), qui expose son système, et l’&lt;em&gt;Injeong&lt;/em&gt; (« Le gouvernement des hommes »), consacré à l’éducation, au choix des fonctionnaires et à l’économie. Il emploie la notion de « transformation en mouvement » (&lt;em&gt;unhwa&lt;/em&gt;) pour désigner l’activité incessante du &lt;em&gt;gi&lt;/em&gt;, qu’il faut observer et mesurer plutôt que contempler. Ami du géographe Kim Jeong-ho, il publia avec lui en 1834 une carte du globe en deux hémisphères. Oublié de son vivant, il fut redécouvert au XXe siècle comme un précurseur de la pensée scientifique coréenne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/changi-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">savant du XIXe siècle, auteur d’une philosophie empiriste de l’énergie vitale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1824 – 1864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHOE JE-U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Choe_Je-u"  title=" Wikipedia"&gt;CHOE JE-U&lt;/a&gt;, dit Suun, est le fondateur du Donghak, l’« étude de l’Orient », mouvement religieux et philosophique né en réaction à l’« étude de l’Occident » (&lt;em&gt;Seohak&lt;/em&gt;), c’est-à-dire le catholicisme. Issu d’une famille de lettrés déclassés, il affirma avoir reçu en 1860 une révélation du Seigneur du Ciel.&lt;/p&gt; &lt;p&gt;Sa doctrine centrale, « porter en soi le Seigneur du Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;), affirme que le divin réside en chaque être humain, quel que soit son rang : ses successeurs en tirèrent la formule « l’être humain est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Cet égalitarisme radical, qui mêle confucianisme, bouddhisme, taoïsme et chamanisme, séduisit les paysans et inquiéta le pouvoir, qui le fit exécuter en 1864. Le Donghak inspira la grande révolte paysanne de 1894 et subsiste aujourd’hui dans la religion Cheondogyo.&lt;/p&gt; &lt;p&gt;Avant sa révélation, Choe Je-u avait erré une dizaine d’années à travers le pays, notamment comme colporteur, témoin de la misère paysanne, des épidémies et des nouvelles inquiétantes venues de Chine, où les puissances occidentales venaient d’entrer dans Pékin. Sa doctrine est rassemblée dans deux recueils : le &lt;em&gt;Donggyeong daejeon&lt;/em&gt;, en chinois classique, pour les lettrés, et le &lt;em&gt;Yongdam yusa&lt;/em&gt;, des chants en écriture coréenne destinés au peuple et aux femmes. La pratique centrale consiste à réciter une formule de vingt et un caractères invoquant l’énergie suprême et le Seigneur du Ciel présent en soi. Accusé de « tromper le peuple par une doctrine hérétique », c’est-à-dire d’être un catholique déguisé, il fut décapité à Daegu. Son successeur Choe Si-hyeong organisa clandestinement le mouvement et enseigna qu’il faut « servir l’homme comme le Ciel ».&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/cjeu-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donghak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fondateur du Donghak, pensée égalitaire affirmant que le Ciel réside en chaque être humain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1859 – 1925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAK EUN-SIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Pak_%C5%ACnsik"  title=" Wikipedia (en)"&gt;PAK EUN-SIK&lt;/a&gt;, dit Baegam, était un lettré confucéen, historien et journaliste, figure majeure du mouvement d’indépendance coréen. Il fut en 1925 le deuxième président du Gouvernement provisoire de la République de Corée, en exil à Shanghai.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Essai sur la réforme du confucianisme&lt;/em&gt; (1909), il reproche au confucianisme officiel d’être resté au service des élites et d’avoir ignoré le peuple. Il propose de le renouveler à partir de la pensée de Wang Yangming, qui unit connaissance et action, pour en faire une force d’éducation et de résistance nationale. Ses ouvrages d’histoire, comme l’&lt;em&gt;Histoire douloureuse de la Corée&lt;/em&gt;, défendent l’idée que l’âme d’une nation survit tant que son histoire est transmise, même lorsque son État a disparu.&lt;/p&gt; &lt;p&gt;Formé d’abord dans la stricte orthodoxie de Zhu Xi, il changea de voie à la fin des années 1890, au contact des idées nouvelles du Club de l’indépendance, et devint rédacteur de grands journaux réformateurs comme le &lt;em&gt;Hwangseong sinmun&lt;/em&gt; et le &lt;em&gt;Daehan maeil sinbo&lt;/em&gt;. Après l’annexion de 1910, il s’exila en Chine. Dans son &lt;em&gt;Histoire douloureuse&lt;/em&gt; (1915), il distingue l’« âme » d’une nation, sa langue, sa religion, son histoire, de sa « forme », c’est-à-dire ses institutions et son territoire : tant que l’âme demeure, la forme peut être reconquise. Il poursuivit avec une &lt;em&gt;Histoire sanglante du mouvement d’indépendance coréen&lt;/em&gt; (1920), consacrée notamment au soulèvement du 1er mars 1919. Mort à Shanghai quelques mois après avoir accédé à la présidence du Gouvernement provisoire, il ne fut inhumé en Corée qu’en 1993.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/peunsik-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré et historien de l’indépendance, réformateur du confucianisme par la pensée de Wang Yangming.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1879 – 1944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAN YONG-UN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Han_Yong-un"  title=" Wikipedia"&gt;HAN YONG-UN&lt;/a&gt;, dit Manhae, était un moine bouddhiste, poète et militant de l’indépendance. Il fut l’un des trente-trois signataires de la Déclaration d’indépendance du 1er mars 1919, ce qui lui valut trois ans de prison sous l’occupation japonaise.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Traité sur la rénovation du bouddhisme coréen&lt;/em&gt; (1913), il appelle à sortir le bouddhisme des montagnes pour l’engager dans la société : éducation moderne des moines, simplification des rites, autorisation du mariage des religieux. Il y rapproche l’égalité bouddhiste de l’idéal démocratique et de la liberté des peuples. Son recueil &lt;em&gt;Le Silence de l’amour&lt;/em&gt; (1926), où l’être aimé absent peut se lire comme le Bouddha, la patrie ou la liberté, est l’un des chefs-d’œuvre de la poésie coréenne moderne.&lt;/p&gt; &lt;p&gt;Devenu moine en 1905 au monastère de Baekdam, dans les monts Seorak, il voyagea au Japon pour observer un bouddhisme modernisé, mais combattit en 1910-1911 le projet de rattacher le bouddhisme coréen à une école japonaise, au nom de l’indépendance de sa tradition. En prison après 1919, il rédigea une &lt;em&gt;Lettre sur l’indépendance de la Corée&lt;/em&gt;, où il fonde le droit des peuples à disposer d’eux-mêmes sur la liberté, « vie de l’humanité », et sur l’égalité. Il refusa toute compromission avec l’occupant, jusqu’à orienter sa maison de Séoul, le Simujang, vers le nord, pour ne pas faire face au siège du Gouvernement général japonais. Il mourut en 1944, un an avant la libération qu’il avait tant attendue.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hyongun-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moine, poète et résistant, réformateur d’un bouddhisme engagé dans la société.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1880 – 1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIN CHAE-HO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shin_Chae-ho"  title=" Wikipedia"&gt;SIN CHAE-HO&lt;/a&gt;, dit Danjae, était un historien, journaliste et penseur de l’indépendance coréenne. Exilé en Chine après l’annexion de 1910, il participa brièvement au Gouvernement provisoire avant de s’en éloigner et de se tourner vers l’anarchisme.&lt;/p&gt; &lt;p&gt;Pour lui, l’histoire est « la lutte entre le moi (&lt;em&gt;a&lt;/em&gt;) et le non-moi (&lt;em&gt;bia&lt;/em&gt;) » : chaque peuple se construit en résistant à ce qui le nie. Il rompt avec une historiographie confucéenne centrée sur la Chine pour écrire une histoire de la Corée à partir de ses propres peuples anciens. Dans la &lt;em&gt;Déclaration de la révolution coréenne&lt;/em&gt; (1923), il rejette les stratégies diplomatiques et appelle à une révolution populaire directe contre la domination japonaise. Arrêté en 1928, il mourut en prison à Lüshun.&lt;/p&gt; &lt;p&gt;Lettré formé au Seonggyungwan, il devint dès 1905 l’une des plumes les plus redoutées de la presse patriotique, au &lt;em&gt;Hwangseong sinmun&lt;/em&gt; puis au &lt;em&gt;Daehan maeil sinbo&lt;/em&gt;. Sa &lt;em&gt;Nouvelle lecture de l’histoire&lt;/em&gt; (1908) fait remonter l’histoire nationale à Dangun et aux royaumes du Nord, Buyeo et Goguryeo, et il écrivit des biographies de héros comme Eulji Mundeok ou l’amiral Yi Sun-sin pour éveiller l’esprit de résistance. On raconte qu’il se lavait le visage debout, sans se pencher, pour ne s’incliner devant personne. Arrêté à Taïwan en 1928 alors qu’il tentait de financer une organisation anarchiste d’Asie orientale, il fut condamné à dix ans de prison. Son &lt;em&gt;Histoire ancienne de la Corée&lt;/em&gt; parut en feuilleton dans la presse en 1931, alors qu’il était captif.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/schaeho-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anarchisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historien et anarchiste, penseur de l’histoire comme lutte du moi contre le non-moi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1890 – 1981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RYU YEONG-MO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%EB%A5%98%EC%98%81%EB%AA%A8"  title=" Wikipedia (coréen)"&gt;RYU YEONG-MO&lt;/a&gt;, dit Dayeong, était un penseur religieux et éducateur, maître de Ham Seok-heon. Converti au christianisme dans sa jeunesse, il s’éloigna de ses formes institutionnelles et développa une spiritualité personnelle, nourrie de la Bible, des classiques confucéens et taoïstes et des textes bouddhistes.&lt;/p&gt; &lt;p&gt;Il cherchait à penser le christianisme à partir de la langue et de la tradition coréennes, en jouant sur le sens des mots coréens pour exprimer le rapport entre l’être humain et l’Absolu. Il menait une existence ascétique et comptait sa vie en jours plutôt qu’en années, voyant dans chaque journée une vie entière à accomplir. Son idée du peuple comme « graine » (&lt;em&gt;ssial&lt;/em&gt;), porteuse d’une vie divine, fut reprise et développée par Ham Seok-heon.&lt;/p&gt; &lt;p&gt;Directeur pendant un temps de l’école d’Osan, dans le nord du pays, où il eut Ham Seok-heon pour élève, il tint ensuite pendant plus de trente ans, à la YMCA de Séoul, des cours hebdomadaires de lecture spirituelle ouverts à tous. À partir de 1941, il ne prit plus qu’un repas par jour, renonça à la vie conjugale et dormit sur une planche, voyant dans cette ascèse une façon de libérer l’esprit du désir. Il traduisit en coréen le &lt;em&gt;Daodejing&lt;/em&gt; de Laozi, qu’il lisait comme un texte proche de l’Évangile. Pour lui, Jésus n’était pas l’unique fils de Dieu, mais le modèle de tout homme qui laisse naître en lui l’esprit divin, une conviction qui le tint à l’écart des Églises. Son enseignement oral, transcrit par ses disciples, reste une source importante de la spiritualité coréenne moderne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/ryeongmo-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiritualisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penseur religieux coréen, maître de Ham Seok-heon et inspirateur de la pensée ssial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1901 – 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAM SEOK-HEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ham_Seok-heon"  title=" Wikipedia"&gt;HAM SEOK-HEON&lt;/a&gt; était un penseur, éducateur et militant quaker, figure majeure de la résistance non violente en Corée du Sud. Emprisonné sous l’occupation japonaise, il quitta le Nord communiste en 1947, puis s’opposa aux régimes autoritaires de Syngman Rhee, Park Chung-hee et Chun Doo-hwan.&lt;/p&gt; &lt;p&gt;Sa « philosophie ssial » fait du peuple ordinaire, la « graine » (&lt;em&gt;ssial&lt;/em&gt;), le véritable sujet de l’histoire : chaque personne porte en elle une vie spirituelle qui doit germer, et aucune autorité politique ou religieuse ne peut se substituer à elle. Dans &lt;em&gt;La Corée vue à travers le sens&lt;/em&gt;, il lit l’histoire coréenne, faite de souffrances répétées, comme une souffrance qui a une signification pour l’humanité entière. Inspiré par Gandhi, il défendit la non-violence et fut proposé pour le prix Nobel de la paix.&lt;/p&gt; &lt;p&gt;Étudiant à Tokyo dans les années 1920, il découvrit le mouvement « sans Église » d’Uchimura Kanzō, qui marqua durablement sa foi, avant de se rapprocher des quakers après la guerre. Son livre majeur parut d’abord sous le titre &lt;em&gt;L’histoire coréenne vue à la lumière de la Bible&lt;/em&gt;, avant d’être élargi pour s’adresser à tous, croyants ou non. En 1958, son article « Seul un peuple qui pense peut vivre », publié dans la revue &lt;em&gt;Sasanggye&lt;/em&gt;, lui valut d’être arrêté. En 1970, il fonda la revue &lt;em&gt;La Voix de la graine&lt;/em&gt; (&lt;em&gt;Ssial ui sori&lt;/em&gt;), interdite à plusieurs reprises par la censure. Sa pensée relie la non-violence de Gandhi, la mystique chrétienne et le taoïsme, et elle fut l’une des sources de la théologie du minjung.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hseokheon-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minjung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penseur quaker non violent, auteur d’une philosophie du peuple comme « graine » de l’histoire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1903 – 1976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAK CHONG-HONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ko.wikipedia.org/wiki/%EB%B0%95%EC%A2%85%ED%99%8D"  title=" Wikipedia (coréen)"&gt;PAK CHONG-HONG&lt;/a&gt;, dit Yeoram, est considéré comme le premier grand philosophe universitaire de la Corée moderne. Formé à l’université impériale de Keijō (Séoul) sous l’occupation japonaise, il enseigna ensuite pendant des décennies à l’université nationale de Séoul, où il forma plusieurs générations de philosophes.&lt;/p&gt; &lt;p&gt;Nourri de Hegel et de Heidegger, il veut une philosophie qui parte de la réalité vécue plutôt que de systèmes importés : la pensée doit naître de la situation concrète de son peuple et de son temps. Il relit dans cette perspective l’histoire de la pensée coréenne, de Wonhyo à Yi Hwang, Yi I et au Silhak, pour en dégager les ressources d’une philosophie créatrice, et contribue ainsi à fonder l’étude moderne de la philosophie coréenne. Conseiller du président Park Chung-hee, il participa à la rédaction de la Charte de l’éducation nationale de 1968, ce qui lui est aussi reproché.&lt;/p&gt; &lt;p&gt;Avant de se tourner vers la philosophie, il s’était intéressé à l’histoire de l’art : dès 1922, jeune enseignant, il publia dans la revue &lt;em&gt;Gaebyeok&lt;/em&gt; une série d’articles sur l’art coréen, avec l’ambition de montrer que la Corée possédait une culture propre. Il n’entra à l’université qu’à vingt-six ans, après plusieurs années d’enseignement et de lectures personnelles. Pour lui, la philosophie ne commence pas dans les livres mais dans la « réalité », c’est-à-dire dans les questions et les souffrances concrètes d’un peuple : il faut s’interroger sur soi-même avant d’importer les systèmes étrangers. Son &lt;em&gt;Histoire de la pensée coréenne&lt;/em&gt;, issue de ses cours, fit connaître à des générations d’étudiants des penseurs jusque-là négligés. Ses œuvres complètes ont paru après sa mort.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/pchonghong-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premier grand philosophe universitaire de la Corée moderne et historien de la pensée coréenne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1912 – 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEONGCHEOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Seongcheol"  title=" Wikipedia (en)"&gt;SEONGCHEOL&lt;/a&gt; était un maître Seon, patriarche suprême de l’ordre Jogye de 1981 à sa mort. Réputé pour son ascèse, il resta, dit-on, huit ans sans jamais s’allonger pour dormir, et vécut retiré au monastère de Haeinsa.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Voie droite du Seon&lt;/em&gt; (1981), il critique la doctrine de Jinul, « éveil soudain, culture graduelle », qui domine la tradition coréenne depuis le XIIe siècle. Pour lui, un éveil authentique est complet d’emblée et n’appelle aucune culture ultérieure : c’est l’« éveil soudain, culture soudaine » (&lt;em&gt;donodonsu&lt;/em&gt;). Un éveil qui a encore besoin d’être cultivé n’est qu’une compréhension intellectuelle. Cette thèse relança un grand débat dans le bouddhisme coréen contemporain.&lt;/p&gt; &lt;p&gt;Né Yi Yeong-ju dans une famille de propriétaires terriens de Sancheong, il se forma d’abord seul, en lisant philosophie occidentale et textes bouddhistes, avant de devenir moine au monastère de Haeinsa en 1936. En 1947, il fonda avec d’autres moines, au monastère de Bongam, une communauté qui voulait rétablir une discipline stricte, abîmée par l’époque coloniale : robe traditionnelle, travail manuel, refus des offrandes faciles. Ce « pacte de Bongamsa » inspira la reconstruction de l’ordre Jogye après la guerre. On raconte qu’il exigeait de ses visiteurs, même les plus illustres, trois mille prosternations devant le Bouddha avant d’accepter de les recevoir. Lors de son entrée en fonctions, en 1981, il prononça une formule restée célèbre : « Les montagnes sont des montagnes, l’eau est de l’eau. »&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/seongcheol-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patriarche de l’ordre Jogye, défenseur de l’éveil soudain et de la culture soudaine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1922 – 1996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHN BYUNG-MU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ahn_Byung-Mu"  title=" Wikipedia (en)"&gt;AHN BYUNG-MU&lt;/a&gt; était un théologien et bibliste, l’un des fondateurs de la théologie du &lt;em&gt;minjung&lt;/em&gt; (« le peuple ») dans les années 1970. Formé en Allemagne, à Heidelberg, il enseigna en Corée du Sud et fut emprisonné pour son opposition au régime de Park Chung-hee.&lt;/p&gt; &lt;p&gt;Relisant l’Évangile de Marc, il remarque que Jésus y est toujours entouré de l’&lt;em&gt;ochlos&lt;/em&gt;, la foule des pauvres et des exclus, et en conclut que le peuple souffrant n’est pas seulement l’objet du salut, mais le lieu même où se révèle le divin. Cette pensée, proche de la théologie de la libération latino-américaine mais enracinée dans l’histoire coréenne, fait du peuple opprimé le sujet de l’histoire. Elle accompagna les luttes pour la démocratie et les droits des travailleurs en Corée du Sud.&lt;/p&gt; &lt;p&gt;Né dans le nord de la Corée et élevé en Mandchourie, il fit ses études de théologie après la guerre, soutint sa thèse à Heidelberg, puis revint enseigner à l’université Hanshin. En 1973, il fonda l’Institut coréen de recherche théologique et sa revue, qui devinrent des foyers de la théologie du minjung. Signataire de la « Déclaration pour le salut démocratique de la nation », lue le 1er mars 1976 à la cathédrale de Myeongdong, il fut chassé de son poste et emprisonné. Pour lui, le Christ n’est pas d’abord une doctrine mais un « événement », qui se reproduit chaque fois que les opprimés se lèvent : il disait avoir été bouleversé par la mort de l’ouvrier Jeon Tae-il, qui s’immola par le feu en 1970 pour dénoncer les conditions de travail, et y voyait l’écho de la passion du Christ.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/abyungmu-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">théologien fondateur de la pensée minjung, qui fait du peuple opprimé le sujet de l’histoire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIM YONG-OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kim_Yong-ok"  title=" Wikipedia (en)"&gt;KIM YONG-OK&lt;/a&gt;, connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de Choe Han-gi, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/kyongok-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe et commentateur des classiques, vulgarisateur d’une philosophie coréenne du gi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1613 – 1682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GU Yanwu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gu_Yanwu"  title=" Wikipedia"&gt;GU Yanwu&lt;/a&gt; dit Tinglin, est l’un des trois grands penseurs de la transition entre les Ming et les Qing, avec Huang Zongxi et Wang Fuzhi. Originaire de Kunshan, près de Suzhou, il participa à la résistance contre les Mandchous, au cours de laquelle sa mère adoptive se laissa mourir de faim plutôt que de vivre sous la nouvelle dynastie, et il refusa toute sa vie de servir les Qing.&lt;/p&gt; &lt;p&gt;Pour lui, l’effondrement des Ming s’explique en partie par les spéculations creuses de l’école de Wang Yangming, qui avaient détourné les lettrés des affaires du monde. Il prône un retour à l’« étude solide » : lire les classiques dans leur sens originel, grâce à la philologie, à la phonétique ancienne et à l’épigraphie, et étudier la géographie, l’économie et les institutions pour être utile à son temps. On lui attribue la formule selon laquelle « l’étude des classiques est l’étude du principe ».&lt;/p&gt; &lt;p&gt;Voyageur infatigable, il parcourut pendant plus de vingt ans le nord de la Chine, avec des mulets chargés de livres, vérifiant sur le terrain les données des textes. Son &lt;em&gt;Rizhi lu&lt;/em&gt; (« Notes de connaissances acquises au jour le jour ») rassemble trente ans de recherches. Il y distingue la chute d’une dynastie, affaire des princes, de la perte de « tout ce qui est sous le Ciel », c’est-à-dire de la civilisation elle-même, dont chaque homme du peuple porte la responsabilité : Liang Qichao en tira une formule devenue une devise du patriotisme chinois. Il est considéré comme le fondateur de l’école des « preuves textuelles » (&lt;em&gt;kaozheng&lt;/em&gt;).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/guyanwu-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaozheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré loyaliste des Ming, fondateur de la critique philologique et de l’« étude solide ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1619 – 1692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WANG Fuzhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wang_Fuzhi"  title=" Wikipedia"&gt;WANG Fuzhi&lt;/a&gt; dit Chuanshan, est l’un des plus grands philosophes de la fin des Ming. Né à Hengyang, dans le Hunan, il prit part à la résistance contre les Mandchous après la chute de la dynastie en 1644 puis, refusant de servir les Qing, vécut retiré pendant près de quarante ans au pied des montagnes, où il écrivit dans la solitude une œuvre immense d’une centaine de titres.&lt;/p&gt; &lt;p&gt;Contre Zhu Xi, il affirme que le principe (&lt;em&gt;li&lt;/em&gt;) n’existe pas hors de l’énergie (&lt;em&gt;qi&lt;/em&gt;) : il n’est que l’ordre selon lequel l’énergie se meut. De même, la Voie n’est pas au-delà des choses concrètes, mais dans les « ustensiles » eux-mêmes. La nature humaine n’est pas donnée une fois pour toutes : elle « naît chaque jour et s’accomplit chaque jour ». Les désirs ne sont pas mauvais en eux-mêmes, et c’est dans leur juste satisfaction que se réalise le principe.&lt;/p&gt; &lt;p&gt;Penseur de l’histoire, il voit dans les institutions des réponses à des situations changeantes, et non des modèles éternels à restaurer : les « tendances » (&lt;em&gt;shi&lt;/em&gt;) de l’histoire ont leur propre logique. Dans ses &lt;em&gt;Lectures du Miroir universel&lt;/em&gt; et ses commentaires des classiques, il critique le despotisme et défend l’identité culturelle chinoise face aux conquérants. Ses manuscrits, longtemps restés inédits, furent publiés au XIXe siècle par Zeng Guofan, et ses idées inspirèrent réformateurs et révolutionnaires, de Tan Sitong au jeune Mao Zedong, lui aussi originaire du Hunan.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/wangfuzhi-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lettré de la fin des Ming, philosophe de l’énergie vitale et penseur de l’histoire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1724 – 1777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAI Zhen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dai_Zhen"  title=" Wikipedia"&gt;DAI Zhen&lt;/a&gt; dit Dongyuan, est le plus grand savant de l’école des « preuves textuelles » (&lt;em&gt;kaozheng&lt;/em&gt;) et l’un des philosophes chinois les plus originaux du XVIIIe siècle. Fils d’un marchand de tissus de l’Anhui, il échoua plusieurs fois aux examens supérieurs, mais sa réputation d’érudit lui valut d’être appelé à Pékin pour travailler à la grande &lt;em&gt;Bibliothèque complète des quatre trésors&lt;/em&gt; (&lt;em&gt;Siku quanshu&lt;/em&gt;), et l’empereur Qianlong lui accorda par faveur le titre de docteur.&lt;/p&gt; &lt;p&gt;Mathématicien, astronome, spécialiste de phonétique ancienne et de géographie, il appliquait aux classiques une méthode rigoureuse : comprendre chaque mot par son sens ancien, pour comprendre la phrase, puis la pensée des sages. Mais il ne s’en tenait pas à la philologie : dans son &lt;em&gt;Commentaire du sens des mots du Mencius&lt;/em&gt;, il s’attaque au cœur de l’orthodoxie néoconfucéenne.&lt;/p&gt; &lt;p&gt;Pour Zhu Xi, le principe (&lt;em&gt;li&lt;/em&gt;) est une réalité supérieure qui s’oppose aux désirs. Pour Dai Zhen, le principe n’est que l’ordre inhérent aux choses, que l’on découvre par une analyse attentive, et la morale consiste non à extirper les désirs, mais à les satisfaire avec mesure, en tenant compte de ceux d’autrui. Il dénonce une morale devenue instrument de domination : « Quand un homme meurt par la loi, il se trouve encore quelqu’un pour le plaindre ; quand il meurt par le principe, qui le plaindra ? » Redécouvert au début du XXe siècle par Liang Qichao et Hu Shi, il est souvent présenté comme un précurseur de la pensée moderne en Chine.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/daizhen-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grand philologue des Qing, critique de la morale néoconfucéenne au nom des désirs humains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1854 – 1921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAN Fu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yan_Fu"  title=" Wikipedia"&gt;YAN Fu&lt;/a&gt; est le grand passeur de la pensée occidentale moderne en Chine. Formé à l’école navale de Fuzhou, il fut envoyé de 1877 à 1879 au Collège naval royal de Greenwich, en Angleterre, où il s’intéressa moins à la marine qu’aux institutions, au droit et à la philosophie britanniques.&lt;/p&gt; &lt;p&gt;Après la défaite face au Japon en 1895, il entreprit de faire connaître aux lettrés chinois les idées qui, selon lui, expliquaient la puissance de l’Occident. Sa traduction libre d’&lt;em&gt;Evolution and Ethics&lt;/em&gt; de Thomas Huxley, parue en 1898 sous le titre &lt;em&gt;Tianyan lun&lt;/em&gt;, eut un retentissement immense : la formule « les êtres s’affrontent, le Ciel sélectionne, le plus apte survit » devint le mot d’ordre d’une génération inquiète de la survie de la Chine. Il traduisit ensuite Adam Smith, John Stuart Mill, Montesquieu et Herbert Spencer. Écrites dans une langue classique très soignée pour convaincre les lettrés, ses traductions sont accompagnées de longs commentaires où il confronte les idées occidentales aux textes chinois.&lt;/p&gt; &lt;p&gt;Il fixa aussi pour la traduction trois exigences restées célèbres : fidélité, intelligibilité et élégance. Pour lui, la force des nations occidentales venait de la liberté laissée aux individus, qui libère leurs énergies au profit de la collectivité. Déçu par la République, il se rapprocha à la fin de sa vie de positions conservatrices, soutint la tentative de restauration monarchique de Yuan Shikai et revint au confucianisme et au taoïsme, signe des tensions d’une génération partagée entre deux mondes.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/yanfu-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libéralisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">traducteur de Huxley, Mill et Spencer, introducteur de la pensée libérale et évolutionniste en Chine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1858 – 1927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KANG Youwei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kang_Youwei"  title=" Wikipedia"&gt;KANG Youwei&lt;/a&gt; est le principal inspirateur du mouvement réformiste de la fin des Qing. Originaire du Guangdong, formé aux classiques confucéens, il découvrit à Hong Kong et à Shanghai l’efficacité des institutions occidentales. Après la défaite de la Chine face au Japon en 1895, il organisa la pétition de plus d’un millier de candidats aux examens réunis à Pékin pour réclamer des réformes.&lt;/p&gt; &lt;p&gt;En 1898, le jeune empereur Guangxu l’appela et lança, sur ses conseils, la « réforme des Cent Jours » : modernisation de l’administration, des examens, de l’armée et de l’enseignement. L’impératrice douairière Cixi y mit fin par un coup d’État ; six réformateurs furent exécutés, et Kang Youwei dut fuir et vivre plus de quinze ans en exil. Pour justifier ses réformes, il présentait Confucius non comme un gardien de la tradition, mais comme un réformateur qui avait lui-même invoqué l’Antiquité pour changer son temps.&lt;/p&gt; &lt;p&gt;Son œuvre la plus audacieuse, le &lt;em&gt;Livre de la Grande Unité&lt;/em&gt; (&lt;em&gt;Datong shu&lt;/em&gt;), décrit une humanité future délivrée de toutes les frontières : plus d’États, de classes, de races ni de familles, un gouvernement mondial, l’égalité entre hommes et femmes et des institutions publiques prenant en charge chaque vie, de la naissance à la mort. Jugé trop radical, l’ouvrage ne fut publié intégralement qu’après sa mort. Paradoxalement, Kang Youwei resta fidèle à la monarchie après 1911 et voulut faire du confucianisme une religion d’État.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/kangyouwei-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confucianisme ; Utopisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">réformateur confucéen, inspirateur des Cent Jours de 1898 et auteur du Livre de la Grande Unité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1865 – 1898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAN Sitong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Tan_Sitong"  title=" Wikipedia (en)"&gt;TAN Sitong&lt;/a&gt; est le plus radical des réformateurs de 1898 et l’un de ses martyrs. Fils d’un haut fonctionnaire du Hunan, il parcourut la Chine dans sa jeunesse, pratiqua les arts martiaux et étudia à la fois les classiques, le bouddhisme et les sciences occidentales diffusées par les missionnaires. Bouleversé par la défaite de 1895, il fonda dans le Hunan, avec d’autres lettrés, des écoles et des sociétés savantes pour diffuser les idées nouvelles, comme l’École des affaires du temps, où enseignait Liang Qichao.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Étude de la bienveillance&lt;/em&gt; (&lt;em&gt;Renxue&lt;/em&gt;), il fait de la bienveillance confucéenne (&lt;em&gt;ren&lt;/em&gt;) le principe même de l’univers : tout est relié par une substance subtile, qu’il rapproche de l’éther de la physique de son temps, et la bienveillance est cette « communication » universelle qui fait tomber les barrières entre les êtres. Il en tire une critique violente des hiérarchies : les « trois liens » qui soumettent le sujet au prince, le fils au père et l’épouse au mari ne sont à ses yeux que des « filets » qu’il faut briser.&lt;/p&gt; &lt;p&gt;Appelé à Pékin pour participer à la réforme des Cent Jours, il refusa de fuir lors du coup d’État de Cixi, déclarant qu’aucune réforme au monde n’avait réussi sans que le sang ait coulé, et qu’il voulait être le premier à verser le sien en Chine. Il fut exécuté avec cinq autres réformateurs le 28 septembre 1898, à trente-trois ans. Publié après sa mort par Liang Qichao, le &lt;em&gt;Renxue&lt;/em&gt; inspira les révolutionnaires du début du XXe siècle.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/tansitong-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confucianisme ; Bouddhisme Mahayana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">réformateur et martyr de 1898, philosophe de la bienveillance universelle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1869 – 1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZHANG Taiyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zhang_Binglin"  title=" Wikipedia"&gt;ZHANG Taiyan&lt;/a&gt; de son vrai nom Zhang Binglin, est l’une des figures les plus singulières de la pensée chinoise moderne : grand philologue, militant révolutionnaire et philosophe. Disciple du savant Yu Yue, formé dans la tradition des « preuves textuelles », il rompit avec la dynastie mandchoue et devint l’un des principaux idéologues du mouvement révolutionnaire de Sun Yat-sen. À Tokyo, il dirigea la revue révolutionnaire &lt;em&gt;Minbao&lt;/em&gt;, où il attaqua avec violence les réformistes partisans d’une monarchie constitutionnelle.&lt;/p&gt; &lt;p&gt;Emprisonné à Shanghai de 1903 à 1906 pour un article jugé injurieux envers l’empereur, il y étudia le bouddhisme Yogācāra (« Rien-que-conscience »), qui transforma sa pensée. Il oppose à l’évolutionnisme triomphant de son époque une critique originale : le progrès fait croître à la fois le bien et le mal, et aucune « loi de l’histoire » ne justifie de sacrifier les individus. Dans son commentaire du chapitre « De l’égalité des choses » de Zhuangzi, il défend une égalité radicale qui respecte la diversité des êtres et des cultures, sans les ramener à un modèle unique.&lt;/p&gt; &lt;p&gt;Après 1911, il s’opposa à Yuan Shikai, qui le fit assigner à résidence, puis se consacra à l’enseignement et à l’étude de la langue et de l’histoire chinoises, qu’il considérait comme l’âme de la nation. Parmi ses élèves figurent l’écrivain Lu Xun et de nombreux grands linguistes. Sa pensée, longtemps négligée, est aujourd’hui redécouverte comme une critique précoce de la modernité.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/zhangtaiyan-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philologue révolutionnaire, penseur nationaliste nourri du bouddhisme Yogācāra et de Zhuangzi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1873 – 1929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIANG Qichao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Liang_Qichao"  title=" Wikipedia"&gt;LIANG Qichao&lt;/a&gt; est le penseur le plus influent de la Chine du début du XXe siècle. Disciple de Kang Youwei, il participa avec lui à la réforme des Cent Jours de 1898, puis s’exila au Japon, d’où il diffusa par ses revues les idées occidentales, qu’il lisait souvent dans leurs traductions japonaises.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Du nouveau peuple&lt;/em&gt; (&lt;em&gt;Xinmin shuo&lt;/em&gt;), publié en feuilleton à partir de 1902, il affirme que la Chine ne pourra se relever sans transformer ses habitants : les sujets passifs d’un empire doivent devenir des citoyens dotés de droits, du sens du bien public et de l’esprit d’initiative. La nation, plus que l’empire ou la famille, devient la communauté qui doit mobiliser les loyautés. Il popularise une grande partie du vocabulaire politique moderne et invente une prose claire et passionnée, à mi-chemin entre la langue classique et la langue parlée, qui toucha des millions de lecteurs.&lt;/p&gt; &lt;p&gt;Rentré en Chine après 1911, il fut ministre sous la République, puis se consacra à l’histoire et à l’enseignement, notamment à l’université Tsinghua. Après un voyage en Europe au lendemain de la Première Guerre mondiale, il douta de la civilisation matérielle de l’Occident et plaida pour une synthèse entre la culture chinoise et la science occidentale. Ses ouvrages d’histoire, comme son &lt;em&gt;Aperçu de la pensée des Qing&lt;/em&gt; (1920), ont fondé l’historiographie moderne de la pensée chinoise. Plusieurs de ses enfants devinrent de grands savants, dont Liang Sicheng, pionnier de l’histoire de l’architecture chinoise.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/liangqichao-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journaliste et penseur réformiste, théoricien du « nouveau citoyen » et de la nation chinoise moderne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1885 – 1968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIONG Shili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili"  title=" Wikipedia"&gt;XIONG Shili&lt;/a&gt; est le principal métaphysicien du nouveau confucianisme. D’origine modeste, engagé comme soldat dans la révolution de 1911, il se tourna ensuite vers la philosophie et étudia le bouddhisme Yogācāra à Nankin, auprès du maître Ouyang Jingwu, avant d’enseigner à l’université de Pékin.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Nouveau traité de la Rien-que-conscience&lt;/em&gt; (1932), il rompt avec ses maîtres bouddhistes : il leur reproche de séparer la réalité ultime du monde des phénomènes et de faire de la vie une illusion dont il faudrait se délivrer. Inspiré du &lt;em&gt;Livre des mutations&lt;/em&gt;, il soutient au contraire que la « substance » et sa « fonction » ne font qu’un : la réalité ultime n’est pas un fond immobile, mais un mouvement créateur incessant, fait de « contraction » et d’« expansion », que l’on retrouve dans l’esprit humain. Connaître le réel, c’est d’abord le reconnaître en soi.&lt;/p&gt; &lt;p&gt;Cette « ontologie de la vie » donna au nouveau confucianisme ses fondements philosophiques. Xiong Shili forma notamment Mou Zongsan et Tang Junyi, qui développèrent sa pensée à Hong Kong et à Taïwan. Resté en Chine populaire après 1949, il continua d’écrire, mais fut persécuté pendant la Révolution culturelle et mourut à Shanghai en 1968. Dans &lt;em&gt;Aux sources du confucianisme&lt;/em&gt; (1956), il soutenait que l’enseignement authentique de Confucius, déformé par les dynasties impériales, était un idéal d’égalité et de gouvernement par le peuple.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/xiongshili-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouveau confucianisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe de l’unité de la substance et de la fonction, fondateur métaphysique du nouveau confucianisme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1891 – 1962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HU Shi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hu_Shi"  title=" Wikipedia"&gt;HU Shi&lt;/a&gt; est l’une des grandes figures du mouvement de la Nouvelle Culture. Boursier aux États-Unis, il étudia à Cornell puis à Columbia, où il suivit l’enseignement de John Dewey, dont il devint le principal interprète en Chine et qu’il accompagna lors de sa tournée de conférences chinoise, de 1919 à 1921.&lt;/p&gt; &lt;p&gt;En 1917, dans la revue &lt;em&gt;Nouvelle Jeunesse&lt;/em&gt;, il appela à écrire la littérature en langue parlée (&lt;em&gt;baihua&lt;/em&gt;) plutôt qu’en chinois classique, une révolution qui transforma profondément la culture chinoise. Professeur à l’université de Pékin, il appliqua la méthode pragmatiste à l’histoire de la pensée : « hypothèses audacieuses, vérifications minutieuses ». Son &lt;em&gt;Esquisse d’une histoire de la philosophie chinoise&lt;/em&gt; (1919) fut la première à traiter les penseurs anciens avec les outils de la critique moderne. Pionnier de la poésie moderne en langue parlée avec son recueil &lt;em&gt;Expériences&lt;/em&gt; (1920), il lança aussi le mouvement de « réexamen de l’héritage national », qui soumettait les textes anciens à la critique historique.&lt;/p&gt; &lt;p&gt;Libéral convaincu, il préférait les réformes graduelles, « problème par problème », aux grandes doctrines qui promettent de tout résoudre, ce qui l’opposa aux marxistes comme Li Dazhao. Ambassadeur de la République de Chine aux États-Unis de 1938 à 1942, puis président de l’université de Pékin, il quitta le continent en 1949 et présida l’Academia Sinica à Taïwan, tandis qu’une vaste campagne de critique était menée contre sa pensée en Chine populaire.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/hushi-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pragmatisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">élève de John Dewey, figure du mouvement du 4 Mai et promoteur de la langue parlée en littérature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1893 – 1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIANG Shuming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming"  title=" Wikipedia"&gt;LIANG Shuming&lt;/a&gt; est souvent considéré comme le premier des « nouveaux confucéens ». Autodidacte, d’abord attiré par le bouddhisme, il fut recruté à vingt-quatre ans par l’université de Pékin pour enseigner la philosophie indienne, avant de se tourner vers le confucianisme.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), il distingue trois orientations fondamentales de la volonté humaine : l’Occident cherche à maîtriser le monde extérieur, la Chine à harmoniser ses désirs avec son milieu, l’Inde à se libérer des désirs. Chaque voie répond à un problème différent, et l’humanité, une fois ses besoins matériels satisfaits par la science, devra selon lui se tourner vers l’attitude chinoise. Ce livre, qui défendait la culture chinoise au moment où le mouvement du 4 Mai la rejetait, fit grand bruit.&lt;/p&gt; &lt;p&gt;Convaincu que la Chine devait se reconstruire à partir de ses villages, il dirigea dans les années 1930, dans le Shandong, un vaste mouvement de « reconstruction rurale » associant éducation, coopératives et organisation communautaire. Après 1949, il osa critiquer devant Mao Zedong le sort fait aux paysans, ce qui lui valut d’être violemment attaqué. En 1974, il refusa de participer à la campagne contre Confucius, en citant les &lt;em&gt;Entretiens&lt;/em&gt; : « On peut enlever son général à une armée, on ne peut enlever sa volonté au plus humble des hommes. » Il vécut assez longtemps pour voir sa pensée redécouverte dans la Chine des réformes ; l’historien américain Guy Alitto lui a consacré une biographie intitulée &lt;em&gt;Le Dernier Confucéen&lt;/em&gt;.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/liangshuming-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penseur des cultures d’Orient et d’Occident, pionnier du nouveau confucianisme et de la reconstruction rurale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1895 – 1990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FENG Youlan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Feng_Youlan"  title=" Wikipedia"&gt;FENG Youlan&lt;/a&gt; est l’historien de la philosophie chinoise le plus lu au monde. Formé à l’université de Pékin puis à Columbia, où il fut l’élève de John Dewey, il enseigna à l’université Tsinghua et publia en 1931 et 1934 les deux volumes de son &lt;em&gt;Histoire de la philosophie chinoise&lt;/em&gt; qui, traduite en anglais par Derk Bodde, devint la référence internationale ; son &lt;em&gt;Précis d’histoire de la philosophie chinoise&lt;/em&gt; (1948) a été lu par des générations d’étudiants en Occident.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre le Japon, réfugié avec les universités chinoises dans le sud-ouest du pays, il élabora son propre système, le « nouveau néoconfucianisme », exposé en six livres, dont le &lt;em&gt;Nouveau traité du principe&lt;/em&gt;. Il y relit Zhu Xi à l’aide de la logique moderne : les principes sont des concepts formels, distincts des choses concrètes. Il distingue aussi quatre degrés de conscience chez l’homme, du niveau naturel, où l’on suit ses instincts, au niveau utilitaire, puis moral, et enfin au « niveau du Ciel et de la Terre », où l’on se sait partie de l’univers entier.&lt;/p&gt; &lt;p&gt;Resté en Chine après 1949, il renia publiquement ses travaux antérieurs et dut se soumettre aux campagnes politiques ; il participa même, pendant la Révolution culturelle, à la critique de Confucius, ce qui lui fut longtemps reproché. À la fin de sa vie, il entreprit une nouvelle &lt;em&gt;Histoire de la philosophie chinoise&lt;/em&gt; en sept volumes, achevée peu avant sa mort, où il revint plus librement à ses propres convictions.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/fengyoulan-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historien de la philosophie chinoise et auteur d’un « nouveau néoconfucianisme ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1909 – 1978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANG Junyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Tang_Junyi"  title=" Wikipedia (en)"&gt;TANG Junyi&lt;/a&gt; est, avec Mou Zongsan, l’une des deux grandes figures du nouveau confucianisme d’après-guerre. Né dans le Sichuan, élève de Xiong Shili et lecteur passionné de Hegel, il quitta la Chine en 1949 pour Hong Kong, où il fonda avec l’historien Qian Mu et d’autres lettrés exilés le New Asia College, intégré plus tard à l’Université chinoise de Hong Kong.&lt;/p&gt; &lt;p&gt;Pour lui, la culture tout entière est l’expression d’un sujet moral : sciences, arts, religions et institutions sont autant de manifestations de l’effort de l’esprit pour se dépasser. Son œuvre ultime, &lt;em&gt;L’Existence de la vie et les horizons de l’esprit&lt;/em&gt; (1977), décrit neuf « horizons » de la conscience, du monde des choses individuelles jusqu’aux horizons religieux du christianisme, du bouddhisme et, au sommet, de la « Voie du Ciel » confucéenne, qui unit la plus haute exigence morale et la vie quotidienne. Il voyait dans la vénération du Ciel, des ancêtres et des sages le cœur religieux d’une tradition trop souvent réduite à une simple morale.&lt;/p&gt; &lt;p&gt;Profondément marqué par l’exil, il comparait la culture chinoise à un arbre dont « les fleurs et les fruits sont tombés et dispersés », et appelait les Chinois de la diaspora à faire renaître cette tradition par eux-mêmes. Cosignataire en 1958 du &lt;em&gt;Manifeste pour une réévaluation de la culture chinoise&lt;/em&gt;, il consacra aussi de grands ouvrages à l’histoire des concepts de la philosophie chinoise. Son enseignement a durablement marqué la vie intellectuelle de Hong Kong et de Taïwan.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/tangjunyi-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe néoconfucéen de Hong Kong, penseur des neuf horizons de l’esprit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1909 – 1995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOU Zongsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mou_Zongsan"  title=" Wikipedia (en)"&gt;MOU Zongsan&lt;/a&gt; est le plus systématique des nouveaux confucéens. Né dans le Shandong, élève de Xiong Shili à l’université de Pékin, il quitta le continent en 1949 et enseigna à Taïwan puis à Hong Kong, où il forma, avec Tang Junyi, la plupart des penseurs confucéens de la seconde moitié du XXe siècle.&lt;/p&gt; &lt;p&gt;Il mena un dialogue serré avec Kant, dont il traduisit les trois &lt;em&gt;Critiques&lt;/em&gt; en chinois. Pour Kant, l’être humain, être fini, n’a pas accès à une « intuition intellectuelle » qui lui ferait saisir les choses en soi. Mou Zongsan soutient au contraire que les grandes traditions chinoises, confucianisme, taoïsme et bouddhisme, reconnaissent toutes cette possibilité : par la culture morale, l’esprit humain, tout fini qu’il est, peut participer de l’infini. Le confucianisme fonde ainsi une « métaphysique morale », où la conscience morale ouvre l’accès au réel lui-même.&lt;/p&gt; &lt;p&gt;Il voulait aussi montrer que la tradition chinoise peut produire la science et la démocratie, à condition que l’esprit moral accepte de se « limiter » lui-même pour laisser place à la connaissance objective et aux institutions politiques. En 1958, il signa avec Tang Junyi, Xu Fuguan et Zhang Junmai un &lt;em&gt;Manifeste pour une réévaluation de la culture chinoise&lt;/em&gt;, acte fondateur du nouveau confucianisme d’après-guerre. Son grand ouvrage, &lt;em&gt;Substance de l’esprit et substance de la nature&lt;/em&gt;, propose une relecture d’ensemble du néoconfucianisme des Song et des Ming.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/mouzongsan-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe néoconfucéen de Taïwan et de Hong Kong, lecteur de Kant à la lumière de la sagesse chinoise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1930 – 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LI Zehou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Li_Zehou"  title=" Wikipedia"&gt;LI Zehou&lt;/a&gt; est l’un des philosophes chinois les plus influents de la seconde moitié du XXe siècle. Originaire du Hunan, diplômé de philosophie de l’université de Pékin en 1954, il se fit connaître dès les années 1950 dans les grands débats sur l’esthétique, puis devint, dans les années 1980, le maître à penser de toute une génération d’étudiants chinois.&lt;/p&gt; &lt;p&gt;Lecteur de Kant et de Marx, il soutient que les formes de la sensibilité et de la raison ne sont pas données d’avance, mais se sont formées au cours de l’histoire humaine, par la fabrication et l’usage des outils : c’est ce qu’il appelle la « sédimentation ». Le beau est ainsi « la forme de la liberté », l’humanisation de la nature par le travail collectif. Son livre &lt;em&gt;Le Chemin de la beauté&lt;/em&gt; (1981), qui parcourt l’histoire de l’art chinois, fut un immense succès. Il propose aussi de comprendre la culture chinoise comme une « culture de la joie » et du sentiment, plutôt que de la faute et du salut.&lt;/p&gt; &lt;p&gt;Après les événements de Tiananmen en 1989, ses ouvrages furent critiqués et il s’installa en 1992 aux États-Unis, où il enseigna dans plusieurs universités ; il mourut en 2021 à Boulder, dans le Colorado. Dans ses derniers livres, il développe une « ontologie du sentiment » qui fait des émotions, cultivées par les rites et la musique, le fondement de la vie morale. Il est l’un des rares philosophes chinois contemporains à figurer dans la grande anthologie Norton de théorie et de critique littéraires.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laphilo.fr/pho/lizehou-mini.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esthetique ; ethique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">philosophe de l’esthétique et de la « sédimentation », figure intellectuelle majeure de la Chine des années 1980.</t>
   </si>
 </sst>
 </file>
@@ -5442,7 +6264,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -6166,8 +6988,6 @@
       <c r="P18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="XFC18" s="0"/>
-      <c r="XFD18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="208.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -8133,7 +8953,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="342.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="390.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
         <v>721</v>
       </c>
@@ -8175,7 +8995,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="303.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="266.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
         <v>724</v>
       </c>
@@ -8217,7 +9037,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="197" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
         <v>768</v>
       </c>
@@ -13198,6 +14018,1822 @@
         <v>401</v>
       </c>
       <c r="P190" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="n">
+        <v>613</v>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>696</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O191" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="n">
+        <v>617</v>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>686</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="O192" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P192" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="n">
+        <v>625</v>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>702</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="J193" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="O193" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="n">
+        <v>857</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>910</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E194" s="10" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="J194" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="O194" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>1101</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J195" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="O195" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>1210</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="O196" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>1392</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="J197" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P197" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>1398</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P198" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>1433</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E199" s="10" t="s">
+        <v>1506</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K199" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L199" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M199" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="n">
+        <v>1482</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>1519</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M200" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O200" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>1546</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>1516</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M201" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="O201" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="1" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>1572</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K202" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L202" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M202" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="O202" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>1604</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="J203" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M203" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="O203" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>1572</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="J204" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M204" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="O204" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="1" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>1598</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M205" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="O205" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="1" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>1584</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E206" s="10" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="J206" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="O206" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P206" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>1689</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="J207" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="O207" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P207" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>1673</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J208" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="M208" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="O208" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>1736</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J209" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="M209" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="O209" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P209" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>1751</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="J210" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L210" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M210" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="O210" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="n">
+        <v>1731</v>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="J211" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="L211" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="M211" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="O211" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="n">
+        <v>1737</v>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>1805</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="M212" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="O212" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="n">
+        <v>1762</v>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L213" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="M213" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="O213" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P213" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="n">
+        <v>1792</v>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>1868</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E214" s="10" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="J214" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L214" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M214" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="O214" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="1" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>1877</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="J215" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="L215" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="M215" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="O215" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="1" t="n">
+        <v>1824</v>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>1864</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J216" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L216" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M216" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="O216" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>1925</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J217" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L217" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M217" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="O217" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="1" t="n">
+        <v>1879</v>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>1944</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J218" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L218" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M218" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="O218" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P218" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="1" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="L219" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M219" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="O219" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="1" t="n">
+        <v>1890</v>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>1981</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L220" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="M220" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="O220" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="1" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>1989</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L221" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="M221" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="O221" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A222" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>1976</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="M222" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="O222" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="1" t="n">
+        <v>1912</v>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E223" s="10" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L223" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="M223" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="O223" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A224" s="1" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>1996</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>1635</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="L224" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="M224" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="O224" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A225" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E225" s="10" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L225" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="O225" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P225" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A226" s="1" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K226" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="L226" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M226" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="O226" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P226" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A227" s="1" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K227" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L227" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="M227" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="O227" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P227" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="1" t="n">
+        <v>1724</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="L228" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M228" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P228" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A229" s="1" t="n">
+        <v>1854</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E229" s="10" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="L229" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P229" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="n">
+        <v>1858</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L230" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="M230" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="O230" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P230" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A231" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="J231" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L231" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="O231" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P231" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A232" s="1" t="n">
+        <v>1869</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E232" s="10" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="J232" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="O232" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P232" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A233" s="1" t="n">
+        <v>1873</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>1690</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L233" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M233" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="O233" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P233" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A234" s="1" t="n">
+        <v>1885</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E234" s="10" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L234" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="O234" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P234" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="n">
+        <v>1891</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E235" s="10" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K235" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L235" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="M235" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="O235" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P235" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A236" s="1" t="n">
+        <v>1893</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E236" s="10" t="s">
+        <v>1710</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L236" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M236" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P236" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A237" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E237" s="10" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K237" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L237" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M237" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="O237" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P237" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A238" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E238" s="10" t="s">
+        <v>1722</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L238" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M238" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="O238" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P238" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E239" s="10" t="s">
+        <v>1728</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K239" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L239" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M239" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P239" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A240" s="1" t="n">
+        <v>1930</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>1734</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L240" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="M240" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P240" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13218,7 +15854,7 @@
     <hyperlink ref="H11" r:id="rId5" display="https://www.laphilo.fr/pho/merikare-mini.webp"/>
     <hyperlink ref="E12" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Akshapada_Gautama&quot; title=&quot; Wikipedia&quot;&gt;Akshapada Gautama&lt;/a&gt; est le sage fondateur traditionnel de l’école Nyâya, l’une des six écoles orthodoxes (&lt;em&gt;āstika&lt;/em&gt;) de la philosophie indienne. Auteur présumé des &lt;em&gt;Nyâya-sûtras&lt;/em&gt;, il y pose les bases d’une logique et d’une épistémologie rigoureuses, centrées sur les moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : perception, inférence, comparaison et témoignage. Le&lt;a href=&quot;https://www.youtube.com/watch?v=axjvz9FZPfU&quot;  title=&quot;Nyaya philosophy par TrueColors&quot;&gt; Nyâya &lt;/a&gt; a profondément influencé le débat philosophique indien pendant plus de deux millénaires, notamment dans ses joutes argumentatives avec le bouddhisme et le jaïnisme.&lt;/p&gt;"/>
     <hyperlink ref="H12" r:id="rId7" display="https://www.laphilo.fr/pho/agautama-mini.webp"/>
-    <hyperlink ref="H13" r:id="rId8" display="https://www.laphilo.fr/pho/deserpere-mini.webp"/>
+    <hyperlink ref="H13" r:id="rId8" display="https://www.laphilo.fr/pho/desespere-mini.webp"/>
     <hyperlink ref="E14" r:id="rId9" display="&lt;p&gt;Les &lt;a href=&quot;https://fr.wikipedia.org/wiki/Papyrus_d%27Ipou-Our&quot;  title=&quot; Wikipedia&quot;&gt;Lamentations d’IPOU-OUR&lt;/a&gt; sont un texte égyptien composé au plus tôt à la fin de la XIIe dynastie. Le sage Ipou-our s'y adresse au roi pour lui décrire un pays sens dessus dessous : les pauvres sont devenus riches, les nobles sont dans la misère, les lois ne sont plus respectées et le Nil lui-même semble ensanglanté.&lt;/p&gt; &lt;p&gt;Ce tableau d'un monde en chaos est moins une chronique historique qu'une réflexion sur ce qui arrive quand l'ordre juste, la Maât, n'est plus garanti. Il reproche même au dieu créateur de laisser faire le mal, et appelle un pouvoir fort à rétablir l'harmonie.&lt;/p&gt; &lt;p&gt;Le texte nous est parvenu sur un seul papyrus, conservé aujourd'hui au musée de Leyde, aux Pays-Bas, dont le début et la fin manquent. Il se compose de longues séries de lamentations commençant par le même refrain, « En vérité… », qui décrivent tour à tour la violence, la famine, le pillage des tombes, la fuite des serviteurs et l'effondrement de l'administration.&lt;/p&gt; &lt;p&gt;Certains y ont vu le témoignage d'une révolution sociale réelle, d'autres un écho des plaies d'Égypte du livre de l'Exode ; les égyptologues y lisent plutôt un genre littéraire, celui   &lt;a href=&quot;https://www.worldhistory.org/trans/fr/2-981/lamentations-dipou-our/&quot;   title=&quot;lamentations d’Ipou-Our par worldhistory&quot;&gt;des « lamentations »,&lt;/a&gt;  qui montre l'image inversée de l'ordre idéal pour mieux en faire sentir la valeur. Le désordre décrit n'est pas seulement politique : c'est tout l'équilibre entre les hommes, la nature et les dieux qui semble rompu.&lt;/p&gt; &lt;p&gt;Le texte pose ainsi, très tôt, la question du mal et de la responsabilité des dirigeants et des dieux face au désordre du monde.&lt;/p&gt;"/>
     <hyperlink ref="H14" r:id="rId10" display="https://www.laphilo.fr/pho/iour-mini.webp"/>
     <hyperlink ref="H15" r:id="rId11" display="https://www.laphilo.fr/pho/hammurabi-mini.webp"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -11729,8 +11729,10 @@
       <c r="K129" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L129" s="2" t="s">
-        <v>799</v>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen ; École de Kyōto</t>
+        </is>
       </c>
       <c r="M129" s="2" t="s">
         <v>1094</v>
@@ -12086,14 +12088,18 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B138" s="1" t="n">
-        <v>1966</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>1162</v>
+      <c r="A138" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900 — 1990</t>
+        </is>
       </c>
       <c r="D138" s="2" t="s">
         <v>1163</v>
@@ -12116,8 +12122,10 @@
       <c r="K138" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L138" s="2" t="s">
-        <v>799</v>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen ; École de Kyōto</t>
+        </is>
       </c>
       <c r="M138" s="2" t="s">
         <v>1168</v>
@@ -15834,6 +15842,881 @@
         <v>271</v>
       </c>
       <c r="P240" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1">
+        <v>767</v>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">767 – 822</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAICHŌ</t>
+        </is>
+      </c>
+      <c r="E241" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D"  title=" Wikipedia"&gt;SAICHŌ&lt;/a&gt; connu sous son nom posthume de Dengyō Daishi, est le fondateur de l’école bouddhiste Tendai au Japon. Ordonné à Nara, il se retira dès 785 sur le mont Hiei, au nord-est de la future capitale Kyōto, pour y mener une vie de méditation, loin d’un clergé de Nara trop mêlé au pouvoir. En 804, il fit partie de l’ambassade envoyée en Chine des Tang, où il étudia l’école Tiantai, fondée sur le &lt;em&gt;Sûtra du Lotus&lt;/em&gt;, ainsi que le zen, le tantrisme et la discipline monastique.&lt;/p&gt; &lt;p&gt;À son retour, il fit du monastère de l’Enryaku-ji, sur le mont Hiei, le centre d’une synthèse ambitieuse : le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; y est tenu pour l’enseignement ultime du Bouddha, qui réunit toutes les voies en un « Véhicule unique ». Contre les écoles de Nara, il soutient que tous les êtres, sans exception, possèdent la nature de bouddha et peuvent atteindre l’Éveil. Il défendit aussi une ordination propre au Japon, fondée sur les seuls préceptes du Grand Véhicule, que la cour autorisa quelques jours après sa mort.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Règles pour les étudiants de la montagne&lt;/em&gt; prévoyaient douze années de retraite sur le mont Hiei pour former des moines au service du pays, qu’il appelait des « trésors de la nation ». L’Enryaku-ji devint pendant des siècles le plus grand foyer intellectuel du bouddhisme japonais : les fondateurs des grandes écoles de l’époque de Kamakura, Hōnen, Shinran, Eisai, Dōgen et Nichiren, y firent tous leurs études. Son contemporain et rival Kūkai fonda de son côté l’école Shingon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/saicho-mini.webp</t>
+        </is>
+      </c>
+      <c r="J241" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine fondateur de l’école Tendai au Japon et du grand monastère du mont Hiei.</t>
+        </is>
+      </c>
+      <c r="O241" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P241" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1">
+        <v>1133</v>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133 – 1212</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HŌNEN</t>
+        </is>
+      </c>
+      <c r="E242" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C5%8Dnen"  title=" Wikipedia"&gt;HŌNEN&lt;/a&gt; est le fondateur de l’école japonaise de la Terre pure (&lt;em&gt;Jōdo-shū&lt;/em&gt;). Son père, officier de province, ayant été tué dans une attaque lorsqu’il avait neuf ans, il entra au monastère du mont Hiei, où il étudia pendant une trentaine d’années les textes de toutes les écoles, sans y trouver de voie accessible aux hommes ordinaires d’un temps que l’on disait entré dans l’« âge de la fin de la Loi ».&lt;/p&gt; &lt;p&gt;En 1175, la lecture d’un commentaire du maître chinois Shandao lui apporta la réponse : face à l’impuissance humaine, seul compte le vœu du bouddha Amida de sauver tous ceux qui l’invoquent. Il suffit donc de réciter avec foi le &lt;em&gt;nembutsu&lt;/em&gt;, « Namu Amida Butsu » (« Hommage au bouddha Amida »), pour renaître dans la Terre pure. Dans son &lt;em&gt;Recueil sur le nembutsu du vœu originel choisi&lt;/em&gt; (1198), il affirme que cette pratique, à la portée de tous, hommes et femmes, nobles et paysans, savants et ignorants, suffit, sans méditations savantes ni dons aux monastères.&lt;/p&gt; &lt;p&gt;Cette simplicité radicale attira de nombreux disciples, mais inquiéta les grands monastères, qui obtinrent l’interdiction du &lt;em&gt;nembutsu&lt;/em&gt; exclusif. En 1207, Hōnen, alors âgé de soixante-quatorze ans, fut exilé dans l’île de Shikoku, tandis que plusieurs disciples étaient exécutés. Gracié, il revint à Kyōto peu avant sa mort. Son disciple Shinran approfondit sa pensée en fondant la « véritable école de la Terre pure », qui devint l’une des plus grandes communautés bouddhistes du Japon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/honen-mini.webp</t>
+        </is>
+      </c>
+      <c r="J242" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine fondateur de l’école de la Terre pure, pour qui l’invocation du nom d’Amida suffit au salut.</t>
+        </is>
+      </c>
+      <c r="O242" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P242" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1">
+        <v>1222</v>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222 – 1282</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NICHIREN</t>
+        </is>
+      </c>
+      <c r="E243" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nichiren"  title=" Wikipedia"&gt;NICHIREN&lt;/a&gt; est l’une des figures les plus combatives du bouddhisme japonais. Fils de pêcheur de la province d’Awa, il étudia au mont Hiei et dans les grands monastères, avant d’acquérir la conviction que seul le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; contenait la vérité ultime du Bouddha. En 1253, il proclama publiquement la formule « Namu Myōhō Renge Kyō » (« Hommage au Sûtra du Lotus de la Loi merveilleuse »), dont la récitation devait selon lui suffire à manifester la nature de bouddha en chacun.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Traité pour établir la juste Loi et pacifier le pays&lt;/em&gt; (1260), adressé au pouvoir militaire de Kamakura, il attribue les famines, les épidémies et les tremblements de terre de son époque à l’abandon du &lt;em&gt;Sûtra du Lotus&lt;/em&gt; au profit d’autres écoles, en particulier celle de la Terre pure, et annonce une invasion étrangère si le pays ne se convertit pas. Pour Nichiren, le salut n’est pas seulement individuel : c’est la société tout entière qui doit être transformée, ici-bas, en « terre de bouddha ».&lt;/p&gt; &lt;p&gt;Ses attaques contre les autres écoles et contre le pouvoir lui valurent des persécutions, une tentative d’exécution en 1271, à laquelle il échappa selon la tradition par miracle, et un exil de près de trois ans sur l’île de Sado. Les tentatives d’invasion mongole de 1274 et 1281 parurent confirmer ses prophéties. Son bouddhisme a donné naissance à de nombreuses écoles et à de grands mouvements laïcs modernes, comme la Sōka Gakkai, qui revendiquent aujourd’hui des millions de fidèles dans le monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nichiren-mini.webp</t>
+        </is>
+      </c>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine prophétique, fondateur d’un bouddhisme centré sur le Sûtra du Lotus.</t>
+        </is>
+      </c>
+      <c r="O243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P243" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A244" s="1">
+        <v>1363</v>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1443</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1363 – vers 1443</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZEAMI</t>
+        </is>
+      </c>
+      <c r="E244" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zeami"  title=" Wikipedia"&gt;ZEAMI&lt;/a&gt; Motokiyo est le grand maître du théâtre nō, qu’il porta à sa perfection après son père Kan’ami. Remarqué à douze ans par le shōgun Ashikaga Yoshimitsu, qui le prit sous sa protection, il fut formé aux lettres et à la poésie dans l’entourage de la cour, et écrivit plusieurs dizaines de pièces, dont beaucoup sont encore jouées aujourd’hui.&lt;/p&gt; &lt;p&gt;Ses traités, longtemps transmis en secret dans sa famille et redécouverts seulement au début du XXe siècle, forment l’une des premières grandes réflexions esthétiques du Japon. Dans &lt;em&gt;De la transmission de la fleur et du style&lt;/em&gt; (&lt;em&gt;Fūshikaden&lt;/em&gt;), il explique que l’acteur doit cultiver la « fleur », ce charme qui surprend et touche le public, et qui change avec l’âge : la fleur de la jeunesse passe, seule demeure celle que l’on a conquise par la discipline. Le sommet de l’art est le &lt;em&gt;yūgen&lt;/em&gt;, une beauté profonde et voilée, faite d’élégance et de mélancolie, qui suggère plus qu’elle ne montre.&lt;/p&gt; &lt;p&gt;Zeami insiste aussi sur la conscience de soi de l’acteur, qui doit se voir comme le voit le spectateur, avec un « regard détaché ». Pour lui, le plus haut moment du jeu est l’instant où l’acteur ne fait rien, où l’intensité intérieure se transmet dans le silence. Tombé en disgrâce sous le shōgun Ashikaga Yoshinori, il fut exilé en 1434 sur l’île de Sado, à plus de soixante-dix ans. Sa pensée, marquée par le bouddhisme zen, inspire encore la réflexion contemporaine sur l’art de l’acteur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/zeami-mini.webp</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">acteur et dramaturge, théoricien du théâtre nō et de la beauté du yūgen.</t>
+        </is>
+      </c>
+      <c r="O244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P244" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A245" s="1">
+        <v>1627</v>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1705</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1627 – 1705</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Itō JINSAI</t>
+        </is>
+      </c>
+      <c r="E245" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/It%C5%8D_Jinsai"  title=" Wikipedia"&gt;Itō JINSAI&lt;/a&gt; est l’un des penseurs confucéens les plus originaux du Japon. Fils d’un marchand de bois de Kyōto, il refusa la carrière de médecin que sa famille lui destinait et, sans jamais servir de seigneur, ouvrit en 1662 dans sa maison une école privée, le Kogidō (« Salle de l’étude du sens ancien »), qui accueillit pendant plus de quarante ans des milliers d’élèves, samouraïs comme roturiers.&lt;/p&gt; &lt;p&gt;D’abord fervent disciple de Zhu Xi, il traversa une longue crise personnelle, puis rompit avec le néoconfucianisme. Selon lui, les commentaires des Song ont recouvert la pensée de Confucius et de Mencius de notions étrangères, venues du bouddhisme et du taoïsme, comme celle d’un principe abstrait et immobile. Il propose de revenir directement au sens ancien des &lt;em&gt;Entretiens&lt;/em&gt;, qu’il tenait pour « le livre suprême de l’univers », et du &lt;em&gt;Mencius&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Pour Jinsai, le monde est mouvement et vie, et la vertu confucéenne essentielle, la bienveillance (&lt;em&gt;jin&lt;/em&gt;), est avant tout amour : elle se vit dans les relations concrètes de la vie quotidienne, entre parents, amis et voisins, et non dans la contemplation solitaire d’un principe. Sa pensée, accessible aux marchands et aux artisans, contribua à faire du confucianisme une morale de la vie ordinaire. Elle prépara la critique plus radicale d’Ogyū Sorai, et son école fut poursuivie par son fils Itō Tōgai.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/itojinsai-mini.webp</t>
+        </is>
+      </c>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confucéen de Kyōto, critique de Zhu Xi et penseur d’une morale de l’amour humain.</t>
+        </is>
+      </c>
+      <c r="O245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P245" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A246" s="1">
+        <v>1686</v>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1769</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1686 – 1769</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAKUIN Ekaku</t>
+        </is>
+      </c>
+      <c r="E246" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hakuin_Ekaku"  title=" Wikipedia"&gt;HAKUIN Ekaku&lt;/a&gt; est le grand rénovateur du zen Rinzai au Japon. Terrifié dans son enfance par un sermon sur les enfers, il devint moine à quinze ans, connut plusieurs expériences d’éveil, puis une grave « maladie du zen », un épuisement dont il dit s’être guéri grâce à des techniques de respiration et de visualisation enseignées par un ermite. Il passa l’essentiel de sa vie dans un petit temple de sa région natale, le Shōin-ji, au pied du mont Fuji.&lt;/p&gt; &lt;p&gt;Pour lui, l’éveil n’est pas un savoir mais une percée, qui exige une « grande foi », un « grand doute » et une « grande détermination ». Il systématisa l’entraînement par les kōans, ces énigmes qui brisent la pensée ordinaire, et en créa de nouveaux, dont le plus célèbre demande : « Quel est le son d’une seule main ? » Toutes les lignées actuelles du zen Rinzai se rattachent à lui.&lt;/p&gt; &lt;p&gt;Hakuin voulait aussi rendre le zen accessible aux laïcs : il écrivit des chants et des lettres en langue simple, ainsi que des textes sur la santé et la méditation. Peintre et calligraphe prolifique, il laissa des milliers d’œuvres à l’encre, souvent pleines d’humour, représentant Daruma, des dieux populaires ou des scènes de la vie quotidienne, aujourd’hui conservées dans les grands musées. Son &lt;em&gt;Chant de la méditation assise&lt;/em&gt;, qui commence par « Les êtres sont fondamentalement bouddhas », est encore récité dans les temples zen.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hakuin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maître zen rinzai, rénovateur de la pratique des kōans et peintre.</t>
+        </is>
+      </c>
+      <c r="O246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P246" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A247" s="1">
+        <v>1703</v>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1762</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1703 – 1762</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andō SHŌEKI</t>
+        </is>
+      </c>
+      <c r="E247" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/And%C5%8D_Sh%C5%8Deki"  title=" Wikipedia"&gt;Andō SHŌEKI&lt;/a&gt; est l’un des penseurs les plus radicaux de l’époque d’Edo. Médecin installé à Hachinohe, dans le nord du Japon, puis revenu dans son village natal de la province d’Akita, il vécut loin des grands centres intellectuels et resta presque inconnu jusqu’à ce que l’érudit Kanō Kōkichi redécouvre son manuscrit à la fin du XIXe siècle.&lt;/p&gt; &lt;p&gt;Dans son grand ouvrage, &lt;em&gt;La Voie de la nature et du vrai fonctionnement&lt;/em&gt; (&lt;em&gt;Shizen shin’eidō&lt;/em&gt;), il oppose au monde des hommes un « monde naturel » originel, où chacun cultivait lui-même la terre pour se nourrir. Cette « culture directe » (&lt;em&gt;chokkō&lt;/em&gt;) est à ses yeux la seule activité vraiment humaine : tous les autres, seigneurs, guerriers, prêtres, marchands, lettrés, vivent en parasites du travail des paysans. Il accuse les sages chinois, Confucius en tête, mais aussi le Bouddha, d’avoir inventé les hiérarchies, l’argent et les lois pour justifier cette exploitation.&lt;/p&gt; &lt;p&gt;Il refuse aussi la supériorité de l’homme sur la femme et pense la nature comme un mouvement unique d’énergie, où les contraires ne s’opposent pas mais se complètent, sans haut ni bas. Ce rejet total de l’ordre féodal a valu à Andō Shōeki d’être présenté, après la guerre, comme un précurseur de l’anarchisme, de l’écologie et de l’égalitarisme. L’historien canadien E. H. Norman lui consacra en 1949 un livre, &lt;em&gt;Andō Shōeki and the Anatomy of Japanese Feudalism&lt;/em&gt;, qui le fit connaître en Occident.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/andoshoeki-mini.webp</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utopisme</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">médecin de province, critique radical de la société féodale et penseur d’une égalité naturelle.</t>
+        </is>
+      </c>
+      <c r="O247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P247" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1">
+        <v>1829</v>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1897</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1829 – 1897</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amane NISHI</t>
+        </is>
+      </c>
+      <c r="E248" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nishi_Amane"  title=" Wikipedia"&gt;Amane NISHI&lt;/a&gt; est l’un des principaux passeurs de la philosophie occidentale au Japon. Formé d’abord au confucianisme, il apprit le néerlandais puis fut envoyé de 1862 à 1865 à l’université de Leyde, aux Pays-Bas, où il étudia le droit et l’économie et découvrit le positivisme d’Auguste Comte et l’utilitarisme de John Stuart Mill.&lt;/p&gt; &lt;p&gt;De retour au Japon, il entreprit de faire entrer ces idées dans la langue japonaise, ce qui exigeait d’inventer un vocabulaire. On lui doit de nombreux termes encore en usage, formés à partir de caractères chinois : « philosophie » (&lt;em&gt;tetsugaku&lt;/em&gt;), « subjectif » et « objectif », « raison », « conscience », « induction » ou « déduction », mots ensuite adoptés en Chine et en Corée. Dans sa &lt;em&gt;Nouvelle théorie des cent enseignements unifiés&lt;/em&gt;, il présente la philosophie comme la science qui rassemble toutes les autres.&lt;/p&gt; &lt;p&gt;Membre de la Meirokusha, la « Société de l’an six de Meiji » fondée en 1873 avec Fukuzawa Yukichi et d’autres réformateurs, il fut aussi haut fonctionnaire au ministère de la Guerre, où il participa à la rédaction du &lt;em&gt;Rescrit impérial aux soldats&lt;/em&gt; de 1882. Dans ses &lt;em&gt;Trois trésors de la vie humaine&lt;/em&gt;, il adapte l’utilitarisme en faisant de la santé, du savoir et de la richesse les biens que la société doit promouvoir. Son œuvre marque la naissance de la philosophie universitaire au Japon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nishiamane-mini.webp</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; logique</t>
+        </is>
+      </c>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Utilitarisme</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">introducteur de la philosophie occidentale au Japon, inventeur du mot japonais « tetsugaku ».</t>
+        </is>
+      </c>
+      <c r="O248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P248" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A249" s="1">
+        <v>1835</v>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1901</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1835 – 1901</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yukichi FUKUZAWA</t>
+        </is>
+      </c>
+      <c r="E249" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fukuzawa_Yukichi"  title=" Wikipedia"&gt;Yukichi FUKUZAWA&lt;/a&gt; est le principal penseur des Lumières japonaises de l’ère Meiji. Issu d’une famille de samouraïs de rang inférieur, qui souffrit du système des statuts héréditaires, il apprit le néerlandais puis l’anglais, et participa en 1860 à la première ambassade japonaise aux États-Unis, puis en 1862 à une mission en Europe. Ses &lt;em&gt;Choses de l’Occident&lt;/em&gt; (&lt;em&gt;Seiyō jijō&lt;/em&gt;) firent découvrir aux Japonais les institutions, les écoles et les hôpitaux occidentaux.&lt;/p&gt; &lt;p&gt;Son &lt;em&gt;Encouragement à l’étude&lt;/em&gt; (&lt;em&gt;Gakumon no susume&lt;/em&gt;, 1872-1876), vendu à des centaines de milliers d’exemplaires, s’ouvre sur une phrase restée célèbre : « Le Ciel ne crée pas un homme au-dessus d’un autre homme, ni un homme au-dessous d’un autre homme. » Il y défend l’égalité des droits et l’« indépendance de l’individu » : seul un peuple de personnes libres, instruites et responsables peut former une nation indépendante. Dans son &lt;em&gt;Esquisse d’une théorie de la civilisation&lt;/em&gt; (1875), il voit dans l’esprit critique et scientifique, plus que dans les machines, le vrai moteur de la civilisation.&lt;/p&gt; &lt;p&gt;Il fonda en 1858 une école qui devint l’université Keiō, l’une des plus prestigieuses du Japon, ainsi qu’un grand quotidien. Défenseur de la dignité des femmes et de la monogamie, il soutint aussi, à la fin de sa vie, une politique de puissance face à la Chine et à la Corée, ce qui rend son héritage discuté. Son portrait a figuré pendant quarante ans sur le billet de 10 000 yens.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fukuzawa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fondateur de l’université Keiō, grand promoteur des Lumières et de l’indépendance individuelle au Japon de Meiji.</t>
+        </is>
+      </c>
+      <c r="O249" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P249" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A250" s="1">
+        <v>1863</v>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1913</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1863 – 1913</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kakuzō OKAKURA</t>
+        </is>
+      </c>
+      <c r="E250" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Okakura_Kakuz%C5%8D"  title=" Wikipedia"&gt;Kakuzō OKAKURA&lt;/a&gt; aussi appelé Okakura Tenshin, est l’un des grands défenseurs de l’art et de la culture d’Asie à l’époque Meiji. Élève et collaborateur de l’Américain Ernest Fenollosa, il recensa avec lui les trésors des temples japonais, menacés par l’occidentalisation, dirigea l’école des Beaux-Arts de Tōkyō, puis fonda avec ses élèves l’Institut des Beaux-Arts du Japon. Il devint ensuite conservateur de l’art asiatique au musée des Beaux-Arts de Boston.&lt;/p&gt; &lt;p&gt;Ses livres, écrits directement en anglais, voulaient faire comprendre l’Asie à l’Occident. &lt;em&gt;Les Idéaux de l’Orient&lt;/em&gt; (1903) s’ouvrent sur la formule « L’Asie est une », qui fut plus tard récupérée par le nationalisme japonais. &lt;em&gt;Le Livre du thé&lt;/em&gt; (1906), son œuvre la plus célèbre, fait de la cérémonie du thé une philosophie de la vie : le « théisme », inspiré du taoïsme et du zen, est un « culte de l’imparfait », une manière de trouver la beauté dans les choses simples et éphémères de l’existence quotidienne.&lt;/p&gt; &lt;p&gt;Pour Okakura, l’Occident moderne a gagné la puissance matérielle mais perdu le sens de l’harmonie et du vide, que l’art asiatique sait encore préserver : la valeur d’une pièce tient à l’espace vide entre ses murs, celle d’un vase au vide qu’il contient. Ami du poète indien Rabindranath Tagore, rencontré lors d’un séjour en Inde en 1902, il rêvait d’une renaissance commune des cultures d’Asie. Lu dans le monde entier, &lt;em&gt;Le Livre du thé&lt;/em&gt; reste l’un des textes les plus influents sur l’esthétique japonaise.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/okakura-mini.webp</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme ; Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien de l’art et auteur du Livre du thé, défenseur de l’esthétique asiatique.</t>
+        </is>
+      </c>
+      <c r="O250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P250" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A251" s="1">
+        <v>1870</v>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1966</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1870 – 1966</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daisetz Teitaro SUZUKI</t>
+        </is>
+      </c>
+      <c r="E251" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daisetz_Teitaro_Suzuki"  title=" Wikipedia"&gt;Daisetz Teitaro SUZUKI&lt;/a&gt; est l’homme qui a fait connaître le bouddhisme zen en Occident. Ami d’enfance de Kitarō Nishida, il pratiqua le zen au monastère d’Engaku-ji, à Kamakura, auprès du maître Shaku Sōen, dont il traduisit en anglais l’intervention au Parlement mondial des religions de Chicago en 1893. Parti en 1897 pour les États-Unis, il y vécut onze ans, traduisant des textes bouddhistes et taoïstes, avant d’enseigner au Japon, notamment à l’université Ōtani de Kyōto.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Essais sur le bouddhisme zen&lt;/em&gt; (1927-1934), écrits en anglais, il présente le zen non comme une doctrine mais comme une expérience directe, le &lt;em&gt;satori&lt;/em&gt;, éveil soudain qui fait voir le monde sans la médiation des concepts. Il insiste sur l’influence du zen sur toute la culture japonaise : la cérémonie du thé, les arts martiaux, le haïku et la peinture. Il étudia aussi le bouddhisme de la Terre pure et la spiritualité populaire japonaise, qu’il voyait comme une autre expression de la même intuition religieuse.&lt;/p&gt; &lt;p&gt;Après la guerre, il donna de nombreuses conférences aux États-Unis, notamment à l’université Columbia dans les années 1950, et ses livres eurent une grande influence sur des psychologues comme Carl Gustav Jung et Erich Fromm, des artistes comme John Cage et les écrivains de la Beat generation. On lui a reproché d’avoir présenté un zen idéalisé et d’avoir associé, avant la guerre, l’esprit du zen à l’éthique guerrière. Il mourut à Tōkyō à quatre-vingt-quinze ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dtsuzuki-mini.webp</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouddhologue et grand passeur du zen en Occident au XXe siècle.</t>
+        </is>
+      </c>
+      <c r="O251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P251" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A252" s="1">
+        <v>1885</v>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1962</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1885 – 1962</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hajime TANABE</t>
+        </is>
+      </c>
+      <c r="E252" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tanabe_Hajime"  title=" Wikipedia"&gt;Hajime TANABE&lt;/a&gt; est, avec Kitarō Nishida, l’un des deux fondateurs de l’école de Kyōto. Formé aux mathématiques et à la philosophie des sciences, il étudia en Allemagne au début des années 1920 auprès de Husserl, à Fribourg, où il rencontra le jeune Heidegger, puis succéda à Nishida à l’université impériale de Kyōto, tout en développant une pensée critique envers celle de son maître.&lt;/p&gt; &lt;p&gt;Contre Nishida, à qui il reproche une philosophie trop contemplative, Tanabe élabore une « logique de l’espèce » : entre l’individu et le genre humain universel, il place les communautés particulières, peuples et nations, que la philosophie doit selon lui penser comme telles. Cette théorie, développée dans les années 1930, servit à justifier l’État japonais en guerre, ce que Tanabe reconnut ensuite comme une faute.&lt;/p&gt; &lt;p&gt;À la fin de la guerre, il publia &lt;em&gt;La Philosophie comme métanoétique&lt;/em&gt; (1946), l’un des livres les plus singuliers du siècle : le philosophe, conscient de son impuissance et de sa responsabilité, doit passer par la « repentance » (&lt;em&gt;zange&lt;/em&gt;) et renoncer à la toute-puissance de la raison, pour s’en remettre à une « puissance autre », à la manière de la foi en Amida du bouddhisme de Shinran. Retiré dans les montagnes de Kita-Karuizawa, il consacra ses dernières années à une philosophie de la mort et au dialogue avec le christianisme et le marxisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tanabe-mini.webp</t>
+        </is>
+      </c>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École de Kyōto</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe de l’école de Kyōto, auteur d’une « philosophie comme métanoétique ».</t>
+        </is>
+      </c>
+      <c r="O252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P252" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A253" s="1">
+        <v>1886</v>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1971</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886 – 1971</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raichō HIRATSUKA</t>
+        </is>
+      </c>
+      <c r="E253" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raich%C5%8D_Hiratsuka"  title=" Wikipedia"&gt;Raichō HIRATSUKA&lt;/a&gt; est la grande pionnière du féminisme au Japon. Fille d’un haut fonctionnaire de Tōkyō, diplômée de l’université pour femmes du Japon, elle pratiqua le zen dans sa jeunesse et fit scandale en 1908 par une fugue suivie d’une tentative de double suicide avec l’écrivain Morita Sōhei, dont la presse fit ses gros titres.&lt;/p&gt; &lt;p&gt;En 1911, elle fonda la revue &lt;em&gt;Seitō&lt;/em&gt; (« Bas-bleu »), première revue littéraire entièrement faite par des femmes au Japon. Son manifeste d’ouverture est resté célèbre : « À l’origine, la femme était le soleil. Elle était une personne authentique. Aujourd’hui, la femme est la lune », qui ne brille que de la lumière d’un autre. Elle y appelle les femmes à retrouver leur « génie caché », par une libération intérieure autant que sociale, et la revue ouvrit des débats alors très audacieux sur la chasteté, l’avortement et la prostitution.&lt;/p&gt; &lt;p&gt;Influencée par la penseuse suédoise Ellen Key, elle défendit ensuite la protection de la maternité par l’État, ce qui l’opposa à la poétesse Yosano Akiko, partisane de l’indépendance économique des femmes. En 1920, elle fonda avec Ichikawa Fusae l’Association des femmes nouvelles, qui obtint en 1922 le droit pour les femmes d’assister à des réunions politiques. Elle vécut en union libre avec le peintre Okumura Hiroshi, refusant longtemps un mariage qui soumettait l’épouse à la loi familiale. Après la guerre, elle s’engagea dans le pacifisme et le mouvement contre les armes nucléaires.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hiratsuka-mini.webp</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Féminisme</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pionnière du féminisme japonais, fondatrice de la revue Seitō.</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P253" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A254" s="1">
+        <v>1888</v>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1941</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1888 – 1941</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shūzō KUKI</t>
+        </is>
+      </c>
+      <c r="E254" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kuki_Sh%C5%ABz%C5%8D"  title=" Wikipedia"&gt;Shūzō KUKI&lt;/a&gt; est l’un des philosophes japonais les plus cosmopolites de son temps. Fils du baron Kuki Ryūichi, haut fonctionnaire de Meiji, et d’une mère qui fut proche d’Okakura Kakuzō, il passa huit années en Europe dans les années 1920 : il étudia auprès de Rickert à Heidelberg, rencontra Bergson à Paris, où le jeune Jean-Paul Sartre lui donna des leçons de français, et suivit à Marbourg les cours de Heidegger. De retour au Japon, il enseigna à l’université impériale de Kyōto.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Structure de l’iki&lt;/em&gt; (1930), il analyse une notion clé de l’esthétique d’Edo, l’&lt;em&gt;iki&lt;/em&gt;, une élégance raffinée née dans les quartiers de plaisir : un mélange de séduction, de fierté et de détachement, qui garde toujours une distance. Kuki y applique la méthode de la phénoménologie et de l’herméneutique à une expérience proprement japonaise, et montre ce que les mots d’une culture révèlent de sa manière d’être au monde.&lt;/p&gt; &lt;p&gt;Son autre grand livre, &lt;em&gt;Le Problème de la contingence&lt;/em&gt; (1935), fait de la contingence, la rencontre de deux séries indépendantes, ce « qui aurait pu ne pas être », une question philosophique centrale : c’est dans l’étonnement devant la rencontre fortuite que l’existence humaine prend son sens. Heidegger évoqua plus tard leurs échanges dans son &lt;em&gt;Dialogue avec un Japonais&lt;/em&gt;. Kuki mourut en 1941, à cinquante-trois ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kuki-mini.webp</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École de Kyōto ; Phénoménologie</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe de l’iki et de la contingence, passeur entre Kyōto et la phénoménologie européenne.</t>
+        </is>
+      </c>
+      <c r="O254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P254" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A255" s="1">
+        <v>1889</v>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1960</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889 – 1960</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tetsurō WATSUJI</t>
+        </is>
+      </c>
+      <c r="E255" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Watsuji_Tetsur%C5%8D"  title=" Wikipedia"&gt;Tetsurō WATSUJI&lt;/a&gt; est l’un des grands philosophes japonais du XXe siècle, proche de l’école de Kyōto. D’abord attiré par Nietzsche et Kierkegaard, auxquels il consacra ses premiers livres, il se tourna vers l’étude de la culture japonaise ancienne, des temples de Nara au bouddhisme de Dōgen, avant d’enseigner l’éthique à l’université impériale de Kyōto, puis à celle de Tōkyō.&lt;/p&gt; &lt;p&gt;En 1927, lors d’un séjour en Allemagne, il lut &lt;em&gt;Être et Temps&lt;/em&gt; de Heidegger et lui reprocha d’avoir pensé l’existence humaine à partir du temps en négligeant l’espace. Dans &lt;em&gt;Fūdo&lt;/em&gt; (1935), traduit en français sous le titre &lt;em&gt;Fûdo, le milieu humain&lt;/em&gt;, il montre que l’être humain est façonné par son climat et son paysage : les cultures de la mousson, du désert et des prairies européennes donnent naissance à des manières différentes d’être au monde.&lt;/p&gt; &lt;p&gt;Son grand œuvre, l’&lt;em&gt;Éthique&lt;/em&gt; (1937-1949), part du mot japonais &lt;em&gt;ningen&lt;/em&gt;, « être humain », écrit avec les caractères « homme » et « entre » : l’humain n’est pas d’abord un individu isolé, mais un être de relations, et l’éthique est la science de cet « entre-deux ». La personne n’existe que dans un double mouvement, par lequel elle se distingue de la communauté puis y revient. Cette pensée de la relation, qui servit aussi à justifier l’ordre impérial, reste l’une des contributions majeures du Japon à la philosophie morale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/watsuji-mini.webp</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École de Kyōto</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe de l’éthique comme « entre-deux » humain et du milieu (fūdo).</t>
+        </is>
+      </c>
+      <c r="O255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P255" s="1">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -12756,14 +12756,33 @@
       <c r="D154" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="E154" s="10" t="s">
-        <v>1289</v>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_pessimisme" title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé en Mésopotamie qui met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître &lt;a href="http://www.aroumah.net/seminar/Dialogue%20of%20Pessimism.pdf"&gt;annonce tour à tour &lt;/a&gt;qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0aawol43UdU</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Dialogue of Pessimism (Full Audiobook)" par abitof_ane_rd</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dialoguedupessimisme-mini.webp</t>
+        </is>
       </c>
       <c r="J154" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K154" s="2" t="s">
-        <v>1290</v>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
       </c>
       <c r="L154" s="2" t="s">
         <v>53</v>
@@ -12788,8 +12807,25 @@
       <c r="D155" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="E155" s="10" t="s">
-        <v>1294</v>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AX9Hmh5qJ9U</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
+        </is>
       </c>
       <c r="J155" s="1" t="s">
         <v>51</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -11744,432 +11744,459 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L130" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="M130" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="O130" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P130" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1">
+        <v>1870</v>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1966</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1870 – 1966</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Daisetz Teitaro SUZUKI</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daisetz_Teitaro_Suzuki" title=" Wikipedia"&gt;Daisetz Teitaro SUZUKI&lt;/a&gt; est l’homme qui a fait connaître le bouddhisme zen en Occident. Ami d’enfance de Kitarō Nishida, il pratiqua le zen au monastère d’Engaku-ji, à Kamakura, auprès du maître Shaku Sōen, dont il traduisit en anglais l’intervention au Parlement mondial des religions de Chicago en 1893. Parti en 1897 pour les États-Unis, il y vécut onze ans, traduisant des textes bouddhistes et taoïstes, avant d’enseigner au Japon, notamment à l’université Ōtani de Kyōto.&lt;/p&gt; &lt;p&gt;Dans ses&lt;a href="https://www.youtube.com/watch?v=7S46x9NGGR8" title="DT Susuki par St Nederlands Boeddhistisch"&gt; &lt;em&gt;Essais sur le bouddhisme zen&lt;/em&gt;&lt;/a&gt; (1927-1934), écrits en anglais, il présente le zen non comme une doctrine mais comme une expérience directe, le &lt;em&gt;satori&lt;/em&gt;, éveil soudain qui fait voir le monde sans la médiation des concepts. Il insiste sur &lt;a href="https://www.nippon.com/fr/japan-topics/b07214/" title="Suzuki Daisetsu : le philosophe bouddhiste qui a répandu le zen dans le monde entier par nippon.com"&gt;l’influence du zen&lt;/a&gt; sur toute la culture japonaise : la cérémonie du thé, les arts martiaux, le haïku et la peinture. Il étudia aussi le bouddhisme de la Terre pure et la spiritualité populaire japonaise, qu’il voyait comme une autre expression de la même intuition religieuse.&lt;/p&gt; &lt;p&gt;Après la guerre, il donna de nombreuses conférences aux États-Unis, notamment à l’université Columbia dans les années 1950, et ses livres eurent une grande influence sur des psychologues comme Carl Gustav Jung et Erich Fromm, des artistes comme John Cage et les écrivains de la Beat generation. On lui a reproché d’avoir présenté un zen idéalisé et d’avoir associé, avant la guerre, l’esprit du zen à l’éthique guerrière. Il mourut à Tōkyō à quatre-vingt-quinze ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hkHZA9gaKHI</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Au-delà des Illusions : L'Essence du Bouddhisme selon Daisetz Teitaro Suzuki" par Life-learner</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dtsuzuki-mini.webp</t>
+        </is>
+      </c>
+      <c r="J130" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouddhologue et grand passeur du zen en Occident au XXe siècle.</t>
+        </is>
+      </c>
+      <c r="O130" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P130" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="n">
         <v>1872</v>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P131" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B132" s="1" t="n">
         <v>1949</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E132" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="G131" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="H132" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="J132" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="K132" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="L131" s="2" t="s">
+      <c r="L132" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="M131" s="2" t="s">
+      <c r="M132" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="O131" s="1" t="s">
+      <c r="O132" s="1" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="291.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="n">
-        <v>1877</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E132" s="20" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="M132" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="291.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="n">
         <v>1877</v>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="n">
+        <v>1877</v>
+      </c>
+      <c r="B134" s="1" t="n">
         <v>1938</v>
       </c>
-      <c r="C133" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="E133" s="13" t="s">
+      <c r="E134" s="13" t="s">
         <v>1123</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="G134" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H134" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="J133" s="1" t="s">
+      <c r="J134" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O133" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="n">
-        <v>1879</v>
-      </c>
-      <c r="B134" s="1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E134" s="13" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>206</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>602</v>
+        <v>1128</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>1136</v>
+        <v>1129</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="350.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
-        <v>1891</v>
+        <v>1879</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="E135" s="20" t="s">
-        <v>1139</v>
+        <v>1131</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>1132</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>1143</v>
+        <v>206</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>602</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="O135" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="P135" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="136" customFormat="false" ht="350.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>1986</v>
+        <v>1956</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>1147</v>
+        <v>1138</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>1139</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>96</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>641</v>
+        <v>80</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>1143</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="O136" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="137" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P136" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
-        <v>1906</v>
+        <v>1895</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>2001</v>
+        <v>1986</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E137" s="20" t="s">
-        <v>1154</v>
+        <v>1146</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>1147</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>1158</v>
+        <v>96</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>1159</v>
+        <v>397</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>1160</v>
+        <v>641</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P137" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1">
-        <v>1900</v>
-      </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1990</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1900 — 1990</t>
-        </is>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>1714</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>1166</v>
+        <v>1715</v>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Feng_Youlan" title=" Wikipedia"&gt;FENG Youlan&lt;/a&gt; est l’historien de la philosophie chinoise le plus lu au monde. Formé à l’université de Pékin puis à Columbia, où il fut l’élève de John Dewey, il enseigna à l’université Tsinghua et publia en 1931 et 1934 les deux volumes de son &lt;em&gt;Histoire de la philosophie chinoise&lt;/em&gt; qui, traduite en anglais par Derk Bodde, devint la référence internationale ; son &lt;em&gt;Précis d’histoire de la philosophie chinoise&lt;/em&gt; (1948) a été lu par des générations d’étudiants en Occident.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre le Japon, réfugié avec les universités chinoises dans le sud-ouest du pays, il élabora &lt;a href="https://maitron.fr/feng-youlan-%E9%A6%AE%E5%8F%8B%E8%98%AD/" title="FENG Joulan par Le Maitron"&gt;son propre système&lt;/a&gt;, le « nouveau néoconfucianisme », exposé en six livres, dont le &lt;em&gt;Nouveau traité du principe&lt;/em&gt;. Il y relit Zhu Xi à l’aide de la logique moderne : les principes sont des concepts formels, distincts des choses concrètes. Il distingue aussi quatre degrés de conscience chez l’homme, du niveau naturel, où l’on suit ses instincts, au niveau utilitaire, puis moral, et enfin au « niveau du Ciel et de la Terre », où l’on se sait partie de l’univers entier.&lt;/p&gt; &lt;p&gt;Resté en Chine après 1949, il renia publiquement ses travaux antérieurs et dut se soumettre aux campagnes politiques ; il participa même, pendant la Révolution culturelle, à la critique de Confucius, ce qui lui fut longtemps reproché. À la fin de sa vie, il entreprit une nouvelle &lt;em&gt;&lt;a href="https://www.persee.fr/doc/oroc_0754-5010_2005_num_27_27_1200" title="De l'écriture d'une « histoire de la philosophie chinoise » par persée"&gt;Histoire de la philosophie chinoise&lt;/a&gt;&lt;/em&gt; en sept volumes, achevée peu avant sa mort, où il revint plus librement à ses propres convictions.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVGyQLeHgSc</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Feng Youlan: Rediscovering Chinese Philosophy｜Philosopher Biography" par VIS PHILO.</t>
+        </is>
       </c>
       <c r="H138" s="2" t="s">
-        <v>1167</v>
+        <v>1717</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>582</v>
+        <v>267</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Zen ; École de Kyōto</t>
-        </is>
+        <v>247</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>1698</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>1168</v>
+        <v>1718</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="139" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P138" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>1972</v>
+        <v>2001</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1169</v>
+        <v>1152</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>1171</v>
+        <v>1153</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>1154</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1172</v>
+        <v>1155</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1173</v>
+        <v>1156</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1174</v>
+        <v>1157</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1000</v>
+        <v>1158</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>1175</v>
+        <v>1159</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>1160</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>1176</v>
+        <v>1161</v>
       </c>
       <c r="O139" s="1" t="s">
         <v>660</v>
@@ -12178,130 +12205,133 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="n">
+    <row r="140" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1">
+        <v>1900</v>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900 — 1990</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen ; École de Kyōto</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>1972</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="P141" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="n">
         <v>1913</v>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B142" s="1" t="n">
         <v>2008</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D142" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="E140" s="22" t="s">
+      <c r="E142" s="22" t="s">
         <v>1179</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G142" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="H140" s="2" t="s">
+      <c r="H142" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="J140" s="1" t="s">
+      <c r="J142" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="K140" s="2" t="s">
+      <c r="K142" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="L140" s="2" t="s">
+      <c r="L142" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="M140" s="2" t="s">
+      <c r="M142" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="O140" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P140" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="54.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="n">
-        <v>1917</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="J141" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="K141" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="L141" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="M141" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="N141" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="O141" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1" t="n">
-        <v>1923</v>
-      </c>
-      <c r="B142" s="1" t="n">
-        <v>1986</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E142" s="22" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="J142" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="M142" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="O142" s="1" t="s">
         <v>660</v>
@@ -12310,77 +12340,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="54.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B143" s="1" t="n">
-        <v>1961</v>
+        <v>1917</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1185</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1202</v>
+        <v>1186</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E143" s="22" t="s">
-        <v>1204</v>
+        <v>1187</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>1188</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1205</v>
+        <v>1189</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>1206</v>
+        <v>1190</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1207</v>
+        <v>1191</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>1183</v>
+        <v>874</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>80</v>
+        <v>1192</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>1208</v>
+        <v>1193</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>1209</v>
+        <v>1194</v>
+      </c>
+      <c r="N143" s="1" t="s">
+        <v>513</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P143" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="n">
-        <v>1931</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>1210</v>
+        <v>1923</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>1986</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1211</v>
+        <v>1195</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>1213</v>
+        <v>1196</v>
+      </c>
+      <c r="E144" s="22" t="s">
+        <v>1197</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1214</v>
+        <v>1198</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>1215</v>
+        <v>1199</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>1216</v>
+        <v>1200</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1217</v>
+        <v>1158</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>848</v>
@@ -12389,48 +12419,51 @@
         <v>1061</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>1218</v>
+        <v>1201</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="145" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P144" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="n">
-        <v>1931</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>1219</v>
+        <v>1925</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>1961</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1220</v>
+        <v>1202</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>1222</v>
+        <v>1203</v>
+      </c>
+      <c r="E145" s="22" t="s">
+        <v>1204</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1223</v>
+        <v>1205</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>1224</v>
+        <v>1206</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>1225</v>
+        <v>1207</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>1000</v>
+        <v>1183</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>1001</v>
+        <v>80</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>952</v>
+        <v>1208</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>1226</v>
+        <v>1209</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>660</v>
@@ -12439,545 +12472,595 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1227</v>
+        <v>1731</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1228</v>
+        <v>1732</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>1232</v>
+        <v>1733</v>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Li_Zehou" title=" Wikipedia"&gt;LI Zehou&lt;/a&gt; est l’un des philosophes chinois les plus influents de la seconde moitié du XXe siècle. Originaire du Hunan, diplômé de philosophie de l’université de Pékin en 1954, il se fit connaître dès les années 1950 dans les grands débats sur l’esthétique, puis devint, dans les années 1980, le maître à penser de toute une génération d’étudiants chinois.&lt;/p&gt; &lt;p&gt;Lecteur de Kant et de Marx, il soutient que les formes de la sensibilité et de la raison ne sont pas données d’avance, mais se sont formées au cours de l’histoire humaine, par la fabrication et l’usage des outils : c’est ce qu’il appelle la « sédimentation ». Le beau est ainsi « la forme de la liberté »,&lt;a href="https://www.youtube.com/watch?v=JEfuhVCN-fU" title="Hidden Truths About Confucius and Li Zehou's Philosophical par Vis Philo"&gt; l’humanisation de la nature&lt;/a&gt; par le travail collectif. Son livre &lt;em&gt;Le Chemin de la beauté&lt;/em&gt; (1981), qui parcourt l’histoire de l’art chinois, fut un immense succès. Il propose aussi de comprendre la culture chinoise comme une « culture de la joie » et du sentiment, plutôt que de la faute et du salut.&lt;/p&gt; &lt;p&gt;Après les événements de Tiananmen en 1989, ses ouvrages furent critiqués et il s’installa en 1992 aux États-Unis, où il enseigna dans plusieurs universités ; il mourut en 2021 à Boulder, dans le Colorado.&lt;a href="https://www.loyolaparis.fr/wp-content/uploads/2022/03/103-coin-des-penseurs-mars-2022.pdf" title="En mémoire à Li Zehou par loyolaparis"&gt; Dans ses derniers livres&lt;/a&gt;, il développe une « ontologie du sentiment » qui fait des émotions, cultivées par les rites et la musique, le fondement de la vie morale. Il est l’un des rares philosophes chinois contemporains à figurer dans la grande anthologie Norton de théorie et de critique littéraires.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p4w9h3oS5Hc</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"What Confucius and Li Zehou Can Teach Us About the True Meaning of Life?" par VIS PHILO.</t>
+        </is>
       </c>
       <c r="H146" s="2" t="s">
-        <v>1233</v>
+        <v>1735</v>
       </c>
       <c r="J146" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P146" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J147" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="K146" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L146" s="2" t="s">
+      <c r="K147" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="L147" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="M146" s="2" t="s">
-        <v>1234</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E147" s="20" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="J147" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="L147" s="2" t="s">
-        <v>952</v>
-      </c>
       <c r="M147" s="2" t="s">
-        <v>1242</v>
-      </c>
-      <c r="N147" s="1" t="s">
-        <v>72</v>
+        <v>1218</v>
       </c>
       <c r="O147" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="n">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1244</v>
+        <v>1220</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>1246</v>
+        <v>1222</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1247</v>
+        <v>1223</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>1248</v>
+        <v>1224</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>1192</v>
+        <v>1001</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>1251</v>
+        <v>1226</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+      <c r="P148" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="n">
-        <v>1936</v>
-      </c>
-      <c r="B149" s="1" t="n">
-        <v>2005</v>
+        <v>1934</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>1227</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>1254</v>
+        <v>1229</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>1230</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1258</v>
+        <v>1217</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>1043</v>
+        <v>80</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>1259</v>
+        <v>1061</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>1260</v>
+        <v>1234</v>
       </c>
       <c r="O149" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="n">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1261</v>
+        <v>1227</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1262</v>
+        <v>1235</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>1264</v>
+        <v>1236</v>
+      </c>
+      <c r="E150" s="20" t="s">
+        <v>1237</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1265</v>
+        <v>1238</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>1266</v>
+        <v>1239</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>1267</v>
+        <v>1240</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1268</v>
+        <v>1241</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>1192</v>
+        <v>1001</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>1061</v>
+        <v>952</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>1269</v>
+        <v>1242</v>
+      </c>
+      <c r="N150" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="n">
-        <v>1942</v>
+        <v>1935</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1270</v>
+        <v>1243</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1271</v>
+        <v>1244</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>1273</v>
+        <v>1245</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>1246</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1274</v>
+        <v>1247</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1275</v>
+        <v>1248</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1276</v>
+        <v>1249</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1277</v>
+        <v>1250</v>
       </c>
       <c r="K151" s="2" t="s">
         <v>1192</v>
       </c>
       <c r="L151" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M151" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fatima_Mernissi" title=" Wikipedia"&gt;Fatima MERNISSI&lt;/a&gt; est une sociologue et écrivaine marocaine qui grandit dans une grande maison familiale où les femmes vivent à l'écart, enfance qu'elle racontera dans &lt;em&gt;Rêves de femmes&lt;/em&gt; (1994). Appartenant à la première génération de Marocaines scolarisées, elle étudie à Rabat, à Paris, puis aux États-Unis, où elle obtient un doctorat, avant d'enseigner la sociologie à l'université Mohammed V de Rabat.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;Sexe, idéologie, islam&lt;/em&gt; (1975), étudie la&lt;a href="https://scienceetbiencommun.pressbooks.pub/citoyennes/chapter/__unknown__/" title="Fatima Mernissi, sociologue, écrivaine et féministe marocaine par esbc"&gt; place faite aux femmes&lt;/a&gt; dans la société marocaine. Mais c'est &lt;em&gt;Le Harem politique&lt;/em&gt; (1987) qui la rend célèbre, et qui fut interdit dans son pays. Traduite dans de nombreuses langues, son œuvre a ouvert la voie à ce que l'on a appelé le féminisme islamique.&lt;/p&gt; &lt;p&gt;Elle y mène une &lt;a href="https://www.youtube.com/watch?v=Qb6iaPFs-ZI" title="Une vie : Fatima Mernissi par Brut"&gt;enquête d'historienne&lt;/a&gt; sur les paroles attribuées au Prophète qui servent à écarter les femmes de la vie publique. En utilisant les règles mêmes de la science religieuse traditionnelle, elle examine qui les a rapportées, à quel moment et dans quel intérêt, et montre leur fragilité. Pour elle, le message du Prophète était favorable à l'égalité ; ce sont les hommes de pouvoir qui, après lui, ont imposé une lecture hostile aux femmes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Sultanes oubliées&lt;/em&gt;, elle rappelle les femmes qui ont gouverné en terre d'islam. Elle a aussi retourné le regard vers l'Europe : &lt;em&gt;Le Harem et l'Occident&lt;/em&gt; montre que les femmes occidentales sont enfermées, elles, par la tyrannie de l'image et de la minceur. Elle a animé au Maroc de nombreux ateliers d'écriture et reçu en 2003 le prix Prince des Asturies. L'année suivante, le prix Érasme lui fut décerné en même temps qu'au philosophe iranien Abdolkarim Soroush.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UQab1UXbrM4</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Fatima Mernissi : Islam et Féminisme" par ​L'Art de Comprendre</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fatimamernissi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="P153" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J155" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L155" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="M151" s="2" t="s">
+      <c r="M155" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="O151" s="1" t="s">
+      <c r="O155" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="P151" s="1" t="n">
+      <c r="P155" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="n">
+    <row r="156" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="n">
         <v>1943</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C156" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D156" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="E152" s="10" t="s">
+      <c r="E156" s="10" t="s">
         <v>1282</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="F156" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="G156" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="H152" s="2" t="s">
+      <c r="H156" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="J152" s="1" t="s">
+      <c r="J156" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K152" s="2" t="s">
+      <c r="K156" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L152" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="M152" s="2" t="s">
-        <v>1286</v>
-      </c>
-      <c r="O152" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
-      <c r="G153" s="1"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
-      <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
-      <c r="M153" s="1"/>
-    </row>
-    <row r="154" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="B154" s="1" t="n">
-        <v>-900</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>1288</v>
-      </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_pessimisme" title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé en Mésopotamie qui met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître &lt;a href="http://www.aroumah.net/seminar/Dialogue%20of%20Pessimism.pdf"&gt;annonce tour à tour &lt;/a&gt;qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0aawol43UdU</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The Dialogue of Pessimism (Full Audiobook)" par abitof_ane_rd</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dialoguedupessimisme-mini.webp</t>
-        </is>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; ethique</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M154" s="2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B155" s="1" t="n">
-        <v>-640</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E155" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AX9Hmh5qJ9U</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
-        </is>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L155" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M155" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="O155" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="n">
-        <v>-550</v>
-      </c>
-      <c r="B156" s="1" t="n">
-        <v>-400</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="L156" s="2" t="s">
         <v>398</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>1299</v>
-      </c>
-      <c r="N156" s="1" t="s">
-        <v>400</v>
+        <v>1286</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P156" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="n">
-        <v>-340</v>
-      </c>
-      <c r="B157" s="1" t="n">
-        <v>-270</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>1302</v>
-      </c>
-      <c r="J157" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
+      <c r="M157" s="1"/>
+    </row>
+    <row r="158" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>-900</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_pessimisme" title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé en Mésopotamie qui met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître &lt;a href="http://www.aroumah.net/seminar/Dialogue%20of%20Pessimism.pdf"&gt;annonce tour à tour &lt;/a&gt;qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0aawol43UdU</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Dialogue of Pessimism (Full Audiobook)" par abitof_ane_rd</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dialoguedupessimisme-mini.webp</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K157" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="L157" s="2" t="s">
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M157" s="2" t="s">
-        <v>1304</v>
-      </c>
-      <c r="O157" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="n">
-        <v>-250</v>
-      </c>
-      <c r="B158" s="1" t="n">
-        <v>-220</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>1307</v>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="K158" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L158" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="M158" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="N158" s="1" t="s">
-        <v>400</v>
+        <v>1291</v>
       </c>
       <c r="O158" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P158" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="159" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
-        <v>-250</v>
+        <v>-700</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>-100</v>
+        <v>-640</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1309</v>
+        <v>1292</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1310</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>1311</v>
+        <v>1293</v>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AX9Hmh5qJ9U</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
+        </is>
       </c>
       <c r="J159" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="K159" s="2" t="s">
         <v>36</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1312</v>
+        <v>1295</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>29</v>
@@ -12985,276 +13068,279 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
-        <v>154</v>
+        <v>-550</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>222</v>
+        <v>-400</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1313</v>
+        <v>1296</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1314</v>
+        <v>1297</v>
       </c>
       <c r="E160" s="10" t="s">
-        <v>1315</v>
+        <v>1298</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1316</v>
+        <v>396</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>1317</v>
+        <v>398</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1318</v>
+        <v>1299</v>
+      </c>
+      <c r="N160" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O160" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="P160" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
-        <v>45</v>
+        <v>-340</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>117</v>
+        <v>-270</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1319</v>
+        <v>1300</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1320</v>
+        <v>1301</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>1321</v>
+        <v>1302</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>267</v>
+        <v>51</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>62</v>
+        <v>1303</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>296</v>
+        <v>53</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="N161" s="1" t="s">
-        <v>72</v>
+        <v>1304</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P161" s="1" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
-        <v>1130</v>
+        <v>-250</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>1160</v>
+        <v>-220</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1323</v>
+        <v>1305</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>427</v>
+        <v>107</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>641</v>
+        <v>398</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1326</v>
+        <v>1308</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>72</v>
+        <v>400</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
+      </c>
+      <c r="P162" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
-        <v>832</v>
+        <v>-250</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>932</v>
+        <v>-100</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1327</v>
+        <v>1309</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1328</v>
+        <v>1310</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>1329</v>
+        <v>1311</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>396</v>
+        <v>25</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>346</v>
+        <v>36</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>1330</v>
+        <v>27</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="N163" s="1" t="s">
-        <v>400</v>
+        <v>1312</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>401</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
-        <v>853</v>
+        <v>154</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>944</v>
+        <v>222</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1332</v>
+        <v>1313</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1333</v>
+        <v>1314</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>1334</v>
+        <v>1315</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>147</v>
+        <v>1316</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>401</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
-        <v>874</v>
+        <v>45</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>936</v>
+        <v>117</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>545</v>
+        <v>267</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>1340</v>
+        <v>296</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1341</v>
+        <v>1322</v>
+      </c>
+      <c r="N165" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>401</v>
+        <v>271</v>
       </c>
       <c r="P165" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
-        <v>882</v>
+        <v>1130</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>942</v>
+        <v>1160</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1342</v>
+        <v>1323</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1343</v>
+        <v>1324</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>1344</v>
+        <v>1325</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>396</v>
+        <v>96</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>1345</v>
+        <v>641</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1346</v>
+        <v>1326</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>400</v>
+        <v>72</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="P166" s="1" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1347</v>
+        <v>1327</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1348</v>
+        <v>1328</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>1349</v>
+        <v>1329</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>138</v>
+        <v>346</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1350</v>
+        <v>1330</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1351</v>
+        <v>1331</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>401</v>
@@ -13262,98 +13348,98 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
-        <v>994</v>
+        <v>853</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>1064</v>
+        <v>944</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1352</v>
+        <v>1332</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1353</v>
+        <v>1333</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>1354</v>
+        <v>1334</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>545</v>
+        <v>147</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>1355</v>
+        <v>138</v>
       </c>
       <c r="L168" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1356</v>
+        <v>1336</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P168" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
-        <v>1004</v>
+        <v>874</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>1088</v>
+        <v>936</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1357</v>
+        <v>1337</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1358</v>
+        <v>1338</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>1359</v>
+        <v>1339</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>511</v>
+        <v>1340</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P169" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
-        <v>1021</v>
+        <v>882</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>1058</v>
+        <v>942</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1362</v>
+        <v>1343</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>1363</v>
+        <v>1344</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>1364</v>
+        <v>206</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1330</v>
+        <v>1345</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
       <c r="N170" s="1" t="s">
         <v>400</v>
@@ -13367,34 +13453,31 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
-        <v>1050</v>
+        <v>883</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>1120</v>
+        <v>931</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1366</v>
+        <v>1347</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>1368</v>
+        <v>1349</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="N171" s="1" t="s">
-        <v>400</v>
+        <v>1351</v>
       </c>
       <c r="O171" s="1" t="s">
         <v>401</v>
@@ -13402,34 +13485,31 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
-        <v>1075</v>
+        <v>994</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>1141</v>
+        <v>1064</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1371</v>
+        <v>1352</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1372</v>
+        <v>1353</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>1373</v>
+        <v>1354</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>742</v>
+        <v>1355</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1374</v>
+        <v>1335</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1375</v>
-      </c>
-      <c r="N172" s="1" t="s">
-        <v>400</v>
+        <v>1356</v>
       </c>
       <c r="O172" s="1" t="s">
         <v>401</v>
@@ -13440,34 +13520,31 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
-        <v>1092</v>
+        <v>1004</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>1167</v>
+        <v>1088</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1376</v>
+        <v>1357</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1377</v>
+        <v>1358</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>1378</v>
+        <v>1359</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1330</v>
+        <v>511</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="N173" s="1" t="s">
-        <v>400</v>
+        <v>1360</v>
       </c>
       <c r="O173" s="1" t="s">
         <v>401</v>
@@ -13475,31 +13552,31 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
-        <v>1110</v>
+        <v>1021</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>1180</v>
+        <v>1058</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1380</v>
+        <v>1361</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1381</v>
+        <v>1362</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1382</v>
+        <v>1363</v>
       </c>
       <c r="J174" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>206</v>
+        <v>1364</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1383</v>
+        <v>1330</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1384</v>
+        <v>1365</v>
       </c>
       <c r="N174" s="1" t="s">
         <v>400</v>
@@ -13507,34 +13584,40 @@
       <c r="O174" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P174" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
-        <v>1150</v>
+        <v>1050</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>1210</v>
+        <v>1120</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1385</v>
+        <v>1366</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1386</v>
+        <v>1367</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>1387</v>
+        <v>1368</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>1388</v>
+        <v>397</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1340</v>
+        <v>1369</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1389</v>
+        <v>1370</v>
+      </c>
+      <c r="N175" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O175" s="1" t="s">
         <v>401</v>
@@ -13542,104 +13625,107 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
-        <v>1194</v>
+        <v>1075</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>1270</v>
+        <v>1141</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1391</v>
+        <v>1372</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>1392</v>
+        <v>1373</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>791</v>
+        <v>742</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1393</v>
+        <v>1375</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>1394</v>
+        <v>400</v>
       </c>
       <c r="O176" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P176" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
-        <v>1263</v>
+        <v>1092</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>1328</v>
+        <v>1167</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1395</v>
+        <v>1376</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1396</v>
+        <v>1377</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1397</v>
+        <v>1378</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>1398</v>
+        <v>546</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1399</v>
+        <v>1330</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1400</v>
+        <v>1379</v>
+      </c>
+      <c r="N177" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O177" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P177" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
-        <v>1340</v>
+        <v>1110</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>1411</v>
+        <v>1180</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1401</v>
+        <v>1380</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1402</v>
+        <v>1381</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1374</v>
+        <v>1383</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1404</v>
+        <v>1384</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>1394</v>
+        <v>400</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>401</v>
@@ -13647,34 +13733,31 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
-        <v>1380</v>
+        <v>1150</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>1444</v>
+        <v>1210</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1405</v>
+        <v>1385</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1406</v>
+        <v>1386</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>1407</v>
+        <v>1387</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>1408</v>
+        <v>1388</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1374</v>
+        <v>1340</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="N179" s="1" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="O179" s="1" t="s">
         <v>401</v>
@@ -13682,31 +13765,31 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
-        <v>1437</v>
+        <v>1194</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>1508</v>
+        <v>1270</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1410</v>
+        <v>1390</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1411</v>
+        <v>1391</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>1412</v>
+        <v>1392</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>1043</v>
+        <v>791</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>1413</v>
+        <v>1369</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1414</v>
+        <v>1393</v>
       </c>
       <c r="N180" s="1" t="s">
         <v>1394</v>
@@ -13717,133 +13800,139 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
-        <v>1561</v>
+        <v>1263</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>1631</v>
+        <v>1328</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1415</v>
+        <v>1395</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1416</v>
+        <v>1396</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1417</v>
+        <v>1397</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>206</v>
+        <v>1398</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>775</v>
+        <v>1399</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1418</v>
+        <v>1400</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P181" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
-        <v>1801</v>
+        <v>1340</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>1873</v>
+        <v>1411</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1419</v>
+        <v>1401</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1420</v>
+        <v>1402</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>304</v>
+        <v>231</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1422</v>
+        <v>1374</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1423</v>
+        <v>1404</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O182" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P182" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
-        <v>1849</v>
+        <v>1380</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>1905</v>
+        <v>1444</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1424</v>
+        <v>1405</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1425</v>
+        <v>1406</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>1426</v>
+        <v>1407</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K183" s="2" t="s">
         <v>1408</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>1427</v>
+        <v>1374</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1428</v>
+        <v>1409</v>
+      </c>
+      <c r="N183" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O183" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P183" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
-        <v>1888</v>
+        <v>1437</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>1966</v>
+        <v>1508</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1429</v>
+        <v>1410</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1430</v>
+        <v>1411</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>1431</v>
+        <v>1412</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>304</v>
+        <v>1043</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1422</v>
+        <v>1413</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1432</v>
+        <v>1414</v>
+      </c>
+      <c r="N184" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>401</v>
@@ -13851,34 +13940,31 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
-        <v>1905</v>
+        <v>1561</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>1973</v>
+        <v>1631</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>1435</v>
+        <v>1417</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>1436</v>
+        <v>147</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1259</v>
+        <v>775</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="N185" s="1" t="s">
-        <v>660</v>
+        <v>1418</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>401</v>
@@ -13886,107 +13972,101 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
-        <v>1928</v>
+        <v>1801</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>2010</v>
+        <v>1873</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1438</v>
+        <v>1419</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1439</v>
+        <v>1420</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>1440</v>
+        <v>1421</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>1436</v>
+        <v>25</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>26</v>
+        <v>304</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1441</v>
+        <v>1422</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="N186" s="1" t="s">
-        <v>513</v>
+        <v>1423</v>
       </c>
       <c r="O186" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P186" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
-        <v>1933</v>
+        <v>1849</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>1977</v>
+        <v>1905</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1444</v>
+        <v>1425</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>1043</v>
+        <v>1408</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1446</v>
+        <v>1427</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="N187" s="1" t="s">
-        <v>660</v>
+        <v>1428</v>
       </c>
       <c r="O187" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P187" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
-        <v>1935</v>
+        <v>1888</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>2021</v>
+        <v>1966</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1449</v>
+        <v>1430</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>1450</v>
+        <v>1431</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>1043</v>
+        <v>304</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>1451</v>
+        <v>1422</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>401</v>
@@ -13994,31 +14074,31 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
-        <v>1938</v>
+        <v>1905</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>2009</v>
+        <v>1973</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1453</v>
+        <v>1433</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1454</v>
+        <v>1434</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>1455</v>
+        <v>1435</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1250</v>
+        <v>1436</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>1456</v>
+        <v>304</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1457</v>
+        <v>1259</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1458</v>
+        <v>1437</v>
       </c>
       <c r="N189" s="1" t="s">
         <v>660</v>
@@ -14029,180 +14109,177 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
-        <v>1940</v>
+        <v>1928</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1459</v>
+        <v>1438</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1460</v>
+        <v>1439</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>1461</v>
+        <v>1440</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1250</v>
+        <v>1436</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>1043</v>
+        <v>26</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1462</v>
+        <v>1441</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1463</v>
+        <v>1442</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>72</v>
+        <v>513</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P190" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
-        <v>613</v>
+        <v>1933</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>696</v>
+        <v>1977</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1464</v>
+        <v>1443</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>1466</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>1467</v>
+        <v>1445</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>916</v>
+        <v>147</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>231</v>
+        <v>1043</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>444</v>
+        <v>1446</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1468</v>
+        <v>1447</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O191" s="1" t="s">
-        <v>271</v>
+        <v>401</v>
+      </c>
+      <c r="P191" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
-        <v>617</v>
+        <v>1935</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>686</v>
+        <v>2021</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1469</v>
+        <v>1448</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>1471</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>1472</v>
+        <v>1450</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>916</v>
+        <v>25</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>206</v>
+        <v>1043</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>444</v>
+        <v>1451</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1473</v>
+        <v>1452</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P192" s="1" t="n">
-        <v>3</v>
+        <v>401</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
-        <v>625</v>
+        <v>1938</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>702</v>
+        <v>2009</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1474</v>
+        <v>1453</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1475</v>
+        <v>1454</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>1476</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>1477</v>
+        <v>1455</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>916</v>
+        <v>1250</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>206</v>
+        <v>1456</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>444</v>
+        <v>1457</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>1478</v>
+        <v>1458</v>
+      </c>
+      <c r="N193" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O193" s="1" t="s">
-        <v>271</v>
+        <v>401</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="n">
-        <v>857</v>
+        <v>613</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>910</v>
+        <v>696</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1479</v>
+        <v>1464</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1480</v>
+        <v>1465</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>1481</v>
+        <v>1466</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>1482</v>
+        <v>1467</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>397</v>
+        <v>231</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>917</v>
+        <v>444</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>1483</v>
+        <v>1468</v>
       </c>
       <c r="O194" s="1" t="s">
         <v>271</v>
@@ -14210,69 +14287,72 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="n">
-        <v>1055</v>
+        <v>617</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>1101</v>
+        <v>686</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1484</v>
+        <v>1469</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1485</v>
+        <v>1470</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>1486</v>
+        <v>1471</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>1487</v>
+        <v>1472</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="L195" s="2" t="s">
         <v>444</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>1488</v>
+        <v>1473</v>
       </c>
       <c r="O195" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P195" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
-        <v>1158</v>
+        <v>625</v>
       </c>
       <c r="B196" s="1" t="n">
-        <v>1210</v>
+        <v>702</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1489</v>
+        <v>1474</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1490</v>
+        <v>1475</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>1491</v>
+        <v>1476</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>1492</v>
+        <v>1477</v>
       </c>
       <c r="J196" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>799</v>
+        <v>444</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>1493</v>
+        <v>1478</v>
       </c>
       <c r="O196" s="1" t="s">
         <v>271</v>
@@ -14280,110 +14360,104 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="n">
-        <v>1337</v>
+        <v>857</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>1392</v>
+        <v>910</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1494</v>
+        <v>1479</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1495</v>
+        <v>1480</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>1496</v>
+        <v>1481</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>1497</v>
+        <v>1482</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>62</v>
+        <v>397</v>
       </c>
       <c r="L197" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>1498</v>
+        <v>1483</v>
       </c>
       <c r="O197" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P197" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="n">
-        <v>1342</v>
+        <v>1055</v>
       </c>
       <c r="B198" s="1" t="n">
-        <v>1398</v>
+        <v>1101</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1499</v>
+        <v>1484</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1500</v>
+        <v>1485</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>1501</v>
+        <v>1486</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1502</v>
+        <v>1487</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>80</v>
+        <v>546</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>917</v>
+        <v>444</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>1503</v>
+        <v>1488</v>
       </c>
       <c r="O198" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P198" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
-        <v>1376</v>
+        <v>1158</v>
       </c>
       <c r="B199" s="1" t="n">
-        <v>1433</v>
+        <v>1210</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1504</v>
+        <v>1489</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1505</v>
+        <v>1490</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>1506</v>
+        <v>1491</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1507</v>
+        <v>1492</v>
       </c>
       <c r="J199" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>427</v>
+        <v>546</v>
       </c>
       <c r="L199" s="2" t="s">
         <v>799</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>1508</v>
+        <v>1493</v>
       </c>
       <c r="O199" s="1" t="s">
         <v>271</v>
@@ -14391,104 +14465,110 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
-        <v>1482</v>
+        <v>1337</v>
       </c>
       <c r="B200" s="1" t="n">
-        <v>1519</v>
+        <v>1392</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1509</v>
+        <v>1494</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1510</v>
+        <v>1495</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>1511</v>
+        <v>1496</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1512</v>
+        <v>1497</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="L200" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>1513</v>
+        <v>1498</v>
       </c>
       <c r="O200" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P200" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
-        <v>1489</v>
+        <v>1342</v>
       </c>
       <c r="B201" s="1" t="n">
-        <v>1546</v>
+        <v>1398</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1514</v>
+        <v>1499</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1515</v>
+        <v>1500</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>1516</v>
+        <v>1501</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>1517</v>
+        <v>1502</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="L201" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>1518</v>
+        <v>1503</v>
       </c>
       <c r="O201" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P201" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="n">
-        <v>1501</v>
+        <v>1376</v>
       </c>
       <c r="B202" s="1" t="n">
-        <v>1572</v>
+        <v>1433</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1519</v>
+        <v>1504</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1520</v>
+        <v>1505</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>1521</v>
+        <v>1506</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>1522</v>
+        <v>1507</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>62</v>
+        <v>427</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="M202" s="2" t="s">
-        <v>1523</v>
+        <v>1508</v>
       </c>
       <c r="O202" s="1" t="s">
         <v>271</v>
@@ -14496,34 +14576,34 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="n">
-        <v>1520</v>
+        <v>1482</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>1604</v>
+        <v>1519</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>1524</v>
+        <v>1509</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1525</v>
+        <v>1510</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>1527</v>
+        <v>1512</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>799</v>
+        <v>917</v>
       </c>
       <c r="M203" s="2" t="s">
-        <v>1528</v>
+        <v>1513</v>
       </c>
       <c r="O203" s="1" t="s">
         <v>271</v>
@@ -14531,34 +14611,34 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="n">
-        <v>1527</v>
+        <v>1489</v>
       </c>
       <c r="B204" s="1" t="n">
-        <v>1572</v>
+        <v>1546</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1529</v>
+        <v>1514</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1530</v>
+        <v>1515</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>1531</v>
+        <v>1516</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>1532</v>
+        <v>1517</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K204" s="2" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="L204" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>1533</v>
+        <v>1518</v>
       </c>
       <c r="O204" s="1" t="s">
         <v>271</v>
@@ -14566,34 +14646,34 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="n">
-        <v>1535</v>
+        <v>1501</v>
       </c>
       <c r="B205" s="1" t="n">
-        <v>1598</v>
+        <v>1572</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>1534</v>
+        <v>1519</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1535</v>
+        <v>1520</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>1536</v>
+        <v>1521</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>1537</v>
+        <v>1522</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>257</v>
+        <v>62</v>
       </c>
       <c r="L205" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M205" s="2" t="s">
-        <v>1538</v>
+        <v>1523</v>
       </c>
       <c r="O205" s="1" t="s">
         <v>271</v>
@@ -14601,110 +14681,104 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="n">
-        <v>1536</v>
+        <v>1520</v>
       </c>
       <c r="B206" s="1" t="n">
-        <v>1584</v>
+        <v>1604</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1539</v>
+        <v>1524</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>1540</v>
+        <v>1525</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>1541</v>
+        <v>1526</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>1542</v>
+        <v>1527</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>268</v>
+        <v>427</v>
       </c>
       <c r="L206" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="M206" s="2" t="s">
-        <v>1543</v>
+        <v>1528</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P206" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="n">
-        <v>1607</v>
+        <v>1527</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>1689</v>
+        <v>1572</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1544</v>
+        <v>1529</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>1545</v>
+        <v>1530</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>1546</v>
+        <v>1531</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>1547</v>
+        <v>1532</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="L207" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M207" s="2" t="s">
-        <v>1548</v>
+        <v>1533</v>
       </c>
       <c r="O207" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P207" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="n">
-        <v>1622</v>
+        <v>1535</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>1673</v>
+        <v>1598</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1549</v>
+        <v>1534</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>1550</v>
+        <v>1535</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>1551</v>
+        <v>1536</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>1552</v>
+        <v>1537</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
       <c r="M208" s="2" t="s">
-        <v>1553</v>
+        <v>1538</v>
       </c>
       <c r="O208" s="1" t="s">
         <v>271</v>
@@ -14712,107 +14786,110 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="n">
-        <v>1649</v>
+        <v>1536</v>
       </c>
       <c r="B209" s="1" t="n">
-        <v>1736</v>
+        <v>1584</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1554</v>
+        <v>1539</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1555</v>
+        <v>1540</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>1556</v>
+        <v>1541</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>1557</v>
+        <v>1542</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>951</v>
+        <v>268</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>691</v>
+        <v>917</v>
       </c>
       <c r="M209" s="2" t="s">
-        <v>1558</v>
+        <v>1543</v>
       </c>
       <c r="O209" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P209" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="n">
-        <v>1682</v>
+        <v>1607</v>
       </c>
       <c r="B210" s="1" t="n">
-        <v>1751</v>
+        <v>1689</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1559</v>
+        <v>1544</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1560</v>
+        <v>1545</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>1561</v>
+        <v>1546</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>1562</v>
+        <v>1547</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="L210" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M210" s="2" t="s">
-        <v>1563</v>
+        <v>1548</v>
       </c>
       <c r="O210" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P210" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="n">
-        <v>1731</v>
+        <v>1622</v>
       </c>
       <c r="B211" s="1" t="n">
-        <v>1783</v>
+        <v>1673</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>1564</v>
+        <v>1549</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1565</v>
+        <v>1550</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>1566</v>
+        <v>1551</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>1567</v>
+        <v>1552</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="L211" s="2" t="s">
         <v>992</v>
       </c>
       <c r="M211" s="2" t="s">
-        <v>1568</v>
+        <v>1553</v>
       </c>
       <c r="O211" s="1" t="s">
         <v>271</v>
@@ -14820,107 +14897,107 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="n">
-        <v>1737</v>
+        <v>1649</v>
       </c>
       <c r="B212" s="1" t="n">
-        <v>1805</v>
+        <v>1736</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>1569</v>
+        <v>1554</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1570</v>
+        <v>1555</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>1571</v>
+        <v>1556</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>1572</v>
+        <v>1557</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>1159</v>
+        <v>951</v>
       </c>
       <c r="L212" s="2" t="s">
-        <v>992</v>
+        <v>691</v>
       </c>
       <c r="M212" s="2" t="s">
-        <v>1573</v>
+        <v>1558</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P212" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="n">
-        <v>1762</v>
+        <v>1682</v>
       </c>
       <c r="B213" s="1" t="n">
-        <v>1836</v>
+        <v>1751</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>1574</v>
+        <v>1559</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>1575</v>
+        <v>1560</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>1576</v>
+        <v>1561</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>1577</v>
+        <v>1562</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P213" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="n">
-        <v>1792</v>
+        <v>1731</v>
       </c>
       <c r="B214" s="1" t="n">
-        <v>1868</v>
+        <v>1783</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>1579</v>
+        <v>1564</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>1580</v>
+        <v>1565</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>1581</v>
+        <v>1566</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>1582</v>
+        <v>1567</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>917</v>
+        <v>992</v>
       </c>
       <c r="M214" s="2" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>271</v>
@@ -14928,34 +15005,34 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="n">
-        <v>1803</v>
+        <v>1737</v>
       </c>
       <c r="B215" s="1" t="n">
-        <v>1877</v>
+        <v>1805</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1584</v>
+        <v>1569</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1585</v>
+        <v>1570</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>1586</v>
+        <v>1571</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>1587</v>
+        <v>1572</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>409</v>
+        <v>1159</v>
       </c>
       <c r="L215" s="2" t="s">
         <v>992</v>
       </c>
       <c r="M215" s="2" t="s">
-        <v>1588</v>
+        <v>1573</v>
       </c>
       <c r="O215" s="1" t="s">
         <v>271</v>
@@ -14963,69 +15040,72 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="n">
-        <v>1824</v>
+        <v>1762</v>
       </c>
       <c r="B216" s="1" t="n">
-        <v>1864</v>
+        <v>1836</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1589</v>
+        <v>1574</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>1590</v>
+        <v>1575</v>
       </c>
       <c r="E216" s="10" t="s">
-        <v>1591</v>
+        <v>1576</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>1592</v>
+        <v>1577</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>1408</v>
+        <v>80</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>1593</v>
+        <v>992</v>
       </c>
       <c r="M216" s="2" t="s">
-        <v>1594</v>
+        <v>1578</v>
       </c>
       <c r="O216" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P216" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="n">
-        <v>1859</v>
+        <v>1792</v>
       </c>
       <c r="B217" s="1" t="n">
-        <v>1925</v>
+        <v>1868</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1595</v>
+        <v>1579</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1596</v>
+        <v>1580</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>1597</v>
+        <v>1581</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>1598</v>
+        <v>1582</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="L217" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="O217" s="1" t="s">
         <v>271</v>
@@ -15033,72 +15113,69 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="n">
-        <v>1879</v>
+        <v>1803</v>
       </c>
       <c r="B218" s="1" t="n">
-        <v>1944</v>
+        <v>1877</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
       <c r="E218" s="10" t="s">
-        <v>1602</v>
+        <v>1586</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>1603</v>
+        <v>1587</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>1408</v>
+        <v>409</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>799</v>
+        <v>992</v>
       </c>
       <c r="M218" s="2" t="s">
-        <v>1604</v>
+        <v>1588</v>
       </c>
       <c r="O218" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P218" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="n">
-        <v>1880</v>
+        <v>1824</v>
       </c>
       <c r="B219" s="1" t="n">
-        <v>1936</v>
+        <v>1864</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>1606</v>
+        <v>1590</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>1607</v>
+        <v>1591</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>1608</v>
+        <v>1592</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>848</v>
+        <v>1408</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>1609</v>
+        <v>1593</v>
       </c>
       <c r="M219" s="2" t="s">
-        <v>1610</v>
+        <v>1594</v>
       </c>
       <c r="O219" s="1" t="s">
         <v>271</v>
@@ -15106,34 +15183,34 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="n">
-        <v>1890</v>
+        <v>1859</v>
       </c>
       <c r="B220" s="1" t="n">
-        <v>1981</v>
+        <v>1925</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>1612</v>
+        <v>1596</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>1613</v>
+        <v>1597</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>1615</v>
+        <v>917</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>1616</v>
+        <v>1599</v>
       </c>
       <c r="O220" s="1" t="s">
         <v>271</v>
@@ -15141,22 +15218,22 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="n">
-        <v>1901</v>
+        <v>1879</v>
       </c>
       <c r="B221" s="1" t="n">
-        <v>1989</v>
+        <v>1944</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1617</v>
+        <v>1600</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>1618</v>
+        <v>1601</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>1619</v>
+        <v>1602</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>1620</v>
+        <v>1603</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>916</v>
@@ -15165,42 +15242,48 @@
         <v>1408</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>1621</v>
+        <v>799</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>1622</v>
+        <v>1604</v>
       </c>
       <c r="O221" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P221" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="n">
-        <v>1903</v>
+        <v>1880</v>
       </c>
       <c r="B222" s="1" t="n">
-        <v>1976</v>
+        <v>1936</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1623</v>
+        <v>1605</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>1624</v>
+        <v>1606</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>1625</v>
+        <v>1607</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>1626</v>
+        <v>1608</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>231</v>
+        <v>848</v>
+      </c>
+      <c r="L222" s="2" t="s">
+        <v>1609</v>
       </c>
       <c r="M222" s="2" t="s">
-        <v>1627</v>
+        <v>1610</v>
       </c>
       <c r="O222" s="1" t="s">
         <v>271</v>
@@ -15208,34 +15291,34 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="n">
-        <v>1912</v>
+        <v>1890</v>
       </c>
       <c r="B223" s="1" t="n">
-        <v>1993</v>
+        <v>1981</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>1628</v>
+        <v>1611</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>1629</v>
+        <v>1612</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>1630</v>
+        <v>1613</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>1631</v>
+        <v>1614</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>546</v>
+        <v>138</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>799</v>
+        <v>1615</v>
       </c>
       <c r="M223" s="2" t="s">
-        <v>1632</v>
+        <v>1616</v>
       </c>
       <c r="O223" s="1" t="s">
         <v>271</v>
@@ -15243,22 +15326,22 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="n">
-        <v>1922</v>
+        <v>1901</v>
       </c>
       <c r="B224" s="1" t="n">
-        <v>1996</v>
+        <v>1989</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>1633</v>
+        <v>1617</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>1634</v>
+        <v>1618</v>
       </c>
       <c r="E224" s="10" t="s">
-        <v>1635</v>
+        <v>1619</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>1636</v>
+        <v>1620</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>916</v>
@@ -15270,7 +15353,7 @@
         <v>1621</v>
       </c>
       <c r="M224" s="2" t="s">
-        <v>1637</v>
+        <v>1622</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>271</v>
@@ -15278,145 +15361,136 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="n">
-        <v>1948</v>
+        <v>1903</v>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>1976</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>1079</v>
+        <v>1623</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K225" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L225" s="2" t="s">
-        <v>917</v>
+        <v>231</v>
       </c>
       <c r="M225" s="2" t="s">
-        <v>1641</v>
+        <v>1627</v>
       </c>
       <c r="O225" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P225" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="n">
-        <v>1613</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>1642</v>
+        <v>1912</v>
+      </c>
+      <c r="B226" s="1" t="n">
+        <v>1993</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>1644</v>
+        <v>1629</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>267</v>
+        <v>916</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>848</v>
+        <v>546</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>1647</v>
+        <v>799</v>
       </c>
       <c r="M226" s="2" t="s">
-        <v>1648</v>
+        <v>1632</v>
       </c>
       <c r="O226" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P226" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="n">
-        <v>1619</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>943</v>
+        <v>1922</v>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>1996</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>1649</v>
+        <v>1633</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>1650</v>
+        <v>1634</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>1651</v>
+        <v>1635</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>1652</v>
+        <v>1636</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>267</v>
+        <v>916</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>268</v>
+        <v>1408</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>691</v>
+        <v>1621</v>
       </c>
       <c r="M227" s="2" t="s">
-        <v>1653</v>
+        <v>1637</v>
       </c>
       <c r="O227" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P227" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="n">
-        <v>1724</v>
+        <v>1613</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1654</v>
+        <v>1642</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>1655</v>
+        <v>1643</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>1656</v>
+        <v>1644</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>1657</v>
+        <v>1645</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>1658</v>
+        <v>1646</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K228" s="2" t="s">
-        <v>951</v>
+        <v>848</v>
       </c>
       <c r="L228" s="2" t="s">
         <v>1647</v>
       </c>
       <c r="M228" s="2" t="s">
-        <v>1659</v>
+        <v>1648</v>
       </c>
       <c r="O228" s="1" t="s">
         <v>271</v>
@@ -15427,72 +15501,72 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="n">
-        <v>1854</v>
+        <v>1619</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1660</v>
+        <v>943</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>1661</v>
+        <v>1649</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1662</v>
+        <v>1650</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>1663</v>
+        <v>1651</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>1664</v>
+        <v>1652</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>848</v>
+        <v>268</v>
       </c>
       <c r="L229" s="2" t="s">
-        <v>1665</v>
+        <v>691</v>
       </c>
       <c r="M229" s="2" t="s">
-        <v>1666</v>
+        <v>1653</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P229" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="n">
-        <v>1858</v>
+        <v>1724</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1667</v>
+        <v>1654</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1668</v>
+        <v>1655</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1669</v>
+        <v>1656</v>
       </c>
       <c r="E230" s="10" t="s">
-        <v>1670</v>
+        <v>1657</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>80</v>
+        <v>951</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>1672</v>
+        <v>1647</v>
       </c>
       <c r="M230" s="2" t="s">
-        <v>1673</v>
+        <v>1659</v>
       </c>
       <c r="O230" s="1" t="s">
         <v>271</v>
@@ -15503,34 +15577,34 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="n">
-        <v>1865</v>
+        <v>1854</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1674</v>
+        <v>1660</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1675</v>
+        <v>1661</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1676</v>
+        <v>1662</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>1677</v>
+        <v>1663</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>1678</v>
+        <v>1664</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>257</v>
+        <v>848</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>1679</v>
+        <v>1665</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>1680</v>
+        <v>1666</v>
       </c>
       <c r="O231" s="1" t="s">
         <v>271</v>
@@ -15541,34 +15615,34 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="n">
-        <v>1869</v>
+        <v>1858</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1681</v>
+        <v>1667</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1682</v>
+        <v>1668</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>1683</v>
+        <v>1669</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>1684</v>
+        <v>1670</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>1685</v>
+        <v>1671</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>268</v>
+        <v>80</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>444</v>
+        <v>1672</v>
       </c>
       <c r="M232" s="2" t="s">
-        <v>1686</v>
+        <v>1673</v>
       </c>
       <c r="O232" s="1" t="s">
         <v>271</v>
@@ -15579,72 +15653,72 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="n">
-        <v>1873</v>
+        <v>1865</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1687</v>
+        <v>1674</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1688</v>
+        <v>1675</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1689</v>
+        <v>1676</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>1690</v>
+        <v>1677</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>1691</v>
+        <v>1678</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>1665</v>
+        <v>1679</v>
       </c>
       <c r="M233" s="2" t="s">
-        <v>1692</v>
+        <v>1680</v>
       </c>
       <c r="O233" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P233" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="n">
-        <v>1885</v>
+        <v>1869</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1693</v>
+        <v>1681</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>1694</v>
+        <v>1682</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1695</v>
+        <v>1683</v>
       </c>
       <c r="E234" s="10" t="s">
-        <v>1696</v>
+        <v>1684</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>1697</v>
+        <v>1685</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>1698</v>
+        <v>444</v>
       </c>
       <c r="M234" s="2" t="s">
-        <v>1699</v>
+        <v>1686</v>
       </c>
       <c r="O234" s="1" t="s">
         <v>271</v>
@@ -15655,72 +15729,72 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="n">
-        <v>1891</v>
+        <v>1873</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1700</v>
+        <v>1687</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1701</v>
+        <v>1688</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>1702</v>
+        <v>1689</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>1703</v>
+        <v>1690</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>1704</v>
+        <v>1691</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>1192</v>
+        <v>80</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>1705</v>
+        <v>1665</v>
       </c>
       <c r="M235" s="2" t="s">
-        <v>1706</v>
+        <v>1692</v>
       </c>
       <c r="O235" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P235" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="n">
-        <v>1893</v>
+        <v>1885</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1707</v>
+        <v>1693</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>1708</v>
+        <v>1694</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>1709</v>
+        <v>1695</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>1710</v>
+        <v>1696</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>1711</v>
+        <v>1697</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="L236" s="2" t="s">
         <v>1698</v>
       </c>
       <c r="M236" s="2" t="s">
-        <v>1712</v>
+        <v>1699</v>
       </c>
       <c r="O236" s="1" t="s">
         <v>271</v>
@@ -15731,72 +15805,72 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="n">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1713</v>
+        <v>1700</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1714</v>
+        <v>1701</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>1715</v>
+        <v>1702</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>1716</v>
+        <v>1703</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>1717</v>
+        <v>1704</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>247</v>
+        <v>1192</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="M237" s="2" t="s">
-        <v>1718</v>
+        <v>1706</v>
       </c>
       <c r="O237" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P237" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="n">
-        <v>1909</v>
+        <v>1893</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1719</v>
+        <v>1707</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>1720</v>
+        <v>1708</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1721</v>
+        <v>1709</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>1722</v>
+        <v>1710</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>1723</v>
+        <v>1711</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="L238" s="2" t="s">
         <v>1698</v>
       </c>
       <c r="M238" s="2" t="s">
-        <v>1724</v>
+        <v>1712</v>
       </c>
       <c r="O238" s="1" t="s">
         <v>271</v>
@@ -15810,19 +15884,19 @@
         <v>1909</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>1726</v>
+        <v>1720</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1727</v>
+        <v>1721</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>1728</v>
+        <v>1722</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>1729</v>
+        <v>1723</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>267</v>
@@ -15834,51 +15908,51 @@
         <v>1698</v>
       </c>
       <c r="M239" s="2" t="s">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="O239" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P239" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="n">
-        <v>1930</v>
+        <v>1909</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>1732</v>
+        <v>1726</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>1734</v>
+        <v>1728</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>1735</v>
+        <v>1729</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>1736</v>
+        <v>247</v>
       </c>
       <c r="L240" s="2" t="s">
-        <v>1193</v>
+        <v>1698</v>
       </c>
       <c r="M240" s="2" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P240" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16463,31 +16537,31 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1">
-        <v>1870</v>
+        <v>1885</v>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870 – 1966</t>
+          <t xml:space="preserve">1885 – 1962</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daisetz Teitaro SUZUKI</t>
+          <t xml:space="preserve">Hajime TANABE</t>
         </is>
       </c>
       <c r="E251" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Daisetz_Teitaro_Suzuki"  title=" Wikipedia"&gt;Daisetz Teitaro SUZUKI&lt;/a&gt; est l’homme qui a fait connaître le bouddhisme zen en Occident. Ami d’enfance de Kitarō Nishida, il pratiqua le zen au monastère d’Engaku-ji, à Kamakura, auprès du maître Shaku Sōen, dont il traduisit en anglais l’intervention au Parlement mondial des religions de Chicago en 1893. Parti en 1897 pour les États-Unis, il y vécut onze ans, traduisant des textes bouddhistes et taoïstes, avant d’enseigner au Japon, notamment à l’université Ōtani de Kyōto.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Essais sur le bouddhisme zen&lt;/em&gt; (1927-1934), écrits en anglais, il présente le zen non comme une doctrine mais comme une expérience directe, le &lt;em&gt;satori&lt;/em&gt;, éveil soudain qui fait voir le monde sans la médiation des concepts. Il insiste sur l’influence du zen sur toute la culture japonaise : la cérémonie du thé, les arts martiaux, le haïku et la peinture. Il étudia aussi le bouddhisme de la Terre pure et la spiritualité populaire japonaise, qu’il voyait comme une autre expression de la même intuition religieuse.&lt;/p&gt; &lt;p&gt;Après la guerre, il donna de nombreuses conférences aux États-Unis, notamment à l’université Columbia dans les années 1950, et ses livres eurent une grande influence sur des psychologues comme Carl Gustav Jung et Erich Fromm, des artistes comme John Cage et les écrivains de la Beat generation. On lui a reproché d’avoir présenté un zen idéalisé et d’avoir associé, avant la guerre, l’esprit du zen à l’éthique guerrière. Il mourut à Tōkyō à quatre-vingt-quinze ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tanabe_Hajime"  title=" Wikipedia"&gt;Hajime TANABE&lt;/a&gt; est, avec Kitarō Nishida, l’un des deux fondateurs de l’école de Kyōto. Formé aux mathématiques et à la philosophie des sciences, il étudia en Allemagne au début des années 1920 auprès de Husserl, à Fribourg, où il rencontra le jeune Heidegger, puis succéda à Nishida à l’université impériale de Kyōto, tout en développant une pensée critique envers celle de son maître.&lt;/p&gt; &lt;p&gt;Contre Nishida, à qui il reproche une philosophie trop contemplative, Tanabe élabore une « logique de l’espèce » : entre l’individu et le genre humain universel, il place les communautés particulières, peuples et nations, que la philosophie doit selon lui penser comme telles. Cette théorie, développée dans les années 1930, servit à justifier l’État japonais en guerre, ce que Tanabe reconnut ensuite comme une faute.&lt;/p&gt; &lt;p&gt;À la fin de la guerre, il publia &lt;em&gt;La Philosophie comme métanoétique&lt;/em&gt; (1946), l’un des livres les plus singuliers du siècle : le philosophe, conscient de son impuissance et de sa responsabilité, doit passer par la « repentance » (&lt;em&gt;zange&lt;/em&gt;) et renoncer à la toute-puissance de la raison, pour s’en remettre à une « puissance autre », à la manière de la foi en Amida du bouddhisme de Shinran. Retiré dans les montagnes de Kita-Karuizawa, il consacra ses dernières années à une philosophie de la mort et au dialogue avec le christianisme et le marxisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dtsuzuki-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tanabe-mini.webp</t>
         </is>
       </c>
       <c r="J251" s="1" t="inlineStr">
@@ -16497,17 +16571,17 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen</t>
+          <t xml:space="preserve">École de Kyōto</t>
         </is>
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bouddhologue et grand passeur du zen en Occident au XXe siècle.</t>
+          <t xml:space="preserve">philosophe de l’école de Kyōto, auteur d’une « philosophie comme métanoétique ».</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr">
@@ -16521,31 +16595,31 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">1971</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885 – 1962</t>
+          <t xml:space="preserve">1886 – 1971</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hajime TANABE</t>
+          <t xml:space="preserve">Raichō HIRATSUKA</t>
         </is>
       </c>
       <c r="E252" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tanabe_Hajime"  title=" Wikipedia"&gt;Hajime TANABE&lt;/a&gt; est, avec Kitarō Nishida, l’un des deux fondateurs de l’école de Kyōto. Formé aux mathématiques et à la philosophie des sciences, il étudia en Allemagne au début des années 1920 auprès de Husserl, à Fribourg, où il rencontra le jeune Heidegger, puis succéda à Nishida à l’université impériale de Kyōto, tout en développant une pensée critique envers celle de son maître.&lt;/p&gt; &lt;p&gt;Contre Nishida, à qui il reproche une philosophie trop contemplative, Tanabe élabore une « logique de l’espèce » : entre l’individu et le genre humain universel, il place les communautés particulières, peuples et nations, que la philosophie doit selon lui penser comme telles. Cette théorie, développée dans les années 1930, servit à justifier l’État japonais en guerre, ce que Tanabe reconnut ensuite comme une faute.&lt;/p&gt; &lt;p&gt;À la fin de la guerre, il publia &lt;em&gt;La Philosophie comme métanoétique&lt;/em&gt; (1946), l’un des livres les plus singuliers du siècle : le philosophe, conscient de son impuissance et de sa responsabilité, doit passer par la « repentance » (&lt;em&gt;zange&lt;/em&gt;) et renoncer à la toute-puissance de la raison, pour s’en remettre à une « puissance autre », à la manière de la foi en Amida du bouddhisme de Shinran. Retiré dans les montagnes de Kita-Karuizawa, il consacra ses dernières années à une philosophie de la mort et au dialogue avec le christianisme et le marxisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raich%C5%8D_Hiratsuka"  title=" Wikipedia"&gt;Raichō HIRATSUKA&lt;/a&gt; est la grande pionnière du féminisme au Japon. Fille d’un haut fonctionnaire de Tōkyō, diplômée de l’université pour femmes du Japon, elle pratiqua le zen dans sa jeunesse et fit scandale en 1908 par une fugue suivie d’une tentative de double suicide avec l’écrivain Morita Sōhei, dont la presse fit ses gros titres.&lt;/p&gt; &lt;p&gt;En 1911, elle fonda la revue &lt;em&gt;Seitō&lt;/em&gt; (« Bas-bleu »), première revue littéraire entièrement faite par des femmes au Japon. Son manifeste d’ouverture est resté célèbre : « À l’origine, la femme était le soleil. Elle était une personne authentique. Aujourd’hui, la femme est la lune », qui ne brille que de la lumière d’un autre. Elle y appelle les femmes à retrouver leur « génie caché », par une libération intérieure autant que sociale, et la revue ouvrit des débats alors très audacieux sur la chasteté, l’avortement et la prostitution.&lt;/p&gt; &lt;p&gt;Influencée par la penseuse suédoise Ellen Key, elle défendit ensuite la protection de la maternité par l’État, ce qui l’opposa à la poétesse Yosano Akiko, partisane de l’indépendance économique des femmes. En 1920, elle fonda avec Ichikawa Fusae l’Association des femmes nouvelles, qui obtint en 1922 le droit pour les femmes d’assister à des réunions politiques. Elle vécut en union libre avec le peintre Okumura Hiroshi, refusant longtemps un mariage qui soumettait l’épouse à la loi familiale. Après la guerre, elle s’engagea dans le pacifisme et le mouvement contre les armes nucléaires.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tanabe-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hiratsuka-mini.webp</t>
         </is>
       </c>
       <c r="J252" s="1" t="inlineStr">
@@ -16555,17 +16629,22 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">École de Kyōto</t>
+          <t xml:space="preserve">Féminisme</t>
         </is>
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe de l’école de Kyōto, auteur d’une « philosophie comme métanoétique ».</t>
+          <t xml:space="preserve">pionnière du féminisme japonais, fondatrice de la revue Seitō.</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr">
@@ -16579,31 +16658,31 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971</t>
+          <t xml:space="preserve">1941</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886 – 1971</t>
+          <t xml:space="preserve">1888 – 1941</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raichō HIRATSUKA</t>
+          <t xml:space="preserve">Shūzō KUKI</t>
         </is>
       </c>
       <c r="E253" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raich%C5%8D_Hiratsuka"  title=" Wikipedia"&gt;Raichō HIRATSUKA&lt;/a&gt; est la grande pionnière du féminisme au Japon. Fille d’un haut fonctionnaire de Tōkyō, diplômée de l’université pour femmes du Japon, elle pratiqua le zen dans sa jeunesse et fit scandale en 1908 par une fugue suivie d’une tentative de double suicide avec l’écrivain Morita Sōhei, dont la presse fit ses gros titres.&lt;/p&gt; &lt;p&gt;En 1911, elle fonda la revue &lt;em&gt;Seitō&lt;/em&gt; (« Bas-bleu »), première revue littéraire entièrement faite par des femmes au Japon. Son manifeste d’ouverture est resté célèbre : « À l’origine, la femme était le soleil. Elle était une personne authentique. Aujourd’hui, la femme est la lune », qui ne brille que de la lumière d’un autre. Elle y appelle les femmes à retrouver leur « génie caché », par une libération intérieure autant que sociale, et la revue ouvrit des débats alors très audacieux sur la chasteté, l’avortement et la prostitution.&lt;/p&gt; &lt;p&gt;Influencée par la penseuse suédoise Ellen Key, elle défendit ensuite la protection de la maternité par l’État, ce qui l’opposa à la poétesse Yosano Akiko, partisane de l’indépendance économique des femmes. En 1920, elle fonda avec Ichikawa Fusae l’Association des femmes nouvelles, qui obtint en 1922 le droit pour les femmes d’assister à des réunions politiques. Elle vécut en union libre avec le peintre Okumura Hiroshi, refusant longtemps un mariage qui soumettait l’épouse à la loi familiale. Après la guerre, elle s’engagea dans le pacifisme et le mouvement contre les armes nucléaires.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kuki_Sh%C5%ABz%C5%8D"  title=" Wikipedia"&gt;Shūzō KUKI&lt;/a&gt; est l’un des philosophes japonais les plus cosmopolites de son temps. Fils du baron Kuki Ryūichi, haut fonctionnaire de Meiji, et d’une mère qui fut proche d’Okakura Kakuzō, il passa huit années en Europe dans les années 1920 : il étudia auprès de Rickert à Heidelberg, rencontra Bergson à Paris, où le jeune Jean-Paul Sartre lui donna des leçons de français, et suivit à Marbourg les cours de Heidegger. De retour au Japon, il enseigna à l’université impériale de Kyōto.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Structure de l’iki&lt;/em&gt; (1930), il analyse une notion clé de l’esthétique d’Edo, l’&lt;em&gt;iki&lt;/em&gt;, une élégance raffinée née dans les quartiers de plaisir : un mélange de séduction, de fierté et de détachement, qui garde toujours une distance. Kuki y applique la méthode de la phénoménologie et de l’herméneutique à une expérience proprement japonaise, et montre ce que les mots d’une culture révèlent de sa manière d’être au monde.&lt;/p&gt; &lt;p&gt;Son autre grand livre, &lt;em&gt;Le Problème de la contingence&lt;/em&gt; (1935), fait de la contingence, la rencontre de deux séries indépendantes, ce « qui aurait pu ne pas être », une question philosophique centrale : c’est dans l’étonnement devant la rencontre fortuite que l’existence humaine prend son sens. Heidegger évoqua plus tard leurs échanges dans son &lt;em&gt;Dialogue avec un Japonais&lt;/em&gt;. Kuki mourut en 1941, à cinquante-trois ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hiratsuka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kuki-mini.webp</t>
         </is>
       </c>
       <c r="J253" s="1" t="inlineStr">
@@ -16613,22 +16692,17 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Féminisme</t>
+          <t xml:space="preserve">École de Kyōto ; Phénoménologie</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pionnière du féminisme japonais, fondatrice de la revue Seitō.</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">philosophe de l’iki et de la contingence, passeur entre Kyōto et la phénoménologie européenne.</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr">
@@ -16642,31 +16716,31 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941</t>
+          <t xml:space="preserve">1960</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888 – 1941</t>
+          <t xml:space="preserve">1889 – 1960</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shūzō KUKI</t>
+          <t xml:space="preserve">Tetsurō WATSUJI</t>
         </is>
       </c>
       <c r="E254" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kuki_Sh%C5%ABz%C5%8D"  title=" Wikipedia"&gt;Shūzō KUKI&lt;/a&gt; est l’un des philosophes japonais les plus cosmopolites de son temps. Fils du baron Kuki Ryūichi, haut fonctionnaire de Meiji, et d’une mère qui fut proche d’Okakura Kakuzō, il passa huit années en Europe dans les années 1920 : il étudia auprès de Rickert à Heidelberg, rencontra Bergson à Paris, où le jeune Jean-Paul Sartre lui donna des leçons de français, et suivit à Marbourg les cours de Heidegger. De retour au Japon, il enseigna à l’université impériale de Kyōto.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Structure de l’iki&lt;/em&gt; (1930), il analyse une notion clé de l’esthétique d’Edo, l’&lt;em&gt;iki&lt;/em&gt;, une élégance raffinée née dans les quartiers de plaisir : un mélange de séduction, de fierté et de détachement, qui garde toujours une distance. Kuki y applique la méthode de la phénoménologie et de l’herméneutique à une expérience proprement japonaise, et montre ce que les mots d’une culture révèlent de sa manière d’être au monde.&lt;/p&gt; &lt;p&gt;Son autre grand livre, &lt;em&gt;Le Problème de la contingence&lt;/em&gt; (1935), fait de la contingence, la rencontre de deux séries indépendantes, ce « qui aurait pu ne pas être », une question philosophique centrale : c’est dans l’étonnement devant la rencontre fortuite que l’existence humaine prend son sens. Heidegger évoqua plus tard leurs échanges dans son &lt;em&gt;Dialogue avec un Japonais&lt;/em&gt;. Kuki mourut en 1941, à cinquante-trois ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Watsuji_Tetsur%C5%8D"  title=" Wikipedia"&gt;Tetsurō WATSUJI&lt;/a&gt; est l’un des grands philosophes japonais du XXe siècle, proche de l’école de Kyōto. D’abord attiré par Nietzsche et Kierkegaard, auxquels il consacra ses premiers livres, il se tourna vers l’étude de la culture japonaise ancienne, des temples de Nara au bouddhisme de Dōgen, avant d’enseigner l’éthique à l’université impériale de Kyōto, puis à celle de Tōkyō.&lt;/p&gt; &lt;p&gt;En 1927, lors d’un séjour en Allemagne, il lut &lt;em&gt;Être et Temps&lt;/em&gt; de Heidegger et lui reprocha d’avoir pensé l’existence humaine à partir du temps en négligeant l’espace. Dans &lt;em&gt;Fūdo&lt;/em&gt; (1935), traduit en français sous le titre &lt;em&gt;Fûdo, le milieu humain&lt;/em&gt;, il montre que l’être humain est façonné par son climat et son paysage : les cultures de la mousson, du désert et des prairies européennes donnent naissance à des manières différentes d’être au monde.&lt;/p&gt; &lt;p&gt;Son grand œuvre, l’&lt;em&gt;Éthique&lt;/em&gt; (1937-1949), part du mot japonais &lt;em&gt;ningen&lt;/em&gt;, « être humain », écrit avec les caractères « homme » et « entre » : l’humain n’est pas d’abord un individu isolé, mais un être de relations, et l’éthique est la science de cet « entre-deux ». La personne n’existe que dans un double mouvement, par lequel elle se distingue de la communauté puis y revient. Cette pensée de la relation, qui servit aussi à justifier l’ordre impérial, reste l’une des contributions majeures du Japon à la philosophie morale.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kuki-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/watsuji-mini.webp</t>
         </is>
       </c>
       <c r="J254" s="1" t="inlineStr">
@@ -16676,17 +16750,17 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; metaphysique</t>
+          <t xml:space="preserve">ethique ; esthetique</t>
         </is>
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">École de Kyōto ; Phénoménologie</t>
+          <t xml:space="preserve">École de Kyōto</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe de l’iki et de la contingence, passeur entre Kyōto et la phénoménologie européenne.</t>
+          <t xml:space="preserve">philosophe de l’éthique comme « entre-deux » humain et du milieu (fūdo).</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr">
@@ -16699,60 +16773,49 @@
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="1">
-        <v>1889</v>
-      </c>
-      <c r="B255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1960</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1889 – 1960</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tetsurō WATSUJI</t>
-        </is>
+      <c r="A255" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>1638</v>
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Watsuji_Tetsur%C5%8D"  title=" Wikipedia"&gt;Tetsurō WATSUJI&lt;/a&gt; est l’un des grands philosophes japonais du XXe siècle, proche de l’école de Kyōto. D’abord attiré par Nietzsche et Kierkegaard, auxquels il consacra ses premiers livres, il se tourna vers l’étude de la culture japonaise ancienne, des temples de Nara au bouddhisme de Dōgen, avant d’enseigner l’éthique à l’université impériale de Kyōto, puis à celle de Tōkyō.&lt;/p&gt; &lt;p&gt;En 1927, lors d’un séjour en Allemagne, il lut &lt;em&gt;Être et Temps&lt;/em&gt; de Heidegger et lui reprocha d’avoir pensé l’existence humaine à partir du temps en négligeant l’espace. Dans &lt;em&gt;Fūdo&lt;/em&gt; (1935), traduit en français sous le titre &lt;em&gt;Fûdo, le milieu humain&lt;/em&gt;, il montre que l’être humain est façonné par son climat et son paysage : les cultures de la mousson, du désert et des prairies européennes donnent naissance à des manières différentes d’être au monde.&lt;/p&gt; &lt;p&gt;Son grand œuvre, l’&lt;em&gt;Éthique&lt;/em&gt; (1937-1949), part du mot japonais &lt;em&gt;ningen&lt;/em&gt;, « être humain », écrit avec les caractères « homme » et « entre » : l’humain n’est pas d’abord un individu isolé, mais un être de relations, et l’éthique est la science de cet « entre-deux ». La personne n’existe que dans un double mouvement, par lequel elle se distingue de la communauté puis y revient. Cette pensée de la relation, qui servit aussi à justifier l’ordre impérial, reste l’une des contributions majeures du Japon à la philosophie morale.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/watsuji-mini.webp</t>
-        </is>
-      </c>
-      <c r="J255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japonaise</t>
-        </is>
-      </c>
-      <c r="K255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; esthetique</t>
-        </is>
-      </c>
-      <c r="L255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">École de Kyōto</t>
-        </is>
-      </c>
-      <c r="M255" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">philosophe de l’éthique comme « entre-deux » humain et du milieu (fūdo).</t>
-        </is>
-      </c>
-      <c r="O255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="P255" s="1">
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Do-ol" title=" Wikipedia (en)"&gt;KIM YONG-OK,&lt;/a&gt; connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de &lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi" title=" Wikipedia (en)"&gt;Choe Han-gi&lt;/a&gt;, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JDg8l7CsF8Y</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"[도올 김용옥]우리는 누구인가-동아시아 국제정세(대만편)_01" par jae hak Lee</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J255" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K255" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L255" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M255" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="O255" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P255" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16840,18 +16903,18 @@
     <hyperlink ref="E127" r:id="rId72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vivekananda&quot;  title=&quot; Wikipedia&quot;&gt;VIVEKANANDA&lt;/a&gt; était l'une des figures spirituelles les plus influentes de l'Inde moderne et un ardent défenseur de la  &lt;a href=&quot;https://www.rggpodcast.fr/c%C3%A9l%C3%A9brations/swami-vivekananda/&quot;  title=&quot;Radio Gandharva gana par Rggweb&quot;&gt;philosophie vedanta&lt;/a&gt; et du yoga. Né sous le nom de Narendranath Datta à Calcutta, il est devenu un disciple du grand saint et mystique Ramakrishna Paramahamsa, un saint mystique de Dakshineswar. &lt;/p&gt; &lt;p&gt; Il croyait que toutes les religions mènent au même but ultime et que les différences ne sont que superficielles. Selon lui, chaque être humain possède en lui une étincelle divine et peut réaliser sa nature divine par la pratique spirituelle. Il a insisté sur l'importance du service désintéressé (seva) envers les pauvres et les nécessiteux, considérant cela comme une forme de culte et a plaidé pour une éducation qui combine les connaissances modernes et les valeurs spirituelles traditionnelles. &lt;/p&gt; &lt;p&gt; Il  a fondé la Ramakrishna Mission, une organisation dédiée au service social, à l'éducation et à la diffusion des enseignements spirituels.  Il  est considéré comme un pionnier du dialogue interreligieux et un inspirateur du mouvement nationaliste indien. Ses enseignements ont influencé des leaders comme Mahatma Gandhi, Subhas Chandra Bose et Aurobindo Ghosh. Il est également crédité d'avoir &lt;a href=&quot;https://blog.green-yoga.fr/vivekananda-premier-maitre-yogi-moderne/&quot;  title=&quot;Vivekananda, premier maître yogi moderne par blog-green-yoga&quot;&gt;popularisé le yoga&lt;/a&gt; et la méditation en Occident. &lt;/p&gt;"/>
     <hyperlink ref="H127" r:id="rId73" display="https://www.laphilo.fr/pho/vivekananda-mini.webp"/>
     <hyperlink ref="E128" r:id="rId74" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohandas_Karamchand_Gandhi&quot;  title=&quot; Wikipedia&quot;&gt;Mohandas Karamchand GANDHI&lt;/a&gt;  était un &lt;a href=&quot;https://www.youtube.com/watch?v=zTmg8qs5B_w&amp;ab_channel=Brut&quot;  title=&quot;Une vie par Brut&quot;&gt;leader spirituel&lt;/a&gt; et un militant politique Indien. Il est surtout connu pour sa lutte pacifique pour l'indépendance de l'Inde vis-à-vis du Royaume-Uni par  des désobéissances civile non-violentes contre le gouvernement britannique,  grève de la faim, manifestations et boycotts. &lt;/p&gt; &lt;p&gt;   Gandhi était surtout un philosophe qui a développé sa propre vision du monde et de la vie. &lt;a href=&quot;https://www.psychaanalyse.com/pdf/ghandi_sa_pensee.pdf&quot;   title=&quot;Livre de Gandhi&quot;&gt;Sa philosophie&lt;/a&gt; est souvent appelée &quot;satyagraha&quot;, un terme sanskrit qui signifie &quot;force de la vérité&quot; ou &quot;force de l'âme&quot;. Elle est centrée sur la non-violence, l'amour et la vérité. C'est la seule façon de résoudre les conflits de manière pacifique et durable. &lt;/p&gt; &lt;p&gt;   l croyait que chaque être humain possède une âme divine, et que cette âme est la source de notre force intérieure. Il a encouragé les gens à chercher la vérité en eux-mêmes et à suivre leur conscience plutôt que de se conformer aux normes sociales ou religieuses imposées.&lt;/p&gt; &lt;p&gt;   Il a souligné l'importance de l'autonomie et de l'autosuffisance et a encouragé les gens à vivre de manière simple, à cultiver leur propre nourriture, à produire leurs propres vêtements et à être autosuffisants autant que possible. &lt;/p&gt; &lt;p&gt;  Cette vision était basée sur le concept de &lt;a href=&quot;https://www.editionscienceetbiencommun.org/wp-content/uploads/2018/01/Swaraj-des-savoirs-un-manifeste-indien-pour-la-science-et-la-technologie-1515376288.pdf&quot;    title=&quot;Un manifeste indien&quot;&gt;&quot;swaraj&quot;&lt;/a&gt;, ou l'autonomie, qui est devenu un thème majeur de la lutte de Gandhi pour l'indépendance de l'Inde. &lt;/P&gt;  &lt;audio controls title=&quot;Mémoires de Gandhi par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11739-29.01.2018-ITEMA_21570326-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H132" r:id="rId75" display="https://www.laphilo.fr/pho/coomaraswamy-mini.webp"/>
-    <hyperlink ref="E133" r:id="rId76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohamed_Iqbal&quot; title=&quot;Wikipedia&quot;&gt;Muhammad IQBAL&lt;/a&gt; était un philosophe‑poète pakistanais, poète se plaçant à la croisée de l’islam, de la modernité et de la pensée occidentale. Considéré comme l’un des  &lt;a href=&quot;https://www.saphirnews.com/Mohammed-Iqbal-un-revolutionnaire-en-islam_a24652.html&quot; title=&quot;Mohamed Iqbal, un révolutionnaire en Islam par saphirnews&quot;&gt;grands penseurs musulmans &lt;/a&gt; de son époque, il cherche à réformer l’Islam en l’ouvrant à la rationalité et à l’action, tout en restant profondément enraciné dans la tradition soufie et coranique. &lt;/p&gt; &lt;p&gt; Sa philosophie tourne autour du « Khudi » (le Soi), c’est‑à‑dire une  &lt;a href=&quot;https://www.youtube.com/watch?v=ekC6_wffi10&quot; title=&quot;Mohamed Iqbal par Perennial Wisdom&quot;&gt;individualité spirituelle forte, &lt;/a&gt; capable de se libérer de toute passivité mystique et de toute soumission fataliste. Pour lui, l’homme n’est pas appelé à s’effacer dans un tout indifférencié, mais à affirmer son moi comme centre de liberté, de volonté et de responsabilité devant Dieu, en prolongeant ainsi la dynamique de la création. &lt;/p&gt; &lt;p&gt; Il  valorise aussi une lecture active et historique de l’Islam, où la loi et la pensée religieuse ne sont pas figées, mais appelées à se réinterpréter à la lumière de l’expérience humaine et du progrès. Il milite pour une société ouverte, où la foi se traduit par l’engagement, la justice, l’éducation et la dignité du travail, plutôt que par un rigorisme puritain ou un repli identitaire. &lt;/p&gt; &lt;p&gt; Il est souvent vu comme un penseur à la fois panislamiste et humaniste : il rêve d’une communauté musulmane unifiée, mais fondée sur la liberté intérieure, la créativité individuelle et le respect de la diversité humaine. Son œuvre, surtout poétique, mêle mystique et volonté de transformer le monde, ce qui fait de lui un des premiers philosophes à articuler Islam, modernité et affirmation de soi. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Iqbal : soufisme indo-pakistanais par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-02.10.2011-ITEMA_20312518-2011C14958E0033-ITE_00045911_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="H135" r:id="rId77" display="https://www.laphilo.fr/pho/brambedkar-mini.webp"/>
-    <hyperlink ref="E136" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jiddu_Krishnamurti&quot;  title=&quot;Wikipedia&quot;&gt;Jiddu KRISHNAMURTI&lt;/a&gt;  était  un penseur indien qui a profondément marqué la réflexion sur la liberté intérieure, la conscience et l’éducation.  &lt;a href=&quot;https://citations.ouest-france.fr/citations-jiddu-krishnamurti-1049.html&quot; title=&quot;Citations Krishnamurti par citations ouest france&quot;&gt;Sa parole &lt;/a&gt; est souvent résumée par l’idée que « la vérité est un pays sans chemins » : on ne peut pas atteindre le réel par l’autorité, le dogme, le rituel ou un système de pensée tout fait.  .&lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve la critique du conditionnement psychologique. Il explique que l’être humain vit prisonnier de ses peurs, de ses habitudes, de ses croyances et des images qu’il se fabrique sur lui-même et sur les autres ; pour lui, cette prison mentale empêche de voir clairement. &lt;/p&gt; &lt;p&gt; Il ne propose pas une  &lt;a href=&quot;https://www.youtube.com/watch?v=Uk3Kdoouw-E&quot; title=&quot;Perceptions Empties consciousness : Krishnamurti &quot;&gt;méthode au sens classique, &lt;/a&gt; ni un chemin spirituel à suivre mécaniquement. À la place, il invite à une observation directe de l’esprit, sans jugement et sans choix, qu’il associe à une forme de méditation véritable ; cette attention nue permettrait de comprendre la pensée en train de se faire et de se défaire. &lt;/p&gt; &lt;p&gt; Il relie toujours la transformation individuelle au changement du monde. Il pense qu’une société plus juste ne peut naître que d’une conscience intérieure libérée de l’autorité, de la violence psychologique et de la dépendance aux systèmes ; sa philosophie est donc moins une doctrine qu’un appel à voir par soi-même, ici et maintenant. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Krishnamurti, une vie par France Culture&quot;&gt;&#10;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14090-10.10.2014-ITEMA_20678757-2014C23018S0283-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt;&#10;&lt;/audio&gt;"/>
-    <hyperlink ref="E137" r:id="rId79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor&quot; title=&quot;Wikipedia&quot;&gt;Léopold Sédar SENGHOR&lt;/a&gt; était à la fois un grand poète-philosophe francophone et un homme d’État sénégalais, premier président de la République du Sénégal (1960–1980) et premier Africain membre de l’Académie française. Formé dans le système scolaire français, il incarne une figure hybride, à la croisée de l’Afrique et de la France, de la négritude et de la francophonie. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot;Négridude par Wikipedia&quot;&gt;« négritude », &lt;/a&gt; qu’il définit comme la reconnaissance du fait d’être noir et l’acceptation de cette identité, de son histoire, de sa culture et de sa destinée. Il en fait une valeur poétique et politique : la négritude vise à restaurer la dignité du peuple noir après la colonisation, en affirmant la beauté de la culture afro‑africaine, de ses langues, de ses rythmes et de son rapport à la vie et à la nature. &lt;/p&gt; &lt;p&gt; Dans sa poésie, il met en avant une sensibilité particulière, une « sensorialité » et une intuition qu’il oppose à la rationalité occidentale jugée plus froide, ce qui fait de ses vers une ode à la terre africaine, aux corps noirs, aux masques, aux danses et aux ancêtres. Des textes comme Femme noire ou Chants d’ombre célèbrent à la fois la femme‑enfant, la femme‑mère, la terre‑Afrique et la mémoire collective, dans une langue riche en images et en musique. &lt;/p&gt; &lt;p&gt; Par‑delà la négritude, il rêve d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=sINJIeY4UKo&quot;  title=&quot;Senghor par RTS&quot;&gt;« Civilisation de l’Universel »,&lt;/a&gt;  c’est‑à‑dire d’un monde où différentes traditions (africaines, européennes, etc.) pourraient se mêler dans un métissage créateur plutôt que s’affronter. Philosophe politique, poète et humaniste, il reste l’une des figures majeures de la littérature francophone, à la fois comme chantre de la fierté noire et comme théoricien d’un dialogue entre cultures. &lt;/p&gt; &lt;audio controls title=&quot;Senghor ‘Tu te languis’ par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21713-25.11.2025-ITEMA_24321734-2025C53416E0132-ITE_00154728_RSCE-21-996409c1a2c68ce243e4f4ef83e00211.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="E138" r:id="rId80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Keiji_Nishitani&quot;  title=&quot;Wikipedia&quot;&gt;Keiji NISHITANI &lt;/a&gt; un philosophe japonais membre de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89cole_de_Kyoto&quot;  title=&quot;école de Kyoto par Wikipedia&quot;&gt;l’École de Kyoto, &lt;/a&gt;  au côté de Nishida Kitarō et Tanabe Hajime, et l’un des penseurs modernes les plus originaux sur la religion, le bouddhisme et l’expérience du néant. Il cherche à penser ensemble la crise métaphysique de la modernité occidentale et la voie spirituelle du bouddhisme, notamment le zen et le bouddhisme du Vide (śūnyatā). &lt;/p&gt; &lt;p&gt; Sa réflexion prend comme point de départ le nihilisme moderne, c’est‑à‑dire le sentiment profond que tout est vidé de sens, de valeur et d’origine absolue, auquel il confronte l’expérience bouddhique de la vacuité radicale. Selon lui, la modernité enferme l’homme dans un soi narcissique et isolé, coupé de tout fondement ultime, et ce qui surgit alors n’est pas seulement le doute, mais une « grande incertitude » qui mène au vide de soi‑même. &lt;/p&gt; &lt;p&gt; Il propose alors une  &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_2005_num_34_1_1419&quot;  title=&quot;l’un e le tout en question par Persée&quot;&gt;« conversion » spirituelle &lt;/a&gt; : le même néant qui menaçait d’anéantir l’individu peut devenir, lorsque l’on cesse de le fuir, le point de départ d’une nouvelle compréhension du religieux, où le soi s’efface au profit d’une ouverture à l’être tout entier. Pour lui, la religion ne se réduit ni à dogme, ni à institution, ni à simple psychologie, mais à une expérience où le sujet, au cœur de sa plus grande déréliction, découvre que le monde peut être habité de sacrement, de manière « immanemment sainte ». &lt;/p&gt; &lt;p&gt; Il s’inscrit dans une entreprise de « philosophie entre Orient et Occident », où la pensée occidentale rencontre la tradition bouddhique pour repenser ensemble l’être, le mal, la liberté et la responsabilité. À travers des ouvrages comme Religion et néant (Religion and Nothingness), il devient l’une des figures clés du dialogue philosophique et religieux entre Asie et Europe, articulant la crise de la modernité et la possibilité d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=Ak12Fplzo0U&quot;  title=&quot;The void is not the end Nishitani Keiji par NullSOPHY&quot;&gt;renaissance spirituelle &lt;/a&gt; fondée sur la vacuité éclairée. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H139" r:id="rId81" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
-    <hyperlink ref="E141" r:id="rId82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E142" r:id="rId83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E143" r:id="rId84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="H143" r:id="rId85" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
-    <hyperlink ref="H152" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
+    <hyperlink ref="H133" r:id="rId75" display="https://www.laphilo.fr/pho/coomaraswamy-mini.webp"/>
+    <hyperlink ref="E134" r:id="rId76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mohamed_Iqbal&quot; title=&quot;Wikipedia&quot;&gt;Muhammad IQBAL&lt;/a&gt; était un philosophe‑poète pakistanais, poète se plaçant à la croisée de l’islam, de la modernité et de la pensée occidentale. Considéré comme l’un des  &lt;a href=&quot;https://www.saphirnews.com/Mohammed-Iqbal-un-revolutionnaire-en-islam_a24652.html&quot; title=&quot;Mohamed Iqbal, un révolutionnaire en Islam par saphirnews&quot;&gt;grands penseurs musulmans &lt;/a&gt; de son époque, il cherche à réformer l’Islam en l’ouvrant à la rationalité et à l’action, tout en restant profondément enraciné dans la tradition soufie et coranique. &lt;/p&gt; &lt;p&gt; Sa philosophie tourne autour du « Khudi » (le Soi), c’est‑à‑dire une  &lt;a href=&quot;https://www.youtube.com/watch?v=ekC6_wffi10&quot; title=&quot;Mohamed Iqbal par Perennial Wisdom&quot;&gt;individualité spirituelle forte, &lt;/a&gt; capable de se libérer de toute passivité mystique et de toute soumission fataliste. Pour lui, l’homme n’est pas appelé à s’effacer dans un tout indifférencié, mais à affirmer son moi comme centre de liberté, de volonté et de responsabilité devant Dieu, en prolongeant ainsi la dynamique de la création. &lt;/p&gt; &lt;p&gt; Il  valorise aussi une lecture active et historique de l’Islam, où la loi et la pensée religieuse ne sont pas figées, mais appelées à se réinterpréter à la lumière de l’expérience humaine et du progrès. Il milite pour une société ouverte, où la foi se traduit par l’engagement, la justice, l’éducation et la dignité du travail, plutôt que par un rigorisme puritain ou un repli identitaire. &lt;/p&gt; &lt;p&gt; Il est souvent vu comme un penseur à la fois panislamiste et humaniste : il rêve d’une communauté musulmane unifiée, mais fondée sur la liberté intérieure, la créativité individuelle et le respect de la diversité humaine. Son œuvre, surtout poétique, mêle mystique et volonté de transformer le monde, ce qui fait de lui un des premiers philosophes à articuler Islam, modernité et affirmation de soi. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Iqbal : soufisme indo-pakistanais par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/11200-02.10.2011-ITEMA_20312518-2011C14958E0033-ITE_00045911_RSCE-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="H136" r:id="rId77" display="https://www.laphilo.fr/pho/brambedkar-mini.webp"/>
+    <hyperlink ref="E137" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jiddu_Krishnamurti&quot;  title=&quot;Wikipedia&quot;&gt;Jiddu KRISHNAMURTI&lt;/a&gt;  était  un penseur indien qui a profondément marqué la réflexion sur la liberté intérieure, la conscience et l’éducation.  &lt;a href=&quot;https://citations.ouest-france.fr/citations-jiddu-krishnamurti-1049.html&quot; title=&quot;Citations Krishnamurti par citations ouest france&quot;&gt;Sa parole &lt;/a&gt; est souvent résumée par l’idée que « la vérité est un pays sans chemins » : on ne peut pas atteindre le réel par l’autorité, le dogme, le rituel ou un système de pensée tout fait.  .&lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve la critique du conditionnement psychologique. Il explique que l’être humain vit prisonnier de ses peurs, de ses habitudes, de ses croyances et des images qu’il se fabrique sur lui-même et sur les autres ; pour lui, cette prison mentale empêche de voir clairement. &lt;/p&gt; &lt;p&gt; Il ne propose pas une  &lt;a href=&quot;https://www.youtube.com/watch?v=Uk3Kdoouw-E&quot; title=&quot;Perceptions Empties consciousness : Krishnamurti &quot;&gt;méthode au sens classique, &lt;/a&gt; ni un chemin spirituel à suivre mécaniquement. À la place, il invite à une observation directe de l’esprit, sans jugement et sans choix, qu’il associe à une forme de méditation véritable ; cette attention nue permettrait de comprendre la pensée en train de se faire et de se défaire. &lt;/p&gt; &lt;p&gt; Il relie toujours la transformation individuelle au changement du monde. Il pense qu’une société plus juste ne peut naître que d’une conscience intérieure libérée de l’autorité, de la violence psychologique et de la dépendance aux systèmes ; sa philosophie est donc moins une doctrine qu’un appel à voir par soi-même, ici et maintenant. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Krishnamurti, une vie par France Culture&quot;&gt;&#10;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14090-10.10.2014-ITEMA_20678757-2014C23018S0283-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt;&#10;&lt;/audio&gt;"/>
+    <hyperlink ref="E139" r:id="rId79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor&quot; title=&quot;Wikipedia&quot;&gt;Léopold Sédar SENGHOR&lt;/a&gt; était à la fois un grand poète-philosophe francophone et un homme d’État sénégalais, premier président de la République du Sénégal (1960–1980) et premier Africain membre de l’Académie française. Formé dans le système scolaire français, il incarne une figure hybride, à la croisée de l’Afrique et de la France, de la négritude et de la francophonie. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot;Négridude par Wikipedia&quot;&gt;« négritude », &lt;/a&gt; qu’il définit comme la reconnaissance du fait d’être noir et l’acceptation de cette identité, de son histoire, de sa culture et de sa destinée. Il en fait une valeur poétique et politique : la négritude vise à restaurer la dignité du peuple noir après la colonisation, en affirmant la beauté de la culture afro‑africaine, de ses langues, de ses rythmes et de son rapport à la vie et à la nature. &lt;/p&gt; &lt;p&gt; Dans sa poésie, il met en avant une sensibilité particulière, une « sensorialité » et une intuition qu’il oppose à la rationalité occidentale jugée plus froide, ce qui fait de ses vers une ode à la terre africaine, aux corps noirs, aux masques, aux danses et aux ancêtres. Des textes comme Femme noire ou Chants d’ombre célèbrent à la fois la femme‑enfant, la femme‑mère, la terre‑Afrique et la mémoire collective, dans une langue riche en images et en musique. &lt;/p&gt; &lt;p&gt; Par‑delà la négritude, il rêve d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=sINJIeY4UKo&quot;  title=&quot;Senghor par RTS&quot;&gt;« Civilisation de l’Universel »,&lt;/a&gt;  c’est‑à‑dire d’un monde où différentes traditions (africaines, européennes, etc.) pourraient se mêler dans un métissage créateur plutôt que s’affronter. Philosophe politique, poète et humaniste, il reste l’une des figures majeures de la littérature francophone, à la fois comme chantre de la fierté noire et comme théoricien d’un dialogue entre cultures. &lt;/p&gt; &lt;audio controls title=&quot;Senghor ‘Tu te languis’ par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21713-25.11.2025-ITEMA_24321734-2025C53416E0132-ITE_00154728_RSCE-21-996409c1a2c68ce243e4f4ef83e00211.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="E140" r:id="rId80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Keiji_Nishitani&quot;  title=&quot;Wikipedia&quot;&gt;Keiji NISHITANI &lt;/a&gt; un philosophe japonais membre de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89cole_de_Kyoto&quot;  title=&quot;école de Kyoto par Wikipedia&quot;&gt;l’École de Kyoto, &lt;/a&gt;  au côté de Nishida Kitarō et Tanabe Hajime, et l’un des penseurs modernes les plus originaux sur la religion, le bouddhisme et l’expérience du néant. Il cherche à penser ensemble la crise métaphysique de la modernité occidentale et la voie spirituelle du bouddhisme, notamment le zen et le bouddhisme du Vide (śūnyatā). &lt;/p&gt; &lt;p&gt; Sa réflexion prend comme point de départ le nihilisme moderne, c’est‑à‑dire le sentiment profond que tout est vidé de sens, de valeur et d’origine absolue, auquel il confronte l’expérience bouddhique de la vacuité radicale. Selon lui, la modernité enferme l’homme dans un soi narcissique et isolé, coupé de tout fondement ultime, et ce qui surgit alors n’est pas seulement le doute, mais une « grande incertitude » qui mène au vide de soi‑même. &lt;/p&gt; &lt;p&gt; Il propose alors une  &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_2005_num_34_1_1419&quot;  title=&quot;l’un e le tout en question par Persée&quot;&gt;« conversion » spirituelle &lt;/a&gt; : le même néant qui menaçait d’anéantir l’individu peut devenir, lorsque l’on cesse de le fuir, le point de départ d’une nouvelle compréhension du religieux, où le soi s’efface au profit d’une ouverture à l’être tout entier. Pour lui, la religion ne se réduit ni à dogme, ni à institution, ni à simple psychologie, mais à une expérience où le sujet, au cœur de sa plus grande déréliction, découvre que le monde peut être habité de sacrement, de manière « immanemment sainte ». &lt;/p&gt; &lt;p&gt; Il s’inscrit dans une entreprise de « philosophie entre Orient et Occident », où la pensée occidentale rencontre la tradition bouddhique pour repenser ensemble l’être, le mal, la liberté et la responsabilité. À travers des ouvrages comme Religion et néant (Religion and Nothingness), il devient l’une des figures clés du dialogue philosophique et religieux entre Asie et Europe, articulant la crise de la modernité et la possibilité d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=Ak12Fplzo0U&quot;  title=&quot;The void is not the end Nishitani Keiji par NullSOPHY&quot;&gt;renaissance spirituelle &lt;/a&gt; fondée sur la vacuité éclairée. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="H141" r:id="rId81" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
+    <hyperlink ref="E143" r:id="rId82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E144" r:id="rId83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E145" r:id="rId84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H145" r:id="rId85" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
+    <hyperlink ref="H156" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -7256,8 +7256,10 @@
       <c r="D25" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>202</v>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Y%C4%81j%C3%B1avalkya" title=" Wikipedia"&gt;Yâjñavalkya&lt;/a&gt; est l’un des grands sages (&lt;em&gt;ṛṣi&lt;/em&gt;) des Upanishads, figure centrale de la &lt;a href="https://fr.wikipedia.org/wiki/Brihadaranyaka_Upanishad" title=" Wikipedia"&gt;&lt;em&gt;Brihadâranyaka Upanishad&lt;/em&gt;&lt;/a&gt;. La tradition lui attribue aussi la révélation du Yajur-Véda « blanc », le &lt;em&gt;Shatapatha Brâhmana&lt;/em&gt; et, bien plus tardivement, un célèbre traité de droit. Dans l’Upanishad, il développe une réflexion fondatrice sur l’identité entre le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et le principe universel (&lt;em&gt;brahman&lt;/em&gt;), posant les bases philosophiques du brahmanisme et, plus tard, du Vedânta.&lt;/p&gt; &lt;p&gt;L’Upanishad le montre à la cour du roi Janaka de Videha, où il remporte un grand tournoi de questions contre les brahmanes les plus savants, dont la philosophe Gârgî. Celle-ci l’interroge sur la trame de l’univers : tout est tissé sur l’espace, répond-il, et l’espace lui-même sur l’Impérissable (&lt;em&gt;akṣara&lt;/em&gt;), sous le commandement duquel se tiennent le soleil et la lune. Il y enseigne que le Soi ne peut être saisi comme un objet : « On ne peut voir le voyant de la vue, ni entendre l’entendeur de l’audition. » On ne peut le décrire que négativement : « Il n’est ni ceci, ni cela » (&lt;em&gt;neti neti&lt;/em&gt;). Insaisissable, il échappe au changement, à la souffrance et à la mort.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=tdfdWUqQrwE"  title="a masterpiece of indian philosophy par BharatVerse"&gt; Ses dialogues, &lt;/a&gt; notamment avec son épouse &lt;a href="https://fr.wikipedia.org/wiki/Maitreyi" title=" Wikipedia"&gt;Maitreyî&lt;/a&gt; sur la nature du désir et de la connaissance, comptent parmi les textes fondateurs de la métaphysique indienne. Sur le point de partir pour la vie d’ascète, il veut partager ses biens entre ses deux épouses ; Maitreyî lui demande si la richesse rend immortel, et il lui répond : « Ce n’est pas pour l’amour de l’époux que l’époux est cher, mais pour l’amour du Soi. » Ce passage a nourri toute la tradition du Vedânta.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F25" s="1" t="s">
         <v>203</v>
@@ -7384,8 +7386,10 @@
       <c r="D28" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>227</v>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kanada" title=" Wikipedia"&gt;Kanada&lt;/a&gt; (ou Kaṇāda) est le fondateur traditionnel de l’école Vaisheshika, l’une des six écoles orthodoxes de la philosophie indienne. Son nom signifie « mangeur de grains » : la légende raconte qu’il vivait des grains glanés dans les champs, mais on y voit aussi une allusion aux particules infimes au cœur de sa doctrine.&lt;/p&gt; &lt;p&gt;Auteur des &lt;em&gt;Vaisheshika-sûtras&lt;/em&gt;, il développe une physique atomiste : la réalité est composée de substances élémentaires indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;) combinées selon des catégories logiques précises. Les atomes de terre, d’eau, de feu et d’air sont éternels et invisibles ; ils s’unissent par deux, puis par trois, pour former les corps perceptibles. À ces quatre éléments s’ajoutent l’éther, le temps, l’espace, l’âme et le mental, soit neuf substances. Le réel se répartit en six catégories : la substance, la qualité, l’action, le général, le particulier et l’inhérence. C’est la « particularité » (&lt;em&gt;viśeṣa&lt;/em&gt;), qui distingue chaque atome et chaque âme, qui a donné son nom à l’école. On compare souvent cet &lt;a href="https://fr.wikipedia.org/wiki/Atomisme" title=" Wikipedia"&gt;atomisme&lt;/a&gt; à celui de Démocrite, mais ses atomes diffèrent par leurs qualités et sont mis en mouvement par une force invisible, liée aux actes des êtres.&lt;/p&gt; &lt;p&gt;Les sûtras s’ouvrent sur le &lt;em&gt;dharma&lt;/em&gt;, « ce qui procure la prospérité et le bien suprême » : connaître exactement les catégories du réel conduit à la délivrance. Cette approche fait du &lt;a href="https://www.youtube.com/watch?v=WDTGhajiZyo"  title="sage Kanada Vaisesika par Maynka Vadya"&gt; Vaisheshika &lt;/a&gt; l’une des premières tentatives systématiques de philosophie de la nature en Inde, plus tard fusionnée avec le &lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Nyâya&lt;/a&gt;. Ses commentateurs, à commencer par Prashastapada vers le VIe siècle, systématisèrent la doctrine, et les auteurs ultérieurs ajoutèrent une septième catégorie : la non-existence.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F28" s="1" t="s">
         <v>228</v>
@@ -7425,8 +7429,10 @@
       <c r="D29" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>236</v>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt; est le sage fondateur traditionnel du Sâmkhya, l’une des plus anciennes écoles de philosophie indienne. Sa figure appartient à la légende : la &lt;em&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhagavad-G%C4%ABt%C4%81" title=" Wikipedia"&gt;Bhagavad-Gîtâ&lt;/a&gt;&lt;/em&gt; le nomme parmi les sages accomplis, et les Purânas en font une incarnation de Vishnou enseignant la délivrance à sa mère. Aucun de ses écrits ne nous est parvenu ; le plus ancien exposé conservé de la doctrine, les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; d’Îshvarakrishna, date des premiers siècles de notre ère.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=PcOxBi1VRL4"  title="kapila and sankhya par foolish musings"&gt;Le Sâmkhya &lt;/a&gt; propose un dualisme radical entre la conscience pure (&lt;em&gt;puruṣa&lt;/em&gt;) et la matière primordiale (&lt;em&gt;prakṛti&lt;/em&gt;), dont l’évolution engendre l’ensemble du monde phénoménal. La matière est faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté, l’énergie et l’inertie ; de leur déséquilibre naissent successivement l’intellect, le sens du moi, le mental, les sens et les éléments, soit vingt-cinq principes en tout : le mot &lt;em&gt;sâmkhya&lt;/em&gt; signifie d’ailleurs « dénombrement ». L’effet préexiste dans sa cause, comme l’huile dans la graine de sésame. Ce dualisme de l’âme et de la matière rappelle celui du &lt;a href="https://www.youtube.com/watch?v=Q0AR1mxTME4&amp;t=106s&amp;ab_channel=Ja%C3%AFnisme-Uneintroduction"  title="Jaïnisme Introduction par Jaïnisme Université de Gent "&gt;jaïnisme &lt;/a&gt;, qui distingue lui aussi les âmes de la matière inerte.&lt;/p&gt; &lt;p&gt;La souffrance vient de ce que la conscience se confond avec les activités de la matière ; la délivrance (&lt;em&gt;kaivalya&lt;/em&gt;) est leur discernement, l’« isolement » de la conscience, spectatrice immobile. Contrairement au Vedânta, le Sâmkhya admet une infinité de consciences distinctes, une pour chaque être. Les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; comparent la matière à une danseuse qui se retire une fois qu’elle s’est montrée au spectateur. Cette cosmologie, indépendante de toute divinité créatrice, a profondément marqué l’hindouisme classique et sert de socle théorique aux &lt;a href="https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Yoga-sûtras&lt;/em&gt; de Patañjali&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F29" s="1" t="s">
         <v>237</v>
@@ -7466,8 +7472,10 @@
       <c r="D30" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>243</v>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Brihaspati" title=" Wikipedia"&gt;Brihaspati&lt;/a&gt; est le sage auquel la tradition attribue  &lt;a href="https://www.wisdomlib.org/fr/concept/brihaspati"  title="Brihaspati par wisdom library"&gt;la fondation du Lokâyata&lt;/a&gt;  (ou &lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka" title=" Wikipedia"&gt;Cârvâka&lt;/a&gt;), école matérialiste et athée de la philosophie indienne. Le nom est aussi celui du précepteur des dieux, et un récit des Purânas prétend qu’il aurait enseigné le matérialisme aux démons pour les égarer. Ses &lt;em&gt;Bârhaspatya-sûtras&lt;/em&gt; sont perdus : la doctrine n’est connue que par les citations de ses adversaires, notamment le &lt;em&gt;Sarva-darshana-samgraha&lt;/em&gt; de Mâdhava, au XIVe siècle.&lt;/p&gt; &lt;p&gt;Rejetant l’autorité des Védas, la réincarnation et toute réalité suprasensible, ce courant ne reconnaît comme source de connaissance valide que la perception directe. L’inférence est incertaine, car on ne peut jamais avoir observé tous les cas : une critique qui annonce le problème de l’induction. Le monde est fait de quatre éléments, terre, eau, feu et air, et la conscience naît de leur combinaison dans le corps, comme le pouvoir enivrant naît du mélange de certains ingrédients. Il n’y a donc pas d’âme qui survive à la mort, et le bonheur comme le malheur s’expliquent par la nature des choses, sans qu’il soit besoin d’invoquer le karma.&lt;/p&gt; &lt;p&gt;Le Lokâyata prône une éthique hédoniste centrée sur le plaisir dans cette vie : « Tant que tu vis, vis heureux ; une fois le corps réduit en cendres, comment reviendrait-il ? » Il raille les prêtres, qui vivraient des rites qu’ils prescrivent : si la victime sacrifiée monte au ciel, pourquoi le sacrifiant n’y envoie-t-il pas son propre père ? Et si les offrandes nourrissent les morts, pourquoi les voyageurs emportent-ils des provisions ? Le Lokâyata demeure la voix la plus radicalement sceptique de la pensée indienne classique.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F30" s="1" t="s">
         <v>244</v>
@@ -7771,8 +7779,10 @@
       <c r="D37" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>309</v>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ajivika" title=" Wikipedia"&gt;Makkhali Gosala&lt;/a&gt; est le principal fondateur de l’Ajîvika, courant hétérodoxe (&lt;em&gt;nâstika&lt;/em&gt;) contemporain du Bouddha et de &lt;a href="https://fr.wikipedia.org/wiki/Mah%C4%81v%C4%ABra" title=" Wikipedia"&gt;Mahâvîra&lt;/a&gt;. Ses écrits sont perdus, et on ne le connaît que par les textes de ses rivaux bouddhistes et jaïns, peu bienveillants. Son surnom de Gosala (« étable ») viendrait de ce qu’il y serait né. Selon les sources jaïnes, il fut pendant six ans le compagnon d’ascèse de Mahâvîra, avant une rupture violente : Gosala se proclamait lui aussi « vainqueur » (&lt;em&gt;jina&lt;/em&gt;) des passions, ce que Mahâvîra lui contestait. Il mourut à Shrâvastî dans l’atelier d’une potière qui le soutenait.&lt;/p&gt; &lt;p&gt;Il défend un déterminisme absolu (&lt;em&gt;niyati&lt;/em&gt;) : tout événement, y compris le destin de chaque âme à travers ses réincarnations, est fixé d’avance, rendant vain tout effort moral ou ascétique pour infléchir son sort. Les sages comme les sots traversent un nombre fixe de grands cycles avant de voir leur souffrance prendre fin, comme une pelote de fil lancée se déroule jusqu’à son terme. Tout dépend de la destinée, des circonstances et de la nature propre de chaque être, sans que les actes y changent rien. Le Bouddha jugeait cette doctrine la pire de toutes, car elle ôte à l’homme toute raison d’agir.&lt;/p&gt; &lt;p&gt;Les Ajîvikas étaient pourtant des ascètes rigoureux, vivant nus, mendiant leur nourriture et pratiquant le jeûne. L’empereur Ashoka et son petit-fils leur offrirent les &lt;a href="https://fr.wikipedia.org/wiki/Grottes_de_Barabar" title=" Wikipedia"&gt;grottes de Barabar&lt;/a&gt;, au Bihar, parmi les plus anciennes grottes artificielles de l’Inde. Bien que  &lt;a href="https://www.youtube.com/watch?v=4_LtAMsQgMM"   title="who were the ajjivika par jay Vardhan Singh"&gt; l’Ajîvika ait disparu &lt;/a&gt; vers le XIVe siècle, il constitue un jalon important de la pensée indienne sur le déterminisme et le libre arbitre.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F37" s="1" t="s">
         <v>310</v>
@@ -7902,8 +7912,10 @@
       <c r="D40" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>333</v>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jaimini" title=" Wikipedia"&gt;Jaimini&lt;/a&gt; est l’auteur traditionnel des &lt;em&gt;Mîmâmsâ-sûtras&lt;/em&gt;, texte fondateur de l’école &lt;a href="https://fr.wikipedia.org/wiki/Mimamsa" title=" Wikipedia"&gt;Mimamsa&lt;/a&gt; (ou Pûrva-Mîmâmsâ, « première investigation »), l’une des six écoles orthodoxes de la philosophie indienne. On ne sait presque rien de sa vie : la tradition en fait un disciple de Vyâsa, le compilateur légendaire des Védas.&lt;/p&gt; &lt;p&gt;Les &lt;em&gt;Mîmâmsâ-sûtras&lt;/em&gt;, environ 2 700 aphorismes répartis en douze livres, s’ouvrent sur ces mots : « Maintenant, donc, le désir de connaître le &lt;em&gt;dharma&lt;/em&gt; ». Le &lt;em&gt;dharma&lt;/em&gt;, c’est-à-dire le devoir rituel et moral, ne se connaît ni par la perception ni par le raisonnement, mais seulement par l’injonction védique : le Véda ne décrit pas le monde, il ordonne, comme dans la formule « que celui qui désire le ciel accomplisse le sacrifice ». Le Véda n’a pas d’auteur, ni humain ni divin : il est éternel, et le lien entre les mots et leur sens l’est aussi. Cette école orthodoxe se consacre donc à l’interprétation rigoureuse des textes védiques et de leurs prescriptions rituelles, en fixant des règles pour distinguer l’ordre principal du détail, lever les contradictions apparentes et déterminer qui doit accomplir quel rite.&lt;/p&gt; &lt;p&gt;Elle développe au passage une théorie du langage et de l’herméneutique parmi les plus sophistiquées de l’Inde ancienne, fondée sur l’autorité intrinsèque et éternelle du Véda. Commentée par Shabara, puis au VIIe siècle par &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumârila Bhatta&lt;/a&gt; et Prabhâkara, qui fondèrent deux écoles rivales, la Mîmâmsâ inspira durablement le droit hindou et prépara la voie au Vedânta, sa « seconde investigation ». Pour la Mîmâmsâ ancienne, nul dieu créateur n’est nécessaire : le rite produit ses fruits par sa propre force.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F40" s="1" t="s">
         <v>334</v>
@@ -8674,8 +8686,10 @@
       <c r="D58" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>489</v>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buddhaghosa" title=" Wikipedia"&gt;Buddhaghosa&lt;/a&gt; est le plus grand commentateur et systématisateur du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title=" Wikipedia"&gt;Theravâda&lt;/a&gt;. Selon les chroniques de Ceylan, il naquit dans une famille de brahmanes près de Bodh-Gaya, au Ve siècle, et se convertit après avoir été vaincu dans un débat par un moine bouddhiste. Une tradition birmane en fait au contraire un moine de Thaton, en Birmanie.&lt;/p&gt; &lt;p&gt;Moine originaire d’Inde établi au Sri Lanka, au grand monastère (&lt;em&gt;Mahâvihâra&lt;/em&gt;) d’Anurâdhapura, &lt;a href="https://www.babelio.com/auteur/-Buddhaghosa/231082/citations"   title="citations de Buddhaghosa par babelio"&gt;il rédige &lt;/a&gt; en pâli le &lt;a href="https://fr.wikipedia.org/wiki/Visuddhimagga" title=" Wikipedia"&gt;&lt;em&gt;Visuddhimagga&lt;/em&gt;&lt;/a&gt; (« Chemin de la pureté »), somme doctrinale qui organise l’ensemble de l’enseignement du Bouddha ancien autour de la discipline morale (&lt;em&gt;sīla&lt;/em&gt;), de la concentration (&lt;em&gt;samādhi&lt;/em&gt;) et de la sagesse (&lt;em&gt;paññā&lt;/em&gt;). Selon la légende, les moines l’avaient mis à l’épreuve avec deux strophes à commenter ; les dieux cachèrent deux fois son manuscrit, et il le récrivit à l’identique, si bien que les trois versions concordaient mot pour mot. L’ouvrage décrit avec précision quarante sujets de méditation et les sept étapes de la purification, de la conduite à la vision libératrice. Il y articule la méditation de quiétude (&lt;em&gt;samatha&lt;/em&gt;), qui apaise l’esprit, et celle de vision pénétrante (&lt;em&gt;vipassanā&lt;/em&gt;), qui en saisit l’impermanence.&lt;/p&gt; &lt;p&gt;Il traduisit aussi en pâli les anciens commentaires conservés en cinghalais et commenta la discipline monastique et les grands recueils de sermons. Fidèle à l’Abhidhamma, il analyse la personne en phénomènes momentanés, sans soi permanent. Son œuvre fixa l’interprétation orthodoxe des textes et demeure aujourd’hui encore la référence doctrinale du bouddhisme Theravâda, au Sri Lanka comme en Asie du Sud-Est.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F58" s="1" t="s">
         <v>490</v>
@@ -12776,402 +12790,416 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fatima_Mernissi" title=" Wikipedia"&gt;Fatima MERNISSI&lt;/a&gt; est une sociologue et écrivaine marocaine qui grandit dans une grande maison familiale où les femmes vivent à l'écart, enfance qu'elle racontera dans &lt;em&gt;Rêves de femmes&lt;/em&gt; (1994). Appartenant à la première génération de Marocaines scolarisées, elle étudie à Rabat, à Paris, puis aux États-Unis, où elle obtient un doctorat, avant d'enseigner la sociologie à l'université Mohammed V de Rabat.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;Sexe, idéologie, islam&lt;/em&gt; (1975), étudie la&lt;a href="https://scienceetbiencommun.pressbooks.pub/citoyennes/chapter/__unknown__/" title="Fatima Mernissi, sociologue, écrivaine et féministe marocaine par esbc"&gt; place faite aux femmes&lt;/a&gt; dans la société marocaine. Mais c'est &lt;em&gt;Le Harem politique&lt;/em&gt; (1987) qui la rend célèbre, et qui fut interdit dans son pays. Traduite dans de nombreuses langues, son œuvre a ouvert la voie à ce que l'on a appelé le féminisme islamique.&lt;/p&gt; &lt;p&gt;Elle y mène une &lt;a href="https://www.youtube.com/watch?v=Qb6iaPFs-ZI" title="Une vie : Fatima Mernissi par Brut"&gt;enquête d'historienne&lt;/a&gt; sur les paroles attribuées au Prophète qui servent à écarter les femmes de la vie publique. En utilisant les règles mêmes de la science religieuse traditionnelle, elle examine qui les a rapportées, à quel moment et dans quel intérêt, et montre leur fragilité. Pour elle, le message du Prophète était favorable à l'égalité ; ce sont les hommes de pouvoir qui, après lui, ont imposé une lecture hostile aux femmes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Sultanes oubliées&lt;/em&gt;, elle rappelle les femmes qui ont gouverné en terre d'islam. Elle a aussi retourné le regard vers l'Europe : &lt;em&gt;Le Harem et l'Occident&lt;/em&gt; montre que les femmes occidentales sont enfermées, elles, par la tyrannie de l'image et de la minceur. Elle a animé au Maroc de nombreux ateliers d'écriture et reçu en 2003 le prix Prince des Asturies. L'année suivante, le prix Érasme lui fut décerné en même temps qu'au philosophe iranien Abdolkarim Soroush.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdelk%C3%A9bir_Khatibi" title=" Wikipedia"&gt;Abdelkébir KHATIBI&lt;/a&gt; est un écrivain, sociologue et penseur marocain né à El Jadida. Il étudie la sociologie à la Sorbonne, où il soutient la première thèse consacrée au roman maghrébin, puis dirige à Rabat l'Institut de sociologie, et ensuite l'Institut universitaire de la recherche scientifique. Il a &lt;a href="https://www.contretemps.eu/abdelkebir-khatibi-principe-revolution/" title="Abdelkebir Khatibi, le principe révolution par contretemps"&gt;également animé &lt;/a&gt;pendant de longues années la principale revue marocaine de sciences sociales.&lt;/p&gt; &lt;p&gt;Son œuvre, écrite en français, mêle le roman, la poésie et l'essai. &lt;em&gt;La Mémoire tatouée&lt;/em&gt; (1971), sous-titrée « autobiographie d'un décolonisé », raconte son enfance entre deux langues et deux cultures. Il étudie aussi les signes de la culture populaire et savante du Maghreb : le tatouage, la calligraphie, le conte, le tapis. Roland Barthes lui rendit hommage dans un texte intitulé « Ce que je dois à Khatibi ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Maghreb pluriel&lt;/em&gt; (1983), il formule son idée centrale, la « double critique ». Pour décoloniser la pensée, il ne suffit pas de critiquer l'Occident et sa prétention à l'universel ; il faut critiquer en même temps son propre héritage, la théologie et le pouvoir patriarcal, sans quoi l'on ne fait que retourner le discours du maître. Il appelle &lt;a href="https://www.persee.fr/doc/horma_0984-2616_2009_num_60_1_2725" title="hommage à Abdelkébir Khatibi par persée"&gt;« pensée-autre » &lt;/a&gt;cette pensée qui ne se réfugie ni dans l'identité ni dans l'imitation.&lt;/p&gt; &lt;p&gt;Avec &lt;em&gt;Amour bilingue&lt;/em&gt;, il médite sur la « bi-langue » : écrire dans la langue de l'autre, habitée en secret par la langue maternelle, n'est pas une perte mais une chance. Jacques Derrida dialogue avec lui dans &lt;em&gt;Le Monolinguisme de l'autre&lt;/em&gt;. Il a aussi forgé le mot « aimance » pour désigner une relation d'affinité et d'hospitalité entre les êtres, les langues et les cultures.&lt;/p&gt;  &lt;audio controls title="Les arabes immigrés, traditions et racines par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/27050-16.09.2026-ITEMA_24673584-2023C3372E0379-NET_MFC_351639A3-9329-4471-B711-76D39FE2EEF5-25-c35cc310ff8a2a782c2f9f8d9928d6e9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">UQab1UXbrM4</t>
+          <t xml:space="preserve">f8Kms-rwdIc</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Fatima Mernissi : Islam et Féminisme" par ​L'Art de Comprendre</t>
+          <t xml:space="preserve">"Marc Gontard - Abdelkébir Khatibi de Selegan au déconstructivisme" par سلسلة لقاء مع الموجه</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fatimamernissi-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/abdelkebirkhatibi-mini.webp</t>
         </is>
       </c>
       <c r="J153" s="1" t="s">
         <v>1250</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>1043</v>
+        <v>1456</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>72</v>
+        <v>660</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P153" s="1" t="n">
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fatima_Mernissi" title=" Wikipedia"&gt;Fatima MERNISSI&lt;/a&gt; est une sociologue et écrivaine marocaine qui grandit dans une grande maison familiale où les femmes vivent à l'écart, enfance qu'elle racontera dans &lt;em&gt;Rêves de femmes&lt;/em&gt; (1994). Appartenant à la première génération de Marocaines scolarisées, elle étudie à Rabat, à Paris, puis aux États-Unis, où elle obtient un doctorat, avant d'enseigner la sociologie à l'université Mohammed V de Rabat.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;Sexe, idéologie, islam&lt;/em&gt; (1975), étudie la&lt;a href="https://scienceetbiencommun.pressbooks.pub/citoyennes/chapter/__unknown__/" title="Fatima Mernissi, sociologue, écrivaine et féministe marocaine par esbc"&gt; place faite aux femmes&lt;/a&gt; dans la société marocaine. Mais c'est &lt;em&gt;Le Harem politique&lt;/em&gt; (1987) qui la rend célèbre, et qui fut interdit dans son pays. Traduite dans de nombreuses langues, son œuvre a ouvert la voie à ce que l'on a appelé le féminisme islamique.&lt;/p&gt; &lt;p&gt;Elle y mène une &lt;a href="https://www.youtube.com/watch?v=Qb6iaPFs-ZI" title="Une vie : Fatima Mernissi par Brut"&gt;enquête d'historienne&lt;/a&gt; sur les paroles attribuées au Prophète qui servent à écarter les femmes de la vie publique. En utilisant les règles mêmes de la science religieuse traditionnelle, elle examine qui les a rapportées, à quel moment et dans quel intérêt, et montre leur fragilité. Pour elle, le message du Prophète était favorable à l'égalité ; ce sont les hommes de pouvoir qui, après lui, ont imposé une lecture hostile aux femmes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Sultanes oubliées&lt;/em&gt;, elle rappelle les femmes qui ont gouverné en terre d'islam. Elle a aussi retourné le regard vers l'Europe : &lt;em&gt;Le Harem et l'Occident&lt;/em&gt; montre que les femmes occidentales sont enfermées, elles, par la tyrannie de l'image et de la minceur. Elle a animé au Maroc de nombreux ateliers d'écriture et reçu en 2003 le prix Prince des Asturies. L'année suivante, le prix Érasme lui fut décerné en même temps qu'au philosophe iranien Abdolkarim Soroush.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UQab1UXbrM4</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Fatima Mernissi : Islam et Féminisme" par ​L'Art de Comprendre</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fatimamernissi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="N154" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="P154" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="n">
+    <row r="155" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="n">
         <v>1941</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B155" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D155" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="E154" s="2" t="s">
+      <c r="E155" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F155" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="G155" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="H154" s="2" t="s">
+      <c r="H155" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="J154" s="1" t="s">
+      <c r="J155" s="1" t="s">
         <v>1268</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="L154" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="M154" s="2" t="s">
-        <v>1269</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>1275</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>1276</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>1277</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>1192</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>1278</v>
+        <v>1061</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1279</v>
+        <v>1269</v>
       </c>
       <c r="O155" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="P155" s="1" t="n">
+    </row>
+    <row r="156" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O156" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="P156" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="n">
+    <row r="157" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="n">
         <v>1943</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="C157" s="2" t="s">
         <v>1280</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D157" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="E156" s="10" t="s">
+      <c r="E157" s="10" t="s">
         <v>1282</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F157" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G157" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="H156" s="2" t="s">
+      <c r="H157" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="J156" s="1" t="s">
+      <c r="J157" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K156" s="2" t="s">
+      <c r="K157" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L156" s="2" t="s">
+      <c r="L157" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="M156" s="2" t="s">
+      <c r="M157" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="O156" s="1" t="s">
+      <c r="O157" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
-      <c r="E157" s="1"/>
-      <c r="G157" s="1"/>
-      <c r="H157" s="1"/>
-      <c r="I157" s="1"/>
-      <c r="K157" s="1"/>
-      <c r="L157" s="1"/>
-      <c r="M157" s="1"/>
-    </row>
-    <row r="158" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="n">
+    <row r="158" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+      <c r="K158" s="1"/>
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+    </row>
+    <row r="159" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="n">
         <v>-1000</v>
       </c>
-      <c r="B158" s="1" t="n">
+      <c r="B159" s="1" t="n">
         <v>-900</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C159" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D159" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="E158" s="10" t="inlineStr">
+      <c r="E159" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_pessimisme" title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé en Mésopotamie qui met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître &lt;a href="http://www.aroumah.net/seminar/Dialogue%20of%20Pessimism.pdf"&gt;annonce tour à tour &lt;/a&gt;qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t xml:space="preserve">0aawol43UdU</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">"The Dialogue of Pessimism (Full Audiobook)" par abitof_ane_rd</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/dialoguedupessimisme-mini.webp</t>
-        </is>
-      </c>
-      <c r="J158" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; ethique</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M158" s="2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="O158" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B159" s="1" t="n">
-        <v>-640</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E159" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AX9Hmh5qJ9U</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
         </is>
       </c>
       <c r="J159" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K159" s="2" t="s">
-        <v>36</v>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
       </c>
       <c r="L159" s="2" t="s">
         <v>53</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
-        <v>-550</v>
+        <v>-700</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>-400</v>
+        <v>-640</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>1298</v>
+        <v>1293</v>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AX9Hmh5qJ9U</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
+        </is>
       </c>
       <c r="J160" s="1" t="s">
-        <v>396</v>
+        <v>51</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>398</v>
+        <v>53</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1299</v>
-      </c>
-      <c r="N160" s="1" t="s">
-        <v>400</v>
+        <v>1295</v>
       </c>
       <c r="O160" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P160" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
-        <v>-340</v>
+        <v>-550</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>-270</v>
+        <v>-400</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>51</v>
+        <v>396</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>1303</v>
+        <v>174</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>53</v>
+        <v>398</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>1304</v>
+        <v>1299</v>
+      </c>
+      <c r="N161" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O161" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="P161" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
-        <v>-250</v>
+        <v>-340</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>-220</v>
+        <v>-270</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="E162" s="10" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>396</v>
+        <v>51</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>107</v>
+        <v>1303</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>398</v>
+        <v>53</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="N162" s="1" t="s">
-        <v>400</v>
+        <v>1304</v>
       </c>
       <c r="O162" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="P162" s="1" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13179,60 +13207,66 @@
         <v>-250</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>-100</v>
+        <v>-220</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>27</v>
+        <v>398</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>1312</v>
+        <v>1308</v>
+      </c>
+      <c r="N163" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="P163" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
-        <v>154</v>
+        <v>-250</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>222</v>
+        <v>-100</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E164" s="10" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>1316</v>
+        <v>25</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>1317</v>
+        <v>27</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>29</v>
@@ -13240,139 +13274,139 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
-        <v>45</v>
+        <v>154</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>267</v>
+        <v>1316</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>296</v>
+        <v>1317</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>72</v>
+        <v>1318</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P165" s="1" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
-        <v>1130</v>
+        <v>45</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>1160</v>
+        <v>117</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="E166" s="10" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>427</v>
+        <v>62</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>641</v>
+        <v>296</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="N166" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>100</v>
+        <v>271</v>
+      </c>
+      <c r="P166" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
-        <v>832</v>
+        <v>1130</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>932</v>
+        <v>1160</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>396</v>
+        <v>96</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1330</v>
+        <v>641</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>400</v>
+        <v>72</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>401</v>
+        <v>100</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>138</v>
+        <v>346</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1336</v>
+        <v>1331</v>
+      </c>
+      <c r="N168" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>401</v>
@@ -13380,69 +13414,63 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
-        <v>874</v>
+        <v>853</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>545</v>
+        <v>147</v>
       </c>
       <c r="K169" s="2" t="s">
         <v>138</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P169" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="N170" s="1" t="s">
-        <v>400</v>
+        <v>1341</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>401</v>
@@ -13453,168 +13481,168 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1351</v>
+        <v>1346</v>
+      </c>
+      <c r="N171" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O171" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P171" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
-        <v>994</v>
+        <v>883</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>1064</v>
+        <v>931</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="J172" s="1" t="s">
         <v>545</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>1355</v>
+        <v>138</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1335</v>
+        <v>1350</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="O172" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P172" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>1088</v>
+        <v>1064</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>206</v>
+        <v>1355</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>511</v>
+        <v>1335</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="O173" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P173" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
-        <v>1021</v>
+        <v>1004</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>1058</v>
+        <v>1088</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>1364</v>
+        <v>206</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1330</v>
+        <v>511</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1365</v>
-      </c>
-      <c r="N174" s="1" t="s">
-        <v>400</v>
+        <v>1360</v>
       </c>
       <c r="O174" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P174" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
-        <v>1050</v>
+        <v>1021</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>1120</v>
+        <v>1058</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>397</v>
+        <v>1364</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>1369</v>
+        <v>1330</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="N175" s="1" t="s">
         <v>400</v>
@@ -13622,34 +13650,37 @@
       <c r="O175" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P175" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>1141</v>
+        <v>1120</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>742</v>
+        <v>397</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="N176" s="1" t="s">
         <v>400</v>
@@ -13657,37 +13688,34 @@
       <c r="O176" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P176" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
-        <v>1092</v>
+        <v>1075</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>1167</v>
+        <v>1141</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>546</v>
+        <v>742</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1330</v>
+        <v>1374</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="N177" s="1" t="s">
         <v>400</v>
@@ -13695,34 +13723,37 @@
       <c r="O177" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P177" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
-        <v>1110</v>
+        <v>1092</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>206</v>
+        <v>546</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1383</v>
+        <v>1330</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="N178" s="1" t="s">
         <v>400</v>
@@ -13733,31 +13764,34 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
-        <v>1150</v>
+        <v>1110</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>1210</v>
+        <v>1180</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>1388</v>
+        <v>206</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1340</v>
+        <v>1383</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1389</v>
+        <v>1384</v>
+      </c>
+      <c r="N179" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O179" s="1" t="s">
         <v>401</v>
@@ -13765,34 +13799,31 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>1270</v>
+        <v>1210</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>791</v>
+        <v>1388</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>1369</v>
+        <v>1340</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="N180" s="1" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>401</v>
@@ -13800,101 +13831,101 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
-        <v>1263</v>
+        <v>1194</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>1328</v>
+        <v>1270</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>1398</v>
+        <v>791</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1399</v>
+        <v>1369</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1400</v>
+        <v>1393</v>
+      </c>
+      <c r="N181" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O181" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P181" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
-        <v>1340</v>
+        <v>1263</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>1411</v>
+        <v>1328</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>231</v>
+        <v>1398</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1374</v>
+        <v>1399</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1404</v>
-      </c>
-      <c r="N182" s="1" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="O182" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P182" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
-        <v>1380</v>
+        <v>1340</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>1444</v>
+        <v>1411</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>1408</v>
+        <v>231</v>
       </c>
       <c r="L183" s="2" t="s">
         <v>1374</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="N183" s="1" t="s">
         <v>1394</v>
@@ -13905,31 +13936,31 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
-        <v>1437</v>
+        <v>1380</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>1508</v>
+        <v>1444</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="J184" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>1043</v>
+        <v>1408</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1413</v>
+        <v>1374</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="N184" s="1" t="s">
         <v>1394</v>
@@ -13940,31 +13971,34 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
-        <v>1561</v>
+        <v>1437</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>1631</v>
+        <v>1508</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>206</v>
+        <v>1043</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>775</v>
+        <v>1413</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1418</v>
+        <v>1414</v>
+      </c>
+      <c r="N185" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>401</v>
@@ -13972,136 +14006,133 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
-        <v>1801</v>
+        <v>1561</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>1873</v>
+        <v>1631</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1422</v>
+        <v>775</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="O186" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P186" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
-        <v>1849</v>
+        <v>1801</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>1905</v>
+        <v>1873</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>1408</v>
+        <v>304</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="O187" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P187" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
-        <v>1888</v>
+        <v>1849</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>1966</v>
+        <v>1905</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="J188" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>304</v>
+        <v>1408</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P188" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
-        <v>1905</v>
+        <v>1888</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>1973</v>
+        <v>1966</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1436</v>
+        <v>25</v>
       </c>
       <c r="K189" s="2" t="s">
         <v>304</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1259</v>
+        <v>1422</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="N189" s="1" t="s">
-        <v>660</v>
+        <v>1432</v>
       </c>
       <c r="O189" s="1" t="s">
         <v>401</v>
@@ -14109,142 +14140,142 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
-        <v>1928</v>
+        <v>1905</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>2010</v>
+        <v>1973</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>1436</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>26</v>
+        <v>304</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1441</v>
+        <v>1259</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>513</v>
+        <v>660</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P190" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>1977</v>
+        <v>2010</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>147</v>
+        <v>1436</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>1043</v>
+        <v>26</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="O191" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P191" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>2021</v>
+        <v>1977</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="K192" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1452</v>
+        <v>1447</v>
+      </c>
+      <c r="N192" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O192" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P192" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1250</v>
+        <v>25</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>1456</v>
+        <v>1043</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="N193" s="1" t="s">
-        <v>660</v>
+        <v>1452</v>
       </c>
       <c r="O193" s="1" t="s">
         <v>401</v>
@@ -16914,7 +16945,7 @@
     <hyperlink ref="E144" r:id="rId83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
     <hyperlink ref="E145" r:id="rId84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
     <hyperlink ref="H145" r:id="rId85" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
-    <hyperlink ref="H156" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
+    <hyperlink ref="H157" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -16849,142 +16849,147 @@
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="1">
+        <v>1946</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1977</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1946 – 1977</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steve BIKO</t>
+        </is>
+      </c>
+      <c r="E255" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Steve_Biko" title=" Wikipedia"&gt;Steve BIKO&lt;/a&gt; est un militant sud-africain de la lutte contre l’&lt;a href="https://fr.wikipedia.org/wiki/Apartheid" title=" Wikipedia"&gt;apartheid&lt;/a&gt; et le fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Mouvement_de_conscience_noire" title=" Wikipedia"&gt;Mouvement de la conscience noire&lt;/a&gt;. Né à King William’s Town, dans la province du Cap, il étudie la médecine à l’université du Natal. En 1969, il rompt avec le syndicat étudiant multiracial dominé par les Blancs et fonde la South African Students’ Organisation (SASO), réservée aux étudiants noirs, dont il devient le premier président. Il y rassemble Africains, Indiens et métis, tous désignés comme « Noirs » face au pouvoir blanc.&lt;/p&gt; &lt;p&gt;Pour lui, l’oppression ne s’exerce pas seulement par les lois, mais aussi dans les esprits : « L’arme la plus puissante entre les mains de l’oppresseur est l’esprit de l’opprimé. » La libération psychologique doit donc précéder la libération politique :&lt;a href="https://www.youtube.com/watch?v=FeNNeAsLpNo" title="STEVE BIKO, Un Symbole de la Résistance Noire par Renaissance africaine"&gt; les Noirs doivent cesser &lt;/a&gt;de se juger à travers le regard des Blancs, retrouver la fierté de leur culture et prendre eux-mêmes en main leur lutte, sans la tutelle, même bienveillante, des libéraux blancs. Nourrie de Fanon, de la &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude" title=" Wikipedia"&gt;négritude&lt;/a&gt; et du mouvement noir américain, sa pensée vise pourtant à terme une société sans race.&lt;/p&gt; &lt;p&gt;Interdit de parole et de déplacement à partir de 1973, il est arrêté en août 1977, torturé en détention et meurt le 12 septembre 1977, à trente ans, après avoir été transporté nu et sans soins jusqu’à Pretoria. Ses écrits sont réunis dans &lt;em&gt;I Write What I Like&lt;/em&gt; (« J’écris ce qui me plaît », 1978). Sa mort, devenue un symbole mondial de la lutte contre l’apartheid, a inspiré la chanson &lt;em&gt;Biko&lt;/em&gt; de Peter Gabriel et le film &lt;em&gt;Cry Freedom&lt;/em&gt;.&lt;/p&gt;  &lt;audio controls title="En Afrique du Sud avec la réouverture de l'enquête sur la mort de Steve Biko, 48 ans après son décès par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13958-15.09.2025-ITEMA_24246880-2025F33228S0258-NET_MFI_0623E44E-6117-4DF1-9729-F661211C1454-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iJA4mLzXjfg</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’Histoire Interdite de Steve Biko – Le Héros qui a Défie l’Apartheid" par Légendes et Vérités</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/biko-mini.webp</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sud-Africaine</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme ; Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">militant sud-africain contre l’apartheid, fondateur du Mouvement de la conscience noire.</t>
+        </is>
+      </c>
+      <c r="O255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P255" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A256" s="1" t="n">
         <v>1948</v>
       </c>
-      <c r="C255" s="2" t="s">
+      <c r="C256" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="D255" s="2" t="s">
+      <c r="D256" s="2" t="s">
         <v>1638</v>
       </c>
-      <c r="E255" s="10" t="inlineStr">
+      <c r="E256" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Do-ol" title=" Wikipedia (en)"&gt;KIM YONG-OK,&lt;/a&gt; connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de &lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi" title=" Wikipedia (en)"&gt;Choe Han-gi&lt;/a&gt;, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t xml:space="preserve">JDg8l7CsF8Y</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
+      <c r="G256" t="inlineStr">
         <is>
           <t xml:space="preserve">"[도올 김용옥]우리는 누구인가-동아시아 국제정세(대만편)_01" par jae hak Lee</t>
         </is>
       </c>
-      <c r="H255" s="2" t="s">
+      <c r="H256" s="2" t="s">
         <v>1640</v>
       </c>
-      <c r="J255" s="1" t="s">
+      <c r="J256" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="K255" s="2" t="s">
+      <c r="K256" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L255" s="2" t="s">
+      <c r="L256" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="M255" s="2" t="s">
+      <c r="M256" s="2" t="s">
         <v>1641</v>
       </c>
-      <c r="O255" s="1" t="s">
+      <c r="O256" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P255" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="1">
-        <v>1556</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1627</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1556 – 1627</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
-        </is>
-      </c>
-      <c r="E256" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
-        </is>
-      </c>
-      <c r="J256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Malienne</t>
-        </is>
-      </c>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie africaine</t>
-        </is>
-      </c>
-      <c r="M256" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="P256" s="1">
+      <c r="P256" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1">
-        <v>1901</v>
+        <v>1556</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1991</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901 – 1991</t>
+          <t xml:space="preserve">1556 – 1627</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
+          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
         </is>
       </c>
       <c r="E257" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
         </is>
       </c>
       <c r="J257" s="1" t="inlineStr">
@@ -16994,27 +16999,27 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
+          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O257" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="O257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="P257" s="1">
@@ -17023,51 +17028,56 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1">
-        <v>1912</v>
+        <v>1901</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981</t>
+          <t xml:space="preserve">1991</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912 – 1981</t>
+          <t xml:space="preserve">1901 – 1991</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexis KAGAME</t>
+          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
         </is>
       </c>
       <c r="E258" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
         </is>
       </c>
       <c r="J258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rwandaise</t>
+          <t xml:space="preserve">Malienne</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
+          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="O258" s="1" t="inlineStr">
@@ -17081,51 +17091,51 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1">
-        <v>1922</v>
+        <v>1912</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999</t>
+          <t xml:space="preserve">1981</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1999</t>
+          <t xml:space="preserve">1912 – 1981</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius NYERERE</t>
+          <t xml:space="preserve">Alexis KAGAME</t>
         </is>
       </c>
       <c r="E259" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
         </is>
       </c>
       <c r="J259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tanzanienne</t>
+          <t xml:space="preserve">Rwandaise</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
+          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr">
@@ -17139,36 +17149,36 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924 – 1973</t>
+          <t xml:space="preserve">1922 – 1999</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amílcar CABRAL</t>
+          <t xml:space="preserve">Julius NYERERE</t>
         </is>
       </c>
       <c r="E260" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
         </is>
       </c>
       <c r="J260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bissau-Guinéenne</t>
+          <t xml:space="preserve">Tanzanienne</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -17178,12 +17188,12 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
+          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
+          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr">
@@ -17197,51 +17207,51 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1">
-        <v>1931</v>
+        <v>1924</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">1973</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931 – 2019</t>
+          <t xml:space="preserve">1924 – 1973</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">John MBITI</t>
+          <t xml:space="preserve">Amílcar CABRAL</t>
         </is>
       </c>
       <c r="E261" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/John_Mbiti" title=" Wikipedia (en)"&gt;John MBITI&lt;/a&gt; est un philosophe et théologien kényan, pionnier de l’étude des religions africaines. Né à Kitui, dans l’est du Kenya, il étudie à l’université de Makerere, en Ouganda, puis aux États-Unis et à Cambridge, où il soutient un doctorat de théologie. Prêtre anglican, il enseigne à Makerere de 1964 à 1974, puis dirige l’Institut œcuménique du Conseil œcuménique des Églises, en Suisse, où il est ensuite pasteur à Burgdorf et professeur à l’université de Berne.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969), fondé sur de longues enquêtes, conteste l’idée répandue chez les missionnaires que les religions traditionnelles africaines seraient « démoniaques » : elles méritent selon lui le même respect que le christianisme, l’islam ou le bouddhisme. Il y propose une thèse célèbre sur le temps : dans les langues qu’il étudie, le temps se compose surtout du présent vécu (&lt;em&gt;sasa&lt;/em&gt;) et d’un passé profond (&lt;em&gt;zamani&lt;/em&gt;), le futur lointain restant presque absent. Les défunts dont on garde le souvenir, les « morts-vivants », appartiennent encore au présent de la communauté.&lt;/p&gt; &lt;p&gt;Il résume la conception africaine de la personne par une formule souvent citée : « Je suis parce que nous sommes, et puisque nous sommes, donc je suis », qui fait écho à la notion d’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;. Ses thèses ont été discutées, notamment par ceux qui lui reprochent de généraliser à toute l’Afrique des observations particulières, mais elles ont ouvert un champ immense à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;philosophie africaine&lt;/a&gt;. Il meurt à Burgdorf en 2019.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/jmbiti-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
         </is>
       </c>
       <c r="J261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kényane</t>
+          <t xml:space="preserve">Bissau-Guinéenne</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">théologien et philosophe kényan, auteur de Religions et philosophie africaines, penseur du temps africain.</t>
+          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr">
@@ -17255,31 +17265,31 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1">
-        <v>1944</v>
+        <v>1931</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995</t>
+          <t xml:space="preserve">2019</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944 – 1995</t>
+          <t xml:space="preserve">1931 – 2019</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henry ODERA ORUKA</t>
+          <t xml:space="preserve">John MBITI</t>
         </is>
       </c>
       <c r="E262" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/John_Mbiti" title=" Wikipedia (en)"&gt;John MBITI&lt;/a&gt; est un philosophe et théologien kényan, pionnier de l’étude des religions africaines. Né à Kitui, dans l’est du Kenya, il étudie à l’université de Makerere, en Ouganda, puis aux États-Unis et à Cambridge, où il soutient un doctorat de théologie. Prêtre anglican, il enseigne à Makerere de 1964 à 1974, puis dirige l’Institut œcuménique du Conseil œcuménique des Églises, en Suisse, où il est ensuite pasteur à Burgdorf et professeur à l’université de Berne.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969), fondé sur de longues enquêtes, conteste l’idée répandue chez les missionnaires que les religions traditionnelles africaines seraient « démoniaques » : elles méritent selon lui le même respect que le christianisme, l’islam ou le bouddhisme. Il y propose une thèse célèbre sur le temps : dans les langues qu’il étudie, le temps se compose surtout du présent vécu (&lt;em&gt;sasa&lt;/em&gt;) et d’un passé profond (&lt;em&gt;zamani&lt;/em&gt;), le futur lointain restant presque absent. Les défunts dont on garde le souvenir, les « morts-vivants », appartiennent encore au présent de la communauté.&lt;/p&gt; &lt;p&gt;Il résume la conception africaine de la personne par une formule souvent citée : « Je suis parce que nous sommes, et puisque nous sommes, donc je suis », qui fait écho à la notion d’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;. Ses thèses ont été discutées, notamment par ceux qui lui reprochent de généraliser à toute l’Afrique des observations particulières, mais elles ont ouvert un champ immense à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;philosophie africaine&lt;/a&gt;. Il meurt à Burgdorf en 2019.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jmbiti-mini.webp</t>
         </is>
       </c>
       <c r="J262" s="1" t="inlineStr">
@@ -17289,7 +17299,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; ethique</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
@@ -17299,7 +17309,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
+          <t xml:space="preserve">théologien et philosophe kényan, auteur de Religions et philosophie africaines, penseur du temps africain.</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr">
@@ -17313,51 +17323,51 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977</t>
+          <t xml:space="preserve">1995</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946 – 1977</t>
+          <t xml:space="preserve">1944 – 1995</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steve BIKO</t>
+          <t xml:space="preserve">Henry ODERA ORUKA</t>
         </is>
       </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Steve_Biko" title=" Wikipedia"&gt;Steve BIKO&lt;/a&gt; est un militant sud-africain de la lutte contre l’&lt;a href="https://fr.wikipedia.org/wiki/Apartheid" title=" Wikipedia"&gt;apartheid&lt;/a&gt; et le fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Mouvement_de_conscience_noire" title=" Wikipedia"&gt;Mouvement de la conscience noire&lt;/a&gt;. Né à King William’s Town, dans la province du Cap, il étudie la médecine à l’université du Natal. En 1969, il rompt avec le syndicat étudiant multiracial dominé par les Blancs et fonde la South African Students’ Organisation (SASO), réservée aux étudiants noirs, dont il devient le premier président. Il y rassemble Africains, Indiens et métis, tous désignés comme « Noirs » face au pouvoir blanc.&lt;/p&gt; &lt;p&gt;Pour Biko, l’oppression ne s’exerce pas seulement par les lois, mais aussi dans les esprits : « L’arme la plus puissante entre les mains de l’oppresseur est l’esprit de l’opprimé. » La libération psychologique doit donc précéder la libération politique : les Noirs doivent cesser de se juger à travers le regard des Blancs, retrouver la fierté de leur culture et prendre eux-mêmes en main leur lutte, sans la tutelle, même bienveillante, des libéraux blancs. Nourrie de Fanon, de la &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude" title=" Wikipedia"&gt;négritude&lt;/a&gt; et du mouvement noir américain, sa pensée vise pourtant à terme une société sans race.&lt;/p&gt; &lt;p&gt;Interdit de parole et de déplacement à partir de 1973, il est arrêté en août 1977, torturé en détention et meurt le 12 septembre 1977, à trente ans, après avoir été transporté nu et sans soins jusqu’à Pretoria. Ses écrits sont réunis dans &lt;em&gt;I Write What I Like&lt;/em&gt; (« J’écris ce qui me plaît », 1978). Sa mort, devenue un symbole mondial de la lutte contre l’apartheid, a inspiré la chanson &lt;em&gt;Biko&lt;/em&gt; de Peter Gabriel et le film &lt;em&gt;Cry Freedom&lt;/em&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/biko-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
         </is>
       </c>
       <c r="J263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sud-Africaine</t>
+          <t xml:space="preserve">Kényane</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; ethique</t>
         </is>
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Anticolonialisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">militant sud-africain contre l’apartheid, fondateur du Mouvement de la conscience noire.</t>
+          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr">
@@ -17894,6 +17904,122 @@
       </c>
       <c r="P272" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="1">
+        <v>1901</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1989</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1901 – 1989</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C. L. R. JAMES</t>
+        </is>
+      </c>
+      <c r="E273" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cyril_Lionel_Robert_James" title=" Wikipedia"&gt;C. L. R. JAMES&lt;/a&gt; (de son nom complet Cyril Lionel Robert James) est un historien, théoricien marxiste et militant né à Trinidad, alors colonie britannique, dans une famille descendant d’esclaves. Fils d’instituteur, élève brillant et rebelle, passionné de cricket et de littérature anglaise, il enseigne d’abord à Port-d’Espagne avant de partir en 1932 pour l’Angleterre, où il devient journaliste sportif, militant trotskiste et panafricaniste, aux côtés de son ami d’enfance George Padmore.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Les Jacobins noirs&lt;/em&gt; (1938) raconte la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_ha%C3%AFtienne" title=" Wikipedia"&gt;révolution de Saint-Domingue&lt;/a&gt; et la vie de &lt;a href="https://fr.wikipedia.org/wiki/Toussaint_Louverture" title=" Wikipedia"&gt;Toussaint Louverture&lt;/a&gt; : pour la première fois, des esclaves y apparaissent non comme des victimes passives, mais comme les acteurs d’une révolution qui pousse jusqu’au bout les idéaux de la Révolution française. Cet ouvrage, devenu un classique, montre que les peuples colonisés font eux-mêmes leur histoire. Installé aux États-Unis de 1938 à 1953, James y développe un marxisme qui fait confiance à l’auto-organisation des travailleurs plutôt qu’aux partis d’avant-garde, avant d’être expulsé en pleine guerre froide.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Beyond a Boundary&lt;/em&gt; (1963), il fait du cricket un miroir de la société coloniale, de ses hiérarchies de race et de classe, mais aussi un art populaire : « Que savent du cricket ceux qui ne connaissent que le cricket ? » Il inspire les mouvements d’indépendance des Caraïbes et de l’Afrique, de Nkrumah aux militants noirs américains, et défend une fédération des Antilles. Il meurt à Londres en 1989.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/clrjames-mini.webp</t>
+        </is>
+      </c>
+      <c r="J273" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidadienne</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme ; Pan-africanisme</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien et théoricien marxiste de Trinidad, auteur des Jacobins noirs, penseur de l’émancipation des peuples colonisés.</t>
+        </is>
+      </c>
+      <c r="O273" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P273" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A274" s="1">
+        <v>1928</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2011</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928 – 2011</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Édouard GLISSANT</t>
+        </is>
+      </c>
+      <c r="E274" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Glissant" title=" Wikipedia"&gt;Édouard GLISSANT&lt;/a&gt; est un poète, romancier et philosophe martiniquais, l’un des penseurs majeurs des Caraïbes et de la mondialisation. Né à Sainte-Marie, en &lt;a href="https://fr.wikipedia.org/wiki/Martinique" title=" Wikipedia"&gt;Martinique&lt;/a&gt;, il étudie la philosophie à la Sorbonne et l’ethnologie au musée de l’Homme. Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/La_L%C3%A9zarde" title=" Wikipedia"&gt;&lt;em&gt;La Lézarde&lt;/em&gt;&lt;/a&gt;, reçoit le prix Renaudot en 1958. Militant de la décolonisation, il cofonde en 1961 un front pour l’autonomie des Antilles, ce qui lui vaut d’être interdit de retour en Martinique pendant plusieurs années. Il participe aussi aux congrès des écrivains et artistes noirs de 1956 et 1959.&lt;/p&gt; &lt;p&gt;Héritier de Césaire, il veut dépasser la négritude, qui cherche une origine africaine perdue. Dans &lt;em&gt;Le Discours antillais&lt;/em&gt; (1981), il propose l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : une identité née du mélange, de la plantation et de l’oubli, qui ne se réduit à aucune racine unique. Il oppose l’« identité-racine », exclusive et fondée sur une seule origine, à l’« identité-relation », ouverte à l’autre, et la pensée de « système », qui veut tout ramener à l’unité, à la « pensée de l’archipel », attentive aux liens entre des îles toutes différentes.&lt;/p&gt; &lt;p&gt;La « créolisation » est pour lui le mouvement même du monde actuel : des cultures se rencontrent et produisent du nouveau, de manière imprévisible. Dans &lt;a href="https://fr.wikipedia.org/wiki/Po%C3%A9tique_de_la_Relation" title=" Wikipedia"&gt;&lt;em&gt;Poétique de la Relation&lt;/em&gt;&lt;/a&gt; (1990), il défend un « droit à l’opacité » : comprendre l’autre ne doit pas signifier le réduire à soi. Directeur du &lt;em&gt;Courrier de l’UNESCO&lt;/em&gt; de 1981 à 1988, puis professeur à New York, il fonde en 2006 à Paris l’Institut du &lt;a href="https://fr.wikipedia.org/wiki/Tout-Monde" title=" Wikipedia"&gt;Tout-Monde&lt;/a&gt; et meurt en 2011.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/glissant-mini.webp</t>
+        </is>
+      </c>
+      <c r="J274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martiniquaise</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poète, romancier et philosophe martiniquais, penseur de la Relation, de la créolisation et du Tout-monde.</t>
+        </is>
+      </c>
+      <c r="O274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P274" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -18022,6 +18022,238 @@
         <v>3</v>
       </c>
     </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A275" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1052 – 1135</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MILARÉPA</t>
+        </is>
+      </c>
+      <c r="E275" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Milar%C3%A9pa" title=" Wikipedia"&gt;MILARÉPA&lt;/a&gt; est un yogi et poète tibétain, devenu l’un des plus grands saints du bouddhisme tibétain. Selon sa célèbre biographie, rédigée au XVe siècle, son père meurt alors qu’il est enfant, et son oncle et sa tante s’emparent des biens de la famille, réduisant sa mère et sa sœur à la misère. Poussé par sa mère à se venger, il apprend la magie noire et fait périr plusieurs personnes en provoquant l’effondrement d’une maison et une tempête de grêle.&lt;/p&gt; &lt;p&gt;Rongé par le remords, il cherche un maître et trouve &lt;a href="https://fr.wikipedia.org/wiki/Marpa_le_Traducteur" title=" Wikipedia"&gt;Marpa le Traducteur&lt;/a&gt;, qui avait rapporté de l’Inde les enseignements de Naropa. Pendant des années, Marpa lui impose des épreuves terribles, comme bâtir puis démolir plusieurs fois des tours de pierre, pour le purifier de ses fautes avant de lui transmettre son enseignement. Milarépa se retire alors dans des grottes de l’Himalaya, où il médite pendant des années dans le froid et la solitude, vêtu d’un simple tissu de coton, d’où son nom de « Mila le vêtu de coton », et se nourrit, dit-on, d’orties, au point que sa peau en devient verte.&lt;/p&gt; &lt;p&gt;Il atteint l’éveil en une seule vie, montrant que même un grand criminel peut se transformer. Il enseigne par des chants improvisés, réunis dans les &lt;em&gt;Cent Mille Chants&lt;/em&gt;, où il parle de l’impermanence, de la mort et de la nature de l’esprit avec une liberté et une simplicité qui en font l’un des poètes les plus aimés du Tibet. Sa vie, contée dans &lt;em&gt;La Vie de Milarépa&lt;/em&gt;, a été comparée aux Évangiles. Il est l’un des fondateurs de l’école &lt;a href="https://fr.wikipedia.org/wiki/Kagy%C3%BCpa" title=" Wikipedia"&gt;Kagyü&lt;/a&gt;, que développera son disciple Gampopa.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/milarepa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J275" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tibétaine</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yogi et poète tibétain, ancien magicien devenu le plus célèbre des saints du Tibet.</t>
+        </is>
+      </c>
+      <c r="O275" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P275" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A276" s="1">
+        <v>1079</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079 – 1153</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAMPOPA</t>
+        </is>
+      </c>
+      <c r="E276" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gampopa" title=" Wikipedia"&gt;GAMPOPA&lt;/a&gt; est un maître du bouddhisme tibétain, disciple de Milarépa et véritable fondateur de l’école Kagyü. Né dans le sud-est du Tibet, il apprend d’abord la médecine auprès de son père, d’où son surnom de « médecin de Dagpo ». Marié jeune, il perd à quelques jours d’intervalle ses deux enfants, puis sa femme, emportés par une épidémie. Devant sa femme mourante, qu’il ne parvient pas à guérir, il comprend que toute chose est impermanente et lui promet de consacrer sa vie au Dharma.&lt;/p&gt; &lt;p&gt;Devenu moine dans un monastère de l’école Kadampa, connue pour son enseignement rigoureux et progressif, il étudie la discipline monastique et la « voie graduée » vers l’éveil. Ayant entendu parler de Milarépa par des mendiants, il part à sa recherche et reçoit de lui les pratiques de méditation des yogis, notamment celle du &lt;a href="https://fr.wikipedia.org/wiki/Mahamudra" title=" Wikipedia"&gt;mahamudra&lt;/a&gt;, le « grand sceau », qui vise à reconnaître directement la nature de l’esprit.&lt;/p&gt; &lt;p&gt;Son génie est d’unir ces deux traditions : la vie monastique et l’étude méthodique des Kadampas, et l’expérience directe des yogis ermites comme Milarépa. Son traité &lt;em&gt;L’Ornement de la libération&lt;/em&gt; expose pas à pas le chemin, de la prise de conscience de la valeur d’une vie humaine et de l’impermanence jusqu’à l’éveil, en passant par la compassion et les six perfections. Il y rappelle que tous les êtres possèdent la &lt;a href="https://fr.wikipedia.org/wiki/Nature_de_bouddha" title=" Wikipedia"&gt;nature de bouddha&lt;/a&gt;, cause première de l’éveil. Il fonde le monastère de Dagla Gampo, d’où il tire son nom. Ses disciples fondent les quatre grandes branches de l’école Kagyü, dont celle des Karmapas, toujours vivante aujourd’hui.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gampopa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J276" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tibétaine</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">médecin devenu moine, disciple de Milarépa, fondateur de l’école Kagyü du bouddhisme tibétain.</t>
+        </is>
+      </c>
+      <c r="O276" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P276" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A277" s="1">
+        <v>1876</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1924</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1876 – 1924</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ziya GÖKALP</t>
+        </is>
+      </c>
+      <c r="E277" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ziya_G%C3%B6kalp" title=" Wikipedia"&gt;Ziya GÖKALP&lt;/a&gt; est un sociologue, écrivain et poète turc, le principal théoricien du nationalisme turc. Né à Çermik, près de Diyarbakır, dans une famille de lettrés, il étudie à Istanbul, où il est arrêté en 1898 pour ses liens avec les opposants au sultan. Après la révolution jeune-turque de 1908, il entre au comité central du &lt;a href="https://fr.wikipedia.org/wiki/Comit%C3%A9_union_et_progr%C3%A8s" title=" Wikipedia"&gt;Comité union et progrès&lt;/a&gt;, le parti au pouvoir, et adopte le nom de Gökalp, « héros du ciel ». Il enseigne la sociologie à Salonique, puis à l’université d’Istanbul de 1913 à 1919.&lt;/p&gt; &lt;p&gt;Lecteur d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mile_Durkheim" title=" Wikipedia"&gt;Émile Durkheim&lt;/a&gt;, dont il introduit la sociologie en Turquie, il distingue la culture, propre à chaque nation, faite de sa langue, de ses mœurs et de ses valeurs, et la civilisation, internationale, faite des sciences et des techniques que les peuples se transmettent. Les Turcs peuvent donc emprunter à l’Europe sa civilisation tout en gardant leur culture. D’où sa formule : « Se turquiser, s’islamiser, se moderniser. » Il définit la nation par la langue et la culture, et non par la race.&lt;/p&gt; &lt;p&gt;Après la défaite de 1918, il est arrêté par les Britanniques et exilé à Malte. Ses idées ont profondément inspiré &lt;a href="https://fr.wikipedia.org/wiki/Mustafa_Kemal_Atat%C3%BCrk" title=" Wikipedia"&gt;Mustafa Kemal Atatürk&lt;/a&gt; et la république fondée en 1923 : l’usage de la langue turque, la séparation de la religion et de l’État, la modernisation de l’éducation. Elles restent aussi discutées, car le nationalisme qu’il a nourri s’est accompagné, dans les dernières années de l’Empire ottoman, de la persécution des minorités. Il meurt à Istanbul en 1924.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gokalp-mini.webp</t>
+        </is>
+      </c>
+      <c r="J277" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turque</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sociologue et poète turc, théoricien du nationalisme turc, inspirateur des réformes d’Atatürk.</t>
+        </is>
+      </c>
+      <c r="O277" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P277" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A278" s="1">
+        <v>1909</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1975</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1909 – 1975</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nurettin TOPÇU</t>
+        </is>
+      </c>
+      <c r="E278" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://tr.wikipedia.org/wiki/Nurettin_Top%C3%A7u" title=" Wikipedia (tr)"&gt;Nurettin TOPÇU&lt;/a&gt; est un philosophe, écrivain et enseignant turc, l’une des grandes figures de la pensée conservatrice et spirituelle de la Turquie républicaine. Né à Istanbul dans une famille originaire d’Erzurum, il obtient en 1928 une bourse pour étudier en France. Il suit des cours à Aix-en-Provence, où il découvre la philosophie de Maurice Blondel, avec qui il correspond, puis étudie la philosophie à Strasbourg et y rencontre l’historien du soufisme &lt;a href="https://fr.wikipedia.org/wiki/Louis_Massignon" title=" Wikipedia"&gt;Louis Massignon&lt;/a&gt;, à qui il donne des leçons de turc.&lt;/p&gt; &lt;p&gt;En 1934, il soutient à la Sorbonne une thèse intitulée &lt;em&gt;Conformisme et révolte&lt;/em&gt;, publiée la même année à Paris : il est le premier Turc à y obtenir un doctorat de philosophie. Il y oppose le conformisme, qui soumet l’individu aux habitudes et aux pouvoirs de la société, à la « révolte » morale, par laquelle la personne s’arrache à ce qui l’aliène pour répondre à une exigence intérieure. Inspirée de Blondel, cette philosophie de l’action voit dans l’acte libre et responsable le lieu où l’homme rencontre l’absolu.&lt;/p&gt; &lt;p&gt;Rentré en Turquie, il enseigne la philosophie dans les lycées d’Istanbul pendant plus de trente ans et fonde en 1939 la revue &lt;em&gt;Hareket&lt;/em&gt; (« Mouvement »). Il défend un humanisme spirituel enraciné dans l’Anatolie, dans la mystique musulmane et dans la justice sociale, et critique à la fois le matérialisme, le capitalisme et un nationalisme sans âme. Il meurt à Istanbul en 1975. Ses œuvres complètes, rééditées depuis, continuent d’influencer la pensée turque contemporaine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/topcu-mini.webp</t>
+        </is>
+      </c>
+      <c r="J278" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turque</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme ; Soufisme</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe turc, penseur de la « morale de la révolte » et d’un humanisme spirituel nourri de Blondel et du soufisme.</t>
+        </is>
+      </c>
+      <c r="O278" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P278" s="1">
+        <v>2</v>
+      </c>
+    </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -12425,86 +12425,110 @@
         <v>271</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="n">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1">
+        <v>1906</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1993</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1906 – 1993</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUDDHADASA Bhikkhu</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buddhadasa" title=" Wikipedia"&gt;BUDDHADASA Bhikkhu&lt;/a&gt; est un moine bouddhiste thaïlandais, l’un des grands réformateurs du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title=" Wikipedia"&gt;Theravâda&lt;/a&gt; au XXe siècle. Son nom signifie « serviteur du Bouddha ». Fils d’un commerçant du sud de la Thaïlande, ordonné moine en 1926, il part étudier à Bangkok, mais il est déçu par des monastères qu’il juge plus soucieux de prestige que de libération. Il rentre&lt;a href="https://www.youtube.com/watch?v=8XrO_mjL9E4" title="Life and Work of Buddhadasa Bhikkhu par Buddhist Insights"&gt; dans sa région natale &lt;/a&gt;et fonde en 1932, dans une forêt, Suan Mokkh, le « jardin de la libération », qui deviendra un lieu de retraite pour des pratiquants du monde entier.&lt;/p&gt; &lt;p&gt;Revenant aux textes anciens en pâli, il veut dégager le cœur de l’enseignement du Bouddha des rituels, des superstitions et du commerce des mérites. Il distingue la « langue des gens », qui prend les mots à la lettre, et la « langue du dhamma », qui en saisit le sens profond. Ainsi, la renaissance ne désigne pas d’abord le passage d’une vie à une autre, mais la naissance du sentiment de « moi » et de « mien », qui se produit à chaque instant et que la pratique doit apprendre à défaire. Son idéal est un esprit « libre et vide » de cet attachement.&lt;/p&gt; &lt;p&gt;Persuadé qu’au fond toutes les religions disent la même chose, il dialogue avec des chrétiens et des musulmans. Il propose aussi un «&lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1988_num_205_2_1932" title="Bhikkhu Buddhadasa. Bouddhisme et socialismes par Persée"&gt; socialisme du dhamma &lt;/a&gt;», qui fonde l’organisation de la société sur la modération et le partage plutôt que sur l’accumulation. Pendant les années démocratiques de 1973 à 1976, ses idées sont largement diffusées, et il débat à la télévision avec l’homme politique Kukrit Pramoj.&amp;nbsp;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B7qLDffCy_s</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"8612 - [3 of 6] TheThings Called 'The Five Khandhas' | Buddhadāsa Bhikkhu" par Buddhadasa Bhikkhu</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/buddhadasa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J144" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thaïlandaise</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Theravada</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine bouddhiste thaïlandais, réformateur du Theravâda, penseur du « socialisme du dhamma ».</t>
+        </is>
+      </c>
+      <c r="O144" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P144" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="n">
         <v>1909</v>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B145" s="1" t="n">
         <v>1972</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D145" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="G145" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="H144" s="2" t="s">
+      <c r="H145" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="J144" s="1" t="s">
+      <c r="J145" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="K144" s="2" t="s">
+      <c r="K145" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L144" s="1" t="s">
+      <c r="L145" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="M144" s="2" t="s">
+      <c r="M145" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="O144" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P144" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B145" s="1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E145" s="22" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="K145" s="2" t="s">
-        <v>1159</v>
-      </c>
-      <c r="L145" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="M145" s="2" t="s">
-        <v>1184</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>660</v>
@@ -12513,130 +12537,130 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="54.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="236.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E146" s="22" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="P146" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="54.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="n">
         <v>1917</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>1187</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E147" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F147" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="G147" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="H146" s="2" t="s">
+      <c r="H147" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="J147" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="K146" s="2" t="s">
+      <c r="K147" s="2" t="s">
         <v>1192</v>
       </c>
-      <c r="L146" s="2" t="s">
+      <c r="L147" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="M146" s="2" t="s">
+      <c r="M147" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="N146" s="1" t="s">
+      <c r="N147" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="O146" s="1" t="s">
+      <c r="O147" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="n">
+    <row r="148" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="n">
         <v>1923</v>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B148" s="1" t="n">
         <v>1986</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>1195</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="E147" s="22" t="s">
+      <c r="E148" s="22" t="s">
         <v>1197</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="F148" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="G148" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="H148" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="J148" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="K147" s="2" t="s">
+      <c r="K148" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="L147" s="2" t="s">
+      <c r="L148" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="M147" s="2" t="s">
+      <c r="M148" s="2" t="s">
         <v>1201</v>
-      </c>
-      <c r="O147" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P147" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B148" s="1" t="n">
-        <v>1961</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E148" s="22" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L148" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="M148" s="2" t="s">
-        <v>1209</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>660</v>
@@ -12645,781 +12669,852 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E149" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="P149" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="n">
         <v>1930</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B150" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="C150" s="2" t="s">
         <v>1732</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D150" s="2" t="s">
         <v>1733</v>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="E150" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Li_Zehou" title=" Wikipedia"&gt;LI Zehou&lt;/a&gt; est l’un des philosophes chinois les plus influents de la seconde moitié du XXe siècle. Originaire du Hunan, diplômé de philosophie de l’université de Pékin en 1954, il se fit connaître dès les années 1950 dans les grands débats sur l’esthétique, puis devint, dans les années 1980, le maître à penser de toute une génération d’étudiants chinois.&lt;/p&gt; &lt;p&gt;Lecteur de Kant et de Marx, il soutient que les formes de la sensibilité et de la raison ne sont pas données d’avance, mais se sont formées au cours de l’histoire humaine, par la fabrication et l’usage des outils : c’est ce qu’il appelle la « sédimentation ». Le beau est ainsi « la forme de la liberté »,&lt;a href="https://www.youtube.com/watch?v=JEfuhVCN-fU" title="Hidden Truths About Confucius and Li Zehou's Philosophical par Vis Philo"&gt; l’humanisation de la nature&lt;/a&gt; par le travail collectif. Son livre &lt;em&gt;Le Chemin de la beauté&lt;/em&gt; (1981), qui parcourt l’histoire de l’art chinois, fut un immense succès. Il propose aussi de comprendre la culture chinoise comme une « culture de la joie » et du sentiment, plutôt que de la faute et du salut.&lt;/p&gt; &lt;p&gt;Après les événements de Tiananmen en 1989, ses ouvrages furent critiqués et il s’installa en 1992 aux États-Unis, où il enseigna dans plusieurs universités ; il mourut en 2021 à Boulder, dans le Colorado.&lt;a href="https://www.loyolaparis.fr/wp-content/uploads/2022/03/103-coin-des-penseurs-mars-2022.pdf" title="En mémoire à Li Zehou par loyolaparis"&gt; Dans ses derniers livres&lt;/a&gt;, il développe une « ontologie du sentiment » qui fait des émotions, cultivées par les rites et la musique, le fondement de la vie morale. Il est l’un des rares philosophes chinois contemporains à figurer dans la grande anthologie Norton de théorie et de critique littéraires.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t xml:space="preserve">p4w9h3oS5Hc</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">"What Confucius and Li Zehou Can Teach Us About the True Meaning of Life?" par VIS PHILO.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="s">
+      <c r="H150" s="2" t="s">
         <v>1735</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="J150" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="K149" s="2" t="s">
+      <c r="K150" s="2" t="s">
         <v>1736</v>
       </c>
-      <c r="L149" s="2" t="s">
+      <c r="L150" s="2" t="s">
         <v>1193</v>
       </c>
-      <c r="M149" s="2" t="s">
+      <c r="M150" s="2" t="s">
         <v>1737</v>
       </c>
-      <c r="O149" s="1" t="s">
+      <c r="O150" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P149" s="1" t="n">
+      <c r="P150" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="n">
-        <v>1931</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>1216</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="M150" s="2" t="s">
-        <v>1218</v>
-      </c>
-      <c r="O150" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="272.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="n">
         <v>1931</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1219</v>
+        <v>1210</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1220</v>
+        <v>1211</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>1222</v>
+        <v>1212</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>1213</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1224</v>
+        <v>1215</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1225</v>
+        <v>1216</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1000</v>
+        <v>1217</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>1001</v>
+        <v>848</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>952</v>
+        <v>1061</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="P151" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="152" customFormat="false" ht="307.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>1230</v>
+        <v>1221</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>1222</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>1217</v>
+        <v>1000</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>80</v>
+        <v>1001</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>1061</v>
+        <v>952</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="153" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P152" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>1227</v>
+        <v>1928</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>2010</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1235</v>
+        <v>1438</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E153" s="20" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>1239</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1240</v>
+        <v>1439</v>
+      </c>
+      <c r="E153" s="10" t="s">
+        <v>1440</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>1241</v>
+        <v>1436</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>1001</v>
+        <v>26</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>952</v>
+        <v>1441</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>1242</v>
+        <v>1442</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>72</v>
+        <v>513</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E154" s="10" t="s">
-        <v>1246</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="J154" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="L154" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="M154" s="2" t="s">
-        <v>1251</v>
-      </c>
-      <c r="O154" s="1" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="155" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P153" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1">
+        <v>1931</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931 – 2019</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">John MBITI</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/John_Mbiti" title=" Wikipedia (en)"&gt;John MBITI&lt;/a&gt; est un philosophe et théologien kényan, pionnier de l’étude des religions africaines. Né à Kitui, dans l’est du Kenya, il étudie à l’université de Makerere, en Ouganda, puis aux États-Unis et à Cambridge, où il soutient un doctorat de théologie. Prêtre anglican, il enseigne à Makerere de 1964 à 1974, puis dirige l’Institut œcuménique du Conseil œcuménique des Églises, en Suisse, où il est ensuite pasteur à Burgdorf et professeur à l’université de Berne.&lt;/p&gt; &lt;p&gt;Son livre&lt;a href="https://www.youtube.com/watch?v=DElzy-ho9SA" title="Was Mbiti right? Why Africa struggles to build the future par In My Own Personal Opinion"&gt; &lt;em&gt;Religions et philosophie africaines&lt;/em&gt;&lt;/a&gt; (1969), fondé sur de longues enquêtes, conteste l’idée répandue chez les missionnaires que les religions traditionnelles africaines seraient « démoniaques » : elles méritent selon lui le même respect que le christianisme, l’islam ou le bouddhisme. Il y propose une thèse célèbre sur le temps : dans les langues qu’il étudie, le temps se compose surtout du présent vécu (&lt;em&gt;sasa&lt;/em&gt;) et d’un passé profond (&lt;em&gt;zamani&lt;/em&gt;), le futur lointain restant presque absent. Les défunts dont on garde le souvenir, les « morts-vivants », appartiennent encore au présent de la communauté.&lt;/p&gt; &lt;p&gt;Il résume la conception africaine de la personne par une formule souvent citée : « Je suis parce que nous sommes, et puisque nous sommes, donc je suis », qui fait écho à la notion d’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;. Ses thèses ont été discutées, notamment par ceux qui lui reprochent de généraliser à toute l’Afrique des observations particulières, mais elles ont ouvert un champ immense à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;philosophie africaine&lt;/a&gt;. Il meurt à Burgdorf en 2019.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mIaNQw1ECeI</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Prof Mbiti Interview Full" par Missio Africanus</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jmbiti-mini.webp</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kényane</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie africaine</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien et philosophe kényan, auteur de Religions et philosophie africaines, penseur du temps africain.</t>
+        </is>
+      </c>
+      <c r="O154" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P154" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>2005</v>
+        <v>1977</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1252</v>
+        <v>1443</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E155" s="10" t="s">
-        <v>1254</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>1257</v>
+        <v>1444</v>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%27Al%C3%AE_Shar%C3%AE%27at%C3%AE" title=" Wikipedia"&gt;Ali SHARIATI&lt;/a&gt; est un sociologue et penseur iranien né dans un village du Khorassan et mort à Southampton, en Angleterre, en 1977. Fils d'un prédicateur réformateur, il part en 1959 étudier à Paris, où il soutient un doctorat à la Sorbonne. Il y suit les cours de l'orientaliste Louis Massignon, s'engage aux côtés des Algériens en lutte pour leur indépendance et découvre Sartre et Frantz Fanon, qu'il contribue à faire connaître en Iran.&lt;/p&gt; &lt;p&gt;De retour en 1964, il est arrêté, puis enseigne à Mashhad. À partir de 1969, ses conférences dans un centre religieux de Téhéran attirent des milliers d'étudiants, et&lt;a href="https://www.youtube.com/watch?v=B0A3DJotbp4" title="Construire l'identité révolutionnaire par le Dr. Ali Shariati par Incroyable Maisvrai"&gt; leurs enregistrements &lt;/a&gt;circulent dans tout le pays. Le régime du shah ferme le centre en 1972 et l'emprisonne dix-huit mois. Il meurt peu après avoir quitté l'Iran, dans des circonstances que ses partisans jugent suspectes.&lt;/p&gt; &lt;p&gt;Il oppose deux chiismes. Le « chiisme rouge », celui d'Ali et de son fils Hussein, mort en martyr, est une religion de justice et de révolte contre l'oppression. Le « chiisme noir », devenu religion d'État sous les Safavides, est une religion de deuil, de résignation et de soumission au clergé.&lt;/p&gt; &lt;p&gt;Il appelle les peuples du tiers-monde au « retour à soi » : retrouver dans leur propre culture la force de se libérer, sans imiter ni le capitalisme occidental ni le marxisme, dont il reprend pourtant le vocabulaire. Mort deux ans avant la révolution de 1979, il en est souvent considéré comme l'inspirateur. Dans &lt;em&gt;Fatima est Fatima&lt;/em&gt;, il propose aux Iraniennes la fille du Prophète comme modèle d'une femme engagée, ni recluse ni occidentalisée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11mj2VwIgpA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Connaître l'Islam par la méthode par le Dr. Ali Shariati (Conférence 2) en Français" par Incroyable Maisvrai</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alishariati-mini.webp</t>
+        </is>
       </c>
       <c r="J155" s="1" t="s">
-        <v>1258</v>
+        <v>147</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>1043</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>1259</v>
+        <v>1446</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>1260</v>
+        <v>1447</v>
+      </c>
+      <c r="N155" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O155" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="P155" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="248.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="n">
+        <v>1934</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="O156" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="n">
-        <v>1938</v>
-      </c>
-      <c r="B156" s="1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E156" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdelk%C3%A9bir_Khatibi" title=" Wikipedia"&gt;Abdelkébir KHATIBI&lt;/a&gt; est un écrivain, sociologue et penseur marocain né à El Jadida. Il étudie la sociologie à la Sorbonne, où il soutient la première thèse consacrée au roman maghrébin, puis dirige à Rabat l'Institut de sociologie, et ensuite l'Institut universitaire de la recherche scientifique. Il a &lt;a href="https://www.contretemps.eu/abdelkebir-khatibi-principe-revolution/" title="Abdelkebir Khatibi, le principe révolution par contretemps"&gt;également animé &lt;/a&gt;pendant de longues années la principale revue marocaine de sciences sociales.&lt;/p&gt; &lt;p&gt;Son œuvre, écrite en français, mêle le roman, la poésie et l'essai. &lt;em&gt;La Mémoire tatouée&lt;/em&gt; (1971), sous-titrée « autobiographie d'un décolonisé », raconte son enfance entre deux langues et deux cultures. Il étudie aussi les signes de la culture populaire et savante du Maghreb : le tatouage, la calligraphie, le conte, le tapis. Roland Barthes lui rendit hommage dans un texte intitulé « Ce que je dois à Khatibi ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Maghreb pluriel&lt;/em&gt; (1983), il formule son idée centrale, la « double critique ». Pour décoloniser la pensée, il ne suffit pas de critiquer l'Occident et sa prétention à l'universel ; il faut critiquer en même temps son propre héritage, la théologie et le pouvoir patriarcal, sans quoi l'on ne fait que retourner le discours du maître. Il appelle &lt;a href="https://www.persee.fr/doc/horma_0984-2616_2009_num_60_1_2725" title="hommage à Abdelkébir Khatibi par persée"&gt;« pensée-autre » &lt;/a&gt;cette pensée qui ne se réfugie ni dans l'identité ni dans l'imitation.&lt;/p&gt; &lt;p&gt;Avec &lt;em&gt;Amour bilingue&lt;/em&gt;, il médite sur la « bi-langue » : écrire dans la langue de l'autre, habitée en secret par la langue maternelle, n'est pas une perte mais une chance. Jacques Derrida dialogue avec lui dans &lt;em&gt;Le Monolinguisme de l'autre&lt;/em&gt;. Il a aussi forgé le mot « aimance » pour désigner une relation d'affinité et d'hospitalité entre les êtres, les langues et les cultures.&lt;/p&gt;  &lt;audio controls title="Les arabes immigrés, traditions et racines par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/27050-16.09.2026-ITEMA_24673584-2023C3372E0379-NET_MFC_351639A3-9329-4471-B711-76D39FE2EEF5-25-c35cc310ff8a2a782c2f9f8d9928d6e9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">f8Kms-rwdIc</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Marc Gontard - Abdelkébir Khatibi de Selegan au déconstructivisme" par سلسلة لقاء مع الموجه</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/abdelkebirkhatibi-mini.webp</t>
-        </is>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="L156" s="2" t="s">
-        <v>1457</v>
-      </c>
-      <c r="M156" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="N156" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="O156" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="328.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="B157" s="1" t="n">
-        <v>2015</v>
+        <v>1935</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1227</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1459</v>
+        <v>1235</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="E157" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fatima_Mernissi" title=" Wikipedia"&gt;Fatima MERNISSI&lt;/a&gt; est une sociologue et écrivaine marocaine qui grandit dans une grande maison familiale où les femmes vivent à l'écart, enfance qu'elle racontera dans &lt;em&gt;Rêves de femmes&lt;/em&gt; (1994). Appartenant à la première génération de Marocaines scolarisées, elle étudie à Rabat, à Paris, puis aux États-Unis, où elle obtient un doctorat, avant d'enseigner la sociologie à l'université Mohammed V de Rabat.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;Sexe, idéologie, islam&lt;/em&gt; (1975), étudie la&lt;a href="https://scienceetbiencommun.pressbooks.pub/citoyennes/chapter/__unknown__/" title="Fatima Mernissi, sociologue, écrivaine et féministe marocaine par esbc"&gt; place faite aux femmes&lt;/a&gt; dans la société marocaine. Mais c'est &lt;em&gt;Le Harem politique&lt;/em&gt; (1987) qui la rend célèbre, et qui fut interdit dans son pays. Traduite dans de nombreuses langues, son œuvre a ouvert la voie à ce que l'on a appelé le féminisme islamique.&lt;/p&gt; &lt;p&gt;Elle y mène une &lt;a href="https://www.youtube.com/watch?v=Qb6iaPFs-ZI" title="Une vie : Fatima Mernissi par Brut"&gt;enquête d'historienne&lt;/a&gt; sur les paroles attribuées au Prophète qui servent à écarter les femmes de la vie publique. En utilisant les règles mêmes de la science religieuse traditionnelle, elle examine qui les a rapportées, à quel moment et dans quel intérêt, et montre leur fragilité. Pour elle, le message du Prophète était favorable à l'égalité ; ce sont les hommes de pouvoir qui, après lui, ont imposé une lecture hostile aux femmes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Sultanes oubliées&lt;/em&gt;, elle rappelle les femmes qui ont gouverné en terre d'islam. Elle a aussi retourné le regard vers l'Europe : &lt;em&gt;Le Harem et l'Occident&lt;/em&gt; montre que les femmes occidentales sont enfermées, elles, par la tyrannie de l'image et de la minceur. Elle a animé au Maroc de nombreux ateliers d'écriture et reçu en 2003 le prix Prince des Asturies. L'année suivante, le prix Érasme lui fut décerné en même temps qu'au philosophe iranien Abdolkarim Soroush.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UQab1UXbrM4</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Fatima Mernissi : Islam et Féminisme" par ​L'Art de Comprendre</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fatimamernissi-mini.webp</t>
-        </is>
+        <v>1236</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>1240</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>1043</v>
+        <v>1001</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>1462</v>
+        <v>952</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>1463</v>
+        <v>1242</v>
       </c>
       <c r="N157" s="1" t="s">
         <v>72</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="P157" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="323.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1261</v>
+        <v>1243</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1262</v>
+        <v>1244</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>1264</v>
+        <v>1245</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>1246</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1265</v>
+        <v>1247</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>1266</v>
+        <v>1248</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>1267</v>
+        <v>1249</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>1268</v>
+        <v>1250</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>1192</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>1061</v>
+        <v>1128</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>1269</v>
+        <v>1251</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="347.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>1270</v>
+        <v>1936</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>2005</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1271</v>
+        <v>1252</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>1273</v>
+        <v>1253</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>1254</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>1275</v>
+        <v>1256</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>1276</v>
+        <v>1257</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1277</v>
+        <v>1258</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>1192</v>
+        <v>1043</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>1278</v>
+        <v>1259</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>1279</v>
+        <v>1260</v>
       </c>
       <c r="O159" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="P159" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>1243</v>
+        <v>1938</v>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>2009</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1280</v>
+        <v>1453</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>1282</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>1284</v>
-      </c>
-      <c r="H160" s="2" t="s">
-        <v>1285</v>
+        <v>1454</v>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abdelk%C3%A9bir_Khatibi" title=" Wikipedia"&gt;Abdelkébir KHATIBI&lt;/a&gt; est un écrivain, sociologue et penseur marocain né à El Jadida. Il étudie la sociologie à la Sorbonne, où il soutient la première thèse consacrée au roman maghrébin, puis dirige à Rabat l'Institut de sociologie, et ensuite l'Institut universitaire de la recherche scientifique. Il a &lt;a href="https://www.contretemps.eu/abdelkebir-khatibi-principe-revolution/" title="Abdelkebir Khatibi, le principe révolution par contretemps"&gt;également animé &lt;/a&gt;pendant de longues années la principale revue marocaine de sciences sociales.&lt;/p&gt; &lt;p&gt;Son œuvre, écrite en français, mêle le roman, la poésie et l'essai. &lt;em&gt;La Mémoire tatouée&lt;/em&gt; (1971), sous-titrée « autobiographie d'un décolonisé », raconte son enfance entre deux langues et deux cultures. Il étudie aussi les signes de la culture populaire et savante du Maghreb : le tatouage, la calligraphie, le conte, le tapis. Roland Barthes lui rendit hommage dans un texte intitulé « Ce que je dois à Khatibi ».&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Maghreb pluriel&lt;/em&gt; (1983), il formule son idée centrale, la « double critique ». Pour décoloniser la pensée, il ne suffit pas de critiquer l'Occident et sa prétention à l'universel ; il faut critiquer en même temps son propre héritage, la théologie et le pouvoir patriarcal, sans quoi l'on ne fait que retourner le discours du maître. Il appelle &lt;a href="https://www.persee.fr/doc/horma_0984-2616_2009_num_60_1_2725" title="hommage à Abdelkébir Khatibi par persée"&gt;« pensée-autre » &lt;/a&gt;cette pensée qui ne se réfugie ni dans l'identité ni dans l'imitation.&lt;/p&gt; &lt;p&gt;Avec &lt;em&gt;Amour bilingue&lt;/em&gt;, il médite sur la « bi-langue » : écrire dans la langue de l'autre, habitée en secret par la langue maternelle, n'est pas une perte mais une chance. Jacques Derrida dialogue avec lui dans &lt;em&gt;Le Monolinguisme de l'autre&lt;/em&gt;. Il a aussi forgé le mot « aimance » pour désigner une relation d'affinité et d'hospitalité entre les êtres, les langues et les cultures.&lt;/p&gt;  &lt;audio controls title="Les arabes immigrés, traditions et racines par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/27050-16.09.2026-ITEMA_24673584-2023C3372E0379-NET_MFC_351639A3-9329-4471-B711-76D39FE2EEF5-25-c35cc310ff8a2a782c2f9f8d9928d6e9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f8Kms-rwdIc</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Marc Gontard - Abdelkébir Khatibi de Selegan au déconstructivisme" par سلسلة لقاء مع الموجه</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/abdelkebirkhatibi-mini.webp</t>
+        </is>
       </c>
       <c r="J160" s="1" t="s">
-        <v>25</v>
+        <v>1250</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>26</v>
+        <v>1456</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>398</v>
+        <v>1457</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>1286</v>
+        <v>1458</v>
+      </c>
+      <c r="N160" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O160" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
-      <c r="E161" s="1"/>
-      <c r="G161" s="1"/>
-      <c r="H161" s="1"/>
-      <c r="I161" s="1"/>
-      <c r="K161" s="1"/>
-      <c r="L161" s="1"/>
-      <c r="M161" s="1"/>
-    </row>
-    <row r="162" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fatima_Mernissi" title=" Wikipedia"&gt;Fatima MERNISSI&lt;/a&gt; est une sociologue et écrivaine marocaine qui grandit dans une grande maison familiale où les femmes vivent à l'écart, enfance qu'elle racontera dans &lt;em&gt;Rêves de femmes&lt;/em&gt; (1994). Appartenant à la première génération de Marocaines scolarisées, elle étudie à Rabat, à Paris, puis aux États-Unis, où elle obtient un doctorat, avant d'enseigner la sociologie à l'université Mohammed V de Rabat.&lt;/p&gt; &lt;p&gt;Son premier livre, &lt;em&gt;Sexe, idéologie, islam&lt;/em&gt; (1975), étudie la&lt;a href="https://scienceetbiencommun.pressbooks.pub/citoyennes/chapter/__unknown__/" title="Fatima Mernissi, sociologue, écrivaine et féministe marocaine par esbc"&gt; place faite aux femmes&lt;/a&gt; dans la société marocaine. Mais c'est &lt;em&gt;Le Harem politique&lt;/em&gt; (1987) qui la rend célèbre, et qui fut interdit dans son pays. Traduite dans de nombreuses langues, son œuvre a ouvert la voie à ce que l'on a appelé le féminisme islamique.&lt;/p&gt; &lt;p&gt;Elle y mène une &lt;a href="https://www.youtube.com/watch?v=Qb6iaPFs-ZI" title="Une vie : Fatima Mernissi par Brut"&gt;enquête d'historienne&lt;/a&gt; sur les paroles attribuées au Prophète qui servent à écarter les femmes de la vie publique. En utilisant les règles mêmes de la science religieuse traditionnelle, elle examine qui les a rapportées, à quel moment et dans quel intérêt, et montre leur fragilité. Pour elle, le message du Prophète était favorable à l'égalité ; ce sont les hommes de pouvoir qui, après lui, ont imposé une lecture hostile aux femmes.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Sultanes oubliées&lt;/em&gt;, elle rappelle les femmes qui ont gouverné en terre d'islam. Elle a aussi retourné le regard vers l'Europe : &lt;em&gt;Le Harem et l'Occident&lt;/em&gt; montre que les femmes occidentales sont enfermées, elles, par la tyrannie de l'image et de la minceur. Elle a animé au Maroc de nombreux ateliers d'écriture et reçu en 2003 le prix Prince des Asturies. L'année suivante, le prix Érasme lui fut décerné en même temps qu'au philosophe iranien Abdolkarim Soroush.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UQab1UXbrM4</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Fatima Mernissi : Islam et Féminisme" par ​L'Art de Comprendre</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fatimamernissi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="N161" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O161" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="P161" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="351.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
+        <v>1941</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="O162" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="303" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O163" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="P163" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="265.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="O164" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="124.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+    </row>
+    <row r="166" customFormat="false" ht="280.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="n">
         <v>-1000</v>
       </c>
-      <c r="B162" s="1" t="n">
+      <c r="B166" s="1" t="n">
         <v>-900</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="E162" s="10" t="inlineStr">
+      <c r="E166" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_pessimisme" title=" Wikipedia"&gt;Dialogue du PESSIMISME&lt;/a&gt; est un court texte akkadien composé en Mésopotamie qui met en scène un maître et son esclave.&lt;/p&gt; &lt;p&gt;Le maître &lt;a href="http://www.aroumah.net/seminar/Dialogue%20of%20Pessimism.pdf"&gt;annonce tour à tour &lt;/a&gt;qu'il va aller au palais, festoyer, aimer une femme, faire un sacrifice, prêter de l'argent ou servir son pays ; à chaque fois l'esclave l'approuve avec de bonnes raisons, puis, quand le maître change d'avis, l'approuve encore avec des raisons tout aussi bonnes. À la fin, le maître demande ce qui est bon : l'esclave répond qu'il vaut mieux mourir.&lt;/p&gt; &lt;p&gt;Chaque échange suit le même schéma : « Esclave, obéis-moi ! — Oui, mon maître, oui. » Le maître propose une action, l'esclave en vante les avantages ; le maître y renonce, l'esclave en montre aussitôt les dangers. Ainsi, faire l'amour à une femme fait oublier le chagrin, mais la femme est « un piège, un trou, un fossé » ; faire le bien de son pays est louable, mais personne ne distingue, parmi les crânes des morts, le bienfaiteur du malfaiteur.&lt;/p&gt; &lt;p&gt;Les spécialistes hésitent sur le sens du texte : satire comique du maître capricieux et de l'esclave flatteur, ou méditation sérieuse sur l'absence de valeur sûre ? Dans les deux cas, il met en évidence une idée troublante : pour chaque choix, on peut trouver des raisons aussi convaincantes que pour le choix contraire, de sorte que la raison seule ne permet pas de décider comment vivre.&lt;/p&gt; &lt;p&gt;Ironique ou désespéré, ce dialogue interroge la valeur de toute action humaine et annonce les grandes réflexions sceptiques et pessimistes, de Qohélet à Schopenhauer.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t xml:space="preserve">0aawol43UdU</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t xml:space="preserve">"The Dialogue of Pessimism (Full Audiobook)" par abitof_ane_rd</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/dialoguedupessimisme-mini.webp</t>
         </is>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="J166" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K162" s="2" t="inlineStr">
+      <c r="K166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L162" s="2" t="s">
+      <c r="L166" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M162" s="2" t="s">
+      <c r="M166" s="2" t="s">
         <v>1291</v>
-      </c>
-      <c r="O162" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B163" s="1" t="n">
-        <v>-640</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AX9Hmh5qJ9U</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
-        </is>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K163" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L163" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M163" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="O163" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="n">
-        <v>-340</v>
-      </c>
-      <c r="B164" s="1" t="n">
-        <v>-270</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E164" s="10" t="s">
-        <v>1302</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="L164" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M164" s="2" t="s">
-        <v>1304</v>
-      </c>
-      <c r="O164" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="n">
-        <v>-250</v>
-      </c>
-      <c r="B165" s="1" t="n">
-        <v>-220</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E165" s="10" t="s">
-        <v>1307</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L165" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="M165" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="O165" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P165" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="n">
-        <v>-250</v>
-      </c>
-      <c r="B166" s="1" t="n">
-        <v>-100</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>1310</v>
-      </c>
-      <c r="E166" s="10" t="s">
-        <v>1311</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L166" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M166" s="2" t="s">
-        <v>1312</v>
       </c>
       <c r="O166" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="292.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
-        <v>154</v>
+        <v>-700</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>222</v>
+        <v>-640</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>1313</v>
+        <v>1292</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1314</v>
-      </c>
-      <c r="E167" s="10" t="s">
-        <v>1315</v>
+        <v>1293</v>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahiqar" title=" Wikipedia"&gt;AHIQAR&lt;/a&gt; est un sage présenté comme le chancelier des rois assyriens Sennachérib et Assarhaddon (680-669 avant J.-C.). Son histoire et ses maximes nous sont parvenues par des papyrus araméens retrouvés à Éléphantine, en Égypte, datant de la fin du Ve siècle avant J.-C.&lt;/p&gt; &lt;p&gt;Le récit raconte comment Ahiqar, trahi par son neveu adoptif Nadin qu'il avait élevé, est condamné à mort, sauvé par un ami, puis rétabli dans son honneur. Il est suivi d'un recueil de proverbes sur la prudence dans les paroles, l'éducation des enfants, la loyauté et l'ingratitude.&lt;/p&gt; &lt;p&gt;Parmi ses maximes, beaucoup&lt;a href="https://www.persee.fr/doc/ethio_0066-2127_1978_num_11_1_912" title="L'histoire d'Ahiqar en éthiopien par persée"&gt; concernent la parole &lt;/a&gt;: « Garde ta bouche plus que toute autre chose », « Un mot est un oiseau : une fois lâché, personne ne peut le rattraper ». D'autres prônent la sévérité dans l'éducation des enfants, la fidélité au roi, la méfiance envers les méchants et la reconnaissance envers ceux qui nous ont fait du bien. Dans certaines versions, Ahiqar reproche longuement à Nadin son ingratitude à travers une série de comparaisons tirées de la nature.&lt;/p&gt; &lt;p&gt;Les Grecs le connaissaient : le philosophe Démocrite aurait, selon une tradition, emprunté ses préceptes, et la légendaire &lt;em&gt;Vie d'Ésope&lt;/em&gt; reprend presque entièrement son histoire. Le personnage apparaît aussi dans le Coran sous les traits de Luqman le Sage selon certains commentateurs. Peu de textes antiques ont connu une &lt;a href="https://www.youtube.com/watch?v=3HCHSrvEwuc" title="Sage Ahiqar Quotes Ancient Assyrian Wisdom par mir allround"&gt;diffusion aussi large &lt;/a&gt;à travers les langues et les religions.&lt;/p&gt; &lt;p&gt;L'histoire d'Ahiqar a connu un succès immense : on la retrouve dans la Bible (livre de Tobie), chez les Grecs, dans les traditions syriaque, arabe et arménienne. Elle montre la circulation d'une même sagesse populaire dans tout le Proche-Orient.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AX9Hmh5qJ9U</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Story of Ahikar" par Study of Antiquity and the Middle Ages</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahiqar-mini.webp</t>
+        </is>
       </c>
       <c r="J167" s="1" t="s">
-        <v>1316</v>
+        <v>51</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>1317</v>
+        <v>53</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>1318</v>
+        <v>1295</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>29</v>
@@ -13427,244 +13522,241 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
-        <v>45</v>
+        <v>-340</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>117</v>
+        <v>-270</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>1319</v>
+        <v>1300</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1320</v>
+        <v>1301</v>
       </c>
       <c r="E168" s="10" t="s">
-        <v>1321</v>
+        <v>1302</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>267</v>
+        <v>51</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>62</v>
+        <v>1303</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>296</v>
+        <v>53</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="N168" s="1" t="s">
-        <v>72</v>
+        <v>1304</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P168" s="1" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
-        <v>1130</v>
+        <v>-250</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>1160</v>
+        <v>-220</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1323</v>
+        <v>1305</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1324</v>
+        <v>1306</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>1325</v>
+        <v>1307</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>96</v>
+        <v>396</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>427</v>
+        <v>107</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>641</v>
+        <v>398</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>1326</v>
+        <v>1308</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>72</v>
+        <v>400</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>100</v>
+        <v>29</v>
+      </c>
+      <c r="P169" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
-        <v>832</v>
+        <v>-250</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>932</v>
+        <v>-100</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1327</v>
+        <v>1309</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1328</v>
+        <v>1310</v>
       </c>
       <c r="E170" s="10" t="s">
-        <v>1329</v>
+        <v>1311</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>396</v>
+        <v>25</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>346</v>
+        <v>36</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>1330</v>
+        <v>27</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="N170" s="1" t="s">
-        <v>400</v>
+        <v>1312</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>401</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
-        <v>853</v>
+        <v>154</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>944</v>
+        <v>222</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>1332</v>
+        <v>1313</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1333</v>
+        <v>1314</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>1334</v>
+        <v>1315</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>147</v>
+        <v>1316</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>1336</v>
+        <v>1318</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>401</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
-        <v>874</v>
+        <v>45</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>936</v>
+        <v>117</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1338</v>
+        <v>1320</v>
       </c>
       <c r="E172" s="10" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>545</v>
+        <v>267</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>1340</v>
+        <v>296</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>1341</v>
+        <v>1322</v>
+      </c>
+      <c r="N172" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>401</v>
+        <v>271</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
-        <v>882</v>
+        <v>1130</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>942</v>
+        <v>1160</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>1342</v>
+        <v>1323</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1343</v>
+        <v>1324</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>1344</v>
+        <v>1325</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>396</v>
+        <v>96</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>1345</v>
+        <v>641</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>1346</v>
+        <v>1326</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>400</v>
+        <v>72</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="P173" s="1" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>1347</v>
+        <v>1327</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1348</v>
+        <v>1328</v>
       </c>
       <c r="E174" s="10" t="s">
-        <v>1349</v>
+        <v>1329</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>138</v>
+        <v>346</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>1350</v>
+        <v>1330</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>1351</v>
+        <v>1331</v>
+      </c>
+      <c r="N174" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O174" s="1" t="s">
         <v>401</v>
@@ -13672,98 +13764,98 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
-        <v>994</v>
+        <v>853</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>1064</v>
+        <v>944</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1352</v>
+        <v>1332</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1353</v>
+        <v>1333</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>1354</v>
+        <v>1334</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>545</v>
+        <v>147</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>1355</v>
+        <v>138</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>1335</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>1356</v>
+        <v>1336</v>
       </c>
       <c r="O175" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P175" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
-        <v>1004</v>
+        <v>874</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>1088</v>
+        <v>936</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>1357</v>
+        <v>1337</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1358</v>
+        <v>1338</v>
       </c>
       <c r="E176" s="10" t="s">
-        <v>1359</v>
+        <v>1339</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>511</v>
+        <v>1340</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="O176" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P176" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
-        <v>1021</v>
+        <v>882</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>1058</v>
+        <v>942</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1362</v>
+        <v>1343</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>1363</v>
+        <v>1344</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>1364</v>
+        <v>206</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>1330</v>
+        <v>1345</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
       <c r="N177" s="1" t="s">
         <v>400</v>
@@ -13777,34 +13869,31 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
-        <v>1050</v>
+        <v>883</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>1120</v>
+        <v>931</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>1366</v>
+        <v>1347</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="E178" s="10" t="s">
-        <v>1368</v>
+        <v>1349</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>1370</v>
-      </c>
-      <c r="N178" s="1" t="s">
-        <v>400</v>
+        <v>1351</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>401</v>
@@ -13812,34 +13901,31 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
-        <v>1075</v>
+        <v>994</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>1141</v>
+        <v>1064</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>1371</v>
+        <v>1352</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1372</v>
+        <v>1353</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>1373</v>
+        <v>1354</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>742</v>
+        <v>1355</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>1374</v>
+        <v>1335</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>1375</v>
-      </c>
-      <c r="N179" s="1" t="s">
-        <v>400</v>
+        <v>1356</v>
       </c>
       <c r="O179" s="1" t="s">
         <v>401</v>
@@ -13850,34 +13936,31 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
-        <v>1092</v>
+        <v>1004</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>1167</v>
+        <v>1088</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>1376</v>
+        <v>1357</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1377</v>
+        <v>1358</v>
       </c>
       <c r="E180" s="10" t="s">
-        <v>1378</v>
+        <v>1359</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>1330</v>
+        <v>511</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="N180" s="1" t="s">
-        <v>400</v>
+        <v>1360</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>401</v>
@@ -13885,31 +13968,31 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
-        <v>1110</v>
+        <v>1021</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>1180</v>
+        <v>1058</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1380</v>
+        <v>1361</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1381</v>
+        <v>1362</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>1382</v>
+        <v>1363</v>
       </c>
       <c r="J181" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>206</v>
+        <v>1364</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>1383</v>
+        <v>1330</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>1384</v>
+        <v>1365</v>
       </c>
       <c r="N181" s="1" t="s">
         <v>400</v>
@@ -13917,34 +14000,40 @@
       <c r="O181" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P181" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
-        <v>1150</v>
+        <v>1050</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>1210</v>
+        <v>1120</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>1385</v>
+        <v>1366</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1386</v>
+        <v>1367</v>
       </c>
       <c r="E182" s="10" t="s">
-        <v>1387</v>
+        <v>1368</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>1388</v>
+        <v>397</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>1340</v>
+        <v>1369</v>
       </c>
       <c r="M182" s="2" t="s">
-        <v>1389</v>
+        <v>1370</v>
+      </c>
+      <c r="N182" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O182" s="1" t="s">
         <v>401</v>
@@ -13952,104 +14041,107 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
-        <v>1194</v>
+        <v>1075</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>1270</v>
+        <v>1141</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1391</v>
+        <v>1372</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>1392</v>
+        <v>1373</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>791</v>
+        <v>742</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>1393</v>
+        <v>1375</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>1394</v>
+        <v>400</v>
       </c>
       <c r="O183" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P183" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
-        <v>1263</v>
+        <v>1092</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>1328</v>
+        <v>1167</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>1395</v>
+        <v>1376</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1396</v>
+        <v>1377</v>
       </c>
       <c r="E184" s="10" t="s">
-        <v>1397</v>
+        <v>1378</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>1398</v>
+        <v>546</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>1399</v>
+        <v>1330</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>1400</v>
+        <v>1379</v>
+      </c>
+      <c r="N184" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P184" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
-        <v>1340</v>
+        <v>1110</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>1411</v>
+        <v>1180</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>1401</v>
+        <v>1380</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1402</v>
+        <v>1381</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>1374</v>
+        <v>1383</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>1404</v>
+        <v>1384</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>1394</v>
+        <v>400</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>401</v>
@@ -14057,34 +14149,31 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
-        <v>1380</v>
+        <v>1150</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>1444</v>
+        <v>1210</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>1405</v>
+        <v>1385</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1406</v>
+        <v>1386</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>1407</v>
+        <v>1387</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>1408</v>
+        <v>1388</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>1374</v>
+        <v>1340</v>
       </c>
       <c r="M186" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="N186" s="1" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="O186" s="1" t="s">
         <v>401</v>
@@ -14092,31 +14181,31 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
-        <v>1437</v>
+        <v>1194</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>1508</v>
+        <v>1270</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>1410</v>
+        <v>1390</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1411</v>
+        <v>1391</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>1412</v>
+        <v>1392</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>1043</v>
+        <v>791</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>1413</v>
+        <v>1369</v>
       </c>
       <c r="M187" s="2" t="s">
-        <v>1414</v>
+        <v>1393</v>
       </c>
       <c r="N187" s="1" t="s">
         <v>1394</v>
@@ -14127,133 +14216,139 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
-        <v>1561</v>
+        <v>1263</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>1631</v>
+        <v>1328</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>1415</v>
+        <v>1395</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1416</v>
+        <v>1396</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>1417</v>
+        <v>1397</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>206</v>
+        <v>1398</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>775</v>
+        <v>1399</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>1418</v>
+        <v>1400</v>
       </c>
       <c r="O188" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="P188" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
-        <v>1801</v>
+        <v>1340</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>1873</v>
+        <v>1411</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>1419</v>
+        <v>1401</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1420</v>
+        <v>1402</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>304</v>
+        <v>231</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>1422</v>
+        <v>1374</v>
       </c>
       <c r="M189" s="2" t="s">
-        <v>1423</v>
+        <v>1404</v>
+      </c>
+      <c r="N189" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O189" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P189" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
-        <v>1849</v>
+        <v>1380</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>1905</v>
+        <v>1444</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>1424</v>
+        <v>1405</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1425</v>
+        <v>1406</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>1426</v>
+        <v>1407</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K190" s="2" t="s">
         <v>1408</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>1427</v>
+        <v>1374</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>1428</v>
+        <v>1409</v>
+      </c>
+      <c r="N190" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="P190" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
-        <v>1888</v>
+        <v>1437</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>1966</v>
+        <v>1508</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>1429</v>
+        <v>1410</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>1430</v>
+        <v>1411</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>1431</v>
+        <v>1412</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>304</v>
+        <v>1043</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>1422</v>
+        <v>1413</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1432</v>
+        <v>1414</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>1394</v>
       </c>
       <c r="O191" s="1" t="s">
         <v>401</v>
@@ -14261,34 +14356,31 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
-        <v>1905</v>
+        <v>1561</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>1973</v>
+        <v>1631</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1434</v>
+        <v>1416</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>1435</v>
+        <v>1417</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1436</v>
+        <v>147</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>1259</v>
+        <v>775</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="N192" s="1" t="s">
-        <v>660</v>
+        <v>1418</v>
       </c>
       <c r="O192" s="1" t="s">
         <v>401</v>
@@ -14296,107 +14388,101 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
-        <v>1928</v>
+        <v>1801</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>2010</v>
+        <v>1873</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1438</v>
+        <v>1419</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1439</v>
+        <v>1420</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>1440</v>
+        <v>1421</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>1436</v>
+        <v>25</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>26</v>
+        <v>304</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>1441</v>
+        <v>1422</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="N193" s="1" t="s">
-        <v>513</v>
+        <v>1423</v>
       </c>
       <c r="O193" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P193" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="n">
-        <v>1933</v>
+        <v>1849</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>1977</v>
+        <v>1905</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1444</v>
+        <v>1425</v>
       </c>
       <c r="E194" s="10" t="s">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>1043</v>
+        <v>1408</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>1446</v>
+        <v>1427</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="N194" s="1" t="s">
-        <v>660</v>
+        <v>1428</v>
       </c>
       <c r="O194" s="1" t="s">
         <v>401</v>
       </c>
       <c r="P194" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="n">
-        <v>1935</v>
+        <v>1888</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>2021</v>
+        <v>1966</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1449</v>
+        <v>1430</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>1450</v>
+        <v>1431</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>1043</v>
+        <v>304</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>1451</v>
+        <v>1422</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="O195" s="1" t="s">
         <v>401</v>
@@ -14404,107 +14490,101 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
-        <v>613</v>
+        <v>1905</v>
       </c>
       <c r="B196" s="1" t="n">
-        <v>696</v>
+        <v>1973</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1464</v>
+        <v>1433</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1465</v>
+        <v>1434</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>1466</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>1467</v>
+        <v>1435</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>916</v>
+        <v>1436</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>231</v>
+        <v>304</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>444</v>
+        <v>1259</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>1468</v>
+        <v>1437</v>
+      </c>
+      <c r="N196" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="O196" s="1" t="s">
-        <v>271</v>
+        <v>401</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="n">
-        <v>617</v>
+        <v>1935</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>686</v>
+        <v>2021</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1469</v>
+        <v>1448</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>1471</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>1472</v>
+        <v>1450</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>916</v>
+        <v>25</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>206</v>
+        <v>1043</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>444</v>
+        <v>1451</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>1473</v>
+        <v>1452</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P197" s="1" t="n">
-        <v>3</v>
+        <v>401</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="n">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="B198" s="1" t="n">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1474</v>
+        <v>1464</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
       <c r="E198" s="10" t="s">
-        <v>1476</v>
+        <v>1466</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1477</v>
+        <v>1467</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="L198" s="2" t="s">
         <v>444</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
       <c r="O198" s="1" t="s">
         <v>271</v>
@@ -14512,69 +14592,72 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
-        <v>857</v>
+        <v>617</v>
       </c>
       <c r="B199" s="1" t="n">
-        <v>910</v>
+        <v>686</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1479</v>
+        <v>1469</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1480</v>
+        <v>1470</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="J199" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>397</v>
+        <v>206</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>917</v>
+        <v>444</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>1483</v>
+        <v>1473</v>
       </c>
       <c r="O199" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P199" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
-        <v>1055</v>
+        <v>625</v>
       </c>
       <c r="B200" s="1" t="n">
-        <v>1101</v>
+        <v>702</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1484</v>
+        <v>1474</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1485</v>
+        <v>1475</v>
       </c>
       <c r="E200" s="10" t="s">
-        <v>1486</v>
+        <v>1476</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1487</v>
+        <v>1477</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="L200" s="2" t="s">
         <v>444</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
       <c r="O200" s="1" t="s">
         <v>271</v>
@@ -14582,34 +14665,34 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
-        <v>1158</v>
+        <v>857</v>
       </c>
       <c r="B201" s="1" t="n">
-        <v>1210</v>
+        <v>910</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1489</v>
+        <v>1479</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1490</v>
+        <v>1480</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>1491</v>
+        <v>1481</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>1492</v>
+        <v>1482</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>546</v>
+        <v>397</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>799</v>
+        <v>917</v>
       </c>
       <c r="M201" s="2" t="s">
-        <v>1493</v>
+        <v>1483</v>
       </c>
       <c r="O201" s="1" t="s">
         <v>271</v>
@@ -14617,133 +14700,130 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="n">
-        <v>1337</v>
+        <v>1055</v>
       </c>
       <c r="B202" s="1" t="n">
-        <v>1392</v>
+        <v>1101</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="E202" s="10" t="s">
-        <v>1496</v>
+        <v>1486</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>1497</v>
+        <v>1487</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>62</v>
+        <v>546</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>917</v>
+        <v>444</v>
       </c>
       <c r="M202" s="2" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
       <c r="O202" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P202" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="n">
-        <v>1342</v>
+        <v>1158</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>1398</v>
+        <v>1210</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>1499</v>
+        <v>1489</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>1502</v>
+        <v>1492</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>80</v>
+        <v>546</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="M203" s="2" t="s">
-        <v>1503</v>
+        <v>1493</v>
       </c>
       <c r="O203" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P203" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="n">
-        <v>1376</v>
+        <v>1337</v>
       </c>
       <c r="B204" s="1" t="n">
-        <v>1433</v>
+        <v>1392</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1504</v>
+        <v>1494</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1505</v>
+        <v>1495</v>
       </c>
       <c r="E204" s="10" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K204" s="2" t="s">
-        <v>427</v>
+        <v>62</v>
       </c>
       <c r="L204" s="2" t="s">
-        <v>799</v>
+        <v>917</v>
       </c>
       <c r="M204" s="2" t="s">
-        <v>1508</v>
+        <v>1498</v>
       </c>
       <c r="O204" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P204" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="n">
-        <v>1482</v>
+        <v>1342</v>
       </c>
       <c r="B205" s="1" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>1509</v>
+        <v>1499</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1510</v>
+        <v>1500</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>1512</v>
+        <v>1502</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>916</v>
@@ -14755,42 +14835,45 @@
         <v>917</v>
       </c>
       <c r="M205" s="2" t="s">
-        <v>1513</v>
+        <v>1503</v>
       </c>
       <c r="O205" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P205" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="n">
-        <v>1489</v>
+        <v>1376</v>
       </c>
       <c r="B206" s="1" t="n">
-        <v>1546</v>
+        <v>1433</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1514</v>
+        <v>1504</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>1515</v>
+        <v>1505</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>1516</v>
+        <v>1506</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="L206" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="M206" s="2" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="O206" s="1" t="s">
         <v>271</v>
@@ -14798,34 +14881,34 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="n">
-        <v>1501</v>
+        <v>1482</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>1572</v>
+        <v>1519</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>1521</v>
+        <v>1511</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="L207" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M207" s="2" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="O207" s="1" t="s">
         <v>271</v>
@@ -14833,34 +14916,34 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="n">
-        <v>1520</v>
+        <v>1489</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>1604</v>
+        <v>1546</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1524</v>
+        <v>1514</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="E208" s="10" t="s">
-        <v>1526</v>
+        <v>1516</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>1527</v>
+        <v>1517</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>427</v>
+        <v>231</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>799</v>
+        <v>917</v>
       </c>
       <c r="M208" s="2" t="s">
-        <v>1528</v>
+        <v>1518</v>
       </c>
       <c r="O208" s="1" t="s">
         <v>271</v>
@@ -14868,34 +14951,34 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="n">
-        <v>1527</v>
+        <v>1501</v>
       </c>
       <c r="B209" s="1" t="n">
         <v>1572</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>1531</v>
+        <v>1521</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>1532</v>
+        <v>1522</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>257</v>
+        <v>62</v>
       </c>
       <c r="L209" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M209" s="2" t="s">
-        <v>1533</v>
+        <v>1523</v>
       </c>
       <c r="O209" s="1" t="s">
         <v>271</v>
@@ -14903,34 +14986,34 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="n">
-        <v>1535</v>
+        <v>1520</v>
       </c>
       <c r="B210" s="1" t="n">
-        <v>1598</v>
+        <v>1604</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1534</v>
+        <v>1524</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="E210" s="10" t="s">
-        <v>1536</v>
+        <v>1526</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>257</v>
+        <v>427</v>
       </c>
       <c r="L210" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="M210" s="2" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
       <c r="O210" s="1" t="s">
         <v>271</v>
@@ -14938,145 +15021,142 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="n">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="B211" s="1" t="n">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="L211" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M211" s="2" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="O211" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P211" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="n">
-        <v>1607</v>
+        <v>1535</v>
       </c>
       <c r="B212" s="1" t="n">
-        <v>1689</v>
+        <v>1598</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1545</v>
+        <v>1535</v>
       </c>
       <c r="E212" s="10" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="L212" s="2" t="s">
         <v>917</v>
       </c>
       <c r="M212" s="2" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P212" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="n">
-        <v>1622</v>
+        <v>1536</v>
       </c>
       <c r="B213" s="1" t="n">
-        <v>1673</v>
+        <v>1584</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>1550</v>
+        <v>1540</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P213" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="n">
-        <v>1649</v>
+        <v>1607</v>
       </c>
       <c r="B214" s="1" t="n">
-        <v>1736</v>
+        <v>1689</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>1555</v>
+        <v>1545</v>
       </c>
       <c r="E214" s="10" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>1557</v>
+        <v>1547</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>951</v>
+        <v>80</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>691</v>
+        <v>917</v>
       </c>
       <c r="M214" s="2" t="s">
-        <v>1558</v>
+        <v>1548</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>271</v>
@@ -15087,34 +15167,34 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="n">
-        <v>1682</v>
+        <v>1622</v>
       </c>
       <c r="B215" s="1" t="n">
-        <v>1751</v>
+        <v>1673</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>917</v>
+        <v>992</v>
       </c>
       <c r="M215" s="2" t="s">
-        <v>1563</v>
+        <v>1553</v>
       </c>
       <c r="O215" s="1" t="s">
         <v>271</v>
@@ -15122,69 +15202,72 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="n">
-        <v>1731</v>
+        <v>1649</v>
       </c>
       <c r="B216" s="1" t="n">
-        <v>1783</v>
+        <v>1736</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="E216" s="10" t="s">
-        <v>1566</v>
+        <v>1556</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>1567</v>
+        <v>1557</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>409</v>
+        <v>951</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>992</v>
+        <v>691</v>
       </c>
       <c r="M216" s="2" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="O216" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P216" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="n">
-        <v>1737</v>
+        <v>1682</v>
       </c>
       <c r="B217" s="1" t="n">
-        <v>1805</v>
+        <v>1751</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>1571</v>
+        <v>1561</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>1159</v>
+        <v>247</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="O217" s="1" t="s">
         <v>271</v>
@@ -15192,72 +15275,69 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="n">
-        <v>1762</v>
+        <v>1731</v>
       </c>
       <c r="B218" s="1" t="n">
-        <v>1836</v>
+        <v>1783</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="E218" s="10" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="L218" s="2" t="s">
         <v>992</v>
       </c>
       <c r="M218" s="2" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="O218" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P218" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="n">
-        <v>1792</v>
+        <v>1737</v>
       </c>
       <c r="B219" s="1" t="n">
-        <v>1868</v>
+        <v>1805</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>1581</v>
+        <v>1571</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>387</v>
+        <v>1159</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>917</v>
+        <v>992</v>
       </c>
       <c r="M219" s="2" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="O219" s="1" t="s">
         <v>271</v>
@@ -15265,69 +15345,72 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="n">
-        <v>1803</v>
+        <v>1762</v>
       </c>
       <c r="B220" s="1" t="n">
-        <v>1877</v>
+        <v>1836</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>1585</v>
+        <v>1575</v>
       </c>
       <c r="E220" s="10" t="s">
-        <v>1586</v>
+        <v>1576</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>1587</v>
+        <v>1577</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="L220" s="2" t="s">
         <v>992</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>1588</v>
+        <v>1578</v>
       </c>
       <c r="O220" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P220" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="n">
-        <v>1824</v>
+        <v>1792</v>
       </c>
       <c r="B221" s="1" t="n">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>1591</v>
+        <v>1581</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>1592</v>
+        <v>1582</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>1408</v>
+        <v>387</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>1593</v>
+        <v>917</v>
       </c>
       <c r="M221" s="2" t="s">
-        <v>1594</v>
+        <v>1583</v>
       </c>
       <c r="O221" s="1" t="s">
         <v>271</v>
@@ -15335,34 +15418,34 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="n">
-        <v>1859</v>
+        <v>1803</v>
       </c>
       <c r="B222" s="1" t="n">
-        <v>1925</v>
+        <v>1877</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>1595</v>
+        <v>1584</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>1596</v>
+        <v>1585</v>
       </c>
       <c r="E222" s="10" t="s">
-        <v>1597</v>
+        <v>1586</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>1598</v>
+        <v>1587</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>917</v>
+        <v>992</v>
       </c>
       <c r="M222" s="2" t="s">
-        <v>1599</v>
+        <v>1588</v>
       </c>
       <c r="O222" s="1" t="s">
         <v>271</v>
@@ -15370,22 +15453,22 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="n">
-        <v>1879</v>
+        <v>1824</v>
       </c>
       <c r="B223" s="1" t="n">
-        <v>1944</v>
+        <v>1864</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>1600</v>
+        <v>1589</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>1601</v>
+        <v>1590</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>1602</v>
+        <v>1591</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>1603</v>
+        <v>1592</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>916</v>
@@ -15394,48 +15477,45 @@
         <v>1408</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>799</v>
+        <v>1593</v>
       </c>
       <c r="M223" s="2" t="s">
-        <v>1604</v>
+        <v>1594</v>
       </c>
       <c r="O223" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P223" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="n">
-        <v>1880</v>
+        <v>1859</v>
       </c>
       <c r="B224" s="1" t="n">
-        <v>1936</v>
+        <v>1925</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>1605</v>
+        <v>1595</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="E224" s="10" t="s">
-        <v>1607</v>
+        <v>1597</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>1608</v>
+        <v>1598</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>848</v>
+        <v>80</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>1609</v>
+        <v>917</v>
       </c>
       <c r="M224" s="2" t="s">
-        <v>1610</v>
+        <v>1599</v>
       </c>
       <c r="O224" s="1" t="s">
         <v>271</v>
@@ -15443,69 +15523,72 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="n">
-        <v>1890</v>
+        <v>1879</v>
       </c>
       <c r="B225" s="1" t="n">
-        <v>1981</v>
+        <v>1944</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>1611</v>
+        <v>1600</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>1612</v>
+        <v>1601</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>1613</v>
+        <v>1602</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>1614</v>
+        <v>1603</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K225" s="2" t="s">
-        <v>138</v>
+        <v>1408</v>
       </c>
       <c r="L225" s="2" t="s">
-        <v>1615</v>
+        <v>799</v>
       </c>
       <c r="M225" s="2" t="s">
-        <v>1616</v>
+        <v>1604</v>
       </c>
       <c r="O225" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="P225" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="n">
-        <v>1901</v>
+        <v>1880</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>1989</v>
+        <v>1936</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>1617</v>
+        <v>1605</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>1618</v>
+        <v>1606</v>
       </c>
       <c r="E226" s="10" t="s">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>1620</v>
+        <v>1608</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>1408</v>
+        <v>848</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>1621</v>
+        <v>1609</v>
       </c>
       <c r="M226" s="2" t="s">
-        <v>1622</v>
+        <v>1610</v>
       </c>
       <c r="O226" s="1" t="s">
         <v>271</v>
@@ -15513,31 +15596,34 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="n">
-        <v>1903</v>
+        <v>1890</v>
       </c>
       <c r="B227" s="1" t="n">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>1623</v>
+        <v>1611</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>1624</v>
+        <v>1612</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>1625</v>
+        <v>1613</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>1626</v>
+        <v>1614</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>231</v>
+        <v>138</v>
+      </c>
+      <c r="L227" s="2" t="s">
+        <v>1615</v>
       </c>
       <c r="M227" s="2" t="s">
-        <v>1627</v>
+        <v>1616</v>
       </c>
       <c r="O227" s="1" t="s">
         <v>271</v>
@@ -15545,34 +15631,34 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="n">
-        <v>1912</v>
+        <v>1901</v>
       </c>
       <c r="B228" s="1" t="n">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>1628</v>
+        <v>1617</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>1629</v>
+        <v>1618</v>
       </c>
       <c r="E228" s="10" t="s">
-        <v>1630</v>
+        <v>1619</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>1631</v>
+        <v>1620</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K228" s="2" t="s">
-        <v>546</v>
+        <v>1408</v>
       </c>
       <c r="L228" s="2" t="s">
-        <v>799</v>
+        <v>1621</v>
       </c>
       <c r="M228" s="2" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="O228" s="1" t="s">
         <v>271</v>
@@ -15580,34 +15666,31 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="n">
-        <v>1922</v>
+        <v>1903</v>
       </c>
       <c r="B229" s="1" t="n">
-        <v>1996</v>
+        <v>1976</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>1633</v>
+        <v>1623</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>1635</v>
+        <v>1625</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>916</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>1408</v>
-      </c>
-      <c r="L229" s="2" t="s">
-        <v>1621</v>
+        <v>231</v>
       </c>
       <c r="M229" s="2" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>271</v>
@@ -15615,110 +15698,104 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="n">
-        <v>1613</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>1642</v>
+        <v>1912</v>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>1993</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1644</v>
+        <v>1629</v>
       </c>
       <c r="E230" s="10" t="s">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>267</v>
+        <v>916</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>848</v>
+        <v>546</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>1647</v>
+        <v>799</v>
       </c>
       <c r="M230" s="2" t="s">
-        <v>1648</v>
+        <v>1632</v>
       </c>
       <c r="O230" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P230" s="1" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="n">
-        <v>1619</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>943</v>
+        <v>1922</v>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>1996</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1649</v>
+        <v>1633</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1650</v>
+        <v>1634</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>1651</v>
+        <v>1635</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>1652</v>
+        <v>1636</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>267</v>
+        <v>916</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>268</v>
+        <v>1408</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>691</v>
+        <v>1621</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>1653</v>
+        <v>1637</v>
       </c>
       <c r="O231" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P231" s="1" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="n">
-        <v>1724</v>
+        <v>1613</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1654</v>
+        <v>1642</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1655</v>
+        <v>1643</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>1656</v>
+        <v>1644</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>1657</v>
+        <v>1645</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>1658</v>
+        <v>1646</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>951</v>
+        <v>848</v>
       </c>
       <c r="L232" s="2" t="s">
         <v>1647</v>
       </c>
       <c r="M232" s="2" t="s">
-        <v>1659</v>
+        <v>1648</v>
       </c>
       <c r="O232" s="1" t="s">
         <v>271</v>
@@ -15729,72 +15806,72 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="n">
-        <v>1858</v>
+        <v>1619</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1667</v>
+        <v>943</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1668</v>
+        <v>1649</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1669</v>
+        <v>1650</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>1670</v>
+        <v>1651</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>1671</v>
+        <v>1652</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>1672</v>
+        <v>691</v>
       </c>
       <c r="M233" s="2" t="s">
-        <v>1673</v>
+        <v>1653</v>
       </c>
       <c r="O233" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P233" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="n">
-        <v>1869</v>
+        <v>1724</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1681</v>
+        <v>1654</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>1682</v>
+        <v>1655</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1683</v>
+        <v>1656</v>
       </c>
       <c r="E234" s="10" t="s">
-        <v>1684</v>
+        <v>1657</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>1685</v>
+        <v>1658</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>268</v>
+        <v>951</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>444</v>
+        <v>1647</v>
       </c>
       <c r="M234" s="2" t="s">
-        <v>1686</v>
+        <v>1659</v>
       </c>
       <c r="O234" s="1" t="s">
         <v>271</v>
@@ -15805,22 +15882,22 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="n">
-        <v>1873</v>
+        <v>1858</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1687</v>
+        <v>1667</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1688</v>
+        <v>1668</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>1689</v>
+        <v>1669</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>1690</v>
+        <v>1670</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>1691</v>
+        <v>1671</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>267</v>
@@ -15829,48 +15906,48 @@
         <v>80</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>1665</v>
+        <v>1672</v>
       </c>
       <c r="M235" s="2" t="s">
-        <v>1692</v>
+        <v>1673</v>
       </c>
       <c r="O235" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P235" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="n">
-        <v>1885</v>
+        <v>1869</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1693</v>
+        <v>1681</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>1694</v>
+        <v>1682</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>1695</v>
+        <v>1683</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>1696</v>
+        <v>1684</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>1697</v>
+        <v>1685</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>1698</v>
+        <v>444</v>
       </c>
       <c r="M236" s="2" t="s">
-        <v>1699</v>
+        <v>1686</v>
       </c>
       <c r="O236" s="1" t="s">
         <v>271</v>
@@ -15881,72 +15958,72 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="n">
-        <v>1891</v>
+        <v>1873</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1700</v>
+        <v>1687</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1701</v>
+        <v>1688</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>1702</v>
+        <v>1689</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>1703</v>
+        <v>1690</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>1704</v>
+        <v>1691</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>1192</v>
+        <v>80</v>
       </c>
       <c r="L237" s="2" t="s">
-        <v>1705</v>
+        <v>1665</v>
       </c>
       <c r="M237" s="2" t="s">
-        <v>1706</v>
+        <v>1692</v>
       </c>
       <c r="O237" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P237" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="n">
-        <v>1893</v>
+        <v>1885</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1707</v>
+        <v>1693</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>1708</v>
+        <v>1694</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1709</v>
+        <v>1695</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>1710</v>
+        <v>1696</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>1711</v>
+        <v>1697</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="L238" s="2" t="s">
         <v>1698</v>
       </c>
       <c r="M238" s="2" t="s">
-        <v>1712</v>
+        <v>1699</v>
       </c>
       <c r="O238" s="1" t="s">
         <v>271</v>
@@ -15957,34 +16034,34 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="n">
-        <v>1909</v>
+        <v>1891</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1719</v>
+        <v>1700</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>1720</v>
+        <v>1701</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1721</v>
+        <v>1702</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>1722</v>
+        <v>1703</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>1723</v>
+        <v>1704</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>247</v>
+        <v>1192</v>
       </c>
       <c r="L239" s="2" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="M239" s="2" t="s">
-        <v>1724</v>
+        <v>1706</v>
       </c>
       <c r="O239" s="1" t="s">
         <v>271</v>
@@ -15995,185 +16072,145 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="n">
-        <v>1909</v>
+        <v>1893</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1725</v>
+        <v>1707</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>1726</v>
+        <v>1708</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>1727</v>
+        <v>1709</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>1728</v>
+        <v>1710</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>1729</v>
+        <v>1711</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>267</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="L240" s="2" t="s">
         <v>1698</v>
       </c>
       <c r="M240" s="2" t="s">
-        <v>1730</v>
+        <v>1712</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>271</v>
       </c>
       <c r="P240" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A241" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E241" s="10" t="s">
+        <v>1722</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L241" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M241" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P241" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A242" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>1728</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K242" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L242" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M242" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="O242" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P242" s="1" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="1">
-        <v>767</v>
-      </c>
-      <c r="B241" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">767 – 822</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAICHŌ</t>
-        </is>
-      </c>
-      <c r="E241" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D"  title=" Wikipedia"&gt;SAICHŌ&lt;/a&gt; connu sous son nom posthume de Dengyō Daishi, est le fondateur de l’école bouddhiste Tendai au Japon. Ordonné à Nara, il se retira dès 785 sur le mont Hiei, au nord-est de la future capitale Kyōto, pour y mener une vie de méditation, loin d’un clergé de Nara trop mêlé au pouvoir. En 804, il fit partie de l’ambassade envoyée en Chine des Tang, où il étudia l’école Tiantai, fondée sur le &lt;em&gt;Sûtra du Lotus&lt;/em&gt;, ainsi que le zen, le tantrisme et la discipline monastique.&lt;/p&gt; &lt;p&gt;À son retour, il fit du monastère de l’Enryaku-ji, sur le mont Hiei, le centre d’une synthèse ambitieuse : le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; y est tenu pour l’enseignement ultime du Bouddha, qui réunit toutes les voies en un « Véhicule unique ». Contre les écoles de Nara, il soutient que tous les êtres, sans exception, possèdent la nature de bouddha et peuvent atteindre l’Éveil. Il défendit aussi une ordination propre au Japon, fondée sur les seuls préceptes du Grand Véhicule, que la cour autorisa quelques jours après sa mort.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Règles pour les étudiants de la montagne&lt;/em&gt; prévoyaient douze années de retraite sur le mont Hiei pour former des moines au service du pays, qu’il appelait des « trésors de la nation ». L’Enryaku-ji devint pendant des siècles le plus grand foyer intellectuel du bouddhisme japonais : les fondateurs des grandes écoles de l’époque de Kamakura, Hōnen, Shinran, Eisai, Dōgen et Nichiren, y firent tous leurs études. Son contemporain et rival Kūkai fonda de son côté l’école Shingon.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/saicho-mini.webp</t>
-        </is>
-      </c>
-      <c r="J241" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japonaise</t>
-        </is>
-      </c>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-      <c r="M241" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">moine fondateur de l’école Tendai au Japon et du grand monastère du mont Hiei.</t>
-        </is>
-      </c>
-      <c r="O241" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="P241" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1">
-        <v>1133</v>
-      </c>
-      <c r="B242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133 – 1212</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HŌNEN</t>
-        </is>
-      </c>
-      <c r="E242" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C5%8Dnen"  title=" Wikipedia"&gt;HŌNEN&lt;/a&gt; est le fondateur de l’école japonaise de la Terre pure (&lt;em&gt;Jōdo-shū&lt;/em&gt;). Son père, officier de province, ayant été tué dans une attaque lorsqu’il avait neuf ans, il entra au monastère du mont Hiei, où il étudia pendant une trentaine d’années les textes de toutes les écoles, sans y trouver de voie accessible aux hommes ordinaires d’un temps que l’on disait entré dans l’« âge de la fin de la Loi ».&lt;/p&gt; &lt;p&gt;En 1175, la lecture d’un commentaire du maître chinois Shandao lui apporta la réponse : face à l’impuissance humaine, seul compte le vœu du bouddha Amida de sauver tous ceux qui l’invoquent. Il suffit donc de réciter avec foi le &lt;em&gt;nembutsu&lt;/em&gt;, « Namu Amida Butsu » (« Hommage au bouddha Amida »), pour renaître dans la Terre pure. Dans son &lt;em&gt;Recueil sur le nembutsu du vœu originel choisi&lt;/em&gt; (1198), il affirme que cette pratique, à la portée de tous, hommes et femmes, nobles et paysans, savants et ignorants, suffit, sans méditations savantes ni dons aux monastères.&lt;/p&gt; &lt;p&gt;Cette simplicité radicale attira de nombreux disciples, mais inquiéta les grands monastères, qui obtinrent l’interdiction du &lt;em&gt;nembutsu&lt;/em&gt; exclusif. En 1207, Hōnen, alors âgé de soixante-quatorze ans, fut exilé dans l’île de Shikoku, tandis que plusieurs disciples étaient exécutés. Gracié, il revint à Kyōto peu avant sa mort. Son disciple Shinran approfondit sa pensée en fondant la « véritable école de la Terre pure », qui devint l’une des plus grandes communautés bouddhistes du Japon.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/honen-mini.webp</t>
-        </is>
-      </c>
-      <c r="J242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japonaise</t>
-        </is>
-      </c>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
-        </is>
-      </c>
-      <c r="L242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-      <c r="M242" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">moine fondateur de l’école de la Terre pure, pour qui l’invocation du nom d’Amida suffit au salut.</t>
-        </is>
-      </c>
-      <c r="O242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="P242" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1">
-        <v>1222</v>
+        <v>767</v>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282</t>
+          <t xml:space="preserve">822</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222 – 1282</t>
+          <t xml:space="preserve">767 – 822</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICHIREN</t>
+          <t xml:space="preserve">SAICHŌ</t>
         </is>
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nichiren"  title=" Wikipedia"&gt;NICHIREN&lt;/a&gt; est l’une des figures les plus combatives du bouddhisme japonais. Fils de pêcheur de la province d’Awa, il étudia au mont Hiei et dans les grands monastères, avant d’acquérir la conviction que seul le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; contenait la vérité ultime du Bouddha. En 1253, il proclama publiquement la formule « Namu Myōhō Renge Kyō » (« Hommage au Sûtra du Lotus de la Loi merveilleuse »), dont la récitation devait selon lui suffire à manifester la nature de bouddha en chacun.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Traité pour établir la juste Loi et pacifier le pays&lt;/em&gt; (1260), adressé au pouvoir militaire de Kamakura, il attribue les famines, les épidémies et les tremblements de terre de son époque à l’abandon du &lt;em&gt;Sûtra du Lotus&lt;/em&gt; au profit d’autres écoles, en particulier celle de la Terre pure, et annonce une invasion étrangère si le pays ne se convertit pas. Pour Nichiren, le salut n’est pas seulement individuel : c’est la société tout entière qui doit être transformée, ici-bas, en « terre de bouddha ».&lt;/p&gt; &lt;p&gt;Ses attaques contre les autres écoles et contre le pouvoir lui valurent des persécutions, une tentative d’exécution en 1271, à laquelle il échappa selon la tradition par miracle, et un exil de près de trois ans sur l’île de Sado. Les tentatives d’invasion mongole de 1274 et 1281 parurent confirmer ses prophéties. Son bouddhisme a donné naissance à de nombreuses écoles et à de grands mouvements laïcs modernes, comme la Sōka Gakkai, qui revendiquent aujourd’hui des millions de fidèles dans le monde.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D"  title=" Wikipedia"&gt;SAICHŌ&lt;/a&gt; connu sous son nom posthume de Dengyō Daishi, est le fondateur de l’école bouddhiste Tendai au Japon. Ordonné à Nara, il se retira dès 785 sur le mont Hiei, au nord-est de la future capitale Kyōto, pour y mener une vie de méditation, loin d’un clergé de Nara trop mêlé au pouvoir. En 804, il fit partie de l’ambassade envoyée en Chine des Tang, où il étudia l’école Tiantai, fondée sur le &lt;em&gt;Sûtra du Lotus&lt;/em&gt;, ainsi que le zen, le tantrisme et la discipline monastique.&lt;/p&gt; &lt;p&gt;À son retour, il fit du monastère de l’Enryaku-ji, sur le mont Hiei, le centre d’une synthèse ambitieuse : le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; y est tenu pour l’enseignement ultime du Bouddha, qui réunit toutes les voies en un « Véhicule unique ». Contre les écoles de Nara, il soutient que tous les êtres, sans exception, possèdent la nature de bouddha et peuvent atteindre l’Éveil. Il défendit aussi une ordination propre au Japon, fondée sur les seuls préceptes du Grand Véhicule, que la cour autorisa quelques jours après sa mort.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Règles pour les étudiants de la montagne&lt;/em&gt; prévoyaient douze années de retraite sur le mont Hiei pour former des moines au service du pays, qu’il appelait des « trésors de la nation ». L’Enryaku-ji devint pendant des siècles le plus grand foyer intellectuel du bouddhisme japonais : les fondateurs des grandes écoles de l’époque de Kamakura, Hōnen, Shinran, Eisai, Dōgen et Nichiren, y firent tous leurs études. Son contemporain et rival Kūkai fonda de son côté l’école Shingon.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/nichiren-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/saicho-mini.webp</t>
         </is>
       </c>
       <c r="J243" s="1" t="inlineStr">
@@ -16183,7 +16220,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L243" s="2" t="inlineStr">
@@ -16193,7 +16230,7 @@
       </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">moine prophétique, fondateur d’un bouddhisme centré sur le Sûtra du Lotus.</t>
+          <t xml:space="preserve">moine fondateur de l’école Tendai au Japon et du grand monastère du mont Hiei.</t>
         </is>
       </c>
       <c r="O243" s="1" t="inlineStr">
@@ -16207,31 +16244,31 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1">
-        <v>1363</v>
+        <v>1133</v>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1443</t>
+          <t xml:space="preserve">1212</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 1363 – vers 1443</t>
+          <t xml:space="preserve">1133 – 1212</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEAMI</t>
+          <t xml:space="preserve">HŌNEN</t>
         </is>
       </c>
       <c r="E244" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zeami"  title=" Wikipedia"&gt;ZEAMI&lt;/a&gt; Motokiyo est le grand maître du théâtre nō, qu’il porta à sa perfection après son père Kan’ami. Remarqué à douze ans par le shōgun Ashikaga Yoshimitsu, qui le prit sous sa protection, il fut formé aux lettres et à la poésie dans l’entourage de la cour, et écrivit plusieurs dizaines de pièces, dont beaucoup sont encore jouées aujourd’hui.&lt;/p&gt; &lt;p&gt;Ses traités, longtemps transmis en secret dans sa famille et redécouverts seulement au début du XXe siècle, forment l’une des premières grandes réflexions esthétiques du Japon. Dans &lt;em&gt;De la transmission de la fleur et du style&lt;/em&gt; (&lt;em&gt;Fūshikaden&lt;/em&gt;), il explique que l’acteur doit cultiver la « fleur », ce charme qui surprend et touche le public, et qui change avec l’âge : la fleur de la jeunesse passe, seule demeure celle que l’on a conquise par la discipline. Le sommet de l’art est le &lt;em&gt;yūgen&lt;/em&gt;, une beauté profonde et voilée, faite d’élégance et de mélancolie, qui suggère plus qu’elle ne montre.&lt;/p&gt; &lt;p&gt;Zeami insiste aussi sur la conscience de soi de l’acteur, qui doit se voir comme le voit le spectateur, avec un « regard détaché ». Pour lui, le plus haut moment du jeu est l’instant où l’acteur ne fait rien, où l’intensité intérieure se transmet dans le silence. Tombé en disgrâce sous le shōgun Ashikaga Yoshinori, il fut exilé en 1434 sur l’île de Sado, à plus de soixante-dix ans. Sa pensée, marquée par le bouddhisme zen, inspire encore la réflexion contemporaine sur l’art de l’acteur.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C5%8Dnen"  title=" Wikipedia"&gt;HŌNEN&lt;/a&gt; est le fondateur de l’école japonaise de la Terre pure (&lt;em&gt;Jōdo-shū&lt;/em&gt;). Son père, officier de province, ayant été tué dans une attaque lorsqu’il avait neuf ans, il entra au monastère du mont Hiei, où il étudia pendant une trentaine d’années les textes de toutes les écoles, sans y trouver de voie accessible aux hommes ordinaires d’un temps que l’on disait entré dans l’« âge de la fin de la Loi ».&lt;/p&gt; &lt;p&gt;En 1175, la lecture d’un commentaire du maître chinois Shandao lui apporta la réponse : face à l’impuissance humaine, seul compte le vœu du bouddha Amida de sauver tous ceux qui l’invoquent. Il suffit donc de réciter avec foi le &lt;em&gt;nembutsu&lt;/em&gt;, « Namu Amida Butsu » (« Hommage au bouddha Amida »), pour renaître dans la Terre pure. Dans son &lt;em&gt;Recueil sur le nembutsu du vœu originel choisi&lt;/em&gt; (1198), il affirme que cette pratique, à la portée de tous, hommes et femmes, nobles et paysans, savants et ignorants, suffit, sans méditations savantes ni dons aux monastères.&lt;/p&gt; &lt;p&gt;Cette simplicité radicale attira de nombreux disciples, mais inquiéta les grands monastères, qui obtinrent l’interdiction du &lt;em&gt;nembutsu&lt;/em&gt; exclusif. En 1207, Hōnen, alors âgé de soixante-quatorze ans, fut exilé dans l’île de Shikoku, tandis que plusieurs disciples étaient exécutés. Gracié, il revint à Kyōto peu avant sa mort. Son disciple Shinran approfondit sa pensée en fondant la « véritable école de la Terre pure », qui devint l’une des plus grandes communautés bouddhistes du Japon.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/zeami-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/honen-mini.webp</t>
         </is>
       </c>
       <c r="J244" s="1" t="inlineStr">
@@ -16241,17 +16278,17 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; spiritualite</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen</t>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">acteur et dramaturge, théoricien du théâtre nō et de la beauté du yūgen.</t>
+          <t xml:space="preserve">moine fondateur de l’école de la Terre pure, pour qui l’invocation du nom d’Amida suffit au salut.</t>
         </is>
       </c>
       <c r="O244" s="1" t="inlineStr">
@@ -16265,31 +16302,31 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1">
-        <v>1627</v>
+        <v>1222</v>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1705</t>
+          <t xml:space="preserve">1282</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627 – 1705</t>
+          <t xml:space="preserve">1222 – 1282</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Itō JINSAI</t>
+          <t xml:space="preserve">NICHIREN</t>
         </is>
       </c>
       <c r="E245" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/It%C5%8D_Jinsai"  title=" Wikipedia"&gt;Itō JINSAI&lt;/a&gt; est l’un des penseurs confucéens les plus originaux du Japon. Fils d’un marchand de bois de Kyōto, il refusa la carrière de médecin que sa famille lui destinait et, sans jamais servir de seigneur, ouvrit en 1662 dans sa maison une école privée, le Kogidō (« Salle de l’étude du sens ancien »), qui accueillit pendant plus de quarante ans des milliers d’élèves, samouraïs comme roturiers.&lt;/p&gt; &lt;p&gt;D’abord fervent disciple de Zhu Xi, il traversa une longue crise personnelle, puis rompit avec le néoconfucianisme. Selon lui, les commentaires des Song ont recouvert la pensée de Confucius et de Mencius de notions étrangères, venues du bouddhisme et du taoïsme, comme celle d’un principe abstrait et immobile. Il propose de revenir directement au sens ancien des &lt;em&gt;Entretiens&lt;/em&gt;, qu’il tenait pour « le livre suprême de l’univers », et du &lt;em&gt;Mencius&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Pour Jinsai, le monde est mouvement et vie, et la vertu confucéenne essentielle, la bienveillance (&lt;em&gt;jin&lt;/em&gt;), est avant tout amour : elle se vit dans les relations concrètes de la vie quotidienne, entre parents, amis et voisins, et non dans la contemplation solitaire d’un principe. Sa pensée, accessible aux marchands et aux artisans, contribua à faire du confucianisme une morale de la vie ordinaire. Elle prépara la critique plus radicale d’Ogyū Sorai, et son école fut poursuivie par son fils Itō Tōgai.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nichiren"  title=" Wikipedia"&gt;NICHIREN&lt;/a&gt; est l’une des figures les plus combatives du bouddhisme japonais. Fils de pêcheur de la province d’Awa, il étudia au mont Hiei et dans les grands monastères, avant d’acquérir la conviction que seul le &lt;em&gt;Sûtra du Lotus&lt;/em&gt; contenait la vérité ultime du Bouddha. En 1253, il proclama publiquement la formule « Namu Myōhō Renge Kyō » (« Hommage au Sûtra du Lotus de la Loi merveilleuse »), dont la récitation devait selon lui suffire à manifester la nature de bouddha en chacun.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Traité pour établir la juste Loi et pacifier le pays&lt;/em&gt; (1260), adressé au pouvoir militaire de Kamakura, il attribue les famines, les épidémies et les tremblements de terre de son époque à l’abandon du &lt;em&gt;Sûtra du Lotus&lt;/em&gt; au profit d’autres écoles, en particulier celle de la Terre pure, et annonce une invasion étrangère si le pays ne se convertit pas. Pour Nichiren, le salut n’est pas seulement individuel : c’est la société tout entière qui doit être transformée, ici-bas, en « terre de bouddha ».&lt;/p&gt; &lt;p&gt;Ses attaques contre les autres écoles et contre le pouvoir lui valurent des persécutions, une tentative d’exécution en 1271, à laquelle il échappa selon la tradition par miracle, et un exil de près de trois ans sur l’île de Sado. Les tentatives d’invasion mongole de 1274 et 1281 parurent confirmer ses prophéties. Son bouddhisme a donné naissance à de nombreuses écoles et à de grands mouvements laïcs modernes, comme la Sōka Gakkai, qui revendiquent aujourd’hui des millions de fidèles dans le monde.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/itojinsai-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nichiren-mini.webp</t>
         </is>
       </c>
       <c r="J245" s="1" t="inlineStr">
@@ -16299,17 +16336,17 @@
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme</t>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">confucéen de Kyōto, critique de Zhu Xi et penseur d’une morale de l’amour humain.</t>
+          <t xml:space="preserve">moine prophétique, fondateur d’un bouddhisme centré sur le Sûtra du Lotus.</t>
         </is>
       </c>
       <c r="O245" s="1" t="inlineStr">
@@ -16323,31 +16360,31 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1">
-        <v>1686</v>
+        <v>1363</v>
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769</t>
+          <t xml:space="preserve">1443</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686 – 1769</t>
+          <t xml:space="preserve">vers 1363 – vers 1443</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAKUIN Ekaku</t>
+          <t xml:space="preserve">ZEAMI</t>
         </is>
       </c>
       <c r="E246" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hakuin_Ekaku"  title=" Wikipedia"&gt;HAKUIN Ekaku&lt;/a&gt; est le grand rénovateur du zen Rinzai au Japon. Terrifié dans son enfance par un sermon sur les enfers, il devint moine à quinze ans, connut plusieurs expériences d’éveil, puis une grave « maladie du zen », un épuisement dont il dit s’être guéri grâce à des techniques de respiration et de visualisation enseignées par un ermite. Il passa l’essentiel de sa vie dans un petit temple de sa région natale, le Shōin-ji, au pied du mont Fuji.&lt;/p&gt; &lt;p&gt;Pour lui, l’éveil n’est pas un savoir mais une percée, qui exige une « grande foi », un « grand doute » et une « grande détermination ». Il systématisa l’entraînement par les kōans, ces énigmes qui brisent la pensée ordinaire, et en créa de nouveaux, dont le plus célèbre demande : « Quel est le son d’une seule main ? » Toutes les lignées actuelles du zen Rinzai se rattachent à lui.&lt;/p&gt; &lt;p&gt;Hakuin voulait aussi rendre le zen accessible aux laïcs : il écrivit des chants et des lettres en langue simple, ainsi que des textes sur la santé et la méditation. Peintre et calligraphe prolifique, il laissa des milliers d’œuvres à l’encre, souvent pleines d’humour, représentant Daruma, des dieux populaires ou des scènes de la vie quotidienne, aujourd’hui conservées dans les grands musées. Son &lt;em&gt;Chant de la méditation assise&lt;/em&gt;, qui commence par « Les êtres sont fondamentalement bouddhas », est encore récité dans les temples zen.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zeami"  title=" Wikipedia"&gt;ZEAMI&lt;/a&gt; Motokiyo est le grand maître du théâtre nō, qu’il porta à sa perfection après son père Kan’ami. Remarqué à douze ans par le shōgun Ashikaga Yoshimitsu, qui le prit sous sa protection, il fut formé aux lettres et à la poésie dans l’entourage de la cour, et écrivit plusieurs dizaines de pièces, dont beaucoup sont encore jouées aujourd’hui.&lt;/p&gt; &lt;p&gt;Ses traités, longtemps transmis en secret dans sa famille et redécouverts seulement au début du XXe siècle, forment l’une des premières grandes réflexions esthétiques du Japon. Dans &lt;em&gt;De la transmission de la fleur et du style&lt;/em&gt; (&lt;em&gt;Fūshikaden&lt;/em&gt;), il explique que l’acteur doit cultiver la « fleur », ce charme qui surprend et touche le public, et qui change avec l’âge : la fleur de la jeunesse passe, seule demeure celle que l’on a conquise par la discipline. Le sommet de l’art est le &lt;em&gt;yūgen&lt;/em&gt;, une beauté profonde et voilée, faite d’élégance et de mélancolie, qui suggère plus qu’elle ne montre.&lt;/p&gt; &lt;p&gt;Zeami insiste aussi sur la conscience de soi de l’acteur, qui doit se voir comme le voit le spectateur, avec un « regard détaché ». Pour lui, le plus haut moment du jeu est l’instant où l’acteur ne fait rien, où l’intensité intérieure se transmet dans le silence. Tombé en disgrâce sous le shōgun Ashikaga Yoshinori, il fut exilé en 1434 sur l’île de Sado, à plus de soixante-dix ans. Sa pensée, marquée par le bouddhisme zen, inspire encore la réflexion contemporaine sur l’art de l’acteur.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hakuin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/zeami-mini.webp</t>
         </is>
       </c>
       <c r="J246" s="1" t="inlineStr">
@@ -16357,7 +16394,7 @@
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
@@ -16367,7 +16404,7 @@
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">maître zen rinzai, rénovateur de la pratique des kōans et peintre.</t>
+          <t xml:space="preserve">acteur et dramaturge, théoricien du théâtre nō et de la beauté du yūgen.</t>
         </is>
       </c>
       <c r="O246" s="1" t="inlineStr">
@@ -16381,31 +16418,31 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1">
-        <v>1703</v>
+        <v>1627</v>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1762</t>
+          <t xml:space="preserve">1705</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1703 – 1762</t>
+          <t xml:space="preserve">1627 – 1705</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andō SHŌEKI</t>
+          <t xml:space="preserve">Itō JINSAI</t>
         </is>
       </c>
       <c r="E247" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/And%C5%8D_Sh%C5%8Deki"  title=" Wikipedia"&gt;Andō SHŌEKI&lt;/a&gt; est l’un des penseurs les plus radicaux de l’époque d’Edo. Médecin installé à Hachinohe, dans le nord du Japon, puis revenu dans son village natal de la province d’Akita, il vécut loin des grands centres intellectuels et resta presque inconnu jusqu’à ce que l’érudit Kanō Kōkichi redécouvre son manuscrit à la fin du XIXe siècle.&lt;/p&gt; &lt;p&gt;Dans son grand ouvrage, &lt;em&gt;La Voie de la nature et du vrai fonctionnement&lt;/em&gt; (&lt;em&gt;Shizen shin’eidō&lt;/em&gt;), il oppose au monde des hommes un « monde naturel » originel, où chacun cultivait lui-même la terre pour se nourrir. Cette « culture directe » (&lt;em&gt;chokkō&lt;/em&gt;) est à ses yeux la seule activité vraiment humaine : tous les autres, seigneurs, guerriers, prêtres, marchands, lettrés, vivent en parasites du travail des paysans. Il accuse les sages chinois, Confucius en tête, mais aussi le Bouddha, d’avoir inventé les hiérarchies, l’argent et les lois pour justifier cette exploitation.&lt;/p&gt; &lt;p&gt;Il refuse aussi la supériorité de l’homme sur la femme et pense la nature comme un mouvement unique d’énergie, où les contraires ne s’opposent pas mais se complètent, sans haut ni bas. Ce rejet total de l’ordre féodal a valu à Andō Shōeki d’être présenté, après la guerre, comme un précurseur de l’anarchisme, de l’écologie et de l’égalitarisme. L’historien canadien E. H. Norman lui consacra en 1949 un livre, &lt;em&gt;Andō Shōeki and the Anatomy of Japanese Feudalism&lt;/em&gt;, qui le fit connaître en Occident.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/It%C5%8D_Jinsai"  title=" Wikipedia"&gt;Itō JINSAI&lt;/a&gt; est l’un des penseurs confucéens les plus originaux du Japon. Fils d’un marchand de bois de Kyōto, il refusa la carrière de médecin que sa famille lui destinait et, sans jamais servir de seigneur, ouvrit en 1662 dans sa maison une école privée, le Kogidō (« Salle de l’étude du sens ancien »), qui accueillit pendant plus de quarante ans des milliers d’élèves, samouraïs comme roturiers.&lt;/p&gt; &lt;p&gt;D’abord fervent disciple de Zhu Xi, il traversa une longue crise personnelle, puis rompit avec le néoconfucianisme. Selon lui, les commentaires des Song ont recouvert la pensée de Confucius et de Mencius de notions étrangères, venues du bouddhisme et du taoïsme, comme celle d’un principe abstrait et immobile. Il propose de revenir directement au sens ancien des &lt;em&gt;Entretiens&lt;/em&gt;, qu’il tenait pour « le livre suprême de l’univers », et du &lt;em&gt;Mencius&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Pour Jinsai, le monde est mouvement et vie, et la vertu confucéenne essentielle, la bienveillance (&lt;em&gt;jin&lt;/em&gt;), est avant tout amour : elle se vit dans les relations concrètes de la vie quotidienne, entre parents, amis et voisins, et non dans la contemplation solitaire d’un principe. Sa pensée, accessible aux marchands et aux artisans, contribua à faire du confucianisme une morale de la vie ordinaire. Elle prépara la critique plus radicale d’Ogyū Sorai, et son école fut poursuivie par son fils Itō Tōgai.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/andoshoeki-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/itojinsai-mini.webp</t>
         </is>
       </c>
       <c r="J247" s="1" t="inlineStr">
@@ -16415,17 +16452,17 @@
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">ethique ; epistemologie</t>
         </is>
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Utopisme</t>
+          <t xml:space="preserve">Confucianisme</t>
         </is>
       </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">médecin de province, critique radical de la société féodale et penseur d’une égalité naturelle.</t>
+          <t xml:space="preserve">confucéen de Kyōto, critique de Zhu Xi et penseur d’une morale de l’amour humain.</t>
         </is>
       </c>
       <c r="O247" s="1" t="inlineStr">
@@ -16439,31 +16476,31 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1">
-        <v>1829</v>
+        <v>1686</v>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897</t>
+          <t xml:space="preserve">1769</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829 – 1897</t>
+          <t xml:space="preserve">1686 – 1769</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amane NISHI</t>
+          <t xml:space="preserve">HAKUIN Ekaku</t>
         </is>
       </c>
       <c r="E248" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nishi_Amane"  title=" Wikipedia"&gt;Amane NISHI&lt;/a&gt; est l’un des principaux passeurs de la philosophie occidentale au Japon. Formé d’abord au confucianisme, il apprit le néerlandais puis fut envoyé de 1862 à 1865 à l’université de Leyde, aux Pays-Bas, où il étudia le droit et l’économie et découvrit le positivisme d’Auguste Comte et l’utilitarisme de John Stuart Mill.&lt;/p&gt; &lt;p&gt;De retour au Japon, il entreprit de faire entrer ces idées dans la langue japonaise, ce qui exigeait d’inventer un vocabulaire. On lui doit de nombreux termes encore en usage, formés à partir de caractères chinois : « philosophie » (&lt;em&gt;tetsugaku&lt;/em&gt;), « subjectif » et « objectif », « raison », « conscience », « induction » ou « déduction », mots ensuite adoptés en Chine et en Corée. Dans sa &lt;em&gt;Nouvelle théorie des cent enseignements unifiés&lt;/em&gt;, il présente la philosophie comme la science qui rassemble toutes les autres.&lt;/p&gt; &lt;p&gt;Membre de la Meirokusha, la « Société de l’an six de Meiji » fondée en 1873 avec Fukuzawa Yukichi et d’autres réformateurs, il fut aussi haut fonctionnaire au ministère de la Guerre, où il participa à la rédaction du &lt;em&gt;Rescrit impérial aux soldats&lt;/em&gt; de 1882. Dans ses &lt;em&gt;Trois trésors de la vie humaine&lt;/em&gt;, il adapte l’utilitarisme en faisant de la santé, du savoir et de la richesse les biens que la société doit promouvoir. Son œuvre marque la naissance de la philosophie universitaire au Japon.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hakuin_Ekaku"  title=" Wikipedia"&gt;HAKUIN Ekaku&lt;/a&gt; est le grand rénovateur du zen Rinzai au Japon. Terrifié dans son enfance par un sermon sur les enfers, il devint moine à quinze ans, connut plusieurs expériences d’éveil, puis une grave « maladie du zen », un épuisement dont il dit s’être guéri grâce à des techniques de respiration et de visualisation enseignées par un ermite. Il passa l’essentiel de sa vie dans un petit temple de sa région natale, le Shōin-ji, au pied du mont Fuji.&lt;/p&gt; &lt;p&gt;Pour lui, l’éveil n’est pas un savoir mais une percée, qui exige une « grande foi », un « grand doute » et une « grande détermination ». Il systématisa l’entraînement par les kōans, ces énigmes qui brisent la pensée ordinaire, et en créa de nouveaux, dont le plus célèbre demande : « Quel est le son d’une seule main ? » Toutes les lignées actuelles du zen Rinzai se rattachent à lui.&lt;/p&gt; &lt;p&gt;Hakuin voulait aussi rendre le zen accessible aux laïcs : il écrivit des chants et des lettres en langue simple, ainsi que des textes sur la santé et la méditation. Peintre et calligraphe prolifique, il laissa des milliers d’œuvres à l’encre, souvent pleines d’humour, représentant Daruma, des dieux populaires ou des scènes de la vie quotidienne, aujourd’hui conservées dans les grands musées. Son &lt;em&gt;Chant de la méditation assise&lt;/em&gt;, qui commence par « Les êtres sont fondamentalement bouddhas », est encore récité dans les temples zen.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/nishiamane-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hakuin-mini.webp</t>
         </is>
       </c>
       <c r="J248" s="1" t="inlineStr">
@@ -16473,17 +16510,17 @@
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; logique</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme ; Utilitarisme</t>
+          <t xml:space="preserve">Bouddhisme Zen</t>
         </is>
       </c>
       <c r="M248" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">introducteur de la philosophie occidentale au Japon, inventeur du mot japonais « tetsugaku ».</t>
+          <t xml:space="preserve">maître zen rinzai, rénovateur de la pratique des kōans et peintre.</t>
         </is>
       </c>
       <c r="O248" s="1" t="inlineStr">
@@ -16497,31 +16534,31 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1">
-        <v>1835</v>
+        <v>1703</v>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901</t>
+          <t xml:space="preserve">1762</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835 – 1901</t>
+          <t xml:space="preserve">1703 – 1762</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yukichi FUKUZAWA</t>
+          <t xml:space="preserve">Andō SHŌEKI</t>
         </is>
       </c>
       <c r="E249" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fukuzawa_Yukichi"  title=" Wikipedia"&gt;Yukichi FUKUZAWA&lt;/a&gt; est le principal penseur des Lumières japonaises de l’ère Meiji. Issu d’une famille de samouraïs de rang inférieur, qui souffrit du système des statuts héréditaires, il apprit le néerlandais puis l’anglais, et participa en 1860 à la première ambassade japonaise aux États-Unis, puis en 1862 à une mission en Europe. Ses &lt;em&gt;Choses de l’Occident&lt;/em&gt; (&lt;em&gt;Seiyō jijō&lt;/em&gt;) firent découvrir aux Japonais les institutions, les écoles et les hôpitaux occidentaux.&lt;/p&gt; &lt;p&gt;Son &lt;em&gt;Encouragement à l’étude&lt;/em&gt; (&lt;em&gt;Gakumon no susume&lt;/em&gt;, 1872-1876), vendu à des centaines de milliers d’exemplaires, s’ouvre sur une phrase restée célèbre : « Le Ciel ne crée pas un homme au-dessus d’un autre homme, ni un homme au-dessous d’un autre homme. » Il y défend l’égalité des droits et l’« indépendance de l’individu » : seul un peuple de personnes libres, instruites et responsables peut former une nation indépendante. Dans son &lt;em&gt;Esquisse d’une théorie de la civilisation&lt;/em&gt; (1875), il voit dans l’esprit critique et scientifique, plus que dans les machines, le vrai moteur de la civilisation.&lt;/p&gt; &lt;p&gt;Il fonda en 1858 une école qui devint l’université Keiō, l’une des plus prestigieuses du Japon, ainsi qu’un grand quotidien. Défenseur de la dignité des femmes et de la monogamie, il soutint aussi, à la fin de sa vie, une politique de puissance face à la Chine et à la Corée, ce qui rend son héritage discuté. Son portrait a figuré pendant quarante ans sur le billet de 10 000 yens.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/And%C5%8D_Sh%C5%8Deki"  title=" Wikipedia"&gt;Andō SHŌEKI&lt;/a&gt; est l’un des penseurs les plus radicaux de l’époque d’Edo. Médecin installé à Hachinohe, dans le nord du Japon, puis revenu dans son village natal de la province d’Akita, il vécut loin des grands centres intellectuels et resta presque inconnu jusqu’à ce que l’érudit Kanō Kōkichi redécouvre son manuscrit à la fin du XIXe siècle.&lt;/p&gt; &lt;p&gt;Dans son grand ouvrage, &lt;em&gt;La Voie de la nature et du vrai fonctionnement&lt;/em&gt; (&lt;em&gt;Shizen shin’eidō&lt;/em&gt;), il oppose au monde des hommes un « monde naturel » originel, où chacun cultivait lui-même la terre pour se nourrir. Cette « culture directe » (&lt;em&gt;chokkō&lt;/em&gt;) est à ses yeux la seule activité vraiment humaine : tous les autres, seigneurs, guerriers, prêtres, marchands, lettrés, vivent en parasites du travail des paysans. Il accuse les sages chinois, Confucius en tête, mais aussi le Bouddha, d’avoir inventé les hiérarchies, l’argent et les lois pour justifier cette exploitation.&lt;/p&gt; &lt;p&gt;Il refuse aussi la supériorité de l’homme sur la femme et pense la nature comme un mouvement unique d’énergie, où les contraires ne s’opposent pas mais se complètent, sans haut ni bas. Ce rejet total de l’ordre féodal a valu à Andō Shōeki d’être présenté, après la guerre, comme un précurseur de l’anarchisme, de l’écologie et de l’égalitarisme. L’historien canadien E. H. Norman lui consacra en 1949 un livre, &lt;em&gt;Andō Shōeki and the Anatomy of Japanese Feudalism&lt;/em&gt;, qui le fit connaître en Occident.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fukuzawa-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/andoshoeki-mini.webp</t>
         </is>
       </c>
       <c r="J249" s="1" t="inlineStr">
@@ -16531,17 +16568,17 @@
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Libéralisme</t>
+          <t xml:space="preserve">Utopisme</t>
         </is>
       </c>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fondateur de l’université Keiō, grand promoteur des Lumières et de l’indépendance individuelle au Japon de Meiji.</t>
+          <t xml:space="preserve">médecin de province, critique radical de la société féodale et penseur d’une égalité naturelle.</t>
         </is>
       </c>
       <c r="O249" s="1" t="inlineStr">
@@ -16550,36 +16587,36 @@
         </is>
       </c>
       <c r="P249" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1">
-        <v>1863</v>
+        <v>1829</v>
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">1897</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863 – 1913</t>
+          <t xml:space="preserve">1829 – 1897</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kakuzō OKAKURA</t>
+          <t xml:space="preserve">Amane NISHI</t>
         </is>
       </c>
       <c r="E250" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Okakura_Kakuz%C5%8D"  title=" Wikipedia"&gt;Kakuzō OKAKURA&lt;/a&gt; aussi appelé Okakura Tenshin, est l’un des grands défenseurs de l’art et de la culture d’Asie à l’époque Meiji. Élève et collaborateur de l’Américain Ernest Fenollosa, il recensa avec lui les trésors des temples japonais, menacés par l’occidentalisation, dirigea l’école des Beaux-Arts de Tōkyō, puis fonda avec ses élèves l’Institut des Beaux-Arts du Japon. Il devint ensuite conservateur de l’art asiatique au musée des Beaux-Arts de Boston.&lt;/p&gt; &lt;p&gt;Ses livres, écrits directement en anglais, voulaient faire comprendre l’Asie à l’Occident. &lt;em&gt;Les Idéaux de l’Orient&lt;/em&gt; (1903) s’ouvrent sur la formule « L’Asie est une », qui fut plus tard récupérée par le nationalisme japonais. &lt;em&gt;Le Livre du thé&lt;/em&gt; (1906), son œuvre la plus célèbre, fait de la cérémonie du thé une philosophie de la vie : le « théisme », inspiré du taoïsme et du zen, est un « culte de l’imparfait », une manière de trouver la beauté dans les choses simples et éphémères de l’existence quotidienne.&lt;/p&gt; &lt;p&gt;Pour Okakura, l’Occident moderne a gagné la puissance matérielle mais perdu le sens de l’harmonie et du vide, que l’art asiatique sait encore préserver : la valeur d’une pièce tient à l’espace vide entre ses murs, celle d’un vase au vide qu’il contient. Ami du poète indien Rabindranath Tagore, rencontré lors d’un séjour en Inde en 1902, il rêvait d’une renaissance commune des cultures d’Asie. Lu dans le monde entier, &lt;em&gt;Le Livre du thé&lt;/em&gt; reste l’un des textes les plus influents sur l’esthétique japonaise.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nishi_Amane"  title=" Wikipedia"&gt;Amane NISHI&lt;/a&gt; est l’un des principaux passeurs de la philosophie occidentale au Japon. Formé d’abord au confucianisme, il apprit le néerlandais puis fut envoyé de 1862 à 1865 à l’université de Leyde, aux Pays-Bas, où il étudia le droit et l’économie et découvrit le positivisme d’Auguste Comte et l’utilitarisme de John Stuart Mill.&lt;/p&gt; &lt;p&gt;De retour au Japon, il entreprit de faire entrer ces idées dans la langue japonaise, ce qui exigeait d’inventer un vocabulaire. On lui doit de nombreux termes encore en usage, formés à partir de caractères chinois : « philosophie » (&lt;em&gt;tetsugaku&lt;/em&gt;), « subjectif » et « objectif », « raison », « conscience », « induction » ou « déduction », mots ensuite adoptés en Chine et en Corée. Dans sa &lt;em&gt;Nouvelle théorie des cent enseignements unifiés&lt;/em&gt;, il présente la philosophie comme la science qui rassemble toutes les autres.&lt;/p&gt; &lt;p&gt;Membre de la Meirokusha, la « Société de l’an six de Meiji » fondée en 1873 avec Fukuzawa Yukichi et d’autres réformateurs, il fut aussi haut fonctionnaire au ministère de la Guerre, où il participa à la rédaction du &lt;em&gt;Rescrit impérial aux soldats&lt;/em&gt; de 1882. Dans ses &lt;em&gt;Trois trésors de la vie humaine&lt;/em&gt;, il adapte l’utilitarisme en faisant de la santé, du savoir et de la richesse les biens que la société doit promouvoir. Son œuvre marque la naissance de la philosophie universitaire au Japon.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/okakura-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nishiamane-mini.webp</t>
         </is>
       </c>
       <c r="J250" s="1" t="inlineStr">
@@ -16589,17 +16626,17 @@
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; spiritualite</t>
+          <t xml:space="preserve">epistemologie ; logique</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme ; Bouddhisme Zen</t>
+          <t xml:space="preserve">Positivisme ; Utilitarisme</t>
         </is>
       </c>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien de l’art et auteur du Livre du thé, défenseur de l’esthétique asiatique.</t>
+          <t xml:space="preserve">introducteur de la philosophie occidentale au Japon, inventeur du mot japonais « tetsugaku ».</t>
         </is>
       </c>
       <c r="O250" s="1" t="inlineStr">
@@ -16613,31 +16650,31 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1">
-        <v>1885</v>
+        <v>1835</v>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">1901</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885 – 1962</t>
+          <t xml:space="preserve">1835 – 1901</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hajime TANABE</t>
+          <t xml:space="preserve">Yukichi FUKUZAWA</t>
         </is>
       </c>
       <c r="E251" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tanabe_Hajime"  title=" Wikipedia"&gt;Hajime TANABE&lt;/a&gt; est, avec Kitarō Nishida, l’un des deux fondateurs de l’école de Kyōto. Formé aux mathématiques et à la philosophie des sciences, il étudia en Allemagne au début des années 1920 auprès de Husserl, à Fribourg, où il rencontra le jeune Heidegger, puis succéda à Nishida à l’université impériale de Kyōto, tout en développant une pensée critique envers celle de son maître.&lt;/p&gt; &lt;p&gt;Contre Nishida, à qui il reproche une philosophie trop contemplative, Tanabe élabore une « logique de l’espèce » : entre l’individu et le genre humain universel, il place les communautés particulières, peuples et nations, que la philosophie doit selon lui penser comme telles. Cette théorie, développée dans les années 1930, servit à justifier l’État japonais en guerre, ce que Tanabe reconnut ensuite comme une faute.&lt;/p&gt; &lt;p&gt;À la fin de la guerre, il publia &lt;em&gt;La Philosophie comme métanoétique&lt;/em&gt; (1946), l’un des livres les plus singuliers du siècle : le philosophe, conscient de son impuissance et de sa responsabilité, doit passer par la « repentance » (&lt;em&gt;zange&lt;/em&gt;) et renoncer à la toute-puissance de la raison, pour s’en remettre à une « puissance autre », à la manière de la foi en Amida du bouddhisme de Shinran. Retiré dans les montagnes de Kita-Karuizawa, il consacra ses dernières années à une philosophie de la mort et au dialogue avec le christianisme et le marxisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fukuzawa_Yukichi"  title=" Wikipedia"&gt;Yukichi FUKUZAWA&lt;/a&gt; est le principal penseur des Lumières japonaises de l’ère Meiji. Issu d’une famille de samouraïs de rang inférieur, qui souffrit du système des statuts héréditaires, il apprit le néerlandais puis l’anglais, et participa en 1860 à la première ambassade japonaise aux États-Unis, puis en 1862 à une mission en Europe. Ses &lt;em&gt;Choses de l’Occident&lt;/em&gt; (&lt;em&gt;Seiyō jijō&lt;/em&gt;) firent découvrir aux Japonais les institutions, les écoles et les hôpitaux occidentaux.&lt;/p&gt; &lt;p&gt;Son &lt;em&gt;Encouragement à l’étude&lt;/em&gt; (&lt;em&gt;Gakumon no susume&lt;/em&gt;, 1872-1876), vendu à des centaines de milliers d’exemplaires, s’ouvre sur une phrase restée célèbre : « Le Ciel ne crée pas un homme au-dessus d’un autre homme, ni un homme au-dessous d’un autre homme. » Il y défend l’égalité des droits et l’« indépendance de l’individu » : seul un peuple de personnes libres, instruites et responsables peut former une nation indépendante. Dans son &lt;em&gt;Esquisse d’une théorie de la civilisation&lt;/em&gt; (1875), il voit dans l’esprit critique et scientifique, plus que dans les machines, le vrai moteur de la civilisation.&lt;/p&gt; &lt;p&gt;Il fonda en 1858 une école qui devint l’université Keiō, l’une des plus prestigieuses du Japon, ainsi qu’un grand quotidien. Défenseur de la dignité des femmes et de la monogamie, il soutint aussi, à la fin de sa vie, une politique de puissance face à la Chine et à la Corée, ce qui rend son héritage discuté. Son portrait a figuré pendant quarante ans sur le billet de 10 000 yens.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tanabe-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fukuzawa-mini.webp</t>
         </is>
       </c>
       <c r="J251" s="1" t="inlineStr">
@@ -16647,17 +16684,17 @@
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">politique ; epistemologie</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">École de Kyōto</t>
+          <t xml:space="preserve">Libéralisme</t>
         </is>
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe de l’école de Kyōto, auteur d’une « philosophie comme métanoétique ».</t>
+          <t xml:space="preserve">fondateur de l’université Keiō, grand promoteur des Lumières et de l’indépendance individuelle au Japon de Meiji.</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr">
@@ -16666,36 +16703,36 @@
         </is>
       </c>
       <c r="P251" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1">
-        <v>1886</v>
+        <v>1863</v>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886 – 1971</t>
+          <t xml:space="preserve">1863 – 1913</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raichō HIRATSUKA</t>
+          <t xml:space="preserve">Kakuzō OKAKURA</t>
         </is>
       </c>
       <c r="E252" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raich%C5%8D_Hiratsuka"  title=" Wikipedia"&gt;Raichō HIRATSUKA&lt;/a&gt; est la grande pionnière du féminisme au Japon. Fille d’un haut fonctionnaire de Tōkyō, diplômée de l’université pour femmes du Japon, elle pratiqua le zen dans sa jeunesse et fit scandale en 1908 par une fugue suivie d’une tentative de double suicide avec l’écrivain Morita Sōhei, dont la presse fit ses gros titres.&lt;/p&gt; &lt;p&gt;En 1911, elle fonda la revue &lt;em&gt;Seitō&lt;/em&gt; (« Bas-bleu »), première revue littéraire entièrement faite par des femmes au Japon. Son manifeste d’ouverture est resté célèbre : « À l’origine, la femme était le soleil. Elle était une personne authentique. Aujourd’hui, la femme est la lune », qui ne brille que de la lumière d’un autre. Elle y appelle les femmes à retrouver leur « génie caché », par une libération intérieure autant que sociale, et la revue ouvrit des débats alors très audacieux sur la chasteté, l’avortement et la prostitution.&lt;/p&gt; &lt;p&gt;Influencée par la penseuse suédoise Ellen Key, elle défendit ensuite la protection de la maternité par l’État, ce qui l’opposa à la poétesse Yosano Akiko, partisane de l’indépendance économique des femmes. En 1920, elle fonda avec Ichikawa Fusae l’Association des femmes nouvelles, qui obtint en 1922 le droit pour les femmes d’assister à des réunions politiques. Elle vécut en union libre avec le peintre Okumura Hiroshi, refusant longtemps un mariage qui soumettait l’épouse à la loi familiale. Après la guerre, elle s’engagea dans le pacifisme et le mouvement contre les armes nucléaires.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Okakura_Kakuz%C5%8D"  title=" Wikipedia"&gt;Kakuzō OKAKURA&lt;/a&gt; aussi appelé Okakura Tenshin, est l’un des grands défenseurs de l’art et de la culture d’Asie à l’époque Meiji. Élève et collaborateur de l’Américain Ernest Fenollosa, il recensa avec lui les trésors des temples japonais, menacés par l’occidentalisation, dirigea l’école des Beaux-Arts de Tōkyō, puis fonda avec ses élèves l’Institut des Beaux-Arts du Japon. Il devint ensuite conservateur de l’art asiatique au musée des Beaux-Arts de Boston.&lt;/p&gt; &lt;p&gt;Ses livres, écrits directement en anglais, voulaient faire comprendre l’Asie à l’Occident. &lt;em&gt;Les Idéaux de l’Orient&lt;/em&gt; (1903) s’ouvrent sur la formule « L’Asie est une », qui fut plus tard récupérée par le nationalisme japonais. &lt;em&gt;Le Livre du thé&lt;/em&gt; (1906), son œuvre la plus célèbre, fait de la cérémonie du thé une philosophie de la vie : le « théisme », inspiré du taoïsme et du zen, est un « culte de l’imparfait », une manière de trouver la beauté dans les choses simples et éphémères de l’existence quotidienne.&lt;/p&gt; &lt;p&gt;Pour Okakura, l’Occident moderne a gagné la puissance matérielle mais perdu le sens de l’harmonie et du vide, que l’art asiatique sait encore préserver : la valeur d’une pièce tient à l’espace vide entre ses murs, celle d’un vase au vide qu’il contient. Ami du poète indien Rabindranath Tagore, rencontré lors d’un séjour en Inde en 1902, il rêvait d’une renaissance commune des cultures d’Asie. Lu dans le monde entier, &lt;em&gt;Le Livre du thé&lt;/em&gt; reste l’un des textes les plus influents sur l’esthétique japonaise.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hiratsuka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/okakura-mini.webp</t>
         </is>
       </c>
       <c r="J252" s="1" t="inlineStr">
@@ -16705,22 +16742,17 @@
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Féminisme</t>
+          <t xml:space="preserve">Taoïsme ; Bouddhisme Zen</t>
         </is>
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pionnière du féminisme japonais, fondatrice de la revue Seitō.</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
+          <t xml:space="preserve">historien de l’art et auteur du Livre du thé, défenseur de l’esthétique asiatique.</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr">
@@ -16734,31 +16766,31 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888 – 1941</t>
+          <t xml:space="preserve">1885 – 1962</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shūzō KUKI</t>
+          <t xml:space="preserve">Hajime TANABE</t>
         </is>
       </c>
       <c r="E253" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kuki_Sh%C5%ABz%C5%8D"  title=" Wikipedia"&gt;Shūzō KUKI&lt;/a&gt; est l’un des philosophes japonais les plus cosmopolites de son temps. Fils du baron Kuki Ryūichi, haut fonctionnaire de Meiji, et d’une mère qui fut proche d’Okakura Kakuzō, il passa huit années en Europe dans les années 1920 : il étudia auprès de Rickert à Heidelberg, rencontra Bergson à Paris, où le jeune Jean-Paul Sartre lui donna des leçons de français, et suivit à Marbourg les cours de Heidegger. De retour au Japon, il enseigna à l’université impériale de Kyōto.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Structure de l’iki&lt;/em&gt; (1930), il analyse une notion clé de l’esthétique d’Edo, l’&lt;em&gt;iki&lt;/em&gt;, une élégance raffinée née dans les quartiers de plaisir : un mélange de séduction, de fierté et de détachement, qui garde toujours une distance. Kuki y applique la méthode de la phénoménologie et de l’herméneutique à une expérience proprement japonaise, et montre ce que les mots d’une culture révèlent de sa manière d’être au monde.&lt;/p&gt; &lt;p&gt;Son autre grand livre, &lt;em&gt;Le Problème de la contingence&lt;/em&gt; (1935), fait de la contingence, la rencontre de deux séries indépendantes, ce « qui aurait pu ne pas être », une question philosophique centrale : c’est dans l’étonnement devant la rencontre fortuite que l’existence humaine prend son sens. Heidegger évoqua plus tard leurs échanges dans son &lt;em&gt;Dialogue avec un Japonais&lt;/em&gt;. Kuki mourut en 1941, à cinquante-trois ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tanabe_Hajime"  title=" Wikipedia"&gt;Hajime TANABE&lt;/a&gt; est, avec Kitarō Nishida, l’un des deux fondateurs de l’école de Kyōto. Formé aux mathématiques et à la philosophie des sciences, il étudia en Allemagne au début des années 1920 auprès de Husserl, à Fribourg, où il rencontra le jeune Heidegger, puis succéda à Nishida à l’université impériale de Kyōto, tout en développant une pensée critique envers celle de son maître.&lt;/p&gt; &lt;p&gt;Contre Nishida, à qui il reproche une philosophie trop contemplative, Tanabe élabore une « logique de l’espèce » : entre l’individu et le genre humain universel, il place les communautés particulières, peuples et nations, que la philosophie doit selon lui penser comme telles. Cette théorie, développée dans les années 1930, servit à justifier l’État japonais en guerre, ce que Tanabe reconnut ensuite comme une faute.&lt;/p&gt; &lt;p&gt;À la fin de la guerre, il publia &lt;em&gt;La Philosophie comme métanoétique&lt;/em&gt; (1946), l’un des livres les plus singuliers du siècle : le philosophe, conscient de son impuissance et de sa responsabilité, doit passer par la « repentance » (&lt;em&gt;zange&lt;/em&gt;) et renoncer à la toute-puissance de la raison, pour s’en remettre à une « puissance autre », à la manière de la foi en Amida du bouddhisme de Shinran. Retiré dans les montagnes de Kita-Karuizawa, il consacra ses dernières années à une philosophie de la mort et au dialogue avec le christianisme et le marxisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/kuki-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tanabe-mini.webp</t>
         </is>
       </c>
       <c r="J253" s="1" t="inlineStr">
@@ -16768,17 +16800,17 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; metaphysique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">École de Kyōto ; Phénoménologie</t>
+          <t xml:space="preserve">École de Kyōto</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe de l’iki et de la contingence, passeur entre Kyōto et la phénoménologie européenne.</t>
+          <t xml:space="preserve">philosophe de l’école de Kyōto, auteur d’une « philosophie comme métanoétique ».</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr">
@@ -16792,31 +16824,31 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960</t>
+          <t xml:space="preserve">1971</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889 – 1960</t>
+          <t xml:space="preserve">1886 – 1971</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetsurō WATSUJI</t>
+          <t xml:space="preserve">Raichō HIRATSUKA</t>
         </is>
       </c>
       <c r="E254" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Watsuji_Tetsur%C5%8D"  title=" Wikipedia"&gt;Tetsurō WATSUJI&lt;/a&gt; est l’un des grands philosophes japonais du XXe siècle, proche de l’école de Kyōto. D’abord attiré par Nietzsche et Kierkegaard, auxquels il consacra ses premiers livres, il se tourna vers l’étude de la culture japonaise ancienne, des temples de Nara au bouddhisme de Dōgen, avant d’enseigner l’éthique à l’université impériale de Kyōto, puis à celle de Tōkyō.&lt;/p&gt; &lt;p&gt;En 1927, lors d’un séjour en Allemagne, il lut &lt;em&gt;Être et Temps&lt;/em&gt; de Heidegger et lui reprocha d’avoir pensé l’existence humaine à partir du temps en négligeant l’espace. Dans &lt;em&gt;Fūdo&lt;/em&gt; (1935), traduit en français sous le titre &lt;em&gt;Fûdo, le milieu humain&lt;/em&gt;, il montre que l’être humain est façonné par son climat et son paysage : les cultures de la mousson, du désert et des prairies européennes donnent naissance à des manières différentes d’être au monde.&lt;/p&gt; &lt;p&gt;Son grand œuvre, l’&lt;em&gt;Éthique&lt;/em&gt; (1937-1949), part du mot japonais &lt;em&gt;ningen&lt;/em&gt;, « être humain », écrit avec les caractères « homme » et « entre » : l’humain n’est pas d’abord un individu isolé, mais un être de relations, et l’éthique est la science de cet « entre-deux ». La personne n’existe que dans un double mouvement, par lequel elle se distingue de la communauté puis y revient. Cette pensée de la relation, qui servit aussi à justifier l’ordre impérial, reste l’une des contributions majeures du Japon à la philosophie morale.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raich%C5%8D_Hiratsuka"  title=" Wikipedia"&gt;Raichō HIRATSUKA&lt;/a&gt; est la grande pionnière du féminisme au Japon. Fille d’un haut fonctionnaire de Tōkyō, diplômée de l’université pour femmes du Japon, elle pratiqua le zen dans sa jeunesse et fit scandale en 1908 par une fugue suivie d’une tentative de double suicide avec l’écrivain Morita Sōhei, dont la presse fit ses gros titres.&lt;/p&gt; &lt;p&gt;En 1911, elle fonda la revue &lt;em&gt;Seitō&lt;/em&gt; (« Bas-bleu »), première revue littéraire entièrement faite par des femmes au Japon. Son manifeste d’ouverture est resté célèbre : « À l’origine, la femme était le soleil. Elle était une personne authentique. Aujourd’hui, la femme est la lune », qui ne brille que de la lumière d’un autre. Elle y appelle les femmes à retrouver leur « génie caché », par une libération intérieure autant que sociale, et la revue ouvrit des débats alors très audacieux sur la chasteté, l’avortement et la prostitution.&lt;/p&gt; &lt;p&gt;Influencée par la penseuse suédoise Ellen Key, elle défendit ensuite la protection de la maternité par l’État, ce qui l’opposa à la poétesse Yosano Akiko, partisane de l’indépendance économique des femmes. En 1920, elle fonda avec Ichikawa Fusae l’Association des femmes nouvelles, qui obtint en 1922 le droit pour les femmes d’assister à des réunions politiques. Elle vécut en union libre avec le peintre Okumura Hiroshi, refusant longtemps un mariage qui soumettait l’épouse à la loi familiale. Après la guerre, elle s’engagea dans le pacifisme et le mouvement contre les armes nucléaires.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/watsuji-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hiratsuka-mini.webp</t>
         </is>
       </c>
       <c r="J254" s="1" t="inlineStr">
@@ -16826,17 +16858,22 @@
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; esthetique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">École de Kyōto</t>
+          <t xml:space="preserve">Féminisme</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe de l’éthique comme « entre-deux » humain et du milieu (fūdo).</t>
+          <t xml:space="preserve">pionnière du féminisme japonais, fondatrice de la revue Seitō.</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr">
@@ -16850,66 +16887,56 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1">
-        <v>1946</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1977</t>
+        <v>1888</v>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1941</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1946 – 1977</t>
+          <t xml:space="preserve">1888 – 1941</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steve BIKO</t>
+          <t xml:space="preserve">Shūzō KUKI</t>
         </is>
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Steve_Biko" title=" Wikipedia"&gt;Steve BIKO&lt;/a&gt; est un militant sud-africain de la lutte contre l’&lt;a href="https://fr.wikipedia.org/wiki/Apartheid" title=" Wikipedia"&gt;apartheid&lt;/a&gt; et le fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Mouvement_de_conscience_noire" title=" Wikipedia"&gt;Mouvement de la conscience noire&lt;/a&gt;. Né à King William’s Town, dans la province du Cap, il étudie la médecine à l’université du Natal. En 1969, il rompt avec le syndicat étudiant multiracial dominé par les Blancs et fonde la South African Students’ Organisation (SASO), réservée aux étudiants noirs, dont il devient le premier président. Il y rassemble Africains, Indiens et métis, tous désignés comme « Noirs » face au pouvoir blanc.&lt;/p&gt; &lt;p&gt;Pour lui, l’oppression ne s’exerce pas seulement par les lois, mais aussi dans les esprits : « L’arme la plus puissante entre les mains de l’oppresseur est l’esprit de l’opprimé. » La libération psychologique doit donc précéder la libération politique :&lt;a href="https://www.youtube.com/watch?v=FeNNeAsLpNo" title="STEVE BIKO, Un Symbole de la Résistance Noire par Renaissance africaine"&gt; les Noirs doivent cesser &lt;/a&gt;de se juger à travers le regard des Blancs, retrouver la fierté de leur culture et prendre eux-mêmes en main leur lutte, sans la tutelle, même bienveillante, des libéraux blancs. Nourrie de Fanon, de la &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude" title=" Wikipedia"&gt;négritude&lt;/a&gt; et du mouvement noir américain, sa pensée vise pourtant à terme une société sans race.&lt;/p&gt; &lt;p&gt;Interdit de parole et de déplacement à partir de 1973, il est arrêté en août 1977, torturé en détention et meurt le 12 septembre 1977, à trente ans, après avoir été transporté nu et sans soins jusqu’à Pretoria. Ses écrits sont réunis dans &lt;em&gt;I Write What I Like&lt;/em&gt; (« J’écris ce qui me plaît », 1978). Sa mort, devenue un symbole mondial de la lutte contre l’apartheid, a inspiré la chanson &lt;em&gt;Biko&lt;/em&gt; de Peter Gabriel et le film &lt;em&gt;Cry Freedom&lt;/em&gt;.&lt;/p&gt;  &lt;audio controls title="En Afrique du Sud avec la réouverture de l'enquête sur la mort de Steve Biko, 48 ans après son décès par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13958-15.09.2025-ITEMA_24246880-2025F33228S0258-NET_MFI_0623E44E-6117-4DF1-9729-F661211C1454-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">iJA4mLzXjfg</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L’Histoire Interdite de Steve Biko – Le Héros qui a Défie l’Apartheid" par Légendes et Vérités</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kuki_Sh%C5%ABz%C5%8D"  title=" Wikipedia"&gt;Shūzō KUKI&lt;/a&gt; est l’un des philosophes japonais les plus cosmopolites de son temps. Fils du baron Kuki Ryūichi, haut fonctionnaire de Meiji, et d’une mère qui fut proche d’Okakura Kakuzō, il passa huit années en Europe dans les années 1920 : il étudia auprès de Rickert à Heidelberg, rencontra Bergson à Paris, où le jeune Jean-Paul Sartre lui donna des leçons de français, et suivit à Marbourg les cours de Heidegger. De retour au Japon, il enseigna à l’université impériale de Kyōto.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Structure de l’iki&lt;/em&gt; (1930), il analyse une notion clé de l’esthétique d’Edo, l’&lt;em&gt;iki&lt;/em&gt;, une élégance raffinée née dans les quartiers de plaisir : un mélange de séduction, de fierté et de détachement, qui garde toujours une distance. Kuki y applique la méthode de la phénoménologie et de l’herméneutique à une expérience proprement japonaise, et montre ce que les mots d’une culture révèlent de sa manière d’être au monde.&lt;/p&gt; &lt;p&gt;Son autre grand livre, &lt;em&gt;Le Problème de la contingence&lt;/em&gt; (1935), fait de la contingence, la rencontre de deux séries indépendantes, ce « qui aurait pu ne pas être », une question philosophique centrale : c’est dans l’étonnement devant la rencontre fortuite que l’existence humaine prend son sens. Heidegger évoqua plus tard leurs échanges dans son &lt;em&gt;Dialogue avec un Japonais&lt;/em&gt;. Kuki mourut en 1941, à cinquante-trois ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/biko-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kuki-mini.webp</t>
         </is>
       </c>
       <c r="J255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sud-Africaine</t>
+          <t xml:space="preserve">Japonaise</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
         </is>
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Anticolonialisme</t>
+          <t xml:space="preserve">École de Kyōto ; Phénoménologie</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">militant sud-africain contre l’apartheid, fondateur du Mouvement de la conscience noire.</t>
+          <t xml:space="preserve">philosophe de l’iki et de la contingence, passeur entre Kyōto et la phénoménologie européenne.</t>
         </is>
       </c>
       <c r="O255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
       <c r="P255" s="1">
@@ -16917,109 +16944,125 @@
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="1" t="n">
-        <v>1948</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>1638</v>
+      <c r="A256" s="1">
+        <v>1889</v>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1960</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889 – 1960</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tetsurō WATSUJI</t>
+        </is>
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Do-ol" title=" Wikipedia (en)"&gt;KIM YONG-OK,&lt;/a&gt; connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de &lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi" title=" Wikipedia (en)"&gt;Choe Han-gi&lt;/a&gt;, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JDg8l7CsF8Y</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"[도올 김용옥]우리는 누구인가-동아시아 국제정세(대만편)_01" par jae hak Lee</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J256" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="K256" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L256" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="M256" s="2" t="s">
-        <v>1641</v>
-      </c>
-      <c r="O256" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P256" s="1" t="n">
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Watsuji_Tetsur%C5%8D"  title=" Wikipedia"&gt;Tetsurō WATSUJI&lt;/a&gt; est l’un des grands philosophes japonais du XXe siècle, proche de l’école de Kyōto. D’abord attiré par Nietzsche et Kierkegaard, auxquels il consacra ses premiers livres, il se tourna vers l’étude de la culture japonaise ancienne, des temples de Nara au bouddhisme de Dōgen, avant d’enseigner l’éthique à l’université impériale de Kyōto, puis à celle de Tōkyō.&lt;/p&gt; &lt;p&gt;En 1927, lors d’un séjour en Allemagne, il lut &lt;em&gt;Être et Temps&lt;/em&gt; de Heidegger et lui reprocha d’avoir pensé l’existence humaine à partir du temps en négligeant l’espace. Dans &lt;em&gt;Fūdo&lt;/em&gt; (1935), traduit en français sous le titre &lt;em&gt;Fûdo, le milieu humain&lt;/em&gt;, il montre que l’être humain est façonné par son climat et son paysage : les cultures de la mousson, du désert et des prairies européennes donnent naissance à des manières différentes d’être au monde.&lt;/p&gt; &lt;p&gt;Son grand œuvre, l’&lt;em&gt;Éthique&lt;/em&gt; (1937-1949), part du mot japonais &lt;em&gt;ningen&lt;/em&gt;, « être humain », écrit avec les caractères « homme » et « entre » : l’humain n’est pas d’abord un individu isolé, mais un être de relations, et l’éthique est la science de cet « entre-deux ». La personne n’existe que dans un double mouvement, par lequel elle se distingue de la communauté puis y revient. Cette pensée de la relation, qui servit aussi à justifier l’ordre impérial, reste l’une des contributions majeures du Japon à la philosophie morale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/watsuji-mini.webp</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École de Kyōto</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe de l’éthique comme « entre-deux » humain et du milieu (fūdo).</t>
+        </is>
+      </c>
+      <c r="O256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P256" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1">
-        <v>1556</v>
+        <v>1946</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627</t>
+          <t xml:space="preserve">1977</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556 – 1627</t>
+          <t xml:space="preserve">1946 – 1977</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
+          <t xml:space="preserve">Steve BIKO</t>
         </is>
       </c>
       <c r="E257" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Steve_Biko" title=" Wikipedia"&gt;Steve BIKO&lt;/a&gt; est un militant sud-africain de la lutte contre l’&lt;a href="https://fr.wikipedia.org/wiki/Apartheid" title=" Wikipedia"&gt;apartheid&lt;/a&gt; et le fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Mouvement_de_conscience_noire" title=" Wikipedia"&gt;Mouvement de la conscience noire&lt;/a&gt;. Né à King William’s Town, dans la province du Cap, il étudie la médecine à l’université du Natal. En 1969, il rompt avec le syndicat étudiant multiracial dominé par les Blancs et fonde la South African Students’ Organisation (SASO), réservée aux étudiants noirs, dont il devient le premier président. Il y rassemble Africains, Indiens et métis, tous désignés comme « Noirs » face au pouvoir blanc.&lt;/p&gt; &lt;p&gt;Pour lui, l’oppression ne s’exerce pas seulement par les lois, mais aussi dans les esprits : « L’arme la plus puissante entre les mains de l’oppresseur est l’esprit de l’opprimé. » La libération psychologique doit donc précéder la libération politique :&lt;a href="https://www.youtube.com/watch?v=FeNNeAsLpNo" title="STEVE BIKO, Un Symbole de la Résistance Noire par Renaissance africaine"&gt; les Noirs doivent cesser &lt;/a&gt;de se juger à travers le regard des Blancs, retrouver la fierté de leur culture et prendre eux-mêmes en main leur lutte, sans la tutelle, même bienveillante, des libéraux blancs. Nourrie de Fanon, de la &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude" title=" Wikipedia"&gt;négritude&lt;/a&gt; et du mouvement noir américain, sa pensée vise pourtant à terme une société sans race.&lt;/p&gt; &lt;p&gt;Interdit de parole et de déplacement à partir de 1973, il est arrêté en août 1977, torturé en détention et meurt le 12 septembre 1977, à trente ans, après avoir été transporté nu et sans soins jusqu’à Pretoria. Ses écrits sont réunis dans &lt;em&gt;I Write What I Like&lt;/em&gt; (« J’écris ce qui me plaît », 1978). Sa mort, devenue un symbole mondial de la lutte contre l’apartheid, a inspiré la chanson &lt;em&gt;Biko&lt;/em&gt; de Peter Gabriel et le film &lt;em&gt;Cry Freedom&lt;/em&gt;.&lt;/p&gt;  &lt;audio controls title="En Afrique du Sud avec la réouverture de l'enquête sur la mort de Steve Biko, 48 ans après son décès par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13958-15.09.2025-ITEMA_24246880-2025F33228S0258-NET_MFI_0623E44E-6117-4DF1-9729-F661211C1454-27.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iJA4mLzXjfg</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L’Histoire Interdite de Steve Biko – Le Héros qui a Défie l’Apartheid" par Légendes et Vérités</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/biko-mini.webp</t>
         </is>
       </c>
       <c r="J257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malienne</t>
+          <t xml:space="preserve">Sud-Africaine</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Pan-africanisme ; Anticolonialisme</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
+          <t xml:space="preserve">militant sud-africain contre l’apartheid, fondateur du Mouvement de la conscience noire.</t>
+        </is>
+      </c>
+      <c r="O257" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P257" s="1">
@@ -17027,105 +17070,89 @@
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="1">
-        <v>1901</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1991</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1901 – 1991</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
-        </is>
+      <c r="A258" s="1" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1638</v>
       </c>
       <c r="E258" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
-        </is>
-      </c>
-      <c r="J258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Malienne</t>
-        </is>
-      </c>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
-        </is>
-      </c>
-      <c r="L258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
-        </is>
-      </c>
-      <c r="M258" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="O258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="P258" s="1">
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Do-ol" title=" Wikipedia (en)"&gt;KIM YONG-OK,&lt;/a&gt; connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de &lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi" title=" Wikipedia (en)"&gt;Choe Han-gi&lt;/a&gt;, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JDg8l7CsF8Y</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"[도올 김용옥]우리는 누구인가-동아시아 국제정세(대만편)_01" par jae hak Lee</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L258" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="M258" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="O258" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P258" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1">
-        <v>1912</v>
+        <v>1556</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912 – 1981</t>
+          <t xml:space="preserve">1556 – 1627</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexis KAGAME</t>
+          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
         </is>
       </c>
       <c r="E259" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
         </is>
       </c>
       <c r="J259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rwandaise</t>
+          <t xml:space="preserve">Malienne</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L259" s="2" t="inlineStr">
@@ -17135,12 +17162,17 @@
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
+          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P259" s="1">
@@ -17149,51 +17181,56 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1">
-        <v>1922</v>
+        <v>1901</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999</t>
+          <t xml:space="preserve">1991</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1999</t>
+          <t xml:space="preserve">1901 – 1991</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius NYERERE</t>
+          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
         </is>
       </c>
       <c r="E260" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
         </is>
       </c>
       <c r="J260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tanzanienne</t>
+          <t xml:space="preserve">Malienne</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme</t>
+          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
+          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr">
@@ -17207,51 +17244,51 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1">
-        <v>1924</v>
+        <v>1912</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973</t>
+          <t xml:space="preserve">1981</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924 – 1973</t>
+          <t xml:space="preserve">1912 – 1981</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amílcar CABRAL</t>
+          <t xml:space="preserve">Alexis KAGAME</t>
         </is>
       </c>
       <c r="E261" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
         </is>
       </c>
       <c r="J261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bissau-Guinéenne</t>
+          <t xml:space="preserve">Rwandaise</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
+          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr">
@@ -17265,51 +17302,51 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1">
-        <v>1931</v>
+        <v>1922</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931 – 2019</t>
+          <t xml:space="preserve">1922 – 1999</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">John MBITI</t>
+          <t xml:space="preserve">Julius NYERERE</t>
         </is>
       </c>
       <c r="E262" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/John_Mbiti" title=" Wikipedia (en)"&gt;John MBITI&lt;/a&gt; est un philosophe et théologien kényan, pionnier de l’étude des religions africaines. Né à Kitui, dans l’est du Kenya, il étudie à l’université de Makerere, en Ouganda, puis aux États-Unis et à Cambridge, où il soutient un doctorat de théologie. Prêtre anglican, il enseigne à Makerere de 1964 à 1974, puis dirige l’Institut œcuménique du Conseil œcuménique des Églises, en Suisse, où il est ensuite pasteur à Burgdorf et professeur à l’université de Berne.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969), fondé sur de longues enquêtes, conteste l’idée répandue chez les missionnaires que les religions traditionnelles africaines seraient « démoniaques » : elles méritent selon lui le même respect que le christianisme, l’islam ou le bouddhisme. Il y propose une thèse célèbre sur le temps : dans les langues qu’il étudie, le temps se compose surtout du présent vécu (&lt;em&gt;sasa&lt;/em&gt;) et d’un passé profond (&lt;em&gt;zamani&lt;/em&gt;), le futur lointain restant presque absent. Les défunts dont on garde le souvenir, les « morts-vivants », appartiennent encore au présent de la communauté.&lt;/p&gt; &lt;p&gt;Il résume la conception africaine de la personne par une formule souvent citée : « Je suis parce que nous sommes, et puisque nous sommes, donc je suis », qui fait écho à la notion d’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;. Ses thèses ont été discutées, notamment par ceux qui lui reprochent de généraliser à toute l’Afrique des observations particulières, mais elles ont ouvert un champ immense à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;philosophie africaine&lt;/a&gt;. Il meurt à Burgdorf en 2019.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/jmbiti-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
         </is>
       </c>
       <c r="J262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kényane</t>
+          <t xml:space="preserve">Tanzanienne</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">théologien et philosophe kényan, auteur de Religions et philosophie africaines, penseur du temps africain.</t>
+          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr">
@@ -17323,51 +17360,51 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1">
-        <v>1944</v>
+        <v>1924</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995</t>
+          <t xml:space="preserve">1973</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944 – 1995</t>
+          <t xml:space="preserve">1924 – 1973</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henry ODERA ORUKA</t>
+          <t xml:space="preserve">Amílcar CABRAL</t>
         </is>
       </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
         </is>
       </c>
       <c r="J263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kényane</t>
+          <t xml:space="preserve">Bissau-Guinéenne</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; ethique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
+          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr">
@@ -17381,56 +17418,56 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1">
-        <v>1340</v>
+        <v>1944</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400</t>
+          <t xml:space="preserve">1995</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XIVe siècle</t>
+          <t xml:space="preserve">1944 – 1995</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mpu TANTULAR</t>
+          <t xml:space="preserve">Henry ODERA ORUKA</t>
         </is>
       </c>
       <c r="E264" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mpu_Tantular" title=" Wikipedia (en)"&gt;Mpu TANTULAR&lt;/a&gt; est un poète et sage javanais du XIVe siècle, qui vécut à la cour de l’empire de &lt;a href="https://fr.wikipedia.org/wiki/Majapahit" title=" Wikipedia"&gt;Majapahit&lt;/a&gt;, sous le règne du roi Hayam Wuruk, à l’apogée de cette grande puissance hindoue-bouddhiste de l’archipel. Bouddhiste, il était aussi réputé pour son respect des autres religions. Son nom même signifie « qui ne se laisse pas influencer » : celui d’un maître ferme dans ses convictions. On ne connaît de lui que deux grands poèmes en vieux javanais, le &lt;em&gt;Sutasoma&lt;/em&gt; et l’&lt;em&gt;Arjunawijaya&lt;/em&gt;, des &lt;em&gt;kakawin&lt;/em&gt; composés selon la métrique sanskrite.&lt;/p&gt; &lt;p&gt;Le plus célèbre, le &lt;em&gt;Sutasoma&lt;/em&gt;, raconte l’histoire d’un prince qui est une incarnation du Bouddha : renonçant au trône pour la vie spirituelle, il triomphe de ses ennemis, y compris d’un roi démon mangeur d’hommes, non par la force mais par la compassion, en allant jusqu’à offrir sa propre vie. Le poème défend l’idée que le shivaïsme et le bouddhisme, les deux grandes religions de Java, conduisent à une même vérité : « Le Bouddha et Shiva sont différents, mais ils sont un ; la vérité n’est pas double. »&lt;/p&gt; &lt;p&gt;Cette formule, &lt;a href="https://fr.wikipedia.org/wiki/Bhinneka_Tunggal_Ika" title=" Wikipedia"&gt;&lt;em&gt;Bhinneka Tunggal Ika&lt;/em&gt;&lt;/a&gt;, que l’on traduit par « unité dans la diversité », a été reprise par le juriste Mohammad Yamin et choisie au XXe siècle comme devise nationale de la république d’Indonésie, pays aux centaines de langues et aux multiples religions. Elle figure sur les armoiries du pays, inscrite sur le ruban que tient l’aigle Garuda. Ainsi, une méditation religieuse du XIVe siècle est devenue le principe philosophique d’une nation moderne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tantular-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
         </is>
       </c>
       <c r="J264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indonésienne</t>
+          <t xml:space="preserve">Kényane</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">epistemologie ; ethique</t>
         </is>
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana ; Hindouisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète bouddhiste de Java, auteur du Sutasoma, d’où vient la devise de l’Indonésie « Unité dans la diversité ».</t>
+          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
         </is>
       </c>
       <c r="O264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="P264" s="1">
@@ -17439,31 +17476,31 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1">
-        <v>1530</v>
+        <v>1340</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">1400</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XVIe siècle</t>
+          <t xml:space="preserve">XIVe siècle</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAMZAH FANSURI</t>
+          <t xml:space="preserve">Mpu TANTULAR</t>
         </is>
       </c>
       <c r="E265" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;HAMZAH FANSURI&lt;/a&gt; est un poète et mystique soufi de Sumatra, le premier grand écrivain connu de langue malaise. Sa vie est mal connue : on la reconstitue surtout à partir des dernières strophes de ses poèmes, où il glisse son nom et quelques indications sur lui-même. Son nom suggère qu’il venait de Barus, appelé Fansur par les Arabes, un port de la côte ouest de Sumatra. Il voyagea beaucoup, dans la péninsule malaise, en Inde moghole, à La Mecque, à Médine et à Bagdad, et aurait été initié à une confrérie soufie.&lt;/p&gt; &lt;p&gt;Il est le premier à exprimer en malais la doctrine de l’« unicité de l’être » (&lt;a href="https://fr.wikipedia.org/wiki/Wahdat_al-wujud" title=" Wikipedia"&gt;&lt;em&gt;wahdat al-wujud&lt;/em&gt;&lt;/a&gt;) issue d’&lt;a href="https://fr.wikipedia.org/wiki/Ibn_Arabi" title=" Wikipedia"&gt;Ibn Arabî&lt;/a&gt; : toute réalité est une, et Dieu se manifeste en toutes choses, par degrés successifs, jusqu’à l’« Homme parfait » et au cœur de chacun, qui doit le retrouver en lui-même. Il le dit dans des poèmes de forme nouvelle, les &lt;em&gt;syair&lt;/em&gt;, dont il est considéré comme l’inventeur, et dans trois traités en prose, dont &lt;em&gt;La Boisson des amants&lt;/em&gt; et &lt;em&gt;Les Secrets des gnostiques&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Au XVIIe siècle, sous l’influence du théologien Nuruddin ar-Raniri, son enseignement fut jugé hérétique à la cour du sultanat d’&lt;a href="https://fr.wikipedia.org/wiki/Aceh" title=" Wikipedia"&gt;Aceh&lt;/a&gt;, car il semblait confondre Dieu et sa création, et ses livres furent brûlés. Une trentaine de ses poèmes ont pourtant survécu. Leur virtuosité, l’art d’y fondre les mots arabes dans la langue malaise et leur goût du jeu de mots font de lui le fondateur de la poésie malaise. Le philosophe Naquib al-Attas lui a consacré sa thèse de doctorat, qui a contribué à le faire redécouvrir.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mpu_Tantular" title=" Wikipedia (en)"&gt;Mpu TANTULAR&lt;/a&gt; est un poète et sage javanais du XIVe siècle, qui vécut à la cour de l’empire de &lt;a href="https://fr.wikipedia.org/wiki/Majapahit" title=" Wikipedia"&gt;Majapahit&lt;/a&gt;, sous le règne du roi Hayam Wuruk, à l’apogée de cette grande puissance hindoue-bouddhiste de l’archipel. Bouddhiste, il était aussi réputé pour son respect des autres religions. Son nom même signifie « qui ne se laisse pas influencer » : celui d’un maître ferme dans ses convictions. On ne connaît de lui que deux grands poèmes en vieux javanais, le &lt;em&gt;Sutasoma&lt;/em&gt; et l’&lt;em&gt;Arjunawijaya&lt;/em&gt;, des &lt;em&gt;kakawin&lt;/em&gt; composés selon la métrique sanskrite.&lt;/p&gt; &lt;p&gt;Le plus célèbre, le &lt;em&gt;Sutasoma&lt;/em&gt;, raconte l’histoire d’un prince qui est une incarnation du Bouddha : renonçant au trône pour la vie spirituelle, il triomphe de ses ennemis, y compris d’un roi démon mangeur d’hommes, non par la force mais par la compassion, en allant jusqu’à offrir sa propre vie. Le poème défend l’idée que le shivaïsme et le bouddhisme, les deux grandes religions de Java, conduisent à une même vérité : « Le Bouddha et Shiva sont différents, mais ils sont un ; la vérité n’est pas double. »&lt;/p&gt; &lt;p&gt;Cette formule, &lt;a href="https://fr.wikipedia.org/wiki/Bhinneka_Tunggal_Ika" title=" Wikipedia"&gt;&lt;em&gt;Bhinneka Tunggal Ika&lt;/em&gt;&lt;/a&gt;, que l’on traduit par « unité dans la diversité », a été reprise par le juriste Mohammad Yamin et choisie au XXe siècle comme devise nationale de la république d’Indonésie, pays aux centaines de langues et aux multiples religions. Elle figure sur les armoiries du pays, inscrite sur le ruban que tient l’aigle Garuda. Ainsi, une méditation religieuse du XIVe siècle est devenue le principe philosophique d’une nation moderne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fansuri-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tantular-mini.webp</t>
         </is>
       </c>
       <c r="J265" s="1" t="inlineStr">
@@ -17478,17 +17515,17 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soufisme</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Hindouisme</t>
         </is>
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète soufi de Sumatra, premier grand auteur mystique de langue malaise.</t>
+          <t xml:space="preserve">poète bouddhiste de Java, auteur du Sutasoma, d’où vient la devise de l’Indonésie « Unité dans la diversité ».</t>
         </is>
       </c>
       <c r="O265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="P265" s="1">
@@ -17497,56 +17534,56 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1">
-        <v>1861</v>
+        <v>1530</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896</t>
+          <t xml:space="preserve">1590</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1861 – 1896</t>
+          <t xml:space="preserve">XVIe siècle</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">José RIZAL</t>
+          <t xml:space="preserve">HAMZAH FANSURI</t>
         </is>
       </c>
       <c r="E266" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Rizal" title=" Wikipedia"&gt;José RIZAL&lt;/a&gt; est le héros national des Philippines, écrivain, médecin et penseur de l’émancipation de son peuple sous la domination espagnole. Né à Calamba dans une famille aisée, il étudie à Manille puis en Europe, à Madrid, Paris et Heidelberg, où il devient ophtalmologiste. Polyglotte, il parle une vingtaine de langues et traduit Schiller en tagalog. Il appartient aux &lt;em&gt;ilustrados&lt;/em&gt;, la jeune élite philippine instruite en Europe et nourrie des idées libérales. Il réédite même une chronique espagnole du XVIe siècle pour montrer que les Philippins avaient une civilisation avant la conquête.&lt;/p&gt; &lt;p&gt;Son roman &lt;a href="https://fr.wikipedia.org/wiki/Noli_me_tangere_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Noli me tangere&lt;/em&gt;&lt;/a&gt;, publié à Berlin en 1887, puis sa suite, &lt;em&gt;El Filibusterismo&lt;/em&gt; (1891), dont le titre, emprunté à l’Évangile (« Ne me touche pas »), désigne un mal si sensible qu’on n’ose y toucher, dénoncent les abus des ordres religieux et de l’administration coloniale, l’ignorance entretenue et le mépris des « indios ». Rizal croit d’abord à la réforme plutôt qu’à la révolution : il demande l’égalité des droits, la représentation des Philippines aux Cortes espagnoles et surtout l’éducation, car un peuple ne peut être libre s’il n’a pas appris à penser par lui-même et à se respecter.&lt;/p&gt; &lt;p&gt;De retour aux Philippines en 1892, il fonde la Ligue philippine, une association réformiste et pacifique, ce qui lui vaut d’être exilé à Dapitan, où il ouvre une école et un dispensaire. Accusé à tort d’avoir inspiré l’insurrection de 1896, qu’il n’approuvait pas, il est fusillé à Manille le 30 décembre 1896, à trente-cinq ans. La veille, il écrit son poème d’adieu, &lt;em&gt;Mi último adiós&lt;/em&gt;. Sa mort accélère la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution philippine&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;HAMZAH FANSURI&lt;/a&gt; est un poète et mystique soufi de Sumatra, le premier grand écrivain connu de langue malaise. Sa vie est mal connue : on la reconstitue surtout à partir des dernières strophes de ses poèmes, où il glisse son nom et quelques indications sur lui-même. Son nom suggère qu’il venait de Barus, appelé Fansur par les Arabes, un port de la côte ouest de Sumatra. Il voyagea beaucoup, dans la péninsule malaise, en Inde moghole, à La Mecque, à Médine et à Bagdad, et aurait été initié à une confrérie soufie.&lt;/p&gt; &lt;p&gt;Il est le premier à exprimer en malais la doctrine de l’« unicité de l’être » (&lt;a href="https://fr.wikipedia.org/wiki/Wahdat_al-wujud" title=" Wikipedia"&gt;&lt;em&gt;wahdat al-wujud&lt;/em&gt;&lt;/a&gt;) issue d’&lt;a href="https://fr.wikipedia.org/wiki/Ibn_Arabi" title=" Wikipedia"&gt;Ibn Arabî&lt;/a&gt; : toute réalité est une, et Dieu se manifeste en toutes choses, par degrés successifs, jusqu’à l’« Homme parfait » et au cœur de chacun, qui doit le retrouver en lui-même. Il le dit dans des poèmes de forme nouvelle, les &lt;em&gt;syair&lt;/em&gt;, dont il est considéré comme l’inventeur, et dans trois traités en prose, dont &lt;em&gt;La Boisson des amants&lt;/em&gt; et &lt;em&gt;Les Secrets des gnostiques&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Au XVIIe siècle, sous l’influence du théologien Nuruddin ar-Raniri, son enseignement fut jugé hérétique à la cour du sultanat d’&lt;a href="https://fr.wikipedia.org/wiki/Aceh" title=" Wikipedia"&gt;Aceh&lt;/a&gt;, car il semblait confondre Dieu et sa création, et ses livres furent brûlés. Une trentaine de ses poèmes ont pourtant survécu. Leur virtuosité, l’art d’y fondre les mots arabes dans la langue malaise et leur goût du jeu de mots font de lui le fondateur de la poésie malaise. Le philosophe Naquib al-Attas lui a consacré sa thèse de doctorat, qui a contribué à le faire redécouvrir.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rizal-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fansuri-mini.webp</t>
         </is>
       </c>
       <c r="J266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippine</t>
+          <t xml:space="preserve">Indonésienne</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
+          <t xml:space="preserve">Soufisme</t>
         </is>
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain, médecin et humaniste philippin, héros national, critique de la domination coloniale espagnole.</t>
+          <t xml:space="preserve">poète soufi de Sumatra, premier grand auteur mystique de langue malaise.</t>
         </is>
       </c>
       <c r="O266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P266" s="1">
@@ -17555,31 +17592,31 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1">
-        <v>1864</v>
+        <v>1861</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1896</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864 – 1903</t>
+          <t xml:space="preserve">1861 – 1896</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apolinario MABINI</t>
+          <t xml:space="preserve">José RIZAL</t>
         </is>
       </c>
       <c r="E267" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apolinario_Mabini" title=" Wikipedia"&gt;Apolinario MABINI&lt;/a&gt; est le principal penseur politique de la révolution philippine, surnommé « le cerveau de la révolution ». Fils de paysans pauvres de Tanauan, il fait ses études grâce à des bourses et à des leçons qu’il donne pour vivre, puis obtient en 1894 un diplôme de droit, choisi pour défendre les pauvres. Peu avant la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution de 1896&lt;/a&gt;, il perd l’usage de ses deux jambes, sans doute à cause de la polio : c’est sur une chaise à porteurs qu’il accomplira toute son action politique.&lt;/p&gt; &lt;p&gt;Conseiller d’Emilio Aguinaldo, il rédige en 1898 &lt;em&gt;Le Vrai Décalogue&lt;/em&gt;, dix commandements civiques qui mêlent devoirs envers Dieu, envers la patrie et envers autrui : aimer sa patrie, ne reconnaître pour chef que celui qui est élu par le peuple, voir en chacun un égal. Son &lt;em&gt;Programme constitutionnel de la République philippine&lt;/em&gt; inspire la Constitution de Malolos. En 1899, il devient le premier chef du gouvernement de la Première République philippine, et défend une souveraineté populaire fondée sur la raison et sur la morale plutôt que sur la force. Opposé au pouvoir personnel, il entre en conflit avec Aguinaldo et doit démissionner la même année.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre les États-Unis, il est capturé puis exilé sur l’île de Guam, où il écrit &lt;em&gt;La Révolution philippine&lt;/em&gt;, où il attribue l’échec du mouvement aux divisions et à l’ambition de ses chefs plus qu’à la seule force de l’ennemi. Autorisé à rentrer en 1903 après avoir prêté serment d’allégeance aux Américains, il meurt du choléra à Manille quelques mois plus tard, à trente-huit ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Rizal" title=" Wikipedia"&gt;José RIZAL&lt;/a&gt; est le héros national des Philippines, écrivain, médecin et penseur de l’émancipation de son peuple sous la domination espagnole. Né à Calamba dans une famille aisée, il étudie à Manille puis en Europe, à Madrid, Paris et Heidelberg, où il devient ophtalmologiste. Polyglotte, il parle une vingtaine de langues et traduit Schiller en tagalog. Il appartient aux &lt;em&gt;ilustrados&lt;/em&gt;, la jeune élite philippine instruite en Europe et nourrie des idées libérales. Il réédite même une chronique espagnole du XVIe siècle pour montrer que les Philippins avaient une civilisation avant la conquête.&lt;/p&gt; &lt;p&gt;Son roman &lt;a href="https://fr.wikipedia.org/wiki/Noli_me_tangere_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Noli me tangere&lt;/em&gt;&lt;/a&gt;, publié à Berlin en 1887, puis sa suite, &lt;em&gt;El Filibusterismo&lt;/em&gt; (1891), dont le titre, emprunté à l’Évangile (« Ne me touche pas »), désigne un mal si sensible qu’on n’ose y toucher, dénoncent les abus des ordres religieux et de l’administration coloniale, l’ignorance entretenue et le mépris des « indios ». Rizal croit d’abord à la réforme plutôt qu’à la révolution : il demande l’égalité des droits, la représentation des Philippines aux Cortes espagnoles et surtout l’éducation, car un peuple ne peut être libre s’il n’a pas appris à penser par lui-même et à se respecter.&lt;/p&gt; &lt;p&gt;De retour aux Philippines en 1892, il fonde la Ligue philippine, une association réformiste et pacifique, ce qui lui vaut d’être exilé à Dapitan, où il ouvre une école et un dispensaire. Accusé à tort d’avoir inspiré l’insurrection de 1896, qu’il n’approuvait pas, il est fusillé à Manille le 30 décembre 1896, à trente-cinq ans. La veille, il écrit son poème d’adieu, &lt;em&gt;Mi último adiós&lt;/em&gt;. Sa mort accélère la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution philippine&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/mabini-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rizal-mini.webp</t>
         </is>
       </c>
       <c r="J267" s="1" t="inlineStr">
@@ -17594,12 +17631,12 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juriste et penseur de la révolution philippine, premier chef du gouvernement des Philippines, surnommé « le cerveau de la révolution ».</t>
+          <t xml:space="preserve">écrivain, médecin et humaniste philippin, héros national, critique de la domination coloniale espagnole.</t>
         </is>
       </c>
       <c r="O267" s="1" t="inlineStr">
@@ -17613,41 +17650,41 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1">
-        <v>1889</v>
+        <v>1864</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889 – 1959</t>
+          <t xml:space="preserve">1864 – 1903</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KI HAJAR DEWANTARA</t>
+          <t xml:space="preserve">Apolinario MABINI</t>
         </is>
       </c>
       <c r="E268" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ki_Hajar_Dewantara" title=" Wikipedia"&gt;KI HAJAR DEWANTARA&lt;/a&gt; est le grand penseur de l’éducation indonésienne. Né à Yogyakarta sous le nom de Raden Mas Soewardi Soerjaningrat, petit-fils d’un prince javanais, il devient journaliste et militant nationaliste, et cofonde en 1912 l’Indische Partij, premier parti à réclamer l’indépendance. Il est l’un des premiers à employer le nom d’« Indonésie ». En 1913, son article ironique « Si j’étais Néerlandais », qui raille les fêtes organisées dans la colonie pour célébrer l’indépendance des Pays-Bas, lui vaut d’être exilé en Europe. Il y découvre les pédagogies de Fröbel et de Montessori, ainsi que l’école de Tagore en Inde.&lt;/p&gt; &lt;p&gt;De retour, il fonde en 1922 à Yogyakarta le &lt;a href="https://fr.wikipedia.org/wiki/Taman_Siswa" title=" Wikipedia"&gt;Taman Siswa&lt;/a&gt; (« jardin des élèves »), un réseau d’écoles indépendantes du pouvoir colonial, qui enseignent à la fois les savoirs modernes et la culture javanaise. La même année, il abandonne son titre aristocratique pour le nom plus simple de Ki Hajar Dewantara. Pour lui, l’éducation ne consiste pas à remplir les esprits, mais à « guider les forces naturelles » de l’enfant pour qu’il devienne un être libre, autonome et responsable envers sa communauté.&lt;/p&gt; &lt;p&gt;Sa devise résume le rôle du maître : « Devant, donner l’exemple ; au milieu, susciter la volonté ; derrière, soutenir. » Sa dernière partie, &lt;em&gt;Tut wuri handayani&lt;/em&gt;, est aujourd’hui celle du ministère indonésien de l’Éducation. Premier ministre de l’Éducation de l’Indonésie indépendante, il est proclamé héros national en 1959, et le jour de sa naissance, le 2 mai, est devenu la Journée nationale de l’éducation.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apolinario_Mabini" title=" Wikipedia"&gt;Apolinario MABINI&lt;/a&gt; est le principal penseur politique de la révolution philippine, surnommé « le cerveau de la révolution ». Fils de paysans pauvres de Tanauan, il fait ses études grâce à des bourses et à des leçons qu’il donne pour vivre, puis obtient en 1894 un diplôme de droit, choisi pour défendre les pauvres. Peu avant la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution de 1896&lt;/a&gt;, il perd l’usage de ses deux jambes, sans doute à cause de la polio : c’est sur une chaise à porteurs qu’il accomplira toute son action politique.&lt;/p&gt; &lt;p&gt;Conseiller d’Emilio Aguinaldo, il rédige en 1898 &lt;em&gt;Le Vrai Décalogue&lt;/em&gt;, dix commandements civiques qui mêlent devoirs envers Dieu, envers la patrie et envers autrui : aimer sa patrie, ne reconnaître pour chef que celui qui est élu par le peuple, voir en chacun un égal. Son &lt;em&gt;Programme constitutionnel de la République philippine&lt;/em&gt; inspire la Constitution de Malolos. En 1899, il devient le premier chef du gouvernement de la Première République philippine, et défend une souveraineté populaire fondée sur la raison et sur la morale plutôt que sur la force. Opposé au pouvoir personnel, il entre en conflit avec Aguinaldo et doit démissionner la même année.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre les États-Unis, il est capturé puis exilé sur l’île de Guam, où il écrit &lt;em&gt;La Révolution philippine&lt;/em&gt;, où il attribue l’échec du mouvement aux divisions et à l’ambition de ses chefs plus qu’à la seule force de l’ennemi. Autorisé à rentrer en 1903 après avoir prêté serment d’allégeance aux Américains, il meurt du choléra à Manille quelques mois plus tard, à trente-huit ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dewantara-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mabini-mini.webp</t>
         </is>
       </c>
       <c r="J268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indonésienne</t>
+          <t xml:space="preserve">Philippine</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L268" s="2" t="inlineStr">
@@ -17657,7 +17694,7 @@
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue et militant indonésien, fondateur des écoles Taman Siswa, père de l’éducation nationale.</t>
+          <t xml:space="preserve">juriste et penseur de la révolution philippine, premier chef du gouvernement des Philippines, surnommé « le cerveau de la révolution ».</t>
         </is>
       </c>
       <c r="O268" s="1" t="inlineStr">
@@ -17671,31 +17708,31 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1">
-        <v>1897</v>
+        <v>1889</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1949</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897 – 1949</t>
+          <t xml:space="preserve">1889 – 1959</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAN MALAKA</t>
+          <t xml:space="preserve">KI HAJAR DEWANTARA</t>
         </is>
       </c>
       <c r="E269" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tan_Malaka" title=" Wikipedia"&gt;TAN MALAKA&lt;/a&gt; est un révolutionnaire et penseur indonésien, l’un des premiers à concevoir une république indonésienne indépendante. Né dans le pays minangkabau, à Sumatra, il étudie pour devenir instituteur, puis aux Pays-Bas, où il découvre le marxisme et la révolution russe. Rentré en 1919, il enseigne aux enfants des ouvriers des plantations puis prend en 1921 la tête du Parti communiste indonésien. Arrêté et banni dès 1922, il passe plus de vingt ans en exil et dans la clandestinité, en Europe, en Chine, aux Philippines et à Singapour, comme agent de l’Internationale communiste.&lt;/p&gt; &lt;p&gt;Son livre le plus important, &lt;em&gt;Madilog&lt;/em&gt; (1943), dont le titre réunit matérialisme, dialectique et logique, veut libérer ses compatriotes de ce qu’il appelle la « logique mystique » : l’habitude d’expliquer les événements par des forces surnaturelles, des esprits ou le destin, qui selon lui entretient la passivité face à l’oppression. Il leur oppose la méthode scientifique et la pensée critique, condition d’une véritable indépendance. Il refuse aussi d’opposer l’islam et le communisme, deux forces qu’il voulait unir contre le colonialisme.&lt;/p&gt; &lt;p&gt;Revenu en Indonésie pendant la révolution, il s’oppose aux négociations avec les Pays-Bas menées par le gouvernement de &lt;a href="https://fr.wikipedia.org/wiki/Soekarno" title=" Wikipedia"&gt;Soekarno&lt;/a&gt;, que ses écrits avaient pourtant inspiré, et réclame une « indépendance à cent pour cent ». En février 1949, il est capturé et exécuté par des soldats de l’armée indonésienne. Longtemps passé sous silence, il a été proclamé héros national en 1963.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ki_Hajar_Dewantara" title=" Wikipedia"&gt;KI HAJAR DEWANTARA&lt;/a&gt; est le grand penseur de l’éducation indonésienne. Né à Yogyakarta sous le nom de Raden Mas Soewardi Soerjaningrat, petit-fils d’un prince javanais, il devient journaliste et militant nationaliste, et cofonde en 1912 l’Indische Partij, premier parti à réclamer l’indépendance. Il est l’un des premiers à employer le nom d’« Indonésie ». En 1913, son article ironique « Si j’étais Néerlandais », qui raille les fêtes organisées dans la colonie pour célébrer l’indépendance des Pays-Bas, lui vaut d’être exilé en Europe. Il y découvre les pédagogies de Fröbel et de Montessori, ainsi que l’école de Tagore en Inde.&lt;/p&gt; &lt;p&gt;De retour, il fonde en 1922 à Yogyakarta le &lt;a href="https://fr.wikipedia.org/wiki/Taman_Siswa" title=" Wikipedia"&gt;Taman Siswa&lt;/a&gt; (« jardin des élèves »), un réseau d’écoles indépendantes du pouvoir colonial, qui enseignent à la fois les savoirs modernes et la culture javanaise. La même année, il abandonne son titre aristocratique pour le nom plus simple de Ki Hajar Dewantara. Pour lui, l’éducation ne consiste pas à remplir les esprits, mais à « guider les forces naturelles » de l’enfant pour qu’il devienne un être libre, autonome et responsable envers sa communauté.&lt;/p&gt; &lt;p&gt;Sa devise résume le rôle du maître : « Devant, donner l’exemple ; au milieu, susciter la volonté ; derrière, soutenir. » Sa dernière partie, &lt;em&gt;Tut wuri handayani&lt;/em&gt;, est aujourd’hui celle du ministère indonésien de l’Éducation. Premier ministre de l’Éducation de l’Indonésie indépendante, il est proclamé héros national en 1959, et le jour de sa naissance, le 2 mai, est devenu la Journée nationale de l’éducation.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tanmalaka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dewantara-mini.webp</t>
         </is>
       </c>
       <c r="J269" s="1" t="inlineStr">
@@ -17705,17 +17742,17 @@
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme ; Anticolonialisme</t>
+          <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">révolutionnaire indonésien, marxiste indépendant, auteur de Madilog, critique de la « logique mystique ».</t>
+          <t xml:space="preserve">pédagogue et militant indonésien, fondateur des écoles Taman Siswa, père de l’éducation nationale.</t>
         </is>
       </c>
       <c r="O269" s="1" t="inlineStr">
@@ -17729,56 +17766,56 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1">
-        <v>1906</v>
+        <v>1897</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993</t>
+          <t xml:space="preserve">1949</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906 – 1993</t>
+          <t xml:space="preserve">1897 – 1949</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUDDHADASA Bhikkhu</t>
+          <t xml:space="preserve">TAN MALAKA</t>
         </is>
       </c>
       <c r="E270" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buddhadasa" title=" Wikipedia"&gt;BUDDHADASA Bhikkhu&lt;/a&gt; est un moine bouddhiste thaïlandais, l’un des grands réformateurs du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title=" Wikipedia"&gt;Theravâda&lt;/a&gt; au XXe siècle. Son nom signifie « serviteur du Bouddha ». Fils d’un commerçant du sud de la Thaïlande, ordonné moine en 1926, il part étudier à Bangkok, mais il est déçu par des monastères qu’il juge plus soucieux de prestige que de libération. Il rentre dans sa région natale et fonde en 1932, dans une forêt, Suan Mokkh, le « jardin de la libération », qui deviendra un lieu de retraite pour des pratiquants du monde entier.&lt;/p&gt; &lt;p&gt;Revenant aux textes anciens en pâli, il veut dégager le cœur de l’enseignement du Bouddha des rituels, des superstitions et du commerce des mérites. Il distingue la « langue des gens », qui prend les mots à la lettre, et la « langue du dhamma », qui en saisit le sens profond. Ainsi, la renaissance ne désigne pas d’abord le passage d’une vie à une autre, mais la naissance du sentiment de « moi » et de « mien », qui se produit à chaque instant et que la pratique doit apprendre à défaire. Son idéal est un esprit « libre et vide » de cet attachement.&lt;/p&gt; &lt;p&gt;Persuadé qu’au fond toutes les religions disent la même chose, il dialogue avec des chrétiens et des musulmans. Il propose aussi un « socialisme du dhamma », qui fonde l’organisation de la société sur la modération et le partage plutôt que sur l’accumulation. Pendant les années démocratiques de 1973 à 1976, ses idées sont largement diffusées, et il débat à la télévision avec l’homme politique Kukrit Pramoj. Il meurt en 1993 à Suan Mokkh.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tan_Malaka" title=" Wikipedia"&gt;TAN MALAKA&lt;/a&gt; est un révolutionnaire et penseur indonésien, l’un des premiers à concevoir une république indonésienne indépendante. Né dans le pays minangkabau, à Sumatra, il étudie pour devenir instituteur, puis aux Pays-Bas, où il découvre le marxisme et la révolution russe. Rentré en 1919, il enseigne aux enfants des ouvriers des plantations puis prend en 1921 la tête du Parti communiste indonésien. Arrêté et banni dès 1922, il passe plus de vingt ans en exil et dans la clandestinité, en Europe, en Chine, aux Philippines et à Singapour, comme agent de l’Internationale communiste.&lt;/p&gt; &lt;p&gt;Son livre le plus important, &lt;em&gt;Madilog&lt;/em&gt; (1943), dont le titre réunit matérialisme, dialectique et logique, veut libérer ses compatriotes de ce qu’il appelle la « logique mystique » : l’habitude d’expliquer les événements par des forces surnaturelles, des esprits ou le destin, qui selon lui entretient la passivité face à l’oppression. Il leur oppose la méthode scientifique et la pensée critique, condition d’une véritable indépendance. Il refuse aussi d’opposer l’islam et le communisme, deux forces qu’il voulait unir contre le colonialisme.&lt;/p&gt; &lt;p&gt;Revenu en Indonésie pendant la révolution, il s’oppose aux négociations avec les Pays-Bas menées par le gouvernement de &lt;a href="https://fr.wikipedia.org/wiki/Soekarno" title=" Wikipedia"&gt;Soekarno&lt;/a&gt;, que ses écrits avaient pourtant inspiré, et réclame une « indépendance à cent pour cent ». En février 1949, il est capturé et exécuté par des soldats de l’armée indonésienne. Longtemps passé sous silence, il a été proclamé héros national en 1963.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/buddhadasa-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tanmalaka-mini.webp</t>
         </is>
       </c>
       <c r="J270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thaïlandaise</t>
+          <t xml:space="preserve">Indonésienne</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">politique ; epistemologie</t>
         </is>
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Theravada</t>
+          <t xml:space="preserve">Marxisme ; Anticolonialisme</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">moine bouddhiste thaïlandais, réformateur du Theravâda, penseur du « socialisme du dhamma ».</t>
+          <t xml:space="preserve">révolutionnaire indonésien, marxiste indépendant, auteur de Madilog, critique de la « logique mystique ».</t>
         </is>
       </c>
       <c r="O270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="P270" s="1">
@@ -18251,6 +18288,964 @@
         </is>
       </c>
       <c r="P278" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A279" s="1">
+        <v>538</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">597</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">538 – 597</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHIYI</t>
+        </is>
+      </c>
+      <c r="E279" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zhiyi" title=" Wikipedia"&gt;ZHIYI&lt;/a&gt; est un moine bouddhiste chinois, véritable fondateur de l’école &lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Tiantai&lt;/a&gt;, la première grande école du bouddhisme proprement chinois. Né dans une famille de fonctionnaires du Hubei, il perd ses parents dans les guerres qui déchirent la Chine du Sud et entre en religion vers dix-huit ans. Disciple du maître Huisi, il enseigne à la cour des Chen à Nankin, puis se retire en 575 dans les monts Tiantai, qui donneront leur nom à son école. L’empereur Sui lui décerne le titre de « Maître de sagesse ».&lt;/p&gt; &lt;p&gt;Face à l’immense masse de textes venus de l’Inde, souvent contradictoires, il propose un grand classement des enseignements du Bouddha, ordonnés selon les étapes de sa prédication et les capacités de ses auditeurs : tous sont vrais, mais à des degrés différents, et tous culminent dans le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sûtra du Lotus&lt;/em&gt;&lt;/a&gt;, qui affirme que chaque être peut devenir bouddha. Il enseigne aussi les « trois vérités » : toute chose est vide, existe de façon provisoire et se tient au milieu entre ces deux aspects, qui ne font qu’un.&lt;/p&gt; &lt;p&gt;Sa formule la plus célèbre, « trois mille mondes en un instant de pensée », signifie que la totalité du réel, des enfers jusqu’à l’éveil, est présente dans chaque moment de conscience. Dans &lt;em&gt;La Grande Concentration et contemplation&lt;/em&gt;, il unit la méditation qui apaise l’esprit et celle qui voit clair, et refuse de séparer l’étude et la pratique. Son école, transmise au Japon par &lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D" title=" Wikipedia"&gt;Saichō&lt;/a&gt; sous le nom de Tendai, a nourri presque tout le bouddhisme japonais : Hōnen, Shinran et Nichiren furent tous formés dans ses monastères du mont Hiei.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/zhiyi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J279" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine chinois, fondateur de l’école bouddhiste Tiantai, qui fit du Sûtra du Lotus le sommet de l’enseignement.</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O279" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P279" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A280" s="1">
+        <v>638</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638 – 713</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUINENG</t>
+        </is>
+      </c>
+      <c r="E280" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huineng" title=" Wikipedia"&gt;HUINENG&lt;/a&gt; est le sixième patriarche du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A1n_%28bouddhisme%29" title=" Wikipedia"&gt;chan&lt;/a&gt;, l’ancêtre du zen, et l’une des figures les plus célèbres de la spiritualité chinoise. Ce que l’on sait de lui vient surtout du &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_de_l%E2%80%99Estrade" title=" Wikipedia"&gt;&lt;em&gt;Sûtra de l’Estrade&lt;/em&gt;&lt;/a&gt;, son enseignement recueilli par ses disciples. Selon ce récit, il naît dans le sud de la Chine dans une famille pauvre et vend du bois pour nourrir sa mère. Illettré, il entend un jour réciter le &lt;em&gt;Sûtra du Diamant&lt;/em&gt; et s’éveille aussitôt. Il part alors pour le monastère du cinquième patriarche, Hongren, où on l’emploie à piler le riz.&lt;/p&gt; &lt;p&gt;Pour choisir son successeur, Hongren demande à ses disciples un poème. Le plus savant écrit que l’esprit est comme un miroir qu’il faut sans cesse épousseter. Huineng fait écrire à côté : « L’éveil n’est pas un arbre, le clair miroir n’a pas de support ; fondamentalement, il n’y a pas une chose : où la poussière pourrait-elle se poser ? » Hongren lui transmet en secret la robe et le bol du patriarcat et lui conseille de fuir. Huineng vit caché pendant quinze ans, puis enseigne dans le sud.&lt;/p&gt; &lt;p&gt;Son enseignement est celui de l’« éveil subit » : la nature de bouddha est déjà présente en chacun, et il ne s’agit pas de la conquérir par degrés, mais de la voir d’un coup, en cessant de s’attacher aux pensées. Deux moines se disputant pour savoir si c’est le vent ou le drapeau qui bouge, il leur répond : « Ni le vent ni le drapeau : c’est votre esprit qui bouge. » Toutes les écoles du chan et du zen qui ont survécu, en Chine, en Corée, au Japon et au Vietnam, se réclament de lui.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/huineng-mini.webp</t>
+        </is>
+      </c>
+      <c r="J280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sixième patriarche du bouddhisme chan, maître de l’éveil subit, dont descendent toutes les écoles zen.</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P280" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A281" s="1">
+        <v>685</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">763</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 685 – vers 763</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHANTIDEVA</t>
+        </is>
+      </c>
+      <c r="E281" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shantideva" title=" Wikipedia"&gt;SHANTIDEVA&lt;/a&gt; est un moine et poète bouddhiste indien, auteur de l’un des textes les plus aimés du bouddhisme : le &lt;a href="https://fr.wikipedia.org/wiki/Bodhicary%C4%81vat%C4%81ra" title=" Wikipedia"&gt;&lt;em&gt;Bodhicaryâvatâra&lt;/em&gt;&lt;/a&gt;, ou &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Selon la tradition, il est le fils d’un roi du Gujarat et renonce au trône la veille de son couronnement. Il devient moine à &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A2land%C3%A2" title=" Wikipedia"&gt;Nâlandâ&lt;/a&gt;, la grande université monastique de l’Inde, où les autres moines le surnomment avec mépris « Bhusuku », celui qui ne sait que manger, dormir et se promener.&lt;/p&gt; &lt;p&gt;Invités à le ridiculiser en le faisant parler devant tous, ils l’entendent réciter un poème inconnu d’une beauté saisissante : &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Ce texte en dix chapitres décrit le chemin du bodhisattva, celui qui fait le vœu d’atteindre l’éveil pour le bien de tous les êtres. Il y enseigne la patience face à la colère, qui détruit en un instant le bien accumulé, et l’« échange de soi et d’autrui » : toute la souffrance du monde vient de vouloir son propre bonheur, tout le bonheur du monde vient de vouloir celui des autres.&lt;/p&gt; &lt;p&gt;Le neuvième chapitre expose la philosophie du &lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Madhyamaka&lt;/a&gt; : aucune chose, ni le moi, n’existe par elle-même. Shantideva est aussi l’auteur d’un &lt;em&gt;Recueil des enseignements&lt;/em&gt;, qui cite de nombreux sûtras aujourd’hui perdus. Traduit très tôt en tibétain et commenté par des générations de maîtres, son poème est au cœur du bouddhisme tibétain, et le dalaï-lama cite souvent sa prière : « Aussi longtemps que durera l’espace, aussi longtemps que vivront les êtres, puissé-je moi aussi demeurer pour dissiper la souffrance du monde. »&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/shantideva-mini.webp</t>
+        </is>
+      </c>
+      <c r="J281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine et poète indien, auteur de La Marche vers l’éveil, grand texte de la compassion bouddhiste.</t>
+        </is>
+      </c>
+      <c r="O281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P281" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A282" s="1">
+        <v>1469</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1539</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1469 – 1539</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GURU NANAK</t>
+        </is>
+      </c>
+      <c r="E282" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guru_Nanak" title=" Wikipedia"&gt;GURU NANAK&lt;/a&gt; est un mystique et poète indien, fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Sikhisme" title=" Wikipedia"&gt;sikhisme&lt;/a&gt; et premier des dix gurus de cette religion. Né en 1469 à Talwandi, au Pendjab, aujourd’hui au Pakistan, dans une famille lettrée, il apprend le sanskrit et le persan, et fréquente dès l’enfance les ascètes hindous et les soufis musulmans qui parcourent la région. Devenu intendant au service d’un gouverneur, il disparaît, selon la tradition, trois jours dans une rivière et en revient en déclarant : « Il n’y a ni hindou ni musulman. »&lt;/p&gt; &lt;p&gt;Il passe ensuite de longues années à voyager à travers l’Inde et, selon ses biographies, jusqu’à La Mecque et Bagdad, chantant ses hymnes accompagné d’un musicien musulman. Son message tient en une affirmation : Dieu est un, sans forme, présent en toute chose, et on l’atteint non par les rites, les pèlerinages ou l’ascèse, mais par l’amour et la méditation de son Nom. Il critique les castes, les idoles et le formalisme des religieux, hindous comme musulmans, et affirme la dignité des femmes.&lt;/p&gt; &lt;p&gt;À la fin de sa vie, il fonde à Kartarpur une communauté où l’on vit de son travail. Il y résume la vie juste en trois préceptes : se souvenir de Dieu, gagner honnêtement sa vie et partager avec les autres. Il institue la cuisine commune, le &lt;a href="https://fr.wikipedia.org/wiki/Langar" title=" Wikipedia"&gt;&lt;em&gt;langar&lt;/em&gt;&lt;/a&gt;, où tous mangent ensemble assis au même rang, quelle que soit leur caste, pratique toujours vivante dans les temples sikhs. Ses hymnes, réunis dans le &lt;a href="https://fr.wikipedia.org/wiki/Guru_Granth_Sahib" title=" Wikipedia"&gt;&lt;em&gt;Guru Granth Sahib&lt;/em&gt;&lt;/a&gt;, le livre saint des sikhs, s’ouvrent sur les mots &lt;em&gt;Ik Onkar&lt;/em&gt; : « Il n’y a qu’un Dieu ».&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gurunanak-mini.webp</t>
+        </is>
+      </c>
+      <c r="J282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sikhisme</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fondateur du sikhisme, mystique et poète du Pendjab, qui refusa les divisions entre religions et entre castes.</t>
+        </is>
+      </c>
+      <c r="O282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P282" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A283" s="1">
+        <v>480</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">540</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 480 – vers 540</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIGNAGA</t>
+        </is>
+      </c>
+      <c r="E283" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dign%C4%81ga" title=" Wikipedia"&gt;DIGNAGA&lt;/a&gt; est un philosophe et logicien bouddhiste indien, fondateur de la grande tradition de la logique et de la théorie de la connaissance bouddhistes. On sait peu de choses de sa vie : né dans une famille brahmane près de Kanchi, dans le sud de l’Inde, il devient moine très jeune, enseigne en Andhra et fréquente l’université monastique de Nâlandâ. Il vit à une époque de débats intenses entre les écoles bouddhistes et brahmaniques, où il faut savoir démontrer et réfuter.&lt;/p&gt; &lt;p&gt;Dans son grand traité, le &lt;em&gt;Compendium des moyens de connaissance&lt;/em&gt;, il n’admet que deux sources de savoir valides, les &lt;a href="https://fr.wikipedia.org/wiki/Pramana" title=" Wikipedia"&gt;&lt;em&gt;pramâna&lt;/em&gt;&lt;/a&gt; : la perception, qui saisit le particulier, l’instant unique et sans nom, et l’inférence, qui passe par des notions générales. Le témoignage des Écritures, que les brahmanes tiennent pour une source autonome, n’est pour lui qu’une forme d’inférence. Il formalise aussi le raisonnement valide, en précisant à quelles conditions un signe permet de conclure, comme la fumée permet de conclure au feu.&lt;/p&gt; &lt;p&gt;Sa théorie de l’« exclusion » (&lt;em&gt;apoha&lt;/em&gt;) explique le sens des mots : un mot comme « vache » ne désigne pas une essence commune à toutes les vaches, mais exclut tout ce qui n’est pas vache. Ainsi, le langage ne copie pas le réel, fait d’instants singuliers, il le découpe. Prolongée par Dharmakîrti, sa pensée a dominé la philosophie indienne et tibétaine pendant des siècles, et ses adversaires de l’école du Nyâya ont dû lui répondre. Elle est aujourd’hui comparée aux grands débats occidentaux sur la logique et le langage.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dignaga-mini.webp</t>
+        </is>
+      </c>
+      <c r="J283" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logicien bouddhiste indien, fondateur de la théorie bouddhiste de la connaissance et de l’inférence.</t>
+        </is>
+      </c>
+      <c r="O283" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P283" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A284" s="1">
+        <v>700</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIIIe siècle</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PADMASAMBHAVA</t>
+        </is>
+      </c>
+      <c r="E284" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Padmasambhava" title=" Wikipedia"&gt;PADMASAMBHAVA&lt;/a&gt; est un maître bouddhiste tantrique du VIIIe siècle, considéré comme le fondateur du bouddhisme au &lt;a href="https://fr.wikipedia.org/wiki/Tibet" title=" Wikipedia"&gt;Tibet&lt;/a&gt;, où on l’appelle Guru Rinpoché, le « précieux maître ». Il serait né dans la vallée de Swat, dans l’actuel Pakistan, alors appelée Oddiyana, et sa légende le fait naître d’une fleur de lotus, d’où son nom, « né du lotus ». Maître de méditation et des pratiques tantriques du Vajrayana, il est invité au Tibet vers 760 par le roi Trisong Detsen.&lt;/p&gt; &lt;p&gt;Selon la tradition, il soumet par sa puissance spirituelle les esprits et les divinités locales hostiles au bouddhisme, qu’il transforme en protecteurs de l’enseignement. Avec le savant indien Shantarakshita, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Monast%C3%A8re_de_Samy%C3%A9" title=" Wikipedia"&gt;monastère de Samyé&lt;/a&gt;, premier monastère du Tibet, où sont formés les premiers moines tibétains et où l’on entreprend la traduction en tibétain des textes bouddhistes indiens. Sa compagne et disciple Yeshe Tsogyal recueille son enseignement.&lt;/p&gt; &lt;p&gt;Il aurait caché dans des grottes, des rochers et même dans l’esprit de ses disciples des enseignements secrets, les « trésors » (&lt;em&gt;terma&lt;/em&gt;), destinés à être redécouverts plus tard, au moment opportun. Le célèbre &lt;em&gt;Livre des morts tibétain&lt;/em&gt;, guide pour traverser l’état intermédiaire entre la mort et la renaissance, appartient à cette tradition. L’école &lt;a href="https://fr.wikipedia.org/wiki/Nyingmapa" title=" Wikipedia"&gt;Nyingma&lt;/a&gt;, la plus ancienne du bouddhisme tibétain, le vénère comme un second Bouddha, et sa figure reste omniprésente dans l’art et les fêtes de l’Himalaya, où on le représente coiffé d’un bonnet en forme de lotus, tenant un vajra et une coupe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/padmasambhava-mini.webp</t>
+        </is>
+      </c>
+      <c r="J284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maître tantrique indien du VIIIe siècle, « Guru Rinpoché », fondateur légendaire du bouddhisme tibétain.</t>
+        </is>
+      </c>
+      <c r="O284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P284" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A285" s="1">
+        <v>643</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">712</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">643 – 712</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAZANG</t>
+        </is>
+      </c>
+      <c r="E285" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fazang" title=" Wikipedia"&gt;FAZANG&lt;/a&gt; est un moine bouddhiste chinois, le principal penseur de l’école &lt;a href="https://fr.wikipedia.org/wiki/Huayan" title=" Wikipedia"&gt;Huayan&lt;/a&gt; (« Ornementation fleurie »). Ses ancêtres venaient de Sogdiane, en Asie centrale, une grande région de commerce de la route de la soie, mais il naît à Chang’an, la capitale des Tang. Traducteur connaissant le sanskrit, il participe à une nouvelle traduction du &lt;em&gt;Sûtra de l’ornementation fleurie&lt;/em&gt;, l’immense texte qui donne son nom à l’école, et rédige plus d’une centaine d’ouvrages.&lt;/p&gt; &lt;p&gt;Il jouit de la faveur de l’impératrice &lt;a href="https://fr.wikipedia.org/wiki/Wu_Zetian" title=" Wikipedia"&gt;Wu Zetian&lt;/a&gt;, à qui il explique la doctrine par des images restées célèbres. Dans son &lt;em&gt;Essai sur le lion d’or&lt;/em&gt;, il montre une statue de lion : l’or est comme le principe, le vide de toute chose, et la forme du lion comme les phénomènes. On ne peut les séparer : chaque partie du lion contient l’or tout entier, et l’or n’existe ici que sous la forme du lion. Pour une autre démonstration, il dispose des miroirs autour d’une statue du Bouddha et d’une lampe, si bien que chaque miroir reflète tous les autres à l’infini.&lt;/p&gt; &lt;p&gt;C’est l’image du « filet d’Indra » : un filet dont chaque nœud porte une perle qui reflète toutes les autres. Toute chose est en toutes les autres, et toutes sont en chacune ; rien n’existe isolément, tout s’interpénètre sans obstacle. Cette vision d’une interdépendance totale a profondément marqué le bouddhisme chinois, coréen et japonais, notamment le chan, et elle est souvent rapprochée aujourd’hui de la pensée écologique. En Corée, elle a été développée par &lt;a href="https://fr.wikipedia.org/wiki/Uisang" title=" Wikipedia"&gt;Uisang&lt;/a&gt;, condisciple et correspondant de Fazang.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fazang-mini.webp</t>
+        </is>
+      </c>
+      <c r="J285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine chinois d’origine sogdienne, maître de l’école Huayan et du Lion d’or, penseur de l’interdépendance universelle.</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P285" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A286" s="1">
+        <v>810</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">866</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 810 – 866</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LINJI Yixuan</t>
+        </is>
+      </c>
+      <c r="E286" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Linji" title=" Wikipedia"&gt;LINJI Yixuan&lt;/a&gt; est un maître du bouddhisme chan de la dynastie Tang, considéré comme le fondateur de l’école qui porte son nom, devenue au Japon le zen &lt;a href="https://fr.wikipedia.org/wiki/Rinzai" title=" Wikipedia"&gt;Rinzai&lt;/a&gt;. Sa vie, mêlée de légende, est connue par les &lt;em&gt;Entretiens de Linji&lt;/em&gt;, recueil de ses paroles. Formé à l’étude des textes, il les abandonne pour suivre le maître Huangbo. Trois fois, il lui demande quel est le sens essentiel du bouddhisme, et trois fois Huangbo le frappe. Ce n’est qu’auprès d’un autre maître qu’il comprend la bienveillance de ces coups, et s’éveille.&lt;/p&gt; &lt;p&gt;Installé dans un petit temple du nord de la Chine, au bord d’une rivière, il enseigne avec une liberté et une brusquerie qui font scandale. Il crie, frappe, répond par des paradoxes, pour arracher ses disciples à leurs idées toutes faites. Son message : le Bouddha n’est pas ailleurs, il est « l’homme vrai sans rang » qui entre et sort par les portes de nos sens. Il faut cesser de chercher au dehors, dans les textes, les rites ou les saints.&lt;/p&gt; &lt;p&gt;D’où sa formule provocante : « Si tu rencontres le Bouddha, tue le Bouddha ; si tu rencontres un patriarche, tue le patriarche. » Il ne s’agit pas de violence, mais de ne s’attacher à rien, pas même aux figures sacrées, pour être libre. « Sois maître partout où tu te trouves, et là où tu es, tout est vrai. » Son école, qui utilisera plus tard les célèbres énigmes appelées &lt;em&gt;kôans&lt;/em&gt;, s’est répandue en Chine, en Corée, au Japon et au Vietnam. Il meurt en 866, et ses &lt;em&gt;Entretiens&lt;/em&gt; sont devenus l’un des textes majeurs du zen.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/linji-mini.webp</t>
+        </is>
+      </c>
+      <c r="J286" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maître chan de la dynastie Tang, iconoclaste et radical, fondateur de l’école qui deviendra le zen Rinzai.</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="O286" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P286" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A287" s="1">
+        <v>982</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1054</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">982 – 1054</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATISHA</t>
+        </is>
+      </c>
+      <c r="E287" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Atisha" title=" Wikipedia"&gt;ATISHA&lt;/a&gt; est un maître bouddhiste indien, né au Bengale dans une famille royale, qui joua un rôle décisif dans la renaissance du bouddhisme au Tibet. Renonçant à la vie princière, il étudie pendant de longues années auprès de nombreux maîtres, dans toutes les écoles bouddhistes et même hindoues, puis devient l’un des grands savants de l’université monastique de &lt;a href="https://fr.wikipedia.org/wiki/Vikrama%C5%9B%C4%ABla" title=" Wikipedia"&gt;Vikramashila&lt;/a&gt;. Il aurait aussi voyagé jusqu’à Sumatra, pour étudier pendant douze ans auprès d’un maître de la compassion.&lt;/p&gt; &lt;p&gt;Vers 1042, il accepte l’invitation d’un roi de l’ouest du Tibet, où le bouddhisme s’était affaibli et mêlé de pratiques douteuses. Il y passe le reste de sa vie. Pour remettre de l’ordre, il écrit &lt;em&gt;La Lampe sur la voie de l’éveil&lt;/em&gt;, un court texte qui organise tout le chemin spirituel en étapes, selon les capacités de chacun : d’abord se soucier de ses vies futures, puis viser sa propre libération, enfin travailler à l’éveil de tous les êtres. Il y montre que la discipline morale, la compassion et les pratiques tantriques ne s’opposent pas.&lt;/p&gt; &lt;p&gt;Cette « voie graduée » (&lt;em&gt;lamrim&lt;/em&gt;) est devenue le cadre de l’enseignement de presque toutes les écoles tibétaines. Atisha insiste aussi sur l’« entraînement de l’esprit », qui apprend à transformer les difficultés en occasions de compassion. Son disciple Dromtön fonde l’école &lt;a href="https://fr.wikipedia.org/wiki/Kadampa" title=" Wikipedia"&gt;Kadampa&lt;/a&gt;, dont l’héritage est repris au XIVe siècle par l’école &lt;a href="https://fr.wikipedia.org/wiki/Gelugpa" title=" Wikipedia"&gt;Gelugpa&lt;/a&gt; de Tsongkhapa, celle des dalaï-lamas. Il meurt en 1054 près de Lhassa, où son souvenir est toujours vénéré.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/atisha-mini.webp</t>
+        </is>
+      </c>
+      <c r="J287" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana ; Bouddhisme Mahayana</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maître bouddhiste bengali, réformateur du bouddhisme tibétain, auteur de La Lampe sur la voie de l’éveil.</t>
+        </is>
+      </c>
+      <c r="O287" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P287" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A288" s="1">
+        <v>1888</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1975</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1888 – 1975</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarvepalli RADHAKRISHNAN</t>
+        </is>
+      </c>
+      <c r="E288" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sarvepalli_Radhakrishnan" title=" Wikipedia"&gt;Sarvepalli RADHAKRISHNAN&lt;/a&gt; est un philosophe et homme d’État indien, l’un des grands passeurs de la pensée indienne vers l’Occident. Né dans le sud de l’Inde dans une famille brahmane modeste, il étudie dans des écoles chrétiennes, où il entend critiquer l’hindouisme comme une religion irrationnelle. Piqué au vif, il consacre son mémoire à l’éthique du Vedânta et décide de montrer la profondeur de sa tradition. Professeur à Mysore et à Calcutta, il publie en 1923 et 1927 une monumentale &lt;em&gt;Philosophie indienne&lt;/em&gt; en deux volumes.&lt;/p&gt; &lt;p&gt;Interprète de l’Advaïta Védanta de Shankara, il voit dans les &lt;a href="https://fr.wikipedia.org/wiki/Upanishad" title=" Wikipedia"&gt;Upanishads&lt;/a&gt; et la &lt;a href="https://fr.wikipedia.org/wiki/Bhagavad-G%C4%ABt%C4%81" title=" Wikipedia"&gt;&lt;em&gt;Bhagavad-Gîtâ&lt;/em&gt;&lt;/a&gt; une philosophie fondée sur l’expérience spirituelle : par l’intuition, l’esprit humain peut saisir directement l’unité de toute réalité. Mais il refuse l’idée d’un monde illusoire et sans valeur : le monde est une manifestation de l’absolu, et l’action morale y a tout son sens. Il voit dans l’hindouisme une religion ouverte, qui reconnaît la part de vérité de toutes les autres.&lt;/p&gt; &lt;p&gt;Premier Indien à occuper une chaire à Oxford, celle des religions et de l’éthique orientales, de 1936 à 1952, il dialogue avec les penseurs occidentaux et défend une « religion de l’esprit » commune à l’humanité. Anobli par les Britanniques en 1931, il cesse d’utiliser ce titre après l’indépendance. Après l’indépendance, il est ambassadeur à Moscou, vice-président puis président de l’Inde de 1962 à 1967. Le jour de son anniversaire, le 5 septembre, est célébré en Inde comme la Journée des enseignants. Il meurt à Madras en 1975.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/radhakrishnan-mini.webp</t>
+        </is>
+      </c>
+      <c r="J288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advaïta Védanta ; Védanta</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe indien, interprète du Vedânta pour l’Occident, président de l’Inde de 1962 à 1967.</t>
+        </is>
+      </c>
+      <c r="O288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P288" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A289" s="1">
+        <v>1698</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1760</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1698 – 1760</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAAL SHEM TOV</t>
+        </is>
+      </c>
+      <c r="E289" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baal_Shem_Tov" title=" Wikipedia"&gt;BAAL SHEM TOV&lt;/a&gt; (de son vrai nom Israël ben Eliezer), « le Maître du Bon Nom », est le fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;hassidisme&lt;/a&gt;, grand mouvement de renouveau spirituel du judaïsme. Né vers 1698 en Podolie, aux confins de la Pologne et de l’actuelle Ukraine, orphelin et pauvre, il mène d’abord une vie modeste et retirée, comme aide-instituteur, gardien de synagogue et guérisseur, avant de se révéler vers 1736 comme un maître spirituel. Il s’installe à Medjybij, où se forme autour de lui un cercle de disciples. Son surnom rappelle qu’il était guérisseur et faiseur d’amulettes, un « maître du Nom » divin.&lt;/p&gt; &lt;p&gt;À une époque où le judaïsme d’Europe de l’Est sort meurtri des massacres et de la crise messianique de Sabbataï Tsevi, et où la piété semble réservée aux savants, il enseigne que Dieu est présent partout, même dans les actes les plus ordinaires, et que chacun peut s’unir à lui par la ferveur de la prière, l’« attachement » (&lt;em&gt;devekout&lt;/em&gt;). Le simple fidèle qui prie avec un cœur sincère vaut plus que l’érudit orgueilleux. Il refuse la tristesse et l’ascèse excessive : on sert Dieu dans la joie, par le chant et la danse.&lt;/p&gt; &lt;p&gt;Il n’a presque rien écrit : son enseignement nous est parvenu par ses disciples et par une foule de récits, les &lt;em&gt;Louanges du Baal Shem Tov&lt;/em&gt;, qui en font un saint thaumaturge. Après sa mort, ses disciples, comme le Maggid de Mezeritch, organisent le mouvement, et le hassidisme se répand rapidement dans toute l’Europe orientale, malgré l’opposition des rabbins traditionalistes. Martin Buber, qui a recueilli ses histoires, l’a fait connaître aux lecteurs du XXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/baalshemtov-mini.webp</t>
+        </is>
+      </c>
+      <c r="J289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rabbin et mystique de Podolie, fondateur du hassidisme, maître de la joie et de la ferveur.</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P289" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A290" s="1">
+        <v>1924</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1978</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1924 – 1978</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robert SOBUKWE</t>
+        </is>
+      </c>
+      <c r="E290" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Sobukwe" title=" Wikipedia"&gt;Robert SOBUKWE&lt;/a&gt; est un enseignant et militant sud-africain de la lutte contre l’&lt;a href="https://fr.wikipedia.org/wiki/Apartheid" title=" Wikipedia"&gt;apartheid&lt;/a&gt;, fondateur et premier président du &lt;a href="https://fr.wikipedia.org/wiki/Congr%C3%A8s_panafricain_d%27Azanie" title=" Wikipedia"&gt;Congrès panafricain&lt;/a&gt;. Né à Graaff-Reinet, dans la province du Cap, fils d’un ouvrier et d’une domestique, il étudie grâce à des bourses à l’université de Fort Hare, où il s’engage dans la ligue de la jeunesse de l’ANC. Professeur de langues bantoues à l’université du Witwatersrand, il est surnommé « le Prof ».&lt;/p&gt; &lt;p&gt;En 1959, il quitte l’ANC, qu’il juge trop dépendant de ses alliés blancs et communistes, et fonde le Congrès panafricain. Pour lui, les Africains doivent mener eux-mêmes leur libération ; mais il précise qu’est africain quiconque vit en Afrique, lui doit allégeance et accepte la règle de la majorité, sans considération de race : il n’existe qu’une seule race, la race humaine. En mars 1960, il lance une campagne non violente contre les « pass », les laissez-passer imposés aux Noirs ; à Sharpeville, la police tire sur la foule et tue soixante-neuf personnes. Le 21 mars, jour de ce massacre, est aujourd’hui en Afrique du Sud la Journée des droits de l’homme.&lt;/p&gt; &lt;p&gt;Condamné à trois ans de prison, il est maintenu en détention par une loi votée exprès, la « clause Sobukwe », et isolé pendant six ans à &lt;a href="https://fr.wikipedia.org/wiki/Robben_Island" title=" Wikipedia"&gt;Robben Island&lt;/a&gt;, dans une maison séparée, sans contact avec les autres prisonniers. Libéré en 1969, il est assigné à résidence à Kimberley, où il devient avocat. Il meurt d’un cancer en 1978. Sa pensée a inspiré le Mouvement de la conscience noire de Steve Biko.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sobukwe-mini.webp</t>
+        </is>
+      </c>
+      <c r="J290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sud-Africaine</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme ; Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enseignant et militant sud-africain, fondateur du Congrès panafricain, emprisonné seul à Robben Island.</t>
+        </is>
+      </c>
+      <c r="O290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P290" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A291" s="1">
+        <v>1931</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931 – 2021</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desmond TUTU</t>
+        </is>
+      </c>
+      <c r="E291" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond TUTU&lt;/a&gt; est un archevêque anglican sud-africain, l’une des grandes voix de la lutte non violente contre l’apartheid. Né à Klerksdorp, fils d’instituteur, il devient lui-même enseignant, puis prêtre, après avoir quitté l’enseignement pour protester contre une éducation au rabais imposée aux Noirs. Secrétaire général du Conseil sud-africain des Églises, il dénonce sans relâche le régime, appelle aux sanctions internationales et reçoit le &lt;a href="https://fr.wikipedia.org/wiki/Prix_Nobel_de_la_paix" title=" Wikipedia"&gt;prix Nobel de la paix&lt;/a&gt; en 1984. Il devient en 1986 le premier archevêque noir du Cap.&lt;/p&gt; &lt;p&gt;Après la fin de l’apartheid, Nelson Mandela lui confie la présidence de la &lt;a href="https://fr.wikipedia.org/wiki/Commission_de_v%C3%A9rit%C3%A9_et_de_r%C3%A9conciliation" title=" Wikipedia"&gt;Commission vérité et réconciliation&lt;/a&gt; (1995-1998), chargée d’établir la vérité sur les crimes du passé. Les auteurs de violences politiques peuvent y obtenir l’amnistie en reconnaissant publiquement leurs actes devant les victimes. Tutu défend cette justice « restauratrice », qui cherche à réparer les liens plutôt qu’à punir, et invente l’expression de « nation arc-en-ciel ».&lt;/p&gt; &lt;p&gt;Sa pensée s’appuie sur l’&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_%28philosophie%29" title=" Wikipedia"&gt;ubuntu&lt;/a&gt;, notion des langues bantoues : « une personne est une personne grâce aux autres personnes ». Mon humanité est liée à la tienne ; en déshumanisant l’autre, l’oppresseur se déshumanise lui-même. Dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999), il explique que le pardon n’est pas l’oubli, mais la condition pour que victimes et coupables puissent vivre ensemble. Resté indépendant, il critique ensuite aussi les dirigeants de l’ANC au pouvoir et défend les droits humains dans le monde entier. Il meurt au Cap en 2021.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tutu-mini.webp</t>
+        </is>
+      </c>
+      <c r="J291" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sud-Africaine</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ubuntu</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">archevêque anglican sud-africain, prix Nobel de la paix, penseur de l’ubuntu et du pardon.</t>
+        </is>
+      </c>
+      <c r="O291" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P291" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A292" s="1">
+        <v>1933</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2014</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1933 – 2014</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ali MAZRUI</t>
+        </is>
+      </c>
+      <c r="E292" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ali_Mazrui" title=" Wikipedia"&gt;Ali MAZRUI&lt;/a&gt; est un politologue et essayiste kényan, l’un des intellectuels africains les plus influents de la fin du XXe siècle. Né à &lt;a href="https://fr.wikipedia.org/wiki/Mombasa" title=" Wikipedia"&gt;Mombasa&lt;/a&gt;, sur la côte swahilie, fils du grand juge islamique du Kenya, il grandit dans une famille de lettrés musulmans. Il étudie en Angleterre, à Manchester puis à Oxford, et aux États-Unis, enseigne à l’&lt;a href="https://fr.wikipedia.org/wiki/Universit%C3%A9_Makerere" title=" Wikipedia"&gt;université Makerere&lt;/a&gt; en Ouganda, puis aux États-Unis, notamment à l’université du Michigan et à Binghamton, dans l’État de New York.&lt;/p&gt; &lt;p&gt;Sa thèse la plus connue est celle du « triple héritage » de l’Afrique. Le continent est façonné à la fois par ses cultures et religions autochtones, par l’islam, présent depuis plus de mille ans, et par l’Occident, arrivé avec la traite et la colonisation. Aucun de ces héritages ne doit être nié : l’Afrique doit les assumer ensemble pour inventer son avenir. Il la présente en 1986 dans une grande série documentaire de la BBC, &lt;em&gt;The Africans: A Triple Heritage&lt;/em&gt;, qui suscita de vives polémiques par ses critiques de l’Occident.&lt;/p&gt; &lt;p&gt;Auteur de plus de vingt livres, il analyse aussi la dépendance économique et culturelle de l’Afrique, les rapports entre le Nord et le Sud et la place de l’islam dans le monde. Esprit indépendant, il critique aussi bien l’impérialisme occidental que les dictatures africaines, ce qui lui vaut d’être contraint de quitter l’Ouganda d’Idi Amin. Il parlait swahili, arabe et anglais. Il meurt en 2014 aux États-Unis et est enterré à Mombasa, dans le cimetière de sa famille.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mazrui-mini.webp</t>
+        </is>
+      </c>
+      <c r="J292" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kényane</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politologue kényan, penseur de la « triple héritage » de l’Afrique : africain, islamique et occidental.</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="O292" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P292" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A293" s="1">
+        <v>1938</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938 – 2025</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NGŨGĨ WA THIONG'O</t>
+        </is>
+      </c>
+      <c r="E293" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ng%C5%A9g%C4%A9_wa_Thiong%27o" title=" Wikipedia (en)"&gt;NGŨGĨ WA THIONG'O&lt;/a&gt; est un écrivain kényan, le plus grand romancier d’Afrique de l’Est et un penseur majeur de la décolonisation culturelle. Né en 1938 dans une famille paysanne kikuyu, il grandit pendant la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volte_des_Mau_Mau" title=" Wikipedia"&gt;révolte des Mau Mau&lt;/a&gt;, qui coûte la vie à l’un de ses frères. Il étudie à Makerere, en Ouganda, et à Leeds, en Angleterre, et publie en anglais des romans comme &lt;em&gt;Enfant, ne pleure pas&lt;/em&gt; (1964) et &lt;em&gt;Et le blé jaillira&lt;/em&gt; (1967).&lt;/p&gt; &lt;p&gt;En 1977, il crée avec des paysans et des ouvriers de son village une pièce de théâtre en kikuyu qui dénonce les inégalités du Kenya indépendant. Elle est interdite au bout de six semaines, et il est emprisonné sans jugement pendant près d’un an. En prison, il écrit sur du papier toilette son premier roman en kikuyu. Libéré, il doit s’exiler et enseigne aux États-Unis, notamment en Californie. Il abandonne son prénom chrétien, James Ngugi, et son roman &lt;em&gt;Pétales de sang&lt;/em&gt; (1977) dénonce la nouvelle élite du pays. Il décide alors de ne plus écrire ses œuvres de fiction qu’en &lt;a href="https://fr.wikipedia.org/wiki/Kikuyu_%28langue%29" title=" Wikipedia"&gt;kikuyu&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Décoloniser l’esprit&lt;/em&gt; (1986), il explique que la colonisation la plus profonde est celle de la langue : en apprenant aux enfants africains à mépriser leurs langues maternelles, punies à l’école, et à penser dans la langue du colonisateur, on les coupe de leur culture et de leur propre monde. Écrire dans les langues africaines est donc un acte de libération. Souvent cité pour le prix Nobel de littérature, il meurt aux États-Unis en mai 2025, à quatre-vingt-sept ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ngugi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kényane</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain kényan, auteur de Décoloniser l’esprit, défenseur de l’écriture dans les langues africaines.</t>
+        </is>
+      </c>
+      <c r="O293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P293" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A294" s="1">
+        <v>1939</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1939 – 2019</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kwame GYEKYE</t>
+        </is>
+      </c>
+      <c r="E294" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kwame_Gyekye" title=" Wikipedia (en)"&gt;Kwame GYEKYE&lt;/a&gt; est un philosophe ghanéen, l’une des grandes figures de la philosophie africaine moderne. Né en 1939 dans la région occidentale du Ghana, alors la Côte-de-l’Or, il grandit dans la culture des &lt;a href="https://fr.wikipedia.org/wiki/Akan_%28peuple%29" title=" Wikipedia"&gt;Akan&lt;/a&gt;, dont il apprend les proverbes et les traditions orales. Il étudie au Ghana, à Oxford, puis à Harvard, où il soutient une thèse sur la philosophie gréco-arabe ; il publie aussi une étude sur la logique arabe médiévale. Il enseigne ensuite pendant plus de quarante ans à l’université du Ghana, ainsi qu’à l’université Temple aux États-Unis.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Essai sur la pensée philosophique africaine&lt;/em&gt; (1987), il montre que les proverbes, les concepts et les institutions akan contiennent une véritable réflexion philosophique, que l’on peut analyser avec rigueur sans tomber dans l’« ethnophilosophie ». Il y discute la conception akan de la personne, faite d’un principe vital venu de Dieu, d’un esprit et d’un corps, et s’oppose sur ce point à son compatriote &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; : leur débat est devenu l’un des grands moments de la philosophie africaine.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Tradition et modernité&lt;/em&gt; (1997), il défend un « communautarisme modéré ». La personne est d’abord un être social, inscrit dans une communauté qui lui donne son identité et ses devoirs ; mais elle garde des droits et une capacité de choix qui empêchent la communauté de l’écraser. Il invite les sociétés africaines à garder de leurs traditions ce qui sert la dignité humaine et à rejeter ce qui l’entrave. Il meurt en 2019.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gyekye-mini.webp</t>
+        </is>
+      </c>
+      <c r="J294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghanéenne</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie africaine ; Communautarisme</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe ghanéen, penseur akan de la personne et d’un « communautarisme modéré ».</t>
+        </is>
+      </c>
+      <c r="O294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P294" s="1">
         <v>2</v>
       </c>
     </row>
@@ -18344,12 +19339,12 @@
     <hyperlink ref="E140" r:id="rId78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Jiddu_Krishnamurti&quot;  title=&quot;Wikipedia&quot;&gt;Jiddu KRISHNAMURTI&lt;/a&gt;  était  un penseur indien qui a profondément marqué la réflexion sur la liberté intérieure, la conscience et l’éducation.  &lt;a href=&quot;https://citations.ouest-france.fr/citations-jiddu-krishnamurti-1049.html&quot; title=&quot;Citations Krishnamurti par citations ouest france&quot;&gt;Sa parole &lt;/a&gt; est souvent résumée par l’idée que « la vérité est un pays sans chemins » : on ne peut pas atteindre le réel par l’autorité, le dogme, le rituel ou un système de pensée tout fait.  .&lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie se trouve la critique du conditionnement psychologique. Il explique que l’être humain vit prisonnier de ses peurs, de ses habitudes, de ses croyances et des images qu’il se fabrique sur lui-même et sur les autres ; pour lui, cette prison mentale empêche de voir clairement. &lt;/p&gt; &lt;p&gt; Il ne propose pas une  &lt;a href=&quot;https://www.youtube.com/watch?v=Uk3Kdoouw-E&quot; title=&quot;Perceptions Empties consciousness : Krishnamurti &quot;&gt;méthode au sens classique, &lt;/a&gt; ni un chemin spirituel à suivre mécaniquement. À la place, il invite à une observation directe de l’esprit, sans jugement et sans choix, qu’il associe à une forme de méditation véritable ; cette attention nue permettrait de comprendre la pensée en train de se faire et de se défaire. &lt;/p&gt; &lt;p&gt; Il relie toujours la transformation individuelle au changement du monde. Il pense qu’une société plus juste ne peut naître que d’une conscience intérieure libérée de l’autorité, de la violence psychologique et de la dépendance aux systèmes ; sa philosophie est donc moins une doctrine qu’un appel à voir par soi-même, ici et maintenant. &lt;/p&gt; &#10;&lt;audio controls title=&quot;Krishnamurti, une vie par France Culture&quot;&gt;&#10;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/14090-10.10.2014-ITEMA_20678757-2014C23018S0283-21.mp3&quot; type=&quot;audio/mpeg&quot;&gt;&#10;&lt;/audio&gt;"/>
     <hyperlink ref="E142" r:id="rId79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor&quot; title=&quot;Wikipedia&quot;&gt;Léopold Sédar SENGHOR&lt;/a&gt; était à la fois un grand poète-philosophe francophone et un homme d’État sénégalais, premier président de la République du Sénégal (1960–1980) et premier Africain membre de l’Académie française. Formé dans le système scolaire français, il incarne une figure hybride, à la croisée de l’Afrique et de la France, de la négritude et de la francophonie. &lt;/p&gt; &lt;p&gt; Au cœur de sa pensée se trouve le concept de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot;Négridude par Wikipedia&quot;&gt;« négritude », &lt;/a&gt; qu’il définit comme la reconnaissance du fait d’être noir et l’acceptation de cette identité, de son histoire, de sa culture et de sa destinée. Il en fait une valeur poétique et politique : la négritude vise à restaurer la dignité du peuple noir après la colonisation, en affirmant la beauté de la culture afro‑africaine, de ses langues, de ses rythmes et de son rapport à la vie et à la nature. &lt;/p&gt; &lt;p&gt; Dans sa poésie, il met en avant une sensibilité particulière, une « sensorialité » et une intuition qu’il oppose à la rationalité occidentale jugée plus froide, ce qui fait de ses vers une ode à la terre africaine, aux corps noirs, aux masques, aux danses et aux ancêtres. Des textes comme Femme noire ou Chants d’ombre célèbrent à la fois la femme‑enfant, la femme‑mère, la terre‑Afrique et la mémoire collective, dans une langue riche en images et en musique. &lt;/p&gt; &lt;p&gt; Par‑delà la négritude, il rêve d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=sINJIeY4UKo&quot;  title=&quot;Senghor par RTS&quot;&gt;« Civilisation de l’Universel »,&lt;/a&gt;  c’est‑à‑dire d’un monde où différentes traditions (africaines, européennes, etc.) pourraient se mêler dans un métissage créateur plutôt que s’affronter. Philosophe politique, poète et humaniste, il reste l’une des figures majeures de la littérature francophone, à la fois comme chantre de la fierté noire et comme théoricien d’un dialogue entre cultures. &lt;/p&gt; &lt;audio controls title=&quot;Senghor ‘Tu te languis’ par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/21713-25.11.2025-ITEMA_24321734-2025C53416E0132-ITE_00154728_RSCE-21-996409c1a2c68ce243e4f4ef83e00211.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
     <hyperlink ref="E143" r:id="rId80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Keiji_Nishitani&quot;  title=&quot;Wikipedia&quot;&gt;Keiji NISHITANI &lt;/a&gt; un philosophe japonais membre de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/%C3%89cole_de_Kyoto&quot;  title=&quot;école de Kyoto par Wikipedia&quot;&gt;l’École de Kyoto, &lt;/a&gt;  au côté de Nishida Kitarō et Tanabe Hajime, et l’un des penseurs modernes les plus originaux sur la religion, le bouddhisme et l’expérience du néant. Il cherche à penser ensemble la crise métaphysique de la modernité occidentale et la voie spirituelle du bouddhisme, notamment le zen et le bouddhisme du Vide (śūnyatā). &lt;/p&gt; &lt;p&gt; Sa réflexion prend comme point de départ le nihilisme moderne, c’est‑à‑dire le sentiment profond que tout est vidé de sens, de valeur et d’origine absolue, auquel il confronte l’expérience bouddhique de la vacuité radicale. Selon lui, la modernité enferme l’homme dans un soi narcissique et isolé, coupé de tout fondement ultime, et ce qui surgit alors n’est pas seulement le doute, mais une « grande incertitude » qui mène au vide de soi‑même. &lt;/p&gt; &lt;p&gt; Il propose alors une  &lt;a href=&quot;https://www.persee.fr/doc/ebisu_1340-3656_2005_num_34_1_1419&quot;  title=&quot;l’un e le tout en question par Persée&quot;&gt;« conversion » spirituelle &lt;/a&gt; : le même néant qui menaçait d’anéantir l’individu peut devenir, lorsque l’on cesse de le fuir, le point de départ d’une nouvelle compréhension du religieux, où le soi s’efface au profit d’une ouverture à l’être tout entier. Pour lui, la religion ne se réduit ni à dogme, ni à institution, ni à simple psychologie, mais à une expérience où le sujet, au cœur de sa plus grande déréliction, découvre que le monde peut être habité de sacrement, de manière « immanemment sainte ». &lt;/p&gt; &lt;p&gt; Il s’inscrit dans une entreprise de « philosophie entre Orient et Occident », où la pensée occidentale rencontre la tradition bouddhique pour repenser ensemble l’être, le mal, la liberté et la responsabilité. À travers des ouvrages comme Religion et néant (Religion and Nothingness), il devient l’une des figures clés du dialogue philosophique et religieux entre Asie et Europe, articulant la crise de la modernité et la possibilité d’une   &lt;a href=&quot;https://www.youtube.com/watch?v=Ak12Fplzo0U&quot;  title=&quot;The void is not the end Nishitani Keiji par NullSOPHY&quot;&gt;renaissance spirituelle &lt;/a&gt; fondée sur la vacuité éclairée. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="H144" r:id="rId81" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
-    <hyperlink ref="E146" r:id="rId82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E147" r:id="rId83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
-    <hyperlink ref="E148" r:id="rId84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
-    <hyperlink ref="H148" r:id="rId85" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
-    <hyperlink ref="H160" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
+    <hyperlink ref="H145" r:id="rId81" display="https://www.laphilo.fr/pho/knkrumah-mini.webp"/>
+    <hyperlink ref="E147" r:id="rId82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Tran_Duc_Thao&quot; title=&quot; Wikipedia&quot;&gt;Tran Duc THAO&lt;/a&gt; était un philosophe vietnamien  connu pour sa tentative originale d’articuler phénoménologie et marxisme, ainsi que pour son engagement anticolonial et révolutionnaire.  Après la victoire vietnamienne de 1954, il retourne au Vietnam, enseigne à l’université de Hanoï et devient doyen de faculté, avant de connaître des mises à l’écart politiques et une relative marginalisation. &lt;/p&gt; &lt;p&gt; Son  &lt;a href=&quot;https://www.historicalmaterialism.org/figure/tran-duc-thao/&quot;  title=&quot;Tran Duc Thao par Historical materialism &quot;&gt;projet central  &lt;/a&gt; est de produire une synthèse entre phénoménologie et matérialisme dialectique, en partant de l’idée que la phénoménologie permet de saisir &quot;l’expérience vécue&quot; de la domination et du travail. &#10;Il cherche à &quot;réviser&quot; le marxisme pour le rendre attentif à la conscience, au vécu, à la subjectivité, tout en refusant un marxisme mécaniste qui réduirait tout au seul niveau économique. Cette synthèse est mise au service d’un projet politique anticolonial : il s’agit de penser l’émancipation à partir de la vie concrète des colonisés, en montrant le colonialisme comme une forme particulièrement &quot;perfectionnée&quot; du capitalisme. &lt;/p&gt; &lt;p&gt; Il publi en 1951 : &lt;a href=&quot;https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_et_mat%C3%A9rialisme_dialectique&quot;  title=&quot;Phénoménologie et matérialisme dialectique par Wikipedia &quot;&gt;&quot;Phénoménologie et matérialisme dialectique&quot; &lt;/a&gt;: Il y soutient que les limites de la phénoménologie ne peuvent être dépassées qu’en intégrant la théorie marxiste du travail et de la société, et que le marxisme a besoin d’une réélaboration phénoménologique pour retrouver &quot;l’inspiration originelle&quot; de Marx. &lt;/p&gt; &lt;p&gt; À partir des années 1960, il développe une théorie matérialiste de la conscience et du langage, en critiquant le structuralisme qui tend à enfermer le langage dans sa seule structure formelle. Il introduit notamment l’idée de &quot;langage de la vie réelle&quot; : un ensemble de significations objectives constituées dans l’activité matérielle des êtres humains, indépendamment de toute conscience individuelle. &lt;/p&gt; &lt;p&gt; Il conçoit la philosophie comme indissociable de la pratique politique : pour lui, la séparation entre théorie et pratique vient d’une compréhension insuffisante de la théorie et  affirme que la libération économique ne suffit pas si elle ne s’accompagne pas de &lt;a href=&quot;https://www.youtube.com/watch?v=NoHrpeGJpr8&quot; title=&quot; GAZA : POURQUOI DISCUTER NE SERT PLUS À RIEN par Padu &quot;&gt;libertés individuelles &lt;/a&gt; effectives (liberté d’expression, de réunion, etc.), distinguant ainsi contenu et forme de la liberté. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E148" r:id="rId83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cheikh_Anta_Diop&quot; title=&quot;Wikipedia&quot;&gt;Cheikh Anta DIOP&lt;/a&gt; était  un intellectuel sénégalais, historien, anthropologue, physicien et homme politique, considéré comme l’un des fondateurs de  &lt;a href=&quot;http://www.cheikhantadiop.net/&quot; title=&quot;cheikhantadiop &quot;&gt;l’historicité de l’Afrique &lt;/a&gt; et de la pensée afrocentrée. Né à Thieytou au Sénégal, il étudie la physique et la chimie en France, tout en approfondissant l’histoire et l’anthropologie, avant de devenir une figure majeure de la renaissance culturelle africaine dans la seconde moitié du XXᵉ siècle. Il milite aussi activement pour le panafricanisme et l’unification politique du continent, ce qui fait de lui à la fois un savant et un penseur politique engagé.  &lt;/p&gt; &lt;p&gt; Son apport le plus célèbre est la thèse selon laquelle l’Égypte ancienne est une   &lt;a href=&quot;https://www.persee.fr/doc/raipr_0033-9075_1969_num_9_1_1296&quot; title=&quot;civilisations Nègres par persée &quot;&gt;civilisation « nègre », &lt;/a&gt;  c’est‑à‑dire née d’une population d’origine subsaharienne et parente des peuples africains actuels. Dans Nations nègres et culture (1954) puis dans ses travaux ultérieurs, il mobilise des données linguistiques, anthropologiques et historiques pour montrer des parentés profondes entre les cosmo‑gonies égyptiennes et plusieurs traditions africaines (dogon, yoruba, ashanti, etc.), ce qui nourrit l’idée d’une « unité culturelle de l’Afrique noire ». Il entend ainsi retourner les discours racistes de l’époque en affirmant que l’Afrique n’est pas un continent sans histoire, mais que l’Égypte est un centre majeur de l’histoire africaine. &lt;/p&gt; &lt;p&gt; Sur le plan scientifique, il développe une approche pluridisciplinaire qui mêle linguistique, comparaison historique, anthropologie et études physique. Il critique fortement les biais culturels et eurocentrés de l’historiographie et de l’anthropologie coloniales, qui ont minimisé ou occulté l’apport des peuples africains aux civilisations humaines.  Pour lui, reconstituer &lt;a href=&quot;https://www.youtube.com/watch?v=KGlbVk3V9es&quot; title=&quot;conférence de Cheikh Anta Diop par pendanz &quot;&gt;une histoire africaine authentique &lt;/a&gt; permet non seulement de restaurer la dignité des peuples noirs, mais aussi de repenser l’histoire mondiale elle‑même. &lt;/p&gt; &lt;p&gt; Il est un penseur politique et un acteur de la scène panafricaniste : il défend un projet d’Afrique unifiée et fédéralisée, inspiré des idéaux de l’Unité africaine, et critique la division du continent héritée de la colonisation. Ses travaux influencent durablement les mouvements noirs, les études africaines et les réflexions sur la décolonisation des savoirs, tout en restant objet de débats parmi les égyptologues et les historiens. Aujourd’hui, il est souvent présenté comme l’un des grands précurseurs de la réhabilitation de l’Afrique dans l’histoire de l’humanité. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E149" r:id="rId84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Frantz_Fanon&quot; title=&quot;Wikipedia&quot;&gt;Frantz FANON&lt;/a&gt; était un penseur majeur de l’anticolonialisme, né en Martinique et devenu psychiatre, essayiste et militant engagé dans la guerre d’indépendance algérienne. Son œuvre cherche &lt;a href=&quot;https://www.youtube.com/watch?v=9hchLgKUSpU&quot; title=&quot;la Philosophie de Frantz FANON par parole de philosophe &quot;&gt;à comprendre comment &lt;/a&gt;  la colonisation détruit psychologiquement et socialement les peuples dominés, tout en fabriquant aussi une image déformée du colonisateur et du colonisé.&lt;/p&gt; &lt;p&gt; Dans Peau noire, masques blancs, il analyse la manière dont le racisme et la domination coloniale produisent un sentiment d’infériorité, des blessures psychiques et une aliénation de soi.  &lt;a href=&quot;https://fondation-frantzfanon.com/&quot; title=&quot;Fondation  Frantz FANON  &quot;&gt;Il montre que le colonisé &lt;/a&gt;  peut finir par intérioriser le regard du dominant, au point de porter un « masque » social pour tenter d’être reconnu dans un monde qui le rejette. &lt;/p&gt; &lt;p&gt; Sa pensée devient encore plus politique dans Les Damnés de la terre, où il défend l’idée que la décolonisation n’est pas seulement un changement administratif, mais une transformation radicale des rapports de pouvoir. Il insiste sur le fait que la colonisation repose elle-même sur la violence, et que la libération des colonisés passe par une rupture profonde avec cet ordre injuste. &lt;/p&gt; &lt;p&gt; Il est lu comme un précurseur des pensées décoloniales et postcoloniales, parce qu’il relie la politique, la psychologie, la culture et le corps vécu des dominés. Sa force est d’avoir montré que la lutte contre le colonialisme ne concerne pas seulement les territoires, mais aussi les esprits, les identités et les façons de penser le monde. &lt;/p&gt; &lt;audio controls title=&quot;Fanon, le phychiatre qui voulait libérer le monde par France Culture&quot;&gt;&lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/20905-24.05.2025-ITEMA_24146065-2025F23811S0145-NET_MFI_E4CF018B-14D9-469C-9942-543F6B9EFCA5-22.mp3&quot; type=&quot;audio/mpeg&quot;&gt; &lt;/audio&gt;"/>
+    <hyperlink ref="H149" r:id="rId85" display="https://www.laphilo.fr/pho/fanon-mini.webp"/>
+    <hyperlink ref="H164" r:id="rId86" display="https://www.laphilo.fr/pho/zayd-mini.webp"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -19738,6 +19738,422 @@
         <v>2</v>
       </c>
     </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A303" s="1">
+        <v>1633</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1633 – 1710</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WALDA HEYWAT</t>
+        </is>
+      </c>
+      <c r="E303" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Walda_Heywat" title=" Wikipedia (en)"&gt;WALDA HEYWAT&lt;/a&gt; est un philosophe éthiopien du XVIIe siècle, disciple de &lt;a href="https://fr.wikipedia.org/wiki/Zera_Yacob" title=" Wikipedia"&gt;Zera Yacob&lt;/a&gt;, l’un des premiers grands penseurs rationalistes d’Afrique. Fils d’un riche marchand d’Emfraz, près du lac Tana, dont la maison avait accueilli Zera Yacob après des années de solitude, il est l’élève de ce dernier, qui enseigne aux enfants de la famille. C’est lui, selon la tradition, qui pousse son maître à mettre par écrit sa vie et sa pensée dans le célèbre &lt;em&gt;Hatata&lt;/em&gt; (« Enquête »).&lt;/p&gt; &lt;p&gt;Il écrit à son tour, en guèze, la langue savante de l’Éthiopie, un &lt;em&gt;Traité&lt;/em&gt; qui prolonge la philosophie de son maître. Comme Zera Yacob, il veut juger de tout par la lumière de la raison que Dieu a donnée à chaque homme, et non par l’autorité des traditions religieuses, souvent contradictoires. Mais là où son maître méditait surtout sur la recherche personnelle de la vérité, Walda Heywat réfléchit à la vie en société et à la manière de bien vivre avec les autres.&lt;/p&gt; &lt;p&gt;« Dieu ne m’a pas créé pour moi seul, écrit-il, mais il m’a placé au milieu d’autres créatures qui sont mes égales. » L’homme ne peut naître, grandir ni servir sans l’aide des autres hommes : il doit donc pratiquer la justice, l’humilité, le travail, la patience et l’amour du prochain. Son traité, rempli de conseils pratiques, s’adresse à tous, y compris aux enfants. Redécouverts au XXe siècle, notamment par le jésuite Claude Sumner, ces textes témoignent d’une philosophie écrite africaine bien antérieure à la colonisation. Leur authenticité a été discutée, certains les attribuant à un missionnaire du XIXe siècle, mais beaucoup de spécialistes la défendent aujourd’hui.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/waldaheywat-mini.webp</t>
+        </is>
+      </c>
+      <c r="J303" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éthiopienne</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie africaine</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe éthiopien, disciple de Zera Yacob, penseur d’une morale sociale fondée sur la raison.</t>
+        </is>
+      </c>
+      <c r="O303" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P303" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A304" s="1">
+        <v>1863</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1950</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1863 – 1950</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLACK ELK</t>
+        </is>
+      </c>
+      <c r="E304" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Black_Elk" title=" Wikipedia"&gt;BLACK ELK&lt;/a&gt; (Héhaka Sápa en lakota, « Wapiti noir ») est un homme-médecine et sage des &lt;a href="https://fr.wikipedia.org/wiki/Lakotas" title=" Wikipedia"&gt;Lakotas&lt;/a&gt; Oglalas, un peuple sioux des grandes plaines d’Amérique du Nord. Cousin du célèbre chef Crazy Horse, il assiste enfant, à treize ans, à la &lt;a href="https://fr.wikipedia.org/wiki/Bataille_de_Little_Bighorn" title=" Wikipedia"&gt;bataille de Little Bighorn&lt;/a&gt; (1876), puis à la défaite de son peuple, parqué dans des réserves. Il voyage en Europe avec le spectacle de Buffalo Bill, et il est blessé en 1890 lors du &lt;a href="https://fr.wikipedia.org/wiki/Massacre_de_Wounded_Knee" title=" Wikipedia"&gt;massacre de Wounded Knee&lt;/a&gt;, où l’armée américaine tue des centaines de Lakotas.&lt;/p&gt; &lt;p&gt;À neuf ans, au cours d’une maladie, il a eu une grande vision : guidé par les « six grands-pères », puissances du monde, il voit le « cercle sacré » de son peuple et l’arbre fleuri au centre du monde, symbole de la vie de la nation. Toute sa vie, il cherche à comprendre et à accomplir cette vision. Pour les Lakotas, tous les êtres, humains, animaux, plantes, pierres, ciel et terre, sont parents, liés dans un même cercle ; la pipe sacrée et les rites unissent l’homme à cette totalité.&lt;/p&gt; &lt;p&gt;Converti au catholicisme et devenu catéchiste, il ne renie pas pour autant sa tradition. En 1930, il confie sa vie et sa vision au poète John Neihardt, qui en tire &lt;em&gt;Élan noir parle&lt;/em&gt; (1932) ; il transmet ensuite les sept rites sacrés des Lakotas à Joseph Epes Brown, publiés sous le titre &lt;em&gt;Les Rites secrets des Indiens sioux&lt;/em&gt;. Ces livres sont devenus des classiques, lus par des générations de chercheurs et de militants des droits des peuples autochtones. Il meurt en 1950 dans la réserve de Pine Ridge, dans le Dakota du Sud.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/blackelk-mini.webp</t>
+        </is>
+      </c>
+      <c r="J304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amérindienne</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamanisme</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sage et homme-médecine lakota, dont la vision et le récit de vie témoignent de la spiritualité des peuples des Plaines.</t>
+        </is>
+      </c>
+      <c r="O304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P304" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A305" s="1">
+        <v>1909</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1985</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1909 – 1985</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mahmoud Mohamed TAHA</t>
+        </is>
+      </c>
+      <c r="E305" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mahmoud_Mohamed_Taha" title=" Wikipedia"&gt;Mahmoud Mohamed TAHA&lt;/a&gt; est un penseur religieux et homme politique soudanais, l’un des grands réformistes de l’islam au XXe siècle. Ingénieur formé à l’époque coloniale, il fonde en 1945 le Parti républicain, qui lutte contre la domination britannique et pour une république démocratique, et il est emprisonné à deux reprises par les autorités coloniales. Après une longue retraite spirituelle, il développe une pensée originale, nourrie de soufisme, qu’il expose dans &lt;em&gt;Le Second Message de l’islam&lt;/em&gt; (1967).&lt;/p&gt; &lt;p&gt;Il y distingue deux messages dans le Coran. Les versets révélés à La Mecque, au début de la prédication du Prophète, expriment selon lui l’islam dans sa forme parfaite et universelle : la liberté, l’égalité entre hommes et femmes, la responsabilité de chaque personne devant Dieu, l’absence de contrainte en religion. Les versets révélés ensuite à Médine, avec leurs règles juridiques et guerrières, étaient une adaptation nécessaire aux conditions d’une société du VIIe siècle. La loi islamique classique, fondée sur eux, n’est donc pas faite pour tous les temps.&lt;/p&gt; &lt;p&gt;Pour Taha, l’humanité est désormais prête à vivre selon le premier message, celui de La Mecque, ce qui ouvre la voie à la démocratie, au socialisme et à l’égalité des sexes. En 1983, le président Nimeiry impose au Soudan une application stricte de la &lt;a href="https://fr.wikipedia.org/wiki/Charia" title=" Wikipedia"&gt;charia&lt;/a&gt; ; Taha la dénonce publiquement. Arrêté, il est condamné à mort pour apostasie et pendu à Khartoum le 18 janvier 1985, à soixante-seize ans. Son disciple Abdullahi Ahmed An-Na’im a poursuivi sa pensée aux États-Unis.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/taha-mini.webp</t>
+        </is>
+      </c>
+      <c r="J305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soudanaise</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soufisme</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penseur musulman soudanais, auteur du Second Message de l’islam, exécuté pour ses idées en 1985.</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P305" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A306" s="1">
+        <v>1922</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2006</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1922 – 2006</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joseph KI-ZERBO</t>
+        </is>
+      </c>
+      <c r="E306" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_Ki-Zerbo" title=" Wikipedia"&gt;Joseph KI-ZERBO&lt;/a&gt; est un historien, homme politique et penseur burkinabè, l’un des fondateurs de l’histoire africaine écrite par les Africains. Né à Toma, en Haute-Volta, il étudie l’histoire à Paris et devient en 1956 le premier Africain reçu à l’agrégation d’histoire. Militant de l’indépendance et du panafricanisme, il enseigne en France, au Sénégal, en Guinée puis dans son pays, où il fonde un parti politique et s’oppose aux régimes militaires successifs, ce qui lui vaut plusieurs années d’exil. Dès 1958, il fonde le Mouvement de libération nationale, qui réclame l’indépendance et l’unité de l’Afrique.&lt;/p&gt; &lt;p&gt;Son &lt;em&gt;Histoire de l’Afrique noire&lt;/em&gt; (1972) montre, contre l’idée coloniale d’un continent « sans histoire », la richesse des sociétés, des États et des civilisations africaines avant la colonisation. Il dirige aussi le premier volume de l’&lt;a href="https://fr.wikipedia.org/wiki/Histoire_g%C3%A9n%C3%A9rale_de_l%27Afrique" title=" Wikipedia"&gt;Histoire générale de l’Afrique&lt;/a&gt; publiée par l’UNESCO, qui fait une large place aux sources orales et aux méthodes nouvelles. Pour lui, un peuple qui ne connaît pas son histoire est comme un individu sans mémoire : il ne peut pas choisir librement son avenir.&lt;/p&gt; &lt;p&gt;Il défend un « développement endogène », pensé à partir des cultures, des langues et des besoins des Africains eux-mêmes, et non imposé de l’extérieur : « On ne développe pas, on se développe. » Il insiste sur l’éducation dans les langues africaines et sur l’unité du continent. Lauréat en 1997 du &lt;a href="https://fr.wikipedia.org/wiki/Right_Livelihood_Award" title=" Wikipedia"&gt;prix Nobel alternatif&lt;/a&gt;, il résume sa pensée dans un livre d’entretiens, &lt;em&gt;À quand l’Afrique ?&lt;/em&gt; (2003). Il meurt à Ouagadougou en 2006.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kizerbo-mini.webp</t>
+        </is>
+      </c>
+      <c r="J306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burkinabè</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien et penseur burkinabè, auteur de l’Histoire de l’Afrique noire, théoricien d’un développement endogène.</t>
+        </is>
+      </c>
+      <c r="O306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P306" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A307" s="1">
+        <v>1931</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1982</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1931 – 1982</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKOT P'BITEK</t>
+        </is>
+      </c>
+      <c r="E307" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Okot_p%27Bitek" title=" Wikipedia"&gt;OKOT P'BITEK&lt;/a&gt; est un poète, anthropologue et essayiste ougandais, l’une des voix les plus libres de la pensée africaine. Né à Gulu, dans le nord de l’Ouganda, d’un père instituteur et d’une mère chanteuse et conteuse acholi, il est à la fois chanteur, danseur et footballeur : c’est avec l’équipe nationale d’Ouganda qu’il vient en Angleterre en 1958. Il y reste pour étudier l’éducation, le droit puis l’anthropologie sociale à Oxford.&lt;/p&gt; &lt;p&gt;Son long poème &lt;em&gt;Le Chant de Lawino&lt;/em&gt; (1966), écrit d’abord en acholi, donne la parole à une femme de la campagne dont le mari, instruit à l’occidentale, méprise sa culture et veut tout imiter de l’Europe. Avec humour et force, Lawino défend la beauté des danses, de la cuisine et des usages de son peuple, et rappelle à son mari qu’il a perdu ses racines. Le poème, suivi du &lt;em&gt;Chant d’Ocol&lt;/em&gt;, la réponse du mari, est devenu un classique de la littérature africaine.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Religions africaines dans la recherche occidentale&lt;/em&gt; (1970), il accuse les chercheurs, missionnaires et même certains savants africains, comme John Mbiti, d’avoir « habillé » les religions africaines de concepts grecs et chrétiens, en leur prêtant par exemple un Dieu unique, éternel et tout-puissant, étranger à leur propre pensée. Il plaide pour que les cultures africaines soient comprises dans leurs propres termes, débat essentiel de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;philosophie africaine&lt;/a&gt;. Directeur du Théâtre national de l’Ouganda, il est renvoyé en 1968 et passe ensuite de longues années au Kenya. Il meurt à Kampala en 1982.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/okotpbitek-mini.webp</t>
+        </is>
+      </c>
+      <c r="J307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ougandaise</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie africaine ; Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poète et anthropologue ougandais, auteur du Chant de Lawino, critique de l’image occidentale des religions africaines.</t>
+        </is>
+      </c>
+      <c r="O307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P307" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A308" s="1">
+        <v>1937</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2002</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1937 – 2002</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viola CORDOVA</t>
+        </is>
+      </c>
+      <c r="E308" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Viola_Cordova" title=" Wikipedia (en)"&gt;Viola CORDOVA&lt;/a&gt; est une philosophe, artiste et écrivaine amérindienne, membre de la nation &lt;a href="https://fr.wikipedia.org/wiki/Apaches" title=" Wikipedia"&gt;apache&lt;/a&gt; jicarilla. Née dans le Nouveau-Mexique d’un père apache et d’une mère hispanique, elle grandit à Taos et étudie la philosophie à l’université du Nouveau-Mexique, où elle soutient en 1992 une thèse sur le monisme dans la pensée &lt;a href="https://fr.wikipedia.org/wiki/Navajos" title=" Wikipedia"&gt;navajo&lt;/a&gt;. Elle est l’une des premières femmes amérindiennes à obtenir un doctorat en philosophie aux États-Unis.&lt;/p&gt; &lt;p&gt;Cordova veut montrer que les peuples autochtones ont une véritable philosophie, avec sa propre vision du monde, et non de simples croyances ou mythes. Au cœur de cette pensée, elle place une conception du monde comme un tout unique, en mouvement constant, dont les êtres humains ne sont qu’une partie parmi d’autres, sans place à part ni supérieure. Il n’y a pas de séparation entre le sacré et le profane, entre l’esprit et la matière : tout est relié.&lt;/p&gt; &lt;p&gt;Il en découle une éthique : un être humain n’existe que dans un réseau de relations, avec les autres humains, avec la terre et avec tous les vivants, et il doit agir de manière à préserver l’équilibre de ce monde pour les générations futures. Elle compare ces conceptions à celles de l’Occident, qu’elle critique pour sa séparation de l’homme et de la nature. En 2001, elle crée avec Anne Waters une revue de l’Association américaine de philosophie consacrée aux Amérindiens en philosophie. Elle meurt en 2002, et l’université du Nouveau-Mexique donne depuis son nom à une conférence annuelle. Ses textes ont été réunis après sa mort dans &lt;em&gt;How It Is&lt;/em&gt; (2007).&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/cordova-mini.webp</t>
+        </is>
+      </c>
+      <c r="J308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amérindienne</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monisme ; Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe amérindienne apache, l’une des premières à formuler une philosophie autochtone dans le langage de la philosophie.</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P308" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A309" s="1">
+        <v>1939</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2009</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1939 – 2009</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epeli HAU'OFA</t>
+        </is>
+      </c>
+      <c r="E309" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Epeli_Hau%27ofa" title=" Wikipedia (en)"&gt;Epeli HAU'OFA&lt;/a&gt; est un écrivain et anthropologue des &lt;a href="https://fr.wikipedia.org/wiki/Tonga" title=" Wikipedia"&gt;Tonga&lt;/a&gt; et des &lt;a href="https://fr.wikipedia.org/wiki/Fidji" title=" Wikipedia"&gt;Fidji&lt;/a&gt;, l’un des grands penseurs de l’Océanie. Né en 1939 en Papouasie de parents missionnaires originaires des Tonga, il étudie en Papouasie, aux Tonga et aux Fidji, puis en Australie et au Canada, et soutient un doctorat d’anthropologie. Secrétaire du roi des Tonga au début des années 1980, il enseigne ensuite la sociologie à l’université du Pacifique Sud, à Suva, aux Fidji.&lt;/p&gt; &lt;p&gt;Dans son essai &lt;em&gt;Notre mer d’îles&lt;/em&gt; (1993), il conteste l’image des petits pays du Pacifique comme des « îles perdues dans un océan lointain », trop petites, trop pauvres et trop isolées pour être autre chose que dépendantes de l’aide des grandes puissances. Selon lui, cette vision vient des colonisateurs, qui ont tracé des frontières sur la mer. Pour les ancêtres océaniens, grands navigateurs, l’océan n’était pas une distance qui sépare, mais une route qui relie : un vaste monde de voyages, d’échanges et de parenté.&lt;/p&gt; &lt;p&gt;Penser l’Océanie comme une « mer d’îles » plutôt que comme des îles dans la mer, c’est rendre aux peuples du Pacifique la fierté et la liberté de définir eux-mêmes leur avenir. Il en tire plus tard l’idée d’une identité océanienne commune, fondée sur l’océan partagé, qui appelle aussi à le protéger. Il fonde en 1997 un centre pour les arts et la culture d’Océanie à Suva, et écrit des récits satiriques, comme les &lt;em&gt;Contes des Tikongs&lt;/em&gt; (1983), qui se moquent avec tendresse des effets du développement. Il meurt en 2009.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hauofa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fidjienne</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et anthropologue tongien et fidjien, auteur de Notre mer d’îles, penseur de l’Océanie.</t>
+        </is>
+      </c>
+      <c r="O309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P309" s="1">
+        <v>2</v>
+      </c>
+    </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -8502,8 +8502,10 @@
       <c r="K53" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L53" s="2" t="s">
-        <v>444</v>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Madhyamaka</t>
+        </is>
       </c>
       <c r="M53" s="2" t="s">
         <v>445</v>
@@ -8673,8 +8675,10 @@
       <c r="K57" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>444</v>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Yogācāra</t>
+        </is>
       </c>
       <c r="M57" s="2" t="s">
         <v>478</v>
@@ -8715,8 +8719,10 @@
       <c r="K58" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>444</v>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Yogācāra</t>
+        </is>
       </c>
       <c r="M58" s="2" t="s">
         <v>486</v>
@@ -8929,8 +8935,10 @@
       <c r="K63" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>279</v>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme ; Yogācāra</t>
+        </is>
       </c>
       <c r="M63" s="2" t="s">
         <v>530</v>
@@ -8971,8 +8979,10 @@
       <c r="K64" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L64" s="2" t="s">
-        <v>444</v>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Yogācāra</t>
+        </is>
       </c>
       <c r="M64" s="2" t="s">
         <v>538</v>
@@ -9483,8 +9493,10 @@
       <c r="K76" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>641</v>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Shivaïsme du Cachemire</t>
+        </is>
       </c>
       <c r="M76" s="2" t="s">
         <v>642</v>
@@ -9525,8 +9537,10 @@
       <c r="K77" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>641</v>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Shivaïsme du Cachemire</t>
+        </is>
       </c>
       <c r="M77" s="2" t="s">
         <v>650</v>
@@ -9696,8 +9710,10 @@
       <c r="K81" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>683</v>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védanta ; Bhakti</t>
+        </is>
       </c>
       <c r="M81" s="2" t="s">
         <v>684</v>
@@ -10263,8 +10279,10 @@
       <c r="K94" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="L94" s="2" t="s">
-        <v>279</v>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme ; Bouddhisme de la Terre pure</t>
+        </is>
       </c>
       <c r="M94" s="2" t="s">
         <v>792</v>
@@ -10350,8 +10368,10 @@
       <c r="K96" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L96" s="2" t="s">
-        <v>808</v>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa ; Ishraqisme ; Ismaélisme</t>
+        </is>
       </c>
       <c r="M96" s="2" t="s">
         <v>809</v>
@@ -10456,7 +10476,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Tiantai</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -10505,8 +10525,10 @@
       <c r="K99" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L99" s="2" t="s">
-        <v>683</v>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védanta ; Bhakti</t>
+        </is>
       </c>
       <c r="M99" s="2" t="s">
         <v>824</v>
@@ -10717,8 +10739,10 @@
       <c r="K104" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L104" s="2" t="s">
-        <v>583</v>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vajrayana ; Madhyamaka</t>
+        </is>
       </c>
       <c r="M104" s="2" t="s">
         <v>867</v>
@@ -10845,8 +10869,10 @@
       <c r="K107" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="L107" s="2" t="s">
-        <v>893</v>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soufisme ; Hindouisme ; Bhakti</t>
+        </is>
       </c>
       <c r="M107" s="2" t="s">
         <v>894</v>
@@ -10887,8 +10913,10 @@
       <c r="K108" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="L108" s="2" t="s">
-        <v>641</v>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Bhakti</t>
+        </is>
       </c>
       <c r="M108" s="2" t="s">
         <v>901</v>
@@ -11063,8 +11091,10 @@
       <c r="K112" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L112" s="2" t="s">
-        <v>775</v>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ishraqisme ; École d'Ispahan</t>
+        </is>
       </c>
       <c r="M112" s="2" t="s">
         <v>934</v>
@@ -11830,8 +11860,10 @@
       <c r="K130" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L130" s="2" t="s">
-        <v>641</v>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Néo-védanta</t>
+        </is>
       </c>
       <c r="M130" s="2" t="s">
         <v>1078</v>
@@ -12084,8 +12116,10 @@
       <c r="K135" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L135" s="2" t="s">
-        <v>641</v>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Néo-védanta</t>
+        </is>
       </c>
       <c r="M135" s="2" t="s">
         <v>1102</v>
@@ -12501,8 +12535,10 @@
       <c r="K144" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="L144" s="2" t="s">
-        <v>1160</v>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Négritude ; Socialisme africain</t>
+        </is>
       </c>
       <c r="M144" s="2" t="s">
         <v>1161</v>
@@ -12660,8 +12696,10 @@
       <c r="K147" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="L147" s="1" t="s">
-        <v>1175</v>
+      <c r="L147" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consciencisme ; Socialisme africain</t>
+        </is>
       </c>
       <c r="M147" s="2" t="s">
         <v>1176</v>
@@ -13073,7 +13111,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Philosophie africaine ; Ethnophilosophie</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -13920,8 +13958,10 @@
       <c r="K177" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L177" s="2" t="s">
-        <v>1335</v>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kalâm ; Maturidisme</t>
+        </is>
       </c>
       <c r="M177" s="2" t="s">
         <v>1336</v>
@@ -14092,8 +14132,10 @@
       <c r="K182" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L182" s="2" t="s">
-        <v>511</v>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme ; Ismaélisme</t>
+        </is>
       </c>
       <c r="M182" s="2" t="s">
         <v>1360</v>
@@ -14337,8 +14379,10 @@
       <c r="K189" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="L189" s="2" t="s">
-        <v>1369</v>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie juive médiévale ; Mysticisme ; Kabbale</t>
+        </is>
       </c>
       <c r="M189" s="2" t="s">
         <v>1393</v>
@@ -14512,8 +14556,10 @@
       <c r="K194" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L194" s="2" t="s">
-        <v>775</v>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ishraqisme ; École d'Ispahan</t>
+        </is>
       </c>
       <c r="M194" s="2" t="s">
         <v>1418</v>
@@ -14789,8 +14835,10 @@
       <c r="K202" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L202" s="2" t="s">
-        <v>444</v>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Huayan</t>
+        </is>
       </c>
       <c r="M202" s="2" t="s">
         <v>1478</v>
@@ -16361,7 +16409,7 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Tiantai</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
@@ -16419,7 +16467,7 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Bouddhisme de la Terre pure</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr">
@@ -17361,7 +17409,7 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Philosophie africaine ; Ethnophilosophie</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
@@ -17419,7 +17467,7 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme</t>
+          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme ; Socialisme africain</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
@@ -18062,7 +18110,7 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme</t>
+          <t xml:space="preserve">Anticolonialisme ; Créolisation</t>
         </is>
       </c>
       <c r="M274" s="2" t="inlineStr">
@@ -18352,7 +18400,7 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Tiantai</t>
         </is>
       </c>
       <c r="M279" s="2" t="inlineStr">
@@ -18478,7 +18526,7 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Madhyamaka</t>
         </is>
       </c>
       <c r="M281" s="2" t="inlineStr">
@@ -18594,7 +18642,7 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Yogācāra</t>
         </is>
       </c>
       <c r="M283" s="2" t="inlineStr">
@@ -18710,7 +18758,7 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Huayan</t>
         </is>
       </c>
       <c r="M285" s="2" t="inlineStr">
@@ -18836,7 +18884,7 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vajrayana ; Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Vajrayana ; Bouddhisme Mahayana ; Madhyamaka</t>
         </is>
       </c>
       <c r="M287" s="2" t="inlineStr">
@@ -18894,7 +18942,7 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advaïta Védanta ; Védanta</t>
+          <t xml:space="preserve">Advaïta Védanta ; Védanta ; Néo-védanta</t>
         </is>
       </c>
       <c r="M288" s="2" t="inlineStr">
@@ -18952,7 +19000,7 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mysticisme</t>
+          <t xml:space="preserve">Mysticisme ; Hassidisme</t>
         </is>
       </c>
       <c r="M289" s="2" t="inlineStr">
@@ -19600,7 +19648,7 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falsafa ; Ishraqisme</t>
+          <t xml:space="preserve">Falsafa ; Ishraqisme ; École d'Ispahan</t>
         </is>
       </c>
       <c r="M300" s="2" t="inlineStr">
@@ -19658,7 +19706,7 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falsafa</t>
+          <t xml:space="preserve">Falsafa ; École d'Ispahan</t>
         </is>
       </c>
       <c r="M301" s="2" t="inlineStr">
@@ -20153,6 +20201,364 @@
       <c r="P309" s="1">
         <v>2</v>
       </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A310" s="1">
+        <v>1534</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1572</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1534 – 1572</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac LOURIA</t>
+        </is>
+      </c>
+      <c r="E310" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac LOURIA&lt;/a&gt; (surnommé le Ari, « le Lion ») est un rabbin et kabbaliste, le plus influent des maîtres de la mystique juive depuis le &lt;em&gt;Zohar&lt;/em&gt;. Né à Jérusalem en 1534 d’un père ashkénaze et d’une mère séfarade, il perd tôt son père et grandit en Égypte, chez un oncle négociant. Il y étudie le Talmud, puis se plonge dans le &lt;em&gt;Zohar&lt;/em&gt; ; la tradition raconte qu’il vécut plusieurs années en ermite sur une île du Nil.&lt;/p&gt; &lt;p&gt;En 1570, il s’installe à Safed, en Galilée, où s’étaient réunis de nombreux kabbalistes après l’expulsion des Juifs d’Espagne, et rassemble autour de lui un petit cercle de disciples. Il n’écrit presque rien : sa doctrine est rédigée après sa mort par son disciple Haïm Vital, notamment dans &lt;em&gt;L’Arbre de vie&lt;/em&gt;. Pour laisser place au monde, l’Infini divin se retire en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Dans l’espace ainsi libéré, l’Infini projette sa lumière, mais les « vases » chargés de la recevoir se brisent, et des étincelles tombent, captives de la matière. L’exil n’est donc pas seulement celui du peuple juif : c’est un exil de Dieu lui-même. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la « réparation » : par la prière, l’étude et chaque commandement accompli avec intention, il libère ces étincelles et prépare la venue du Messie.&lt;/p&gt; &lt;p&gt;Louria meurt d’une épidémie en 1572, à trente-huit ans, après deux ans à peine d’enseignement. Sa Kabbale se répand pourtant dans tout le monde juif ; elle nourrit le messianisme de Sabbataï Tsevi, puis le hassidisme. Traduite en latin au XVIIe siècle, elle a intéressé des penseurs chrétiens, et l’idée d’un Dieu qui se retire pour laisser place au monde a été reprise au XXe siècle par Hans Jonas.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/louria-mini.webp</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kabbaliste de Safed, penseur du retrait de Dieu (tsimtsoum) et de la réparation du monde (tikkoun).</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O310" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P310" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A311" s="1">
+        <v>1240</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1305</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1240 – 1305</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moïse de LEÓN</t>
+        </is>
+      </c>
+      <c r="E311" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de LEÓN&lt;/a&gt; est un kabbaliste espagnol du XIIIe siècle, à qui l’on attribue le &lt;em&gt;Zohar&lt;/em&gt;, le « livre de la Splendeur », l’œuvre majeure de la Kabbale. Né vers 1240, sans doute à Guadalajara, en Castille, il passe une trentaine d’années à Guadalajara et à Valladolid, puis s’établit à Ávila. Il fréquente les cercles de kabbalistes castillans et s’intéresse aussi à la philosophie : il fait copier pour lui le &lt;em&gt;Guide des égarés&lt;/em&gt; de Maïmonide.&lt;/p&gt; &lt;p&gt;À partir des années 1280, il fait circuler des cahiers rédigés en araméen, qu’il présente comme la copie d’un livre très ancien, l’enseignement de Shimon bar Yohaï, un sage du IIe siècle. Le &lt;em&gt;Zohar&lt;/em&gt; se présente comme un vaste commentaire mystique de la Torah, où Rabbi Shimon et ses compagnons, cheminant en Galilée, dévoilent le sens caché des versets. Il y décrit la vie intérieure de Dieu à travers les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, l’union du masculin et du féminin en Dieu, et la présence divine, la &lt;em&gt;Shekhina&lt;/em&gt;, exilée avec Israël. On attribue aussi à Moïse de León une méthode de lecture de l’Écriture à quatre niveaux, du sens littéral jusqu’au « secret ». Sous son propre nom, il écrit en hébreu d’autres ouvrages de Kabbale, comme &lt;em&gt;Le Livre de la grenade&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Il meurt en 1305 à Arévalo, sur le chemin du retour. Selon un récit de l’époque, sa veuve aurait reconnu qu’il avait lui-même composé le livre. Les historiens modernes, à la suite de &lt;a href="https://fr.wikipedia.org/wiki/Gershom_Scholem" title=" Wikipedia"&gt;Gershom Scholem&lt;/a&gt;, pensent en effet qu’il en est le principal auteur, peut-être au sein d’un cercle. Imprimé en Italie au XVIe siècle, le &lt;em&gt;Zohar&lt;/em&gt; est devenu l’un des livres les plus vénérés du judaïsme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/moisedeleon-mini.webp</t>
+        </is>
+      </c>
+      <c r="J311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kabbaliste castillan du XIIIe siècle, auteur présumé du Zohar, le « livre de la Splendeur ».</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive ; occident</t>
+        </is>
+      </c>
+      <c r="O311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P311" s="1"/>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A312" s="1">
+        <v>1240</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1291</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1240 – après 1291</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abraham ABOULAFIA</t>
+        </is>
+      </c>
+      <c r="E312" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abraham_Aboulafia" title=" Wikipedia"&gt;Abraham ABOULAFIA&lt;/a&gt; est un kabbaliste espagnol, fondateur de la « Kabbale prophétique », ou extatique. Né à Saragosse en 1240, il grandit à Tudela, en Navarre, où son père lui enseigne la Bible et le Talmud. Il étudie aussi la philosophie, surtout Maïmonide, qu’il admire au point d’écrire un commentaire mystique de son &lt;em&gt;Guide des égarés&lt;/em&gt;. Jeune homme, il part pour la Terre d’Israël à la recherche du légendaire fleuve Sambatyon, au-delà duquel vivraient les dix tribus perdues ; les troubles provoqués par l’arrivée des Mongols l’obligent à rentrer, et il passe dix ans en Grèce et en Italie.&lt;/p&gt; &lt;p&gt;À Barcelone, vers trente et un ans, il vit une expérience qu’il tient pour une révélation prophétique. Sa Kabbale ne cherche pas d’abord à décrire Dieu et ses émanations, comme celle du &lt;em&gt;Zohar&lt;/em&gt;, mais à conduire l’âme jusqu’à l’union avec le divin. Sa méthode est la méditation sur les lettres hébraïques et les noms de Dieu : combiner et permuter les lettres, en les accompagnant de respirations et de mouvements de la tête, jusqu’à ce que l’esprit, délivré des images du monde, s’unisse à l’intellect divin et parvienne à l’extase prophétique. Convaincu d’avoir une mission messianique, il se rend à Rome en 1280 pour rencontrer le pape Nicolas III ; le pape meurt avant leur entrevue et Aboulafia échappe de peu au bûcher.&lt;/p&gt; &lt;p&gt;Ses prétentions prophétiques lui valent la condamnation du grand rabbin de Barcelone, Salomon ben Adret, et il finit sa vie en exil sur l’île de Comino, près de Malte, où l’on perd sa trace après 1291. Son œuvre, restée en manuscrits, a influencé les kabbalistes de Safed et &lt;a href="https://fr.wikipedia.org/wiki/Pic_de_la_Mirandole" title=" Wikipedia"&gt;Pic de la Mirandole&lt;/a&gt;, avant d’être redécouverte au XXe siècle par Gershom Scholem et Moshe Idel.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/aboulafia-mini.webp</t>
+        </is>
+      </c>
+      <c r="J312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juive</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; langage</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kabbaliste espagnol, fondateur de la Kabbale prophétique : l’extase par la méditation des lettres et des noms divins.</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive ; occident</t>
+        </is>
+      </c>
+      <c r="O312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P312" s="1"/>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A313" s="1">
+        <v>960</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1020</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xe – XIe siècle</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamid al-Din AL-KIRMANI</t>
+        </is>
+      </c>
+      <c r="E313" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hamid_al-Din_al-Kirmani" title=" Wikipedia"&gt;Hamid al-Din AL-KIRMANI&lt;/a&gt; est un philosophe et théologien ismaélien d’origine persane, le plus grand penseur de l’&lt;a href="https://fr.wikipedia.org/wiki/Isma%C3%A9lisme" title=" Wikipedia"&gt;ismaélisme&lt;/a&gt; à l’époque du califat fatimide. Né sans doute dans la province de Kerman, en Iran, au Xe siècle, il passe la plus grande partie de sa vie comme missionnaire (&lt;em&gt;dâ’î&lt;/em&gt;) des Fatimides en Irak, à Bagdad et à Bassora, sur les terres du califat rival des Abbassides, où il cherche à gagner chefs et lettrés à la cause de l’imam du Caire.&lt;/p&gt; &lt;p&gt;Vers 1015, il est appelé au Caire sous le calife al-Hakim, dont le règne agité voit naître des courants extrêmes qui divinisent le calife et d’où sortiront les druzes ; Kirmani les réfute dans plusieurs épîtres et défend l’enseignement officiel. Son grand œuvre, &lt;em&gt;La Tranquillité de l’intellect&lt;/em&gt; (&lt;em&gt;Râhat al-’aql&lt;/em&gt;), est une somme où la philosophie grecque, celle de Plotin et d’Aristote, est mise au service de la doctrine ismaélienne. Dieu y est au-delà de tout attribut, même de l’être : on ne peut rien en dire positivement. De lui procède un premier Intellect, d’où se déploie une hiérarchie de dix intelligences, reprise de la cosmologie d’&lt;a href="https://fr.wikipedia.org/wiki/Al-F%C3%A2r%C3%A2b%C3%AE" title=" Wikipedia"&gt;al-Farabi&lt;/a&gt;, qui gouvernent les sphères célestes jusqu’au monde terrestre. À cette hiérarchie du ciel répond sur terre celle de la communauté, du Prophète et de l’imam aux missionnaires.&lt;/p&gt; &lt;p&gt;L’âme humaine, à la naissance, n’est qu’une intelligence en puissance : elle ne s’accomplit qu’en recevant l’enseignement du guide inspiré, et parvient ainsi à la « tranquillité » éternelle. Kirmani meurt vers 1020. Sa pensée, transmise par les ismaéliens du Yémen puis de l’Inde, reste l’une des plus abouties de la philosophie ismaélienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kirmani-mini.webp</t>
+        </is>
+      </c>
+      <c r="J313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perse</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ismaélisme ; Néoplatonisme</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe ismaélien de l’époque fatimide, auteur de La Tranquillité de l’intellect et de la hiérarchie des dix intelligences.</t>
+        </is>
+      </c>
+      <c r="O313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P313" s="1"/>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A314" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1068 – 1142</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abu Hafs AL-NASAFI</t>
+        </is>
+      </c>
+      <c r="E314" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abu_Hafs_al-Nasafi" title=" Wikipedia"&gt;Abu Hafs AL-NASAFI&lt;/a&gt; (Najm al-Din Abu Hafs Umar al-Nasafi) est un théologien, juriste et exégète musulman d’Asie centrale, auteur du credo le plus étudié de l’école &lt;a href="https://fr.wikipedia.org/wiki/Maturidisme" title=" Wikipedia"&gt;maturidite&lt;/a&gt;. Né en 1068 à Nasaf, l’actuelle Karchi, en Ouzbékistan, il vit surtout à Samarcande, la ville où al-Maturidi avait enseigné deux siècles plus tôt. Juriste de l’école hanafite, il aurait écrit une centaine d’ouvrages de droit, de théologie, d’histoire et de commentaire du Coran.&lt;/p&gt; &lt;p&gt;Son œuvre la plus célèbre, les &lt;em&gt;Croyances&lt;/em&gt; (&lt;em&gt;al-’Aqâ’id&lt;/em&gt;), est un court traité qui résume en une soixantaine d’articles la foi sunnite telle que la définit l’école d’al-Maturidi, d’après le grand ouvrage de son maître &lt;a href="https://en.wikipedia.org/wiki/Abu_al-Mu%27in_al-Nasafi" title=" Wikipedia (en)"&gt;Abu al-Mu’in al-Nasafi&lt;/a&gt;. Il s’ouvre sur une affirmation de méthode : la réalité des choses est établie et la connaissance est possible, contre les sceptiques qui le niaient ; elle a trois sources, les sens, le témoignage véridique et la raison. Viennent ensuite la création du monde à partir de rien, l’unicité de Dieu et ses attributs, sa parole éternelle, la vision de Dieu au paradis, la liberté et la responsabilité humaines, la foi et l’imamat. Selon son élève al-Marghinani, il l’écrivit à la demande du sultan seldjoukide Sanjar, de passage à Samarcande en 1140.&lt;/p&gt; &lt;p&gt;Ce petit texte a connu une fortune immense : au XVIIe siècle, on en comptait plus de cinquante commentaires, dont celui d’&lt;a href="https://fr.wikipedia.org/wiki/Taftazani" title=" Wikipedia"&gt;al-Taftazani&lt;/a&gt;, au XIVe siècle, devenu un manuel des écoles ottomanes et des madrasas d’Asie centrale et de l’Inde. Avec le &lt;em&gt;Fiqh al-akbar&lt;/em&gt; attribué à Abû Hanîfa et le credo d’al-Tahawi, il compte parmi les trois grands textes de référence de la foi sunnite. Al-Nasafi meurt en 1142.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nasafi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perse</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maturidisme ; Kalâm</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien maturidite de Samarcande, auteur des Croyances, le credo sunnite le plus commenté.</t>
+        </is>
+      </c>
+      <c r="O314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P314" s="1"/>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A315" s="1">
+        <v>1906</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1977</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1906 – 1977</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placide TEMPELS</t>
+        </is>
+      </c>
+      <c r="E315" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide TEMPELS&lt;/a&gt; (Frans Tempels de son nom civil) est un prêtre franciscain belge, missionnaire au Congo, dont le livre &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; a ouvert le grand débat sur l’existence d’une philosophie africaine. Né en 1906 à Berlaar, en Flandre, il entre chez les franciscains en 1924 et part au début des années 1930 pour le Congo belge, où il exerce son ministère au Katanga.&lt;/p&gt; &lt;p&gt;Constatant l’échec d’une évangélisation qui ignorait la culture des Africains, il décide d’étudier leur pensée de l’intérieur. Publié en 1945, son livre affirme que les Bantous ont une véritable philosophie, cohérente et rationnelle, même si elle n’est pas écrite. Son centre est la notion de « force vitale » : là où la pensée occidentale conçoit l’être comme une chose qui existe, les Bantous le conçoivent comme une force. Dieu est la force suprême, puis viennent les ancêtres, les vivants, les animaux, les plantes et les choses, tous liés par des influences mutuelles. Le bien suprême est l’accroissement de la vie, le mal sa diminution. Réédité à Paris en 1949 par les éditions &lt;a href="https://fr.wikipedia.org/wiki/Pr%C3%A9sence_africaine" title=" Wikipedia"&gt;Présence africaine&lt;/a&gt;, le livre connaît un retentissement considérable.&lt;/p&gt; &lt;p&gt;Il est aussitôt discuté. Aimé Césaire, dans le &lt;a href="https://fr.wikipedia.org/wiki/Discours_sur_le_colonialisme" title=" Wikipedia"&gt;&lt;em&gt;Discours sur le colonialisme&lt;/em&gt;&lt;/a&gt; (1950), soupçonne cette sympathie de servir encore l’entreprise coloniale, et des philosophes africains, de Paulin Hountondji à Marcien Towa, reprocheront à Tempels d’avoir inauguré l’« ethnophilosophie », qui prête à tout un peuple une pensée collective et figée. Au Katanga, il fonde aussi dans les années 1950 un mouvement spirituel, la Jamaa, « la famille », avant d’être rappelé en Belgique en 1962. Il meurt à Hasselt en 1977.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tempels-mini.webp</t>
+        </is>
+      </c>
+      <c r="J315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belge</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ethnophilosophie</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">missionnaire franciscain belge au Congo, auteur de La Philosophie bantoue (1945), à l’origine du débat sur la philosophie africaine.</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P315" s="1"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -8244,8 +8244,10 @@
       <c r="K47" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>296</v>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme ; École du Yin-Yang</t>
+        </is>
       </c>
       <c r="M47" s="2" t="s">
         <v>388</v>
@@ -8591,8 +8593,10 @@
       <c r="K55" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>269</v>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme ; Xuanxue</t>
+        </is>
       </c>
       <c r="M55" s="2" t="s">
         <v>462</v>
@@ -20559,6 +20563,174 @@
         </is>
       </c>
       <c r="P315" s="1"/>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A316" s="1">
+        <v>-305</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-240</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 305 A JC - vers 240 A JC</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zou YAN</t>
+        </is>
+      </c>
+      <c r="E316" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zou_Yan" title=" Wikipedia"&gt;Zou YAN&lt;/a&gt; est un philosophe chinois de la fin de la période des Royaumes combattants, le maître de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_du_Yin-Yang" title=" Wikipedia"&gt;école du Yin-Yang&lt;/a&gt;. Originaire de l’État de Qi, dans l’actuel Shandong, il appartient à l’Académie de Jixia, où le roi de Qi réunissait les meilleurs savants de son temps. L’historien Sima Qian le présente comme le plus éminent d’entre eux et raconte que les princes l’accueillaient avec des honneurs qu’ils refusaient à Confucius ou à Mencius. On le surnommait « Yan qui discourt du ciel », pour sa science des astres.&lt;/p&gt; &lt;p&gt;Aucun de ses livres ne nous est parvenu, mais des fragments et des résumés permettent de reconstituer sa pensée. Il réunit deux idées anciennes en un grand système. D’un côté le &lt;a href="https://fr.wikipedia.org/wiki/Yin_et_yang" title=" Wikipedia"&gt;yin et le yang&lt;/a&gt;, les deux forces complémentaires dont l’alternance fait vivre l’univers ; de l’autre les &lt;a href="https://fr.wikipedia.org/wiki/Wuxing_%28cosmologie%29" title=" Wikipedia"&gt;cinq phases&lt;/a&gt;, le bois, le feu, la terre, le métal et l’eau, qui s’engendrent et se dominent les unes les autres selon un ordre fixe : le bois nourrit le feu, l’eau éteint le feu. Zou Yan applique cette théorie à l’histoire : chaque dynastie règne par la « vertu » d’une phase, et elle est remplacée quand vient la phase qui la domine. Le ciel annonce ce changement par des présages, que le souverain doit savoir lire.&lt;/p&gt; &lt;p&gt;Il est aussi l’auteur d’une géographie audacieuse : la Chine ne serait qu’un des quatre-vingt-un pays du monde, regroupés en neuf grands continents entourés d’océans. Sa théorie des dynasties est adoptée par le premier empereur de Chine, qui place son règne sous le signe de l’eau, puis par les Han. Ses idées imprègnent ensuite toute la cosmologie, la médecine et la politique chinoises.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/zouyan-mini.webp</t>
+        </is>
+      </c>
+      <c r="J316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; politique</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École du Yin-Yang</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe chinois de l’Académie de Jixia, maître de l’école du Yin-Yang et de la théorie des cinq phases.</t>
+        </is>
+      </c>
+      <c r="O316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P316" s="1"/>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A317" s="1">
+        <v>252</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 252 – 312</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guo XIANG</t>
+        </is>
+      </c>
+      <c r="E317" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guo_Xiang" title=" Wikipedia"&gt;Guo XIANG&lt;/a&gt; est un philosophe chinois de la dynastie des Jin occidentaux, l’un des grands penseurs du &lt;a href="https://fr.wikipedia.org/wiki/Xuanxue" title=" Wikipedia"&gt;Xuanxue&lt;/a&gt;, « l’étude du mystère ». On sait peu de chose de sa vie : brillant causeur, admiré dans les « pures conversations » de l’aristocratie, il aurait longtemps refusé les fonctions officielles pour se consacrer à l’étude, avant de devenir un haut fonctionnaire.&lt;/p&gt; &lt;p&gt;Son œuvre principale est son édition commentée du &lt;em&gt;Zhuangzi&lt;/em&gt;. C’est lui qui a donné au livre sa forme actuelle, en trente-trois chapitres, en écartant ceux qu’il jugeait douteux ; toutes les traductions modernes reposent sur son texte. On l’a accusé d’avoir repris le travail d’un autre lettré, Xiang Xiu, et l’on parle parfois de la pensée de « Xiang-Guo ». Contre Wang Bi, qui faisait du « non-être » l’origine de toutes choses, il affirme que le non-être n’est rien et ne peut rien produire. Il n’y a pas de créateur : chaque chose « advient d’elle-même », spontanément, et se transforme par elle-même. Chaque être a sa nature et sa part, et le bonheur consiste à les accomplir pleinement : le grand oiseau qui vole à des milliers de lieues et la petite caille qui saute de branche en branche sont également libres et heureux s’ils suivent leur nature.&lt;/p&gt; &lt;p&gt;Le sage, pour lui, n’a pas besoin de fuir dans les montagnes : il peut gouverner tout en gardant l’esprit libre, car il ne s’attache à rien. Cette lecture a profondément marqué la manière dont les Chinois ont lu Zhuangzi, et elle a influencé le bouddhisme chinois, en particulier le chan.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/guoxiang-mini.webp</t>
+        </is>
+      </c>
+      <c r="J317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xuanxue ; Taoïsme</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe chinois du Xuanxue, éditeur du Zhuangzi : chaque chose advient d’elle-même et trouve son bonheur à suivre sa nature.</t>
+        </is>
+      </c>
+      <c r="O317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P317" s="1"/>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A318" s="1">
+        <v>223</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223 – 262</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ji KANG</t>
+        </is>
+      </c>
+      <c r="E318" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Xi_Kang" title=" Wikipedia"&gt;Ji KANG&lt;/a&gt; (ou Xi Kang) est un poète, musicien et penseur chinois de l’époque des Trois Royaumes, la figure centrale des &lt;a href="https://fr.wikipedia.org/wiki/Sept_Sages_de_la_for%C3%AAt_de_bambous" title=" Wikipedia"&gt;Sept Sages de la forêt de bambous&lt;/a&gt;. Issu d’une famille riche, apparenté par son mariage à la famille impériale des Wei, il préfère à la carrière une vie libre, consacrée à la musique, à la poésie, à la recherche de la longévité taoïste et aux conversations avec ses amis, dans un bosquet de bambous près de Luoyang.&lt;/p&gt; &lt;p&gt;Il est l’un des esprits les plus originaux du &lt;a href="https://fr.wikipedia.org/wiki/Xuanxue" title=" Wikipedia"&gt;Xuanxue&lt;/a&gt;. Dans son &lt;em&gt;Essai sur l’art de nourrir la vie&lt;/em&gt;, il soutient que l’on peut prolonger sa vie en maîtrisant ses désirs et en vivant en accord avec la nature. Dans un autre essai, il défend que « la musique n’a ni joie ni tristesse » : les sons ne contiennent pas d’émotions, ce sont les auditeurs qui y projettent les leurs ; la musique est harmonie pure. Contre les rites confucéens, devenus une contrainte hypocrite au service du pouvoir, il prône la spontanéité et la sincérité du cœur. Grand joueur de cithare, il écrit aussi une célèbre ode à cet instrument.&lt;/p&gt; &lt;p&gt;Le clan des Sima, qui s’empare du pouvoir, lui propose un poste ; il le refuse dans une lettre restée fameuse où il rompt avec son ami Shan Tao. Accusé à la suite d’une affaire de famille, il est condamné à mort en 262 ou 263. Selon la tradition, trois mille étudiants demandent sa grâce, en vain, et il joue une dernière fois de la cithare avant son exécution. Il est devenu en Chine le symbole de l’intellectuel qui refuse de servir un pouvoir injuste.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jikang-mini.webp</t>
+        </is>
+      </c>
+      <c r="J318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; ethique</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xuanxue ; Taoïsme</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poète, musicien et penseur chinois, figure centrale des Sept Sages de la forêt de bambous, exécuté pour son indépendance.</t>
+        </is>
+      </c>
+      <c r="O318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P318" s="1"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -6495,8 +6495,10 @@
       <c r="D7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>47</v>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Instructions_de_Shuruppak" title=" Wikipedia"&gt;Instructions de SHURUPPAK&lt;/a&gt; sont l'un des plus anciens textes de sagesse de l'humanité : leurs premières versions, rédigées en sumérien. Elles mettent en scène Shuruppak, sage et roi légendaire, qui transmet ses conseils à son fils Ziusudra, le héros sumérien du Déluge.&lt;/p&gt; &lt;p&gt;Les préceptes couvrent tous les domaines de la vie : ne pas voler, ne pas commettre de violence, respecter ses parents, se méfier des paroles imprudentes, choisir avec soin ses terres et ses alliances, et gouverner avec mesure. On y trouve déjà la forme qui fera le succès de la littérature de sagesse du Proche-Orient : des maximes brèves, faciles à retenir, fondées sur l'expérience.&lt;/p&gt; &lt;p&gt;Le texte a été retrouvé sous plusieurs formes, du site d'Abu Salabikh à des copies plus tardives de l'époque &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_pal%C3%A9o-babylonienne" title=" Wikipedia"&gt;paléo-babylonienne&lt;/a&gt;, signe qu'il a été enseigné et recopié pendant des siècles dans les écoles de scribes, les « maisons des tablettes ». Certains conseils paraissent très concrets, comme ne pas construire sa maison près d'une place publique ou ne pas acheter un âne qui braie ; d'autres ont une portée morale plus générale, comme ne pas proférer de mensonges ou ne pas se montrer arrogant.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ziusudra" title=" Wikipedia"&gt;La figure de Ziusudra&lt;/a&gt;, le fils qui reçoit ces instructions, est celle du survivant du Déluge dans la tradition sumérienne, l'équivalent d'Uta-napishti dans l'Épopée de Gilgamesh et de Noé dans la Bible. La sagesse est ainsi placée à l'origine même de l'humanité, comme un savoir transmis depuis les temps les plus anciens.&lt;/p&gt; &lt;p&gt;Ce texte montre qu'une réflexion morale structurée existait en Mésopotamie bien avant la philosophie grecque, et qu'elle a nourri toute une tradition, jusqu'aux Proverbes de la Bible.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F7" s="1" t="s">
         <v>48</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -7396,8 +7396,10 @@
       <c r="F28" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>229</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kanada ancient indian par Few Minutes Knowledge</t>
+        </is>
       </c>
       <c r="H28" s="2" t="s">
         <v>230</v>
@@ -7613,8 +7615,10 @@
       <c r="F33" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>277</v>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Bouddha - une vie, une oeuvre" par Histoire et Mythologie en BD</t>
+        </is>
       </c>
       <c r="H33" s="8" t="s">
         <v>278</v>
@@ -7658,8 +7662,10 @@
       <c r="F34" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>285</v>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patanjali par Mystica</t>
+        </is>
       </c>
       <c r="H34" s="8" t="s">
         <v>286</v>
@@ -7700,8 +7706,10 @@
       <c r="F35" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>294</v>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Confucius: les Enseignements d'un sage Millénbaire" par Film 25 Production  </t>
+        </is>
       </c>
       <c r="H35" s="8" t="s">
         <v>295</v>
@@ -9789,8 +9797,10 @@
       <c r="F83" s="7" t="s">
         <v>696</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>697</v>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omar Khayyam par Le Samouraï Sage</t>
+        </is>
       </c>
       <c r="H83" s="8" t="s">
         <v>698</v>
@@ -9960,8 +9970,10 @@
       <c r="F87" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="G87" s="8" t="s">
-        <v>731</v>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'eternel retour du contresens" par Andrea Cirla</t>
+        </is>
       </c>
       <c r="H87" s="8" t="s">
         <v>732</v>
@@ -10462,7 +10474,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">"NICHIREN DAISHONIN : Le secret enfoui dans le mantra le plus récité au monde." par MYSTICA</t>
+          <t xml:space="preserve">"NICHIREN DAISHONIN : Le secret enfoui dans le mantra le plus récité au monde." par Mystica</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -11260,8 +11272,10 @@
       <c r="F116" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="G116" s="2" t="s">
-        <v>967</v>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le combat de yamaga soko pour l’âme des samouraîs par Vox Temporis</t>
+        </is>
       </c>
       <c r="H116" s="2" t="s">
         <v>968</v>
@@ -12417,7 +12431,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Feng Youlan: Rediscovering Chinese Philosophy｜Philosopher Biography" par VIS PHILO.</t>
+          <t xml:space="preserve">"Feng Youlan: Rediscovering Chinese Philosophy｜Philosopher Biography" par VIS PHILO</t>
         </is>
       </c>
       <c r="H142" s="2" t="s">
@@ -12736,8 +12750,10 @@
       <c r="F148" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>1181</v>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aimé Cesaire : la négritude par Ina Culture</t>
+        </is>
       </c>
       <c r="H148" s="2" t="s">
         <v>1182</v>
@@ -12918,7 +12934,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">"What Confucius and Li Zehou Can Teach Us About the True Meaning of Life?" par VIS PHILO.</t>
+          <t xml:space="preserve">"What Confucius and Li Zehou Can Teach Us About the True Meaning of Life?" par VIS PHILO</t>
         </is>
       </c>
       <c r="H152" s="2" t="s">

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -6416,8 +6416,10 @@
       <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kagemni_(vizir_de_Snéfrou)"  title=" Wikipedia"&gt;KAGEMNI&lt;/a&gt; était un vizir de l'Ancien Empire égyptien, au service du pharaon Snéfrou, fondateur de la IVe dynastie. Son nom reste attaché à l'&lt;em&gt; &lt;a href="https://fr.wikipedia.org/wiki/Instructions_pour_Kagemni"  title="instructions pour kagemni par wikipedia"&gt;Enseignement pour Kagemni&lt;/a&gt; &lt;/em&gt;, un court texte de sagesse conservé sur le célèbre papyrus Prisse, le même manuscrit qui contient les maximes de Ptahhotep.&lt;/p&gt; &lt;p&gt;Comme beaucoup d'enseignements égyptiens, ce texte a sans doute été rédigé plus tard, au Moyen Empire, puis placé sous l'autorité d'un sage du passé. Il se présente comme les conseils d'un père à ses enfants : on y loue la modestie, la maîtrise de soi et la retenue à table comme dans les paroles, et l'on met en garde contre l'orgueil et la gloutonnerie.&lt;/p&gt; &lt;p&gt;L'enseignement commence par une phrase restée célèbre : « L'homme respectueux prospère, le modeste est loué ; la tente est ouverte au silencieux ». Le silence, la discrétion et la politesse y sont présentés comme des vertus sociales, qui protègent contre les conflits et attirent la faveur des supérieurs. La gourmandise est vue comme un manque de maîtrise : celui qui se jette sur la nourriture se laisse gouverner par ses désirs au lieu de se gouverner lui-même.&lt;/p&gt; &lt;p&gt;Ce type de texte, appelé &lt;em&gt;sebayt&lt;/em&gt; (« enseignement »), était copié et recopié par les apprentis scribes. Il servait à la fois à apprendre à écrire et à former le caractère des futurs fonctionnaires de l'État égyptien. La sagesse n'y est pas une spéculation abstraite, mais une éducation pratique à la vie en société.&lt;/p&gt; &lt;p&gt;Derrière ces règles de conduite se dessine une idée centrale de la pensée égyptienne : l'homme sage est celui qui sait se tenir à sa place et préserver l'harmonie de l'ordre social, reflet de la Maât, l'ordre juste du monde.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
@@ -6457,8 +6459,10 @@
       <c r="D6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>40</v>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hordjédef"  title=" Wikipedia"&gt;HORDJÉDEF&lt;/a&gt; était un prince de la IVe dynastie égyptienne, fils du pharaon Khéops. Les Égyptiens eux-mêmes le tenaient pour l'un des plus grands sages de leur histoire : son nom est cité avec admiration jusqu'à l'époque romaine.&lt;/p&gt; &lt;p&gt;On lui attribue un &lt;em&gt;Enseignement&lt;/em&gt; adressé à son fils Aouibrê, dont il ne subsiste que des fragments. Le texte, sans doute composé au Moyen Empire, conseille de fonder un foyer, d'élever un fils et de préparer dignement sa tombe : la sagesse y est d'abord une manière de bien vivre pour bien mourir, en assurant sa mémoire et la continuité de sa lignée.&lt;/p&gt; &lt;p&gt;La célébrité d'Hordjédef dépasse largement ce texte. Un papyrus raconte qu'il fit venir à la cour de son père le magicien Djédi, et le Livre des morts lui attribue la découverte de certaines formules sacrées. Plus tard, les Égyptiens le rangèrent parmi les grands sages du passé, aux côtés d'Imhotep et de Ptahhotep, dont « les noms durent à cause de leurs livres ».&lt;/p&gt; &lt;p&gt;Cette idée est essentielle dans la culture égyptienne : l'écrit est une forme d'immortalité. Plus sûrement qu'une pyramide ou une tombe, le livre transmet le nom et la pensée de son auteur aux générations futures. Il devient ainsi le symbole du sage dont la parole survit au temps.&lt;/p&gt; &lt;p&gt;Il illustre une figure typique de la pensée égyptienne : le sage n'est pas un penseur solitaire mais un homme de rang qui transmet à ses descendants un art de vivre conforme à l'ordre du monde.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="H6" s="2" t="s">
         <v>41</v>
@@ -6751,8 +6755,10 @@
       <c r="D13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>103</v>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Dialogue_du_d%C3%A9sesp%C3%A9r%C3%A9_avec_son_b%C3%A2"  title=" Wikipedia"&gt;Dialogue du DÉSESPÉRÉ avec son ba&lt;/a&gt; est un texte égyptien du Moyen Empire, daté du règne d'Amenemhat III. Un homme accablé par la souffrance et l'injustice y dialogue avec son &lt;em&gt;ba&lt;/em&gt;, une part de son âme.&lt;/p&gt; &lt;p&gt;L'homme songe à mourir et vante la mort comme une délivrance ; son ba lui oppose d'abord la joie de vivre, puis menace de l'abandonner. La discussion, faite de poèmes d'une grande beauté (« La mort est devant moi aujourd'hui comme la guérison d'un malade »), aborde le sens de la vie, la valeur des rites funéraires et la solitude dans un monde où « il n'y a plus de juste ».&lt;/p&gt; &lt;p&gt;Le texte, conservé sur un papyrus aujourd'hui à Berlin dont le début est perdu, est d'une forme très élaborée. Il alterne des passages en prose, où l'homme et le ba argumentent, et quatre poèmes, construits sur des refrains : « Vois, mon nom est méprisé », « À qui parler aujourd'hui ? », « La mort est devant moi aujourd'hui », « Certes, celui qui est là-bas sera un dieu vivant ».&lt;/p&gt; &lt;p&gt;Le ba, pour sa part, rappelle que les tombeaux les plus somptueux finissent en ruine, comme ceux des pauvres, et invite l'homme à « suivre le jour heureux » et à oublier ses soucis. Les spécialistes discutent encore de la conclusion : le ba accepte-t-il de rester avec l'homme jusqu'à sa mort naturelle, ou consent-il à le suivre ? Cette ambiguïté fait toute la richesse du texte.&lt;/p&gt; &lt;p&gt;Souvent présenté comme le premier texte philosophique sur le suicide et le sens de l'existence, ce dialogue montre que la pensée égyptienne savait aussi douter et s'interroger.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F13" s="1" t="s">
         <v>104</v>
@@ -6833,8 +6839,10 @@
       <c r="D15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>118</v>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hammurabi"  title=" Wikipedia"&gt;HAMMURABI&lt;/a&gt; fut roi de Babylone. Par ses conquêtes, il fit de sa cité la capitale d'un grand royaume mésopotamien.&lt;/p&gt; &lt;p&gt;Il est surtout connu pour le &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=cbuBFgmEir4" title="le code d’hammourabi par le prof presente, la chaine histoire"&gt;Code de Hammurabi&lt;/a&gt; &lt;/em&gt;, gravé vers la fin de son règne sur une stèle de basalte aujourd'hui conservée au musée du Louvre. Ce recueil de près de trois cents décisions de justice règle la vie économique, familiale et sociale, avec le célèbre principe de la loi du talion (« œil pour œil »).&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Code_de_Hammurabi" title="le code d’hammourabi par wikipedia"&gt;Le code &lt;/a&gt; ne se présente pas comme une législation abstraite mais comme une liste de cas : « si un homme a fait ceci, alors il lui sera fait cela ». Les peines varient selon le rang social de la victime et du coupable, homme libre, dépendant ou esclave, ce qui reflète une société très hiérarchisée. Le code traite des prix, des salaires, des prêts, du mariage, du divorce, de l'héritage, des soins médicaux et même de la responsabilité des architectes dont la maison s'effondre.&lt;/p&gt; &lt;p&gt;La loi du talion, qui paraît brutale aujourd'hui, avait aussi pour but de limiter la vengeance : la peine doit être proportionnée au dommage, et non illimitée. Le code affirme enfin que tout homme lésé peut venir lire la stèle pour connaître ses droits, idée d'une justice publique et accessible qui marque une étape importante dans l'histoire du droit.&lt;/p&gt; &lt;p&gt;Le prologue en donne la philosophie : le roi a reçu des dieux la mission de « faire apparaître la justice dans le pays, détruire le méchant et le pervers, afin que le fort n'opprime pas le faible ». L'idée que le pouvoir se justifie par la protection des plus faibles traversera toute l'histoire de la pensée politique.&lt;/p&gt;   &lt;audio controls title="oeuvre mesopotamienne ; tête de Hammurabi par France Culture"&gt;&lt;source src="https://media.radiofrance-podcast.net/podcast09/13090-10.01.2016-ITEMA_20885368-2015C21360E0045-21.mp3" type="audio/mpeg"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F15" s="1" t="s">
         <v>119</v>
@@ -6960,8 +6968,10 @@
       <c r="D18" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>143</v>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zarathoustra"  title=" Wikipedia"&gt;ZARATHOUSTRA&lt;/a&gt;, ou Zoroastre, est le prophète fondateur  &lt;a href="https://www.youtube.com/watch?v=bRmvF4sSxRs" title="Le zoroastrisme, religion du feu par Nat Geo Fr"&gt;du zoroastrisme, &lt;/a&gt;  la religion de l'Iran ancien. Ses dates sont très discutées : l'analyse de la langue des &lt;em&gt;Gathas&lt;/em&gt;, les hymnes qui lui sont attribués, conduit aujourd'hui la plupart des spécialistes à le situer vers l'an 1000 avant J.-C.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AupMQo89m6Y" title="avant Jésus, Mahomet par collapX"&gt;Sa pensée &lt;/a&gt;  repose sur l'opposition entre deux principes : l'esprit du bien, lié à Ahura Mazda, le « Seigneur sage », et l'esprit du mal et du mensonge. Chaque être humain est libre de choisir son camp par ses pensées, ses paroles et ses actions, et sera jugé selon ce choix.&lt;/p&gt; &lt;p&gt;Selon la tradition, il reçut sa révélation vers l'âge de trente ans, lors d'une vision au bord d'une rivière. Il dut affronter l'hostilité des prêtres de l'ancienne religion avant de trouver un protecteur, le roi Vishtaspa, qui se convertit à son enseignement. Ses &lt;em&gt;Gathas&lt;/em&gt;, dix-sept hymnes écrits dans une langue très archaïque, forment la partie la plus ancienne de l'Avesta, le livre sacré du zoroastrisme.&lt;/p&gt; &lt;p&gt;Le zoroastrisme devint plus tard la religion des grands empires perses, des Achéménides aux Sassanides, jusqu'à la conquête arabe au VIIe siècle. Il survit aujourd'hui dans de petites communautés en Iran et chez les Parsis de l'Inde. &lt;a href="https://www.histoire-et-civilisations.com/thematiques/antiquite/zarathoustra-le-prophete-du-feu-69413.php" title="Zarathoustra, le prophète du feu par histoire et civilisations"&gt; Le feu, symbole de la vérité &lt;/a&gt;  et de la pureté, y occupe une place centrale, ce qui a valu aux zoroastriens le nom, inexact, d'« adorateurs du feu ».&lt;/p&gt; &lt;p&gt;Cette vision d'un combat cosmique entre le bien et le mal, de la responsabilité morale individuelle et d'un jugement final a profondément influencé le judaïsme, le christianisme et l'islam. Nietzsche a repris son nom dans &lt;em&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ainsi_parlait_Zarathoustra" title="ainsi parlait Zarathoutra par wikipedia"&gt;Ainsi parlait Zarathoustra&lt;/a&gt; &lt;/em&gt;.&lt;/p&gt; &lt;audio controls title="L’iran, de Zarathoustra aux ayatollahs par France Culture"&gt;&lt;source src="https://media.radiofrance-podcast.net/podcast09/14006-17.10.2015-ITEMA_20820029-2015M22763E0049-21.mp3" type="audio/mpeg"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F18" s="1" t="s">
         <v>144</v>
@@ -7131,8 +7141,10 @@
       <c r="D22" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>178</v>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amenemopet_(scribe)"  title=" Wikipedia"&gt;AMEMOPET&lt;/a&gt;, fils de Kanakht, était un scribe égyptien de &lt;a href="https://fr.wikipedia.org/wiki/%C3%89poque_ramesside" title="epoque ramesside par wikipedia"&gt;l'époque Ramesside. &lt;/a&gt; Il composa pour son fils un &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=Q_zws-8V_9g" title="sagesse egyptienne par sinouhe"&gt;Enseignement &lt;/a&gt; &lt;/em&gt; en trente chapitres, l'un des plus beaux textes de sagesse de l'Égypte ancienne.&lt;/p&gt; &lt;p&gt;Il y oppose l'homme « silencieux », calme, honnête et maître de lui, à l'homme « emporté », colérique et avide. Il recommande de ne pas déplacer les bornes des champs, de ne pas se moquer des faibles, de ne pas s'enrichir par la fraude, et rappelle que l'homme ne connaît pas l'avenir : « l'homme est argile et paille, le dieu est son bâtisseur ».&lt;/p&gt; &lt;p&gt;L'enseignement est connu principalement par un papyrus conservé au British Museum, et par de nombreux fragments sur des tablettes d'écoliers, signe qu'il servait à la formation des scribes. Il se distingue des enseignements plus anciens par la place qu'il accorde à la vie intérieure : la vraie valeur de l'homme ne réside pas dans sa réussite sociale mais dans son calme, sa droiture et sa confiance en la divinité.&lt;/p&gt; &lt;p&gt;Le rapprochement avec la Bible est particulièrement frappant pour un passage des Proverbes (22,17 à 24,22), qui reprend souvent de très près les conseils d'Amenemopet, jusqu'à la mention de « trente » sentences. Cette parenté montre que les sages d'Israël connaissaient la littérature de sagesse égyptienne et s'en inspiraient, en l'adaptant à leur propre foi.&lt;/p&gt; &lt;p&gt;Plusieurs passages ont été rapprochés du livre biblique des Proverbes, ce qui montre la circulation des idées de sagesse dans tout le Proche-Orient ancien.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F22" s="1" t="s">
         <v>179</v>
@@ -7346,8 +7358,10 @@
       <c r="D27" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>219</v>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A8s_Trism%C3%A9giste" title=" Wikipedia"&gt;Hermès TRISMÉGISTE&lt;/a&gt; est une figure mythique dont il est difficile de définir son apparition qui mélange des éléments de la religion égyptienne, de la philosophie grecque, et de &lt;a href="https://www.youtube.com/watch?v=hMfG77klDGM&amp;t=1803s&amp;ab_channel=ArcanalesMyst%C3%A8resduMonde"  title="L'Hermétisme par Arcana"&gt; l'Hermétisme&lt;/a&gt;.  Au cours de &lt;a href="https://www.youtube.com/watch?v=EqU-kD8dW4Y" title="l'époque hellénistique par Yannick Rub"&gt;l'époque Hellénistique&lt;/a&gt;, les Grecs ont assimilé Thot, dieu égyptien de la sagesse, de l'écriture et de la magie à Hermès, messager des dieux grecs, dieu du commerce, des voleurs et guide des âmes vers l'au-delà créant ainsi une figure syncrétique qui incarne les attributs des deux dieux. Il est donc vu comme un sage qui détient des connaissances profondes sur les mystères de l'univers et est souvent considéré comme le fondateur de l'alchimie occidentale.&lt;/p&gt; &lt;p&gt; Ses principaux écrits sont regroupés sous le nom de Corpus Hermeticum. Ce recueil, composé de dix-sept traités philosophiques et mystiques rédigés en grec et en latin est la collection la plus importante et la plus connue des écrits hermétiques. Poimandrès est le premier et le plus important des traités, où Hermès reçoit une révélation divine de Poimandrès, l'esprit de la suprême intelligence. Il traite de la création de l'univers, de la nature de l'homme, et du chemin vers la connaissance divine.&lt;/p&gt;  &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=9v4SOqEchVk&amp;ab_channel=Cultination"  title="Les tablettes d'Emeraude par Cultination"&gt;La Table d'Émeraude &lt;/a&gt; est un texte hermétique bref contenant une série d'aphorismes considérés comme les fondements de l'alchimie occidentale. Le plus célèbre d'entre eux est : "Ce qui est en bas est comme ce qui est en haut, et ce qui est en haut est comme ce qui est en bas". Il a été largement étudié et commenté par des alchimistes et des philosophes, dont Paracelse et Isaac Newton. &lt;/p&gt; &lt;p&gt; En 1908, un ouvrage influent,  &lt;a href="https://www.youtube.com/watch?v=N8hmlwapya0&amp;ab_channel=GnothiSeauton" title="Le Kybalion par Gnothi Seauton"&gt;Le Kybalion&lt;/a&gt;, publié par trois auteurs anonymes et associé à Hermès Trismégiste, est un texte moderne qui synthétise et présente des concepts philosophiques et ésotériques inspirés par les enseignements hermétiques. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F27" s="7" t="s">
         <v>220</v>
@@ -7435,7 +7449,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt; est le sage fondateur traditionnel du Sâmkhya, l’une des plus anciennes écoles de philosophie indienne. Sa figure appartient à la légende : la &lt;em&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhagavad-G%C4%ABt%C4%81" title=" Wikipedia"&gt;Bhagavad-Gîtâ&lt;/a&gt;&lt;/em&gt; le nomme parmi les sages accomplis, et les Purânas en font une incarnation de Vishnou enseignant la délivrance à sa mère. Aucun de ses écrits ne nous est parvenu ; le plus ancien exposé conservé de la doctrine, les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; d’Îshvarakrishna, date des premiers siècles de notre ère.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=PcOxBi1VRL4"  title="kapila and sankhya par foolish musings"&gt;Le Sâmkhya &lt;/a&gt; propose un dualisme radical entre la conscience pure (&lt;em&gt;puruṣa&lt;/em&gt;) et la matière primordiale (&lt;em&gt;prakṛti&lt;/em&gt;), dont l’évolution engendre l’ensemble du monde phénoménal. La matière est faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté, l’énergie et l’inertie ; de leur déséquilibre naissent successivement l’intellect, le sens du moi, le mental, les sens et les éléments, soit vingt-cinq principes en tout : le mot &lt;em&gt;sâmkhya&lt;/em&gt; signifie d’ailleurs « dénombrement ». L’effet préexiste dans sa cause, comme l’huile dans la graine de sésame. Ce dualisme de l’âme et de la matière rappelle celui du &lt;a href="https://www.youtube.com/watch?v=Q0AR1mxTME4&amp;t=106s&amp;ab_channel=Ja%C3%AFnisme-Uneintroduction"  title="Jaïnisme Introduction par Jaïnisme Université de Gent "&gt;jaïnisme &lt;/a&gt;, qui distingue lui aussi les âmes de la matière inerte.&lt;/p&gt; &lt;p&gt;La souffrance vient de ce que la conscience se confond avec les activités de la matière ; la délivrance (&lt;em&gt;kaivalya&lt;/em&gt;) est leur discernement, l’« isolement » de la conscience, spectatrice immobile. Contrairement au Vedânta, le Sâmkhya admet une infinité de consciences distinctes, une pour chaque être. Les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; comparent la matière à une danseuse qui se retire une fois qu’elle s’est montrée au spectateur. Cette cosmologie, indépendante de toute divinité créatrice, a profondément marqué l’hindouisme classique et sert de socle théorique aux &lt;a href="https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Yoga-sûtras&lt;/em&gt; de Patañjali&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt; est le sage fondateur traditionnel du Sâmkhya, l’une des plus anciennes écoles de philosophie indienne. Sa figure appartient à la légende : la &lt;em&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhagavad-G%C4%ABt%C4%81" title=" Wikipedia"&gt;Bhagavad-Gîtâ&lt;/a&gt;&lt;/em&gt; le nomme parmi les sages accomplis, et les Purânas en font une incarnation de Vishnou enseignant la délivrance à sa mère. Aucun de ses écrits ne nous est parvenu ; le plus ancien exposé conservé de la doctrine, les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; d’Îshvarakrishna, date des premiers siècles de notre ère.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=PcOxBi1VRL4"  title="kapila and sankhya par foolish musings"&gt;Le Sâmkhya &lt;/a&gt; propose un dualisme radical entre la conscience pure (&lt;em&gt;puruṣa&lt;/em&gt;) et la matière primordiale (&lt;em&gt;prakṛti&lt;/em&gt;), dont l’évolution engendre l’ensemble du monde phénoménal. La matière est faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté, l’énergie et l’inertie ; de leur déséquilibre naissent successivement l’intellect, le sens du moi, le mental, les sens et les éléments, soit vingt-cinq principes en tout : le mot &lt;em&gt;sâmkhya&lt;/em&gt; signifie d’ailleurs « dénombrement ». L’effet préexiste dans sa cause, comme l’huile dans la graine de sésame. Ce dualisme de l’âme et de la matière rappelle celui du &lt;a href="https://www.youtube.com/watch?v=Q0AR1mxTME4&amp;t=106s&amp;ab_channel=Ja%C3%AFnisme-Uneintroduction"  title="Jaïnisme Introduction par Jaïnisme Université de Gent "&gt;jaïnisme&lt;/a&gt;, qui distingue lui aussi les âmes de la matière inerte.&lt;/p&gt; &lt;p&gt;La souffrance vient de ce que la conscience se confond avec les activités de la matière ; la délivrance (&lt;em&gt;kaivalya&lt;/em&gt;) est leur discernement, l’« isolement » de la conscience, spectatrice immobile. Contrairement au Vedânta, le Sâmkhya admet une infinité de consciences distinctes, une pour chaque être. Les &lt;em&gt;Sâmkhya-kârikâ&lt;/em&gt; comparent la matière à une danseuse qui se retire une fois qu’elle s’est montrée au spectateur. Cette cosmologie, indépendante de toute divinité créatrice, a profondément marqué l’hindouisme classique et sert de socle théorique aux &lt;a href="https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Yoga-sûtras&lt;/em&gt; de Patañjali&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F29" s="1" t="s">
@@ -7519,8 +7533,13 @@
       <c r="D31" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>253</v>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Mah%C4%81v%C4%ABra"  title=" Wikipedia"&gt; MAHAVIRA&lt;/a&gt;  connu sous différents noms, comme Vardhamāna et Jina, ce qui signifie "victorieux" en sanskrit. Il était un enseignant spirituel et le vingt-quatrième et dernier Tirthankara du  &lt;a href="https://www.youtube.com/watch?v=Q0AR1mxTME4&amp;t=106s&amp;ab_channel=Ja%C3%AFnisme-Uneintroduction"  title="Jaïnisme Introduction par Jaïnisme Université de Gent "&gt;jaïnisme&lt;/a&gt;, une ancienne religion philosophique indienne. Son nom "Mahāvīra" se traduit par "le grand héros" ou "le grand courageux". Il a vécu une vie d'ascétisme et de méditation, renonçant à tous les plaisirs matériels pour atteindre l'illumination spirituelle. &lt;/p&gt; &lt;p&gt; Mahāvīra est  une figure vénérée et un guide spirituel par les jaïns. Sa vie et ses &lt;a href="https://kriko.fr/jainisme/collectif-%5Bjain-11%5D-lecons-pour-les-juniors.pdf"  title="Jaïnisme pour les juniors par Kriko "&gt;enseignements&lt;/a&gt;  sont racontés dans les textes sacrés du jaïnisme, tels que les &lt;a href="https://fr.wikipedia.org/wiki/Agama_(sanskrit)"   title="Agama (sanskrit) par Wikipédia "&gt;"Agamas"&lt;/a&gt;  et les "Sutras", qui sont vénérés par la communauté jaïne. &lt;/p&gt; &lt;p&gt;
+Selon les croyances jaïnes, il a atteint l'état de moksha, la libération ultime de l'existence cyclique, après une période d'austérité et de méditation intense qui a duré douze ans. Il a ensuite commencé à enseigner les principes du jaïnisme à un large public. Ses enseignements mettaient l'accent sur la non-violence (ahimsa), la vérité (satya), la non-possessivité (aparigraha), l'ascétisme et la compassion envers toutes les formes de vie. &lt;/p&gt; &lt;p&gt;
+Il a également mis l'accent sur le concept de karma, selon lequel les actions d'une personne déterminent son destin et sa progression spirituelle et a encouragé ses disciples à suivre un mode de vie ascétique et à pratiquer la méditation pour purifier leur âme et se libérer du cycle des naissances et des morts. &lt;/p&gt; 
+&lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F31" s="7" t="s">
         <v>254</v>
@@ -7564,8 +7583,11 @@
       <c r="D32" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>263</v>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Lao_Tseu"  title=" Wikipedia"&gt; LAO TSEU&lt;/a&gt; est considéré comme le fondateur du &lt;a href="https://www.youtube.com/watch?v=hL2fYGEt3nM"  title="Taoisme par Histoire et mythologie en BD"&gt; "Taoisme"&lt;/a&gt;, une doctrine philosophique et religieuse chinoise qui prône l'harmonie avec la nature et le rejet des règles et des dogmes sociaux.&lt;/p&gt; &lt;p&gt; Il est l'auteur du &lt;a href="https://www.youtube.com/watch?v=VJjDmTtI4yA&amp;list=RDCMUCgpW5IDGiR_7AZZoJIwBfog&amp;start_radio=1&amp;rv=VJjDmTtI4yA&amp;t=104&amp;ab_channel=LeVieuxSage"   title="Tao Te Ching par Le vieux sage"&gt; "Tao Te Ching"&lt;/a&gt; (ou "Livre de la voie et de la vertu"), qui est considéré comme le texte fondateur. &lt;/p&gt; &lt;p&gt;Il encourage à suivre  &lt;a href="https://www.youtube.com/watch?v=RuDKIDQkV5M&amp;ab_channel=JeanLaval"  title="5 Principes Taoïstes par Jean Laval"&gt; " le Tao"&lt;/a&gt;, ou "la voie", qui est considérée comme un principe fondamental de l'univers, qui guide toutes choses dans leur cycle naturel de naissance, de croissance, de maturité et de mort.&lt;p&gt; &lt;/p&gt;  &lt;a href="https://fr.wikisource.org/wiki/Le_Tao_de_Laotseu_(Traduction_de_Pouvourville)"   title="Oeuvre de Lao-tseu de Wikisource et traduit par Pouvourville"&gt; Le texte&lt;/a&gt; met également en avant la pratique de la non-action (wu-wei) pour atteindre l'harmonie avec le Tao.&lt;/p&gt; &lt;p&gt; Le Taoïsme a eu une grande influence en Chine, notamment dans la pensée politique et culturelle, mais aussi en matière de médecine, d'art et de littérature. Il y est encore pratiqué de nos jours mais aussi dans d'autres parties de l'Asie de l'Est, ainsi que dans le monde occidental où il est devenu une forme de spiritualité alternative. &lt;/p&gt;   &lt;audio controls title="Tao-tö king de Lao-tseu par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/musique/sons/2014/24/RF_EC34FD0A-1A6D-437F-86E2-32B4A31F1304_GENE.MP3?9f68b2c6-e799-42c5-a6d4-6a27cc203040" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F32" s="7" t="s">
         <v>264</v>
@@ -7932,8 +7954,10 @@
       <c r="D40" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>325</v>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mozi" title=" Wikipedia"&gt;MOZI&lt;/a&gt; était un philosophe chinois, fondateur du mohisme, une école rivale du confucianisme pendant la période des Royaumes combattants. Issu d'un milieu modeste, peut-être artisan, et aurait initialement suivi les enseignements de Confucius avant de les rejeter pour leur excès rituel. Il voyagea entre les États féodaux en guerre pour permettre aux princes d'adopter ses idées et éviter les conflits, renforçant même les défenses des États attaqués. Il mena une vie ascétique, simple et dédiée aux gens du peuple, contrastant avec l'orientation aristocratique de Confucius, et forma une école organisée avec des disciples influents.&lt;/p&gt; &lt;p&gt; Son  &lt;a href="https://www.youtube.com/watch?v=QWdxGbZtHog"  title="Universal Love over War par The Thought Table "&gt;concept central&lt;/a&gt;, l'amour impartial (jian ai), prône d'aimer autrui sans distinction comme soi-même, pour remplacer l'égoïsme source de chaos par une universalité bénéfique à tous, justifiée par l'utilitarisme et la volonté du Ciel. Il défendait la méritocratie (élévation des vertueux), l'unité sous un autorité supérieure, l'opposition à la guerre offensive, l'économie dans les dépenses et funérailles, la croyance en des fantômes percevants et en un Ciel moral récompensant la justice. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=lsfv4-EtqEs"  title="Mozi : une sagesse ancestrale pour la paix et l'innovation modernes par The curious codex "&gt;Le "livre Mozi"&lt;/a&gt;, compilé par ses disciples, compte 71 chapitres originaux (dont 18 perdus), divisés en doctrines centrales (ex. exaltation des dignes), chapitres dialectiques sur la logique et sciences, récits et manuels militaires défensifs. Bien que le mohisme ait décliné au IIIe siècle av. J.-C., ses idées sur l'utilitarisme et la méritocratie influencèrent la Chine impériale et résonnent encore aujourd'hui. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F40" s="7" t="s">
         <v>326</v>
@@ -8193,8 +8217,11 @@
       <c r="D46" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>374</v>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Han_Fei_Zi"   title=" Wikipedia"&gt;HAN FEI Zi&lt;/a&gt;  était un philosophe et penseur politique chinois, à l'époque des Royaumes Combattants, une période de chaos où les États se déchiraient pour la domination. Contrairement à Confucius ou Laozi, qui prônaient la vertu ou l’harmonie, il était un peu le   &lt;a href="https://www.youtube.com/watch?v=l1oZpuMmTSI"  title="Han Fei Tzu | The Machiavelli from China  par PhilosophyToons"&gt;"Machiavel Chinois"&lt;/a&gt;, théoricien du &lt;a href="https://www.imaginairedelachine.fr/2025/01/ni-trop-ni-trop-peu-la-mecanique-implacable-du-legisme-selon-han-feizi.html"  title="La mécanique implacable du légisme selon Han Feizi  par overblog"&gt;Légisme&lt;/a&gt;, une doctrine où l'ordre et la prospérité ne peuvent être apportés que par un État fort, reposant sur des lois très strictes et non sur la morale et la compréhension. &lt;/p&gt; &lt;p&gt;  Sa philosophie que l'on retrouve dans son ouvrages, &lt;a href="https://fr.wikipedia.org/wiki/L%27Art_de_gouverner"  title="L'art de gouverner- Han Feizi  par Wikipedia"&gt;"l'art de gouverner" &lt;/a&gt; repose sur trois principes : &lt;/p&gt; &lt;p&gt; -  La Loi doit être claire, écrite, et appliquée sans exception, même pour l’empereur. Pour lui, l’homme est égoïste par nature et  seules des punitions brutales (amputations, exécutions) et des récompenses matérielles peuvent contrôler le peuple. &lt;/p&gt; &lt;p&gt; -  Le Pouvoir :  Un dirigeant doit monopoliser le pouvoir et ne jamais le partager, même avec des ministres talentueux. Il conseille aux souverains d’utiliser ruses et espions pour surveiller leurs sujets. &lt;/p&gt; &lt;p&gt; - La Méthode : Contrôle des Élites : Les ministres sont des loups qu’il faut diviser et surveiler. Le dirigeant idéal reste énigmatique, ne révélant jamais ses intentions. &lt;/p&gt; &lt;p&gt; Han Fei Zi était le penseur de l’État totalitaire avant l’heure. Son héritage, aussi brutal soit-il, reste une clé pour comprendre la politique chinoise, ancienne et moderne. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;   &lt;audio controls title="Han Fei Zi, se cacher pour mieux régner par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.06.2017-ITEMA_21347953-2017C12410S0157-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F46" s="7" t="s">
         <v>375</v>
@@ -8235,8 +8262,15 @@
       <c r="D47" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="E47" s="8" t="s">
-        <v>383</v>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dong_Zhongshu"  style="color:#6A142A"  title=" Wikipedia"&gt;Dong ZHONGSHU&lt;/a&gt; était une des figure influente de la Chine ancienne, connu pour son rôle dans l'établissement du &lt;a href="https://www.youtube.com/watch?v=fo3R4EazLsE" style="color:#88A1E9" title=" le confucianisme par Koala d'Asie"&gt; confucianisme&lt;/a&gt; comme idéologie officielle de l'État sous la dynastie Han. Après la chute de la dynastie Qin, les Han ont cherché à stabiliser leur règne en s'appuyant sur des principes philosophiques et moraux. Dong Zhongshu a joué un rôle clé dans cette transition. &lt;/p&gt; &lt;p&gt; Il est connu pour avoir synthétisé le confucianisme avec des éléments de cosmologie et de pensée naturaliste, créant ainsi une philosophie politique et morale qui a dominé la Chine pendant des siècles. Voici les aspects clés de sa pensée : &lt;/p&gt; 
+&lt;p&gt; - L'harmonie entre le Ciel, la Terre et l'Homme : Il a développé une vision cosmologique où le Ciel est une force morale et ordonnée qui influence les affaires humaines. Les catastrophes naturelles étaient interprétées comme des signes de désapprobation céleste envers les actions de l'empereur. &lt;/p&gt; 
+&lt;p&gt; -  &lt;a href="https://www.youtube.com/watch?v=JUXBcP5hNHc" style="color:#88A1E9" title="La Théorie des 5 Éléments en médecine chinoise par Clara"&gt; La théorie des Cinq Éléments&lt;/a&gt; : Il a intégré la théorie des Cinq Éléments (bois, feu, terre, métal, eau) dans sa philosophie pour expliquer les cycles naturels et les relations entre les phénomènes. Cette théorie a été utilisée pour justifier les changements politiques et sociaux. &lt;/p&gt; 
+&lt;p&gt; - Le confucianisme comme idéologie d'État : Il a promu les valeurs confucéennes, telles que la piété filiale, la loyauté et la moralité, comme fondements de la gouvernance. &lt;/p&gt; 
+&lt;p&gt; - La doctrine des Trois Enseignements : Il a formulé la doctrine des Trois Enseignements, qui définit les relations hiérarchiques fondamentales dans la société : 
+ - Le souverain dirige le sujet. -  Le père dirige le fils.  -  Le mari dirige la femme. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Il est l'auteur de plusieurs textes importants, dont le plus célèbre est le  &lt;a href="https://en.wikipedia.org/wiki/Luxuriant_Dew_of_the_Spring_and_Autumn_Annals" style="color:#88A1E9" title="Luxuriant Dew of the Spring and Autumn Annals par Wikipedia"&gt;"Luxuriant Dew of the Spring and Autumn Annals"&lt;/a&gt;. Cet ouvrage explore les liens entre les événements historiques, les principes moraux et les phénomènes naturels, en s'appuyant sur les enseignements du Classique des Printemps et Automnes. Sous son influence, le confucianisme est devenu l'idéologie officielle de l'État, un statut qu'il a conservé jusqu'à la fin de la dynastie Qing en 1912. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F47" s="7" t="s">
         <v>384</v>
@@ -8324,8 +8358,15 @@
       <c r="D49" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>405</v>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Wang_Chong" title=" Wikipedia"&gt;Wang CHONG&lt;/a&gt; était un philosophe, astronome et écrivain chinois de la dynastie Han. Il est souvent considéré comme un penseur rationaliste et sceptique, en avance sur son temps. &lt;/p&gt; &lt;p&gt; Son oeuvre majeure "Le Lunheng" est une collection de 85 chapitres qui abordent des sujets variés, allant de la cosmologie à la critique sociale, en passant par la philosophie et la science. Il y développe une pensée fondée sur la raison, l'observation et la critique des superstitions. Voici quelques thèmes clés de l'ouvrage : &lt;/p&gt; 
+&lt;dd&gt; -  &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1992_num_105_101_14820" title=" La notion de destin selon Wang Chong et l'idée critique à l'époque des Han orientaux par Persée"&gt;Critique des superstitions&lt;/a&gt; : Il rejette les croyances populaires en les fantômes, les esprits et les présages. Il soutient que ces croyances sont le résultat de l'ignorance et de la peur, et non de faits réels. &lt;/dd&gt; 
+&lt;dd&gt; - Rationalisme et scepticisme : Il insiste sur l'importance de la raison et de l'observation pour comprendre le monde. Il critique les explications surnaturelles des phénomènes naturels et propose des explications basées sur des causes naturelles. &lt;/dd&gt; 
+&lt;dd&gt; - &lt;a href="https://www.persee.fr/doc/etchi_0755-5857_1995_num_14_1_1223" title=" Pourquoi Wang Chong critique-t-il Confucius ?  par Persée"&gt;Critique du confucianisme&lt;/a&gt; : Il critique certains aspects du confucianisme de son époque, notamment son dogmatisme et son attachement aux rituels. Il appelle à une interprétation plus rationnelle et pragmatique des enseignements confucéens. &lt;/dd&gt; 
+&lt;dd&gt; - Cosmologie : Il propose une vision du monde basée sur le concept de QI, qu'il considère comme la force fondamentale de l'univers. Il rejette l'idée d'un ciel anthropomorphe ou moralisateur, affirmant que les phénomènes naturels sont le résultat de processus impersonnels. &lt;/dd&gt; 
+&lt;dd&gt; - Déterminisme et libre arbitre : Il aborde la question du destin et du libre arbitre. Il soutient que les événements sont largement déterminés par des causes naturelles, mais que les individus ont une certaine capacité à influencer leur destin grâce à leurs actions.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il  est un penseur original et audacieux qui a cherché à promouvoir une vision rationnelle et critique du monde. Son œuvre, le Lunheng, reste une référence importante pour comprendre la philosophie et la science dans la Chine ancienne. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F49" s="7" t="s">
         <v>406</v>
@@ -8453,8 +8494,13 @@
       <c r="D52" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>432</v>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kundakunda"   title=" Wikipedia"&gt;KUNDAKUNDA&lt;/a&gt; était  un philosophe jaïn ancien, considéré comme l'une des figures les plus importantes de la tradition  &lt;a href="https://fr.wikipedia.org/wiki/Sectes_Digambara"  title="Sectes Digambara par Wikipedia"&gt;jaïne digambara&lt;/a&gt;. Son influence sur la pensée jaïne est comparable à celle d'Umasvati, mais son approche est plus mystique et centrée sur la libération spirituelle. Il est l'auteur de plusieurs textes fondateurs, rédigés en prakrit. Les plus célèbres sont : &lt;p&gt; &lt;p&gt; -  &lt;a href="https://en.wikipedia.org/wiki/Pancastikayasara"  title="Pancastikayasara par Wikipedia"&gt;Pancastikayasara&lt;/a&gt; qui explore les cinq réalités fondamentales du jaïnisme : -  Jiva (âme). - Pudgala (matière). - Dharma (principe du mouvement). - Adharma (principe du repos). - Akasha (espace). &lt;/p&gt; 
+&lt;p&gt; - Samayasara : Texte clé sur la nature de l'âme (jiva) et sa distinction avec le karma. Insiste sur la perspective "pure" vs la perspective "relative". &lt;/p&gt; 
+&lt;p&gt; - Pravachanasara : Manuel de discipline spirituelle pour les moines jaïns. Met l'accent sur le renoncement et la purification intérieure. &lt;/p&gt; &lt;p&gt; Il  développe une vision dualiste : l'âme est par nature pure, mais elle est enchaînée par les karmas.  La libération consiste à détruire les karmas par l'ascèse, la méditation et la connaissance. Voir l'âme comme pure conscience, indépendante du corps et des attachments, c'est le niveau de vérité ultime. &lt;/p&gt; &lt;p&gt; Il  prône une voie radicale de renoncement avec un détachement des désirs sensoriels, la pratique de la non-violence absolue et une méditation sur la nature véritable de l'âme. Son message central, "La libération vient de la connaissance de soi". &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F52" s="7" t="s">
         <v>433</v>
@@ -8542,8 +8588,11 @@
       <c r="D54" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>449</v>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Mani_(proph%C3%A8te)"  title=" Wikipedia"&gt;MANI&lt;/a&gt;  était un Persan connu pour avoir fondé le &lt;a href="https://www.youtube.com/watch?v=staHDNcztzM"   title=" le Manichéisme par Street Strory"&gt; Manichéisme&lt;/a&gt;, une religion et une philosophie qui a exercé une grande influence sur l'Orient et l'Occident pendant plusieurs siècles et son message a rapidement gagné en popularité en raison de sa nature &lt;a href="https://www.youtube.com/watch?v=DLgAcdiy8LA&amp;t=17s&amp;ab_channel=Kurious"  title="le dualisme par Kurios"&gt; dualiste&lt;/a&gt; et de son interprétation originale de nombreuses croyances religieuses antérieures. Le manichéisme affirme l'existence de deux principes fondamentaux opposés : le bien et le mal, la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt;  Mani a écrit plusieurs ouvrages pour expliquer sa doctrine, y compris le Livre des fondements et le Livre des mystères. &lt;/p&gt; &lt;p&gt;  Malgré sa popularité à un moment donné, le manichéisme a fini par s'effacer au fil du temps, en grande partie en raison de la persécution de ses partisans par les différentes autorités religieuses et politiques.&lt;/p&gt; &lt;p&gt;  
+Mani lui-même a été emprisonné et exécuté pour hérésie par l'empereur sassanide Shapou en 277. Cependant, sa religion philosophique a continué à se propager pendant plusieurs siècles, en particulier en Asie centrale, en Chine et en Perse. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F54" s="7" t="s">
         <v>450</v>
@@ -8670,8 +8719,13 @@
       <c r="D57" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>474</v>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Asanga"  style="color:#6A142A"  title=" Wikipedia"&gt;ASANGA&lt;/a&gt; était un pilosophe bouddhiste de l'école Yogācāra qui joua un rôle clé dans le développement du  &lt;a href="https://www.youtube.com/watch?v=Uzy0byDxXi0" style="color:#88A1E9" title=" Sagesses Bouddhistes - Les tantras dans le bouddhisme tibétain par Inspiration "&gt;bouddhisme Mahāyāna&lt;/a&gt;. Il aurait médité pendant 12 ans dans une grotte, cherchant à rencontrer le futur  &lt;a href="https://www.youtube.com/watch?v=fI_nprPMGnA" style="color:#88A1E9" title=" Kalou Rinpotché. La rencontre d'Asanga et Maitrey par Michel Florelli "&gt;Bouddha Maitreya&lt;/a&gt;. Finalement, Maitreya lui serait apparu et lui aurait transmis des enseignements ésotériques, notamment les Cinq Traités de Maitreya, qui devinrent des textes fondateurs du Yogācāra dont il auait systématisé la doctrine qui se concentre sur : &lt;/p&gt; &lt;p&gt;-  L'idée que tout est conscience : Le monde extérieur n'existe pas indépendamment de l'esprit, il est une projection de la conscience. &lt;/p&gt; 
+ &lt;p&gt; - Les &lt;a href="https://www.youtube.com/watch?v=taPt15kuiX4" style="color:#88A1E9" title=" Sagesses Bouddhistes - Vajrayana : Les Cinq Sagesses par Inspiration Zen"&gt;huit consciences&lt;/a&gt; :  - Les cinq consciences sensorielles (vue, ouïe, etc.). - La conscience mentale. - La conscience souillée. - La conscience-base, une sorte de "réserve karmique" où sont stockées les impressions mentales. &lt;/p&gt; &lt;p&gt; - La théorie des trois natures : -  La nature imagée  : la perception illusoire du monde. - La nature dépendante : le flux causal des phénomènes mentaux. -  La nature parfaite  : la réalité ultime, libre de constructions mentales. &lt;/p&gt; &lt;p&gt; Il a écrit différentes oeuvres durant sa vie dont les plus importantes sont : &lt;/p&gt; &lt;p&gt; -  Le Mahāyāna-saṃgraha  – Un exposé systématique du Yogācāra. &lt;/p&gt; 
+&lt;p&gt; - Le Yogācārabhūmi-śāstra  – Un vaste manuel de pratique méditative et de philosophie. &lt;/p&gt; 
+&lt;p&gt; - Le Abhidharma-samuccaya  – Une synthèse &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1973_num_183_1_9962" style="color:#88A1E9" title=" Le compendium de la super-doctrine (philosophie) d'Asanga par Persée"&gt;des enseignements&lt;/a&gt; psychologiques bouddhistes.&lt;/p&gt; &lt;p&gt;  Penseur majeur dont les idées ont façonné la métaphysique, l'épistémologie et la pratique méditative du bouddhisme Mahāyāna, son héritage reste vivant dans les traditions bouddhistes d'Asie bien que le Yogācāra soit parfois comparé à l'idéalisme occidental. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F57" s="7" t="s">
         <v>475</v>
@@ -8804,8 +8858,10 @@
       <c r="D60" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>498</v>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sengzhao"   title=" Wikipedia"&gt;SENGZHAO&lt;/a&gt; était un philosophe chinois et l’un des penseurs qui ont le plus profondément articulé le dialogue entre bouddhisme, taoïsme et culture intellectuelle chinoise classique.  Souvent présenté comme l’un  &lt;a href="https://www.encyclopedia.com/environment/encyclopedias-almanacs-transcripts-and-maps/sengzhao"  title="SENGZHAO par encyclopedia.com "&gt;des fondateurs&lt;/a&gt; du bouddhisme “à la chinoise”, car il a su reformuler la pensée indienne de la Voie médiane (Mādhyamika) dans un langage sensible aux références taoïstes et confucéennes. &lt;/p&gt; &lt;p&gt; Disciple le plus brillant de Kumārajīva, il contribue à diffuser en Chine la notion de vacuité (śūnyatā) et la logique de la “voie du milieu”, évitant aussi bien l’affirmation d’un être substantiel que le nihilisme.  &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre est "le Zhaolun", recueil de courts traités philosophiques rédigés dans un style dense et allusif. Ses chapitres les plus connus portent des titres comme “Les choses ne se meuvent pas”, “La vacuité non absolue”, “La sagesse sans connaissance dichotomisante” et “Le nirvāṇa sans conceptualisation”, chacun déconstruisant des intuitions ordinaires sur le changement, l’être et le salut.  &lt;/p&gt; &lt;p&gt; Le cœur de sa pensée est une interprétation rigoureuse de la vacuité : tous les phénomènes (dharmas) sont dépourvus de nature propre, ce qui implique qu’aucun “être” ou “non‑être” substantiel ne peut être affirmé. &lt;a href="https://www.youtube.com/watch?v=iV3xtsSsI7M"  title="Tyler Neenan - Section 2 ISEAP 2021 Conference par International Society of East Asian Philosophy "&gt;Il critique &lt;/a&gt; ainsi les lectures chinoises trop simplistes qui réduisent le bouddhisme à l’“existence” ou à la “non‑existence”, et montre que la voie bouddhique consiste à dissoudre les oppositions conceptuelles plutôt qu’à choisir un côté. Pour lui, la vacuité n’est pas une théorie abstraite mais un outil de libération destiné à défaire les fabrications mentales et l’attachement au “moi”, condition de l’éveil. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F60" s="7" t="s">
         <v>499</v>
@@ -8888,8 +8944,15 @@
       <c r="D62" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>517</v>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdak"   title=" Wikipedia"&gt;MAZDAK&lt;/a&gt;,  principalement connue pour avoir fondé le mouvement religieux et social appelé mazdakisme au Ve siècle en Perse (actuel Iran). Ce mouvement a eu un impact significatif sur la société sassanide, en proposant des idées révolutionnaires en matière d'égalité sociale et de redistribution des richesses. &lt;/p&gt; &lt;p&gt; Le  &lt;a href="https://www.youtube.com/watch?v=g7mu4iR_Kyo" title="Histoire antique. Le mazdakisme, une hérésie communiste dans l'empire perse par La cité libre"&gt;mazdakisme&lt;/a&gt; est souvent considéré comme une forme de mouvement proto-socialiste ou égalitariste. Inspiré du zoroastrisme, la religion dominante en Perse, il a introduit des idées radicales qui remettaient en question l'ordre établi. Voici quelques aspects de sa doctrine : &lt;/p&gt;
+&lt;dd&gt; - Égalité sociale : Société où les richesses et les ressources seraient partagées équitablement entre tous les membres.  &lt;/dd&gt; 
+&lt;dd&gt; -   &lt;a href="https://www.youtube.com/watch?v=nwtJCcyLSHc" title="Mazdak The Communalist par Persian Bedtime Stories"&gt;Communauté des biens : &lt;/a&gt;  Biens matériels, y compris les terres et les richesses, devaient être mis en commun et partagés par tous.&lt;/dd&gt;
+&lt;dd&gt; - Égalité entre les sexes : Certaine forme d'égalité entre les hommes et les femmes, ce qui était rare à l'époque. &lt;/dd&gt;
+&lt;dd&gt; -  Non-violence : Accent sur la non-violence et la compassion envers autrui. &lt;/dd&gt; 
+&lt;dd&gt; - Réforme religieuse : Interprété les textes zoroastriens pour la justice sociale. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Mazdak a réussi à gagner le soutien du roi sassanide Kavadh I (règne de 488 à 531), qui a vu dans le mazdakisme un moyen d'affaiblir le pouvoir de l'aristocratie et du clergé. Cependant, cette alliance a été de courte durée. Le mouvement a été réprimé de manière violente par le fils de Kavadh I, Khosro I, qui a orchestré une purge contre les mazdakites après avoir pris le pouvoir. Mazdak et de nombreux de ses disciples ont été exécutés, et le mouvement a été largement éradiqué. &lt;/p&gt; &lt;p&gt; Il reste une référence importante dans l'histoire des idées sociales et religieuses et est souvent cité comme l'un des premiers exemples d'un mouvement cherchant à établir une société plus égalitaire. Certains historiens voient dans le mazdakisme un précurseur des mouvements socialistes modernes.&lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title=" Zoroastrisme, ainsi parlait le feu sacré par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10076-16.04.2024-ITEMA_23711987-2024C36128S0107-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F62" s="7" t="s">
         <v>518</v>
@@ -9059,8 +9122,13 @@
       <c r="D66" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>552</v>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jabir_ibn_Hayyan"    title=" Wikipedia"&gt;Jabir ibn HAYYAN&lt;/a&gt;, également connu sous le nom de Geber en Occident, est une figure majeure de l'histoire des sciences, en particulier dans les domaines de &lt;a href="https://www.youtube.com/watch?v=kyz45wAJEd4" title="De l'alchimie à la chimie : JABIR IBN HAYYAN par l'Histoire Oubliée"&gt;la chimie et de l'alchimie&lt;/a&gt;. Il est souvent considéré comme le "père de la chimie" en raison de ses contributions pionnières à cette discipline.  Il était d'origine persane et a vécu pendant l'âge d'or de la civilisation islamique. &lt;/p&gt; &lt;p&gt;Il a laissé une œuvre immense, avec des centaines de traités attribués à son nom.  &lt;a href="https://www.youtube.com/watch?v=AC68Ds1zEG4"  title="Les scientifiques musulman par AbuMuslimfr"&gt;Ses contributions&lt;/a&gt; couvrent plusieurs domaines, notamment la chimie, l'alchimie, la médecine, la philosophie et l'astronomie. Il  a introduit une approche systématique et expérimentale en chimie, insistant sur l'importance de l'expérimentation et de l'observation et a développé des techniques de laboratoire telles que la distillation, la cristallisation, la sublimation et la calcination. Il a adopté et développé la théorie des quatre éléments (terre, eau, air, feu) d'Aristote, mais il a également introduit la notion de "qualités" (chaud, froid, sec, humide) pour expliquer les transformations chimiques. &lt;/p&gt; &lt;p&gt;  Il a écrit plus de  &lt;a href="https://www.persee.fr/doc/pharm_0035-2349_1992_num_80_292_3264_t1_0102_0000_2" title="Inventaire et première étude des Oeuvres de Geber  par Persée"&gt;3 000 traités&lt;/a&gt;, bien que beaucoup aient été perdus ou attribués à tort. Parmi ses œuvres les plus célèbres figurent : &lt;/p&gt; 
+&lt;dd&gt; -  &lt;a href="https://www.persee.fr/doc/bcai_0259-7373_1989_num_6_1_908_t1_0195_0000_3" style="color:#88A1E9" title="Les dix premiers traités du Livre des Soixante-dixr  par Persée"&gt;Le Livre des Soixante-Dix&lt;/a&gt; : Un texte alchimique majeur. &lt;/dd&gt; 
+&lt;dd&gt; - Le Livre des Balances : Où il explore les relations entre les substances et leurs propriétés. &lt;/dd&gt; 
+&lt;dd&gt; - Le Livre des Pierres : Une étude sur les minéraux et leurs utilisations. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Ses travaux ont été traduits en latin au Moyen Âge et ont eu une influence profonde sur les alchimistes et scientifiques européens, notamment Albert le Grand et Roger Bacon. Il est devenu une figure légendaire dans le monde islamique et au-delà, symbolisant la quête de connaissance et la transformation de la matière. &lt;/p&gt; &lt;/p&gt;   &lt;audio controls title=" Ibn Khaldûn, itinéraire d'un penseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.03.2025-ITEMA_24045140-2025C26163E0007-ITE_00148375_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F66" s="7" t="s">
         <v>553</v>
@@ -9101,8 +9169,14 @@
       <c r="D67" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>560</v>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Alcuin"  title=" Wikipedia"&gt;ALCUIN&lt;/a&gt;  était un érudit et un éducateur anglais connu pour avoir été l'un des conseillers les plus proches de Charlemagne, le roi des Francs, qui a établi le Saint-Empire romain au IXe siècle. &lt;/p&gt; &lt;p&gt;
+En 781, il devient le chef de l'école du palais à Aix-la-Chapelle où il a supervisé l'éducation des enfants de &lt;a href="https://www.youtube.com/watch?v=yqIEe4nptPI&amp;ab_channel=PierrickAuger"  title="L'Empire carolingien par Pierrick Auger"&gt;  l'Empire Carolingien&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;
+Il était un érudit polyvalent qui maîtrisait plusieurs langues, notamment le latin, le grec et le hébreu. Il a écrit de nombreux ouvrages sur la grammaire, la rhétorique, la logique et la théologie, et a également compilé des manuels d'enseignement pour les écoles. &lt;/p&gt; &lt;p&gt;
+Sous son l'influence, Charlemagne a lancé une réforme éducative  en Europe qui visait à améliorer la qualité de l'enseignement et à étendre l'accès à l'éducation. Il a également participé à la réforme liturgique de Charlemagne, qui visait à standardiser les pratiques religieuses dans l'Empire. &lt;/p&gt; &lt;p&gt;
+Il est mort en 804, mais son influence sur l'éducation en Europe a perduré pendant des siècles. Il est aujourd'hui considéré comme l'un des érudits les plus importants de son époque, et son travail a eu un impact significatif sur l'histoire de l'Europe et de l'éducation. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F67" s="7" t="s">
         <v>561</v>
@@ -9401,8 +9475,10 @@
       <c r="D74" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>622</v>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Rhaz%C3%A8s"   title=" Wikipedia"&gt;AL-RAZI&lt;/a&gt; également connu sous le nom de Rhazes, était un médecin, philosophe et alchimiste persan qui a était influencé par la pensée grecque et la philosophie islamique. &lt;/p&gt; &lt;p&gt; Il a développé une approche originale de la philosophie avec une vision de l'éthique qui mettait l'accent sur la raison et la liberté. Parmi ses travaux philosophiques, on peut citer  &lt;a href="https://www.youtube.com/watch?v=4DRw8O29VBM"  title="Al Razi  par Oases of Wisdom"&gt;"Le livre de l'éthique"&lt;/a&gt;, dans lequel il discute de la nature de la vertu et de la moralité, et "Le livre de la prophétie", dans lequel il examine les concepts de prophétie et de révélation dans l'Islam. &lt;/p&gt; &lt;p&gt;  Il était également un critique de la philosophie aristotélicienne, qu'il considérait comme incompatible avec la théologie islamique. &lt;/p&gt; &lt;p&gt; En tant que médecin, il a développé une "philosophie de la médecine"  mettant l'accent sur l'importance de l'observation empirique et de la recherche scientifique pour comprendre les causes sous-jacentes des maladies plutôt que de se contenter de traiter les symptômes et que &lt;a href="https://www.youtube.com/watch?v=4DRw8O29VBM&amp;ab_channel=OasesofWisdom"  title="The Physician Philosopher par Oases of Wisdom"&gt; la médecine&lt;/a&gt; devait être fondée sur une solide compréhension de la nature humaine.  &lt;/p&gt; &lt;p&gt; Il a remis en question la nature de Dieu, affirmant que la raison humaine ne pouvait pas vraiment comprendre l'essence de l'Être suprême et a remis en question les idées sur la nature de l'univers car les théories traditionnelles sur la création et la fin de l'univers étaient insuffisantes. &lt;/p&gt; &lt;audio controls title="Santé de l'âme et santé du corps par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.04.2023-ITEMA_23357688-2023C48904E0005-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F74" s="7" t="s">
         <v>623</v>
@@ -9532,8 +9608,13 @@
       <c r="D77" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="E77" s="15" t="s">
-        <v>646</v>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Abhinavagupta"  title=" Wikipedia"&gt;ABHINAVAGUPTA&lt;/a&gt; était un philosophe, théologien et mystique indien de renom, qui a apporté des contributions importantes à plusieurs domaines, notamment le Shivaïsme cachemirien, l'esthétique indienne et la linguistique. Il a vécu et travaillé dans la région du Cachemire, qui était à l'époque un centre majeur de l'apprentissage et de la culture en Inde. &lt;/p&gt; &lt;p&gt;
+Sa philosophie était enracinée dans la tradition non dualiste du Shivaïsme cachemirien, qui affirme que toute la réalité est une expression de  &lt;a href="https://www.youtube.com/watch?v=vATdYXIBSnc&amp;t=321s&amp;ab_channel=AcharyaDrAmar"  title="Documentary Film par Acharya Dr Amar"&gt; la conscience divine&lt;/a&gt;. Il croyait que le but ultime de la vie humaine était de réaliser cette conscience divine ou  "la connaissance du Soi et d'atteindre la libération du cycle de la naissance et de la mort. Il a souligné l'importance de la pratique spirituelle et de la réalisation de soi, qu'il croyait pouvoir être atteintes grâce à une combinaison de méditation, de contemplation et de dévotion. &lt;/p&gt; &lt;p&gt;
+Son travail dans l'esthétique indienne, en particulier pour son commentaire sur le  &lt;a href="https://www.youtube.com/watch?v=fWto9etrwBU&amp;ab_channel=LakshmanjooAcademy"  style="color:#88A1E9"  title="Bhairava Strotra par Lakshmanjoo Academy "&gt; Natyashastra&lt;/a&gt;, un ancien texte sanskrit sur les arts du spectacle car il considérait l'art comme un moyen d'accéder au divin et croyait que l'expérience esthétique pouvait être un chemin vers la réalisation spirituelle. &lt;/p&gt; &lt;p&gt;
+Il a également apporté des contributions importantes à la linguistique et a développé une théorie du langage qui mettait l'accent sur le rôle de la métaphore et du symbole dans la communication, et il croyait que le langage était un moyen d'exprimer et d'accéder au divin.&lt;p&gt; </t>
+        </is>
       </c>
       <c r="F77" s="7" t="s">
         <v>647</v>
@@ -9618,8 +9699,11 @@
       <c r="D79" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="E79" s="21" t="s">
-        <v>663</v>
+      <c r="E79" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Al-B%C3%AEr%C3%BBn%C3%AE"  title="Wikipedia"&gt;AL-BĪRŪNĪ&lt;/a&gt; était  un érudit persan du haut Moyen Âge, né à Khwārazm (actuel Ouzbékistan) et mort vers à Ghazna (Afghanistan). Polygraphe exceptionnel, il maîtrise à la fois les mathématiques, l’astronomie, la géographie, l’histoire, la minéralogie et la pharmacologie, ce qui lui vaut d’être souvent appelé « le maître de l’an mille » dans l’histoire des sciences.  .&lt;/p&gt;&lt;p&gt; Il écrit près de 180 ouvrages, dont une trentaine nous sont parvenus. Il invente des méthodes très précises pour mesurer la circonférence de la Terre, calcule latitudes et longitudes, et rédige des traités comme Kitāb taḥdīd al‑amākin (« Détermination des lieux ») ou le vaste Al‑Qānūn al‑Masʿūdī, véritable encyclopédie de science de son temps. &lt;/p&gt; &lt;p&gt; &lt;p&gt;Iil apprend le sanscrit et rédige en arabe une somme extraordinaire sur la civilisation indienne : le &lt;em&gt;Kitāb al-Hind&lt;/em&gt; (Livre sur l'Inde). Pour la première fois dans l'histoire, un penseur islamique tente de comprendre une autre civilisation &lt;a href="https://www.youtube.com/watch?v=DgxH3SxjCG4&amp;ab_channel=YusufMutazila"  title="Savants de l'Islam par Yusuf Mutazila"&gt;de l'intérieur&lt;/a&gt;, sans condescendance ni prosélytisme.&lt;/p&gt;&lt;p&gt;Sa méthode — observer, comparer, suspendre le jugement — préfigure l'anthropologie scientifique. Ses travaux de géodésie (mesure du rayon de la Terre avec une précision remarquable), d'astronomie et de pharmacologie en font l'un des génies les plus polyvalents de l'humanité.&lt;/p&gt; &lt;p&gt; Sa pensée se nourrit à la fois des traditions grecque, persane, indienne et arabe, traduisant des textes sanskrits et intégrant leurs résultats dans ses propres travaux. Par cette synthèse, il devient un pivot entre les savoirs antiques et médiévaux, et ses ouvrages restent une source majeure pour l’histoire des sciences, de la géographie et de la pensée indienne. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F79" s="7" t="s">
         <v>664</v>
@@ -9660,8 +9744,12 @@
       <c r="D80" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="E80" s="15" t="s">
-        <v>671</v>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Avicenne" title=" Wikipedia"&gt;AVICENNE&lt;/a&gt;, dit &lt;a  href="https://www.youtube.com/watch?v=OXBM6F0jNlY&amp;ab_channel=UnevieUne%C5%93uvre" style="color:#88A1E9"  title="Le prince des savants par Une Vie Une oeuvre"&gt;"le prince des savants"&lt;/a&gt;, était un philosophe et médecin Persan né en Iran. &lt;/p&gt; &lt;p&gt; Fin lettré, il fut le traducteur des œuvres d'Hippocrate et de Galien et porta un soin particulier à l'étude d'Aristote. Il s'inscrit dans un mouvement général qui voit les philosophes de culture islamique découvrir la culture grecque auprès de l'Empire Byzantin. Il a a cherché à résoudre le problème de la relation entre l'âme et le corps, ainsi que la question de la nature de l'existence. Il a proposé une théorie de la connaissance qui reposait sur la raison et l'intellect, ainsi qu'une théorie de l'être qui distinguait entre l'essence et l'existence. &lt;/p&gt; &lt;p&gt; 
+L'une de ses contributions les plus importantes à la philosophie a été son travail sur la métaphysique. Il a proposé une théorie de l'être qui distinguait entre l'essence et l'existence, a influencé de nombreux penseurs ultérieurs, y compris Thomas d'Aquin. &lt;/p&gt; &lt;p&gt; 
+En médecine, Avicenne a écrit l'un des traités les plus influents de l'histoire de la médecine, le &lt;a  href="https://memoirevive.besancon.fr/editorial/page/befd8f43-8321-4ae6-ba5b-47f957fc51f0" title="Le canon de la médecine par Mémoire Vive"&gt;"Canon de la médecine"&lt;/a&gt;, qui a été largement utilisé dans les universités européennes jusqu'au XVIIe siècle. Il a également apporté des contributions importantes à la science, à la logique et à la théologie.&lt;/p&gt;  &lt;audio controls title="Philosophe et Islam: Avicenne, penseur de l'âme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/03/s10/Les_nouveaux_chemins_de_la_connaissance--France_Culture_1--NET_bf47a03e-ec3a-4fa5-9eee-dcacb85045ae_DF.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F80" s="7" t="s">
         <v>672</v>
@@ -9749,8 +9837,10 @@
       <c r="D82" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="E82" s="18" t="s">
-        <v>687</v>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zhang_Zai" title="Wikipedia"&gt;ZHANG Zai&lt;/a&gt; était un    philosophe néo-confucéen chinois de la dynastie Song, né dans une famille de lettrés à Kaifeng (Henan). Après des études initiales du bouddhisme et du taoïsme qui le déçoivent, il se tourne vers les classiques confucéens sous l'influence de Fan Zhongyan, passant les examens impériaux en 1050. Il occupe des postes administratifs modestes, enseigne à l'Académie du Grand Ultime qu'il fonde près de son village natal Hengqu, et forme ses neveux Cheng Hao et Cheng Yi, futurs piliers du néo-confucianisme. Sa vie mêle érudition, engagement politique réformiste et méditation cosmologique, jusqu'à sa mort prématurée d'une maladie.  &lt;/p&gt; &lt;p&gt; Au cœur de sa philosophie trône le qi (énergie vitale ou souffle cosmique), principe ontologique unique et omniprésent formant toute réalité :  &lt;a href="https://www.persee.fr/doc/etchi_0755-5857_2014_num_33_2_1521" title="nature et destin dans la pensée Zhang Zai par Persée"&gt;minéraux, plantes, &lt;/a&gt; humains, Ciel et Terre ne sont que condensations ou dispersions de ce qi en perpétuel mouvement. Contrairement au bouddhisme et au taoïsme qu'il critique pour leur vide, il affirme la réalité substantielle du monde, où être et non-être, intégration et désintégration s'unissent dans le changement (yi) inspiré du Yijing (Livre des mutations). Son œuvre majeure,   &lt;a href="https://www.persee.fr/doc/oroc_0754-5010_2004_num_26_26_1213" title=" pensée dans Zhengmeng Zhang Zai par Persée"&gt;Zhengmeng  &lt;/a&gt; (Correction de la jeunesse), expose cette cosmologie matérialiste moniste, complétée par l'essai Ximing (Inscription à l'Ouest). &lt;p&gt;  Dans Ximing, Zhang Zai proclame quatre buts ontologiques pour l'intellectuel : manifester l'esprit du Ciel et de la Terre, assurer le bien-être du peuple, raviver l'héritage des sages antiques, ouvrir la grande paix éternelle. Il étend la ren (bienveillance humaine) à l'univers entier, enseignant que le sage « forme un corps avec l'Univers » (tianren heyi), percevant l'interconnexion de tout qi et cultivant une piété cosmique confucéenne. Cette vision éthique universelle valorise la bonté innée de la nature humaine et du cosmos, opposée à l'évasion bouddhiste ou taoïste.  &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F82" s="7" t="s">
         <v>688</v>
@@ -9835,8 +9925,11 @@
       <c r="D84" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="E84" s="15" t="s">
-        <v>704</v>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Al-Ghazali" title=" Wikipedia"&gt; Al-GHAZALI&lt;/a&gt;, également connu sous le nom d'Algazel, était un philosophe et théologien musulman persan considéré comme l'un des plus &lt;a href="https://www.lescahiersdelislam.fr/AL-GHAZALI-1058-1111-sa-vie-sa-pensee-philosophique-et-religieuse-1ere-partie_a546.html" title="Al Ghazali par Les cahiers de l'Islam"&gt; grands penseurs&lt;/a&gt;  de l'islam médiéval et a eu une grande influence sur la théologie et la philosophie musulmane.&lt;/p&gt; &lt;p&gt;
+Al-Ghazali a étudié la théologie et la philosophie dans sa jeunesse, mais il a connu une crise spirituelle à l'âge adulte qui l'a poussé à remettre en question ses croyances et à chercher une compréhension plus profonde de l'islam. Il a finalement abandonné sa carrière académique et est devenu  &lt;a href="https://www.youtube.com/watch?v=YmRoIwv2jkE&amp;t=429s&amp;ab_channel=RappelSunnah"  title="Le Soufisme en Islam par Rappel Sunnah"&gt; un soufi&lt;/a&gt;, se consacrant à la méditation, à la prière et à la recherche de la vérité spirituelle.&lt;/p&gt; &lt;p&gt; Dans ses écrits, il a cherché à réconcilier les enseignements de la philosophie grecque avec ceux de l'islam. Il a critiqué les philosophes qui accordaient trop d'importance à la raison et à la logique, arguant que la foi et la révélation étaient les véritables sources de connaissance. Il a également critiqué les théologiens qui interprétaient la doctrine islamique de manière trop littérale et étroite.&lt;/p&gt; &lt;p&gt; L'œuvre la plus célèbre d'Al-Ghazali est  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1988_num_86_69_6490_t1_0117_0000_2"   title="Le tabernacle des lumières par Persée.fr"&gt; "Le tabernacle des lumières"&lt;/a&gt;, dans lequel il explore la nature de la connaissance et de la foi. Il y soutient que la véritable connaissance ne peut être atteinte que par la grâce divine, et non par la raison ou la logique seules. Il y décrit également les étapes de la voie spirituelle qui mène à la connaissance de Dieu. &lt;/p&gt;&lt;audio controls title="Al-Ghazali par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-05.11.2017-ITEMA_21485088-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F84" s="7" t="s">
         <v>705</v>
@@ -9922,8 +10015,10 @@
       <c r="D86" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="E86" s="8" t="s">
-        <v>721</v>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Ibn_Tufayl"  title=" Wikipedia"&gt; Ibn TUFAYL&lt;/a&gt; était un philosophe autodidacte andalou mais également un médecin, un poète et un administrateur au service de la cour de Grenade, en Espagne.&lt;/p&gt; &lt;p&gt; Il est connu pour son roman philosophique, intitulé  &lt;a href="https://www.youtube.com/watch?v=pW2IoZwrrAE&amp;ab_channel=Camouline"  title="Hayy Ibn Yaqdhan par Camouline "&gt;"Hayy ibn Yaqdhan" &lt;/a&gt; (Vivant, fils de l'éveillé), où il explore les questions philosophiques fondamentales, telles que la nature de la réalité, la connaissance de soi et la relation entre l'homme et Dieu. C'est un traité philosophique et mystique, qui s'appuie sur la pensée d'Avicenne et  &lt;a href="https://www.youtube.com/watch?v=rJLqqp7vsQY&amp;ab_channel=LeCourrierdel%27Atlas"   title="Le soufisme, voie mystique de l'Islam par Le courrier de l'Atlas "&gt; le soufisme&lt;/a&gt;, sous forme de roman allégorique. &lt;/p&gt; &lt;p&gt; Le livre est également fortement ancré dans la pensée néoplatonicienne et aristotélicienne. L'histoire suit le personnage principal, Hayy, un enfant sauvage qui grandit seul sur une île déserte et apprend à découvrir le monde naturel et la vérité à travers l'observation et la réflexion.   Au fil du temps, Hayy atteint un état de connaissance et de sagesse profonde, qui l'amène à comprendre la nature de Dieu et de l'univers.  &lt;/p&gt; &lt;p&gt; Sa philosophie repose sur l'idée que la connaissance de soi et la connaissance de Dieu sont étroitement liées. Il considère que l'expérience directe de la nature et la réflexion personnelle sont essentielles pour parvenir à une compréhension profonde de la vérité. &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F86" s="7" t="s">
         <v>722</v>
@@ -10140,8 +10235,13 @@
       <c r="D91" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="E91" s="8" t="s">
-        <v>762</v>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_Ma%C3%AFmonide"   title=" Wikipedia"&gt; Moïse MAÏMONIDE&lt;/a&gt; était un éminent philosophe, médecin et érudit juif  considéré comme l'une des figures les plus importantes de la pensée juive médiévale et l'un des philosophes les plus influents de tous les temps. &lt;/p&gt; &lt;p&gt;
+Il est connu pour son travail en philosophie et en droit juif. Son œuvre la plus célèbre est le &lt;a href="http://www.theologica.fr/!_Pg_Courants&amp;ContresCourants/MAIMONIDE/LE%20GUIDE%20DES%20EGARES%20TOME%201.pdf"  title="Le guide des égarés par Theologica "&gt;"Guide des égarés" &lt;/a&gt; (Moreh Nevukhim en hébreu), qui est une exploration de la philosophie religieuse juive. Dans ce livre, il tente de concilier la philosophie aristotélicienne avec les enseignements de la religion juive. Il aborde des sujets tels que la nature de Dieu, la création du monde, la providence divine, la libre volonté et l'interprétation des textes sacrés. &lt;/p&gt; &lt;p&gt; Il a également rédigé un code de lois juives appelé &lt;a href="https://www.youtube.com/watch?v=kJH75lzA2BY"  title="la pensée du Ramban : le Mishné Torah par Ayeka France "&gt;"Mishné Torah" &lt;/a&gt; qui couvre tous les aspects de la vie juive, il a été conçu pour être une référence complète et accessible aux personnes ordinaires. Il a grandement influencé le développement ultérieur du droit juif et est encore étudié et consulté de nos jours. &lt;/p&gt; &lt;p&gt;Il était aussi un médecin renommé et a écrit plusieurs ouvrages médicaux, dont le &lt;a href="https://www.biusante.parisdescartes.fr/sfhm/hsm/HSMx2006x040x001/HSMx2006x040x001x0073.pdf"   title="La formation médicale de Maïmonide par Jérôme TALMUD "&gt;"Traité des poisons et des antidotes"&lt;/a&gt;, et a servi comme médecin de cour pour le sultan d'Égypte. &lt;/p&gt; &lt;p&gt;
+Maïmonide a laissé un héritage durable dans le monde de la pensée juive et de la philosophie en général. Ses idées ont influencé des penseurs juifs ultérieurs tels que Baruch Spinoza et ont également été étudiées et discutées par des penseurs non-juifs. Sa capacité à combiner la philosophie grecque et la théologie juive a ouvert de nouvelles perspectives sur la relation entre la raison et la foi, et continue d'être une source d'inspiration et de débat pour de nombreux intellectuels. &lt;/p&gt;   
+</t>
+        </is>
       </c>
       <c r="F91" s="7" t="s">
         <v>763</v>
@@ -10188,8 +10288,11 @@
       <c r="D92" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="E92" s="8" t="s">
-        <v>771</v>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shihab_al-Din_Sohrawardi"  title=" Wikipedia"&gt;Shihab SOHRAWARDI&lt;/a&gt; était un philosophe perse issus du courant oriental de la sagesse illuminative "Ishraq", une tentative audacieuse de fusionner la tradition philosophique grecque ( platonisme et l'aristotélisme revisité), la sagesse de l'ancienne Perse (zoroastrisme) et la mystique islamique (soufisme). Au cœur de sa pensée se trouve la métaphysique de la Lumière. &lt;/p&gt; &lt;p&gt; -  La Lumière des Lumières : La réalité ultime et la source de toute existence est la Lumière des Lumières, qui est Dieu. Tout ce qui existe émane de cette Lumière primordiale par un processus d'illumination et de rayonnement. &lt;/p&gt; &lt;p&gt; -  Hiérarchie des Lumières: L'univers est constitué d'une hiérarchie de lumières, allant de la Lumière des Lumières aux lumières intellectuelles, puis aux lumières astrales et enfin aux lumières qui gouvernent le monde sublunaire. Les ténèbres ne sont pas une réalité en soi, mais une absence ou une privation de lumière. &lt;/p&gt; &lt;p&gt; -  Critique de la &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_p%C3%A9ripat%C3%A9ticienne" style="color:#88A1E9" title=" ecole péripatéticienne  par Wikipedia"&gt;philosophie péripatéticienne&lt;/a&gt; : Bien que formé à celle ci, il en critique certains aspects, notamment la théorie de la connaissance par abstraction. Il privilégie une connaissance directe et intuitive. &lt;/p&gt; &lt;p&gt; -  La connaissance par Présence et Illumination: La véritable connaissance n'est pas simplement discursive ou rationnelle, mais une "connaissance par présence", une intuition directe et une  &lt;a href="https://www.youtube.com/watch?v=00ziXcrWTIc" style="color:#88A1E9" title=" Le malakût de Sohrawardi, un monde intermédiaire par BAGLIS TV"&gt; illumination intérieure&lt;/a&gt;. L'âme humaine, en se purifiant, peut s'ouvrir à cette illumination et contempler les réalités spirituelles. &lt;/p&gt; &lt;p&gt; -  Le Monde Imaginal : Son concept clé est celui du "monde imaginal". C'est un monde intermédiaire entre le monde sensible et le monde purement intelligible. C'est le lieu des visions prophétiques, des songes véridiques, des événements eschatologiques et des corps subtils. Ce monde a sa propre réalité objective et n'est pas une simple fantaisie subjective. &lt;/p&gt; &lt;p&gt; -  Sagesse Orientale : il se voyait comme le rénovateur d'une sagesse antique et universelle qu'il appelait la  &lt;a href="https://www.youtube.com/watch?v=i1USCLFD9QQ" style="color:#88A1E9" title="
+Shihab od-Din Yahya Sohrawardi, Le livre de la Sagesse Orientale par LaMecaniqueUniverselle"&gt; "Sagesse Orientale"&lt;/a&gt;. Il y intégrait les enseignements des sages de l'ancienne Perse aux côtés des philosophes grecs comme Platon et des figures spirituelles de l'islam. &lt;/p&gt; &lt;p&gt; Sa vie fut courte et intense, se terminant tragiquement par son &lt;a href="https://www.persee.fr/doc/efr_0223-5099_1995_act_213_1_4948" style="color:#88A1E9" title=" Hérésie et pouvoir politique en Syrie au XIIe siècle : l'exécution d'al-Suhrawardï  par Persée"&gt;exécution à Alep&lt;/a&gt;  en 1191, sur ordre de Saladin, en raison de ses enseignements jugés hétérodoxes par certains oulémas. Cette fin lui valut le surnom de "Shaykh Maqtul" (le Maître Assassiné). &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F92" s="7" t="s">
         <v>772</v>
@@ -10411,8 +10514,14 @@
       <c r="D97" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="E97" s="15" t="s">
-        <v>813</v>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/R%C3%BBm%C3%AE"  title=" Wikipedia"&gt; Djalâl AD-DÎN RUMÎ&lt;/a&gt; était un poète et philosophe mystique persan considéré comme l'un des plus grands poètes soufis et une figure centrale du &lt;a href="https://www.youtube.com/watch?v=rJLqqp7vsQY&amp;ab_channel=LeCourrierdel%27Atlas" title="Le soufisme, voie mystique de l'Islam par Le Courrier de l'Atlas "&gt;soufisme&lt;/a&gt;, une dimension mystique de l'islam. &lt;/p&gt; &lt;p&gt;
+Rûmî est né à Balkh, dans ce qui est aujourd'hui l'Afghanistan, et a vécu la majeure partie de sa vie à Konya, en Anatolie (aujourd'hui la Turquie). Il est connu sous le nom de Rûmî en raison de son lien étroit avec la ville de Rum, l'ancien nom de la région. &lt;/p&gt; &lt;p&gt;
+Sa vie a été profondément transformée par sa rencontre avec le mystique errant Shams Tabrizi. Leur relation a été marquée par une profonde amitié et un lien spirituel intense. Shams Tabrizi a joué un rôle essentiel dans l'éveil mystique de Rûmî, l'amenant à transcender les limites de la pensée rationnelle et à embrasser l'amour divin de manière intense. &lt;/p&gt; &lt;p&gt;
+L'œuvre la plus célèbre de Rûmî est le &lt;a href="https://consciencesoufie.com/cles-de-lecture-pour-entrer-dans-le-mathnawi-de-rumi/" title="Clé de lecture pour entrer dans le Mathnawi de Rümî par Conscience Soufie "&gt;"Mathnawi"&lt;/a&gt;, un recueil de poèmes mystiques rédigés en persan. Cette œuvre monumentale comprend environ 26 000 vers répartis en six volumes. Le "Mathnawi" explore une grande variété de thèmes, allant de l'amour divin à la recherche de la vérité, en passant par l'abandon de soi et la réalisation de l'union avec Dieu. Les poèmes de Rûmî sont caractérisés par leur langage poétique riche, leurs métaphores envoûtantes et leur expression intense de l'amour spirituel. &lt;/p&gt; &lt;p&gt;
+Un autre aspect important de la philosophie de Rûmî est sa conception de l'amour. Pour lui, l'amour était un moyen d'atteindre l'union avec Dieu et une force motrice capable de transcender les différences et de favoriser l'harmonie et l'unité entre les êtres humains. Son concept de l'amour divin était profondément inclusif et allait au-delà des barrières religieuses et culturelles. &lt;/p&gt;                                    &lt;audio controls title="La doctrine soufie de Rûmî par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-15.12.2019-ITEMA_22230288-0.mp3"  type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
+        </is>
       </c>
       <c r="F97" s="7" t="s">
         <v>814</v>
@@ -10696,8 +10805,10 @@
       <c r="D103" s="9" t="s">
         <v>852</v>
       </c>
-      <c r="E103" s="8" t="s">
-        <v>853</v>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Manuel_Chrysoloras"  style="color:#6A142A"  title=" Wikipedia"&gt;Manuel CHRYSOLORAS&lt;/a&gt; était un philosophe et &lt;a href="https://www.persee.fr/doc/reg_0035-2039_1891_num_4_14_5507" style="color:#88A1E9" title=" Un portrait de Manuel Ghrysoloras. Conservé au musée du Louvre par Persée"&gt;humaniste bizantin&lt;/a&gt; et  l'un des introducteurs de la culture grecque en Italie au début de la Renaissance. Né à Constantinople, il appartenait à une famille  &lt;a href="https://www.youtube.com/watch?v=2OUtiOPO6Bw" style="color:#88A1E9" title="Byzantine Influence on Italian Renaissance par For Art's Sake"&gt;noble byzantine&lt;/a&gt;. Il étudia la philosophie, la rhétorique et la théologie dans le monde grec orthodoxe. Invité à enseigner le grec à Florence à partir de 1397, il forma une génération d’humanistes italiens, dont Leonardo Bruni et Guarino da Verona. &lt;/p&gt; &lt;p&gt;  Son enseignement marqua un tournant dans la redécouverte des textes grecs en Occident. Il  fut un pionnier dans l’enseignement du grec ancien en Occident, permettant la traduction d’œuvres majeures de Platon, Aristote, Homère et d’autres auteurs.&lt;/p&gt; &lt;p&gt;  Il écrivit &lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1994_num_48_1_1687" style="color:#88A1E9" title="Bartholomeo Aragazzi et Manuel Chrysoloras : le codex Vratislav par Persée"&gt;"Erotemata"&lt;/a&gt;, le premier manuel de grammaire grecque pour Latins, structuré sous forme de questions-réponses et il défendait l’idée que la maîtrise du grec était essentielle pour accéder à la sagesse antique et aux textes chrétiens originaux. &lt;/p&gt; &lt;p&gt; Il fut une figure-clé du mouvement humaniste, facilitant la fusion des savoirs grecs et latins. Ses élèves diffusèrent ses méthodes, contribuant à l’essor de la Renaissance. Son travail prépara aussi bien la réception de Platon (via Pléthon et Marsile Ficin) que les débats philologiques des siècles suivants. &lt;/p&gt; </t>
+        </is>
       </c>
       <c r="F103" s="7" t="s">
         <v>854</v>
@@ -10868,8 +10979,15 @@
       <c r="D107" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="E107" s="15" t="s">
-        <v>889</v>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kab%C3%AEr"  style="color:#6A142A"  title=" Wikipedia"&gt;KABIR&lt;/a&gt;  était un mystique et philosophe indien. Il est considéré comme l'une des figures les plus importantes de la tradition mystique indienne et est souvent associé au mouvement &lt;a href="https://fr.hdasianart.com/blogs/news/the-importance-of-bhakti-in-hinduism" style="color:#88A1E9" title="L'importance du Bhakti par Asian Art"&gt;Bhakti&lt;/a&gt;, qui prône une dévotion personnelle et intime à Dieu, transcendant les rituels formels et les distinctions sociales. &lt;/p&gt; &lt;p&gt; Né dans une famille de tisserands musulmans, il a été profondément influencé par les enseignements hindous, en particulier ceux de Ramananda, un saint de la tradition Bhakti. Cette double influence se reflète dans ses écrits, où il synthétise des éléments des deux traditions tout en critiquant leurs aspects ritualistes et dogmatiques. &lt;/p&gt; &lt;p&gt; Il est surtout connu pour ses poèmes et ses chants, qui expriment une spiritualité profondément personnelle et universelle et qui peuvent être résumés autour de plusieurs thèmes clés : &lt;/p&gt;
+&lt;dd&gt;- L'unité de Dieu : Il insiste sur l'unicité de Dieu, qu'il appelle par différents noms, tels que Ram, Allah, Hari ou Khuda. Il rejette les divisions sectaires entre hindous et musulmans, affirmant que Dieu est au-delà des religions et des formes.&lt;/dd&gt;
+&lt;dd&gt; - La critique des rituels et des institutions religieuses : Il dénonce les pratiques ritualistes, les pèlerinages, les sacrifices et les observances extérieures. Il critique également les prêtres, les gourous et les autorités religieuses qui exploitent la foi des gens.&lt;/dd&gt;
+&lt;dd&gt; - La dévotion intérieure (Bhakti) : La véritable dévotion consiste en une relation directe et intime avec Dieu, sans intermédiaires, par une spiritualité basée sur l'amour, la simplicité et la sincérité du cœur.&lt;/dd&gt;
+&lt;dd&gt;  - La recherche de la vérité intérieure : Chercher la vérité en soit-même plutôt que dans les textes sacrés ou les enseignements externes. &lt;/dd&gt;
+&lt;dd&gt; -  L'égalité sociale : Il rejette le système des castes et prône l'égalité de tous les êtres humains devant Dieu, de toutes les couches sociales, des plus humbles aux plus élevées, et insiste sur l'importance de l'humilité et de la compassion. &lt;/dd&gt;  &lt;p&gt; Ses  &lt;a href="https://fr.wikisource.org/wiki/Po%C3%A8mes_de_Kabir"  title="poemes de Kabir par Wikisource"&gt;poèmes&lt;/a&gt;, appelés "dohas" ou "couplets", sont écrits dans une langue simple et directe, souvent en hindi vernaculaire mélangé à des éléments de persan et d'arabe. Ses vers sont riches en métaphores et en paradoxes, invitant le lecteur à réfléchir profondément sur la nature de la réalité et de la spiritualité. Par exemple, il compare souvent l'âme à une abeille cherchant le nectar de la vérité, ou à un oiseau migrateur cherchant à retourner à sa maison divine. &lt;/p&gt;  </t>
+        </is>
       </c>
       <c r="F107" s="7" t="s">
         <v>890</v>
@@ -11198,8 +11316,10 @@
       <c r="K114" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="L114" s="2" t="s">
-        <v>952</v>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rationalisme</t>
+        </is>
       </c>
       <c r="M114" s="2" t="s">
         <v>953</v>
@@ -11818,8 +11938,11 @@
       <c r="D129" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="E129" s="13" t="s">
-        <v>1065</v>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Rabindranath_Tagore"  title=" Wikipedia"&gt;Rabindranath TAGORE&lt;/a&gt; était un poète, romancier, dramaturge, philosophe et compositeur bangladais  &lt;a href="https://www.youtube.com/watch?v=q7c6zqn4L8g"  title="National Anthem Tagore’s Own Voice par Gingerline Media"&gt;d'expression bengalie et anglaise, &lt;/a&gt; devenu le premier non-Européen à recevoir le prix Nobel de littérature en 1913.  Né à Calcutta (Inde) dans une famille de lettrés, &lt;a href="https://agora.qc.ca/dossiers/rabindranath_tagore"  title="Tagore par Agora"&gt; philosophes et artistes, &lt;/a&gt;  il est le plus jeune fils de &lt;a href="https://fr.wikipedia.org/wiki/Debendranath_Tagore"  title=" Debendranath Tagore par wikipedia"&gt; Debendranath Tagore&lt;/a&gt;, un éminent philosophe et réformateur religieux leader du Brahmo Samaj, une nouvelle secte religieuse du Bengale qui tentait de rétablir le monisme ultime de l'hindouisme tel que décrit dans les Upanishads.. Il se rend en Occident vers 1880, renonçant à tout pour « mieux aimer la nature et Dieu ». &lt;/p&gt; &lt;p&gt; Entre 1901 et 1918, il traverse d'immenses souffrances : sa femme, trois de ses enfants et son père meurent successivement. Malgré cela, il transforme sa douleur en création et fonde un centre d'éducation international à Shantiniketan (près de Calcutta) où il applique ses idéaux éducatifs inspirés des Upanishads. Ce centre devient Visva-Bharati University, un lieu dynamique qui rayonne sur toute la région puis sur toute l'Inde. &lt;/p&gt; &lt;p&gt; Il  est avant tout poète et a écrit plus de 50 volumes de poésie, dont les plus célèbres sont Manasi (1890), Sonar Tari (1894) [Le Navire d'or], Gitanjali (1910) [Offrande lyrique], Gitimalya (1914) et Balaka (1916). C'est Gitanjali, traduit en anglais par lui-même en 1912, qui le rend  &lt;a href="https://www.youtube.com/watch?v=v3iix5GSB2I"  title=" Drabindranath TAGORE par Eclair Brut"&gt; mondialement célèbre &lt;/a&gt; et lui vaut le Nobel. Le prix lui est décerné « pour ses vers profondément sensibles, frais et beaux, par lesquels, avec une maîtrise consommée, il a fait de sa pensée poétique, exprimée en ses propres mots anglais, une partie de la littérature occidentale ». &lt;/p&gt; &lt;p&gt; Il est un philosophe humaniste dont la pensée s'enracine dans  &lt;a href="https://www.youtube.com/watch?v=S3HO9PeoqP0"  title="Les Upanishads par Resumons ça"&gt;les Upanishads &lt;/a&gt; et la recherche de l'Absolu comme « unique réalité de la vie ». Il participe ponctuellement au mouvement nationaliste indien, mais de manière « non sentimentale et visionnaire », et entretient une amitié avec Gandhi, qu'il considère comme le père politique de l'Inde moderne. Il rejette le nationalisme étroit et prône un universalisme spirituel, devenant « la voix de l'héritage spirituel de l'Inde » pour le monde. &lt;/p&gt; 
+                               &lt;audio controls title="Rabindranath TAGORE  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10471-11.02.2012-ITEMA_20344077-2012C3330E0006-ITE_00049084_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F129" s="1" t="s">
         <v>1066</v>
@@ -12118,8 +12241,14 @@
       <c r="D135" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>1098</v>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Aurobindo_Ghose"  title=" Wikipedia"&gt;AUROBINDO Ghose&lt;/a&gt; ou Sri AUROBINDO était un philosophe, poète, yogi et leader nationaliste indien, il a développé une vision intégrale de l'évolution humaine et de la transformation spirituelle.  &lt;a href="https://www.sriaurobindoashram.org/sriaurobindo/translations.php"  title="Sri Aurobindo par sriaurobind"&gt;Son œuvre&lt;/a&gt; englobe la métaphysique, la politique, la littérature et la pratique spirituelle. Il apprend le sanskrit, étudie les textes sacrés comme les Védas, les Upanishads et la Bhagavad Gita, et s'immerge dans la pratique du yoga. &lt;/p&gt; &lt;p&gt; Il  s'engage activement dans le mouvement pour l'indépendance de l'Inde et devient l'un des leaders les plus radicaux du Congrès national indien. Il édite des journaux comme Bande Mataram, qui deviennent des voix puissantes pour la cause nationaliste. Il est arrêté par les Britanniques pour son implication présumée dans une conspiration révolutionnaire. Emprisonné pendant un an, il vit une transformation spirituelle profonde pendant sa détention. &lt;/p&gt; &lt;p&gt; Après sa libération, il se consacre entièrement à la pratique spirituelle et propose une &lt;a href="https://www.youtube.com/watch?v=O9SlbbkCP3c&amp;pp=ygUNU3JpIEFVUk9CSU5ETw%3D%3D" title="Sri Aurobindo ou l'aventure de la conscience par Mes livres audio"&gt;vision unique&lt;/a&gt; de l'évolution humaine et de la transformation spirituelle. Selon lui, l'évolution n'est pas terminée ; l'humanité est en train de passer à un nouveau stade de conscience, qu'il appelle la "supermind" ou "conscience supramentale". Cette conscience apportera une unité divine et une harmonie parfaite entre l'esprit et la matière. &lt;/p&gt; &lt;p&gt; Il  a laissé une vaste littérature spirituelle et philosophique. Parmi ses œuvres les plus importantes : &lt;/p&gt; 
+&lt;dd&gt; -  &lt;a href="https://www.youtube.com/watch?v=IZfzmfzAwDA&amp;list=PLOSVK2Agyv7kDNyM5OUg8aszuilSeeza_" title="L'homme et l'évolution par BB AV"&gt;La Vie Divine&lt;/a&gt; : Exploration approfondie de l'évolution et de la transformation spirituelle. &lt;/dd&gt; 
+&lt;dd&gt; -  &lt;a href="https://blog.green-yoga.fr/sri-aurobindo-activiste-maitre-yogi-inspirateur-auroville/"  title="Sri Aurobindo : activiste, maître yogi et inspirateur d’Auroville par blog-green-yoga"&gt;La Synthèse des Yoga&lt;/a&gt; : Analyse des différentes voies du yoga et leur intégration. &lt;/dd&gt; 
+&lt;dd&gt; - Savitri : Thèmes de la destinée humaine, de la mort et de la réalisation spirituelle. &lt;/dd&gt; 
+&lt;dd&gt; - Essais sur la Gita : Une interprétation profonde de la Bhagavad Gita. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il incarne une synthèse unique entre la sagesse ancienne de l'Inde et les aspirations modernes de l'humanité. Son œuvre reste une source inépuisable d'inspiration pour ceux qui cherchent à comprendre et à transformer leur vie intérieure et extérieure. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F135" s="1" t="s">
         <v>1099</v>
@@ -13259,8 +13388,11 @@
       <c r="D159" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="E159" s="20" t="s">
-        <v>1237</v>
+      <c r="E159" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sophie_Oluwole"  title=" Wikipedia"&gt;Sophie OLUWOLE&lt;/a&gt;  était une philosophe nigériane, considérée comme la première femme nigériane à obtenir un doctorat en philosophie dans une université de son pays. Elle a consacré sa vie à montrer que l’Afrique produit une &lt;a href="https://theconversation.com/sophie-oluwole-la-pionniere-nigeriane-qui-a-redefini-la-philosophie-278158" title="Sophie oluwole : la pionnière nigérienne qui a redefini la philosophie par conversation"&gt;pensée philosophique &lt;/a&gt; rigoureuse, ancrée dans ses traditions orales et notamment dans la culture iorubá. Professeure à l’Université d’Ibadan, elle s’est imposée comme une figure majeure de la philosophie africaine contemporaine et une pionnière pour les femmes dans ce domaine. &lt;/p&gt; &lt;p&gt; Elle  se définit comme une « traditionnaliste critique » : elle valorise les sages‑i oraux africains, mais les analyse avec les outils de la raison philosophique moderne. Elle accorde une grande importance à Ifá, le système de sagesse iorubá autour du sage Orunmila, qu’elle considère comme un véritable système philosophique structuré, et non seulement comme une religion ou une superstition. Pour elle, la philosophie n’est pas réservée à ceux qui savent lire et écrire ; la tradition orale africaine abrite une rationalité et une logique comparables à celles des traditions grecques classiques, &lt;/p&gt; &lt;p&gt; Un de ses travaux les plus célèbres est la comparaison entre Socrate et Orunmila, qu’elle présente comme deux « saints‑patrons » de la philosophie, l’un occidental et l’autre africain. Elle montre que tant Socrate que le sage iorubá pratiquent un questionnement critique, une recherche de la vérité et un souci de l’éthique personnelle, ce qui détruit l’idée eurocentrée selon laquelle la philosophie est une invention exclusive de la Grèce antique. Cette démarche vise à décoloniser la &lt;a href="https://www.youtube.com/watch?v=5b-54lmHCOo" title="Sophie Oluwole par Sahara Tv"&gt;discipline philosophique &lt;/a&gt; et à reconnaître la pluralité des sources de la pensée rationnelle humaine. &lt;/p&gt; &lt;p&gt; Dans ses réflexions sur le genre et la culture, Oluwole critique également les représentations négatives des femmes dans les mythes et les traditions orales, tout en défendant leur rôle intellectuel et spirituel. Elle insiste sur la nécessité de rebâtir des politiques de développement africain à partir de la langue et des savoirs autochtones, plutôt que de copier aveuglément les modèles occidentaux. Ainsi, sa philosophie articule critique de la domination culturelle, reconnaissance de la sagesse traditionnelle et engagement concret pour la dignité, l’égalité et l’autonomie des peuples africains.&lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F159" s="1" t="s">
         <v>1238</v>
@@ -13533,8 +13665,11 @@
       <c r="D165" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>1273</v>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji"  title=" Wikipedia"&gt;Paulin HOUTONDJI&lt;/a&gt;  était un philosophe et intellectuel béninois. Il est reconnu pour ses contributions importantes à la philosophie africaine contemporaine, en particulier pour son engagement critique envers les approches essentialistes et ethnophilosophiques qui ont souvent caractérisé la &lt;a href="https://www.youtube.com/watch?v=F3zPoQrzxp8"  title="pauli Hountondji par ithephilosopher"&gt; pensée philosophique africaine&lt;/a&gt;.&lt;/p&gt; &lt;p&gt; Il a étudié la philosophie en France, à la Sorbonne, où il a obtenu son doctorat en philosophie en 1970. Son travail a été influencé par des penseurs occidentaux tels que Karl Marx et Ludwig Wittgenstein, ainsi que par des philosophes africains comme Frantz Fanon. &lt;/p&gt; &lt;p&gt; L'une de ses œuvres les plus célèbres est le livre intitulé "Sur la philosophie africaine : critique de l'ethnophilosophie" (1976), dans lequel il remet en question l'approche essentialiste qui considère la philosophie africaine comme étant &lt;a href="https://theconversation.com/paulin-hountondji-le-penseur-qui-a-defriche-la-reflexion-sur-la-philosophie-africaine-222722"  title="pauli Hountondji parthe conversation"&gt; fondamentalement différente &lt;/a&gt;  de la philosophie occidentale en raison de ses prétendues racines culturelles profondes. Il soutient plutôt que la philosophie doit être étudiée de manière critique et indépendante de toute influence culturelle préconçue.&lt;/p&gt; &lt;p&gt; En plus de son travail philosophique, Paulin J. Il a été impliqué dans la vie politique de son pays. Il a occupé divers postes, notamment celui de ministre de l'Éducation nationale au Bénin. Son engagement envers la promotion de la pensée critique et son influence dans le domaine de la philosophie africaine lui ont valu une reconnaissance internationale. &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F165" s="1" t="s">
         <v>1274</v>
@@ -15894,6 +16029,11 @@
       </c>
       <c r="K231" s="2" t="s">
         <v>231</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme coréen ; Phénoménologie</t>
+        </is>
       </c>
       <c r="M231" s="2" t="s">
         <v>1627</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -12510,11 +12510,15 @@
       <c r="E141" s="13" t="s">
         <v>1147</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>1149</v>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sT4CzSoqbG4</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jiddu Krishnamurti - Entretien en français 1972" par Penser Le Monde</t>
+        </is>
       </c>
       <c r="H141" s="2" t="s">
         <v>1150</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -6702,14 +6702,18 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="61.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>-1900</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-1800</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>90</v>
+      <c r="A12" s="1">
+        <v>-200</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-100</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 200 A JC – 100 A JC</t>
+        </is>
       </c>
       <c r="D12" s="2" t="s">
         <v>91</v>
@@ -6732,8 +6736,10 @@
       <c r="K12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>98</v>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nyâya ; Vaisheshika</t>
+        </is>
       </c>
       <c r="M12" s="2" t="s">
         <v>99</v>
@@ -7290,8 +7296,10 @@
       <c r="K25" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>198</v>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme ; Védisme</t>
+        </is>
       </c>
       <c r="M25" s="2" t="s">
         <v>207</v>
@@ -7424,8 +7432,10 @@
       <c r="K28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>232</v>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaisheshika ; Nyâya</t>
+        </is>
       </c>
       <c r="M28" s="2" t="s">
         <v>233</v>
@@ -7666,14 +7676,18 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="n">
-        <v>-563</v>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>-483</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>281</v>
+      <c r="A34" s="7">
+        <v>-200</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-100</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 200 A JC – 100 A JC</t>
+        </is>
       </c>
       <c r="D34" s="9" t="s">
         <v>282</v>
@@ -7699,8 +7713,10 @@
       <c r="K34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>287</v>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Yoga (école philosophique) ; Sâmkhya</t>
+        </is>
       </c>
       <c r="M34" s="2" t="s">
         <v>288</v>
@@ -9407,8 +9423,10 @@
       <c r="K72" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>602</v>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advaïta Védanta ; Mimamsa</t>
+        </is>
       </c>
       <c r="M72" s="2" t="s">
         <v>610</v>
@@ -9449,8 +9467,10 @@
       <c r="K73" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>593</v>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa ; Mutazilisme</t>
+        </is>
       </c>
       <c r="M73" s="2" t="s">
         <v>618</v>
@@ -10956,8 +10976,10 @@
       <c r="K106" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="L106" s="2" t="s">
-        <v>884</v>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme mésoaméricain ; Pensée Nahua (aztèque)</t>
+        </is>
       </c>
       <c r="M106" s="2" t="s">
         <v>885</v>
@@ -11007,7 +11029,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soufisme ; Hindouisme ; Bhakti</t>
+          <t xml:space="preserve">Soufisme ; Hindouisme ; Bhakti ; Sikhisme</t>
         </is>
       </c>
       <c r="M107" s="2" t="s">
@@ -11274,8 +11296,10 @@
       <c r="K113" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>296</v>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme ; Shintoïsme</t>
+        </is>
       </c>
       <c r="M113" s="2" t="s">
         <v>942</v>
@@ -11699,8 +11723,10 @@
       <c r="K123" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="L123" s="2" t="s">
-        <v>1026</v>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Brahmoïsme</t>
+        </is>
       </c>
       <c r="M123" s="2" t="s">
         <v>1027</v>
@@ -11959,8 +11985,10 @@
       <c r="K129" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="L129" s="2" t="s">
-        <v>857</v>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Brahmoïsme</t>
+        </is>
       </c>
       <c r="M129" s="2" t="s">
         <v>1070</v>
@@ -12005,7 +12033,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouisme ; Néo-védanta</t>
+          <t xml:space="preserve">Hindouisme ; Néo-védanta ; Yoga (école philosophique)</t>
         </is>
       </c>
       <c r="M130" s="2" t="s">
@@ -12267,7 +12295,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouisme ; Néo-védanta</t>
+          <t xml:space="preserve">Hindouisme ; Néo-védanta ; Yoga (école philosophique)</t>
         </is>
       </c>
       <c r="M135" s="2" t="s">
@@ -12529,8 +12557,10 @@
       <c r="K141" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="L141" s="2" t="s">
-        <v>641</v>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme ; Théosophisme</t>
+        </is>
       </c>
       <c r="M141" s="2" t="s">
         <v>1151</v>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -20924,6 +20924,673 @@
       </c>
       <c r="P318" s="1"/>
     </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A319" s="1">
+        <v>-390</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-338</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 390 A JC – 338 A JC</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHANG YANG</t>
+        </is>
+      </c>
+      <c r="E319" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shang_Yang" title=" Wikipedia"&gt;SHANG YANG&lt;/a&gt; (Gongsun Yang, dit le seigneur de Shang) est un homme d’État et penseur chinois de l’époque des Royaumes combattants, l’un des fondateurs du &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9gisme" title=" Wikipedia"&gt;légisme&lt;/a&gt;. Issu d’une branche cadette de la famille régnante du petit État de Wey, il sert d’abord un ministre de l’État de Wei, puis part en 361 av. J.-C. pour l’État de Qin, à l’ouest, où le duc Xiao cherche des conseillers capables de rendre son pays puissant.&lt;/p&gt; &lt;p&gt;Ses réformes, lancées en 356 puis en 350, transforment Qin en machine de guerre. Il abolit les privilèges de l’aristocratie héréditaire : les rangs et les terres ne récompensent plus la naissance, mais les têtes ennemies coupées au combat et le grain produit. Les familles sont regroupées par cinq ou par dix et deviennent responsables les unes des autres : qui ne dénonce pas un crime est puni comme le coupable. Il découpe le pays en districts confiés à des fonctionnaires nommés, unifie les poids et mesures, encourage l’agriculture et méprise le commerce. Pour lui, l’homme recherche le profit et fuit la peine : la loi, écrite, publique et appliquée à tous, avec de lourdes peines même pour les petites fautes, est le seul moyen de gouverner. Les enseignements des confucéens, la poésie et l’histoire ne font qu’affaiblir l’État.&lt;/p&gt; &lt;p&gt;Ses idées sont réunies dans le &lt;em&gt;Livre du seigneur de Shang&lt;/em&gt;, compilé après sa mort. Quand le duc Xiao meurt, en 338, ses ennemis l’accusent de rébellion : il est exécuté, écartelé par des chars, et sa famille est exterminée. Ses réformes, elles, demeurent, et permettent à Qin d’unifier la Chine en 221 av. J.-C. &lt;a href="https://fr.wikipedia.org/wiki/Han_Fei" title=" Wikipedia"&gt;Han Fei&lt;/a&gt; fera la synthèse de sa doctrine de la loi avec celles de Shen Buhai et de Shen Dao.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/shangyang-mini.webp</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Légisme</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homme d’État chinois, réformateur de l’État de Qin et l’un des fondateurs du légisme.</t>
+        </is>
+      </c>
+      <c r="O319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P319" s="1"/>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A320" s="1">
+        <v>-370</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-310</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 370 A JC – 310 A JC</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUI SHI</t>
+        </is>
+      </c>
+      <c r="E320" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;HUI SHI&lt;/a&gt; (ou Huizi, « maître Hui ») est un penseur chinois de l’époque des Royaumes combattants, l’un des principaux représentants de l’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_des_Noms" title=" Wikipedia"&gt;École des Noms&lt;/a&gt;. Originaire de l’État de Song, il devient Premier ministre du roi Hui de Wei, pour qui il rédige des lois, et prend part aux négociations diplomatiques de son temps. Ses contemporains admirent l’étendue de son savoir : on disait que ses livres remplissaient cinq charrettes.&lt;/p&gt; &lt;p&gt;Aucun de ses écrits ne nous est parvenu. On ne connaît sa pensée que par le dernier chapitre du &lt;em&gt;Zhuangzi&lt;/em&gt;, qui cite ses « dix propositions » paradoxales. « Le plus grand n’a rien au-delà de lui : on l’appelle l’Un suprême ; le plus petit n’a rien en deçà de lui : on l’appelle l’Un infime. » « Le ciel est aussi bas que la terre, les montagnes sont au niveau des marais. » « Je pars aujourd’hui pour Yue et j’y suis arrivé hier. » Ces paradoxes, qui rappellent ceux de Zénon d’Élée, montrent que toutes les distinctions, de grandeur, de lieu ou de temps, dépendent du point de vue. Ils s’achèvent sur une conclusion morale : « Aime toutes choses sans distinction : le ciel et la terre ne forment qu’un seul corps. »&lt;/p&gt; &lt;p&gt;Hui Shi est surtout célèbre comme l’ami et l’adversaire de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt;, qui le met en scène dans de nombreux dialogues. Le plus fameux se déroule sur un pont au-dessus de la rivière Hao : « Vois comme les poissons s’ébattent : voilà leur joie », dit Zhuangzi. « Tu n’es pas un poisson : comment sais-tu ce qu’est leur joie ? » répond Hui Shi. Devant sa tombe, Zhuangzi aurait confié que, depuis sa mort, il n’avait plus personne avec qui parler.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/huishi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chinoise</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logique ; langage</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École des Noms</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">logicien chinois de l’École des Noms, auteur de paradoxes et ami-adversaire de Zhuangzi.</t>
+        </is>
+      </c>
+      <c r="O320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P320" s="1"/>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A321" s="1">
+        <v>650</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 650 – 700</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KUMARILA BHATTA</t>
+        </is>
+      </c>
+      <c r="E321" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia (en)"&gt;KUMARILA BHATTA&lt;/a&gt; est un philosophe indien du VIIe siècle, le plus grand maître de la &lt;a href="https://fr.wikipedia.org/wiki/M%C3%AEm%C3%A2ms%C3%A2" title=" Wikipedia"&gt;Mimamsa&lt;/a&gt;, l’école qui interprète les Védas et leurs rites. On sait très peu de chose de sa vie. La tradition raconte qu’il étudia, sans révéler qui il était, chez des maîtres bouddhistes pour mieux les réfuter, et qu’il se donna la mort sur un bûcher pour expier cette ruse, après avoir rencontré le jeune Shankara.&lt;/p&gt; &lt;p&gt;Son œuvre est un vaste commentaire, en trois parties, du commentaire de Shabara aux &lt;em&gt;Mimamsa-sutras&lt;/em&gt; de Jaimini ; la première, le &lt;em&gt;Shlokavarttika&lt;/em&gt;, est écrite en vers. Il y défend une théorie originale de la connaissance : toute connaissance est valide par elle-même ; on n’a pas à la justifier, il suffit qu’aucune raison ne vienne la contredire. Le Véda n’a pas d’auteur, ni humain ni divin : il est éternel et ne peut donc contenir aucune erreur. C’est la seule source qui fasse connaître le devoir religieux, le dharma. Kumarila rejette ainsi l’idée d’un Dieu créateur et omniscient.&lt;/p&gt; &lt;p&gt;Il mène une polémique serrée contre les bouddhistes, en particulier contre Dignaga, dont il conteste la théorie de l’impermanence et l’idée que le monde ne serait que conscience ; Dharmakirti lui répondra. Il défend le réalisme : le monde extérieur existe, et les mots désignent des universaux réels. Ses disciples, dont Mandana Mishra selon la tradition, forment l’école Bhatta, rivale de celle de Prabhakara. Son influence sur l’hindouisme est considérable : il contribue au recul du bouddhisme en Inde et prépare le terrain du Vedanta.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/kumarila-mini.webp</t>
+        </is>
+      </c>
+      <c r="J321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; langage ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mimamsa</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe indien, grand maître de la Mimamsa, défenseur de l’autorité éternelle des Védas.</t>
+        </is>
+      </c>
+      <c r="O321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P321" s="1"/>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A322" s="1">
+        <v>1827</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1890</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1827 – 1890</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyotirao PHULE</t>
+        </is>
+      </c>
+      <c r="E322" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mahatma_Jyotirao_Phule" title=" Wikipedia"&gt;Jyotirao PHULE&lt;/a&gt; est un penseur, écrivain et réformateur social indien, pionnier de la lutte contre le système des castes. Né en 1827 à Pune, dans une famille de jardiniers de la caste des Mali, considérée comme inférieure, il étudie dans une école de missionnaires écossais. En 1848, humilié lors du mariage d’un ami brahmane, il prend conscience de l’injustice des castes.&lt;/p&gt; &lt;p&gt;La même année, avec sa femme &lt;a href="https://fr.wikipedia.org/wiki/Savitribai_Phule" title=" Wikipedia"&gt;Savitribai&lt;/a&gt;, il ouvre à Pune l’une des premières écoles pour filles fondées par des Indiens, puis des écoles pour les enfants des castes dites « intouchables ». Il ouvre son puits aux intouchables et crée un foyer pour les veuves et leurs enfants. En 1873, il fonde la Satyashodhak Samaj, la « Société des chercheurs de vérité », qui célèbre des mariages sans prêtres brahmanes. Dans &lt;em&gt;Gulamgiri&lt;/em&gt; (L’Esclavage, 1873), qu’il dédie aux Américains qui ont combattu l’esclavage, il relit l’histoire de l’Inde comme la domination des brahmanes, venus de l’extérieur, sur les peuples du pays, maintenus en servitude par la religion et l’ignorance.&lt;/p&gt; &lt;p&gt;Pour Phule, l’éducation est la clé de l’émancipation : « Sans savoir, la sagesse fut perdue ; sans sagesse, la morale fut perdue ; sans morale, le progrès fut perdu… » Il attaque les lois de Manou et défend l’égalité des femmes et des hommes. Le titre de « Mahatma » lui est donné en 1888. &lt;a href="https://fr.wikipedia.org/wiki/Bhimrao_Ramji_Ambedkar" title=" Wikipedia"&gt;Ambedkar&lt;/a&gt; le considère comme l’un de ses trois maîtres, avec le Bouddha et Kabir, et voit en lui le père de la pensée qui inspirera les mouvements dalits.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/phule-mini.webp</t>
+        </is>
+      </c>
+      <c r="J322" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie Dalit</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">réformateur social indien, pionnier de la lutte contre les castes et de l’éducation des filles.</t>
+        </is>
+      </c>
+      <c r="O322" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P322" s="1"/>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A323" s="1">
+        <v>1697</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1769</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697 – 1769</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kamo no MABUCHI</t>
+        </is>
+      </c>
+      <c r="E323" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kamo_no_Mabuchi" title=" Wikipedia"&gt;Kamo no MABUCHI&lt;/a&gt; est un philologue et poète japonais de l’époque d’Edo, l’un des « quatre grands maîtres » du &lt;a href="https://fr.wikipedia.org/wiki/Kokugaku" title=" Wikipedia"&gt;Kokugaku&lt;/a&gt;, l’« étude nationale ». Issu d’une famille de prêtres shintō des environs de Hamamatsu, il étudie à Kyoto auprès de Kada no Azumamaro, puis s’installe à Edo, où il devient le professeur de littérature japonaise de Tayasu Munetake, un fils du shogun Tokugawa Yoshimune.&lt;/p&gt; &lt;p&gt;Il consacre sa vie au &lt;em&gt;Man’yōshū&lt;/em&gt;, la plus ancienne anthologie de poésie japonaise, compilée au VIIIe siècle. Il y découvre l’esprit du Japon d’avant les influences étrangères : un cœur droit, sincère et viril, qui chante simplement ce qu’il ressent. Pour lui, le bouddhisme et surtout le confucianisme, venus de Chine, ont corrompu cette simplicité originelle par leurs raisonnements artificiels et leur morale de règles. Dans &lt;em&gt;Kokuikō&lt;/em&gt; (Réflexions sur l’esprit du pays, 1765), il oppose à la Chine, sans cesse déchirée malgré ses sages, un Japon ancien qui vivait en paix en suivant la nature et la voie des dieux.&lt;/p&gt; &lt;p&gt;En 1763, il rencontre une seule fois, dans une auberge de Matsusaka, un jeune médecin passionné par le &lt;em&gt;Kojiki&lt;/em&gt; : &lt;a href="https://fr.wikipedia.org/wiki/Motoori_Norinaga" title=" Wikipedia"&gt;Motoori Norinaga&lt;/a&gt;. Mabuchi l’encourage à étudier d’abord le Man’yōshū pour retrouver la langue ancienne. Leur correspondance dure jusqu’à la mort de Mabuchi, en 1769. Norinaga achèvera l’œuvre de son maître, et le Kokugaku, prolongé par Hirata Atsutane, nourrira au XIXe siècle le renouveau du shintō et le nationalisme de l’ère Meiji.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mabuchi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kokugaku ; Shintoïsme</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philologue et poète japonais, maître du Kokugaku et redécouvreur du Man’yōshū.</t>
+        </is>
+      </c>
+      <c r="O323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P323" s="1"/>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A324" s="1">
+        <v>1659</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1719</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1659 – 1719</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yamamoto TSUNETOMO</t>
+        </is>
+      </c>
+      <c r="E324" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yamamoto_Tsunetomo" title=" Wikipedia"&gt;Yamamoto TSUNETOMO&lt;/a&gt; est un samouraï japonais du domaine de Saga, dans l’île de Kyūshū, au service du clan Nabeshima. Né en 1659, il entre très jeune au service de son seigneur, Nabeshima Mitsushige, auquel il reste attaché pendant plus de trente ans. Quand Mitsushige meurt, en 1700, il voudrait le suivre dans la mort par le suicide rituel, mais cette pratique est désormais interdite : il se fait alors moine bouddhiste et se retire dans un ermitage.&lt;/p&gt; &lt;p&gt;Entre 1709 et 1716, un jeune samouraï, Tashiro Tsuramoto, vient l’écouter et note ses propos. Ils forment le &lt;em&gt;Hagakure&lt;/em&gt;, « À l’ombre des feuilles », recueil de plus de mille réflexions et anecdotes sur le &lt;a href="https://fr.wikipedia.org/wiki/Bushido" title=" Wikipedia"&gt;bushidō&lt;/a&gt;. Sa phrase la plus célèbre ouvre le livre : « J’ai découvert que la voie du samouraï, c’est la mort. » Il ne s’agit pas d’un culte morbide, mais d’une discipline : celui qui vit chaque jour comme s’il était déjà mort est libéré de toute peur et peut servir son maître sans calcul. Le Hagakure exalte la loyauté absolue, l’action immédiate plutôt que la réflexion, la honte plus redoutable que la mort, mais aussi le soin de son apparence et la délicatesse dans les rapports humains.&lt;/p&gt; &lt;p&gt;Écrit à une époque où le Japon vit en paix depuis un siècle et où les samouraïs sont devenus des fonctionnaires, le livre est la nostalgie d’un âge de guerriers. Longtemps resté secret dans le domaine de Saga, il n’est publié qu’au début du XXe siècle. Le militarisme japonais en fait ensuite un texte de propagande, notamment auprès des pilotes kamikazes. L’écrivain Mishima Yukio, qui lui consacre un livre en 1967, en fait son livre de chevet.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tsunetomo-mini.webp</t>
+        </is>
+      </c>
+      <c r="J324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japonaise</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bushido</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samouraï japonais, auteur du Hagakure, le livre de la voie du guerrier.</t>
+        </is>
+      </c>
+      <c r="O324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P324" s="1"/>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A325" s="1">
+        <v>1895</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1982</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1895 – 1982</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinoba BHAVE</t>
+        </is>
+      </c>
+      <c r="E325" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vinoba_Bhave" title=" Wikipedia"&gt;Vinoba BHAVE&lt;/a&gt; est un penseur, réformateur et ascète indien, considéré comme le principal héritier spirituel de &lt;a href="https://fr.wikipedia.org/wiki/Mohandas_Karamchand_Gandhi" title=" Wikipedia"&gt;Gandhi&lt;/a&gt;. Né en 1895 dans un village du Maharashtra, dans une famille brahmane, il abandonne ses études en 1916 pour rejoindre l’ashram de Gandhi à Ahmedabad. Il y mène une vie de travail manuel, de prière et d’étude ; il apprend de nombreuses langues et commente la &lt;em&gt;Bhagavad-Gita&lt;/em&gt;, qu’il présente comme un guide pour l’action désintéressée. En 1940, Gandhi le choisit comme premier satyagrahi, le premier à désobéir individuellement aux Britanniques, et il passe plusieurs années en prison.&lt;/p&gt; &lt;p&gt;Après l’indépendance et l’assassinat de Gandhi, il cherche à réaliser le sarvodaya, le « bien-être de tous ». En 1951, dans la région du Telangana, où des paysans sans terre se sont révoltés, un propriétaire lui offre cent acres : c’est le début du Bhoodan, le « don de la terre ». Pendant treize ans, il parcourt l’Inde à pied, de village en village, et demande aux propriétaires de donner une part de leurs terres aux pauvres. Il recueille ainsi plus de quatre millions d’acres. Il étend ensuite le mouvement au Gramdan, le don du village entier, qui devient propriétaire collectif de ses terres.&lt;/p&gt; &lt;p&gt;Pour Vinoba, la non-violence ne consiste pas seulement à refuser la force : elle doit transformer les cœurs et rendre inutile le pouvoir de l’État. Il soutient pourtant l’état d’urgence décrété par Indira Gandhi en 1975, ce qui lui est vivement reproché. Il meurt en 1982 après avoir cessé de s’alimenter, selon une pratique ascétique de l’Inde. Il reçoit à titre posthume la plus haute distinction indienne, le Bharat Ratna.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vinoba-mini.webp</t>
+        </is>
+      </c>
+      <c r="J325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gandhisme</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">disciple et héritier spirituel de Gandhi, fondateur du mouvement du « don de la terre ».</t>
+        </is>
+      </c>
+      <c r="O325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P325" s="1"/>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A326" s="1">
+        <v>770</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 770 – 830</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYARASHI BHATTA</t>
+        </is>
+      </c>
+      <c r="E326" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Jayar%C4%81%C5%9Bi_Bha%E1%B9%AD%E1%B9%ADa" title=" Wikipedia (en)"&gt;JAYARASHI BHATTA&lt;/a&gt; est un philosophe indien du VIIIe siècle, auteur du seul traité complet qui nous soit parvenu de la tradition du &lt;a href="https://fr.wikipedia.org/wiki/Charvaka" title=" Wikipedia"&gt;Lokayata&lt;/a&gt;, la pensée matérialiste et sceptique de l’Inde, longtemps connue par ses seuls adversaires. On ne sait presque rien de sa vie. Son livre, le &lt;em&gt;Tattvopaplavasimha&lt;/em&gt;, « le lion qui dévore toutes les catégories », a été redécouvert en 1926 dans un manuscrit jaïn conservé à Patan, au Gujarat, et publié en 1940.&lt;/p&gt; &lt;p&gt;Jayarashi pousse le scepticisme jusqu’au bout. Les écoles indiennes reconnaissaient des « moyens de connaissance » valides, les pramanas : la perception, l’inférence, le témoignage des textes. Il les examine l’un après l’autre et montre qu’aucun ne peut être justifié sans tomber dans un cercle ou dans une régression à l’infini. Même la perception, que les matérialistes tenaient pour la seule source fiable, ne résiste pas à son examen : on ne peut jamais établir qu’elle ne nous trompe pas. Il en conclut que toutes les catégories, celles des philosophes comme celles des théologiens, sont « renversées ».&lt;/p&gt; &lt;p&gt;On discute pour savoir s’il appartient vraiment au Lokayata ou s’il est un sceptique indépendant : il critique les matérialistes eux-mêmes, mais partage leur refus de l’au-delà, du karma et de l’autorité des Védas. Puisque rien ne peut être établi, la vie ordinaire peut suivre son cours sans se soumettre aux promesses des prêtres. Son œuvre a souvent été comparée au scepticisme grec de Sextus Empiricus.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jayarashi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J326" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indienne</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lokayata / Carvaka</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe sceptique indien, auteur du seul traité qui nous reste de la tradition du Lokayata.</t>
+        </is>
+      </c>
+      <c r="O326" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="P326" s="1"/>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A327" s="1">
+        <v>1258</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1308</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258 – 1308</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRAN NHAN TONG</t>
+        </is>
+      </c>
+      <c r="E327" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;TRAN NHAN TONG&lt;/a&gt; (Trần Nhân Tông) est un empereur vietnamien de la dynastie des Trần et le fondateur de l’école zen Trúc Lâm, « de la Forêt de bambous », la première école bouddhique proprement vietnamienne. Monté sur le trône en 1278, il dirige avec le général Trần Hưng Đạo la résistance victorieuse du Đại Việt contre les deux invasions mongoles de Kubilai Khan, en 1285 et en 1288.&lt;/p&gt; &lt;p&gt;En 1293, il abdique en faveur de son fils et, quelques années plus tard, se retire comme moine sur le mont Yên Tử, où il fonde l’école Trúc Lâm. Il y enseigne un zen ouvert à la vie dans le monde : l’éveil ne demande pas de fuir la société, car le Bouddha est dans le cœur de chacun. Son poème « Vivre dans le monde en jouissant de la Voie » se termine ainsi : « Quand on a faim, on mange ; quand on est fatigué, on dort. » Cette voie s’accorde avec les devoirs confucéens envers la famille et l’État, et avec la simplicité taoïste : elle est une expression du Tam Giáo, l’harmonie des trois enseignements.&lt;/p&gt; &lt;p&gt;Il agit aussi pour la paix avec ses voisins : à la suite de sa visite au Champa, au sud, sa fille épouse en 1306 le roi de ce pays, qui cède en échange deux provinces au Đại Việt. Il meurt en 1308. Vénéré comme « Bouddha-roi » et premier patriarche de Trúc Lâm, il incarne au Vietnam l’idéal d’un souverain à la fois guerrier, politique et sage.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/trannhantong-mini.webp</t>
+        </is>
+      </c>
+      <c r="J327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vietnamienne</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie vietnamienne (Tam Giáo) ; Bouddhisme Zen</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empereur vietnamien, vainqueur des Mongols et fondateur de l’école zen Trúc Lâm.</t>
+        </is>
+      </c>
+      <c r="O327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P327" s="1"/>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A328" s="1">
+        <v>1827</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1898</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1827 – 1898</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHOE SI-HYEONG</t>
+        </is>
+      </c>
+      <c r="E328" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Choe_Si-hyeong" title=" Wikipedia (en)"&gt;CHOE SI-HYEONG&lt;/a&gt; est le deuxième chef du &lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Donghak&lt;/a&gt;, le « Savoir de l’Est », mouvement religieux et philosophique coréen fondé par Choe Je-u. Né dans une famille pauvre de la région de Gyeongju et orphelin très jeune, il travaille dans une fabrique de papier quand il rencontre Choe Je-u en 1861. Il devient son disciple le plus proche, et en 1863 Choe Je-u le désigne comme son successeur, peu avant d’être arrêté puis exécuté par le gouvernement de Joseon.&lt;/p&gt; &lt;p&gt;Pendant plus de trente ans, pourchassé par les autorités, il vit dans la clandestinité, de village en village. Il rassemble et publie les écrits de son maître, le &lt;em&gt;Donggyeong daejeon&lt;/em&gt; (1880) et les chants du &lt;em&gt;Yongdam yusa&lt;/em&gt; (1881), et organise les fidèles en réseaux. Sa pensée prolonge celle de Choe Je-u : chaque être humain porte en lui le Ciel, et il faut donc « servir l’homme comme le Ciel ». Il étend ce respect aux femmes, aux enfants, aux serviteurs et même aux choses : « Frapper un enfant, c’est frapper le Ciel. »&lt;/p&gt; &lt;p&gt;En 1894, les paysans du Donghak se soulèvent contre l’oppression et la présence étrangère ; Choe Si-hyeong, d’abord hésitant, finit par soutenir la révolte, menée notamment par Jeon Bong-jun. Elle est écrasée par les troupes japonaises et gouvernementales. Arrêté en 1898, il est exécuté à Séoul. Son successeur, Son Byong-hi, transforme le mouvement en une religion, le Cheondogyo, qui jouera un grand rôle dans le mouvement d’indépendance de 1919.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/choesihyeong-mini.webp</t>
+        </is>
+      </c>
+      <c r="J328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coréenne</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donghak</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deuxième maître du Donghak, penseur du respect de l’homme « comme le Ciel ».</t>
+        </is>
+      </c>
+      <c r="O328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="P328" s="1"/>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A329" s="1">
+        <v>1703</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1792</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1703 – 1792</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBN ABD AL-WAHHAB</t>
+        </is>
+      </c>
+      <c r="E329" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mohammed_ben_Abdelwahhab" title=" Wikipedia"&gt;IBN ABD AL-WAHHAB&lt;/a&gt; (Muhammad ibn Abd al-Wahhab) est un théologien et réformateur religieux arabe, fondateur du courant appelé wahhabisme. Né en 1703 à Uyayna, dans le Najd, au centre de l’Arabie, dans une famille de juristes hanbalites, il étudie à Médine et à Bassora. Il revient convaincu que l’islam de son temps s’est corrompu : le culte des saints, les pèlerinages aux tombeaux, les amulettes et certaines pratiques soufies lui paraissent autant de formes de polythéisme.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Livre de l’unicité&lt;/em&gt;, il fait de l’unicité absolue de Dieu, le tawhid, le critère de toute foi : toute prière adressée à un autre que Dieu, tout intermédiaire, est une « association », le plus grave des péchés. Il appelle à revenir au Coran, à la Sunna et aux premières générations de musulmans, en s’appuyant sur &lt;a href="https://fr.wikipedia.org/wiki/Ibn_Taymiyya" title=" Wikipedia"&gt;Ibn Taymiyya&lt;/a&gt;, et rejette l’imitation aveugle des écoles juridiques. Il fait détruire des tombeaux vénérés et déclare infidèles ceux qui refusent sa doctrine.&lt;/p&gt; &lt;p&gt;En 1744, il conclut à Dir’iyya un pacte avec l’émir Muhammad ibn Saoud : le chef politique protège et répand la doctrine, le réformateur légitime son pouvoir. De cette alliance naît le premier État saoudien, et elle fonde encore l’Arabie saoudite d’aujourd’hui. Il meurt en 1792. Dès son époque, de nombreux savants musulmans, dont son propre frère, combattent sa doctrine. Diffusée au XXe siècle grâce aux richesses pétrolières, elle a profondément marqué le salafisme contemporain, et certains de ses aspects ont été repris par des mouvements jihadistes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/abdalwahhab-mini.webp</t>
+        </is>
+      </c>
+      <c r="J329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arabe</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fondamentalisme</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien arabe, fondateur du wahhabisme, réforme rigoriste fondée sur l’unicité de Dieu.</t>
+        </is>
+      </c>
+      <c r="O329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P329" s="1"/>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A330" s="1">
+        <v>1953</v>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1953</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrick CHAMOISEAU</t>
+        </is>
+      </c>
+      <c r="E330" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick CHAMOISEAU&lt;/a&gt; est un écrivain et penseur martiniquais. Né en 1953 à Fort-de-France, il étudie le droit et l’économie sociale à Paris, puis devient éducateur auprès de jeunes en difficulté en Martinique. Il se fait connaître avec &lt;em&gt;Chronique des sept misères&lt;/em&gt; (1986) et reçoit le prix Goncourt en 1992 pour &lt;em&gt;Texaco&lt;/em&gt;, fresque de l’histoire de la Martinique racontée à travers la lutte d’un quartier populaire de Fort-de-France.&lt;/p&gt; &lt;p&gt;En 1989, avec Jean Bernabé et Raphaël Confiant, il publie l’&lt;em&gt;Éloge de la créolité&lt;/em&gt; : « Ni Européens, ni Africains, ni Asiatiques, nous nous proclamons Créoles. » Contre l’assimilation à la France, mais aussi contre le seul retour à l’Afrique de la négritude, le manifeste revendique une identité faite de mélanges, de la langue créole et de la mémoire des conteurs. Chamoiseau prolonge ensuite la pensée d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Glissant" title=" Wikipedia"&gt;Édouard Glissant&lt;/a&gt;, dont il se veut le disciple : à la créolité comme identité, il préfère la créolisation, processus ouvert et imprévisible de rencontre entre les cultures, et une identité-relation plutôt qu’une identité-racine.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Écrire en pays dominé&lt;/em&gt; (1997), il s’interroge sur la place de l’écrivain dans une culture dominée. Avec Glissant, il signe en 2007 &lt;em&gt;Quand les murs tombent&lt;/em&gt;, contre la création d’un ministère de l’Identité nationale. Dans &lt;em&gt;Frères migrants&lt;/em&gt; (2017), il défend l’hospitalité envers les migrants au nom de la « Relation » qui unit tous les peuples.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/chamoiseau-mini.webp</t>
+        </is>
+      </c>
+      <c r="J330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martiniquaise</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; politique</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Créolisation</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain et penseur martiniquais, cosignataire de l’Éloge de la créolité, prix Goncourt 1992.</t>
+        </is>
+      </c>
+      <c r="O330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="P330" s="1"/>
+    </row>
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/data/frise-philosophes-orientaux.xlsx
+++ b/data/frise-philosophes-orientaux.xlsx
@@ -17392,79 +17392,95 @@
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="1" t="n">
-        <v>1948</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>1638</v>
+      <c r="A259" s="1">
+        <v>1556</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1627</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1556 – 1627</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
+        </is>
       </c>
       <c r="E259" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Do-ol" title=" Wikipedia (en)"&gt;KIM YONG-OK,&lt;/a&gt; connu sous son nom de plume Doh-ol, est un philosophe et commentateur des classiques, l’un des intellectuels les plus médiatiques de Corée du Sud. Formé en Corée, à Taïwan, au Japon et à Harvard, où il soutint une thèse sur Wang Fuzhi, il est aussi diplômé de médecine traditionnelle coréenne.&lt;/p&gt; &lt;p&gt;Il défend une philosophie du &lt;em&gt;gi&lt;/em&gt;, dans le sillage notamment de &lt;a href="https://en.wikipedia.org/wiki/Choe_Han-gi" title=" Wikipedia (en)"&gt;Choe Han-gi&lt;/a&gt;, qui refuse le dualisme entre esprit et matière et pense l’être humain comme un corps vivant en relation avec son milieu. Ses cours télévisés sur Laozi, Confucius ou l’histoire coréenne, au style provocateur, ont rendu la philosophie orientale accessible au grand public. Il intervient aussi régulièrement dans le débat public sur l’histoire et la réunification de la Corée.&lt;/p&gt; &lt;p&gt;Professeur à l’université Corée à son retour des États-Unis, il en démissionna avec éclat en 1986, en publiant une « déclaration de conscience » contre le régime militaire de Chun Doo-hwan. Il entreprit alors des études de médecine traditionnelle, convaincu que la philosophie du &lt;em&gt;gi&lt;/em&gt; trouve dans la médecine son lieu d’épreuve : il parle volontiers d’une « philosophie du corps » (&lt;em&gt;mom cheolhak&lt;/em&gt;), pour laquelle l’esprit n’est qu’un aspect de l’organisme vivant. Il a traduit et commenté les grands classiques, des &lt;em&gt;Entretiens&lt;/em&gt; de Confucius au &lt;em&gt;Mencius&lt;/em&gt; et au &lt;em&gt;Daodejing&lt;/em&gt;, et s’est aussi intéressé aux évangiles, qu’il lit comme des textes de sagesse. Ses prises de position tranchées sur l’histoire, la religion ou la politique en font une figure aussi admirée que contestée.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JDg8l7CsF8Y</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"[도올 김용옥]우리는 누구인가-동아시아 국제정세(대만편)_01" par jae hak Lee</t>
-        </is>
-      </c>
-      <c r="H259" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J259" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="K259" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L259" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="M259" s="2" t="s">
-        <v>1641</v>
-      </c>
-      <c r="O259" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="P259" s="1" t="n">
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
+        </is>
+      </c>
+      <c r="J259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malienne</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie africaine</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="P259" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1">
-        <v>1556</v>
+        <v>1901</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627</t>
+          <t xml:space="preserve">1991</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556 – 1627</t>
+          <t xml:space="preserve">1901 – 1991</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AHMED BABA de Tombouctou</t>
+          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
         </is>
       </c>
       <c r="E260" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ahmad_Baba_al-Timbukti" title=" Wikipedia"&gt;AHMED BABA de Tombouctou&lt;/a&gt; est le plus célèbre des savants de &lt;a href="https://fr.wikipedia.org/wiki/Tombouctou" title=" Wikipedia"&gt;Tombouctou&lt;/a&gt;, grand foyer intellectuel de l’Afrique de l’Ouest à l’époque de l’&lt;a href="https://fr.wikipedia.org/wiki/Empire_songha%C3%AF" title=" Wikipedia"&gt;Empire songhaï&lt;/a&gt;. Issu d’une lignée de lettrés berbères, il étudie la langue arabe, la rhétorique, le droit malikite et le commentaire du Coran auprès de son père et du savant Mohammed Bagayogo, puis enseigne à son tour et rédige de nombreux ouvrages.&lt;/p&gt; &lt;p&gt;En 1591, les troupes du sultan du Maroc s’emparent de l’empire songhaï. Accusé de sédition, Ahmed Baba est déporté en 1594 au Maroc avec sa famille, et sa bibliothèque est saisie : il dira avoir perdu 1 600 volumes, alors qu’il possédait, ajoute-t-il, la plus petite bibliothèque de sa famille. Libéré, il enseigne à Marrakech, où les lettrés marocains viennent l’écouter, et y écrit l’essentiel de son œuvre, dont un grand dictionnaire biographique des juristes malikites. Il ne revient à Tombouctou qu’en 1608, où il passe ses dernières années à enseigner, entouré d’une grande réputation.&lt;/p&gt; &lt;p&gt;Son traité &lt;em&gt;Mi’raj al-Su’ud&lt;/em&gt; (1615) répond à des questions sur l’esclavage : il y rejette l’idée qu’on puisse réduire quelqu’un en esclavage à cause de sa couleur de peau, et réfute la prétendue « malédiction de Cham » invoquée pour justifier la traite des Noirs. Sa critique reste toutefois celle d’un juriste de son temps, qui n’abolit pas l’esclavage mais en conteste les critères. Le centre des &lt;a href="https://fr.wikipedia.org/wiki/Manuscrits_de_Tombouctou" title=" Wikipedia"&gt;manuscrits de Tombouctou&lt;/a&gt;, fondé en 1970, porte son nom ; ces manuscrits témoignent d’une tradition savante écrite au cœur de l’Afrique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/ahmedbaba-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
         </is>
       </c>
       <c r="J260" s="1" t="inlineStr">
@@ -17474,27 +17490,27 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">savant de Tombouctou, juriste et biographe, critique de l’esclavage fondé sur la couleur de peau.</t>
+          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="O260" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="O260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P260" s="1">
@@ -17503,56 +17519,51 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1">
-        <v>1901</v>
+        <v>1912</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1991</t>
+          <t xml:space="preserve">1981</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901 – 1991</t>
+          <t xml:space="preserve">1912 – 1981</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amadou HAMPÂTÉ BÂ</t>
+          <t xml:space="preserve">Alexis KAGAME</t>
         </is>
       </c>
       <c r="E261" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Amadou_Hamp%C3%A2t%C3%A9_B%C3%A2" title=" Wikipedia"&gt;Amadou HAMPÂTÉ BÂ&lt;/a&gt; est un écrivain, ethnologue et sage malien, grand défenseur de la tradition orale africaine. Né à Bandiagara, dans une famille peule noble, il fréquente l’école coranique de &lt;a href="https://fr.wikipedia.org/wiki/Tierno_Bokar" title=" Wikipedia"&gt;Tierno Bokar&lt;/a&gt;, maître soufi de la confrérie &lt;a href="https://fr.wikipedia.org/wiki/Tijaniyya" title=" Wikipedia"&gt;Tijaniyya&lt;/a&gt;, qui restera toute sa vie son guide spirituel, avant d’être envoyé de force à l’école française. Il fait ensuite carrière dans l’administration coloniale, en Haute-Volta puis à Bamako. En 1933, il passe plusieurs mois auprès de Tierno Bokar, dont l’enseignement mystique et la bonté le marquent profondément.&lt;/p&gt; &lt;p&gt;En 1942, Théodore Monod l’appelle à l’Institut français d’Afrique noire, à Dakar, où il recueille pendant des années les récits, les généalogies et les savoirs des traditionalistes peuls et bambaras. À l’indépendance du Mali, il fonde l’Institut des sciences humaines de Bamako et siège au Conseil exécutif de l’UNESCO. C’est là qu’il lance en 1960 la formule devenue proverbiale : « En Afrique, quand un vieillard meurt, c’est une bibliothèque qui brûle. » Pour lui, la parole transmise de maître à disciple est un véritable savoir, avec ses méthodes, ses garants et son exigence de vérité.&lt;/p&gt; &lt;p&gt;De Tierno Bokar, dont il écrit la vie, il retient un enseignement de tolérance : « Il y a trois vérités : ma vérité, ta vérité et la Vérité. » Son roman &lt;em&gt;L’Étrange Destin de Wangrin&lt;/em&gt; (1973) et ses mémoires, &lt;a href="https://fr.wikipedia.org/wiki/Amkoullel%2C_l%27enfant_peul" title=" Wikipedia"&gt;&lt;em&gt;Amkoullel, l’enfant peul&lt;/em&gt;&lt;/a&gt; (1991), font revivre l’Afrique de l’Ouest de l’époque coloniale. Il meurt à Abidjan en 1991, et plusieurs de ses livres, comme &lt;em&gt;Oui mon commandant !&lt;/em&gt;, paraissent après sa mort.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/hampateba-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
         </is>
       </c>
       <c r="J261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malienne</t>
+          <t xml:space="preserve">Rwandaise</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine ; Soufisme</t>
+          <t xml:space="preserve">Philosophie africaine ; Ethnophilosophie</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain et ethnologue peul, défenseur de la tradition orale africaine et disciple du sage Tierno Bokar.</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr">
@@ -17566,51 +17577,51 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981</t>
+          <t xml:space="preserve">1999</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912 – 1981</t>
+          <t xml:space="preserve">1922 – 1999</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alexis KAGAME</t>
+          <t xml:space="preserve">Julius NYERERE</t>
         </is>
       </c>
       <c r="E262" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexis_Kagame" title=" Wikipedia"&gt;Alexis KAGAME&lt;/a&gt; est un prêtre catholique, poète, historien et philosophe rwandais. Né à Kiyanza, il entre au séminaire de Kabgayi et se passionne très tôt pour les traditions de son pays : le roi Mutara III Rudahigwa lui fait rencontrer les meilleurs détenteurs de la poésie dynastique et guerrière du Rwanda, qu’il consigne par écrit. Il dirige aussi le journal &lt;em&gt;Kinyamateka&lt;/em&gt;, où il publie ses premiers essais. Ordonné prêtre en 1945, il soutient en 1955 à Rome une thèse de philosophie qui le rend célèbre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), il prolonge, mais aussi corrige, &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;. Comme Aristote avait tiré ses catégories de la langue grecque, il cherche celles de la pensée rwandaise dans la grammaire du kinyarwanda. Il en dégage quatre, construites sur la même racine &lt;em&gt;-ntu&lt;/em&gt; : &lt;em&gt;umuntu&lt;/em&gt;, l’être doué d’intelligence ; &lt;em&gt;ikintu&lt;/em&gt;, la chose ; &lt;em&gt;ahantu&lt;/em&gt;, le lieu et le temps ; &lt;em&gt;ukuntu&lt;/em&gt;, la manière d’être. Il prolonge cette enquête dans &lt;em&gt;La Philosophie bantu comparée&lt;/em&gt; (1976), étendue à de nombreuses langues bantoues. La philosophie consiste pour lui à expliciter ce que la langue pense déjà, sans que ses locuteurs en aient conscience.&lt;/p&gt; &lt;p&gt;Son œuvre a donné une dignité philosophique aux langues et aux traditions africaines, mais elle a aussi été vivement critiquée : &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; y voit le modèle de l’« ethnophilosophie », qui prête à tout un peuple une philosophie collective et implicite. Kagame a aussi laissé une œuvre d’historien du Rwanda ancien et de poète en kinyarwanda.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/akagame-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
         </is>
       </c>
       <c r="J262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rwandaise</t>
+          <t xml:space="preserve">Tanzanienne</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine ; Ethnophilosophie</t>
+          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme ; Socialisme africain</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prêtre, historien et philosophe rwandais, auteur de La philosophie bantu-rwandaise de l’être.</t>
+          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr">
@@ -17624,36 +17635,36 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1999</t>
+          <t xml:space="preserve">1973</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922 – 1999</t>
+          <t xml:space="preserve">1924 – 1973</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius NYERERE</t>
+          <t xml:space="preserve">Amílcar CABRAL</t>
         </is>
       </c>
       <c r="E263" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julius_Nyerere" title=" Wikipedia"&gt;Julius NYERERE&lt;/a&gt; est le père de l’indépendance de la Tanzanie et l’un des grands penseurs du socialisme africain. Fils d’un chef zanaki, instituteur de formation, d’où son surnom de &lt;em&gt;Mwalimu&lt;/em&gt; (« le maître » en swahili), il étudie à Édimbourg puis fonde en 1954 le parti qui mène pacifiquement le Tanganyika à l’indépendance en 1961, après avoir assisté en 1958 à Accra à la conférence panafricaine réunie par Kwame Nkrumah. Il préside la Tanzanie, née de l’union avec Zanzibar, de 1964 à 1985.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Ujamaa, fondement du socialisme africain&lt;/em&gt; (1962), il soutient que le socialisme n’a pas à être importé d’Europe : il existe déjà dans la famille africaine traditionnelle, fondée sur l’entraide, le partage du travail et le refus de l’exploitation. Le mot swahili &lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt; désigne cet « esprit de famille » étendu à la nation. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;Déclaration d’Arusha&lt;/a&gt; (1967) en fait un programme : compter sur ses propres forces, regrouper les paysans dans des villages coopératifs, développer l’éducation pour tous. L’école doit former des citoyens au service de leur village, et non une élite coupée du peuple.&lt;/p&gt; &lt;p&gt;L’expérience améliore l’alphabétisation et l’accès à la santé, mais les regroupements forcés de villages et les difficultés économiques en marquent les limites, que Nyerere reconnaîtra lui-même. Panafricaniste convaincu, il soutient les mouvements de libération d’Afrique australe et quitte volontairement le pouvoir en 1985, fait rare à l’époque. Il traduit aussi Shakespeare en swahili. Il meurt à Londres en 1999.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/nyerere-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
         </is>
       </c>
       <c r="J263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tanzanienne</t>
+          <t xml:space="preserve">Bissau-Guinéenne</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -17663,12 +17674,12 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme ; Tiers-mondisme ; Socialisme africain</t>
+          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">père de l’indépendance tanzanienne, penseur du socialisme africain de l’Ujamaa.</t>
+          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr">
@@ -17682,51 +17693,51 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1">
-        <v>1924</v>
+        <v>1944</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973</t>
+          <t xml:space="preserve">1995</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924 – 1973</t>
+          <t xml:space="preserve">1944 – 1995</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amílcar CABRAL</t>
+          <t xml:space="preserve">Henry ODERA ORUKA</t>
         </is>
       </c>
       <c r="E264" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Am%C3%ADlcar_Cabral" title=" Wikipedia"&gt;Amílcar CABRAL&lt;/a&gt; est le dirigeant de la lutte de libération de la Guinée-Bissau et du Cap-Vert contre le colonialisme portugais, et l’un des théoriciens les plus originaux de la décolonisation. Né à Bafatá, en Guinée portugaise, de parents cap-verdiens, il étudie l’agronomie à Lisbonne, où il fréquente d’autres étudiants africains, comme Agostinho Neto et Mário de Andrade, avec qui il réfléchit à la « réafricanisation des esprits ». Agronome en Guinée, il parcourt le pays pour un recensement agricole qui lui en donne une connaissance intime.&lt;/p&gt; &lt;p&gt;En 1956, il fonde le &lt;a href="https://fr.wikipedia.org/wiki/Parti_africain_pour_l%27ind%C3%A9pendance_de_la_Guin%C3%A9e_et_du_Cap-Vert" title=" Wikipedia"&gt;PAIGC&lt;/a&gt;, qui engage la lutte armée en 1963 et administre bientôt une grande partie du territoire, avec ses écoles, ses dispensaires et ses magasins du peuple. Lecteur de Marx, Cabral refuse d’appliquer des schémas tout faits : dans « L’arme de la théorie » (1966), il analyse la société guinéenne telle qu’elle est, et appelle la petite bourgeoisie instruite à se « suicider en tant que classe » pour se fondre dans le peuple. À ses militants, il recommande de « ne pas mentir » et de « ne pas proclamer de victoires faciles ».&lt;/p&gt; &lt;p&gt;Pour lui, la culture est le cœur de la résistance : un peuple qui garde sa culture garde la possibilité de redevenir maître de son histoire, et la libération nationale est elle-même « un acte de culture ». Mais il met aussi en garde contre un simple « retour aux sources » idéalisé. Il est assassiné à Conakry le 20 janvier 1973, quelques mois avant la proclamation de l’indépendance de la Guinée-Bissau.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/acabral-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
         </is>
       </c>
       <c r="J264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bissau-Guinéenne</t>
+          <t xml:space="preserve">Kényane</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; ethique</t>
         </is>
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Marxisme</t>
+          <t xml:space="preserve">Philosophie africaine</t>
         </is>
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">agronome et chef de la libération de la Guinée-Bissau et du Cap-Vert, penseur de la culture comme résistance.</t>
+          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
         </is>
       </c>
       <c r="O264" s="1" t="inlineStr">
@@ -17740,56 +17751,56 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1">
-        <v>1944</v>
+        <v>1340</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995</t>
+          <t xml:space="preserve">1400</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944 – 1995</t>
+          <t xml:space="preserve">XIVe siècle</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henry ODERA ORUKA</t>
+          <t xml:space="preserve">Mpu TANTULAR</t>
         </is>
       </c>
       <c r="E265" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Henry_Odera_Oruka" title=" Wikipedia (en)"&gt;Henry ODERA ORUKA&lt;/a&gt; est un philosophe kényan, connu pour son projet de « philosophie des sages » (&lt;em&gt;sage philosophy&lt;/em&gt;). Né à Siaya, dans l’ouest du Kenya, il étudie d’abord les sciences à l’université d’Uppsala, en Suède, avant de se tourner vers la philosophie, puis soutient un doctorat aux États-Unis sur la liberté. À partir de 1970, il enseigne à l’université de Nairobi, où il obtient en 1980, après une longue lutte, la création d’un département de philosophie séparé de la théologie.&lt;/p&gt; &lt;p&gt;Dans un article célèbre de 1978, il distingue quatre courants de la philosophie africaine : l’ethnophilosophie, qui prête une sagesse collective à tout un peuple ; la philosophie nationaliste et idéologique de Nkrumah, Nyerere ou Senghor ; la philosophie professionnelle des universitaires ; et la « sagesse philosophique » de certains individus. C’est ce dernier courant qu’il explore : avec ses étudiants, il interroge des sages ruraux, souvent illettrés, pour montrer que certains d’entre eux ne se contentent pas de répéter la tradition mais la soumettent à un examen critique et personnel.&lt;/p&gt; &lt;p&gt;Il répond ainsi à ceux qui doutaient que l’Afrique ait connu une philosophie avant l’écriture, sans tomber dans l’ethnophilosophie qu’il critique, comme &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Hountondji&lt;/a&gt;. Ses entretiens sont réunis dans &lt;em&gt;Sage Philosophy&lt;/em&gt; (1990). Il défend aussi, face aux inégalités mondiales, un « droit au minimum humain » pour chacun, et fonde à Nairobi un institut d’études environnementales. Il meurt à Nairobi en 1995, à cinquante et un ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mpu_Tantular" title=" Wikipedia (en)"&gt;Mpu TANTULAR&lt;/a&gt; est un poète et sage javanais du XIVe siècle, qui vécut à la cour de l’empire de &lt;a href="https://fr.wikipedia.org/wiki/Majapahit" title=" Wikipedia"&gt;Majapahit&lt;/a&gt;, sous le règne du roi Hayam Wuruk, à l’apogée de cette grande puissance hindoue-bouddhiste de l’archipel. Bouddhiste, il était aussi réputé pour son respect des autres religions. Son nom même signifie « qui ne se laisse pas influencer » : celui d’un maître ferme dans ses convictions. On ne connaît de lui que deux grands poèmes en vieux javanais, le &lt;em&gt;Sutasoma&lt;/em&gt; et l’&lt;em&gt;Arjunawijaya&lt;/em&gt;, des &lt;em&gt;kakawin&lt;/em&gt; composés selon la métrique sanskrite.&lt;/p&gt; &lt;p&gt;Le plus célèbre, le &lt;em&gt;Sutasoma&lt;/em&gt;, raconte l’histoire d’un prince qui est une incarnation du Bouddha : renonçant au trône pour la vie spirituelle, il triomphe de ses ennemis, y compris d’un roi démon mangeur d’hommes, non par la force mais par la compassion, en allant jusqu’à offrir sa propre vie. Le poème défend l’idée que le shivaïsme et le bouddhisme, les deux grandes religions de Java, conduisent à une même vérité : « Le Bouddha et Shiva sont différents, mais ils sont un ; la vérité n’est pas double. »&lt;/p&gt; &lt;p&gt;Cette formule, &lt;a href="https://fr.wikipedia.org/wiki/Bhinneka_Tunggal_Ika" title=" Wikipedia"&gt;&lt;em&gt;Bhinneka Tunggal Ika&lt;/em&gt;&lt;/a&gt;, que l’on traduit par « unité dans la diversité », a été reprise par le juriste Mohammad Yamin et choisie au XXe siècle comme devise nationale de la république d’Indonésie, pays aux centaines de langues et aux multiples religions. Elle figure sur les armoiries du pays, inscrite sur le ruban que tient l’aigle Garuda. Ainsi, une méditation religieuse du XIVe siècle est devenue le principe philosophique d’une nation moderne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/oderaoruka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tantular-mini.webp</t>
         </is>
       </c>
       <c r="J265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kényane</t>
+          <t xml:space="preserve">Indonésienne</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; ethique</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie africaine</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Hindouisme</t>
         </is>
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe kényan, fondateur de la « philosophie des sages », qui recueille la pensée critique des sages africains.</t>
+          <t xml:space="preserve">poète bouddhiste de Java, auteur du Sutasoma, d’où vient la devise de l’Indonésie « Unité dans la diversité ».</t>
         </is>
       </c>
       <c r="O265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="P265" s="1">
@@ -17798,31 +17809,31 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1">
-        <v>1340</v>
+        <v>1530</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400</t>
+          <t xml:space="preserve">1590</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XIVe siècle</t>
+          <t xml:space="preserve">XVIe siècle</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mpu TANTULAR</t>
+          <t xml:space="preserve">HAMZAH FANSURI</t>
         </is>
       </c>
       <c r="E266" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mpu_Tantular" title=" Wikipedia (en)"&gt;Mpu TANTULAR&lt;/a&gt; est un poète et sage javanais du XIVe siècle, qui vécut à la cour de l’empire de &lt;a href="https://fr.wikipedia.org/wiki/Majapahit" title=" Wikipedia"&gt;Majapahit&lt;/a&gt;, sous le règne du roi Hayam Wuruk, à l’apogée de cette grande puissance hindoue-bouddhiste de l’archipel. Bouddhiste, il était aussi réputé pour son respect des autres religions. Son nom même signifie « qui ne se laisse pas influencer » : celui d’un maître ferme dans ses convictions. On ne connaît de lui que deux grands poèmes en vieux javanais, le &lt;em&gt;Sutasoma&lt;/em&gt; et l’&lt;em&gt;Arjunawijaya&lt;/em&gt;, des &lt;em&gt;kakawin&lt;/em&gt; composés selon la métrique sanskrite.&lt;/p&gt; &lt;p&gt;Le plus célèbre, le &lt;em&gt;Sutasoma&lt;/em&gt;, raconte l’histoire d’un prince qui est une incarnation du Bouddha : renonçant au trône pour la vie spirituelle, il triomphe de ses ennemis, y compris d’un roi démon mangeur d’hommes, non par la force mais par la compassion, en allant jusqu’à offrir sa propre vie. Le poème défend l’idée que le shivaïsme et le bouddhisme, les deux grandes religions de Java, conduisent à une même vérité : « Le Bouddha et Shiva sont différents, mais ils sont un ; la vérité n’est pas double. »&lt;/p&gt; &lt;p&gt;Cette formule, &lt;a href="https://fr.wikipedia.org/wiki/Bhinneka_Tunggal_Ika" title=" Wikipedia"&gt;&lt;em&gt;Bhinneka Tunggal Ika&lt;/em&gt;&lt;/a&gt;, que l’on traduit par « unité dans la diversité », a été reprise par le juriste Mohammad Yamin et choisie au XXe siècle comme devise nationale de la république d’Indonésie, pays aux centaines de langues et aux multiples religions. Elle figure sur les armoiries du pays, inscrite sur le ruban que tient l’aigle Garuda. Ainsi, une méditation religieuse du XIVe siècle est devenue le principe philosophique d’une nation moderne.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;HAMZAH FANSURI&lt;/a&gt; est un poète et mystique soufi de Sumatra, le premier grand écrivain connu de langue malaise. Sa vie est mal connue : on la reconstitue surtout à partir des dernières strophes de ses poèmes, où il glisse son nom et quelques indications sur lui-même. Son nom suggère qu’il venait de Barus, appelé Fansur par les Arabes, un port de la côte ouest de Sumatra. Il voyagea beaucoup, dans la péninsule malaise, en Inde moghole, à La Mecque, à Médine et à Bagdad, et aurait été initié à une confrérie soufie.&lt;/p&gt; &lt;p&gt;Il est le premier à exprimer en malais la doctrine de l’« unicité de l’être » (&lt;a href="https://fr.wikipedia.org/wiki/Wahdat_al-wujud" title=" Wikipedia"&gt;&lt;em&gt;wahdat al-wujud&lt;/em&gt;&lt;/a&gt;) issue d’&lt;a href="https://fr.wikipedia.org/wiki/Ibn_Arabi" title=" Wikipedia"&gt;Ibn Arabî&lt;/a&gt; : toute réalité est une, et Dieu se manifeste en toutes choses, par degrés successifs, jusqu’à l’« Homme parfait » et au cœur de chacun, qui doit le retrouver en lui-même. Il le dit dans des poèmes de forme nouvelle, les &lt;em&gt;syair&lt;/em&gt;, dont il est considéré comme l’inventeur, et dans trois traités en prose, dont &lt;em&gt;La Boisson des amants&lt;/em&gt; et &lt;em&gt;Les Secrets des gnostiques&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Au XVIIe siècle, sous l’influence du théologien Nuruddin ar-Raniri, son enseignement fut jugé hérétique à la cour du sultanat d’&lt;a href="https://fr.wikipedia.org/wiki/Aceh" title=" Wikipedia"&gt;Aceh&lt;/a&gt;, car il semblait confondre Dieu et sa création, et ses livres furent brûlés. Une trentaine de ses poèmes ont pourtant survécu. Leur virtuosité, l’art d’y fondre les mots arabes dans la langue malaise et leur goût du jeu de mots font de lui le fondateur de la poésie malaise. Le philosophe Naquib al-Attas lui a consacré sa thèse de doctorat, qui a contribué à le faire redécouvrir.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tantular-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fansuri-mini.webp</t>
         </is>
       </c>
       <c r="J266" s="1" t="inlineStr">
@@ -17837,17 +17848,17 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana ; Hindouisme</t>
+          <t xml:space="preserve">Soufisme</t>
         </is>
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète bouddhiste de Java, auteur du Sutasoma, d’où vient la devise de l’Indonésie « Unité dans la diversité ».</t>
+          <t xml:space="preserve">poète soufi de Sumatra, premier grand auteur mystique de langue malaise.</t>
         </is>
       </c>
       <c r="O266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P266" s="1">
@@ -17856,56 +17867,56 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1">
-        <v>1530</v>
+        <v>1861</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">1896</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XVIe siècle</t>
+          <t xml:space="preserve">1861 – 1896</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAMZAH FANSURI</t>
+          <t xml:space="preserve">José RIZAL</t>
         </is>
       </c>
       <c r="E267" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;HAMZAH FANSURI&lt;/a&gt; est un poète et mystique soufi de Sumatra, le premier grand écrivain connu de langue malaise. Sa vie est mal connue : on la reconstitue surtout à partir des dernières strophes de ses poèmes, où il glisse son nom et quelques indications sur lui-même. Son nom suggère qu’il venait de Barus, appelé Fansur par les Arabes, un port de la côte ouest de Sumatra. Il voyagea beaucoup, dans la péninsule malaise, en Inde moghole, à La Mecque, à Médine et à Bagdad, et aurait été initié à une confrérie soufie.&lt;/p&gt; &lt;p&gt;Il est le premier à exprimer en malais la doctrine de l’« unicité de l’être » (&lt;a href="https://fr.wikipedia.org/wiki/Wahdat_al-wujud" title=" Wikipedia"&gt;&lt;em&gt;wahdat al-wujud&lt;/em&gt;&lt;/a&gt;) issue d’&lt;a href="https://fr.wikipedia.org/wiki/Ibn_Arabi" title=" Wikipedia"&gt;Ibn Arabî&lt;/a&gt; : toute réalité est une, et Dieu se manifeste en toutes choses, par degrés successifs, jusqu’à l’« Homme parfait » et au cœur de chacun, qui doit le retrouver en lui-même. Il le dit dans des poèmes de forme nouvelle, les &lt;em&gt;syair&lt;/em&gt;, dont il est considéré comme l’inventeur, et dans trois traités en prose, dont &lt;em&gt;La Boisson des amants&lt;/em&gt; et &lt;em&gt;Les Secrets des gnostiques&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Au XVIIe siècle, sous l’influence du théologien Nuruddin ar-Raniri, son enseignement fut jugé hérétique à la cour du sultanat d’&lt;a href="https://fr.wikipedia.org/wiki/Aceh" title=" Wikipedia"&gt;Aceh&lt;/a&gt;, car il semblait confondre Dieu et sa création, et ses livres furent brûlés. Une trentaine de ses poèmes ont pourtant survécu. Leur virtuosité, l’art d’y fondre les mots arabes dans la langue malaise et leur goût du jeu de mots font de lui le fondateur de la poésie malaise. Le philosophe Naquib al-Attas lui a consacré sa thèse de doctorat, qui a contribué à le faire redécouvrir.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Rizal" title=" Wikipedia"&gt;José RIZAL&lt;/a&gt; est le héros national des Philippines, écrivain, médecin et penseur de l’émancipation de son peuple sous la domination espagnole. Né à Calamba dans une famille aisée, il étudie à Manille puis en Europe, à Madrid, Paris et Heidelberg, où il devient ophtalmologiste. Polyglotte, il parle une vingtaine de langues et traduit Schiller en tagalog. Il appartient aux &lt;em&gt;ilustrados&lt;/em&gt;, la jeune élite philippine instruite en Europe et nourrie des idées libérales. Il réédite même une chronique espagnole du XVIe siècle pour montrer que les Philippins avaient une civilisation avant la conquête.&lt;/p&gt; &lt;p&gt;Son roman &lt;a href="https://fr.wikipedia.org/wiki/Noli_me_tangere_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Noli me tangere&lt;/em&gt;&lt;/a&gt;, publié à Berlin en 1887, puis sa suite, &lt;em&gt;El Filibusterismo&lt;/em&gt; (1891), dont le titre, emprunté à l’Évangile (« Ne me touche pas »), désigne un mal si sensible qu’on n’ose y toucher, dénoncent les abus des ordres religieux et de l’administration coloniale, l’ignorance entretenue et le mépris des « indios ». Rizal croit d’abord à la réforme plutôt qu’à la révolution : il demande l’égalité des droits, la représentation des Philippines aux Cortes espagnoles et surtout l’éducation, car un peuple ne peut être libre s’il n’a pas appris à penser par lui-même et à se respecter.&lt;/p&gt; &lt;p&gt;De retour aux Philippines en 1892, il fonde la Ligue philippine, une association réformiste et pacifique, ce qui lui vaut d’être exilé à Dapitan, où il ouvre une école et un dispensaire. Accusé à tort d’avoir inspiré l’insurrection de 1896, qu’il n’approuvait pas, il est fusillé à Manille le 30 décembre 1896, à trente-cinq ans. La veille, il écrit son poème d’adieu, &lt;em&gt;Mi último adiós&lt;/em&gt;. Sa mort accélère la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution philippine&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fansuri-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/rizal-mini.webp</t>
         </is>
       </c>
       <c r="J267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indonésienne</t>
+          <t xml:space="preserve">Philippine</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soufisme</t>
+          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète soufi de Sumatra, premier grand auteur mystique de langue malaise.</t>
+          <t xml:space="preserve">écrivain, médecin et humaniste philippin, héros national, critique de la domination coloniale espagnole.</t>
         </is>
       </c>
       <c r="O267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="P267" s="1">
@@ -17914,31 +17925,31 @@
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1861 – 1896</t>
+          <t xml:space="preserve">1864 – 1903</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">José RIZAL</t>
+          <t xml:space="preserve">Apolinario MABINI</t>
         </is>
       </c>
       <c r="E268" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jos%C3%A9_Rizal" title=" Wikipedia"&gt;José RIZAL&lt;/a&gt; est le héros national des Philippines, écrivain, médecin et penseur de l’émancipation de son peuple sous la domination espagnole. Né à Calamba dans une famille aisée, il étudie à Manille puis en Europe, à Madrid, Paris et Heidelberg, où il devient ophtalmologiste. Polyglotte, il parle une vingtaine de langues et traduit Schiller en tagalog. Il appartient aux &lt;em&gt;ilustrados&lt;/em&gt;, la jeune élite philippine instruite en Europe et nourrie des idées libérales. Il réédite même une chronique espagnole du XVIe siècle pour montrer que les Philippins avaient une civilisation avant la conquête.&lt;/p&gt; &lt;p&gt;Son roman &lt;a href="https://fr.wikipedia.org/wiki/Noli_me_tangere_%28roman%29" title=" Wikipedia"&gt;&lt;em&gt;Noli me tangere&lt;/em&gt;&lt;/a&gt;, publié à Berlin en 1887, puis sa suite, &lt;em&gt;El Filibusterismo&lt;/em&gt; (1891), dont le titre, emprunté à l’Évangile (« Ne me touche pas »), désigne un mal si sensible qu’on n’ose y toucher, dénoncent les abus des ordres religieux et de l’administration coloniale, l’ignorance entretenue et le mépris des « indios ». Rizal croit d’abord à la réforme plutôt qu’à la révolution : il demande l’égalité des droits, la représentation des Philippines aux Cortes espagnoles et surtout l’éducation, car un peuple ne peut être libre s’il n’a pas appris à penser par lui-même et à se respecter.&lt;/p&gt; &lt;p&gt;De retour aux Philippines en 1892, il fonde la Ligue philippine, une association réformiste et pacifique, ce qui lui vaut d’être exilé à Dapitan, où il ouvre une école et un dispensaire. Accusé à tort d’avoir inspiré l’insurrection de 1896, qu’il n’approuvait pas, il est fusillé à Manille le 30 décembre 1896, à trente-cinq ans. La veille, il écrit son poème d’adieu, &lt;em&gt;Mi último adiós&lt;/em&gt;. Sa mort accélère la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution philippine&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apolinario_Mabini" title=" Wikipedia"&gt;Apolinario MABINI&lt;/a&gt; est le principal penseur politique de la révolution philippine, surnommé « le cerveau de la révolution ». Fils de paysans pauvres de Tanauan, il fait ses études grâce à des bourses et à des leçons qu’il donne pour vivre, puis obtient en 1894 un diplôme de droit, choisi pour défendre les pauvres. Peu avant la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution de 1896&lt;/a&gt;, il perd l’usage de ses deux jambes, sans doute à cause de la polio : c’est sur une chaise à porteurs qu’il accomplira toute son action politique.&lt;/p&gt; &lt;p&gt;Conseiller d’Emilio Aguinaldo, il rédige en 1898 &lt;em&gt;Le Vrai Décalogue&lt;/em&gt;, dix commandements civiques qui mêlent devoirs envers Dieu, envers la patrie et envers autrui : aimer sa patrie, ne reconnaître pour chef que celui qui est élu par le peuple, voir en chacun un égal. Son &lt;em&gt;Programme constitutionnel de la République philippine&lt;/em&gt; inspire la Constitution de Malolos. En 1899, il devient le premier chef du gouvernement de la Première République philippine, et défend une souveraineté populaire fondée sur la raison et sur la morale plutôt que sur la force. Opposé au pouvoir personnel, il entre en conflit avec Aguinaldo et doit démissionner la même année.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre les États-Unis, il est capturé puis exilé sur l’île de Guam, où il écrit &lt;em&gt;La Révolution philippine&lt;/em&gt;, où il attribue l’échec du mouvement aux divisions et à l’ambition de ses chefs plus qu’à la seule force de l’ennemi. Autorisé à rentrer en 1903 après avoir prêté serment d’allégeance aux Américains, il meurt du choléra à Manille quelques mois plus tard, à trente-huit ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/rizal-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mabini-mini.webp</t>
         </is>
       </c>
       <c r="J268" s="1" t="inlineStr">
@@ -17953,12 +17964,12 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Humanisme</t>
+          <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain, médecin et humaniste philippin, héros national, critique de la domination coloniale espagnole.</t>
+          <t xml:space="preserve">juriste et penseur de la révolution philippine, premier chef du gouvernement des Philippines, surnommé « le cerveau de la révolution ».</t>
         </is>
       </c>
       <c r="O268" s="1" t="inlineStr">
@@ -17972,41 +17983,41 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1">
-        <v>1864</v>
+        <v>1889</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864 – 1903</t>
+          <t xml:space="preserve">1889 – 1959</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apolinario MABINI</t>
+          <t xml:space="preserve">KI HAJAR DEWANTARA</t>
         </is>
       </c>
       <c r="E269" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Apolinario_Mabini" title=" Wikipedia"&gt;Apolinario MABINI&lt;/a&gt; est le principal penseur politique de la révolution philippine, surnommé « le cerveau de la révolution ». Fils de paysans pauvres de Tanauan, il fait ses études grâce à des bourses et à des leçons qu’il donne pour vivre, puis obtient en 1894 un diplôme de droit, choisi pour défendre les pauvres. Peu avant la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_philippine" title=" Wikipedia"&gt;révolution de 1896&lt;/a&gt;, il perd l’usage de ses deux jambes, sans doute à cause de la polio : c’est sur une chaise à porteurs qu’il accomplira toute son action politique.&lt;/p&gt; &lt;p&gt;Conseiller d’Emilio Aguinaldo, il rédige en 1898 &lt;em&gt;Le Vrai Décalogue&lt;/em&gt;, dix commandements civiques qui mêlent devoirs envers Dieu, envers la patrie et envers autrui : aimer sa patrie, ne reconnaître pour chef que celui qui est élu par le peuple, voir en chacun un égal. Son &lt;em&gt;Programme constitutionnel de la République philippine&lt;/em&gt; inspire la Constitution de Malolos. En 1899, il devient le premier chef du gouvernement de la Première République philippine, et défend une souveraineté populaire fondée sur la raison et sur la morale plutôt que sur la force. Opposé au pouvoir personnel, il entre en conflit avec Aguinaldo et doit démissionner la même année.&lt;/p&gt; &lt;p&gt;Pendant la guerre contre les États-Unis, il est capturé puis exilé sur l’île de Guam, où il écrit &lt;em&gt;La Révolution philippine&lt;/em&gt;, où il attribue l’échec du mouvement aux divisions et à l’ambition de ses chefs plus qu’à la seule force de l’ennemi. Autorisé à rentrer en 1903 après avoir prêté serment d’allégeance aux Américains, il meurt du choléra à Manille quelques mois plus tard, à trente-huit ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ki_Hajar_Dewantara" title=" Wikipedia"&gt;KI HAJAR DEWANTARA&lt;/a&gt; est le grand penseur de l’éducation indonésienne. Né à Yogyakarta sous le nom de Raden Mas Soewardi Soerjaningrat, petit-fils d’un prince javanais, il devient journaliste et militant nationaliste, et cofonde en 1912 l’Indische Partij, premier parti à réclamer l’indépendance. Il est l’un des premiers à employer le nom d’« Indonésie ». En 1913, son article ironique « Si j’étais Néerlandais », qui raille les fêtes organisées dans la colonie pour célébrer l’indépendance des Pays-Bas, lui vaut d’être exilé en Europe. Il y découvre les pédagogies de Fröbel et de Montessori, ainsi que l’école de Tagore en Inde.&lt;/p&gt; &lt;p&gt;De retour, il fonde en 1922 à Yogyakarta le &lt;a href="https://fr.wikipedia.org/wiki/Taman_Siswa" title=" Wikipedia"&gt;Taman Siswa&lt;/a&gt; (« jardin des élèves »), un réseau d’écoles indépendantes du pouvoir colonial, qui enseignent à la fois les savoirs modernes et la culture javanaise. La même année, il abandonne son titre aristocratique pour le nom plus simple de Ki Hajar Dewantara. Pour lui, l’éducation ne consiste pas à remplir les esprits, mais à « guider les forces naturelles » de l’enfant pour qu’il devienne un être libre, autonome et responsable envers sa communauté.&lt;/p&gt; &lt;p&gt;Sa devise résume le rôle du maître : « Devant, donner l’exemple ; au milieu, susciter la volonté ; derrière, soutenir. » Sa dernière partie, &lt;em&gt;Tut wuri handayani&lt;/em&gt;, est aujourd’hui celle du ministère indonésien de l’Éducation. Premier ministre de l’Éducation de l’Indonésie indépendante, il est proclamé héros national en 1959, et le jour de sa naissance, le 2 mai, est devenu la Journée nationale de l’éducation.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/mabini-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dewantara-mini.webp</t>
         </is>
       </c>
       <c r="J269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippine</t>
+          <t xml:space="preserve">Indonésienne</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L269" s="2" t="inlineStr">
@@ -18016,7 +18027,7 @@
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">juriste et penseur de la révolution philippine, premier chef du gouvernement des Philippines, surnommé « le cerveau de la révolution ».</t>
+          <t xml:space="preserve">pédagogue et militant indonésien, fondateur des écoles Taman Siswa, père de l’éducation nationale.</t>
         </is>
       </c>
       <c r="O269" s="1" t="inlineStr">
@@ -18030,31 +18041,31 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1">
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">1949</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889 – 1959</t>
+          <t xml:space="preserve">1897 – 1949</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KI HAJAR DEWANTARA</t>
+          <t xml:space="preserve">TAN MALAKA</t>
         </is>
       </c>
       <c r="E270" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ki_Hajar_Dewantara" title=" Wikipedia"&gt;KI HAJAR DEWANTARA&lt;/a&gt; est le grand penseur de l’éducation indonésienne. Né à Yogyakarta sous le nom de Raden Mas Soewardi Soerjaningrat, petit-fils d’un prince javanais, il devient journaliste et militant nationaliste, et cofonde en 1912 l’Indische Partij, premier parti à réclamer l’indépendance. Il est l’un des premiers à employer le nom d’« Indonésie ». En 1913, son article ironique « Si j’étais Néerlandais », qui raille les fêtes organisées dans la colonie pour célébrer l’indépendance des Pays-Bas, lui vaut d’être exilé en Europe. Il y découvre les pédagogies de Fröbel et de Montessori, ainsi que l’école de Tagore en Inde.&lt;/p&gt; &lt;p&gt;De retour, il fonde en 1922 à Yogyakarta le &lt;a href="https://fr.wikipedia.org/wiki/Taman_Siswa" title=" Wikipedia"&gt;Taman Siswa&lt;/a&gt; (« jardin des élèves »), un réseau d’écoles indépendantes du pouvoir colonial, qui enseignent à la fois les savoirs modernes et la culture javanaise. La même année, il abandonne son titre aristocratique pour le nom plus simple de Ki Hajar Dewantara. Pour lui, l’éducation ne consiste pas à remplir les esprits, mais à « guider les forces naturelles » de l’enfant pour qu’il devienne un être libre, autonome et responsable envers sa communauté.&lt;/p&gt; &lt;p&gt;Sa devise résume le rôle du maître : « Devant, donner l’exemple ; au milieu, susciter la volonté ; derrière, soutenir. » Sa dernière partie, &lt;em&gt;Tut wuri handayani&lt;/em&gt;, est aujourd’hui celle du ministère indonésien de l’Éducation. Premier ministre de l’Éducation de l’Indonésie indépendante, il est proclamé héros national en 1959, et le jour de sa naissance, le 2 mai, est devenu la Journée nationale de l’éducation.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tan_Malaka" title=" Wikipedia"&gt;TAN MALAKA&lt;/a&gt; est un révolutionnaire et penseur indonésien, l’un des premiers à concevoir une république indonésienne indépendante. Né dans le pays minangkabau, à Sumatra, il étudie pour devenir instituteur, puis aux Pays-Bas, où il découvre le marxisme et la révolution russe. Rentré en 1919, il enseigne aux enfants des ouvriers des plantations puis prend en 1921 la tête du Parti communiste indonésien. Arrêté et banni dès 1922, il passe plus de vingt ans en exil et dans la clandestinité, en Europe, en Chine, aux Philippines et à Singapour, comme agent de l’Internationale communiste.&lt;/p&gt; &lt;p&gt;Son livre le plus important, &lt;em&gt;Madilog&lt;/em&gt; (1943), dont le titre réunit matérialisme, dialectique et logique, veut libérer ses compatriotes de ce qu’il appelle la « logique mystique » : l’habitude d’expliquer les événements par des forces surnaturelles, des esprits ou le destin, qui selon lui entretient la passivité face à l’oppression. Il leur oppose la méthode scientifique et la pensée critique, condition d’une véritable indépendance. Il refuse aussi d’opposer l’islam et le communisme, deux forces qu’il voulait unir contre le colonialisme.&lt;/p&gt; &lt;p&gt;Revenu en Indonésie pendant la révolution, il s’oppose aux négociations avec les Pays-Bas menées par le gouvernement de &lt;a href="https://fr.wikipedia.org/wiki/Soekarno" title=" Wikipedia"&gt;Soekarno&lt;/a&gt;, que ses écrits avaient pourtant inspiré, et réclame une « indépendance à cent pour cent ». En février 1949, il est capturé et exécuté par des soldats de l’armée indonésienne. Longtemps passé sous silence, il a été proclamé héros national en 1963.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/dewantara-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/tanmalaka-mini.webp</t>
         </is>
       </c>
       <c r="J270" s="1" t="inlineStr">
@@ -18064,17 +18075,17 @@
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">politique ; epistemologie</t>
         </is>
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme</t>
+          <t xml:space="preserve">Marxisme ; Anticolonialisme</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pédagogue et militant indonésien, fondateur des écoles Taman Siswa, père de l’éducation nationale.</t>
+          <t xml:space="preserve">révolutionnaire indonésien, marxiste indépendant, auteur de Madilog, critique de la « logique mystique ».</t>
         </is>
       </c>
       <c r="O270" s="1" t="inlineStr">
@@ -18088,56 +18099,61 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1">
-        <v>1897</v>
+        <v>1926</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1949</t>
+          <t xml:space="preserve">2022</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897 – 1949</t>
+          <t xml:space="preserve">1926 – 2022</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAN MALAKA</t>
+          <t xml:space="preserve">THICH NHAT HANH</t>
         </is>
       </c>
       <c r="E271" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tan_Malaka" title=" Wikipedia"&gt;TAN MALAKA&lt;/a&gt; est un révolutionnaire et penseur indonésien, l’un des premiers à concevoir une république indonésienne indépendante. Né dans le pays minangkabau, à Sumatra, il étudie pour devenir instituteur, puis aux Pays-Bas, où il découvre le marxisme et la révolution russe. Rentré en 1919, il enseigne aux enfants des ouvriers des plantations puis prend en 1921 la tête du Parti communiste indonésien. Arrêté et banni dès 1922, il passe plus de vingt ans en exil et dans la clandestinité, en Europe, en Chine, aux Philippines et à Singapour, comme agent de l’Internationale communiste.&lt;/p&gt; &lt;p&gt;Son livre le plus important, &lt;em&gt;Madilog&lt;/em&gt; (1943), dont le titre réunit matérialisme, dialectique et logique, veut libérer ses compatriotes de ce qu’il appelle la « logique mystique » : l’habitude d’expliquer les événements par des forces surnaturelles, des esprits ou le destin, qui selon lui entretient la passivité face à l’oppression. Il leur oppose la méthode scientifique et la pensée critique, condition d’une véritable indépendance. Il refuse aussi d’opposer l’islam et le communisme, deux forces qu’il voulait unir contre le colonialisme.&lt;/p&gt; &lt;p&gt;Revenu en Indonésie pendant la révolution, il s’oppose aux négociations avec les Pays-Bas menées par le gouvernement de &lt;a href="https://fr.wikipedia.org/wiki/Soekarno" title=" Wikipedia"&gt;Soekarno&lt;/a&gt;, que ses écrits avaient pourtant inspiré, et réclame une « indépendance à cent pour cent ». En février 1949, il est capturé et exécuté par des soldats de l’armée indonésienne. Longtemps passé sous silence, il a été proclamé héros national en 1963.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%ADch_Nh%E1%BA%A5t_H%E1%BA%A1nh" title=" Wikipedia"&gt;THICH NHAT HANH&lt;/a&gt; est un moine bouddhiste zen vietnamien, militant pour la paix et l’un des maîtres spirituels les plus connus en Occident. Né à Huế, il entre à seize ans au temple de Từ Hiếu. Pendant la guerre du Vietnam, il refuse de choisir un camp et fonde une école de jeunes pour le service social, qui reconstruit les villages bombardés. Il forge l’expression de « bouddhisme engagé » : la méditation ne doit pas détourner du monde, mais aider à soulager la souffrance là où elle se trouve.&lt;/p&gt; &lt;p&gt;En 1966, lors d’une tournée pour la paix aux États-Unis, il rencontre Martin Luther King, qui le propose l’année suivante pour le prix Nobel de la paix. Interdit de retour dans son pays, il vit en exil en France, où il fonde en 1982, en Dordogne, le Village des Pruniers, qui devient le plus grand monastère bouddhiste d’Europe. Il enseigne la &lt;a href="https://fr.wikipedia.org/wiki/Pleine_conscience" title=" Wikipedia"&gt;pleine conscience&lt;/a&gt; dans les gestes les plus simples, marcher, respirer, laver la vaisselle, comme dans &lt;em&gt;Le Miracle de la pleine conscience&lt;/em&gt; (1975).&lt;/p&gt; &lt;p&gt;Au cœur de sa pensée se trouve l’« inter-être » : rien n’existe par soi seul. Dans une feuille de papier, dit-il, on peut voir le nuage, la pluie, l’arbre et le bûcheron, sans lesquels elle ne serait pas. Comprendre que nous « inter-sommes » fonde la compassion et la non-violence. Auteur de plus d’une centaine de livres, il fonde dès 1966 l’Ordre de l’inter-être, qui réunit moines, moniales et laïcs. Rentré au Vietnam en 2018, il meurt au temple de Từ Hiếu, à Huế, en 2022, à quatre-vingt-quinze ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/tanmalaka-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/thichnhathanh-mini.webp</t>
         </is>
       </c>
       <c r="J271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indonésienne</t>
+          <t xml:space="preserve">Vietnamienne</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme ; Anticolonialisme</t>
+          <t xml:space="preserve">Bouddhisme Zen ; Bouddhisme Mahayana</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">révolutionnaire indonésien, marxiste indépendant, auteur de Madilog, critique de la « logique mystique ».</t>
+          <t xml:space="preserve">moine zen vietnamien, militant pour la paix, maître de la pleine conscience et du « bouddhisme engagé ».</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="O271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
       <c r="P271" s="1">
@@ -18146,61 +18162,56 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1">
-        <v>1926</v>
+        <v>1931</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022</t>
+          <t xml:space="preserve">2026</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926 – 2022</t>
+          <t xml:space="preserve">1931 – 2026</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">THICH NHAT HANH</t>
+          <t xml:space="preserve">Syed Muhammad Naquib AL-ATTAS</t>
         </is>
       </c>
       <c r="E272" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%ADch_Nh%E1%BA%A5t_H%E1%BA%A1nh" title=" Wikipedia"&gt;THICH NHAT HANH&lt;/a&gt; est un moine bouddhiste zen vietnamien, militant pour la paix et l’un des maîtres spirituels les plus connus en Occident. Né à Huế, il entre à seize ans au temple de Từ Hiếu. Pendant la guerre du Vietnam, il refuse de choisir un camp et fonde une école de jeunes pour le service social, qui reconstruit les villages bombardés. Il forge l’expression de « bouddhisme engagé » : la méditation ne doit pas détourner du monde, mais aider à soulager la souffrance là où elle se trouve.&lt;/p&gt; &lt;p&gt;En 1966, lors d’une tournée pour la paix aux États-Unis, il rencontre Martin Luther King, qui le propose l’année suivante pour le prix Nobel de la paix. Interdit de retour dans son pays, il vit en exil en France, où il fonde en 1982, en Dordogne, le Village des Pruniers, qui devient le plus grand monastère bouddhiste d’Europe. Il enseigne la &lt;a href="https://fr.wikipedia.org/wiki/Pleine_conscience" title=" Wikipedia"&gt;pleine conscience&lt;/a&gt; dans les gestes les plus simples, marcher, respirer, laver la vaisselle, comme dans &lt;em&gt;Le Miracle de la pleine conscience&lt;/em&gt; (1975).&lt;/p&gt; &lt;p&gt;Au cœur de sa pensée se trouve l’« inter-être » : rien n’existe par soi seul. Dans une feuille de papier, dit-il, on peut voir le nuage, la pluie, l’arbre et le bûcheron, sans lesquels elle ne serait pas. Comprendre que nous « inter-sommes » fonde la compassion et la non-violence. Auteur de plus d’une centaine de livres, il fonde dès 1966 l’Ordre de l’inter-être, qui réunit moines, moniales et laïcs. Rentré au Vietnam en 2018, il meurt au temple de Từ Hiếu, à Huế, en 2022, à quatre-vingt-quinze ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Syed_Muhammad_Naquib_al-Attas" title=" Wikipedia (en)"&gt;Syed Muhammad Naquib AL-ATTAS&lt;/a&gt; est un philosophe musulman malaisien, l’un des penseurs les plus influents de l’islam contemporain en Asie du Sud-Est. Né à Bogor, à Java, dans une famille de descendants du Prophète venus de l’Hadramaout, il est d’abord officier, formé à l’académie militaire de Sandhurst, en Angleterre, avant de quitter l’armée pour les études. Il étudie à Singapour, à l’université McGill de Montréal, puis à Londres, où il consacre sa thèse de doctorat au mystique &lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;Hamzah Fansuri&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Islam et la sécularisation&lt;/em&gt; (1978), il soutient que la crise du monde musulman n’est pas d’abord politique ou économique, mais intellectuelle : c’est une « perte de l’&lt;em&gt;adab&lt;/em&gt; », c’est-à-dire du sens de la juste place de chaque chose, de chaque savoir et de chaque personne. La science moderne, venue d’Occident, n’est pas neutre selon lui : elle porte une vision du monde sécularisée, qui coupe la connaissance de toute finalité spirituelle. D’où son projet d’« islamisation de la connaissance », qui veut repenser les savoirs modernes à partir de la métaphysique de l’islam.&lt;/p&gt; &lt;p&gt;L’éducation, qu’il appelle &lt;em&gt;ta’dib&lt;/em&gt;, doit former un homme bon, et non seulement un bon citoyen ou un bon producteur. Il fonde en 1987 à Kuala Lumpur l’Institut international de pensée et de civilisation islamiques, dont il dessine même l’architecture. Historien de la langue et de la littérature malaises, il montre aussi le rôle de l’islam dans la formation du monde malais. Il meurt en mars 2026, à quatre-vingt-quatorze ans.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/thichnhathanh-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alattas-mini.webp</t>
         </is>
       </c>
       <c r="J272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vietnamienne</t>
+          <t xml:space="preserve">Malaisienne</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">epistemologie ; spiritualite</t>
         </is>
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen ; Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Soufisme</t>
         </is>
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">moine zen vietnamien, militant pour la paix, maître de la pleine conscience et du « bouddhisme engagé ».</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">philosophe musulman malaisien, penseur de l’« islamisation de la connaissance » et de l’éducation comme adab.</t>
         </is>
       </c>
       <c r="O272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asie-est</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P272" s="1">
@@ -18209,147 +18220,147 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026</t>
+          <t xml:space="preserve">2011</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931 – 2026</t>
+          <t xml:space="preserve">1928 – 2011</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syed Muhammad Naquib AL-ATTAS</t>
+          <t xml:space="preserve">Édouard GLISSANT</t>
         </is>
       </c>
       <c r="E273" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Syed_Muhammad_Naquib_al-Attas" title=" Wikipedia (en)"&gt;Syed Muhammad Naquib AL-ATTAS&lt;/a&gt; est un philosophe musulman malaisien, l’un des penseurs les plus influents de l’islam contemporain en Asie du Sud-Est. Né à Bogor, à Java, dans une famille de descendants du Prophète venus de l’Hadramaout, il est d’abord officier, formé à l’académie militaire de Sandhurst, en Angleterre, avant de quitter l’armée pour les études. Il étudie à Singapour, à l’université McGill de Montréal, puis à Londres, où il consacre sa thèse de doctorat au mystique &lt;a href="https://en.wikipedia.org/wiki/Hamzah_Fansuri" title=" Wikipedia (en)"&gt;Hamzah Fansuri&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Islam et la sécularisation&lt;/em&gt; (1978), il soutient que la crise du monde musulman n’est pas d’abord politique ou économique, mais intellectuelle : c’est une « perte de l’&lt;em&gt;adab&lt;/em&gt; », c’est-à-dire du sens de la juste place de chaque chose, de chaque savoir et de chaque personne. La science moderne, venue d’Occident, n’est pas neutre selon lui : elle porte une vision du monde sécularisée, qui coupe la connaissance de toute finalité spirituelle. D’où son projet d’« islamisation de la connaissance », qui veut repenser les savoirs modernes à partir de la métaphysique de l’islam.&lt;/p&gt; &lt;p&gt;L’éducation, qu’il appelle &lt;em&gt;ta’dib&lt;/em&gt;, doit former un homme bon, et non seulement un bon citoyen ou un bon producteur. Il fonde en 1987 à Kuala Lumpur l’Institut international de pensée et de civilisation islamiques, dont il dessine même l’architecture. Historien de la langue et de la littérature malaises, il montre aussi le rôle de l’islam dans la formation du monde malais. Il meurt en mars 2026, à quatre-vingt-quatorze ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Glissant" title=" Wikipedia"&gt;Édouard GLISSANT&lt;/a&gt; est un poète, romancier et philosophe martiniquais, l’un des penseurs majeurs des Caraïbes et de la mondialisation. Né à Sainte-Marie, en &lt;a href="https://fr.wikipedia.org/wiki/Martinique" title=" Wikipedia"&gt;Martinique&lt;/a&gt;, il étudie la philosophie à la Sorbonne et l’ethnologie au musée de l’Homme. Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/La_L%C3%A9zarde" title=" Wikipedia"&gt;&lt;em&gt;La Lézarde&lt;/em&gt;&lt;/a&gt;, reçoit le prix Renaudot en 1958. Militant de la décolonisation, il cofonde en 1961 un front pour l’autonomie des Antilles, ce qui lui vaut d’être interdit de retour en Martinique pendant plusieurs années. Il participe aussi aux congrès des écrivains et artistes noirs de 1956 et 1959.&lt;/p&gt; &lt;p&gt;Héritier de Césaire, il veut dépasser la négritude, qui cherche une origine africaine perdue. Dans &lt;em&gt;Le Discours antillais&lt;/em&gt; (1981), il propose l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : une identité née du mélange, de la plantation et de l’oubli, qui ne se réduit à aucune racine unique. Il oppose l’« identité-racine », exclusive et fondée sur une seule origine, à l’« identité-relation », ouverte à l’autre, et la pensée de « système », qui veut tout ramener à l’unité, à la « pensée de l’archipel », attentive aux liens entre des îles toutes différentes.&lt;/p&gt; &lt;p&gt;La « créolisation » est pour lui le mouvement même du monde actuel : des cultures se rencontrent et produisent du nouveau, de manière imprévisible. Dans &lt;a href="https://fr.wikipedia.org/wiki/Po%C3%A9tique_de_la_Relation" title=" Wikipedia"&gt;&lt;em&gt;Poétique de la Relation&lt;/em&gt;&lt;/a&gt; (1990), il défend un « droit à l’opacité » : comprendre l’autre ne doit pas signifier le réduire à soi. Directeur du &lt;em&gt;Courrier de l’UNESCO&lt;/em&gt; de 1981 à 1988, puis professeur à New York, il fonde en 2006 à Paris l’Institut du &lt;a href="https://fr.wikipedia.org/wiki/Tout-Monde" title=" Wikipedia"&gt;Tout-Monde&lt;/a&gt; et meurt en 2011.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/alattas-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/glissant-mini.webp</t>
         </is>
       </c>
       <c r="J273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malaisienne</t>
+          <t xml:space="preserve">Martiniquaise</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; spiritualite</t>
+          <t xml:space="preserve">esthetique ; politique</t>
         </is>
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soufisme</t>
+          <t xml:space="preserve">Anticolonialisme ; Créolisation</t>
         </is>
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe musulman malaisien, penseur de l’« islamisation de la connaissance » et de l’éducation comme adab.</t>
+          <t xml:space="preserve">poète, romancier et philosophe martiniquais, penseur de la Relation, de la créolisation et du Tout-monde.</t>
         </is>
       </c>
       <c r="O273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="P273" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1">
-        <v>1928</v>
+        <v>1052</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">1135</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928 – 2011</t>
+          <t xml:space="preserve">1052 – 1135</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Édouard GLISSANT</t>
+          <t xml:space="preserve">MILARÉPA</t>
         </is>
       </c>
       <c r="E274" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89douard_Glissant" title=" Wikipedia"&gt;Édouard GLISSANT&lt;/a&gt; est un poète, romancier et philosophe martiniquais, l’un des penseurs majeurs des Caraïbes et de la mondialisation. Né à Sainte-Marie, en &lt;a href="https://fr.wikipedia.org/wiki/Martinique" title=" Wikipedia"&gt;Martinique&lt;/a&gt;, il étudie la philosophie à la Sorbonne et l’ethnologie au musée de l’Homme. Son premier roman, &lt;a href="https://fr.wikipedia.org/wiki/La_L%C3%A9zarde" title=" Wikipedia"&gt;&lt;em&gt;La Lézarde&lt;/em&gt;&lt;/a&gt;, reçoit le prix Renaudot en 1958. Militant de la décolonisation, il cofonde en 1961 un front pour l’autonomie des Antilles, ce qui lui vaut d’être interdit de retour en Martinique pendant plusieurs années. Il participe aussi aux congrès des écrivains et artistes noirs de 1956 et 1959.&lt;/p&gt; &lt;p&gt;Héritier de Césaire, il veut dépasser la négritude, qui cherche une origine africaine perdue. Dans &lt;em&gt;Le Discours antillais&lt;/em&gt; (1981), il propose l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : une identité née du mélange, de la plantation et de l’oubli, qui ne se réduit à aucune racine unique. Il oppose l’« identité-racine », exclusive et fondée sur une seule origine, à l’« identité-relation », ouverte à l’autre, et la pensée de « système », qui veut tout ramener à l’unité, à la « pensée de l’archipel », attentive aux liens entre des îles toutes différentes.&lt;/p&gt; &lt;p&gt;La « créolisation » est pour lui le mouvement même du monde actuel : des cultures se rencontrent et produisent du nouveau, de manière imprévisible. Dans &lt;a href="https://fr.wikipedia.org/wiki/Po%C3%A9tique_de_la_Relation" title=" Wikipedia"&gt;&lt;em&gt;Poétique de la Relation&lt;/em&gt;&lt;/a&gt; (1990), il défend un « droit à l’opacité » : comprendre l’autre ne doit pas signifier le réduire à soi. Directeur du &lt;em&gt;Courrier de l’UNESCO&lt;/em&gt; de 1981 à 1988, puis professeur à New York, il fonde en 2006 à Paris l’Institut du &lt;a href="https://fr.wikipedia.org/wiki/Tout-Monde" title=" Wikipedia"&gt;Tout-Monde&lt;/a&gt; et meurt en 2011.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Milar%C3%A9pa" title=" Wikipedia"&gt;MILARÉPA&lt;/a&gt; est un yogi et poète tibétain, devenu l’un des plus grands saints du bouddhisme tibétain. Selon sa célèbre biographie, rédigée au XVe siècle, son père meurt alors qu’il est enfant, et son oncle et sa tante s’emparent des biens de la famille, réduisant sa mère et sa sœur à la misère. Poussé par sa mère à se venger, il apprend la magie noire et fait périr plusieurs personnes en provoquant l’effondrement d’une maison et une tempête de grêle.&lt;/p&gt; &lt;p&gt;Rongé par le remords, il cherche un maître et trouve &lt;a href="https://fr.wikipedia.org/wiki/Marpa_le_Traducteur" title=" Wikipedia"&gt;Marpa le Traducteur&lt;/a&gt;, qui avait rapporté de l’Inde les enseignements de Naropa. Pendant des années, Marpa lui impose des épreuves terribles, comme bâtir puis démolir plusieurs fois des tours de pierre, pour le purifier de ses fautes avant de lui transmettre son enseignement. Milarépa se retire alors dans des grottes de l’Himalaya, où il médite pendant des années dans le froid et la solitude, vêtu d’un simple tissu de coton, d’où son nom de « Mila le vêtu de coton », et se nourrit, dit-on, d’orties, au point que sa peau en devient verte.&lt;/p&gt; &lt;p&gt;Il atteint l’éveil en une seule vie, montrant que même un grand criminel peut se transformer. Il enseigne par des chants improvisés, réunis dans les &lt;em&gt;Cent Mille Chants&lt;/em&gt;, où il parle de l’impermanence, de la mort et de la nature de l’esprit avec une liberté et une simplicité qui en font l’un des poètes les plus aimés du Tibet. Sa vie, contée dans &lt;em&gt;La Vie de Milarépa&lt;/em&gt;, a été comparée aux Évangiles. Il est l’un des fondateurs de l’école &lt;a href="https://fr.wikipedia.org/wiki/Kagy%C3%BCpa" title=" Wikipedia"&gt;Kagyü&lt;/a&gt;, que développera son disciple Gampopa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/glissant-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/milarepa-mini.webp</t>
         </is>
       </c>
       <c r="J274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martiniquaise</t>
+          <t xml:space="preserve">Tibétaine</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">esthetique ; politique</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme ; Créolisation</t>
+          <t xml:space="preserve">Vajrayana</t>
         </is>
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">poète, romancier et philosophe martiniquais, penseur de la Relation, de la créolisation et du Tout-monde.</t>
+          <t xml:space="preserve">yogi et poète tibétain, ancien magicien devenu le plus célèbre des saints du Tibet.</t>
         </is>
       </c>
       <c r="O274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="P274" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135</t>
+          <t xml:space="preserve">1153</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052 – 1135</t>
+          <t xml:space="preserve">1079 – 1153</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILARÉPA</t>
+          <t xml:space="preserve">GAMPOPA</t>
         </is>
       </c>
       <c r="E275" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Milar%C3%A9pa" title=" Wikipedia"&gt;MILARÉPA&lt;/a&gt; est un yogi et poète tibétain, devenu l’un des plus grands saints du bouddhisme tibétain. Selon sa célèbre biographie, rédigée au XVe siècle, son père meurt alors qu’il est enfant, et son oncle et sa tante s’emparent des biens de la famille, réduisant sa mère et sa sœur à la misère. Poussé par sa mère à se venger, il apprend la magie noire et fait périr plusieurs personnes en provoquant l’effondrement d’une maison et une tempête de grêle.&lt;/p&gt; &lt;p&gt;Rongé par le remords, il cherche un maître et trouve &lt;a href="https://fr.wikipedia.org/wiki/Marpa_le_Traducteur" title=" Wikipedia"&gt;Marpa le Traducteur&lt;/a&gt;, qui avait rapporté de l’Inde les enseignements de Naropa. Pendant des années, Marpa lui impose des épreuves terribles, comme bâtir puis démolir plusieurs fois des tours de pierre, pour le purifier de ses fautes avant de lui transmettre son enseignement. Milarépa se retire alors dans des grottes de l’Himalaya, où il médite pendant des années dans le froid et la solitude, vêtu d’un simple tissu de coton, d’où son nom de « Mila le vêtu de coton », et se nourrit, dit-on, d’orties, au point que sa peau en devient verte.&lt;/p&gt; &lt;p&gt;Il atteint l’éveil en une seule vie, montrant que même un grand criminel peut se transformer. Il enseigne par des chants improvisés, réunis dans les &lt;em&gt;Cent Mille Chants&lt;/em&gt;, où il parle de l’impermanence, de la mort et de la nature de l’esprit avec une liberté et une simplicité qui en font l’un des poètes les plus aimés du Tibet. Sa vie, contée dans &lt;em&gt;La Vie de Milarépa&lt;/em&gt;, a été comparée aux Évangiles. Il est l’un des fondateurs de l’école &lt;a href="https://fr.wikipedia.org/wiki/Kagy%C3%BCpa" title=" Wikipedia"&gt;Kagyü&lt;/a&gt;, que développera son disciple Gampopa.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gampopa" title=" Wikipedia"&gt;GAMPOPA&lt;/a&gt; est un maître du bouddhisme tibétain, disciple de Milarépa et véritable fondateur de l’école Kagyü. Né dans le sud-est du Tibet, il apprend d’abord la médecine auprès de son père, d’où son surnom de « médecin de Dagpo ». Marié jeune, il perd à quelques jours d’intervalle ses deux enfants, puis sa femme, emportés par une épidémie. Devant sa femme mourante, qu’il ne parvient pas à guérir, il comprend que toute chose est impermanente et lui promet de consacrer sa vie au Dharma.&lt;/p&gt; &lt;p&gt;Devenu moine dans un monastère de l’école Kadampa, connue pour son enseignement rigoureux et progressif, il étudie la discipline monastique et la « voie graduée » vers l’éveil. Ayant entendu parler de Milarépa par des mendiants, il part à sa recherche et reçoit de lui les pratiques de méditation des yogis, notamment celle du &lt;a href="https://fr.wikipedia.org/wiki/Mahamudra" title=" Wikipedia"&gt;mahamudra&lt;/a&gt;, le « grand sceau », qui vise à reconnaître directement la nature de l’esprit.&lt;/p&gt; &lt;p&gt;Son génie est d’unir ces deux traditions : la vie monastique et l’étude méthodique des Kadampas, et l’expérience directe des yogis ermites comme Milarépa. Son traité &lt;em&gt;L’Ornement de la libération&lt;/em&gt; expose pas à pas le chemin, de la prise de conscience de la valeur d’une vie humaine et de l’impermanence jusqu’à l’éveil, en passant par la compassion et les six perfections. Il y rappelle que tous les êtres possèdent la &lt;a href="https://fr.wikipedia.org/wiki/Nature_de_bouddha" title=" Wikipedia"&gt;nature de bouddha&lt;/a&gt;, cause première de l’éveil. Il fonde le monastère de Dagla Gampo, d’où il tire son nom. Ses disciples fondent les quatre grandes branches de l’école Kagyü, dont celle des Karmapas, toujours vivante aujourd’hui.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/milarepa-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gampopa-mini.webp</t>
         </is>
       </c>
       <c r="J275" s="1" t="inlineStr">
@@ -18369,7 +18380,7 @@
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yogi et poète tibétain, ancien magicien devenu le plus célèbre des saints du Tibet.</t>
+          <t xml:space="preserve">médecin devenu moine, disciple de Milarépa, fondateur de l’école Kagyü du bouddhisme tibétain.</t>
         </is>
       </c>
       <c r="O275" s="1" t="inlineStr">
@@ -18383,56 +18394,56 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1">
-        <v>1079</v>
+        <v>1876</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153</t>
+          <t xml:space="preserve">1924</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079 – 1153</t>
+          <t xml:space="preserve">1876 – 1924</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAMPOPA</t>
+          <t xml:space="preserve">Ziya GÖKALP</t>
         </is>
       </c>
       <c r="E276" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gampopa" title=" Wikipedia"&gt;GAMPOPA&lt;/a&gt; est un maître du bouddhisme tibétain, disciple de Milarépa et véritable fondateur de l’école Kagyü. Né dans le sud-est du Tibet, il apprend d’abord la médecine auprès de son père, d’où son surnom de « médecin de Dagpo ». Marié jeune, il perd à quelques jours d’intervalle ses deux enfants, puis sa femme, emportés par une épidémie. Devant sa femme mourante, qu’il ne parvient pas à guérir, il comprend que toute chose est impermanente et lui promet de consacrer sa vie au Dharma.&lt;/p&gt; &lt;p&gt;Devenu moine dans un monastère de l’école Kadampa, connue pour son enseignement rigoureux et progressif, il étudie la discipline monastique et la « voie graduée » vers l’éveil. Ayant entendu parler de Milarépa par des mendiants, il part à sa recherche et reçoit de lui les pratiques de méditation des yogis, notamment celle du &lt;a href="https://fr.wikipedia.org/wiki/Mahamudra" title=" Wikipedia"&gt;mahamudra&lt;/a&gt;, le « grand sceau », qui vise à reconnaître directement la nature de l’esprit.&lt;/p&gt; &lt;p&gt;Son génie est d’unir ces deux traditions : la vie monastique et l’étude méthodique des Kadampas, et l’expérience directe des yogis ermites comme Milarépa. Son traité &lt;em&gt;L’Ornement de la libération&lt;/em&gt; expose pas à pas le chemin, de la prise de conscience de la valeur d’une vie humaine et de l’impermanence jusqu’à l’éveil, en passant par la compassion et les six perfections. Il y rappelle que tous les êtres possèdent la &lt;a href="https://fr.wikipedia.org/wiki/Nature_de_bouddha" title=" Wikipedia"&gt;nature de bouddha&lt;/a&gt;, cause première de l’éveil. Il fonde le monastère de Dagla Gampo, d’où il tire son nom. Ses disciples fondent les quatre grandes branches de l’école Kagyü, dont celle des Karmapas, toujours vivante aujourd’hui.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ziya_G%C3%B6kalp" title=" Wikipedia"&gt;Ziya GÖKALP&lt;/a&gt; est un sociologue, écrivain et poète turc, le principal théoricien du nationalisme turc. Né à Çermik, près de Diyarbakır, dans une famille de lettrés, il étudie à Istanbul, où il est arrêté en 1898 pour ses liens avec les opposants au sultan. Après la révolution jeune-turque de 1908, il entre au comité central du &lt;a href="https://fr.wikipedia.org/wiki/Comit%C3%A9_union_et_progr%C3%A8s" title=" Wikipedia"&gt;Comité union et progrès&lt;/a&gt;, le parti au pouvoir, et adopte le nom de Gökalp, « héros du ciel ». Il enseigne la sociologie à Salonique, puis à l’université d’Istanbul de 1913 à 1919.&lt;/p&gt; &lt;p&gt;Lecteur d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mile_Durkheim" title=" Wikipedia"&gt;Émile Durkheim&lt;/a&gt;, dont il introduit la sociologie en Turquie, il distingue la culture, propre à chaque nation, faite de sa langue, de ses mœurs et de ses valeurs, et la civilisation, internationale, faite des sciences et des techniques que les peuples se transmettent. Les Turcs peuvent donc emprunter à l’Europe sa civilisation tout en gardant leur culture. D’où sa formule : « Se turquiser, s’islamiser, se moderniser. » Il définit la nation par la langue et la culture, et non par la race.&lt;/p&gt; &lt;p&gt;Après la défaite de 1918, il est arrêté par les Britanniques et exilé à Malte. Ses idées ont profondément inspiré &lt;a href="https://fr.wikipedia.org/wiki/Mustafa_Kemal_Atat%C3%BCrk" title=" Wikipedia"&gt;Mustafa Kemal Atatürk&lt;/a&gt; et la république fondée en 1923 : l’usage de la langue turque, la séparation de la religion et de l’État, la modernisation de l’éducation. Elles restent aussi discutées, car le nationalisme qu’il a nourri s’est accompagné, dans les dernières années de l’Empire ottoman, de la persécution des minorités. Il meurt à Istanbul en 1924.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gampopa-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gokalp-mini.webp</t>
         </is>
       </c>
       <c r="J276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tibétaine</t>
+          <t xml:space="preserve">Turque</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; ethique</t>
+          <t xml:space="preserve">politique</t>
         </is>
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vajrayana</t>
+          <t xml:space="preserve">Positivisme</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">médecin devenu moine, disciple de Milarépa, fondateur de l’école Kagyü du bouddhisme tibétain.</t>
+          <t xml:space="preserve">sociologue et poète turc, théoricien du nationalisme turc, inspirateur des réformes d’Atatürk.</t>
         </is>
       </c>
       <c r="O276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="P276" s="1">
@@ -18441,31 +18452,31 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1">
-        <v>1876</v>
+        <v>1909</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924</t>
+          <t xml:space="preserve">1975</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876 – 1924</t>
+          <t xml:space="preserve">1909 – 1975</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ziya GÖKALP</t>
+          <t xml:space="preserve">Nurettin TOPÇU</t>
         </is>
       </c>
       <c r="E277" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ziya_G%C3%B6kalp" title=" Wikipedia"&gt;Ziya GÖKALP&lt;/a&gt; est un sociologue, écrivain et poète turc, le principal théoricien du nationalisme turc. Né à Çermik, près de Diyarbakır, dans une famille de lettrés, il étudie à Istanbul, où il est arrêté en 1898 pour ses liens avec les opposants au sultan. Après la révolution jeune-turque de 1908, il entre au comité central du &lt;a href="https://fr.wikipedia.org/wiki/Comit%C3%A9_union_et_progr%C3%A8s" title=" Wikipedia"&gt;Comité union et progrès&lt;/a&gt;, le parti au pouvoir, et adopte le nom de Gökalp, « héros du ciel ». Il enseigne la sociologie à Salonique, puis à l’université d’Istanbul de 1913 à 1919.&lt;/p&gt; &lt;p&gt;Lecteur d’&lt;a href="https://fr.wikipedia.org/wiki/%C3%89mile_Durkheim" title=" Wikipedia"&gt;Émile Durkheim&lt;/a&gt;, dont il introduit la sociologie en Turquie, il distingue la culture, propre à chaque nation, faite de sa langue, de ses mœurs et de ses valeurs, et la civilisation, internationale, faite des sciences et des techniques que les peuples se transmettent. Les Turcs peuvent donc emprunter à l’Europe sa civilisation tout en gardant leur culture. D’où sa formule : « Se turquiser, s’islamiser, se moderniser. » Il définit la nation par la langue et la culture, et non par la race.&lt;/p&gt; &lt;p&gt;Après la défaite de 1918, il est arrêté par les Britanniques et exilé à Malte. Ses idées ont profondément inspiré &lt;a href="https://fr.wikipedia.org/wiki/Mustafa_Kemal_Atat%C3%BCrk" title=" Wikipedia"&gt;Mustafa Kemal Atatürk&lt;/a&gt; et la république fondée en 1923 : l’usage de la langue turque, la séparation de la religion et de l’État, la modernisation de l’éducation. Elles restent aussi discutées, car le nationalisme qu’il a nourri s’est accompagné, dans les dernières années de l’Empire ottoman, de la persécution des minorités. Il meurt à Istanbul en 1924.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://tr.wikipedia.org/wiki/Nurettin_Top%C3%A7u" title=" Wikipedia (tr)"&gt;Nurettin TOPÇU&lt;/a&gt; est un philosophe, écrivain et enseignant turc, l’une des grandes figures de la pensée conservatrice et spirituelle de la Turquie républicaine. Né à Istanbul dans une famille originaire d’Erzurum, il obtient en 1928 une bourse pour étudier en France. Il suit des cours à Aix-en-Provence, où il découvre la philosophie de Maurice Blondel, avec qui il correspond, puis étudie la philosophie à Strasbourg et y rencontre l’historien du soufisme &lt;a href="https://fr.wikipedia.org/wiki/Louis_Massignon" title=" Wikipedia"&gt;Louis Massignon&lt;/a&gt;, à qui il donne des leçons de turc.&lt;/p&gt; &lt;p&gt;En 1934, il soutient à la Sorbonne une thèse intitulée &lt;em&gt;Conformisme et révolte&lt;/em&gt;, publiée la même année à Paris : il est le premier Turc à y obtenir un doctorat de philosophie. Il y oppose le conformisme, qui soumet l’individu aux habitudes et aux pouvoirs de la société, à la « révolte » morale, par laquelle la personne s’arrache à ce qui l’aliène pour répondre à une exigence intérieure. Inspirée de Blondel, cette philosophie de l’action voit dans l’acte libre et responsable le lieu où l’homme rencontre l’absolu.&lt;/p&gt; &lt;p&gt;Rentré en Turquie, il enseigne la philosophie dans les lycées d’Istanbul pendant plus de trente ans et fonde en 1939 la revue &lt;em&gt;Hareket&lt;/em&gt; (« Mouvement »). Il défend un humanisme spirituel enraciné dans l’Anatolie, dans la mystique musulmane et dans la justice sociale, et critique à la fois le matérialisme, le capitalisme et un nationalisme sans âme. Il meurt à Istanbul en 1975. Ses œuvres complètes, rééditées depuis, continuent d’influencer la pensée turque contemporaine.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/gokalp-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/topcu-mini.webp</t>
         </is>
       </c>
       <c r="J277" s="1" t="inlineStr">
@@ -18475,17 +18486,17 @@
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique</t>
+          <t xml:space="preserve">ethique ; metaphysique</t>
         </is>
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme</t>
+          <t xml:space="preserve">Spiritualisme ; Soufisme</t>
         </is>
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sociologue et poète turc, théoricien du nationalisme turc, inspirateur des réformes d’Atatürk.</t>
+          <t xml:space="preserve">philosophe turc, penseur de la « morale de la révolte » et d’un humanisme spirituel nourri de Blondel et du soufisme.</t>
         </is>
       </c>
       <c r="O277" s="1" t="inlineStr">
@@ -18499,56 +18510,61 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1">
-        <v>1909</v>
+        <v>538</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975</t>
+          <t xml:space="preserve">597</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909 – 1975</t>
+          <t xml:space="preserve">538 – 597</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nurettin TOPÇU</t>
+          <t xml:space="preserve">ZHIYI</t>
         </is>
       </c>
       <c r="E278" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://tr.wikipedia.org/wiki/Nurettin_Top%C3%A7u" title=" Wikipedia (tr)"&gt;Nurettin TOPÇU&lt;/a&gt; est un philosophe, écrivain et enseignant turc, l’une des grandes figures de la pensée conservatrice et spirituelle de la Turquie républicaine. Né à Istanbul dans une famille originaire d’Erzurum, il obtient en 1928 une bourse pour étudier en France. Il suit des cours à Aix-en-Provence, où il découvre la philosophie de Maurice Blondel, avec qui il correspond, puis étudie la philosophie à Strasbourg et y rencontre l’historien du soufisme &lt;a href="https://fr.wikipedia.org/wiki/Louis_Massignon" title=" Wikipedia"&gt;Louis Massignon&lt;/a&gt;, à qui il donne des leçons de turc.&lt;/p&gt; &lt;p&gt;En 1934, il soutient à la Sorbonne une thèse intitulée &lt;em&gt;Conformisme et révolte&lt;/em&gt;, publiée la même année à Paris : il est le premier Turc à y obtenir un doctorat de philosophie. Il y oppose le conformisme, qui soumet l’individu aux habitudes et aux pouvoirs de la société, à la « révolte » morale, par laquelle la personne s’arrache à ce qui l’aliène pour répondre à une exigence intérieure. Inspirée de Blondel, cette philosophie de l’action voit dans l’acte libre et responsable le lieu où l’homme rencontre l’absolu.&lt;/p&gt; &lt;p&gt;Rentré en Turquie, il enseigne la philosophie dans les lycées d’Istanbul pendant plus de trente ans et fonde en 1939 la revue &lt;em&gt;Hareket&lt;/em&gt; (« Mouvement »). Il défend un humanisme spirituel enraciné dans l’Anatolie, dans la mystique musulmane et dans la justice sociale, et critique à la fois le matérialisme, le capitalisme et un nationalisme sans âme. Il meurt à Istanbul en 1975. Ses œuvres complètes, rééditées depuis, continuent d’influencer la pensée turque contemporaine.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zhiyi" title=" Wikipedia"&gt;ZHIYI&lt;/a&gt; est un moine bouddhiste chinois, véritable fondateur de l’école &lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Tiantai&lt;/a&gt;, la première grande école du bouddhisme proprement chinois. Né dans une famille de fonctionnaires du Hubei, il perd ses parents dans les guerres qui déchirent la Chine du Sud et entre en religion vers dix-huit ans. Disciple du maître Huisi, il enseigne à la cour des Chen à Nankin, puis se retire en 575 dans les monts Tiantai, qui donneront leur nom à son école. L’empereur Sui lui décerne le titre de « Maître de sagesse ».&lt;/p&gt; &lt;p&gt;Face à l’immense masse de textes venus de l’Inde, souvent contradictoires, il propose un grand classement des enseignements du Bouddha, ordonnés selon les étapes de sa prédication et les capacités de ses auditeurs : tous sont vrais, mais à des degrés différents, et tous culminent dans le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sûtra du Lotus&lt;/em&gt;&lt;/a&gt;, qui affirme que chaque être peut devenir bouddha. Il enseigne aussi les « trois vérités » : toute chose est vide, existe de façon provisoire et se tient au milieu entre ces deux aspects, qui ne font qu’un.&lt;/p&gt; &lt;p&gt;Sa formule la plus célèbre, « trois mille mondes en un instant de pensée », signifie que la totalité du réel, des enfers jusqu’à l’éveil, est présente dans chaque moment de conscience. Dans &lt;em&gt;La Grande Concentration et contemplation&lt;/em&gt;, il unit la méditation qui apaise l’esprit et celle qui voit clair, et refuse de séparer l’étude et la pratique. Son école, transmise au Japon par &lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D" title=" Wikipedia"&gt;Saichō&lt;/a&gt; sous le nom de Tendai, a nourri presque tout le bouddhisme japonais : Hōnen, Shinran et Nichiren furent tous formés dans ses monastères du mont Hiei.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/topcu-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/zhiyi-mini.webp</t>
         </is>
       </c>
       <c r="J278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turque</t>
+          <t xml:space="preserve">Chinoise</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; metaphysique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Soufisme</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Tiantai</t>
         </is>
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe turc, penseur de la « morale de la révolte » et d’un humanisme spirituel nourri de Blondel et du soufisme.</t>
+          <t xml:space="preserve">moine chinois, fondateur de l’école bouddhiste Tiantai, qui fit du Sûtra du Lotus le sommet de l’enseignement.</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="O278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
       <c r="P278" s="1">
@@ -18557,31 +18573,31 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1">
-        <v>538</v>
+        <v>638</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t xml:space="preserve">597</t>
+          <t xml:space="preserve">713</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538 – 597</t>
+          <t xml:space="preserve">638 – 713</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZHIYI</t>
+          <t xml:space="preserve">HUINENG</t>
         </is>
       </c>
       <c r="E279" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zhiyi" title=" Wikipedia"&gt;ZHIYI&lt;/a&gt; est un moine bouddhiste chinois, véritable fondateur de l’école &lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Tiantai&lt;/a&gt;, la première grande école du bouddhisme proprement chinois. Né dans une famille de fonctionnaires du Hubei, il perd ses parents dans les guerres qui déchirent la Chine du Sud et entre en religion vers dix-huit ans. Disciple du maître Huisi, il enseigne à la cour des Chen à Nankin, puis se retire en 575 dans les monts Tiantai, qui donneront leur nom à son école. L’empereur Sui lui décerne le titre de « Maître de sagesse ».&lt;/p&gt; &lt;p&gt;Face à l’immense masse de textes venus de l’Inde, souvent contradictoires, il propose un grand classement des enseignements du Bouddha, ordonnés selon les étapes de sa prédication et les capacités de ses auditeurs : tous sont vrais, mais à des degrés différents, et tous culminent dans le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sûtra du Lotus&lt;/em&gt;&lt;/a&gt;, qui affirme que chaque être peut devenir bouddha. Il enseigne aussi les « trois vérités » : toute chose est vide, existe de façon provisoire et se tient au milieu entre ces deux aspects, qui ne font qu’un.&lt;/p&gt; &lt;p&gt;Sa formule la plus célèbre, « trois mille mondes en un instant de pensée », signifie que la totalité du réel, des enfers jusqu’à l’éveil, est présente dans chaque moment de conscience. Dans &lt;em&gt;La Grande Concentration et contemplation&lt;/em&gt;, il unit la méditation qui apaise l’esprit et celle qui voit clair, et refuse de séparer l’étude et la pratique. Son école, transmise au Japon par &lt;a href="https://fr.wikipedia.org/wiki/Saich%C5%8D" title=" Wikipedia"&gt;Saichō&lt;/a&gt; sous le nom de Tendai, a nourri presque tout le bouddhisme japonais : Hōnen, Shinran et Nichiren furent tous formés dans ses monastères du mont Hiei.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huineng" title=" Wikipedia"&gt;HUINENG&lt;/a&gt; est le sixième patriarche du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A1n_%28bouddhisme%29" title=" Wikipedia"&gt;chan&lt;/a&gt;, l’ancêtre du zen, et l’une des figures les plus célèbres de la spiritualité chinoise. Ce que l’on sait de lui vient surtout du &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_de_l%E2%80%99Estrade" title=" Wikipedia"&gt;&lt;em&gt;Sûtra de l’Estrade&lt;/em&gt;&lt;/a&gt;, son enseignement recueilli par ses disciples. Selon ce récit, il naît dans le sud de la Chine dans une famille pauvre et vend du bois pour nourrir sa mère. Illettré, il entend un jour réciter le &lt;em&gt;Sûtra du Diamant&lt;/em&gt; et s’éveille aussitôt. Il part alors pour le monastère du cinquième patriarche, Hongren, où on l’emploie à piler le riz.&lt;/p&gt; &lt;p&gt;Pour choisir son successeur, Hongren demande à ses disciples un poème. Le plus savant écrit que l’esprit est comme un miroir qu’il faut sans cesse épousseter. Huineng fait écrire à côté : « L’éveil n’est pas un arbre, le clair miroir n’a pas de support ; fondamentalement, il n’y a pas une chose : où la poussière pourrait-elle se poser ? » Hongren lui transmet en secret la robe et le bol du patriarcat et lui conseille de fuir. Huineng vit caché pendant quinze ans, puis enseigne dans le sud.&lt;/p&gt; &lt;p&gt;Son enseignement est celui de l’« éveil subit » : la nature de bouddha est déjà présente en chacun, et il ne s’agit pas de la conquérir par degrés, mais de la voir d’un coup, en cessant de s’attacher aux pensées. Deux moines se disputant pour savoir si c’est le vent ou le drapeau qui bouge, il leur répond : « Ni le vent ni le drapeau : c’est votre esprit qui bouge. » Toutes les écoles du chan et du zen qui ont survécu, en Chine, en Corée, au Japon et au Vietnam, se réclament de lui.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/zhiyi-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/huineng-mini.webp</t>
         </is>
       </c>
       <c r="J279" s="1" t="inlineStr">
@@ -18591,17 +18607,17 @@
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
         </is>
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana ; Tiantai</t>
+          <t xml:space="preserve">Bouddhisme Zen</t>
         </is>
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">moine chinois, fondateur de l’école bouddhiste Tiantai, qui fit du Sûtra du Lotus le sommet de l’enseignement.</t>
+          <t xml:space="preserve">sixième patriarche du bouddhisme chan, maître de l’éveil subit, dont descendent toutes les écoles zen.</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -18615,99 +18631,94 @@
         </is>
       </c>
       <c r="P279" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t xml:space="preserve">713</t>
+          <t xml:space="preserve">763</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638 – 713</t>
+          <t xml:space="preserve">vers 685 – vers 763</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUINENG</t>
+          <t xml:space="preserve">SHANTIDEVA</t>
         </is>
       </c>
       <c r="E280" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huineng" title=" Wikipedia"&gt;HUINENG&lt;/a&gt; est le sixième patriarche du bouddhisme &lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A1n_%28bouddhisme%29" title=" Wikipedia"&gt;chan&lt;/a&gt;, l’ancêtre du zen, et l’une des figures les plus célèbres de la spiritualité chinoise. Ce que l’on sait de lui vient surtout du &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_de_l%E2%80%99Estrade" title=" Wikipedia"&gt;&lt;em&gt;Sûtra de l’Estrade&lt;/em&gt;&lt;/a&gt;, son enseignement recueilli par ses disciples. Selon ce récit, il naît dans le sud de la Chine dans une famille pauvre et vend du bois pour nourrir sa mère. Illettré, il entend un jour réciter le &lt;em&gt;Sûtra du Diamant&lt;/em&gt; et s’éveille aussitôt. Il part alors pour le monastère du cinquième patriarche, Hongren, où on l’emploie à piler le riz.&lt;/p&gt; &lt;p&gt;Pour choisir son successeur, Hongren demande à ses disciples un poème. Le plus savant écrit que l’esprit est comme un miroir qu’il faut sans cesse épousseter. Huineng fait écrire à côté : « L’éveil n’est pas un arbre, le clair miroir n’a pas de support ; fondamentalement, il n’y a pas une chose : où la poussière pourrait-elle se poser ? » Hongren lui transmet en secret la robe et le bol du patriarcat et lui conseille de fuir. Huineng vit caché pendant quinze ans, puis enseigne dans le sud.&lt;/p&gt; &lt;p&gt;Son enseignement est celui de l’« éveil subit » : la nature de bouddha est déjà présente en chacun, et il ne s’agit pas de la conquérir par degrés, mais de la voir d’un coup, en cessant de s’attacher aux pensées. Deux moines se disputant pour savoir si c’est le vent ou le drapeau qui bouge, il leur répond : « Ni le vent ni le drapeau : c’est votre esprit qui bouge. » Toutes les écoles du chan et du zen qui ont survécu, en Chine, en Corée, au Japon et au Vietnam, se réclament de lui.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shantideva" title=" Wikipedia"&gt;SHANTIDEVA&lt;/a&gt; est un moine et poète bouddhiste indien, auteur de l’un des textes les plus aimés du bouddhisme : le &lt;a href="https://fr.wikipedia.org/wiki/Bodhicary%C4%81vat%C4%81ra" title=" Wikipedia"&gt;&lt;em&gt;Bodhicaryâvatâra&lt;/em&gt;&lt;/a&gt;, ou &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Selon la tradition, il est le fils d’un roi du Gujarat et renonce au trône la veille de son couronnement. Il devient moine à &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A2land%C3%A2" title=" Wikipedia"&gt;Nâlandâ&lt;/a&gt;, la grande université monastique de l’Inde, où les autres moines le surnomment avec mépris « Bhusuku », celui qui ne sait que manger, dormir et se promener.&lt;/p&gt; &lt;p&gt;Invités à le ridiculiser en le faisant parler devant tous, ils l’entendent réciter un poème inconnu d’une beauté saisissante : &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Ce texte en dix chapitres décrit le chemin du bodhisattva, celui qui fait le vœu d’atteindre l’éveil pour le bien de tous les êtres. Il y enseigne la patience face à la colère, qui détruit en un instant le bien accumulé, et l’« échange de soi et d’autrui » : toute la souffrance du monde vient de vouloir son propre bonheur, tout le bonheur du monde vient de vouloir celui des autres.&lt;/p&gt; &lt;p&gt;Le neuvième chapitre expose la philosophie du &lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Madhyamaka&lt;/a&gt; : aucune chose, ni le moi, n’existe par elle-même. Shantideva est aussi l’auteur d’un &lt;em&gt;Recueil des enseignements&lt;/em&gt;, qui cite de nombreux sûtras aujourd’hui perdus. Traduit très tôt en tibétain et commenté par des générations de maîtres, son poème est au cœur du bouddhisme tibétain, et le dalaï-lama cite souvent sa prière : « Aussi longtemps que durera l’espace, aussi longtemps que vivront les êtres, puissé-je moi aussi demeurer pour dissiper la souffrance du monde. »&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/huineng-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/shantideva-mini.webp</t>
         </is>
       </c>
       <c r="J280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chinoise</t>
+          <t xml:space="preserve">Indienne</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; metaphysique</t>
+          <t xml:space="preserve">ethique ; spiritualite</t>
         </is>
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen</t>
+          <t xml:space="preserve">Bouddhisme Mahayana ; Madhyamaka</t>
         </is>
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixième patriarche du bouddhisme chan, maître de l’éveil subit, dont descendent toutes les écoles zen.</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr">
+          <t xml:space="preserve">moine et poète indien, auteur de La Marche vers l’éveil, grand texte de la compassion bouddhiste.</t>
+        </is>
+      </c>
+      <c r="O280" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">inde</t>
         </is>
       </c>
-      <c r="O280" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
       <c r="P280" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1">
-        <v>685</v>
+        <v>1469</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t xml:space="preserve">763</t>
+          <t xml:space="preserve">1539</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 685 – vers 763</t>
+          <t xml:space="preserve">1469 – 1539</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHANTIDEVA</t>
+          <t xml:space="preserve">GURU NANAK</t>
         </is>
       </c>
       <c r="E281" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shantideva" title=" Wikipedia"&gt;SHANTIDEVA&lt;/a&gt; est un moine et poète bouddhiste indien, auteur de l’un des textes les plus aimés du bouddhisme : le &lt;a href="https://fr.wikipedia.org/wiki/Bodhicary%C4%81vat%C4%81ra" title=" Wikipedia"&gt;&lt;em&gt;Bodhicaryâvatâra&lt;/em&gt;&lt;/a&gt;, ou &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Selon la tradition, il est le fils d’un roi du Gujarat et renonce au trône la veille de son couronnement. Il devient moine à &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A2land%C3%A2" title=" Wikipedia"&gt;Nâlandâ&lt;/a&gt;, la grande université monastique de l’Inde, où les autres moines le surnomment avec mépris « Bhusuku », celui qui ne sait que manger, dormir et se promener.&lt;/p&gt; &lt;p&gt;Invités à le ridiculiser en le faisant parler devant tous, ils l’entendent réciter un poème inconnu d’une beauté saisissante : &lt;em&gt;La Marche vers l’éveil&lt;/em&gt;. Ce texte en dix chapitres décrit le chemin du bodhisattva, celui qui fait le vœu d’atteindre l’éveil pour le bien de tous les êtres. Il y enseigne la patience face à la colère, qui détruit en un instant le bien accumulé, et l’« échange de soi et d’autrui » : toute la souffrance du monde vient de vouloir son propre bonheur, tout le bonheur du monde vient de vouloir celui des autres.&lt;/p&gt; &lt;p&gt;Le neuvième chapitre expose la philosophie du &lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Madhyamaka&lt;/a&gt; : aucune chose, ni le moi, n’existe par elle-même. Shantideva est aussi l’auteur d’un &lt;em&gt;Recueil des enseignements&lt;/em&gt;, qui cite de nombreux sûtras aujourd’hui perdus. Traduit très tôt en tibétain et commenté par des générations de maîtres, son poème est au cœur du bouddhisme tibétain, et le dalaï-lama cite souvent sa prière : « Aussi longtemps que durera l’espace, aussi longtemps que vivront les êtres, puissé-je moi aussi demeurer pour dissiper la souffrance du monde. »&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guru_Nanak" title=" Wikipedia"&gt;GURU NANAK&lt;/a&gt; est un mystique et poète indien, fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Sikhisme" title=" Wikipedia"&gt;sikhisme&lt;/a&gt; et premier des dix gurus de cette religion. Né en 1469 à Talwandi, au Pendjab, aujourd’hui au Pakistan, dans une famille lettrée, il apprend le sanskrit et le persan, et fréquente dès l’enfance les ascètes hindous et les soufis musulmans qui parcourent la région. Devenu intendant au service d’un gouverneur, il disparaît, selon la tradition, trois jours dans une rivière et en revient en déclarant : « Il n’y a ni hindou ni musulman. »&lt;/p&gt; &lt;p&gt;Il passe ensuite de longues années à voyager à travers l’Inde et, selon ses biographies, jusqu’à La Mecque et Bagdad, chantant ses hymnes accompagné d’un musicien musulman. Son message tient en une affirmation : Dieu est un, sans forme, présent en toute chose, et on l’atteint non par les rites, les pèlerinages ou l’ascèse, mais par l’amour et la méditation de son Nom. Il critique les castes, les idoles et le formalisme des religieux, hindous comme musulmans, et affirme la dignité des femmes.&lt;/p&gt; &lt;p&gt;À la fin de sa vie, il fonde à Kartarpur une communauté où l’on vit de son travail. Il y résume la vie juste en trois préceptes : se souvenir de Dieu, gagner honnêtement sa vie et partager avec les autres. Il institue la cuisine commune, le &lt;a href="https://fr.wikipedia.org/wiki/Langar" title=" Wikipedia"&gt;&lt;em&gt;langar&lt;/em&gt;&lt;/a&gt;, où tous mangent ensemble assis au même rang, quelle que soit leur caste, pratique toujours vivante dans les temples sikhs. Ses hymnes, réunis dans le &lt;a href="https://fr.wikipedia.org/wiki/Guru_Granth_Sahib" title=" Wikipedia"&gt;&lt;em&gt;Guru Granth Sahib&lt;/em&gt;&lt;/a&gt;, le livre saint des sikhs, s’ouvrent sur les mots &lt;em&gt;Ik Onkar&lt;/em&gt; : « Il n’y a qu’un Dieu ».&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/shantideva-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gurunanak-mini.webp</t>
         </is>
       </c>
       <c r="J281" s="1" t="inlineStr">
@@ -18717,17 +18728,17 @@
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; spiritualite</t>
+          <t xml:space="preserve">spiritualite ; ethique</t>
         </is>
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana ; Madhyamaka</t>
+          <t xml:space="preserve">Sikhisme</t>
         </is>
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">moine et poète indien, auteur de La Marche vers l’éveil, grand texte de la compassion bouddhiste.</t>
+          <t xml:space="preserve">fondateur du sikhisme, mystique et poète du Pendjab, qui refusa les divisions entre religions et entre castes.</t>
         </is>
       </c>
       <c r="O281" s="1" t="inlineStr">
@@ -18736,36 +18747,36 @@
         </is>
       </c>
       <c r="P281" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1">
-        <v>1469</v>
+        <v>480</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539</t>
+          <t xml:space="preserve">540</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469 – 1539</t>
+          <t xml:space="preserve">vers 480 – vers 540</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GURU NANAK</t>
+          <t xml:space="preserve">DIGNAGA</t>
         </is>
       </c>
       <c r="E282" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guru_Nanak" title=" Wikipedia"&gt;GURU NANAK&lt;/a&gt; est un mystique et poète indien, fondateur du &lt;a href="https://fr.wikipedia.org/wiki/Sikhisme" title=" Wikipedia"&gt;sikhisme&lt;/a&gt; et premier des dix gurus de cette religion. Né en 1469 à Talwandi, au Pendjab, aujourd’hui au Pakistan, dans une famille lettrée, il apprend le sanskrit et le persan, et fréquente dès l’enfance